--- a/jogos_2026-08-23.xlsx
+++ b/jogos_2026-08-23.xlsx
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G16">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G20">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>6.07</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="O37">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="P37">
-        <v>6.07</v>
+        <v>0</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G59">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G60">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G133">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G134">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G135">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G136">
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G197">
@@ -32420,13 +32420,13 @@
         </is>
       </c>
       <c r="N197">
-        <v>2.13</v>
+        <v>3.44</v>
       </c>
       <c r="O197">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="P197">
-        <v>3.55</v>
+        <v>2.18</v>
       </c>
       <c r="Q197">
         <v>0</v>
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G198">
@@ -32583,13 +32583,13 @@
         </is>
       </c>
       <c r="N198">
+        <v>2.13</v>
+      </c>
+      <c r="O198">
         <v>3.44</v>
       </c>
-      <c r="O198">
-        <v>3.42</v>
-      </c>
       <c r="P198">
-        <v>2.18</v>
+        <v>3.55</v>
       </c>
       <c r="Q198">
         <v>0</v>

--- a/jogos_2026-08-23.xlsx
+++ b/jogos_2026-08-23.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU213"/>
+  <dimension ref="A1:AU215"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G58">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G59">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G60">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Dubai United</t>
         </is>
       </c>
       <c r="G61">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G62">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Horsens</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lyngby</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O63">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P63">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -10699,22 +10699,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Horsens</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Lyngby</t>
         </is>
       </c>
       <c r="G64">
@@ -10737,17 +10737,17 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G65">
@@ -11025,22 +11025,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G66">
@@ -11063,7 +11063,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N66">
@@ -11183,12 +11183,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G67">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N67">
@@ -11334,7 +11334,7 @@
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>2026-08-23 11:30:00</t>
+          <t>2026-08-23 11:00:00</t>
         </is>
       </c>
     </row>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G68">
@@ -11514,22 +11514,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G69">
@@ -11552,7 +11552,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N69">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G70">
@@ -11840,22 +11840,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G71">
@@ -12003,7 +12003,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G72">
@@ -12161,12 +12161,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G73">
@@ -12312,7 +12312,7 @@
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>2026-08-23 11:45:00</t>
+          <t>2026-08-23 11:30:00</t>
         </is>
       </c>
     </row>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>6.02</v>
+        <v>0</v>
       </c>
       <c r="O74">
-        <v>4.49</v>
+        <v>0</v>
       </c>
       <c r="P74">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -12492,7 +12492,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>0</v>
+        <v>6.02</v>
       </c>
       <c r="O75">
-        <v>0</v>
+        <v>4.49</v>
       </c>
       <c r="P75">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q75">
         <v>0</v>
@@ -12650,12 +12650,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Unia Skierniewice</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G76">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>2026-08-23 12:00:00</t>
+          <t>2026-08-23 11:45:00</t>
         </is>
       </c>
     </row>
@@ -12818,7 +12818,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="G77">
@@ -12981,7 +12981,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G78">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G79">
@@ -13182,7 +13182,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N79">
@@ -13307,22 +13307,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G80">
@@ -13345,7 +13345,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N80">
@@ -13470,22 +13470,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G81">
@@ -13633,22 +13633,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G82">
@@ -13671,7 +13671,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N82">
@@ -13791,27 +13791,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G83">
@@ -13834,17 +13834,17 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N83">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="O83">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="P83">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q83">
         <v>0</v>
@@ -13877,10 +13877,10 @@
         <v>0</v>
       </c>
       <c r="AA83">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB83">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC83">
         <v>0</v>
@@ -13942,7 +13942,7 @@
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>2026-08-23 12:15:00</t>
+          <t>2026-08-23 12:00:00</t>
         </is>
       </c>
     </row>
@@ -13954,12 +13954,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="N84">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="O84">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q84">
         <v>0</v>
@@ -14040,10 +14040,10 @@
         <v>0</v>
       </c>
       <c r="AA84">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB84">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC84">
         <v>0</v>
@@ -14105,7 +14105,7 @@
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>2026-08-23 12:30:00</t>
+          <t>2026-08-23 12:15:00</t>
         </is>
       </c>
     </row>
@@ -14122,22 +14122,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G85">
@@ -14285,22 +14285,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G86">
@@ -14448,7 +14448,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G87">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G88">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G89">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G90">
@@ -15100,7 +15100,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Voluntari</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,13 +15142,13 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="O91">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P91">
-        <v>6.63</v>
+        <v>0</v>
       </c>
       <c r="Q91">
         <v>0</v>
@@ -15263,7 +15263,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Voluntari</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,13 +15305,13 @@
         </is>
       </c>
       <c r="N92">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O92">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P92">
-        <v>0</v>
+        <v>6.63</v>
       </c>
       <c r="Q92">
         <v>0</v>
@@ -15421,27 +15421,27 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G93">
@@ -15572,7 +15572,7 @@
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>2026-08-23 12:45:00</t>
+          <t>2026-08-23 12:30:00</t>
         </is>
       </c>
     </row>
@@ -15584,27 +15584,27 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G94">
@@ -15735,7 +15735,7 @@
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>2026-08-23 13:00:00</t>
+          <t>2026-08-23 12:45:00</t>
         </is>
       </c>
     </row>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G95">
@@ -15915,7 +15915,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G96">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G97">
@@ -16241,7 +16241,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G98">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G99">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G100">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G101">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G102">
@@ -17056,22 +17056,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G103">
@@ -17219,7 +17219,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G104">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G105">
@@ -17545,22 +17545,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G106">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G107">
@@ -17871,22 +17871,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G108">
@@ -18034,7 +18034,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G109">
@@ -18197,22 +18197,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Savoia</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Savoia</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,13 +18402,13 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="O111">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="P111">
-        <v>6.76</v>
+        <v>0</v>
       </c>
       <c r="Q111">
         <v>0</v>
@@ -18523,7 +18523,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mardin BB</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O112">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P112">
-        <v>0</v>
+        <v>6.76</v>
       </c>
       <c r="Q112">
         <v>0</v>
@@ -18686,7 +18686,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Mardin BB</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O113">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P113">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q113">
         <v>0</v>
@@ -18849,7 +18849,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N114">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O114">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P114">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q114">
         <v>0</v>
@@ -19012,7 +19012,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O115">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P115">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -19170,27 +19170,27 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,13 +19217,13 @@
         </is>
       </c>
       <c r="N116">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O116">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P116">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="Q116">
         <v>0</v>
@@ -19321,7 +19321,7 @@
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>2026-08-23 13:15:00</t>
+          <t>2026-08-23 13:00:00</t>
         </is>
       </c>
     </row>
@@ -19333,12 +19333,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G117">
@@ -19484,7 +19484,7 @@
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>2026-08-23 13:30:00</t>
+          <t>2026-08-23 13:15:00</t>
         </is>
       </c>
     </row>
@@ -19501,22 +19501,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G118">
@@ -19664,7 +19664,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="G119">
@@ -19706,13 +19706,13 @@
         </is>
       </c>
       <c r="N119">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O119">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P119">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="Q119">
         <v>0</v>
@@ -19745,10 +19745,10 @@
         <v>0</v>
       </c>
       <c r="AA119">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB119">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC119">
         <v>0</v>
@@ -19827,7 +19827,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,13 +19869,13 @@
         </is>
       </c>
       <c r="N120">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O120">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P120">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="Q120">
         <v>0</v>
@@ -19908,10 +19908,10 @@
         <v>0</v>
       </c>
       <c r="AA120">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB120">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC120">
         <v>0</v>
@@ -19990,7 +19990,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G121">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G122">
@@ -20316,7 +20316,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,13 +20358,13 @@
         </is>
       </c>
       <c r="N123">
-        <v>7.26</v>
+        <v>0</v>
       </c>
       <c r="O123">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="P123">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Q123">
         <v>0</v>
@@ -20397,10 +20397,10 @@
         <v>0</v>
       </c>
       <c r="AA123">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB123">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC123">
         <v>0</v>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G124">
@@ -20521,13 +20521,13 @@
         </is>
       </c>
       <c r="N124">
-        <v>2.41</v>
+        <v>7.26</v>
       </c>
       <c r="O124">
-        <v>3.34</v>
+        <v>4.6</v>
       </c>
       <c r="P124">
-        <v>3.34</v>
+        <v>1.51</v>
       </c>
       <c r="Q124">
         <v>0</v>
@@ -20560,10 +20560,10 @@
         <v>0</v>
       </c>
       <c r="AA124">
-        <v>2.15</v>
+        <v>1.77</v>
       </c>
       <c r="AB124">
-        <v>1.63</v>
+        <v>1.96</v>
       </c>
       <c r="AC124">
         <v>0</v>
@@ -20642,7 +20642,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,13 +20684,13 @@
         </is>
       </c>
       <c r="N125">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O125">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P125">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Q125">
         <v>0</v>
@@ -20723,10 +20723,10 @@
         <v>0</v>
       </c>
       <c r="AA125">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB125">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC125">
         <v>0</v>
@@ -20800,12 +20800,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,13 +20847,13 @@
         </is>
       </c>
       <c r="N126">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="O126">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="P126">
-        <v>4.81</v>
+        <v>0</v>
       </c>
       <c r="Q126">
         <v>0</v>
@@ -20886,10 +20886,10 @@
         <v>0</v>
       </c>
       <c r="AA126">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB126">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC126">
         <v>0</v>
@@ -20951,7 +20951,7 @@
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>2026-08-23 14:00:00</t>
+          <t>2026-08-23 13:30:00</t>
         </is>
       </c>
     </row>
@@ -20963,12 +20963,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,13 +21010,13 @@
         </is>
       </c>
       <c r="N127">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="O127">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P127">
-        <v>5.83</v>
+        <v>0</v>
       </c>
       <c r="Q127">
         <v>0</v>
@@ -21049,10 +21049,10 @@
         <v>0</v>
       </c>
       <c r="AA127">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB127">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC127">
         <v>0</v>
@@ -21114,7 +21114,7 @@
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>2026-08-23 14:00:00</t>
+          <t>2026-08-23 13:35:00</t>
         </is>
       </c>
     </row>
@@ -21131,7 +21131,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,13 +21173,13 @@
         </is>
       </c>
       <c r="N128">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O128">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P128">
-        <v>0</v>
+        <v>4.81</v>
       </c>
       <c r="Q128">
         <v>0</v>
@@ -21212,10 +21212,10 @@
         <v>0</v>
       </c>
       <c r="AA128">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB128">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC128">
         <v>0</v>
@@ -21294,7 +21294,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G129">
@@ -21336,13 +21336,13 @@
         </is>
       </c>
       <c r="N129">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O129">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P129">
-        <v>0</v>
+        <v>5.83</v>
       </c>
       <c r="Q129">
         <v>0</v>
@@ -21375,10 +21375,10 @@
         <v>0</v>
       </c>
       <c r="AA129">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB129">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC129">
         <v>0</v>
@@ -21457,7 +21457,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G130">
@@ -21620,7 +21620,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G131">
@@ -21783,7 +21783,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G132">
@@ -21946,22 +21946,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G133">
@@ -22109,22 +22109,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G134">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G135">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G136">
@@ -22598,22 +22598,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G137">
@@ -22761,22 +22761,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G138">
@@ -22924,7 +22924,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G139">
@@ -23087,7 +23087,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G140">
@@ -23245,12 +23245,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G141">
@@ -23396,7 +23396,7 @@
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>2026-08-23 14:15:00</t>
+          <t>2026-08-23 14:00:00</t>
         </is>
       </c>
     </row>
@@ -23408,12 +23408,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Sporting Hasselt</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G142">
@@ -23559,7 +23559,7 @@
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>2026-08-23 14:15:00</t>
+          <t>2026-08-23 14:00:00</t>
         </is>
       </c>
     </row>
@@ -23571,12 +23571,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G143">
@@ -23722,7 +23722,7 @@
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>2026-08-23 14:30:00</t>
+          <t>2026-08-23 14:15:00</t>
         </is>
       </c>
     </row>
@@ -23734,12 +23734,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Nassaji Mazandaran</t>
+          <t>Sporting Hasselt</t>
         </is>
       </c>
       <c r="G144">
@@ -23885,7 +23885,7 @@
       </c>
       <c r="AU144" t="inlineStr">
         <is>
-          <t>2026-08-23 14:30:00</t>
+          <t>2026-08-23 14:15:00</t>
         </is>
       </c>
     </row>
@@ -23897,12 +23897,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G145">
@@ -24048,7 +24048,7 @@
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>2026-08-23 15:00:00</t>
+          <t>2026-08-23 14:30:00</t>
         </is>
       </c>
     </row>
@@ -24060,12 +24060,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Nassaji Mazandaran</t>
         </is>
       </c>
       <c r="G146">
@@ -24103,17 +24103,17 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N146">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O146">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="P146">
-        <v>12.7</v>
+        <v>0</v>
       </c>
       <c r="Q146">
         <v>0</v>
@@ -24146,10 +24146,10 @@
         <v>0</v>
       </c>
       <c r="AA146">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB146">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC146">
         <v>0</v>
@@ -24211,7 +24211,7 @@
       </c>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>2026-08-23 15:00:00</t>
+          <t>2026-08-23 14:30:00</t>
         </is>
       </c>
     </row>
@@ -24228,7 +24228,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,13 +24270,13 @@
         </is>
       </c>
       <c r="N147">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="O147">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="P147">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q147">
         <v>0</v>
@@ -24391,22 +24391,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G148">
@@ -24429,17 +24429,17 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N148">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O148">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="P148">
-        <v>0</v>
+        <v>12.7</v>
       </c>
       <c r="Q148">
         <v>0</v>
@@ -24472,10 +24472,10 @@
         <v>0</v>
       </c>
       <c r="AA148">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB148">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC148">
         <v>0</v>
@@ -24554,7 +24554,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G149">
@@ -24596,13 +24596,13 @@
         </is>
       </c>
       <c r="N149">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O149">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P149">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q149">
         <v>0</v>
@@ -24717,22 +24717,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G150">
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G151">
@@ -25038,12 +25038,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G152">
@@ -25189,7 +25189,7 @@
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>2026-08-23 15:15:00</t>
+          <t>2026-08-23 15:00:00</t>
         </is>
       </c>
     </row>
@@ -25201,12 +25201,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G153">
@@ -25352,7 +25352,7 @@
       </c>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>2026-08-23 15:15:00</t>
+          <t>2026-08-23 15:00:00</t>
         </is>
       </c>
     </row>
@@ -25369,7 +25369,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G154">
@@ -25527,12 +25527,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G155">
@@ -25678,7 +25678,7 @@
       </c>
       <c r="AU155" t="inlineStr">
         <is>
-          <t>2026-08-23 15:30:00</t>
+          <t>2026-08-23 15:15:00</t>
         </is>
       </c>
     </row>
@@ -25690,12 +25690,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G156">
@@ -25841,7 +25841,7 @@
       </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>2026-08-23 15:30:00</t>
+          <t>2026-08-23 15:15:00</t>
         </is>
       </c>
     </row>
@@ -25858,22 +25858,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G157">
@@ -26021,22 +26021,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G158">
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G159">
@@ -26347,22 +26347,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G160">
@@ -26389,13 +26389,13 @@
         </is>
       </c>
       <c r="N160">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="O160">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P160">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Q160">
         <v>0</v>
@@ -26510,22 +26510,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G161">
@@ -26673,7 +26673,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Batman Petrolspor</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G162">
@@ -26715,13 +26715,13 @@
         </is>
       </c>
       <c r="N162">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O162">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P162">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Q162">
         <v>0</v>
@@ -26836,7 +26836,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G163">
@@ -26878,13 +26878,13 @@
         </is>
       </c>
       <c r="N163">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O163">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P163">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Q163">
         <v>0</v>
@@ -26994,12 +26994,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Batman Petrolspor</t>
         </is>
       </c>
       <c r="G164">
@@ -27041,13 +27041,13 @@
         </is>
       </c>
       <c r="N164">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="O164">
-        <v>5.59</v>
+        <v>0</v>
       </c>
       <c r="P164">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="Q164">
         <v>0</v>
@@ -27086,10 +27086,10 @@
         <v>0</v>
       </c>
       <c r="AC164">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AD164">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE164">
         <v>0</v>
@@ -27145,7 +27145,7 @@
       </c>
       <c r="AU164" t="inlineStr">
         <is>
-          <t>2026-08-23 15:45:00</t>
+          <t>2026-08-23 15:30:00</t>
         </is>
       </c>
     </row>
@@ -27157,12 +27157,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G165">
@@ -27204,13 +27204,13 @@
         </is>
       </c>
       <c r="N165">
-        <v>4.65</v>
+        <v>2.8</v>
       </c>
       <c r="O165">
-        <v>3.89</v>
+        <v>3.15</v>
       </c>
       <c r="P165">
-        <v>1.84</v>
+        <v>2.46</v>
       </c>
       <c r="Q165">
         <v>0</v>
@@ -27243,10 +27243,10 @@
         <v>0</v>
       </c>
       <c r="AA165">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB165">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC165">
         <v>0</v>
@@ -27308,7 +27308,7 @@
       </c>
       <c r="AU165" t="inlineStr">
         <is>
-          <t>2026-08-23 15:45:00</t>
+          <t>2026-08-23 15:30:00</t>
         </is>
       </c>
     </row>
@@ -27325,7 +27325,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G166">
@@ -27367,13 +27367,13 @@
         </is>
       </c>
       <c r="N166">
-        <v>1.59</v>
+        <v>1.48</v>
       </c>
       <c r="O166">
-        <v>4.5</v>
+        <v>5.59</v>
       </c>
       <c r="P166">
-        <v>6.14</v>
+        <v>6.15</v>
       </c>
       <c r="Q166">
         <v>0</v>
@@ -27406,16 +27406,16 @@
         <v>0</v>
       </c>
       <c r="AA166">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB166">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC166">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AD166">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE166">
         <v>0</v>
@@ -27483,12 +27483,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G167">
@@ -27530,13 +27530,13 @@
         </is>
       </c>
       <c r="N167">
-        <v>2.64</v>
+        <v>4.65</v>
       </c>
       <c r="O167">
-        <v>3.24</v>
+        <v>3.89</v>
       </c>
       <c r="P167">
-        <v>2.6</v>
+        <v>1.84</v>
       </c>
       <c r="Q167">
         <v>0</v>
@@ -27569,10 +27569,10 @@
         <v>0</v>
       </c>
       <c r="AA167">
-        <v>1.99</v>
+        <v>1.84</v>
       </c>
       <c r="AB167">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="AC167">
         <v>0</v>
@@ -27634,7 +27634,7 @@
       </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>2026-08-23 16:00:00</t>
+          <t>2026-08-23 15:45:00</t>
         </is>
       </c>
     </row>
@@ -27646,12 +27646,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G168">
@@ -27693,13 +27693,13 @@
         </is>
       </c>
       <c r="N168">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="O168">
-        <v>3.58</v>
+        <v>4.5</v>
       </c>
       <c r="P168">
-        <v>5.71</v>
+        <v>6.14</v>
       </c>
       <c r="Q168">
         <v>0</v>
@@ -27732,10 +27732,10 @@
         <v>0</v>
       </c>
       <c r="AA168">
-        <v>1.98</v>
+        <v>1.66</v>
       </c>
       <c r="AB168">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AC168">
         <v>0</v>
@@ -27797,7 +27797,7 @@
       </c>
       <c r="AU168" t="inlineStr">
         <is>
-          <t>2026-08-23 16:00:00</t>
+          <t>2026-08-23 15:45:00</t>
         </is>
       </c>
     </row>
@@ -27814,7 +27814,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G169">
@@ -27856,13 +27856,13 @@
         </is>
       </c>
       <c r="N169">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="O169">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P169">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q169">
         <v>0</v>
@@ -27895,10 +27895,10 @@
         <v>0</v>
       </c>
       <c r="AA169">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB169">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC169">
         <v>0</v>
@@ -27977,7 +27977,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G170">
@@ -28019,13 +28019,13 @@
         </is>
       </c>
       <c r="N170">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O170">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P170">
-        <v>0</v>
+        <v>5.71</v>
       </c>
       <c r="Q170">
         <v>0</v>
@@ -28058,10 +28058,10 @@
         <v>0</v>
       </c>
       <c r="AA170">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB170">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC170">
         <v>0</v>
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G171">
@@ -28303,22 +28303,22 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G172">
@@ -28345,13 +28345,13 @@
         </is>
       </c>
       <c r="N172">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="O172">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="P172">
-        <v>6.22</v>
+        <v>0</v>
       </c>
       <c r="Q172">
         <v>0</v>
@@ -28384,10 +28384,10 @@
         <v>0</v>
       </c>
       <c r="AA172">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB172">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC172">
         <v>0</v>
@@ -28466,22 +28466,22 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="G173">
@@ -28508,13 +28508,13 @@
         </is>
       </c>
       <c r="N173">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O173">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="P173">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Q173">
         <v>0</v>
@@ -28547,10 +28547,10 @@
         <v>0</v>
       </c>
       <c r="AA173">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB173">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC173">
         <v>0</v>
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G174">
@@ -28671,13 +28671,13 @@
         </is>
       </c>
       <c r="N174">
-        <v>1.91</v>
+        <v>1.58</v>
       </c>
       <c r="O174">
-        <v>3.58</v>
+        <v>4.07</v>
       </c>
       <c r="P174">
-        <v>4.17</v>
+        <v>6.22</v>
       </c>
       <c r="Q174">
         <v>0</v>
@@ -28710,10 +28710,10 @@
         <v>0</v>
       </c>
       <c r="AA174">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB174">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC174">
         <v>0</v>
@@ -28792,7 +28792,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,13 +28834,13 @@
         </is>
       </c>
       <c r="N175">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O175">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="P175">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q175">
         <v>0</v>
@@ -28873,10 +28873,10 @@
         <v>0</v>
       </c>
       <c r="AA175">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB175">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC175">
         <v>0</v>
@@ -28955,7 +28955,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,13 +28997,13 @@
         </is>
       </c>
       <c r="N176">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O176">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P176">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="Q176">
         <v>0</v>
@@ -29036,10 +29036,10 @@
         <v>0</v>
       </c>
       <c r="AA176">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB176">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC176">
         <v>0</v>
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G177">
@@ -29281,7 +29281,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G178">
@@ -29444,7 +29444,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G179">
@@ -29607,22 +29607,22 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G180">
@@ -29770,22 +29770,22 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="G181">
@@ -29933,22 +29933,22 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G182">
@@ -30096,7 +30096,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G183">
@@ -30259,22 +30259,22 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G184">
@@ -30301,13 +30301,13 @@
         </is>
       </c>
       <c r="N184">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O184">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P184">
-        <v>4.94</v>
+        <v>0</v>
       </c>
       <c r="Q184">
         <v>0</v>
@@ -30422,22 +30422,22 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G185">
@@ -30585,22 +30585,22 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="G186">
@@ -30627,13 +30627,13 @@
         </is>
       </c>
       <c r="N186">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O186">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P186">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="Q186">
         <v>0</v>
@@ -30743,27 +30743,27 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G187">
@@ -30894,7 +30894,7 @@
       </c>
       <c r="AU187" t="inlineStr">
         <is>
-          <t>2026-08-23 16:30:00</t>
+          <t>2026-08-23 16:00:00</t>
         </is>
       </c>
     </row>
@@ -30906,27 +30906,27 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G188">
@@ -31057,7 +31057,7 @@
       </c>
       <c r="AU188" t="inlineStr">
         <is>
-          <t>2026-08-23 16:30:00</t>
+          <t>2026-08-23 16:00:00</t>
         </is>
       </c>
     </row>
@@ -31074,7 +31074,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G189">
@@ -31232,27 +31232,27 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G190">
@@ -31383,7 +31383,7 @@
       </c>
       <c r="AU190" t="inlineStr">
         <is>
-          <t>2026-08-23 17:00:00</t>
+          <t>2026-08-23 16:30:00</t>
         </is>
       </c>
     </row>
@@ -31395,27 +31395,27 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G191">
@@ -31546,7 +31546,7 @@
       </c>
       <c r="AU191" t="inlineStr">
         <is>
-          <t>2026-08-23 17:00:00</t>
+          <t>2026-08-23 16:30:00</t>
         </is>
       </c>
     </row>
@@ -31558,12 +31558,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G192">
@@ -31709,7 +31709,7 @@
       </c>
       <c r="AU192" t="inlineStr">
         <is>
-          <t>2026-08-23 17:30:00</t>
+          <t>2026-08-23 17:00:00</t>
         </is>
       </c>
     </row>
@@ -31721,12 +31721,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G193">
@@ -31768,13 +31768,13 @@
         </is>
       </c>
       <c r="N193">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="O193">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="P193">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Q193">
         <v>0</v>
@@ -31872,7 +31872,7 @@
       </c>
       <c r="AU193" t="inlineStr">
         <is>
-          <t>2026-08-23 17:30:00</t>
+          <t>2026-08-23 17:00:00</t>
         </is>
       </c>
     </row>
@@ -31884,12 +31884,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G194">
@@ -32035,7 +32035,7 @@
       </c>
       <c r="AU194" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:00</t>
+          <t>2026-08-23 17:30:00</t>
         </is>
       </c>
     </row>
@@ -32047,12 +32047,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G195">
@@ -32094,13 +32094,13 @@
         </is>
       </c>
       <c r="N195">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="O195">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="P195">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q195">
         <v>0</v>
@@ -32198,7 +32198,7 @@
       </c>
       <c r="AU195" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:00</t>
+          <t>2026-08-23 17:30:00</t>
         </is>
       </c>
     </row>
@@ -32210,12 +32210,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G196">
@@ -32361,7 +32361,7 @@
       </c>
       <c r="AU196" t="inlineStr">
         <is>
-          <t>2026-08-23 18:15:00</t>
+          <t>2026-08-23 18:00:00</t>
         </is>
       </c>
     </row>
@@ -32373,12 +32373,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G197">
@@ -32420,13 +32420,13 @@
         </is>
       </c>
       <c r="N197">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="O197">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="P197">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q197">
         <v>0</v>
@@ -32524,7 +32524,7 @@
       </c>
       <c r="AU197" t="inlineStr">
         <is>
-          <t>2026-08-23 18:30:00</t>
+          <t>2026-08-23 18:00:00</t>
         </is>
       </c>
     </row>
@@ -32536,12 +32536,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G198">
@@ -32583,13 +32583,13 @@
         </is>
       </c>
       <c r="N198">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="O198">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P198">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="Q198">
         <v>0</v>
@@ -32687,7 +32687,7 @@
       </c>
       <c r="AU198" t="inlineStr">
         <is>
-          <t>2026-08-23 18:30:00</t>
+          <t>2026-08-23 18:15:00</t>
         </is>
       </c>
     </row>
@@ -32704,7 +32704,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G199">
@@ -32746,13 +32746,13 @@
         </is>
       </c>
       <c r="N199">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="O199">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P199">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q199">
         <v>0</v>
@@ -32867,7 +32867,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G200">
@@ -32909,13 +32909,13 @@
         </is>
       </c>
       <c r="N200">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O200">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P200">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q200">
         <v>0</v>
@@ -33030,7 +33030,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G201">
@@ -33188,12 +33188,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G202">
@@ -33339,7 +33339,7 @@
       </c>
       <c r="AU202" t="inlineStr">
         <is>
-          <t>2026-08-23 19:00:00</t>
+          <t>2026-08-23 18:30:00</t>
         </is>
       </c>
     </row>
@@ -33351,12 +33351,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -33366,12 +33366,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G203">
@@ -33398,13 +33398,13 @@
         </is>
       </c>
       <c r="N203">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="O203">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P203">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Q203">
         <v>0</v>
@@ -33502,7 +33502,7 @@
       </c>
       <c r="AU203" t="inlineStr">
         <is>
-          <t>2026-08-23 19:30:00</t>
+          <t>2026-08-23 18:30:00</t>
         </is>
       </c>
     </row>
@@ -33514,12 +33514,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G204">
@@ -33665,7 +33665,7 @@
       </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>2026-08-23 20:00:00</t>
+          <t>2026-08-23 19:00:00</t>
         </is>
       </c>
     </row>
@@ -33677,12 +33677,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -33692,12 +33692,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G205">
@@ -33724,13 +33724,13 @@
         </is>
       </c>
       <c r="N205">
-        <v>1.77</v>
+        <v>2.92</v>
       </c>
       <c r="O205">
-        <v>4.04</v>
+        <v>3.15</v>
       </c>
       <c r="P205">
-        <v>4.56</v>
+        <v>2.62</v>
       </c>
       <c r="Q205">
         <v>0</v>
@@ -33828,7 +33828,7 @@
       </c>
       <c r="AU205" t="inlineStr">
         <is>
-          <t>2026-08-23 20:00:00</t>
+          <t>2026-08-23 19:30:00</t>
         </is>
       </c>
     </row>
@@ -33840,12 +33840,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G206">
@@ -33991,7 +33991,7 @@
       </c>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>2026-08-23 20:30:00</t>
+          <t>2026-08-23 20:00:00</t>
         </is>
       </c>
     </row>
@@ -34003,12 +34003,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G207">
@@ -34050,13 +34050,13 @@
         </is>
       </c>
       <c r="N207">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O207">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="P207">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="Q207">
         <v>0</v>
@@ -34154,7 +34154,7 @@
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>2026-08-23 20:30:00</t>
+          <t>2026-08-23 20:00:00</t>
         </is>
       </c>
     </row>
@@ -34166,12 +34166,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G208">
@@ -34317,7 +34317,7 @@
       </c>
       <c r="AU208" t="inlineStr">
         <is>
-          <t>2026-08-23 21:00:00</t>
+          <t>2026-08-23 20:30:00</t>
         </is>
       </c>
     </row>
@@ -34329,12 +34329,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="G209">
@@ -34480,7 +34480,7 @@
       </c>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>2026-08-23 21:00:00</t>
+          <t>2026-08-23 20:30:00</t>
         </is>
       </c>
     </row>
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G210">
@@ -34660,22 +34660,22 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G211">
@@ -34823,7 +34823,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -34833,12 +34833,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G212">
@@ -34986,151 +34986,477 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
+          <t>Russia FNL</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Rotor Volgograd</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Neftekhimik</t>
+        </is>
+      </c>
+      <c r="G213">
+        <v>0</v>
+      </c>
+      <c r="H213">
+        <v>0</v>
+      </c>
+      <c r="I213">
+        <v>0</v>
+      </c>
+      <c r="J213">
+        <v>0</v>
+      </c>
+      <c r="K213">
+        <v>0</v>
+      </c>
+      <c r="L213">
+        <v>0</v>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N213">
+        <v>0</v>
+      </c>
+      <c r="O213">
+        <v>0</v>
+      </c>
+      <c r="P213">
+        <v>0</v>
+      </c>
+      <c r="Q213">
+        <v>0</v>
+      </c>
+      <c r="R213">
+        <v>0</v>
+      </c>
+      <c r="S213">
+        <v>0</v>
+      </c>
+      <c r="T213">
+        <v>0</v>
+      </c>
+      <c r="U213">
+        <v>0</v>
+      </c>
+      <c r="V213">
+        <v>0</v>
+      </c>
+      <c r="W213">
+        <v>0</v>
+      </c>
+      <c r="X213">
+        <v>0</v>
+      </c>
+      <c r="Y213">
+        <v>0</v>
+      </c>
+      <c r="Z213">
+        <v>0</v>
+      </c>
+      <c r="AA213">
+        <v>0</v>
+      </c>
+      <c r="AB213">
+        <v>0</v>
+      </c>
+      <c r="AC213">
+        <v>0</v>
+      </c>
+      <c r="AD213">
+        <v>0</v>
+      </c>
+      <c r="AE213">
+        <v>0</v>
+      </c>
+      <c r="AF213">
+        <v>0</v>
+      </c>
+      <c r="AG213">
+        <v>0</v>
+      </c>
+      <c r="AH213" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI213" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ213">
+        <v>0</v>
+      </c>
+      <c r="AK213">
+        <v>0</v>
+      </c>
+      <c r="AL213">
+        <v>0</v>
+      </c>
+      <c r="AM213">
+        <v>-1</v>
+      </c>
+      <c r="AN213">
+        <v>-1</v>
+      </c>
+      <c r="AO213">
+        <v>-1</v>
+      </c>
+      <c r="AP213">
+        <v>-1</v>
+      </c>
+      <c r="AQ213">
+        <v>0</v>
+      </c>
+      <c r="AR213">
+        <v>0</v>
+      </c>
+      <c r="AS213">
+        <v>0</v>
+      </c>
+      <c r="AT213">
+        <v>0</v>
+      </c>
+      <c r="AU213" t="inlineStr">
+        <is>
+          <t>2026-08-23 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>LDU Quito</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="G214">
+        <v>0</v>
+      </c>
+      <c r="H214">
+        <v>0</v>
+      </c>
+      <c r="I214">
+        <v>0</v>
+      </c>
+      <c r="J214">
+        <v>0</v>
+      </c>
+      <c r="K214">
+        <v>0</v>
+      </c>
+      <c r="L214">
+        <v>0</v>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N214">
+        <v>0</v>
+      </c>
+      <c r="O214">
+        <v>0</v>
+      </c>
+      <c r="P214">
+        <v>0</v>
+      </c>
+      <c r="Q214">
+        <v>0</v>
+      </c>
+      <c r="R214">
+        <v>0</v>
+      </c>
+      <c r="S214">
+        <v>0</v>
+      </c>
+      <c r="T214">
+        <v>0</v>
+      </c>
+      <c r="U214">
+        <v>0</v>
+      </c>
+      <c r="V214">
+        <v>0</v>
+      </c>
+      <c r="W214">
+        <v>0</v>
+      </c>
+      <c r="X214">
+        <v>0</v>
+      </c>
+      <c r="Y214">
+        <v>0</v>
+      </c>
+      <c r="Z214">
+        <v>0</v>
+      </c>
+      <c r="AA214">
+        <v>0</v>
+      </c>
+      <c r="AB214">
+        <v>0</v>
+      </c>
+      <c r="AC214">
+        <v>0</v>
+      </c>
+      <c r="AD214">
+        <v>0</v>
+      </c>
+      <c r="AE214">
+        <v>0</v>
+      </c>
+      <c r="AF214">
+        <v>0</v>
+      </c>
+      <c r="AG214">
+        <v>0</v>
+      </c>
+      <c r="AH214" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI214" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ214">
+        <v>0</v>
+      </c>
+      <c r="AK214">
+        <v>0</v>
+      </c>
+      <c r="AL214">
+        <v>0</v>
+      </c>
+      <c r="AM214">
+        <v>-1</v>
+      </c>
+      <c r="AN214">
+        <v>-1</v>
+      </c>
+      <c r="AO214">
+        <v>-1</v>
+      </c>
+      <c r="AP214">
+        <v>-1</v>
+      </c>
+      <c r="AQ214">
+        <v>0</v>
+      </c>
+      <c r="AR214">
+        <v>0</v>
+      </c>
+      <c r="AS214">
+        <v>0</v>
+      </c>
+      <c r="AT214">
+        <v>0</v>
+      </c>
+      <c r="AU214" t="inlineStr">
+        <is>
+          <t>2026-08-23 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr">
+      <c r="D215" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E213" t="inlineStr">
+      <c r="E215" t="inlineStr">
         <is>
           <t>Angel City</t>
         </is>
       </c>
-      <c r="F213" t="inlineStr">
+      <c r="F215" t="inlineStr">
         <is>
           <t>Gotham FC</t>
         </is>
       </c>
-      <c r="G213">
-        <v>0</v>
-      </c>
-      <c r="H213">
-        <v>0</v>
-      </c>
-      <c r="I213">
-        <v>0</v>
-      </c>
-      <c r="J213">
-        <v>0</v>
-      </c>
-      <c r="K213">
-        <v>0</v>
-      </c>
-      <c r="L213">
-        <v>0</v>
-      </c>
-      <c r="M213" t="inlineStr">
+      <c r="G215">
+        <v>0</v>
+      </c>
+      <c r="H215">
+        <v>0</v>
+      </c>
+      <c r="I215">
+        <v>0</v>
+      </c>
+      <c r="J215">
+        <v>0</v>
+      </c>
+      <c r="K215">
+        <v>0</v>
+      </c>
+      <c r="L215">
+        <v>0</v>
+      </c>
+      <c r="M215" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N213">
-        <v>0</v>
-      </c>
-      <c r="O213">
-        <v>0</v>
-      </c>
-      <c r="P213">
-        <v>0</v>
-      </c>
-      <c r="Q213">
-        <v>0</v>
-      </c>
-      <c r="R213">
-        <v>0</v>
-      </c>
-      <c r="S213">
-        <v>0</v>
-      </c>
-      <c r="T213">
-        <v>0</v>
-      </c>
-      <c r="U213">
-        <v>0</v>
-      </c>
-      <c r="V213">
-        <v>0</v>
-      </c>
-      <c r="W213">
-        <v>0</v>
-      </c>
-      <c r="X213">
-        <v>0</v>
-      </c>
-      <c r="Y213">
-        <v>0</v>
-      </c>
-      <c r="Z213">
-        <v>0</v>
-      </c>
-      <c r="AA213">
-        <v>0</v>
-      </c>
-      <c r="AB213">
-        <v>0</v>
-      </c>
-      <c r="AC213">
-        <v>0</v>
-      </c>
-      <c r="AD213">
-        <v>0</v>
-      </c>
-      <c r="AE213">
-        <v>0</v>
-      </c>
-      <c r="AF213">
-        <v>0</v>
-      </c>
-      <c r="AG213">
-        <v>0</v>
-      </c>
-      <c r="AH213" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI213" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ213">
-        <v>0</v>
-      </c>
-      <c r="AK213">
-        <v>0</v>
-      </c>
-      <c r="AL213">
-        <v>0</v>
-      </c>
-      <c r="AM213">
-        <v>-1</v>
-      </c>
-      <c r="AN213">
-        <v>-1</v>
-      </c>
-      <c r="AO213">
-        <v>-1</v>
-      </c>
-      <c r="AP213">
-        <v>-1</v>
-      </c>
-      <c r="AQ213">
-        <v>0</v>
-      </c>
-      <c r="AR213">
-        <v>0</v>
-      </c>
-      <c r="AS213">
-        <v>0</v>
-      </c>
-      <c r="AT213">
-        <v>0</v>
-      </c>
-      <c r="AU213" t="inlineStr">
+      <c r="N215">
+        <v>0</v>
+      </c>
+      <c r="O215">
+        <v>0</v>
+      </c>
+      <c r="P215">
+        <v>0</v>
+      </c>
+      <c r="Q215">
+        <v>0</v>
+      </c>
+      <c r="R215">
+        <v>0</v>
+      </c>
+      <c r="S215">
+        <v>0</v>
+      </c>
+      <c r="T215">
+        <v>0</v>
+      </c>
+      <c r="U215">
+        <v>0</v>
+      </c>
+      <c r="V215">
+        <v>0</v>
+      </c>
+      <c r="W215">
+        <v>0</v>
+      </c>
+      <c r="X215">
+        <v>0</v>
+      </c>
+      <c r="Y215">
+        <v>0</v>
+      </c>
+      <c r="Z215">
+        <v>0</v>
+      </c>
+      <c r="AA215">
+        <v>0</v>
+      </c>
+      <c r="AB215">
+        <v>0</v>
+      </c>
+      <c r="AC215">
+        <v>0</v>
+      </c>
+      <c r="AD215">
+        <v>0</v>
+      </c>
+      <c r="AE215">
+        <v>0</v>
+      </c>
+      <c r="AF215">
+        <v>0</v>
+      </c>
+      <c r="AG215">
+        <v>0</v>
+      </c>
+      <c r="AH215" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI215" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ215">
+        <v>0</v>
+      </c>
+      <c r="AK215">
+        <v>0</v>
+      </c>
+      <c r="AL215">
+        <v>0</v>
+      </c>
+      <c r="AM215">
+        <v>-1</v>
+      </c>
+      <c r="AN215">
+        <v>-1</v>
+      </c>
+      <c r="AO215">
+        <v>-1</v>
+      </c>
+      <c r="AP215">
+        <v>-1</v>
+      </c>
+      <c r="AQ215">
+        <v>0</v>
+      </c>
+      <c r="AR215">
+        <v>0</v>
+      </c>
+      <c r="AS215">
+        <v>0</v>
+      </c>
+      <c r="AT215">
+        <v>0</v>
+      </c>
+      <c r="AU215" t="inlineStr">
         <is>
           <t>2026-08-23 21:00:00</t>
         </is>

--- a/jogos_2026-08-23.xlsx
+++ b/jogos_2026-08-23.xlsx
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="G172">
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G173">

--- a/jogos_2026-08-23.xlsx
+++ b/jogos_2026-08-23.xlsx
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4423,10 +4423,10 @@
         <v>0</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC25">
         <v>0</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -7357,10 +7357,10 @@
         <v>0</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC43">
         <v>0</v>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -11393,13 +11393,13 @@
         </is>
       </c>
       <c r="N68">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="O68">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P68">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q68">
         <v>0</v>
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O69">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P69">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="N73">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O73">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P73">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="Q73">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA73">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB73">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC73">
         <v>0</v>
@@ -13023,13 +13023,13 @@
         </is>
       </c>
       <c r="N78">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O78">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="P78">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="Q78">
         <v>0</v>
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O87">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="O115">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="P115">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -19093,10 +19093,10 @@
         <v>0</v>
       </c>
       <c r="AA115">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB115">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC115">
         <v>0</v>
@@ -20847,13 +20847,13 @@
         </is>
       </c>
       <c r="N126">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O126">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="P126">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="Q126">
         <v>0</v>
@@ -25737,13 +25737,13 @@
         </is>
       </c>
       <c r="N156">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O156">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="P156">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q156">
         <v>0</v>
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G187">
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G188">

--- a/jogos_2026-08-23.xlsx
+++ b/jogos_2026-08-23.xlsx
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>5.72</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5075,10 +5075,10 @@
         <v>0</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC29">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5564,10 +5564,10 @@
         <v>0</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O70">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q70">
         <v>0</v>
@@ -11758,10 +11758,10 @@
         <v>0</v>
       </c>
       <c r="AA70">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB70">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC70">
         <v>0</v>
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O71">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>5.96</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O81">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -22314,13 +22314,13 @@
         </is>
       </c>
       <c r="N135">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O135">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P135">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q135">
         <v>0</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G136">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G137">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G138">
@@ -22803,13 +22803,13 @@
         </is>
       </c>
       <c r="N138">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O138">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P138">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q138">
         <v>0</v>

--- a/jogos_2026-08-23.xlsx
+++ b/jogos_2026-08-23.xlsx
@@ -6499,7 +6499,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N38">
@@ -9107,7 +9107,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N54">
@@ -31768,13 +31768,13 @@
         </is>
       </c>
       <c r="N193">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O193">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P193">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q193">
         <v>0</v>
@@ -35354,13 +35354,13 @@
         </is>
       </c>
       <c r="N215">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O215">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P215">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q215">
         <v>0</v>

--- a/jogos_2026-08-23.xlsx
+++ b/jogos_2026-08-23.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU228"/>
+  <dimension ref="A1:AU232"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11840,7 +11840,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G71">
@@ -11878,17 +11878,17 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N71">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="O71">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P71">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,13 +12045,13 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.96</v>
+        <v>4.35</v>
       </c>
       <c r="O72">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P72">
-        <v>3.45</v>
+        <v>1.63</v>
       </c>
       <c r="Q72">
         <v>0</v>
@@ -12166,22 +12166,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G73">
@@ -12204,17 +12204,17 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N73">
-        <v>1.47</v>
+        <v>1.96</v>
       </c>
       <c r="O73">
-        <v>4.55</v>
+        <v>3.5</v>
       </c>
       <c r="P73">
-        <v>5.96</v>
+        <v>3.45</v>
       </c>
       <c r="Q73">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.05</v>
+        <v>1.47</v>
       </c>
       <c r="O74">
-        <v>3.46</v>
+        <v>4.55</v>
       </c>
       <c r="P74">
-        <v>3.44</v>
+        <v>5.96</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -12410,10 +12410,10 @@
         <v>0</v>
       </c>
       <c r="AA74">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB74">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC74">
         <v>0</v>
@@ -12492,22 +12492,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>4.2</v>
+        <v>2.05</v>
       </c>
       <c r="O75">
-        <v>3.35</v>
+        <v>3.46</v>
       </c>
       <c r="P75">
-        <v>1.81</v>
+        <v>3.44</v>
       </c>
       <c r="Q75">
         <v>0</v>
@@ -12573,10 +12573,10 @@
         <v>0</v>
       </c>
       <c r="AA75">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB75">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC75">
         <v>0</v>
@@ -12655,7 +12655,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.85</v>
+        <v>4.2</v>
       </c>
       <c r="O76">
-        <v>3.78</v>
+        <v>3.35</v>
       </c>
       <c r="P76">
-        <v>4.42</v>
+        <v>1.81</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -12736,10 +12736,10 @@
         <v>0</v>
       </c>
       <c r="AA76">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB76">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC76">
         <v>0</v>
@@ -12813,12 +12813,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,13 +12860,13 @@
         </is>
       </c>
       <c r="N77">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O77">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P77">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="Q77">
         <v>0</v>
@@ -12899,10 +12899,10 @@
         <v>0</v>
       </c>
       <c r="AA77">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB77">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC77">
         <v>0</v>
@@ -12964,7 +12964,7 @@
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>2026-08-23 11:45:00</t>
+          <t>2026-08-23 11:30:00</t>
         </is>
       </c>
     </row>
@@ -12981,7 +12981,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,13 +13023,13 @@
         </is>
       </c>
       <c r="N78">
-        <v>6.02</v>
+        <v>0</v>
       </c>
       <c r="O78">
-        <v>4.49</v>
+        <v>0</v>
       </c>
       <c r="P78">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Q78">
         <v>0</v>
@@ -13144,7 +13144,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,13 +13186,13 @@
         </is>
       </c>
       <c r="N79">
-        <v>0</v>
+        <v>6.02</v>
       </c>
       <c r="O79">
-        <v>0</v>
+        <v>4.49</v>
       </c>
       <c r="P79">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q79">
         <v>0</v>
@@ -13302,12 +13302,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Unia Skierniewice</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G80">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>2026-08-23 12:00:00</t>
+          <t>2026-08-23 11:45:00</t>
         </is>
       </c>
     </row>
@@ -13470,7 +13470,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O81">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="P81">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -13633,7 +13633,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,13 +13675,13 @@
         </is>
       </c>
       <c r="N82">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O82">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="Q82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G83">
@@ -13834,7 +13834,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N83">
@@ -13959,22 +13959,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G84">
@@ -13997,17 +13997,17 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N84">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="O84">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="P84">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q84">
         <v>0</v>
@@ -14122,22 +14122,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O85">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P85">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q85">
         <v>0</v>
@@ -14285,22 +14285,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G86">
@@ -14323,7 +14323,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N86">
@@ -14443,27 +14443,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G87">
@@ -14486,17 +14486,17 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N87">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="O87">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="P87">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -14529,10 +14529,10 @@
         <v>0</v>
       </c>
       <c r="AA87">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB87">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC87">
         <v>0</v>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>2026-08-23 12:15:00</t>
+          <t>2026-08-23 12:00:00</t>
         </is>
       </c>
     </row>
@@ -14606,12 +14606,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>3.05</v>
+        <v>3.58</v>
       </c>
       <c r="O88">
-        <v>4.03</v>
+        <v>4.02</v>
       </c>
       <c r="P88">
-        <v>2.28</v>
+        <v>2.05</v>
       </c>
       <c r="Q88">
         <v>0</v>
@@ -14692,16 +14692,16 @@
         <v>0</v>
       </c>
       <c r="AA88">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB88">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC88">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD88">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE88">
         <v>0</v>
@@ -14757,7 +14757,7 @@
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>2026-08-23 12:30:00</t>
+          <t>2026-08-23 12:15:00</t>
         </is>
       </c>
     </row>
@@ -14774,22 +14774,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,13 +14816,13 @@
         </is>
       </c>
       <c r="N89">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O89">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="P89">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -14861,10 +14861,10 @@
         <v>0</v>
       </c>
       <c r="AC89">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD89">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE89">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,13 +14979,13 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="O90">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P90">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="Q90">
         <v>0</v>
@@ -15100,7 +15100,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,13 +15142,13 @@
         </is>
       </c>
       <c r="N91">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O91">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P91">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="Q91">
         <v>0</v>
@@ -15263,7 +15263,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O92">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P92">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q92">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R92">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S92">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T92">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U92">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V92">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W92">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X92">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y92">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z92">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA92">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB92">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC92">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD92">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE92">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF92">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG92">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK92">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15426,7 +15426,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>ETO</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O93">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="P93">
-        <v>0</v>
+        <v>7.22</v>
       </c>
       <c r="Q93">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R93">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S93">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T93">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U93">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V93">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W93">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X93">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y93">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z93">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA93">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB93">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AC93">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD93">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE93">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF93">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG93">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK93">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G94">
@@ -15752,7 +15752,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Voluntari</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,13 +15794,13 @@
         </is>
       </c>
       <c r="N95">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="O95">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P95">
-        <v>6.63</v>
+        <v>0</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -15915,7 +15915,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G96">
@@ -16073,27 +16073,27 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G97">
@@ -16224,7 +16224,7 @@
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>2026-08-23 12:45:00</t>
+          <t>2026-08-23 12:30:00</t>
         </is>
       </c>
     </row>
@@ -16236,12 +16236,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Voluntari</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O98">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P98">
-        <v>0</v>
+        <v>6.63</v>
       </c>
       <c r="Q98">
         <v>0</v>
@@ -16387,7 +16387,7 @@
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>2026-08-23 13:00:00</t>
+          <t>2026-08-23 12:30:00</t>
         </is>
       </c>
     </row>
@@ -16399,12 +16399,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O99">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P99">
-        <v>5.29</v>
+        <v>0</v>
       </c>
       <c r="Q99">
         <v>0</v>
@@ -16550,7 +16550,7 @@
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>2026-08-23 13:00:00</t>
+          <t>2026-08-23 12:30:00</t>
         </is>
       </c>
     </row>
@@ -16562,27 +16562,27 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G100">
@@ -16713,7 +16713,7 @@
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>2026-08-23 13:00:00</t>
+          <t>2026-08-23 12:45:00</t>
         </is>
       </c>
     </row>
@@ -16730,7 +16730,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,13 +16772,13 @@
         </is>
       </c>
       <c r="N101">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O101">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P101">
-        <v>0</v>
+        <v>5.29</v>
       </c>
       <c r="Q101">
         <v>0</v>
@@ -16893,7 +16893,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Sertanense</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G102">
@@ -17056,7 +17056,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G103">
@@ -17219,7 +17219,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Gd Nazarenos</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G104">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Sertanense</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G105">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Gd Nazarenos</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G106">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Fazendense</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>AD Nogueirense</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G107">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G108">
@@ -18034,7 +18034,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Fazendense</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>AD Nogueirense</t>
         </is>
       </c>
       <c r="G109">
@@ -18197,7 +18197,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G110">
@@ -18360,7 +18360,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G113">
@@ -18849,22 +18849,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G114">
@@ -19012,22 +19012,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G115">
@@ -19175,22 +19175,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G116">
@@ -19338,22 +19338,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G117">
@@ -19501,22 +19501,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Guarda</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G118">
@@ -19664,22 +19664,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Ovarense</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G119">
@@ -19827,7 +19827,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Ovarense</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G120">
@@ -19990,7 +19990,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G121">
@@ -20153,22 +20153,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Guarda</t>
         </is>
       </c>
       <c r="G122">
@@ -20316,22 +20316,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G123">
@@ -20479,7 +20479,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Savoia</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G124">
@@ -20642,22 +20642,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,13 +20684,13 @@
         </is>
       </c>
       <c r="N125">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="O125">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="P125">
-        <v>6.76</v>
+        <v>0</v>
       </c>
       <c r="Q125">
         <v>0</v>
@@ -20805,22 +20805,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mardin BB</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G126">
@@ -20968,7 +20968,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Savoia</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,13 +21010,13 @@
         </is>
       </c>
       <c r="N127">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O127">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P127">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q127">
         <v>0</v>
@@ -21131,7 +21131,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,13 +21173,13 @@
         </is>
       </c>
       <c r="N128">
-        <v>5.48</v>
+        <v>1.41</v>
       </c>
       <c r="O128">
-        <v>3.82</v>
+        <v>4.3</v>
       </c>
       <c r="P128">
-        <v>1.59</v>
+        <v>6.76</v>
       </c>
       <c r="Q128">
         <v>0</v>
@@ -21212,10 +21212,10 @@
         <v>0</v>
       </c>
       <c r="AA128">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB128">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC128">
         <v>0</v>
@@ -21294,7 +21294,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Mardin BB</t>
         </is>
       </c>
       <c r="G129">
@@ -21336,13 +21336,13 @@
         </is>
       </c>
       <c r="N129">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O129">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P129">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="Q129">
         <v>0</v>
@@ -21452,27 +21452,27 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G130">
@@ -21499,13 +21499,13 @@
         </is>
       </c>
       <c r="N130">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O130">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P130">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q130">
         <v>0</v>
@@ -21603,7 +21603,7 @@
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>2026-08-23 13:15:00</t>
+          <t>2026-08-23 13:00:00</t>
         </is>
       </c>
     </row>
@@ -21615,27 +21615,27 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G131">
@@ -21662,13 +21662,13 @@
         </is>
       </c>
       <c r="N131">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="O131">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="P131">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q131">
         <v>0</v>
@@ -21701,10 +21701,10 @@
         <v>0</v>
       </c>
       <c r="AA131">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB131">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC131">
         <v>0</v>
@@ -21766,7 +21766,7 @@
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>2026-08-23 13:30:00</t>
+          <t>2026-08-23 13:00:00</t>
         </is>
       </c>
     </row>
@@ -21778,12 +21778,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,13 +21825,13 @@
         </is>
       </c>
       <c r="N132">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O132">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P132">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="Q132">
         <v>0</v>
@@ -21929,7 +21929,7 @@
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>2026-08-23 13:30:00</t>
+          <t>2026-08-23 13:00:00</t>
         </is>
       </c>
     </row>
@@ -21941,27 +21941,27 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,13 +21988,13 @@
         </is>
       </c>
       <c r="N133">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O133">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P133">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="Q133">
         <v>0</v>
@@ -22027,10 +22027,10 @@
         <v>0</v>
       </c>
       <c r="AA133">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB133">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC133">
         <v>0</v>
@@ -22092,7 +22092,7 @@
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>2026-08-23 13:30:00</t>
+          <t>2026-08-23 13:15:00</t>
         </is>
       </c>
     </row>
@@ -22109,22 +22109,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G134">
@@ -22272,7 +22272,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="G135">
@@ -22435,7 +22435,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,13 +22477,13 @@
         </is>
       </c>
       <c r="N136">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O136">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P136">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="Q136">
         <v>0</v>
@@ -22516,10 +22516,10 @@
         <v>0</v>
       </c>
       <c r="AA136">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB136">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC136">
         <v>0</v>
@@ -22598,7 +22598,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,13 +22640,13 @@
         </is>
       </c>
       <c r="N137">
-        <v>7.26</v>
+        <v>0</v>
       </c>
       <c r="O137">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="P137">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Q137">
         <v>0</v>
@@ -22679,10 +22679,10 @@
         <v>0</v>
       </c>
       <c r="AA137">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB137">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC137">
         <v>0</v>
@@ -22761,7 +22761,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G138">
@@ -22803,13 +22803,13 @@
         </is>
       </c>
       <c r="N138">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="O138">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P138">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="Q138">
         <v>0</v>
@@ -22842,10 +22842,10 @@
         <v>0</v>
       </c>
       <c r="AA138">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB138">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC138">
         <v>0</v>
@@ -22924,7 +22924,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G139">
@@ -22966,13 +22966,13 @@
         </is>
       </c>
       <c r="N139">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O139">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="P139">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="Q139">
         <v>0</v>
@@ -23082,12 +23082,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G140">
@@ -23129,13 +23129,13 @@
         </is>
       </c>
       <c r="N140">
-        <v>0</v>
+        <v>7.26</v>
       </c>
       <c r="O140">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P140">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Q140">
         <v>0</v>
@@ -23168,10 +23168,10 @@
         <v>0</v>
       </c>
       <c r="AA140">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB140">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC140">
         <v>0</v>
@@ -23233,7 +23233,7 @@
       </c>
       <c r="AU140" t="inlineStr">
         <is>
-          <t>2026-08-23 13:35:00</t>
+          <t>2026-08-23 13:30:00</t>
         </is>
       </c>
     </row>
@@ -23245,12 +23245,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G141">
@@ -23292,13 +23292,13 @@
         </is>
       </c>
       <c r="N141">
-        <v>1.74</v>
+        <v>2.41</v>
       </c>
       <c r="O141">
-        <v>3.52</v>
+        <v>3.34</v>
       </c>
       <c r="P141">
-        <v>4.81</v>
+        <v>3.34</v>
       </c>
       <c r="Q141">
         <v>0</v>
@@ -23331,10 +23331,10 @@
         <v>0</v>
       </c>
       <c r="AA141">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AB141">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AC141">
         <v>0</v>
@@ -23396,7 +23396,7 @@
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>2026-08-23 14:00:00</t>
+          <t>2026-08-23 13:30:00</t>
         </is>
       </c>
     </row>
@@ -23408,12 +23408,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G142">
@@ -23455,13 +23455,13 @@
         </is>
       </c>
       <c r="N142">
-        <v>1.58</v>
+        <v>1.27</v>
       </c>
       <c r="O142">
-        <v>3.8</v>
+        <v>6.5</v>
       </c>
       <c r="P142">
-        <v>5.83</v>
+        <v>9.4</v>
       </c>
       <c r="Q142">
         <v>0</v>
@@ -23494,10 +23494,10 @@
         <v>0</v>
       </c>
       <c r="AA142">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB142">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC142">
         <v>0</v>
@@ -23559,7 +23559,7 @@
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>2026-08-23 14:00:00</t>
+          <t>2026-08-23 13:30:00</t>
         </is>
       </c>
     </row>
@@ -23571,12 +23571,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,13 +23618,13 @@
         </is>
       </c>
       <c r="N143">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O143">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="P143">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="Q143">
         <v>0</v>
@@ -23722,7 +23722,7 @@
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>2026-08-23 14:00:00</t>
+          <t>2026-08-23 13:35:00</t>
         </is>
       </c>
     </row>
@@ -23734,12 +23734,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G144">
@@ -23885,7 +23885,7 @@
       </c>
       <c r="AU144" t="inlineStr">
         <is>
-          <t>2026-08-23 14:00:00</t>
+          <t>2026-08-23 13:45:00</t>
         </is>
       </c>
     </row>
@@ -23902,7 +23902,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,13 +23944,13 @@
         </is>
       </c>
       <c r="N145">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O145">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P145">
-        <v>0</v>
+        <v>4.81</v>
       </c>
       <c r="Q145">
         <v>0</v>
@@ -23983,10 +23983,10 @@
         <v>0</v>
       </c>
       <c r="AA145">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB145">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC145">
         <v>0</v>
@@ -24065,7 +24065,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,13 +24107,13 @@
         </is>
       </c>
       <c r="N146">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O146">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P146">
-        <v>0</v>
+        <v>5.83</v>
       </c>
       <c r="Q146">
         <v>0</v>
@@ -24146,10 +24146,10 @@
         <v>0</v>
       </c>
       <c r="AA146">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB146">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC146">
         <v>0</v>
@@ -24228,7 +24228,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,13 +24270,13 @@
         </is>
       </c>
       <c r="N147">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O147">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P147">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="Q147">
         <v>0</v>
@@ -24391,22 +24391,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G148">
@@ -24433,13 +24433,13 @@
         </is>
       </c>
       <c r="N148">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O148">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P148">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q148">
         <v>0</v>
@@ -24554,22 +24554,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G149">
@@ -24717,22 +24717,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G150">
@@ -24880,22 +24880,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G151">
@@ -24922,13 +24922,13 @@
         </is>
       </c>
       <c r="N151">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O151">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P151">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q151">
         <v>0</v>
@@ -25043,22 +25043,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G152">
@@ -25085,13 +25085,13 @@
         </is>
       </c>
       <c r="N152">
-        <v>2.8</v>
+        <v>1.97</v>
       </c>
       <c r="O152">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="P152">
-        <v>2.35</v>
+        <v>3.05</v>
       </c>
       <c r="Q152">
         <v>0</v>
@@ -25124,10 +25124,10 @@
         <v>0</v>
       </c>
       <c r="AA152">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB152">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC152">
         <v>0</v>
@@ -25206,22 +25206,22 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G153">
@@ -25248,13 +25248,13 @@
         </is>
       </c>
       <c r="N153">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="O153">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P153">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -25369,22 +25369,22 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G154">
@@ -25532,22 +25532,22 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,13 +25574,13 @@
         </is>
       </c>
       <c r="N155">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O155">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P155">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q155">
         <v>0</v>
@@ -25690,12 +25690,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,13 +25737,13 @@
         </is>
       </c>
       <c r="N156">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O156">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P156">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q156">
         <v>0</v>
@@ -25776,10 +25776,10 @@
         <v>0</v>
       </c>
       <c r="AA156">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB156">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC156">
         <v>0</v>
@@ -25841,7 +25841,7 @@
       </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>2026-08-23 14:15:00</t>
+          <t>2026-08-23 14:00:00</t>
         </is>
       </c>
     </row>
@@ -25853,12 +25853,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Sporting Hasselt</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,13 +25900,13 @@
         </is>
       </c>
       <c r="N157">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="O157">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P157">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q157">
         <v>0</v>
@@ -26004,7 +26004,7 @@
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>2026-08-23 14:15:00</t>
+          <t>2026-08-23 14:00:00</t>
         </is>
       </c>
     </row>
@@ -26016,12 +26016,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G158">
@@ -26167,7 +26167,7 @@
       </c>
       <c r="AU158" t="inlineStr">
         <is>
-          <t>2026-08-23 14:30:00</t>
+          <t>2026-08-23 14:00:00</t>
         </is>
       </c>
     </row>
@@ -26179,12 +26179,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Nassaji Mazandaran</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G159">
@@ -26330,7 +26330,7 @@
       </c>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>2026-08-23 14:30:00</t>
+          <t>2026-08-23 14:00:00</t>
         </is>
       </c>
     </row>
@@ -26342,12 +26342,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G160">
@@ -26493,7 +26493,7 @@
       </c>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>2026-08-23 15:00:00</t>
+          <t>2026-08-23 14:15:00</t>
         </is>
       </c>
     </row>
@@ -26505,12 +26505,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Sporting Hasselt</t>
         </is>
       </c>
       <c r="G161">
@@ -26548,17 +26548,17 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N161">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O161">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="P161">
-        <v>12.7</v>
+        <v>0</v>
       </c>
       <c r="Q161">
         <v>0</v>
@@ -26591,10 +26591,10 @@
         <v>0</v>
       </c>
       <c r="AA161">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB161">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC161">
         <v>0</v>
@@ -26656,7 +26656,7 @@
       </c>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>2026-08-23 15:00:00</t>
+          <t>2026-08-23 14:15:00</t>
         </is>
       </c>
     </row>
@@ -26668,12 +26668,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G162">
@@ -26715,13 +26715,13 @@
         </is>
       </c>
       <c r="N162">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="O162">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="P162">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q162">
         <v>0</v>
@@ -26819,7 +26819,7 @@
       </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>2026-08-23 15:00:00</t>
+          <t>2026-08-23 14:30:00</t>
         </is>
       </c>
     </row>
@@ -26831,27 +26831,27 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Nassaji Mazandaran</t>
         </is>
       </c>
       <c r="G163">
@@ -26982,7 +26982,7 @@
       </c>
       <c r="AU163" t="inlineStr">
         <is>
-          <t>2026-08-23 15:00:00</t>
+          <t>2026-08-23 14:30:00</t>
         </is>
       </c>
     </row>
@@ -26999,7 +26999,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G164">
@@ -27162,7 +27162,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G165">
@@ -27200,17 +27200,17 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N165">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O165">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="P165">
-        <v>0</v>
+        <v>12.7</v>
       </c>
       <c r="Q165">
         <v>0</v>
@@ -27243,10 +27243,10 @@
         <v>0</v>
       </c>
       <c r="AA165">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB165">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC165">
         <v>0</v>
@@ -27325,7 +27325,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G166">
@@ -27367,13 +27367,13 @@
         </is>
       </c>
       <c r="N166">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O166">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P166">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q166">
         <v>0</v>
@@ -27483,27 +27483,27 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G167">
@@ -27530,13 +27530,13 @@
         </is>
       </c>
       <c r="N167">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="O167">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="P167">
-        <v>5.64</v>
+        <v>0</v>
       </c>
       <c r="Q167">
         <v>0</v>
@@ -27634,7 +27634,7 @@
       </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>2026-08-23 15:15:00</t>
+          <t>2026-08-23 15:00:00</t>
         </is>
       </c>
     </row>
@@ -27646,12 +27646,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G168">
@@ -27693,13 +27693,13 @@
         </is>
       </c>
       <c r="N168">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="O168">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P168">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Q168">
         <v>0</v>
@@ -27797,7 +27797,7 @@
       </c>
       <c r="AU168" t="inlineStr">
         <is>
-          <t>2026-08-23 15:15:00</t>
+          <t>2026-08-23 15:00:00</t>
         </is>
       </c>
     </row>
@@ -27809,12 +27809,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G169">
@@ -27856,13 +27856,13 @@
         </is>
       </c>
       <c r="N169">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O169">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="P169">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q169">
         <v>0</v>
@@ -27960,7 +27960,7 @@
       </c>
       <c r="AU169" t="inlineStr">
         <is>
-          <t>2026-08-23 15:15:00</t>
+          <t>2026-08-23 15:00:00</t>
         </is>
       </c>
     </row>
@@ -27972,12 +27972,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G170">
@@ -28123,7 +28123,7 @@
       </c>
       <c r="AU170" t="inlineStr">
         <is>
-          <t>2026-08-23 15:30:00</t>
+          <t>2026-08-23 15:00:00</t>
         </is>
       </c>
     </row>
@@ -28135,12 +28135,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G171">
@@ -28182,13 +28182,13 @@
         </is>
       </c>
       <c r="N171">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O171">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P171">
-        <v>0</v>
+        <v>5.64</v>
       </c>
       <c r="Q171">
         <v>0</v>
@@ -28286,7 +28286,7 @@
       </c>
       <c r="AU171" t="inlineStr">
         <is>
-          <t>2026-08-23 15:30:00</t>
+          <t>2026-08-23 15:15:00</t>
         </is>
       </c>
     </row>
@@ -28298,27 +28298,27 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G172">
@@ -28345,13 +28345,13 @@
         </is>
       </c>
       <c r="N172">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O172">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P172">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q172">
         <v>0</v>
@@ -28449,7 +28449,7 @@
       </c>
       <c r="AU172" t="inlineStr">
         <is>
-          <t>2026-08-23 15:30:00</t>
+          <t>2026-08-23 15:15:00</t>
         </is>
       </c>
     </row>
@@ -28461,27 +28461,27 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G173">
@@ -28508,13 +28508,13 @@
         </is>
       </c>
       <c r="N173">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O173">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="P173">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q173">
         <v>0</v>
@@ -28612,7 +28612,7 @@
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>2026-08-23 15:30:00</t>
+          <t>2026-08-23 15:15:00</t>
         </is>
       </c>
     </row>
@@ -28629,22 +28629,22 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G174">
@@ -28792,7 +28792,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,13 +28834,13 @@
         </is>
       </c>
       <c r="N175">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="O175">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P175">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Q175">
         <v>0</v>
@@ -28955,22 +28955,22 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G176">
@@ -29118,22 +29118,22 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Batman Petrolspor</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G177">
@@ -29281,22 +29281,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G178">
@@ -29323,13 +29323,13 @@
         </is>
       </c>
       <c r="N178">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O178">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P178">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Q178">
         <v>0</v>
@@ -29439,12 +29439,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G179">
@@ -29486,13 +29486,13 @@
         </is>
       </c>
       <c r="N179">
-        <v>1.48</v>
+        <v>2.58</v>
       </c>
       <c r="O179">
-        <v>5.59</v>
+        <v>3.1</v>
       </c>
       <c r="P179">
-        <v>6.15</v>
+        <v>2.77</v>
       </c>
       <c r="Q179">
         <v>0</v>
@@ -29531,10 +29531,10 @@
         <v>0</v>
       </c>
       <c r="AC179">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AD179">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE179">
         <v>0</v>
@@ -29590,7 +29590,7 @@
       </c>
       <c r="AU179" t="inlineStr">
         <is>
-          <t>2026-08-23 15:45:00</t>
+          <t>2026-08-23 15:30:00</t>
         </is>
       </c>
     </row>
@@ -29602,12 +29602,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -29617,12 +29617,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G180">
@@ -29649,13 +29649,13 @@
         </is>
       </c>
       <c r="N180">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="O180">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="P180">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Q180">
         <v>0</v>
@@ -29688,10 +29688,10 @@
         <v>0</v>
       </c>
       <c r="AA180">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB180">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC180">
         <v>0</v>
@@ -29753,7 +29753,7 @@
       </c>
       <c r="AU180" t="inlineStr">
         <is>
-          <t>2026-08-23 15:45:00</t>
+          <t>2026-08-23 15:30:00</t>
         </is>
       </c>
     </row>
@@ -29765,12 +29765,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Batman Petrolspor</t>
         </is>
       </c>
       <c r="G181">
@@ -29812,13 +29812,13 @@
         </is>
       </c>
       <c r="N181">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O181">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P181">
-        <v>6.14</v>
+        <v>0</v>
       </c>
       <c r="Q181">
         <v>0</v>
@@ -29851,10 +29851,10 @@
         <v>0</v>
       </c>
       <c r="AA181">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB181">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC181">
         <v>0</v>
@@ -29916,7 +29916,7 @@
       </c>
       <c r="AU181" t="inlineStr">
         <is>
-          <t>2026-08-23 15:45:00</t>
+          <t>2026-08-23 15:30:00</t>
         </is>
       </c>
     </row>
@@ -29928,12 +29928,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G182">
@@ -29975,13 +29975,13 @@
         </is>
       </c>
       <c r="N182">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="O182">
-        <v>3.24</v>
+        <v>3.15</v>
       </c>
       <c r="P182">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="Q182">
         <v>0</v>
@@ -30014,10 +30014,10 @@
         <v>0</v>
       </c>
       <c r="AA182">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB182">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC182">
         <v>0</v>
@@ -30079,7 +30079,7 @@
       </c>
       <c r="AU182" t="inlineStr">
         <is>
-          <t>2026-08-23 16:00:00</t>
+          <t>2026-08-23 15:30:00</t>
         </is>
       </c>
     </row>
@@ -30091,12 +30091,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G183">
@@ -30138,13 +30138,13 @@
         </is>
       </c>
       <c r="N183">
-        <v>1.63</v>
+        <v>1.48</v>
       </c>
       <c r="O183">
-        <v>3.58</v>
+        <v>5.59</v>
       </c>
       <c r="P183">
-        <v>5.71</v>
+        <v>6.15</v>
       </c>
       <c r="Q183">
         <v>0</v>
@@ -30177,16 +30177,16 @@
         <v>0</v>
       </c>
       <c r="AA183">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB183">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC183">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AD183">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE183">
         <v>0</v>
@@ -30242,7 +30242,7 @@
       </c>
       <c r="AU183" t="inlineStr">
         <is>
-          <t>2026-08-23 16:00:00</t>
+          <t>2026-08-23 15:45:00</t>
         </is>
       </c>
     </row>
@@ -30254,12 +30254,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -30269,12 +30269,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G184">
@@ -30301,13 +30301,13 @@
         </is>
       </c>
       <c r="N184">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="O184">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="P184">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q184">
         <v>0</v>
@@ -30340,10 +30340,10 @@
         <v>0</v>
       </c>
       <c r="AA184">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB184">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC184">
         <v>0</v>
@@ -30405,7 +30405,7 @@
       </c>
       <c r="AU184" t="inlineStr">
         <is>
-          <t>2026-08-23 16:00:00</t>
+          <t>2026-08-23 15:45:00</t>
         </is>
       </c>
     </row>
@@ -30417,12 +30417,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -30432,12 +30432,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G185">
@@ -30464,13 +30464,13 @@
         </is>
       </c>
       <c r="N185">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O185">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P185">
-        <v>0</v>
+        <v>6.14</v>
       </c>
       <c r="Q185">
         <v>0</v>
@@ -30503,10 +30503,10 @@
         <v>0</v>
       </c>
       <c r="AA185">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB185">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC185">
         <v>0</v>
@@ -30568,7 +30568,7 @@
       </c>
       <c r="AU185" t="inlineStr">
         <is>
-          <t>2026-08-23 16:00:00</t>
+          <t>2026-08-23 15:45:00</t>
         </is>
       </c>
     </row>
@@ -30585,7 +30585,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G186">
@@ -30627,13 +30627,13 @@
         </is>
       </c>
       <c r="N186">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="O186">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P186">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q186">
         <v>0</v>
@@ -30666,10 +30666,10 @@
         <v>0</v>
       </c>
       <c r="AA186">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB186">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC186">
         <v>0</v>
@@ -30748,22 +30748,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G187">
@@ -30790,13 +30790,13 @@
         </is>
       </c>
       <c r="N187">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="O187">
-        <v>4.07</v>
+        <v>3.58</v>
       </c>
       <c r="P187">
-        <v>6.22</v>
+        <v>5.71</v>
       </c>
       <c r="Q187">
         <v>0</v>
@@ -30829,10 +30829,10 @@
         <v>0</v>
       </c>
       <c r="AA187">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AB187">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AC187">
         <v>0</v>
@@ -30911,22 +30911,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G188">
@@ -30953,13 +30953,13 @@
         </is>
       </c>
       <c r="N188">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O188">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="P188">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Q188">
         <v>0</v>
@@ -30992,10 +30992,10 @@
         <v>0</v>
       </c>
       <c r="AA188">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB188">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC188">
         <v>0</v>
@@ -31074,22 +31074,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="G189">
@@ -31116,13 +31116,13 @@
         </is>
       </c>
       <c r="N189">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O189">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P189">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="Q189">
         <v>0</v>
@@ -31155,10 +31155,10 @@
         <v>0</v>
       </c>
       <c r="AA189">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB189">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC189">
         <v>0</v>
@@ -31237,22 +31237,22 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G190">
@@ -31400,7 +31400,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G191">
@@ -31442,13 +31442,13 @@
         </is>
       </c>
       <c r="N191">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O191">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="P191">
-        <v>0</v>
+        <v>6.22</v>
       </c>
       <c r="Q191">
         <v>0</v>
@@ -31481,10 +31481,10 @@
         <v>0</v>
       </c>
       <c r="AA191">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB191">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC191">
         <v>0</v>
@@ -31563,7 +31563,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G192">
@@ -31605,13 +31605,13 @@
         </is>
       </c>
       <c r="N192">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O192">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="P192">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q192">
         <v>0</v>
@@ -31644,10 +31644,10 @@
         <v>0</v>
       </c>
       <c r="AA192">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB192">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC192">
         <v>0</v>
@@ -31726,7 +31726,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G193">
@@ -31768,13 +31768,13 @@
         </is>
       </c>
       <c r="N193">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O193">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P193">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="Q193">
         <v>0</v>
@@ -31807,10 +31807,10 @@
         <v>0</v>
       </c>
       <c r="AA193">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB193">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC193">
         <v>0</v>
@@ -31889,7 +31889,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G194">
@@ -32052,22 +32052,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G195">
@@ -32215,22 +32215,22 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G196">
@@ -32378,7 +32378,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G197">
@@ -32541,22 +32541,22 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="G198">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G199">
@@ -32746,13 +32746,13 @@
         </is>
       </c>
       <c r="N199">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O199">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P199">
-        <v>4.94</v>
+        <v>0</v>
       </c>
       <c r="Q199">
         <v>0</v>
@@ -32867,22 +32867,22 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G200">
@@ -33030,7 +33030,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G201">
@@ -33188,12 +33188,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G202">
@@ -33339,7 +33339,7 @@
       </c>
       <c r="AU202" t="inlineStr">
         <is>
-          <t>2026-08-23 16:30:00</t>
+          <t>2026-08-23 16:00:00</t>
         </is>
       </c>
     </row>
@@ -33351,12 +33351,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -33366,12 +33366,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="G203">
@@ -33398,13 +33398,13 @@
         </is>
       </c>
       <c r="N203">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O203">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P203">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="Q203">
         <v>0</v>
@@ -33502,7 +33502,7 @@
       </c>
       <c r="AU203" t="inlineStr">
         <is>
-          <t>2026-08-23 16:30:00</t>
+          <t>2026-08-23 16:00:00</t>
         </is>
       </c>
     </row>
@@ -33514,27 +33514,27 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G204">
@@ -33561,13 +33561,13 @@
         </is>
       </c>
       <c r="N204">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="O204">
-        <v>7.65</v>
+        <v>0</v>
       </c>
       <c r="P204">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Q204">
         <v>0</v>
@@ -33665,7 +33665,7 @@
       </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>2026-08-23 16:30:00</t>
+          <t>2026-08-23 16:00:00</t>
         </is>
       </c>
     </row>
@@ -33677,12 +33677,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -33692,12 +33692,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G205">
@@ -33828,7 +33828,7 @@
       </c>
       <c r="AU205" t="inlineStr">
         <is>
-          <t>2026-08-23 17:00:00</t>
+          <t>2026-08-23 16:00:00</t>
         </is>
       </c>
     </row>
@@ -33840,27 +33840,27 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G206">
@@ -33887,13 +33887,13 @@
         </is>
       </c>
       <c r="N206">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O206">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P206">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q206">
         <v>0</v>
@@ -33991,7 +33991,7 @@
       </c>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>2026-08-23 17:00:00</t>
+          <t>2026-08-23 16:30:00</t>
         </is>
       </c>
     </row>
@@ -34003,27 +34003,27 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G207">
@@ -34050,13 +34050,13 @@
         </is>
       </c>
       <c r="N207">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="O207">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="P207">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Q207">
         <v>0</v>
@@ -34154,7 +34154,7 @@
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>2026-08-23 17:30:00</t>
+          <t>2026-08-23 16:30:00</t>
         </is>
       </c>
     </row>
@@ -34166,27 +34166,27 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G208">
@@ -34213,13 +34213,13 @@
         </is>
       </c>
       <c r="N208">
-        <v>2.59</v>
+        <v>1.19</v>
       </c>
       <c r="O208">
-        <v>3.57</v>
+        <v>7.65</v>
       </c>
       <c r="P208">
-        <v>2.74</v>
+        <v>16</v>
       </c>
       <c r="Q208">
         <v>0</v>
@@ -34317,7 +34317,7 @@
       </c>
       <c r="AU208" t="inlineStr">
         <is>
-          <t>2026-08-23 17:30:00</t>
+          <t>2026-08-23 16:30:00</t>
         </is>
       </c>
     </row>
@@ -34329,12 +34329,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G209">
@@ -34480,7 +34480,7 @@
       </c>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:00</t>
+          <t>2026-08-23 17:00:00</t>
         </is>
       </c>
     </row>
@@ -34492,12 +34492,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G210">
@@ -34539,13 +34539,13 @@
         </is>
       </c>
       <c r="N210">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O210">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P210">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q210">
         <v>0</v>
@@ -34643,7 +34643,7 @@
       </c>
       <c r="AU210" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:00</t>
+          <t>2026-08-23 17:00:00</t>
         </is>
       </c>
     </row>
@@ -34655,12 +34655,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -34670,12 +34670,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G211">
@@ -34702,13 +34702,13 @@
         </is>
       </c>
       <c r="N211">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O211">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="P211">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q211">
         <v>0</v>
@@ -34806,7 +34806,7 @@
       </c>
       <c r="AU211" t="inlineStr">
         <is>
-          <t>2026-08-23 18:15:00</t>
+          <t>2026-08-23 17:30:00</t>
         </is>
       </c>
     </row>
@@ -34818,12 +34818,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -34833,12 +34833,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G212">
@@ -34865,13 +34865,13 @@
         </is>
       </c>
       <c r="N212">
-        <v>3.44</v>
+        <v>2.59</v>
       </c>
       <c r="O212">
-        <v>3.42</v>
+        <v>3.57</v>
       </c>
       <c r="P212">
-        <v>2.18</v>
+        <v>2.74</v>
       </c>
       <c r="Q212">
         <v>0</v>
@@ -34969,7 +34969,7 @@
       </c>
       <c r="AU212" t="inlineStr">
         <is>
-          <t>2026-08-23 18:30:00</t>
+          <t>2026-08-23 17:30:00</t>
         </is>
       </c>
     </row>
@@ -34981,12 +34981,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G213">
@@ -35028,13 +35028,13 @@
         </is>
       </c>
       <c r="N213">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="O213">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P213">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="Q213">
         <v>0</v>
@@ -35132,7 +35132,7 @@
       </c>
       <c r="AU213" t="inlineStr">
         <is>
-          <t>2026-08-23 18:30:00</t>
+          <t>2026-08-23 18:00:00</t>
         </is>
       </c>
     </row>
@@ -35144,12 +35144,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G214">
@@ -35295,7 +35295,7 @@
       </c>
       <c r="AU214" t="inlineStr">
         <is>
-          <t>2026-08-23 18:30:00</t>
+          <t>2026-08-23 18:00:00</t>
         </is>
       </c>
     </row>
@@ -35307,12 +35307,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G215">
@@ -35458,7 +35458,7 @@
       </c>
       <c r="AU215" t="inlineStr">
         <is>
-          <t>2026-08-23 18:30:00</t>
+          <t>2026-08-23 18:15:00</t>
         </is>
       </c>
     </row>
@@ -35475,7 +35475,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -35485,12 +35485,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G216">
@@ -35517,13 +35517,13 @@
         </is>
       </c>
       <c r="N216">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="O216">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P216">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q216">
         <v>0</v>
@@ -35633,12 +35633,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -35648,12 +35648,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G217">
@@ -35680,13 +35680,13 @@
         </is>
       </c>
       <c r="N217">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O217">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P217">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q217">
         <v>0</v>
@@ -35784,7 +35784,7 @@
       </c>
       <c r="AU217" t="inlineStr">
         <is>
-          <t>2026-08-23 19:00:00</t>
+          <t>2026-08-23 18:30:00</t>
         </is>
       </c>
     </row>
@@ -35796,12 +35796,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -35811,12 +35811,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G218">
@@ -35843,13 +35843,13 @@
         </is>
       </c>
       <c r="N218">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="O218">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P218">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Q218">
         <v>0</v>
@@ -35947,7 +35947,7 @@
       </c>
       <c r="AU218" t="inlineStr">
         <is>
-          <t>2026-08-23 19:30:00</t>
+          <t>2026-08-23 18:30:00</t>
         </is>
       </c>
     </row>
@@ -35959,12 +35959,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -35974,12 +35974,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G219">
@@ -36110,7 +36110,7 @@
       </c>
       <c r="AU219" t="inlineStr">
         <is>
-          <t>2026-08-23 20:00:00</t>
+          <t>2026-08-23 18:30:00</t>
         </is>
       </c>
     </row>
@@ -36122,12 +36122,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -36137,12 +36137,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G220">
@@ -36169,13 +36169,13 @@
         </is>
       </c>
       <c r="N220">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="O220">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="P220">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="Q220">
         <v>0</v>
@@ -36273,7 +36273,7 @@
       </c>
       <c r="AU220" t="inlineStr">
         <is>
-          <t>2026-08-23 20:00:00</t>
+          <t>2026-08-23 18:30:00</t>
         </is>
       </c>
     </row>
@@ -36285,12 +36285,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -36300,12 +36300,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G221">
@@ -36436,7 +36436,7 @@
       </c>
       <c r="AU221" t="inlineStr">
         <is>
-          <t>2026-08-23 20:30:00</t>
+          <t>2026-08-23 19:00:00</t>
         </is>
       </c>
     </row>
@@ -36448,12 +36448,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -36463,12 +36463,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G222">
@@ -36495,13 +36495,13 @@
         </is>
       </c>
       <c r="N222">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O222">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P222">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q222">
         <v>0</v>
@@ -36599,7 +36599,7 @@
       </c>
       <c r="AU222" t="inlineStr">
         <is>
-          <t>2026-08-23 20:30:00</t>
+          <t>2026-08-23 19:30:00</t>
         </is>
       </c>
     </row>
@@ -36611,12 +36611,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -36626,12 +36626,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G223">
@@ -36762,7 +36762,7 @@
       </c>
       <c r="AU223" t="inlineStr">
         <is>
-          <t>2026-08-23 21:00:00</t>
+          <t>2026-08-23 20:00:00</t>
         </is>
       </c>
     </row>
@@ -36774,12 +36774,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -36789,12 +36789,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G224">
@@ -36821,13 +36821,13 @@
         </is>
       </c>
       <c r="N224">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O224">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="P224">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="Q224">
         <v>0</v>
@@ -36925,7 +36925,7 @@
       </c>
       <c r="AU224" t="inlineStr">
         <is>
-          <t>2026-08-23 21:00:00</t>
+          <t>2026-08-23 20:00:00</t>
         </is>
       </c>
     </row>
@@ -36937,12 +36937,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -36952,12 +36952,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G225">
@@ -37088,7 +37088,7 @@
       </c>
       <c r="AU225" t="inlineStr">
         <is>
-          <t>2026-08-23 21:00:00</t>
+          <t>2026-08-23 20:30:00</t>
         </is>
       </c>
     </row>
@@ -37100,27 +37100,27 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="G226">
@@ -37251,7 +37251,7 @@
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>2026-08-23 21:00:00</t>
+          <t>2026-08-23 20:30:00</t>
         </is>
       </c>
     </row>
@@ -37268,7 +37268,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G227">
@@ -37310,13 +37310,13 @@
         </is>
       </c>
       <c r="N227">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="O227">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P227">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q227">
         <v>0</v>
@@ -37349,10 +37349,10 @@
         <v>0</v>
       </c>
       <c r="AA227">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB227">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC227">
         <v>0</v>
@@ -37431,151 +37431,803 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
+          <t>Uzbekistan Uzbekistan Super League</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Termez Surkhon</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>AGMK</t>
+        </is>
+      </c>
+      <c r="G228">
+        <v>0</v>
+      </c>
+      <c r="H228">
+        <v>0</v>
+      </c>
+      <c r="I228">
+        <v>0</v>
+      </c>
+      <c r="J228">
+        <v>0</v>
+      </c>
+      <c r="K228">
+        <v>0</v>
+      </c>
+      <c r="L228">
+        <v>0</v>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N228">
+        <v>0</v>
+      </c>
+      <c r="O228">
+        <v>0</v>
+      </c>
+      <c r="P228">
+        <v>0</v>
+      </c>
+      <c r="Q228">
+        <v>0</v>
+      </c>
+      <c r="R228">
+        <v>0</v>
+      </c>
+      <c r="S228">
+        <v>0</v>
+      </c>
+      <c r="T228">
+        <v>0</v>
+      </c>
+      <c r="U228">
+        <v>0</v>
+      </c>
+      <c r="V228">
+        <v>0</v>
+      </c>
+      <c r="W228">
+        <v>0</v>
+      </c>
+      <c r="X228">
+        <v>0</v>
+      </c>
+      <c r="Y228">
+        <v>0</v>
+      </c>
+      <c r="Z228">
+        <v>0</v>
+      </c>
+      <c r="AA228">
+        <v>0</v>
+      </c>
+      <c r="AB228">
+        <v>0</v>
+      </c>
+      <c r="AC228">
+        <v>0</v>
+      </c>
+      <c r="AD228">
+        <v>0</v>
+      </c>
+      <c r="AE228">
+        <v>0</v>
+      </c>
+      <c r="AF228">
+        <v>0</v>
+      </c>
+      <c r="AG228">
+        <v>0</v>
+      </c>
+      <c r="AH228" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI228" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ228">
+        <v>0</v>
+      </c>
+      <c r="AK228">
+        <v>0</v>
+      </c>
+      <c r="AL228">
+        <v>0</v>
+      </c>
+      <c r="AM228">
+        <v>-1</v>
+      </c>
+      <c r="AN228">
+        <v>-1</v>
+      </c>
+      <c r="AO228">
+        <v>-1</v>
+      </c>
+      <c r="AP228">
+        <v>-1</v>
+      </c>
+      <c r="AQ228">
+        <v>0</v>
+      </c>
+      <c r="AR228">
+        <v>0</v>
+      </c>
+      <c r="AS228">
+        <v>0</v>
+      </c>
+      <c r="AT228">
+        <v>0</v>
+      </c>
+      <c r="AU228" t="inlineStr">
+        <is>
+          <t>2026-08-23 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Uzbekistan Uzbekistan Super League</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Dinamo Samarqand</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Pakhtakor</t>
+        </is>
+      </c>
+      <c r="G229">
+        <v>0</v>
+      </c>
+      <c r="H229">
+        <v>0</v>
+      </c>
+      <c r="I229">
+        <v>0</v>
+      </c>
+      <c r="J229">
+        <v>0</v>
+      </c>
+      <c r="K229">
+        <v>0</v>
+      </c>
+      <c r="L229">
+        <v>0</v>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N229">
+        <v>0</v>
+      </c>
+      <c r="O229">
+        <v>0</v>
+      </c>
+      <c r="P229">
+        <v>0</v>
+      </c>
+      <c r="Q229">
+        <v>0</v>
+      </c>
+      <c r="R229">
+        <v>0</v>
+      </c>
+      <c r="S229">
+        <v>0</v>
+      </c>
+      <c r="T229">
+        <v>0</v>
+      </c>
+      <c r="U229">
+        <v>0</v>
+      </c>
+      <c r="V229">
+        <v>0</v>
+      </c>
+      <c r="W229">
+        <v>0</v>
+      </c>
+      <c r="X229">
+        <v>0</v>
+      </c>
+      <c r="Y229">
+        <v>0</v>
+      </c>
+      <c r="Z229">
+        <v>0</v>
+      </c>
+      <c r="AA229">
+        <v>0</v>
+      </c>
+      <c r="AB229">
+        <v>0</v>
+      </c>
+      <c r="AC229">
+        <v>0</v>
+      </c>
+      <c r="AD229">
+        <v>0</v>
+      </c>
+      <c r="AE229">
+        <v>0</v>
+      </c>
+      <c r="AF229">
+        <v>0</v>
+      </c>
+      <c r="AG229">
+        <v>0</v>
+      </c>
+      <c r="AH229" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI229" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ229">
+        <v>0</v>
+      </c>
+      <c r="AK229">
+        <v>0</v>
+      </c>
+      <c r="AL229">
+        <v>0</v>
+      </c>
+      <c r="AM229">
+        <v>-1</v>
+      </c>
+      <c r="AN229">
+        <v>-1</v>
+      </c>
+      <c r="AO229">
+        <v>-1</v>
+      </c>
+      <c r="AP229">
+        <v>-1</v>
+      </c>
+      <c r="AQ229">
+        <v>0</v>
+      </c>
+      <c r="AR229">
+        <v>0</v>
+      </c>
+      <c r="AS229">
+        <v>0</v>
+      </c>
+      <c r="AT229">
+        <v>0</v>
+      </c>
+      <c r="AU229" t="inlineStr">
+        <is>
+          <t>2026-08-23 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Russia FNL</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Rotor Volgograd</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Neftekhimik</t>
+        </is>
+      </c>
+      <c r="G230">
+        <v>0</v>
+      </c>
+      <c r="H230">
+        <v>0</v>
+      </c>
+      <c r="I230">
+        <v>0</v>
+      </c>
+      <c r="J230">
+        <v>0</v>
+      </c>
+      <c r="K230">
+        <v>0</v>
+      </c>
+      <c r="L230">
+        <v>0</v>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N230">
+        <v>0</v>
+      </c>
+      <c r="O230">
+        <v>0</v>
+      </c>
+      <c r="P230">
+        <v>0</v>
+      </c>
+      <c r="Q230">
+        <v>0</v>
+      </c>
+      <c r="R230">
+        <v>0</v>
+      </c>
+      <c r="S230">
+        <v>0</v>
+      </c>
+      <c r="T230">
+        <v>0</v>
+      </c>
+      <c r="U230">
+        <v>0</v>
+      </c>
+      <c r="V230">
+        <v>0</v>
+      </c>
+      <c r="W230">
+        <v>0</v>
+      </c>
+      <c r="X230">
+        <v>0</v>
+      </c>
+      <c r="Y230">
+        <v>0</v>
+      </c>
+      <c r="Z230">
+        <v>0</v>
+      </c>
+      <c r="AA230">
+        <v>0</v>
+      </c>
+      <c r="AB230">
+        <v>0</v>
+      </c>
+      <c r="AC230">
+        <v>0</v>
+      </c>
+      <c r="AD230">
+        <v>0</v>
+      </c>
+      <c r="AE230">
+        <v>0</v>
+      </c>
+      <c r="AF230">
+        <v>0</v>
+      </c>
+      <c r="AG230">
+        <v>0</v>
+      </c>
+      <c r="AH230" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI230" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ230">
+        <v>0</v>
+      </c>
+      <c r="AK230">
+        <v>0</v>
+      </c>
+      <c r="AL230">
+        <v>0</v>
+      </c>
+      <c r="AM230">
+        <v>-1</v>
+      </c>
+      <c r="AN230">
+        <v>-1</v>
+      </c>
+      <c r="AO230">
+        <v>-1</v>
+      </c>
+      <c r="AP230">
+        <v>-1</v>
+      </c>
+      <c r="AQ230">
+        <v>0</v>
+      </c>
+      <c r="AR230">
+        <v>0</v>
+      </c>
+      <c r="AS230">
+        <v>0</v>
+      </c>
+      <c r="AT230">
+        <v>0</v>
+      </c>
+      <c r="AU230" t="inlineStr">
+        <is>
+          <t>2026-08-23 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>LDU Quito</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="G231">
+        <v>0</v>
+      </c>
+      <c r="H231">
+        <v>0</v>
+      </c>
+      <c r="I231">
+        <v>0</v>
+      </c>
+      <c r="J231">
+        <v>0</v>
+      </c>
+      <c r="K231">
+        <v>0</v>
+      </c>
+      <c r="L231">
+        <v>0</v>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N231">
+        <v>1.48</v>
+      </c>
+      <c r="O231">
+        <v>3.8</v>
+      </c>
+      <c r="P231">
+        <v>7</v>
+      </c>
+      <c r="Q231">
+        <v>0</v>
+      </c>
+      <c r="R231">
+        <v>0</v>
+      </c>
+      <c r="S231">
+        <v>0</v>
+      </c>
+      <c r="T231">
+        <v>0</v>
+      </c>
+      <c r="U231">
+        <v>0</v>
+      </c>
+      <c r="V231">
+        <v>0</v>
+      </c>
+      <c r="W231">
+        <v>0</v>
+      </c>
+      <c r="X231">
+        <v>0</v>
+      </c>
+      <c r="Y231">
+        <v>0</v>
+      </c>
+      <c r="Z231">
+        <v>0</v>
+      </c>
+      <c r="AA231">
+        <v>2.03</v>
+      </c>
+      <c r="AB231">
+        <v>1.78</v>
+      </c>
+      <c r="AC231">
+        <v>0</v>
+      </c>
+      <c r="AD231">
+        <v>0</v>
+      </c>
+      <c r="AE231">
+        <v>0</v>
+      </c>
+      <c r="AF231">
+        <v>0</v>
+      </c>
+      <c r="AG231">
+        <v>0</v>
+      </c>
+      <c r="AH231" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI231" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ231">
+        <v>0</v>
+      </c>
+      <c r="AK231">
+        <v>0</v>
+      </c>
+      <c r="AL231">
+        <v>0</v>
+      </c>
+      <c r="AM231">
+        <v>-1</v>
+      </c>
+      <c r="AN231">
+        <v>-1</v>
+      </c>
+      <c r="AO231">
+        <v>-1</v>
+      </c>
+      <c r="AP231">
+        <v>-1</v>
+      </c>
+      <c r="AQ231">
+        <v>0</v>
+      </c>
+      <c r="AR231">
+        <v>0</v>
+      </c>
+      <c r="AS231">
+        <v>0</v>
+      </c>
+      <c r="AT231">
+        <v>0</v>
+      </c>
+      <c r="AU231" t="inlineStr">
+        <is>
+          <t>2026-08-23 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr">
+      <c r="D232" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E228" t="inlineStr">
+      <c r="E232" t="inlineStr">
         <is>
           <t>Angel City</t>
         </is>
       </c>
-      <c r="F228" t="inlineStr">
+      <c r="F232" t="inlineStr">
         <is>
           <t>Gotham FC</t>
         </is>
       </c>
-      <c r="G228">
-        <v>0</v>
-      </c>
-      <c r="H228">
-        <v>0</v>
-      </c>
-      <c r="I228">
-        <v>0</v>
-      </c>
-      <c r="J228">
-        <v>0</v>
-      </c>
-      <c r="K228">
-        <v>0</v>
-      </c>
-      <c r="L228">
-        <v>0</v>
-      </c>
-      <c r="M228" t="inlineStr">
+      <c r="G232">
+        <v>0</v>
+      </c>
+      <c r="H232">
+        <v>0</v>
+      </c>
+      <c r="I232">
+        <v>0</v>
+      </c>
+      <c r="J232">
+        <v>0</v>
+      </c>
+      <c r="K232">
+        <v>0</v>
+      </c>
+      <c r="L232">
+        <v>0</v>
+      </c>
+      <c r="M232" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N228">
+      <c r="N232">
         <v>3.35</v>
       </c>
-      <c r="O228">
+      <c r="O232">
         <v>3.05</v>
       </c>
-      <c r="P228">
+      <c r="P232">
         <v>1.95</v>
       </c>
-      <c r="Q228">
-        <v>0</v>
-      </c>
-      <c r="R228">
-        <v>0</v>
-      </c>
-      <c r="S228">
-        <v>0</v>
-      </c>
-      <c r="T228">
-        <v>0</v>
-      </c>
-      <c r="U228">
-        <v>0</v>
-      </c>
-      <c r="V228">
-        <v>0</v>
-      </c>
-      <c r="W228">
-        <v>0</v>
-      </c>
-      <c r="X228">
-        <v>0</v>
-      </c>
-      <c r="Y228">
-        <v>0</v>
-      </c>
-      <c r="Z228">
-        <v>0</v>
-      </c>
-      <c r="AA228">
-        <v>0</v>
-      </c>
-      <c r="AB228">
-        <v>0</v>
-      </c>
-      <c r="AC228">
-        <v>0</v>
-      </c>
-      <c r="AD228">
-        <v>0</v>
-      </c>
-      <c r="AE228">
-        <v>0</v>
-      </c>
-      <c r="AF228">
-        <v>0</v>
-      </c>
-      <c r="AG228">
-        <v>0</v>
-      </c>
-      <c r="AH228" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI228" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ228">
-        <v>0</v>
-      </c>
-      <c r="AK228">
-        <v>0</v>
-      </c>
-      <c r="AL228">
-        <v>0</v>
-      </c>
-      <c r="AM228">
-        <v>-1</v>
-      </c>
-      <c r="AN228">
-        <v>-1</v>
-      </c>
-      <c r="AO228">
-        <v>-1</v>
-      </c>
-      <c r="AP228">
-        <v>-1</v>
-      </c>
-      <c r="AQ228">
-        <v>0</v>
-      </c>
-      <c r="AR228">
-        <v>0</v>
-      </c>
-      <c r="AS228">
-        <v>0</v>
-      </c>
-      <c r="AT228">
-        <v>0</v>
-      </c>
-      <c r="AU228" t="inlineStr">
+      <c r="Q232">
+        <v>0</v>
+      </c>
+      <c r="R232">
+        <v>0</v>
+      </c>
+      <c r="S232">
+        <v>0</v>
+      </c>
+      <c r="T232">
+        <v>0</v>
+      </c>
+      <c r="U232">
+        <v>0</v>
+      </c>
+      <c r="V232">
+        <v>0</v>
+      </c>
+      <c r="W232">
+        <v>0</v>
+      </c>
+      <c r="X232">
+        <v>0</v>
+      </c>
+      <c r="Y232">
+        <v>0</v>
+      </c>
+      <c r="Z232">
+        <v>0</v>
+      </c>
+      <c r="AA232">
+        <v>0</v>
+      </c>
+      <c r="AB232">
+        <v>0</v>
+      </c>
+      <c r="AC232">
+        <v>0</v>
+      </c>
+      <c r="AD232">
+        <v>0</v>
+      </c>
+      <c r="AE232">
+        <v>0</v>
+      </c>
+      <c r="AF232">
+        <v>0</v>
+      </c>
+      <c r="AG232">
+        <v>0</v>
+      </c>
+      <c r="AH232" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI232" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ232">
+        <v>0</v>
+      </c>
+      <c r="AK232">
+        <v>0</v>
+      </c>
+      <c r="AL232">
+        <v>0</v>
+      </c>
+      <c r="AM232">
+        <v>-1</v>
+      </c>
+      <c r="AN232">
+        <v>-1</v>
+      </c>
+      <c r="AO232">
+        <v>-1</v>
+      </c>
+      <c r="AP232">
+        <v>-1</v>
+      </c>
+      <c r="AQ232">
+        <v>0</v>
+      </c>
+      <c r="AR232">
+        <v>0</v>
+      </c>
+      <c r="AS232">
+        <v>0</v>
+      </c>
+      <c r="AT232">
+        <v>0</v>
+      </c>
+      <c r="AU232" t="inlineStr">
         <is>
           <t>2026-08-23 21:00:00</t>
         </is>

--- a/jogos_2026-08-23.xlsx
+++ b/jogos_2026-08-23.xlsx
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G114">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G115">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G116">

--- a/jogos_2026-08-23.xlsx
+++ b/jogos_2026-08-23.xlsx
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>7.65</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5407,10 +5407,10 @@
         <v>0</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE31">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q39">
         <v>0</v>
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -11393,13 +11393,13 @@
         </is>
       </c>
       <c r="N68">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O68">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="P68">
-        <v>0</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="Q68">
         <v>0</v>
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O69">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P69">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O70">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q70">
         <v>0</v>
@@ -11758,10 +11758,10 @@
         <v>0</v>
       </c>
       <c r="AA70">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB70">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC70">
         <v>0</v>
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O87">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -16935,13 +16935,13 @@
         </is>
       </c>
       <c r="N102">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O102">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P102">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Sertanense</t>
+          <t>Gd Nazarenos</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G105">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Gd Nazarenos</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G106">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G107">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Fazendense</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>AD Nogueirense</t>
         </is>
       </c>
       <c r="G108">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Fazendense</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>AD Nogueirense</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G109">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Sertanense</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G114">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G115">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G116">
@@ -21010,13 +21010,13 @@
         </is>
       </c>
       <c r="N127">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O127">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P127">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q127">
         <v>0</v>
@@ -24759,13 +24759,13 @@
         </is>
       </c>
       <c r="N150">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O150">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="P150">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="Q150">
         <v>0</v>
@@ -24922,13 +24922,13 @@
         </is>
       </c>
       <c r="N151">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O151">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="P151">
-        <v>0</v>
+        <v>7.31</v>
       </c>
       <c r="Q151">
         <v>0</v>
@@ -24961,10 +24961,10 @@
         <v>0</v>
       </c>
       <c r="AA151">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB151">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC151">
         <v>0</v>
@@ -31279,13 +31279,13 @@
         </is>
       </c>
       <c r="N190">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O190">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P190">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="Q190">
         <v>0</v>
@@ -33887,13 +33887,13 @@
         </is>
       </c>
       <c r="N206">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="O206">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P206">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q206">
         <v>0</v>

--- a/jogos_2026-08-23.xlsx
+++ b/jogos_2026-08-23.xlsx
@@ -20847,13 +20847,13 @@
         </is>
       </c>
       <c r="N126">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O126">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P126">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q126">
         <v>0</v>

--- a/jogos_2026-08-23.xlsx
+++ b/jogos_2026-08-23.xlsx
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G189">
@@ -31116,13 +31116,13 @@
         </is>
       </c>
       <c r="N189">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O189">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P189">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="Q189">
         <v>0</v>
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="G190">
@@ -31279,13 +31279,13 @@
         </is>
       </c>
       <c r="N190">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O190">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="P190">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="Q190">
         <v>0</v>

--- a/jogos_2026-08-23.xlsx
+++ b/jogos_2026-08-23.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU232"/>
+  <dimension ref="A1:AU237"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O60">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P60">
-        <v>0</v>
+        <v>4.81</v>
       </c>
       <c r="Q60">
         <v>0</v>
@@ -10134,10 +10134,10 @@
         <v>0</v>
       </c>
       <c r="AC60">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD60">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE60">
         <v>0</v>
@@ -14448,22 +14448,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="G87">
@@ -14486,17 +14486,17 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N87">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="O87">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="P87">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -14606,27 +14606,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G88">
@@ -14649,17 +14649,17 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N88">
-        <v>3.58</v>
+        <v>3.52</v>
       </c>
       <c r="O88">
-        <v>4.02</v>
+        <v>3.12</v>
       </c>
       <c r="P88">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="Q88">
         <v>0</v>
@@ -14692,10 +14692,10 @@
         <v>0</v>
       </c>
       <c r="AA88">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB88">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC88">
         <v>0</v>
@@ -14757,7 +14757,7 @@
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>2026-08-23 12:15:00</t>
+          <t>2026-08-23 12:00:00</t>
         </is>
       </c>
     </row>
@@ -14769,12 +14769,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,13 +14816,13 @@
         </is>
       </c>
       <c r="N89">
-        <v>3.05</v>
+        <v>3.58</v>
       </c>
       <c r="O89">
-        <v>4.03</v>
+        <v>4.02</v>
       </c>
       <c r="P89">
-        <v>2.28</v>
+        <v>2.05</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -14855,16 +14855,16 @@
         <v>0</v>
       </c>
       <c r="AA89">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB89">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC89">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD89">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE89">
         <v>0</v>
@@ -14920,7 +14920,7 @@
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>2026-08-23 12:30:00</t>
+          <t>2026-08-23 12:15:00</t>
         </is>
       </c>
     </row>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,13 +14979,13 @@
         </is>
       </c>
       <c r="N90">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O90">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q90">
         <v>0</v>
@@ -15024,10 +15024,10 @@
         <v>0</v>
       </c>
       <c r="AC90">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD90">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE90">
         <v>0</v>
@@ -15100,22 +15100,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,13 +15142,13 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="O91">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P91">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="Q91">
         <v>0</v>
@@ -15263,7 +15263,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.78</v>
+        <v>1.94</v>
       </c>
       <c r="O92">
-        <v>3.34</v>
+        <v>3.54</v>
       </c>
       <c r="P92">
-        <v>2.27</v>
+        <v>3.63</v>
       </c>
       <c r="Q92">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R92">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S92">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T92">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="U92">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V92">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W92">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X92">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y92">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z92">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA92">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB92">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC92">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AD92">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE92">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF92">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG92">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK92">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>ETO</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,65 +15468,65 @@
         </is>
       </c>
       <c r="N93">
+        <v>2.78</v>
+      </c>
+      <c r="O93">
+        <v>3.34</v>
+      </c>
+      <c r="P93">
+        <v>2.27</v>
+      </c>
+      <c r="Q93">
+        <v>3.3</v>
+      </c>
+      <c r="R93">
+        <v>2.2</v>
+      </c>
+      <c r="S93">
+        <v>1.32</v>
+      </c>
+      <c r="T93">
+        <v>2.96</v>
+      </c>
+      <c r="U93">
+        <v>2.5</v>
+      </c>
+      <c r="V93">
+        <v>1.44</v>
+      </c>
+      <c r="W93">
+        <v>1.07</v>
+      </c>
+      <c r="X93">
+        <v>1.04</v>
+      </c>
+      <c r="Y93">
+        <v>1.21</v>
+      </c>
+      <c r="Z93">
+        <v>3.58</v>
+      </c>
+      <c r="AA93">
+        <v>1.79</v>
+      </c>
+      <c r="AB93">
+        <v>2</v>
+      </c>
+      <c r="AC93">
+        <v>2.74</v>
+      </c>
+      <c r="AD93">
         <v>1.34</v>
       </c>
-      <c r="O93">
-        <v>4.65</v>
-      </c>
-      <c r="P93">
-        <v>7.22</v>
-      </c>
-      <c r="Q93">
-        <v>1.8</v>
-      </c>
-      <c r="R93">
-        <v>2.6</v>
-      </c>
-      <c r="S93">
-        <v>1.26</v>
-      </c>
-      <c r="T93">
-        <v>3.5</v>
-      </c>
-      <c r="U93">
+      <c r="AE93">
+        <v>1.11</v>
+      </c>
+      <c r="AF93">
+        <v>1.57</v>
+      </c>
+      <c r="AG93">
         <v>2.25</v>
       </c>
-      <c r="V93">
-        <v>1.62</v>
-      </c>
-      <c r="W93">
-        <v>1.15</v>
-      </c>
-      <c r="X93">
-        <v>1.03</v>
-      </c>
-      <c r="Y93">
-        <v>1.17</v>
-      </c>
-      <c r="Z93">
-        <v>4.6</v>
-      </c>
-      <c r="AA93">
-        <v>1.56</v>
-      </c>
-      <c r="AB93">
-        <v>2.27</v>
-      </c>
-      <c r="AC93">
-        <v>2.33</v>
-      </c>
-      <c r="AD93">
-        <v>1.48</v>
-      </c>
-      <c r="AE93">
-        <v>1.2</v>
-      </c>
-      <c r="AF93">
-        <v>1.78</v>
-      </c>
-      <c r="AG93">
-        <v>1.91</v>
-      </c>
       <c r="AH93" t="inlineStr">
         <is>
           <t>[]</t>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="AK93">
-        <v>2.88</v>
+        <v>1.36</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15589,7 +15589,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>ETO</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O94">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="P94">
-        <v>0</v>
+        <v>7.22</v>
       </c>
       <c r="Q94">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R94">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S94">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T94">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U94">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V94">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W94">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X94">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y94">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z94">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA94">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB94">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AC94">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD94">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE94">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF94">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG94">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK94">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G95">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G96">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G97">
@@ -16241,7 +16241,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Voluntari</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="O98">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P98">
-        <v>6.63</v>
+        <v>0</v>
       </c>
       <c r="Q98">
         <v>0</v>
@@ -16404,7 +16404,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Voluntari</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O99">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P99">
-        <v>0</v>
+        <v>6.63</v>
       </c>
       <c r="Q99">
         <v>0</v>
@@ -16562,27 +16562,27 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G100">
@@ -16713,7 +16713,7 @@
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>2026-08-23 12:45:00</t>
+          <t>2026-08-23 12:30:00</t>
         </is>
       </c>
     </row>
@@ -16725,12 +16725,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,13 +16772,13 @@
         </is>
       </c>
       <c r="N101">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O101">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P101">
-        <v>5.29</v>
+        <v>0</v>
       </c>
       <c r="Q101">
         <v>0</v>
@@ -16876,7 +16876,7 @@
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>2026-08-23 13:00:00</t>
+          <t>2026-08-23 12:30:00</t>
         </is>
       </c>
     </row>
@@ -16888,12 +16888,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,13 +16935,13 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O102">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P102">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -17039,7 +17039,7 @@
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>2026-08-23 13:00:00</t>
+          <t>2026-08-23 12:30:00</t>
         </is>
       </c>
     </row>
@@ -17051,27 +17051,27 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G103">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>2026-08-23 13:00:00</t>
+          <t>2026-08-23 12:45:00</t>
         </is>
       </c>
     </row>
@@ -17219,7 +17219,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O104">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P104">
-        <v>0</v>
+        <v>5.29</v>
       </c>
       <c r="Q104">
         <v>0</v>
@@ -17382,7 +17382,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Gd Nazarenos</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,13 +17424,13 @@
         </is>
       </c>
       <c r="N105">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O105">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P105">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q105">
         <v>0</v>
@@ -17545,7 +17545,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G106">
@@ -17708,7 +17708,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G107">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Fazendense</t>
+          <t>Gd Nazarenos</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>AD Nogueirense</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G108">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G109">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Sertanense</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sertanense</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G111">
@@ -18523,7 +18523,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G112">
@@ -18686,7 +18686,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Fazendense</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>AD Nogueirense</t>
         </is>
       </c>
       <c r="G113">
@@ -18849,7 +18849,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G114">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G115">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G116">
@@ -19338,22 +19338,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G117">
@@ -19501,22 +19501,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G118">
@@ -19664,22 +19664,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G119">
@@ -19827,22 +19827,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Ovarense</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G120">
@@ -19990,22 +19990,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G121">
@@ -20153,22 +20153,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Guarda</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G122">
@@ -20316,7 +20316,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Ovarense</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G123">
@@ -20479,7 +20479,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G124">
@@ -20642,22 +20642,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Guarda</t>
         </is>
       </c>
       <c r="G125">
@@ -20805,22 +20805,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,13 +20847,13 @@
         </is>
       </c>
       <c r="N126">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O126">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P126">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q126">
         <v>0</v>
@@ -20968,7 +20968,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Savoia</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,13 +21010,13 @@
         </is>
       </c>
       <c r="N127">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="O127">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P127">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q127">
         <v>0</v>
@@ -21131,22 +21131,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,13 +21173,13 @@
         </is>
       </c>
       <c r="N128">
-        <v>1.41</v>
+        <v>4.5</v>
       </c>
       <c r="O128">
-        <v>4.3</v>
+        <v>4.05</v>
       </c>
       <c r="P128">
-        <v>6.76</v>
+        <v>1.59</v>
       </c>
       <c r="Q128">
         <v>0</v>
@@ -21294,22 +21294,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mardin BB</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G129">
@@ -21336,13 +21336,13 @@
         </is>
       </c>
       <c r="N129">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O129">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P129">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q129">
         <v>0</v>
@@ -21457,7 +21457,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Savoia</t>
         </is>
       </c>
       <c r="G130">
@@ -21499,13 +21499,13 @@
         </is>
       </c>
       <c r="N130">
-        <v>2.75</v>
+        <v>2.22</v>
       </c>
       <c r="O130">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="P130">
-        <v>2.37</v>
+        <v>3.25</v>
       </c>
       <c r="Q130">
         <v>0</v>
@@ -21620,7 +21620,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G131">
@@ -21662,13 +21662,13 @@
         </is>
       </c>
       <c r="N131">
-        <v>5.48</v>
+        <v>1.41</v>
       </c>
       <c r="O131">
-        <v>3.82</v>
+        <v>4.3</v>
       </c>
       <c r="P131">
-        <v>1.59</v>
+        <v>6.76</v>
       </c>
       <c r="Q131">
         <v>0</v>
@@ -21701,10 +21701,10 @@
         <v>0</v>
       </c>
       <c r="AA131">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB131">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC131">
         <v>0</v>
@@ -21783,7 +21783,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Mardin BB</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,13 +21825,13 @@
         </is>
       </c>
       <c r="N132">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O132">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P132">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="Q132">
         <v>0</v>
@@ -21941,27 +21941,27 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,13 +21988,13 @@
         </is>
       </c>
       <c r="N133">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O133">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P133">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q133">
         <v>0</v>
@@ -22092,7 +22092,7 @@
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>2026-08-23 13:15:00</t>
+          <t>2026-08-23 13:00:00</t>
         </is>
       </c>
     </row>
@@ -22104,27 +22104,27 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,13 +22151,13 @@
         </is>
       </c>
       <c r="N134">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="O134">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="P134">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q134">
         <v>0</v>
@@ -22190,10 +22190,10 @@
         <v>0</v>
       </c>
       <c r="AA134">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB134">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC134">
         <v>0</v>
@@ -22255,7 +22255,7 @@
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>2026-08-23 13:30:00</t>
+          <t>2026-08-23 13:00:00</t>
         </is>
       </c>
     </row>
@@ -22267,12 +22267,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,13 +22314,13 @@
         </is>
       </c>
       <c r="N135">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O135">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P135">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="Q135">
         <v>0</v>
@@ -22418,7 +22418,7 @@
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>2026-08-23 13:30:00</t>
+          <t>2026-08-23 13:00:00</t>
         </is>
       </c>
     </row>
@@ -22430,27 +22430,27 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,13 +22477,13 @@
         </is>
       </c>
       <c r="N136">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O136">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P136">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="Q136">
         <v>0</v>
@@ -22516,10 +22516,10 @@
         <v>0</v>
       </c>
       <c r="AA136">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB136">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC136">
         <v>0</v>
@@ -22581,7 +22581,7 @@
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>2026-08-23 13:30:00</t>
+          <t>2026-08-23 13:15:00</t>
         </is>
       </c>
     </row>
@@ -22598,22 +22598,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G137">
@@ -22761,7 +22761,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="G138">
@@ -22924,7 +22924,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G139">
@@ -22966,13 +22966,13 @@
         </is>
       </c>
       <c r="N139">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O139">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P139">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="Q139">
         <v>0</v>
@@ -23005,10 +23005,10 @@
         <v>0</v>
       </c>
       <c r="AA139">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB139">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC139">
         <v>0</v>
@@ -23087,7 +23087,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G140">
@@ -23129,13 +23129,13 @@
         </is>
       </c>
       <c r="N140">
-        <v>7.26</v>
+        <v>0</v>
       </c>
       <c r="O140">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="P140">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Q140">
         <v>0</v>
@@ -23168,10 +23168,10 @@
         <v>0</v>
       </c>
       <c r="AA140">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB140">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC140">
         <v>0</v>
@@ -23250,7 +23250,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G141">
@@ -23292,13 +23292,13 @@
         </is>
       </c>
       <c r="N141">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="O141">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P141">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="Q141">
         <v>0</v>
@@ -23331,10 +23331,10 @@
         <v>0</v>
       </c>
       <c r="AA141">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB141">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC141">
         <v>0</v>
@@ -23413,7 +23413,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G142">
@@ -23455,13 +23455,13 @@
         </is>
       </c>
       <c r="N142">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O142">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="P142">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="Q142">
         <v>0</v>
@@ -23571,12 +23571,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,13 +23618,13 @@
         </is>
       </c>
       <c r="N143">
-        <v>0</v>
+        <v>7.26</v>
       </c>
       <c r="O143">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P143">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Q143">
         <v>0</v>
@@ -23657,10 +23657,10 @@
         <v>0</v>
       </c>
       <c r="AA143">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB143">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC143">
         <v>0</v>
@@ -23722,7 +23722,7 @@
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>2026-08-23 13:35:00</t>
+          <t>2026-08-23 13:30:00</t>
         </is>
       </c>
     </row>
@@ -23734,12 +23734,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,13 +23781,13 @@
         </is>
       </c>
       <c r="N144">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O144">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P144">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Q144">
         <v>0</v>
@@ -23820,10 +23820,10 @@
         <v>0</v>
       </c>
       <c r="AA144">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB144">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC144">
         <v>0</v>
@@ -23885,7 +23885,7 @@
       </c>
       <c r="AU144" t="inlineStr">
         <is>
-          <t>2026-08-23 13:45:00</t>
+          <t>2026-08-23 13:30:00</t>
         </is>
       </c>
     </row>
@@ -23897,12 +23897,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,13 +23944,13 @@
         </is>
       </c>
       <c r="N145">
-        <v>1.74</v>
+        <v>1.27</v>
       </c>
       <c r="O145">
-        <v>3.52</v>
+        <v>6.5</v>
       </c>
       <c r="P145">
-        <v>4.81</v>
+        <v>9.4</v>
       </c>
       <c r="Q145">
         <v>0</v>
@@ -23983,10 +23983,10 @@
         <v>0</v>
       </c>
       <c r="AA145">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB145">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC145">
         <v>0</v>
@@ -24048,7 +24048,7 @@
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>2026-08-23 14:00:00</t>
+          <t>2026-08-23 13:30:00</t>
         </is>
       </c>
     </row>
@@ -24060,12 +24060,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,13 +24107,13 @@
         </is>
       </c>
       <c r="N146">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="O146">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P146">
-        <v>5.83</v>
+        <v>0</v>
       </c>
       <c r="Q146">
         <v>0</v>
@@ -24146,10 +24146,10 @@
         <v>0</v>
       </c>
       <c r="AA146">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB146">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC146">
         <v>0</v>
@@ -24211,7 +24211,7 @@
       </c>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>2026-08-23 14:00:00</t>
+          <t>2026-08-23 13:35:00</t>
         </is>
       </c>
     </row>
@@ -24223,12 +24223,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,13 +24270,13 @@
         </is>
       </c>
       <c r="N147">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O147">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="P147">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="Q147">
         <v>0</v>
@@ -24374,7 +24374,7 @@
       </c>
       <c r="AU147" t="inlineStr">
         <is>
-          <t>2026-08-23 14:00:00</t>
+          <t>2026-08-23 13:45:00</t>
         </is>
       </c>
     </row>
@@ -24391,7 +24391,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G148">
@@ -24433,13 +24433,13 @@
         </is>
       </c>
       <c r="N148">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O148">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P148">
-        <v>0</v>
+        <v>4.81</v>
       </c>
       <c r="Q148">
         <v>0</v>
@@ -24472,10 +24472,10 @@
         <v>0</v>
       </c>
       <c r="AA148">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB148">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC148">
         <v>0</v>
@@ -24554,7 +24554,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G149">
@@ -24596,13 +24596,13 @@
         </is>
       </c>
       <c r="N149">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O149">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P149">
-        <v>0</v>
+        <v>5.83</v>
       </c>
       <c r="Q149">
         <v>0</v>
@@ -24635,10 +24635,10 @@
         <v>0</v>
       </c>
       <c r="AA149">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB149">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC149">
         <v>0</v>
@@ -24717,7 +24717,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G150">
@@ -24759,13 +24759,13 @@
         </is>
       </c>
       <c r="N150">
-        <v>2.35</v>
+        <v>1.66</v>
       </c>
       <c r="O150">
-        <v>3.31</v>
+        <v>3.92</v>
       </c>
       <c r="P150">
-        <v>3.19</v>
+        <v>4.16</v>
       </c>
       <c r="Q150">
         <v>0</v>
@@ -24880,7 +24880,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G151">
@@ -24922,13 +24922,13 @@
         </is>
       </c>
       <c r="N151">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O151">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="P151">
-        <v>7.31</v>
+        <v>0</v>
       </c>
       <c r="Q151">
         <v>0</v>
@@ -24961,10 +24961,10 @@
         <v>0</v>
       </c>
       <c r="AA151">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB151">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC151">
         <v>0</v>
@@ -25043,22 +25043,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G152">
@@ -25085,13 +25085,13 @@
         </is>
       </c>
       <c r="N152">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O152">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P152">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q152">
         <v>0</v>
@@ -25206,22 +25206,22 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G153">
@@ -25248,13 +25248,13 @@
         </is>
       </c>
       <c r="N153">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O153">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="P153">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -25369,22 +25369,22 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,13 +25411,13 @@
         </is>
       </c>
       <c r="N154">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O154">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="P154">
-        <v>0</v>
+        <v>7.31</v>
       </c>
       <c r="Q154">
         <v>0</v>
@@ -25450,10 +25450,10 @@
         <v>0</v>
       </c>
       <c r="AA154">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB154">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC154">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,13 +25574,13 @@
         </is>
       </c>
       <c r="N155">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="O155">
         <v>3.7</v>
       </c>
       <c r="P155">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="Q155">
         <v>0</v>
@@ -25695,22 +25695,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,13 +25737,13 @@
         </is>
       </c>
       <c r="N156">
-        <v>2.8</v>
+        <v>4.58</v>
       </c>
       <c r="O156">
-        <v>3.2</v>
+        <v>5.2</v>
       </c>
       <c r="P156">
-        <v>2.35</v>
+        <v>1.51</v>
       </c>
       <c r="Q156">
         <v>0</v>
@@ -25776,10 +25776,10 @@
         <v>0</v>
       </c>
       <c r="AA156">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB156">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC156">
         <v>0</v>
@@ -25788,7 +25788,7 @@
         <v>0</v>
       </c>
       <c r="AE156">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF156">
         <v>0</v>
@@ -25858,22 +25858,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,13 +25900,13 @@
         </is>
       </c>
       <c r="N157">
-        <v>2.99</v>
+        <v>1.45</v>
       </c>
       <c r="O157">
-        <v>3.05</v>
+        <v>5.1</v>
       </c>
       <c r="P157">
-        <v>2.72</v>
+        <v>5.32</v>
       </c>
       <c r="Q157">
         <v>0</v>
@@ -26021,22 +26021,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,13 +26063,13 @@
         </is>
       </c>
       <c r="N158">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O158">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P158">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q158">
         <v>0</v>
@@ -26184,7 +26184,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G159">
@@ -26226,13 +26226,13 @@
         </is>
       </c>
       <c r="N159">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O159">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P159">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q159">
         <v>0</v>
@@ -26265,10 +26265,10 @@
         <v>0</v>
       </c>
       <c r="AA159">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB159">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC159">
         <v>0</v>
@@ -26342,12 +26342,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G160">
@@ -26389,13 +26389,13 @@
         </is>
       </c>
       <c r="N160">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="O160">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P160">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q160">
         <v>0</v>
@@ -26493,7 +26493,7 @@
       </c>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>2026-08-23 14:15:00</t>
+          <t>2026-08-23 14:00:00</t>
         </is>
       </c>
     </row>
@@ -26505,12 +26505,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Sporting Hasselt</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G161">
@@ -26656,7 +26656,7 @@
       </c>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>2026-08-23 14:15:00</t>
+          <t>2026-08-23 14:00:00</t>
         </is>
       </c>
     </row>
@@ -26668,12 +26668,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G162">
@@ -26819,7 +26819,7 @@
       </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>2026-08-23 14:30:00</t>
+          <t>2026-08-23 14:15:00</t>
         </is>
       </c>
     </row>
@@ -26831,12 +26831,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Nassaji Mazandaran</t>
+          <t>Sporting Hasselt</t>
         </is>
       </c>
       <c r="G163">
@@ -26982,7 +26982,7 @@
       </c>
       <c r="AU163" t="inlineStr">
         <is>
-          <t>2026-08-23 14:30:00</t>
+          <t>2026-08-23 14:15:00</t>
         </is>
       </c>
     </row>
@@ -26994,12 +26994,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G164">
@@ -27145,7 +27145,7 @@
       </c>
       <c r="AU164" t="inlineStr">
         <is>
-          <t>2026-08-23 15:00:00</t>
+          <t>2026-08-23 14:30:00</t>
         </is>
       </c>
     </row>
@@ -27157,12 +27157,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Nassaji Mazandaran</t>
         </is>
       </c>
       <c r="G165">
@@ -27200,17 +27200,17 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N165">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O165">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="P165">
-        <v>12.7</v>
+        <v>0</v>
       </c>
       <c r="Q165">
         <v>0</v>
@@ -27243,10 +27243,10 @@
         <v>0</v>
       </c>
       <c r="AA165">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB165">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC165">
         <v>0</v>
@@ -27308,7 +27308,7 @@
       </c>
       <c r="AU165" t="inlineStr">
         <is>
-          <t>2026-08-23 15:00:00</t>
+          <t>2026-08-23 14:30:00</t>
         </is>
       </c>
     </row>
@@ -27325,7 +27325,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G166">
@@ -27367,13 +27367,13 @@
         </is>
       </c>
       <c r="N166">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="O166">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="P166">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q166">
         <v>0</v>
@@ -27488,22 +27488,22 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G167">
@@ -27526,17 +27526,17 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N167">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O167">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="P167">
-        <v>0</v>
+        <v>12.7</v>
       </c>
       <c r="Q167">
         <v>0</v>
@@ -27569,10 +27569,10 @@
         <v>0</v>
       </c>
       <c r="AA167">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB167">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC167">
         <v>0</v>
@@ -27651,7 +27651,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G168">
@@ -27693,13 +27693,13 @@
         </is>
       </c>
       <c r="N168">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O168">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P168">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q168">
         <v>0</v>
@@ -27814,22 +27814,22 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G169">
@@ -27977,7 +27977,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G170">
@@ -28135,12 +28135,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G171">
@@ -28182,13 +28182,13 @@
         </is>
       </c>
       <c r="N171">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="O171">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="P171">
-        <v>5.64</v>
+        <v>0</v>
       </c>
       <c r="Q171">
         <v>0</v>
@@ -28286,7 +28286,7 @@
       </c>
       <c r="AU171" t="inlineStr">
         <is>
-          <t>2026-08-23 15:15:00</t>
+          <t>2026-08-23 15:00:00</t>
         </is>
       </c>
     </row>
@@ -28298,12 +28298,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G172">
@@ -28345,13 +28345,13 @@
         </is>
       </c>
       <c r="N172">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="O172">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P172">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Q172">
         <v>0</v>
@@ -28449,7 +28449,7 @@
       </c>
       <c r="AU172" t="inlineStr">
         <is>
-          <t>2026-08-23 15:15:00</t>
+          <t>2026-08-23 15:00:00</t>
         </is>
       </c>
     </row>
@@ -28461,12 +28461,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G173">
@@ -28508,13 +28508,13 @@
         </is>
       </c>
       <c r="N173">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O173">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="P173">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q173">
         <v>0</v>
@@ -28612,7 +28612,7 @@
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>2026-08-23 15:15:00</t>
+          <t>2026-08-23 15:00:00</t>
         </is>
       </c>
     </row>
@@ -28624,12 +28624,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G174">
@@ -28775,7 +28775,7 @@
       </c>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>2026-08-23 15:30:00</t>
+          <t>2026-08-23 15:00:00</t>
         </is>
       </c>
     </row>
@@ -28787,12 +28787,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,13 +28834,13 @@
         </is>
       </c>
       <c r="N175">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O175">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P175">
-        <v>0</v>
+        <v>5.64</v>
       </c>
       <c r="Q175">
         <v>0</v>
@@ -28938,7 +28938,7 @@
       </c>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>2026-08-23 15:30:00</t>
+          <t>2026-08-23 15:15:00</t>
         </is>
       </c>
     </row>
@@ -28950,27 +28950,27 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,13 +28997,13 @@
         </is>
       </c>
       <c r="N176">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O176">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P176">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q176">
         <v>0</v>
@@ -29101,7 +29101,7 @@
       </c>
       <c r="AU176" t="inlineStr">
         <is>
-          <t>2026-08-23 15:30:00</t>
+          <t>2026-08-23 15:15:00</t>
         </is>
       </c>
     </row>
@@ -29113,27 +29113,27 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,13 +29160,13 @@
         </is>
       </c>
       <c r="N177">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O177">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="P177">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q177">
         <v>0</v>
@@ -29264,7 +29264,7 @@
       </c>
       <c r="AU177" t="inlineStr">
         <is>
-          <t>2026-08-23 15:30:00</t>
+          <t>2026-08-23 15:15:00</t>
         </is>
       </c>
     </row>
@@ -29281,22 +29281,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G178">
@@ -29444,7 +29444,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G179">
@@ -29486,13 +29486,13 @@
         </is>
       </c>
       <c r="N179">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="O179">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P179">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Q179">
         <v>0</v>
@@ -29607,22 +29607,22 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G180">
@@ -29770,22 +29770,22 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Batman Petrolspor</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G181">
@@ -29933,22 +29933,22 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G182">
@@ -29975,13 +29975,13 @@
         </is>
       </c>
       <c r="N182">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O182">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P182">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Q182">
         <v>0</v>
@@ -30091,12 +30091,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G183">
@@ -30138,13 +30138,13 @@
         </is>
       </c>
       <c r="N183">
-        <v>1.48</v>
+        <v>2.58</v>
       </c>
       <c r="O183">
-        <v>5.59</v>
+        <v>3.1</v>
       </c>
       <c r="P183">
-        <v>6.15</v>
+        <v>2.77</v>
       </c>
       <c r="Q183">
         <v>0</v>
@@ -30183,10 +30183,10 @@
         <v>0</v>
       </c>
       <c r="AC183">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AD183">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE183">
         <v>0</v>
@@ -30242,7 +30242,7 @@
       </c>
       <c r="AU183" t="inlineStr">
         <is>
-          <t>2026-08-23 15:45:00</t>
+          <t>2026-08-23 15:30:00</t>
         </is>
       </c>
     </row>
@@ -30254,12 +30254,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -30269,12 +30269,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G184">
@@ -30301,13 +30301,13 @@
         </is>
       </c>
       <c r="N184">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="O184">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="P184">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Q184">
         <v>0</v>
@@ -30340,10 +30340,10 @@
         <v>0</v>
       </c>
       <c r="AA184">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB184">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC184">
         <v>0</v>
@@ -30405,7 +30405,7 @@
       </c>
       <c r="AU184" t="inlineStr">
         <is>
-          <t>2026-08-23 15:45:00</t>
+          <t>2026-08-23 15:30:00</t>
         </is>
       </c>
     </row>
@@ -30417,12 +30417,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -30432,12 +30432,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Batman Petrolspor</t>
         </is>
       </c>
       <c r="G185">
@@ -30464,13 +30464,13 @@
         </is>
       </c>
       <c r="N185">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O185">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P185">
-        <v>6.14</v>
+        <v>0</v>
       </c>
       <c r="Q185">
         <v>0</v>
@@ -30503,10 +30503,10 @@
         <v>0</v>
       </c>
       <c r="AA185">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB185">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC185">
         <v>0</v>
@@ -30568,7 +30568,7 @@
       </c>
       <c r="AU185" t="inlineStr">
         <is>
-          <t>2026-08-23 15:45:00</t>
+          <t>2026-08-23 15:30:00</t>
         </is>
       </c>
     </row>
@@ -30580,12 +30580,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G186">
@@ -30627,13 +30627,13 @@
         </is>
       </c>
       <c r="N186">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="O186">
-        <v>3.24</v>
+        <v>3.15</v>
       </c>
       <c r="P186">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="Q186">
         <v>0</v>
@@ -30666,10 +30666,10 @@
         <v>0</v>
       </c>
       <c r="AA186">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB186">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC186">
         <v>0</v>
@@ -30731,7 +30731,7 @@
       </c>
       <c r="AU186" t="inlineStr">
         <is>
-          <t>2026-08-23 16:00:00</t>
+          <t>2026-08-23 15:30:00</t>
         </is>
       </c>
     </row>
@@ -30743,12 +30743,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G187">
@@ -30790,13 +30790,13 @@
         </is>
       </c>
       <c r="N187">
-        <v>1.63</v>
+        <v>1.48</v>
       </c>
       <c r="O187">
-        <v>3.58</v>
+        <v>5.59</v>
       </c>
       <c r="P187">
-        <v>5.71</v>
+        <v>6.15</v>
       </c>
       <c r="Q187">
         <v>0</v>
@@ -30829,16 +30829,16 @@
         <v>0</v>
       </c>
       <c r="AA187">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB187">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC187">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AD187">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE187">
         <v>0</v>
@@ -30894,7 +30894,7 @@
       </c>
       <c r="AU187" t="inlineStr">
         <is>
-          <t>2026-08-23 16:00:00</t>
+          <t>2026-08-23 15:45:00</t>
         </is>
       </c>
     </row>
@@ -30906,12 +30906,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G188">
@@ -30953,13 +30953,13 @@
         </is>
       </c>
       <c r="N188">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="O188">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="P188">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q188">
         <v>0</v>
@@ -30992,10 +30992,10 @@
         <v>0</v>
       </c>
       <c r="AA188">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB188">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC188">
         <v>0</v>
@@ -31057,7 +31057,7 @@
       </c>
       <c r="AU188" t="inlineStr">
         <is>
-          <t>2026-08-23 16:00:00</t>
+          <t>2026-08-23 15:45:00</t>
         </is>
       </c>
     </row>
@@ -31069,12 +31069,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G189">
@@ -31116,13 +31116,13 @@
         </is>
       </c>
       <c r="N189">
-        <v>2.07</v>
+        <v>1.59</v>
       </c>
       <c r="O189">
-        <v>3.04</v>
+        <v>4.5</v>
       </c>
       <c r="P189">
-        <v>3.46</v>
+        <v>6.14</v>
       </c>
       <c r="Q189">
         <v>0</v>
@@ -31155,10 +31155,10 @@
         <v>0</v>
       </c>
       <c r="AA189">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB189">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC189">
         <v>0</v>
@@ -31220,7 +31220,7 @@
       </c>
       <c r="AU189" t="inlineStr">
         <is>
-          <t>2026-08-23 16:00:00</t>
+          <t>2026-08-23 15:45:00</t>
         </is>
       </c>
     </row>
@@ -31237,7 +31237,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G190">
@@ -31279,13 +31279,13 @@
         </is>
       </c>
       <c r="N190">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="O190">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P190">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q190">
         <v>0</v>
@@ -31318,10 +31318,10 @@
         <v>0</v>
       </c>
       <c r="AA190">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB190">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC190">
         <v>0</v>
@@ -31400,22 +31400,22 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G191">
@@ -31442,13 +31442,13 @@
         </is>
       </c>
       <c r="N191">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="O191">
-        <v>4.07</v>
+        <v>3.58</v>
       </c>
       <c r="P191">
-        <v>6.22</v>
+        <v>5.71</v>
       </c>
       <c r="Q191">
         <v>0</v>
@@ -31481,10 +31481,10 @@
         <v>0</v>
       </c>
       <c r="AA191">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AB191">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AC191">
         <v>0</v>
@@ -31563,22 +31563,22 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G192">
@@ -31605,13 +31605,13 @@
         </is>
       </c>
       <c r="N192">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O192">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="P192">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Q192">
         <v>0</v>
@@ -31644,10 +31644,10 @@
         <v>0</v>
       </c>
       <c r="AA192">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB192">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC192">
         <v>0</v>
@@ -31726,22 +31726,22 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G193">
@@ -31768,13 +31768,13 @@
         </is>
       </c>
       <c r="N193">
-        <v>1.91</v>
+        <v>2.07</v>
       </c>
       <c r="O193">
-        <v>3.58</v>
+        <v>3.04</v>
       </c>
       <c r="P193">
-        <v>4.17</v>
+        <v>3.46</v>
       </c>
       <c r="Q193">
         <v>0</v>
@@ -31807,10 +31807,10 @@
         <v>0</v>
       </c>
       <c r="AA193">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB193">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC193">
         <v>0</v>
@@ -31889,22 +31889,22 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="G194">
@@ -32052,7 +32052,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G195">
@@ -32094,13 +32094,13 @@
         </is>
       </c>
       <c r="N195">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O195">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="P195">
-        <v>0</v>
+        <v>6.22</v>
       </c>
       <c r="Q195">
         <v>0</v>
@@ -32133,10 +32133,10 @@
         <v>0</v>
       </c>
       <c r="AA195">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB195">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC195">
         <v>0</v>
@@ -32215,7 +32215,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G196">
@@ -32257,13 +32257,13 @@
         </is>
       </c>
       <c r="N196">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O196">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="P196">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q196">
         <v>0</v>
@@ -32296,10 +32296,10 @@
         <v>0</v>
       </c>
       <c r="AA196">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB196">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC196">
         <v>0</v>
@@ -32378,7 +32378,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G197">
@@ -32420,13 +32420,13 @@
         </is>
       </c>
       <c r="N197">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O197">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P197">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="Q197">
         <v>0</v>
@@ -32459,10 +32459,10 @@
         <v>0</v>
       </c>
       <c r="AA197">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB197">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC197">
         <v>0</v>
@@ -32541,7 +32541,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G198">
@@ -32704,22 +32704,22 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G199">
@@ -32867,22 +32867,22 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G200">
@@ -33030,7 +33030,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G201">
@@ -33193,22 +33193,22 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="G202">
@@ -33356,7 +33356,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -33366,12 +33366,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G203">
@@ -33398,13 +33398,13 @@
         </is>
       </c>
       <c r="N203">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O203">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P203">
-        <v>4.94</v>
+        <v>0</v>
       </c>
       <c r="Q203">
         <v>0</v>
@@ -33519,22 +33519,22 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G204">
@@ -33682,7 +33682,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -33692,12 +33692,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G205">
@@ -33840,12 +33840,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G206">
@@ -33887,13 +33887,13 @@
         </is>
       </c>
       <c r="N206">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="O206">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="P206">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="Q206">
         <v>0</v>
@@ -33991,7 +33991,7 @@
       </c>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>2026-08-23 16:30:00</t>
+          <t>2026-08-23 16:00:00</t>
         </is>
       </c>
     </row>
@@ -34003,12 +34003,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G207">
@@ -34154,7 +34154,7 @@
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>2026-08-23 16:30:00</t>
+          <t>2026-08-23 16:00:00</t>
         </is>
       </c>
     </row>
@@ -34166,12 +34166,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="G208">
@@ -34213,13 +34213,13 @@
         </is>
       </c>
       <c r="N208">
-        <v>1.19</v>
+        <v>1.73</v>
       </c>
       <c r="O208">
-        <v>7.65</v>
+        <v>3.25</v>
       </c>
       <c r="P208">
-        <v>16</v>
+        <v>4.94</v>
       </c>
       <c r="Q208">
         <v>0</v>
@@ -34317,7 +34317,7 @@
       </c>
       <c r="AU208" t="inlineStr">
         <is>
-          <t>2026-08-23 16:30:00</t>
+          <t>2026-08-23 16:00:00</t>
         </is>
       </c>
     </row>
@@ -34329,12 +34329,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G209">
@@ -34480,7 +34480,7 @@
       </c>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>2026-08-23 17:00:00</t>
+          <t>2026-08-23 16:00:00</t>
         </is>
       </c>
     </row>
@@ -34492,12 +34492,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G210">
@@ -34539,13 +34539,13 @@
         </is>
       </c>
       <c r="N210">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O210">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P210">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q210">
         <v>0</v>
@@ -34643,7 +34643,7 @@
       </c>
       <c r="AU210" t="inlineStr">
         <is>
-          <t>2026-08-23 17:00:00</t>
+          <t>2026-08-23 16:00:00</t>
         </is>
       </c>
     </row>
@@ -34655,27 +34655,27 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G211">
@@ -34702,13 +34702,13 @@
         </is>
       </c>
       <c r="N211">
-        <v>3.32</v>
+        <v>2.81</v>
       </c>
       <c r="O211">
-        <v>3.01</v>
+        <v>3.46</v>
       </c>
       <c r="P211">
-        <v>2.29</v>
+        <v>2.52</v>
       </c>
       <c r="Q211">
         <v>0</v>
@@ -34806,7 +34806,7 @@
       </c>
       <c r="AU211" t="inlineStr">
         <is>
-          <t>2026-08-23 17:30:00</t>
+          <t>2026-08-23 16:30:00</t>
         </is>
       </c>
     </row>
@@ -34818,27 +34818,27 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G212">
@@ -34865,13 +34865,13 @@
         </is>
       </c>
       <c r="N212">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="O212">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="P212">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Q212">
         <v>0</v>
@@ -34969,7 +34969,7 @@
       </c>
       <c r="AU212" t="inlineStr">
         <is>
-          <t>2026-08-23 17:30:00</t>
+          <t>2026-08-23 16:30:00</t>
         </is>
       </c>
     </row>
@@ -34981,27 +34981,27 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G213">
@@ -35028,13 +35028,13 @@
         </is>
       </c>
       <c r="N213">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="O213">
-        <v>0</v>
+        <v>7.65</v>
       </c>
       <c r="P213">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q213">
         <v>0</v>
@@ -35132,7 +35132,7 @@
       </c>
       <c r="AU213" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:00</t>
+          <t>2026-08-23 16:30:00</t>
         </is>
       </c>
     </row>
@@ -35144,12 +35144,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G214">
@@ -35295,7 +35295,7 @@
       </c>
       <c r="AU214" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:00</t>
+          <t>2026-08-23 17:00:00</t>
         </is>
       </c>
     </row>
@@ -35307,12 +35307,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G215">
@@ -35354,13 +35354,13 @@
         </is>
       </c>
       <c r="N215">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O215">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P215">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q215">
         <v>0</v>
@@ -35458,7 +35458,7 @@
       </c>
       <c r="AU215" t="inlineStr">
         <is>
-          <t>2026-08-23 18:15:00</t>
+          <t>2026-08-23 17:00:00</t>
         </is>
       </c>
     </row>
@@ -35470,12 +35470,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -35485,12 +35485,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G216">
@@ -35517,13 +35517,13 @@
         </is>
       </c>
       <c r="N216">
-        <v>3.44</v>
+        <v>3.32</v>
       </c>
       <c r="O216">
-        <v>3.42</v>
+        <v>3.01</v>
       </c>
       <c r="P216">
-        <v>2.18</v>
+        <v>2.29</v>
       </c>
       <c r="Q216">
         <v>0</v>
@@ -35621,7 +35621,7 @@
       </c>
       <c r="AU216" t="inlineStr">
         <is>
-          <t>2026-08-23 18:30:00</t>
+          <t>2026-08-23 17:30:00</t>
         </is>
       </c>
     </row>
@@ -35633,12 +35633,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -35648,12 +35648,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G217">
@@ -35680,13 +35680,13 @@
         </is>
       </c>
       <c r="N217">
-        <v>2.13</v>
+        <v>2.59</v>
       </c>
       <c r="O217">
-        <v>3.44</v>
+        <v>3.57</v>
       </c>
       <c r="P217">
-        <v>3.55</v>
+        <v>2.74</v>
       </c>
       <c r="Q217">
         <v>0</v>
@@ -35784,7 +35784,7 @@
       </c>
       <c r="AU217" t="inlineStr">
         <is>
-          <t>2026-08-23 18:30:00</t>
+          <t>2026-08-23 17:30:00</t>
         </is>
       </c>
     </row>
@@ -35796,12 +35796,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -35811,12 +35811,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G218">
@@ -35947,7 +35947,7 @@
       </c>
       <c r="AU218" t="inlineStr">
         <is>
-          <t>2026-08-23 18:30:00</t>
+          <t>2026-08-23 18:00:00</t>
         </is>
       </c>
     </row>
@@ -35959,12 +35959,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -35974,12 +35974,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G219">
@@ -36110,7 +36110,7 @@
       </c>
       <c r="AU219" t="inlineStr">
         <is>
-          <t>2026-08-23 18:30:00</t>
+          <t>2026-08-23 18:00:00</t>
         </is>
       </c>
     </row>
@@ -36122,12 +36122,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -36137,12 +36137,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G220">
@@ -36273,7 +36273,7 @@
       </c>
       <c r="AU220" t="inlineStr">
         <is>
-          <t>2026-08-23 18:30:00</t>
+          <t>2026-08-23 18:15:00</t>
         </is>
       </c>
     </row>
@@ -36285,12 +36285,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -36300,12 +36300,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G221">
@@ -36332,13 +36332,13 @@
         </is>
       </c>
       <c r="N221">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="O221">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P221">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q221">
         <v>0</v>
@@ -36436,7 +36436,7 @@
       </c>
       <c r="AU221" t="inlineStr">
         <is>
-          <t>2026-08-23 19:00:00</t>
+          <t>2026-08-23 18:30:00</t>
         </is>
       </c>
     </row>
@@ -36448,7 +36448,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -36463,12 +36463,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G222">
@@ -36495,13 +36495,13 @@
         </is>
       </c>
       <c r="N222">
-        <v>2.92</v>
+        <v>2.13</v>
       </c>
       <c r="O222">
-        <v>3.15</v>
+        <v>3.44</v>
       </c>
       <c r="P222">
-        <v>2.62</v>
+        <v>3.55</v>
       </c>
       <c r="Q222">
         <v>0</v>
@@ -36599,7 +36599,7 @@
       </c>
       <c r="AU222" t="inlineStr">
         <is>
-          <t>2026-08-23 19:30:00</t>
+          <t>2026-08-23 18:30:00</t>
         </is>
       </c>
     </row>
@@ -36611,12 +36611,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -36626,12 +36626,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G223">
@@ -36762,7 +36762,7 @@
       </c>
       <c r="AU223" t="inlineStr">
         <is>
-          <t>2026-08-23 20:00:00</t>
+          <t>2026-08-23 18:30:00</t>
         </is>
       </c>
     </row>
@@ -36774,12 +36774,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -36789,12 +36789,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G224">
@@ -36821,13 +36821,13 @@
         </is>
       </c>
       <c r="N224">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="O224">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="P224">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="Q224">
         <v>0</v>
@@ -36925,7 +36925,7 @@
       </c>
       <c r="AU224" t="inlineStr">
         <is>
-          <t>2026-08-23 20:00:00</t>
+          <t>2026-08-23 18:30:00</t>
         </is>
       </c>
     </row>
@@ -36937,12 +36937,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -36952,12 +36952,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G225">
@@ -37088,7 +37088,7 @@
       </c>
       <c r="AU225" t="inlineStr">
         <is>
-          <t>2026-08-23 20:30:00</t>
+          <t>2026-08-23 18:30:00</t>
         </is>
       </c>
     </row>
@@ -37100,12 +37100,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -37115,12 +37115,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G226">
@@ -37147,13 +37147,13 @@
         </is>
       </c>
       <c r="N226">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O226">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P226">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="Q226">
         <v>0</v>
@@ -37251,7 +37251,7 @@
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>2026-08-23 20:30:00</t>
+          <t>2026-08-23 19:00:00</t>
         </is>
       </c>
     </row>
@@ -37263,12 +37263,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G227">
@@ -37310,13 +37310,13 @@
         </is>
       </c>
       <c r="N227">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O227">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P227">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q227">
         <v>0</v>
@@ -37414,7 +37414,7 @@
       </c>
       <c r="AU227" t="inlineStr">
         <is>
-          <t>2026-08-23 21:00:00</t>
+          <t>2026-08-23 19:30:00</t>
         </is>
       </c>
     </row>
@@ -37426,12 +37426,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G228">
@@ -37577,7 +37577,7 @@
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>2026-08-23 21:00:00</t>
+          <t>2026-08-23 20:00:00</t>
         </is>
       </c>
     </row>
@@ -37589,12 +37589,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G229">
@@ -37636,13 +37636,13 @@
         </is>
       </c>
       <c r="N229">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O229">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="P229">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="Q229">
         <v>0</v>
@@ -37740,7 +37740,7 @@
       </c>
       <c r="AU229" t="inlineStr">
         <is>
-          <t>2026-08-23 21:00:00</t>
+          <t>2026-08-23 20:00:00</t>
         </is>
       </c>
     </row>
@@ -37752,27 +37752,27 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G230">
@@ -37903,7 +37903,7 @@
       </c>
       <c r="AU230" t="inlineStr">
         <is>
-          <t>2026-08-23 21:00:00</t>
+          <t>2026-08-23 20:30:00</t>
         </is>
       </c>
     </row>
@@ -37915,12 +37915,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -37930,12 +37930,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="G231">
@@ -37962,13 +37962,13 @@
         </is>
       </c>
       <c r="N231">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="O231">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P231">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q231">
         <v>0</v>
@@ -38001,10 +38001,10 @@
         <v>0</v>
       </c>
       <c r="AA231">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB231">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC231">
         <v>0</v>
@@ -38066,7 +38066,7 @@
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>2026-08-23 21:00:00</t>
+          <t>2026-08-23 20:30:00</t>
         </is>
       </c>
     </row>
@@ -38083,151 +38083,966 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
+          <t>Uzbekistan Uzbekistan Super League</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Andijan</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Xorazm</t>
+        </is>
+      </c>
+      <c r="G232">
+        <v>0</v>
+      </c>
+      <c r="H232">
+        <v>0</v>
+      </c>
+      <c r="I232">
+        <v>0</v>
+      </c>
+      <c r="J232">
+        <v>0</v>
+      </c>
+      <c r="K232">
+        <v>0</v>
+      </c>
+      <c r="L232">
+        <v>0</v>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N232">
+        <v>0</v>
+      </c>
+      <c r="O232">
+        <v>0</v>
+      </c>
+      <c r="P232">
+        <v>0</v>
+      </c>
+      <c r="Q232">
+        <v>0</v>
+      </c>
+      <c r="R232">
+        <v>0</v>
+      </c>
+      <c r="S232">
+        <v>0</v>
+      </c>
+      <c r="T232">
+        <v>0</v>
+      </c>
+      <c r="U232">
+        <v>0</v>
+      </c>
+      <c r="V232">
+        <v>0</v>
+      </c>
+      <c r="W232">
+        <v>0</v>
+      </c>
+      <c r="X232">
+        <v>0</v>
+      </c>
+      <c r="Y232">
+        <v>0</v>
+      </c>
+      <c r="Z232">
+        <v>0</v>
+      </c>
+      <c r="AA232">
+        <v>0</v>
+      </c>
+      <c r="AB232">
+        <v>0</v>
+      </c>
+      <c r="AC232">
+        <v>0</v>
+      </c>
+      <c r="AD232">
+        <v>0</v>
+      </c>
+      <c r="AE232">
+        <v>0</v>
+      </c>
+      <c r="AF232">
+        <v>0</v>
+      </c>
+      <c r="AG232">
+        <v>0</v>
+      </c>
+      <c r="AH232" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI232" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ232">
+        <v>0</v>
+      </c>
+      <c r="AK232">
+        <v>0</v>
+      </c>
+      <c r="AL232">
+        <v>0</v>
+      </c>
+      <c r="AM232">
+        <v>-1</v>
+      </c>
+      <c r="AN232">
+        <v>-1</v>
+      </c>
+      <c r="AO232">
+        <v>-1</v>
+      </c>
+      <c r="AP232">
+        <v>-1</v>
+      </c>
+      <c r="AQ232">
+        <v>0</v>
+      </c>
+      <c r="AR232">
+        <v>0</v>
+      </c>
+      <c r="AS232">
+        <v>0</v>
+      </c>
+      <c r="AT232">
+        <v>0</v>
+      </c>
+      <c r="AU232" t="inlineStr">
+        <is>
+          <t>2026-08-23 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Uzbekistan Uzbekistan Super League</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Termez Surkhon</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>AGMK</t>
+        </is>
+      </c>
+      <c r="G233">
+        <v>0</v>
+      </c>
+      <c r="H233">
+        <v>0</v>
+      </c>
+      <c r="I233">
+        <v>0</v>
+      </c>
+      <c r="J233">
+        <v>0</v>
+      </c>
+      <c r="K233">
+        <v>0</v>
+      </c>
+      <c r="L233">
+        <v>0</v>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N233">
+        <v>0</v>
+      </c>
+      <c r="O233">
+        <v>0</v>
+      </c>
+      <c r="P233">
+        <v>0</v>
+      </c>
+      <c r="Q233">
+        <v>0</v>
+      </c>
+      <c r="R233">
+        <v>0</v>
+      </c>
+      <c r="S233">
+        <v>0</v>
+      </c>
+      <c r="T233">
+        <v>0</v>
+      </c>
+      <c r="U233">
+        <v>0</v>
+      </c>
+      <c r="V233">
+        <v>0</v>
+      </c>
+      <c r="W233">
+        <v>0</v>
+      </c>
+      <c r="X233">
+        <v>0</v>
+      </c>
+      <c r="Y233">
+        <v>0</v>
+      </c>
+      <c r="Z233">
+        <v>0</v>
+      </c>
+      <c r="AA233">
+        <v>0</v>
+      </c>
+      <c r="AB233">
+        <v>0</v>
+      </c>
+      <c r="AC233">
+        <v>0</v>
+      </c>
+      <c r="AD233">
+        <v>0</v>
+      </c>
+      <c r="AE233">
+        <v>0</v>
+      </c>
+      <c r="AF233">
+        <v>0</v>
+      </c>
+      <c r="AG233">
+        <v>0</v>
+      </c>
+      <c r="AH233" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI233" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ233">
+        <v>0</v>
+      </c>
+      <c r="AK233">
+        <v>0</v>
+      </c>
+      <c r="AL233">
+        <v>0</v>
+      </c>
+      <c r="AM233">
+        <v>-1</v>
+      </c>
+      <c r="AN233">
+        <v>-1</v>
+      </c>
+      <c r="AO233">
+        <v>-1</v>
+      </c>
+      <c r="AP233">
+        <v>-1</v>
+      </c>
+      <c r="AQ233">
+        <v>0</v>
+      </c>
+      <c r="AR233">
+        <v>0</v>
+      </c>
+      <c r="AS233">
+        <v>0</v>
+      </c>
+      <c r="AT233">
+        <v>0</v>
+      </c>
+      <c r="AU233" t="inlineStr">
+        <is>
+          <t>2026-08-23 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Uzbekistan Uzbekistan Super League</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Dinamo Samarqand</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Pakhtakor</t>
+        </is>
+      </c>
+      <c r="G234">
+        <v>0</v>
+      </c>
+      <c r="H234">
+        <v>0</v>
+      </c>
+      <c r="I234">
+        <v>0</v>
+      </c>
+      <c r="J234">
+        <v>0</v>
+      </c>
+      <c r="K234">
+        <v>0</v>
+      </c>
+      <c r="L234">
+        <v>0</v>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N234">
+        <v>0</v>
+      </c>
+      <c r="O234">
+        <v>0</v>
+      </c>
+      <c r="P234">
+        <v>0</v>
+      </c>
+      <c r="Q234">
+        <v>0</v>
+      </c>
+      <c r="R234">
+        <v>0</v>
+      </c>
+      <c r="S234">
+        <v>0</v>
+      </c>
+      <c r="T234">
+        <v>0</v>
+      </c>
+      <c r="U234">
+        <v>0</v>
+      </c>
+      <c r="V234">
+        <v>0</v>
+      </c>
+      <c r="W234">
+        <v>0</v>
+      </c>
+      <c r="X234">
+        <v>0</v>
+      </c>
+      <c r="Y234">
+        <v>0</v>
+      </c>
+      <c r="Z234">
+        <v>0</v>
+      </c>
+      <c r="AA234">
+        <v>0</v>
+      </c>
+      <c r="AB234">
+        <v>0</v>
+      </c>
+      <c r="AC234">
+        <v>0</v>
+      </c>
+      <c r="AD234">
+        <v>0</v>
+      </c>
+      <c r="AE234">
+        <v>0</v>
+      </c>
+      <c r="AF234">
+        <v>0</v>
+      </c>
+      <c r="AG234">
+        <v>0</v>
+      </c>
+      <c r="AH234" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI234" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ234">
+        <v>0</v>
+      </c>
+      <c r="AK234">
+        <v>0</v>
+      </c>
+      <c r="AL234">
+        <v>0</v>
+      </c>
+      <c r="AM234">
+        <v>-1</v>
+      </c>
+      <c r="AN234">
+        <v>-1</v>
+      </c>
+      <c r="AO234">
+        <v>-1</v>
+      </c>
+      <c r="AP234">
+        <v>-1</v>
+      </c>
+      <c r="AQ234">
+        <v>0</v>
+      </c>
+      <c r="AR234">
+        <v>0</v>
+      </c>
+      <c r="AS234">
+        <v>0</v>
+      </c>
+      <c r="AT234">
+        <v>0</v>
+      </c>
+      <c r="AU234" t="inlineStr">
+        <is>
+          <t>2026-08-23 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Russia FNL</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Rotor Volgograd</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Neftekhimik</t>
+        </is>
+      </c>
+      <c r="G235">
+        <v>0</v>
+      </c>
+      <c r="H235">
+        <v>0</v>
+      </c>
+      <c r="I235">
+        <v>0</v>
+      </c>
+      <c r="J235">
+        <v>0</v>
+      </c>
+      <c r="K235">
+        <v>0</v>
+      </c>
+      <c r="L235">
+        <v>0</v>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N235">
+        <v>0</v>
+      </c>
+      <c r="O235">
+        <v>0</v>
+      </c>
+      <c r="P235">
+        <v>0</v>
+      </c>
+      <c r="Q235">
+        <v>0</v>
+      </c>
+      <c r="R235">
+        <v>0</v>
+      </c>
+      <c r="S235">
+        <v>0</v>
+      </c>
+      <c r="T235">
+        <v>0</v>
+      </c>
+      <c r="U235">
+        <v>0</v>
+      </c>
+      <c r="V235">
+        <v>0</v>
+      </c>
+      <c r="W235">
+        <v>0</v>
+      </c>
+      <c r="X235">
+        <v>0</v>
+      </c>
+      <c r="Y235">
+        <v>0</v>
+      </c>
+      <c r="Z235">
+        <v>0</v>
+      </c>
+      <c r="AA235">
+        <v>0</v>
+      </c>
+      <c r="AB235">
+        <v>0</v>
+      </c>
+      <c r="AC235">
+        <v>0</v>
+      </c>
+      <c r="AD235">
+        <v>0</v>
+      </c>
+      <c r="AE235">
+        <v>0</v>
+      </c>
+      <c r="AF235">
+        <v>0</v>
+      </c>
+      <c r="AG235">
+        <v>0</v>
+      </c>
+      <c r="AH235" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI235" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ235">
+        <v>0</v>
+      </c>
+      <c r="AK235">
+        <v>0</v>
+      </c>
+      <c r="AL235">
+        <v>0</v>
+      </c>
+      <c r="AM235">
+        <v>-1</v>
+      </c>
+      <c r="AN235">
+        <v>-1</v>
+      </c>
+      <c r="AO235">
+        <v>-1</v>
+      </c>
+      <c r="AP235">
+        <v>-1</v>
+      </c>
+      <c r="AQ235">
+        <v>0</v>
+      </c>
+      <c r="AR235">
+        <v>0</v>
+      </c>
+      <c r="AS235">
+        <v>0</v>
+      </c>
+      <c r="AT235">
+        <v>0</v>
+      </c>
+      <c r="AU235" t="inlineStr">
+        <is>
+          <t>2026-08-23 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>LDU Quito</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="G236">
+        <v>0</v>
+      </c>
+      <c r="H236">
+        <v>0</v>
+      </c>
+      <c r="I236">
+        <v>0</v>
+      </c>
+      <c r="J236">
+        <v>0</v>
+      </c>
+      <c r="K236">
+        <v>0</v>
+      </c>
+      <c r="L236">
+        <v>0</v>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N236">
+        <v>1.48</v>
+      </c>
+      <c r="O236">
+        <v>3.8</v>
+      </c>
+      <c r="P236">
+        <v>7</v>
+      </c>
+      <c r="Q236">
+        <v>0</v>
+      </c>
+      <c r="R236">
+        <v>0</v>
+      </c>
+      <c r="S236">
+        <v>0</v>
+      </c>
+      <c r="T236">
+        <v>0</v>
+      </c>
+      <c r="U236">
+        <v>0</v>
+      </c>
+      <c r="V236">
+        <v>0</v>
+      </c>
+      <c r="W236">
+        <v>0</v>
+      </c>
+      <c r="X236">
+        <v>0</v>
+      </c>
+      <c r="Y236">
+        <v>0</v>
+      </c>
+      <c r="Z236">
+        <v>0</v>
+      </c>
+      <c r="AA236">
+        <v>2.03</v>
+      </c>
+      <c r="AB236">
+        <v>1.78</v>
+      </c>
+      <c r="AC236">
+        <v>0</v>
+      </c>
+      <c r="AD236">
+        <v>0</v>
+      </c>
+      <c r="AE236">
+        <v>0</v>
+      </c>
+      <c r="AF236">
+        <v>0</v>
+      </c>
+      <c r="AG236">
+        <v>0</v>
+      </c>
+      <c r="AH236" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI236" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ236">
+        <v>0</v>
+      </c>
+      <c r="AK236">
+        <v>0</v>
+      </c>
+      <c r="AL236">
+        <v>0</v>
+      </c>
+      <c r="AM236">
+        <v>-1</v>
+      </c>
+      <c r="AN236">
+        <v>-1</v>
+      </c>
+      <c r="AO236">
+        <v>-1</v>
+      </c>
+      <c r="AP236">
+        <v>-1</v>
+      </c>
+      <c r="AQ236">
+        <v>0</v>
+      </c>
+      <c r="AR236">
+        <v>0</v>
+      </c>
+      <c r="AS236">
+        <v>0</v>
+      </c>
+      <c r="AT236">
+        <v>0</v>
+      </c>
+      <c r="AU236" t="inlineStr">
+        <is>
+          <t>2026-08-23 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr">
+      <c r="D237" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E232" t="inlineStr">
+      <c r="E237" t="inlineStr">
         <is>
           <t>Angel City</t>
         </is>
       </c>
-      <c r="F232" t="inlineStr">
+      <c r="F237" t="inlineStr">
         <is>
           <t>Gotham FC</t>
         </is>
       </c>
-      <c r="G232">
-        <v>0</v>
-      </c>
-      <c r="H232">
-        <v>0</v>
-      </c>
-      <c r="I232">
-        <v>0</v>
-      </c>
-      <c r="J232">
-        <v>0</v>
-      </c>
-      <c r="K232">
-        <v>0</v>
-      </c>
-      <c r="L232">
-        <v>0</v>
-      </c>
-      <c r="M232" t="inlineStr">
+      <c r="G237">
+        <v>0</v>
+      </c>
+      <c r="H237">
+        <v>0</v>
+      </c>
+      <c r="I237">
+        <v>0</v>
+      </c>
+      <c r="J237">
+        <v>0</v>
+      </c>
+      <c r="K237">
+        <v>0</v>
+      </c>
+      <c r="L237">
+        <v>0</v>
+      </c>
+      <c r="M237" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N232">
+      <c r="N237">
         <v>3.35</v>
       </c>
-      <c r="O232">
+      <c r="O237">
         <v>3.05</v>
       </c>
-      <c r="P232">
+      <c r="P237">
         <v>1.95</v>
       </c>
-      <c r="Q232">
-        <v>0</v>
-      </c>
-      <c r="R232">
-        <v>0</v>
-      </c>
-      <c r="S232">
-        <v>0</v>
-      </c>
-      <c r="T232">
-        <v>0</v>
-      </c>
-      <c r="U232">
-        <v>0</v>
-      </c>
-      <c r="V232">
-        <v>0</v>
-      </c>
-      <c r="W232">
-        <v>0</v>
-      </c>
-      <c r="X232">
-        <v>0</v>
-      </c>
-      <c r="Y232">
-        <v>0</v>
-      </c>
-      <c r="Z232">
-        <v>0</v>
-      </c>
-      <c r="AA232">
-        <v>0</v>
-      </c>
-      <c r="AB232">
-        <v>0</v>
-      </c>
-      <c r="AC232">
-        <v>0</v>
-      </c>
-      <c r="AD232">
-        <v>0</v>
-      </c>
-      <c r="AE232">
-        <v>0</v>
-      </c>
-      <c r="AF232">
-        <v>0</v>
-      </c>
-      <c r="AG232">
-        <v>0</v>
-      </c>
-      <c r="AH232" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI232" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ232">
-        <v>0</v>
-      </c>
-      <c r="AK232">
-        <v>0</v>
-      </c>
-      <c r="AL232">
-        <v>0</v>
-      </c>
-      <c r="AM232">
-        <v>-1</v>
-      </c>
-      <c r="AN232">
-        <v>-1</v>
-      </c>
-      <c r="AO232">
-        <v>-1</v>
-      </c>
-      <c r="AP232">
-        <v>-1</v>
-      </c>
-      <c r="AQ232">
-        <v>0</v>
-      </c>
-      <c r="AR232">
-        <v>0</v>
-      </c>
-      <c r="AS232">
-        <v>0</v>
-      </c>
-      <c r="AT232">
-        <v>0</v>
-      </c>
-      <c r="AU232" t="inlineStr">
+      <c r="Q237">
+        <v>0</v>
+      </c>
+      <c r="R237">
+        <v>0</v>
+      </c>
+      <c r="S237">
+        <v>0</v>
+      </c>
+      <c r="T237">
+        <v>0</v>
+      </c>
+      <c r="U237">
+        <v>0</v>
+      </c>
+      <c r="V237">
+        <v>0</v>
+      </c>
+      <c r="W237">
+        <v>0</v>
+      </c>
+      <c r="X237">
+        <v>0</v>
+      </c>
+      <c r="Y237">
+        <v>0</v>
+      </c>
+      <c r="Z237">
+        <v>0</v>
+      </c>
+      <c r="AA237">
+        <v>0</v>
+      </c>
+      <c r="AB237">
+        <v>0</v>
+      </c>
+      <c r="AC237">
+        <v>0</v>
+      </c>
+      <c r="AD237">
+        <v>0</v>
+      </c>
+      <c r="AE237">
+        <v>0</v>
+      </c>
+      <c r="AF237">
+        <v>0</v>
+      </c>
+      <c r="AG237">
+        <v>0</v>
+      </c>
+      <c r="AH237" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI237" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ237">
+        <v>0</v>
+      </c>
+      <c r="AK237">
+        <v>0</v>
+      </c>
+      <c r="AL237">
+        <v>0</v>
+      </c>
+      <c r="AM237">
+        <v>-1</v>
+      </c>
+      <c r="AN237">
+        <v>-1</v>
+      </c>
+      <c r="AO237">
+        <v>-1</v>
+      </c>
+      <c r="AP237">
+        <v>-1</v>
+      </c>
+      <c r="AQ237">
+        <v>0</v>
+      </c>
+      <c r="AR237">
+        <v>0</v>
+      </c>
+      <c r="AS237">
+        <v>0</v>
+      </c>
+      <c r="AT237">
+        <v>0</v>
+      </c>
+      <c r="AU237" t="inlineStr">
         <is>
           <t>2026-08-23 21:00:00</t>
         </is>

--- a/jogos_2026-08-23.xlsx
+++ b/jogos_2026-08-23.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU237"/>
+  <dimension ref="A1:AU235"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G54">
@@ -9107,17 +9107,17 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N54">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="O54">
-        <v>3.01</v>
+        <v>2.82</v>
       </c>
       <c r="P54">
-        <v>2.81</v>
+        <v>2.92</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G55">
@@ -9270,17 +9270,17 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N55">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="O55">
-        <v>2.82</v>
+        <v>3.01</v>
       </c>
       <c r="P55">
-        <v>2.92</v>
+        <v>2.81</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -9558,22 +9558,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="G57">
@@ -9721,7 +9721,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G58">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Estrela Calheta</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G59">
@@ -10047,22 +10047,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Estrela Calheta</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O60">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P60">
-        <v>4.81</v>
+        <v>0</v>
       </c>
       <c r="Q60">
         <v>0</v>
@@ -10134,10 +10134,10 @@
         <v>0</v>
       </c>
       <c r="AC60">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD60">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE60">
         <v>0</v>
@@ -10210,7 +10210,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>4.81</v>
       </c>
       <c r="Q61">
         <v>0</v>
@@ -10297,10 +10297,10 @@
         <v>0</v>
       </c>
       <c r="AC61">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD61">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G62">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G63">
@@ -10699,22 +10699,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dubai United</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G64">
@@ -10862,7 +10862,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Dubai United</t>
         </is>
       </c>
       <c r="G65">
@@ -11025,7 +11025,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G66">
@@ -11188,7 +11188,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Horsens</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lyngby</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O67">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P67">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q67">
         <v>0</v>
@@ -11351,22 +11351,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Horsens</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Lyngby</t>
         </is>
       </c>
       <c r="G68">
@@ -11389,17 +11389,17 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N68">
-        <v>1.45</v>
+        <v>3</v>
       </c>
       <c r="O68">
-        <v>3.82</v>
+        <v>3.5</v>
       </c>
       <c r="P68">
-        <v>8.949999999999999</v>
+        <v>2.27</v>
       </c>
       <c r="Q68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.88</v>
+        <v>1.45</v>
       </c>
       <c r="O69">
-        <v>3.32</v>
+        <v>3.82</v>
       </c>
       <c r="P69">
-        <v>4.33</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -11677,22 +11677,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G70">
@@ -11715,17 +11715,17 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N70">
-        <v>2.42</v>
+        <v>1.88</v>
       </c>
       <c r="O70">
-        <v>3.44</v>
+        <v>3.32</v>
       </c>
       <c r="P70">
-        <v>2.92</v>
+        <v>4.33</v>
       </c>
       <c r="Q70">
         <v>0</v>
@@ -11758,10 +11758,10 @@
         <v>0</v>
       </c>
       <c r="AA70">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB70">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC70">
         <v>0</v>
@@ -11835,12 +11835,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O71">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -11921,10 +11921,10 @@
         <v>0</v>
       </c>
       <c r="AA71">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB71">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC71">
         <v>0</v>
@@ -11986,7 +11986,7 @@
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>2026-08-23 11:30:00</t>
+          <t>2026-08-23 11:00:00</t>
         </is>
       </c>
     </row>
@@ -12003,7 +12003,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G72">
@@ -12041,17 +12041,17 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N72">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="O72">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P72">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q72">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="N73">
-        <v>1.96</v>
+        <v>4.35</v>
       </c>
       <c r="O73">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P73">
-        <v>3.45</v>
+        <v>1.63</v>
       </c>
       <c r="Q73">
         <v>0</v>
@@ -12329,22 +12329,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G74">
@@ -12367,17 +12367,17 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N74">
-        <v>1.47</v>
+        <v>1.96</v>
       </c>
       <c r="O74">
-        <v>4.55</v>
+        <v>3.5</v>
       </c>
       <c r="P74">
-        <v>5.96</v>
+        <v>3.45</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.05</v>
+        <v>1.47</v>
       </c>
       <c r="O75">
-        <v>3.46</v>
+        <v>4.55</v>
       </c>
       <c r="P75">
-        <v>3.44</v>
+        <v>5.96</v>
       </c>
       <c r="Q75">
         <v>0</v>
@@ -12573,10 +12573,10 @@
         <v>0</v>
       </c>
       <c r="AA75">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB75">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC75">
         <v>0</v>
@@ -12655,22 +12655,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>4.2</v>
+        <v>2.05</v>
       </c>
       <c r="O76">
-        <v>3.35</v>
+        <v>3.46</v>
       </c>
       <c r="P76">
-        <v>1.81</v>
+        <v>3.44</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -12736,10 +12736,10 @@
         <v>0</v>
       </c>
       <c r="AA76">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB76">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC76">
         <v>0</v>
@@ -12818,7 +12818,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,13 +12860,13 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.85</v>
+        <v>4.2</v>
       </c>
       <c r="O77">
-        <v>3.78</v>
+        <v>3.35</v>
       </c>
       <c r="P77">
-        <v>4.42</v>
+        <v>1.81</v>
       </c>
       <c r="Q77">
         <v>0</v>
@@ -12899,10 +12899,10 @@
         <v>0</v>
       </c>
       <c r="AA77">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB77">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC77">
         <v>0</v>
@@ -12976,12 +12976,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,13 +13023,13 @@
         </is>
       </c>
       <c r="N78">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O78">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P78">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="Q78">
         <v>0</v>
@@ -13062,10 +13062,10 @@
         <v>0</v>
       </c>
       <c r="AA78">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB78">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC78">
         <v>0</v>
@@ -13127,7 +13127,7 @@
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>2026-08-23 11:45:00</t>
+          <t>2026-08-23 11:30:00</t>
         </is>
       </c>
     </row>
@@ -13144,7 +13144,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,13 +13186,13 @@
         </is>
       </c>
       <c r="N79">
-        <v>6.02</v>
+        <v>0</v>
       </c>
       <c r="O79">
-        <v>4.49</v>
+        <v>0</v>
       </c>
       <c r="P79">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Q79">
         <v>0</v>
@@ -13307,7 +13307,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>0</v>
+        <v>6.02</v>
       </c>
       <c r="O80">
-        <v>0</v>
+        <v>4.49</v>
       </c>
       <c r="P80">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q80">
         <v>0</v>
@@ -13465,12 +13465,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Unia Skierniewice</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G81">
@@ -13616,7 +13616,7 @@
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>2026-08-23 12:00:00</t>
+          <t>2026-08-23 11:45:00</t>
         </is>
       </c>
     </row>
@@ -13633,7 +13633,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,13 +13675,13 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O82">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="P82">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="Q82">
         <v>0</v>
@@ -13796,7 +13796,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O83">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="P83">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="Q83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G84">
@@ -13997,7 +13997,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N84">
@@ -14122,22 +14122,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G85">
@@ -14160,17 +14160,17 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N85">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="O85">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="P85">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q85">
         <v>0</v>
@@ -14285,22 +14285,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O86">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P86">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q86">
         <v>0</v>
@@ -14448,7 +14448,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G87">
@@ -14611,22 +14611,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="G88">
@@ -14649,17 +14649,17 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N88">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="O88">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="P88">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q88">
         <v>0</v>
@@ -14769,27 +14769,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G89">
@@ -14812,17 +14812,17 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N89">
-        <v>3.58</v>
+        <v>3.52</v>
       </c>
       <c r="O89">
-        <v>4.02</v>
+        <v>3.12</v>
       </c>
       <c r="P89">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -14855,10 +14855,10 @@
         <v>0</v>
       </c>
       <c r="AA89">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB89">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC89">
         <v>0</v>
@@ -14920,7 +14920,7 @@
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>2026-08-23 12:15:00</t>
+          <t>2026-08-23 12:00:00</t>
         </is>
       </c>
     </row>
@@ -14932,12 +14932,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,13 +14979,13 @@
         </is>
       </c>
       <c r="N90">
-        <v>3.05</v>
+        <v>3.58</v>
       </c>
       <c r="O90">
-        <v>4.03</v>
+        <v>4.02</v>
       </c>
       <c r="P90">
-        <v>2.28</v>
+        <v>2.05</v>
       </c>
       <c r="Q90">
         <v>0</v>
@@ -15018,16 +15018,16 @@
         <v>0</v>
       </c>
       <c r="AA90">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB90">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC90">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD90">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE90">
         <v>0</v>
@@ -15083,7 +15083,7 @@
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>2026-08-23 12:30:00</t>
+          <t>2026-08-23 12:15:00</t>
         </is>
       </c>
     </row>
@@ -15100,22 +15100,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,13 +15142,13 @@
         </is>
       </c>
       <c r="N91">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O91">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="P91">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q91">
         <v>0</v>
@@ -15187,10 +15187,10 @@
         <v>0</v>
       </c>
       <c r="AC91">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD91">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE91">
         <v>0</v>
@@ -15263,22 +15263,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,13 +15305,13 @@
         </is>
       </c>
       <c r="N92">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="O92">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P92">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="Q92">
         <v>0</v>
@@ -15426,7 +15426,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.78</v>
+        <v>1.94</v>
       </c>
       <c r="O93">
-        <v>3.34</v>
+        <v>3.54</v>
       </c>
       <c r="P93">
-        <v>2.27</v>
+        <v>3.63</v>
       </c>
       <c r="Q93">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R93">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S93">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T93">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="U93">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V93">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W93">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X93">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y93">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z93">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA93">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB93">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC93">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AD93">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE93">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF93">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG93">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK93">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>ETO</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,65 +15631,65 @@
         </is>
       </c>
       <c r="N94">
+        <v>2.78</v>
+      </c>
+      <c r="O94">
+        <v>3.34</v>
+      </c>
+      <c r="P94">
+        <v>2.27</v>
+      </c>
+      <c r="Q94">
+        <v>3.3</v>
+      </c>
+      <c r="R94">
+        <v>2.2</v>
+      </c>
+      <c r="S94">
+        <v>1.32</v>
+      </c>
+      <c r="T94">
+        <v>2.96</v>
+      </c>
+      <c r="U94">
+        <v>2.5</v>
+      </c>
+      <c r="V94">
+        <v>1.44</v>
+      </c>
+      <c r="W94">
+        <v>1.07</v>
+      </c>
+      <c r="X94">
+        <v>1.04</v>
+      </c>
+      <c r="Y94">
+        <v>1.21</v>
+      </c>
+      <c r="Z94">
+        <v>3.58</v>
+      </c>
+      <c r="AA94">
+        <v>1.79</v>
+      </c>
+      <c r="AB94">
+        <v>2</v>
+      </c>
+      <c r="AC94">
+        <v>2.74</v>
+      </c>
+      <c r="AD94">
         <v>1.34</v>
       </c>
-      <c r="O94">
-        <v>4.65</v>
-      </c>
-      <c r="P94">
-        <v>7.22</v>
-      </c>
-      <c r="Q94">
-        <v>1.8</v>
-      </c>
-      <c r="R94">
-        <v>2.6</v>
-      </c>
-      <c r="S94">
-        <v>1.26</v>
-      </c>
-      <c r="T94">
-        <v>3.5</v>
-      </c>
-      <c r="U94">
+      <c r="AE94">
+        <v>1.11</v>
+      </c>
+      <c r="AF94">
+        <v>1.57</v>
+      </c>
+      <c r="AG94">
         <v>2.25</v>
       </c>
-      <c r="V94">
-        <v>1.62</v>
-      </c>
-      <c r="W94">
-        <v>1.15</v>
-      </c>
-      <c r="X94">
-        <v>1.03</v>
-      </c>
-      <c r="Y94">
-        <v>1.17</v>
-      </c>
-      <c r="Z94">
-        <v>4.6</v>
-      </c>
-      <c r="AA94">
-        <v>1.56</v>
-      </c>
-      <c r="AB94">
-        <v>2.27</v>
-      </c>
-      <c r="AC94">
-        <v>2.33</v>
-      </c>
-      <c r="AD94">
-        <v>1.48</v>
-      </c>
-      <c r="AE94">
-        <v>1.2</v>
-      </c>
-      <c r="AF94">
-        <v>1.78</v>
-      </c>
-      <c r="AG94">
-        <v>1.91</v>
-      </c>
       <c r="AH94" t="inlineStr">
         <is>
           <t>[]</t>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="AK94">
-        <v>2.88</v>
+        <v>1.36</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15752,7 +15752,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>ETO</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O95">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="P95">
-        <v>0</v>
+        <v>7.22</v>
       </c>
       <c r="Q95">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R95">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S95">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T95">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U95">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V95">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W95">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X95">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y95">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z95">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA95">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB95">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AC95">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD95">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE95">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF95">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG95">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK95">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G96">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G97">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G98">
@@ -16404,7 +16404,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Voluntari</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="O99">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P99">
-        <v>6.63</v>
+        <v>0</v>
       </c>
       <c r="Q99">
         <v>0</v>
@@ -16567,7 +16567,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Voluntari</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,13 +16609,13 @@
         </is>
       </c>
       <c r="N100">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O100">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P100">
-        <v>0</v>
+        <v>6.63</v>
       </c>
       <c r="Q100">
         <v>0</v>
@@ -16730,7 +16730,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G101">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G102">
@@ -17051,27 +17051,27 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G103">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>2026-08-23 12:45:00</t>
+          <t>2026-08-23 12:30:00</t>
         </is>
       </c>
     </row>
@@ -17214,27 +17214,27 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O104">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P104">
-        <v>5.29</v>
+        <v>0</v>
       </c>
       <c r="Q104">
         <v>0</v>
@@ -17365,7 +17365,7 @@
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>2026-08-23 13:00:00</t>
+          <t>2026-08-23 12:45:00</t>
         </is>
       </c>
     </row>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,13 +17424,13 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.21</v>
+        <v>1.61</v>
       </c>
       <c r="O105">
-        <v>3</v>
+        <v>3.44</v>
       </c>
       <c r="P105">
-        <v>3.3</v>
+        <v>5.29</v>
       </c>
       <c r="Q105">
         <v>0</v>
@@ -17545,7 +17545,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,13 +17587,13 @@
         </is>
       </c>
       <c r="N106">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O106">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P106">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G107">
@@ -17871,7 +17871,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Gd Nazarenos</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G108">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Gd Nazarenos</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G109">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Sertanense</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Sertanense</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Fazendense</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>AD Nogueirense</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Fazendense</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>AD Nogueirense</t>
         </is>
       </c>
       <c r="G114">
@@ -19012,7 +19012,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G115">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G116">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G117">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G118">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G119">
@@ -19827,22 +19827,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G120">
@@ -19990,7 +19990,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G121">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G122">
@@ -20316,22 +20316,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Ovarense</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G123">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Ovarense</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G124">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Guarda</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G125">
@@ -20805,7 +20805,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Guarda</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G127">
@@ -21131,22 +21131,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,13 +21173,13 @@
         </is>
       </c>
       <c r="N128">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O128">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="P128">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q128">
         <v>0</v>
@@ -21294,7 +21294,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G129">
@@ -21336,13 +21336,13 @@
         </is>
       </c>
       <c r="N129">
-        <v>2.42</v>
+        <v>4.5</v>
       </c>
       <c r="O129">
-        <v>3.3</v>
+        <v>4.05</v>
       </c>
       <c r="P129">
-        <v>2.6</v>
+        <v>1.59</v>
       </c>
       <c r="Q129">
         <v>0</v>
@@ -21457,22 +21457,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Savoia</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G130">
@@ -21499,13 +21499,13 @@
         </is>
       </c>
       <c r="N130">
-        <v>2.22</v>
+        <v>2.42</v>
       </c>
       <c r="O130">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="P130">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="Q130">
         <v>0</v>
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Savoia</t>
         </is>
       </c>
       <c r="G131">
@@ -21662,13 +21662,13 @@
         </is>
       </c>
       <c r="N131">
-        <v>1.41</v>
+        <v>2.22</v>
       </c>
       <c r="O131">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="P131">
-        <v>6.76</v>
+        <v>3.25</v>
       </c>
       <c r="Q131">
         <v>0</v>
@@ -21783,7 +21783,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mardin BB</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,13 +21825,13 @@
         </is>
       </c>
       <c r="N132">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O132">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P132">
-        <v>0</v>
+        <v>6.76</v>
       </c>
       <c r="Q132">
         <v>0</v>
@@ -21946,7 +21946,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Mardin BB</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,13 +21988,13 @@
         </is>
       </c>
       <c r="N133">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O133">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P133">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q133">
         <v>0</v>
@@ -22109,7 +22109,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,13 +22151,13 @@
         </is>
       </c>
       <c r="N134">
-        <v>5.48</v>
+        <v>0</v>
       </c>
       <c r="O134">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="P134">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q134">
         <v>0</v>
@@ -22190,10 +22190,10 @@
         <v>0</v>
       </c>
       <c r="AA134">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB134">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC134">
         <v>0</v>
@@ -22272,7 +22272,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,13 +22314,13 @@
         </is>
       </c>
       <c r="N135">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O135">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P135">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="Q135">
         <v>0</v>
@@ -22430,27 +22430,27 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,13 +22477,13 @@
         </is>
       </c>
       <c r="N136">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O136">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P136">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q136">
         <v>0</v>
@@ -22581,7 +22581,7 @@
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>2026-08-23 13:15:00</t>
+          <t>2026-08-23 13:00:00</t>
         </is>
       </c>
     </row>
@@ -22593,27 +22593,27 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,13 +22640,13 @@
         </is>
       </c>
       <c r="N137">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="O137">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="P137">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q137">
         <v>0</v>
@@ -22679,10 +22679,10 @@
         <v>0</v>
       </c>
       <c r="AA137">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB137">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC137">
         <v>0</v>
@@ -22744,7 +22744,7 @@
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>2026-08-23 13:30:00</t>
+          <t>2026-08-23 13:00:00</t>
         </is>
       </c>
     </row>
@@ -22756,12 +22756,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="G138">
@@ -22803,13 +22803,13 @@
         </is>
       </c>
       <c r="N138">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O138">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P138">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="Q138">
         <v>0</v>
@@ -22907,7 +22907,7 @@
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>2026-08-23 13:30:00</t>
+          <t>2026-08-23 13:00:00</t>
         </is>
       </c>
     </row>
@@ -22919,27 +22919,27 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G139">
@@ -22966,13 +22966,13 @@
         </is>
       </c>
       <c r="N139">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O139">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P139">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="Q139">
         <v>0</v>
@@ -23005,10 +23005,10 @@
         <v>0</v>
       </c>
       <c r="AA139">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB139">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC139">
         <v>0</v>
@@ -23070,7 +23070,7 @@
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>2026-08-23 13:30:00</t>
+          <t>2026-08-23 13:15:00</t>
         </is>
       </c>
     </row>
@@ -23087,22 +23087,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G140">
@@ -23250,7 +23250,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="G141">
@@ -23413,7 +23413,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G142">
@@ -23455,13 +23455,13 @@
         </is>
       </c>
       <c r="N142">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O142">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P142">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="Q142">
         <v>0</v>
@@ -23494,10 +23494,10 @@
         <v>0</v>
       </c>
       <c r="AA142">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB142">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC142">
         <v>0</v>
@@ -23576,7 +23576,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,13 +23618,13 @@
         </is>
       </c>
       <c r="N143">
-        <v>7.26</v>
+        <v>0</v>
       </c>
       <c r="O143">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="P143">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Q143">
         <v>0</v>
@@ -23657,10 +23657,10 @@
         <v>0</v>
       </c>
       <c r="AA143">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB143">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC143">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,13 +23781,13 @@
         </is>
       </c>
       <c r="N144">
-        <v>2.41</v>
+        <v>7.26</v>
       </c>
       <c r="O144">
-        <v>3.34</v>
+        <v>4.6</v>
       </c>
       <c r="P144">
-        <v>3.34</v>
+        <v>1.51</v>
       </c>
       <c r="Q144">
         <v>0</v>
@@ -23820,10 +23820,10 @@
         <v>0</v>
       </c>
       <c r="AA144">
-        <v>2.15</v>
+        <v>1.77</v>
       </c>
       <c r="AB144">
-        <v>1.63</v>
+        <v>1.96</v>
       </c>
       <c r="AC144">
         <v>0</v>
@@ -23902,7 +23902,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,13 +23944,13 @@
         </is>
       </c>
       <c r="N145">
-        <v>1.27</v>
+        <v>2.41</v>
       </c>
       <c r="O145">
-        <v>6.5</v>
+        <v>3.34</v>
       </c>
       <c r="P145">
-        <v>9.4</v>
+        <v>3.34</v>
       </c>
       <c r="Q145">
         <v>0</v>
@@ -23983,10 +23983,10 @@
         <v>0</v>
       </c>
       <c r="AA145">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB145">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC145">
         <v>0</v>
@@ -24060,12 +24060,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,13 +24107,13 @@
         </is>
       </c>
       <c r="N146">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O146">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="P146">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="Q146">
         <v>0</v>
@@ -24211,7 +24211,7 @@
       </c>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>2026-08-23 13:35:00</t>
+          <t>2026-08-23 13:30:00</t>
         </is>
       </c>
     </row>
@@ -24223,12 +24223,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G147">
@@ -24374,7 +24374,7 @@
       </c>
       <c r="AU147" t="inlineStr">
         <is>
-          <t>2026-08-23 13:45:00</t>
+          <t>2026-08-23 13:35:00</t>
         </is>
       </c>
     </row>
@@ -24386,12 +24386,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G148">
@@ -24433,13 +24433,13 @@
         </is>
       </c>
       <c r="N148">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="O148">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="P148">
-        <v>4.81</v>
+        <v>0</v>
       </c>
       <c r="Q148">
         <v>0</v>
@@ -24472,10 +24472,10 @@
         <v>0</v>
       </c>
       <c r="AA148">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB148">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC148">
         <v>0</v>
@@ -24537,7 +24537,7 @@
       </c>
       <c r="AU148" t="inlineStr">
         <is>
-          <t>2026-08-23 14:00:00</t>
+          <t>2026-08-23 13:45:00</t>
         </is>
       </c>
     </row>
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G149">
@@ -24596,13 +24596,13 @@
         </is>
       </c>
       <c r="N149">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="O149">
-        <v>3.8</v>
+        <v>3.52</v>
       </c>
       <c r="P149">
-        <v>5.83</v>
+        <v>4.81</v>
       </c>
       <c r="Q149">
         <v>0</v>
@@ -24635,10 +24635,10 @@
         <v>0</v>
       </c>
       <c r="AA149">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="AB149">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="AC149">
         <v>0</v>
@@ -24717,7 +24717,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G150">
@@ -24759,13 +24759,13 @@
         </is>
       </c>
       <c r="N150">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="O150">
-        <v>3.92</v>
+        <v>3.8</v>
       </c>
       <c r="P150">
-        <v>4.16</v>
+        <v>5.83</v>
       </c>
       <c r="Q150">
         <v>0</v>
@@ -24798,10 +24798,10 @@
         <v>0</v>
       </c>
       <c r="AA150">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB150">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC150">
         <v>0</v>
@@ -24880,7 +24880,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G151">
@@ -24922,13 +24922,13 @@
         </is>
       </c>
       <c r="N151">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O151">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P151">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="Q151">
         <v>0</v>
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G152">
@@ -25206,7 +25206,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G153">
@@ -25248,13 +25248,13 @@
         </is>
       </c>
       <c r="N153">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O153">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="P153">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,13 +25411,13 @@
         </is>
       </c>
       <c r="N154">
-        <v>1.5</v>
+        <v>2.35</v>
       </c>
       <c r="O154">
-        <v>4.17</v>
+        <v>3.31</v>
       </c>
       <c r="P154">
-        <v>7.31</v>
+        <v>3.19</v>
       </c>
       <c r="Q154">
         <v>0</v>
@@ -25450,10 +25450,10 @@
         <v>0</v>
       </c>
       <c r="AA154">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB154">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC154">
         <v>0</v>
@@ -25532,22 +25532,22 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,13 +25574,13 @@
         </is>
       </c>
       <c r="N155">
-        <v>1.97</v>
+        <v>1.5</v>
       </c>
       <c r="O155">
-        <v>3.7</v>
+        <v>4.17</v>
       </c>
       <c r="P155">
-        <v>3.05</v>
+        <v>7.31</v>
       </c>
       <c r="Q155">
         <v>0</v>
@@ -25613,10 +25613,10 @@
         <v>0</v>
       </c>
       <c r="AA155">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB155">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC155">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,13 +25737,13 @@
         </is>
       </c>
       <c r="N156">
-        <v>4.58</v>
+        <v>1.97</v>
       </c>
       <c r="O156">
-        <v>5.2</v>
+        <v>3.7</v>
       </c>
       <c r="P156">
-        <v>1.51</v>
+        <v>3.05</v>
       </c>
       <c r="Q156">
         <v>0</v>
@@ -25788,7 +25788,7 @@
         <v>0</v>
       </c>
       <c r="AE156">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF156">
         <v>0</v>
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,13 +25900,13 @@
         </is>
       </c>
       <c r="N157">
-        <v>1.45</v>
+        <v>4.58</v>
       </c>
       <c r="O157">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="P157">
-        <v>5.32</v>
+        <v>1.51</v>
       </c>
       <c r="Q157">
         <v>0</v>
@@ -25951,7 +25951,7 @@
         <v>0</v>
       </c>
       <c r="AE157">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF157">
         <v>0</v>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,13 +26063,13 @@
         </is>
       </c>
       <c r="N158">
-        <v>2.1</v>
+        <v>1.45</v>
       </c>
       <c r="O158">
-        <v>3.7</v>
+        <v>5.1</v>
       </c>
       <c r="P158">
-        <v>2.8</v>
+        <v>5.32</v>
       </c>
       <c r="Q158">
         <v>0</v>
@@ -26184,22 +26184,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G159">
@@ -26226,14 +26226,14 @@
         </is>
       </c>
       <c r="N159">
+        <v>2.1</v>
+      </c>
+      <c r="O159">
+        <v>3.7</v>
+      </c>
+      <c r="P159">
         <v>2.8</v>
       </c>
-      <c r="O159">
-        <v>3.2</v>
-      </c>
-      <c r="P159">
-        <v>2.35</v>
-      </c>
       <c r="Q159">
         <v>0</v>
       </c>
@@ -26265,10 +26265,10 @@
         <v>0</v>
       </c>
       <c r="AA159">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB159">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC159">
         <v>0</v>
@@ -26347,7 +26347,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G160">
@@ -26389,13 +26389,13 @@
         </is>
       </c>
       <c r="N160">
-        <v>2.99</v>
+        <v>2.8</v>
       </c>
       <c r="O160">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="P160">
-        <v>2.72</v>
+        <v>2.35</v>
       </c>
       <c r="Q160">
         <v>0</v>
@@ -26428,10 +26428,10 @@
         <v>0</v>
       </c>
       <c r="AA160">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB160">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC160">
         <v>0</v>
@@ -26510,7 +26510,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G161">
@@ -26552,13 +26552,13 @@
         </is>
       </c>
       <c r="N161">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="O161">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P161">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q161">
         <v>0</v>
@@ -26668,12 +26668,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Nassaji Mazandaran</t>
         </is>
       </c>
       <c r="G162">
@@ -26819,7 +26819,7 @@
       </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>2026-08-23 14:15:00</t>
+          <t>2026-08-23 14:00:00</t>
         </is>
       </c>
     </row>
@@ -26831,12 +26831,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Sporting Hasselt</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G163">
@@ -26982,7 +26982,7 @@
       </c>
       <c r="AU163" t="inlineStr">
         <is>
-          <t>2026-08-23 14:15:00</t>
+          <t>2026-08-23 14:00:00</t>
         </is>
       </c>
     </row>
@@ -26994,12 +26994,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G164">
@@ -27145,7 +27145,7 @@
       </c>
       <c r="AU164" t="inlineStr">
         <is>
-          <t>2026-08-23 14:30:00</t>
+          <t>2026-08-23 14:15:00</t>
         </is>
       </c>
     </row>
@@ -27157,12 +27157,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Nassaji Mazandaran</t>
+          <t>Sporting Hasselt</t>
         </is>
       </c>
       <c r="G165">
@@ -27308,7 +27308,7 @@
       </c>
       <c r="AU165" t="inlineStr">
         <is>
-          <t>2026-08-23 14:30:00</t>
+          <t>2026-08-23 14:15:00</t>
         </is>
       </c>
     </row>
@@ -27320,12 +27320,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G166">
@@ -27471,7 +27471,7 @@
       </c>
       <c r="AU166" t="inlineStr">
         <is>
-          <t>2026-08-23 15:00:00</t>
+          <t>2026-08-23 14:30:00</t>
         </is>
       </c>
     </row>
@@ -27488,7 +27488,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G167">
@@ -27526,17 +27526,17 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N167">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O167">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="P167">
-        <v>12.7</v>
+        <v>0</v>
       </c>
       <c r="Q167">
         <v>0</v>
@@ -27569,10 +27569,10 @@
         <v>0</v>
       </c>
       <c r="AA167">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB167">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC167">
         <v>0</v>
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G168">
@@ -27689,17 +27689,17 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N168">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="O168">
-        <v>4.75</v>
+        <v>5.3</v>
       </c>
       <c r="P168">
-        <v>9</v>
+        <v>12.7</v>
       </c>
       <c r="Q168">
         <v>0</v>
@@ -27732,10 +27732,10 @@
         <v>0</v>
       </c>
       <c r="AA168">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB168">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC168">
         <v>0</v>
@@ -27814,22 +27814,22 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G169">
@@ -27856,13 +27856,13 @@
         </is>
       </c>
       <c r="N169">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O169">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P169">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q169">
         <v>0</v>
@@ -27977,22 +27977,22 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G170">
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G171">
@@ -28303,7 +28303,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G172">
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G173">
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G174">
@@ -28787,12 +28787,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,13 +28834,13 @@
         </is>
       </c>
       <c r="N175">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="O175">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="P175">
-        <v>5.64</v>
+        <v>0</v>
       </c>
       <c r="Q175">
         <v>0</v>
@@ -28938,7 +28938,7 @@
       </c>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>2026-08-23 15:15:00</t>
+          <t>2026-08-23 15:00:00</t>
         </is>
       </c>
     </row>
@@ -28955,7 +28955,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,13 +28997,13 @@
         </is>
       </c>
       <c r="N176">
-        <v>2.33</v>
+        <v>1.48</v>
       </c>
       <c r="O176">
-        <v>3.54</v>
+        <v>4.05</v>
       </c>
       <c r="P176">
-        <v>2.72</v>
+        <v>5.64</v>
       </c>
       <c r="Q176">
         <v>0</v>
@@ -29118,7 +29118,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,13 +29160,13 @@
         </is>
       </c>
       <c r="N177">
-        <v>2.95</v>
+        <v>2.33</v>
       </c>
       <c r="O177">
-        <v>2.99</v>
+        <v>3.54</v>
       </c>
       <c r="P177">
-        <v>2.5</v>
+        <v>2.72</v>
       </c>
       <c r="Q177">
         <v>0</v>
@@ -29276,12 +29276,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G178">
@@ -29323,13 +29323,13 @@
         </is>
       </c>
       <c r="N178">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O178">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="P178">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q178">
         <v>0</v>
@@ -29427,7 +29427,7 @@
       </c>
       <c r="AU178" t="inlineStr">
         <is>
-          <t>2026-08-23 15:30:00</t>
+          <t>2026-08-23 15:15:00</t>
         </is>
       </c>
     </row>
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G179">
@@ -29607,22 +29607,22 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="G180">
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G181">
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G182">
@@ -30096,22 +30096,22 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G183">
@@ -30138,13 +30138,13 @@
         </is>
       </c>
       <c r="N183">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="O183">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P183">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Q183">
         <v>0</v>
@@ -30259,7 +30259,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -30269,12 +30269,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G184">
@@ -30301,13 +30301,13 @@
         </is>
       </c>
       <c r="N184">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O184">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P184">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Q184">
         <v>0</v>
@@ -30432,12 +30432,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Batman Petrolspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G185">
@@ -30585,7 +30585,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Batman Petrolspor</t>
         </is>
       </c>
       <c r="G186">
@@ -30627,13 +30627,13 @@
         </is>
       </c>
       <c r="N186">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O186">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P186">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Q186">
         <v>0</v>
@@ -30743,12 +30743,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G187">
@@ -30790,13 +30790,13 @@
         </is>
       </c>
       <c r="N187">
-        <v>1.48</v>
+        <v>2.8</v>
       </c>
       <c r="O187">
-        <v>5.59</v>
+        <v>3.15</v>
       </c>
       <c r="P187">
-        <v>6.15</v>
+        <v>2.46</v>
       </c>
       <c r="Q187">
         <v>0</v>
@@ -30835,10 +30835,10 @@
         <v>0</v>
       </c>
       <c r="AC187">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AD187">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE187">
         <v>0</v>
@@ -30894,7 +30894,7 @@
       </c>
       <c r="AU187" t="inlineStr">
         <is>
-          <t>2026-08-23 15:45:00</t>
+          <t>2026-08-23 15:30:00</t>
         </is>
       </c>
     </row>
@@ -30911,7 +30911,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G188">
@@ -30953,55 +30953,55 @@
         </is>
       </c>
       <c r="N188">
-        <v>4.65</v>
+        <v>1.48</v>
       </c>
       <c r="O188">
-        <v>3.89</v>
+        <v>5.59</v>
       </c>
       <c r="P188">
+        <v>6.15</v>
+      </c>
+      <c r="Q188">
+        <v>0</v>
+      </c>
+      <c r="R188">
+        <v>0</v>
+      </c>
+      <c r="S188">
+        <v>0</v>
+      </c>
+      <c r="T188">
+        <v>0</v>
+      </c>
+      <c r="U188">
+        <v>0</v>
+      </c>
+      <c r="V188">
+        <v>0</v>
+      </c>
+      <c r="W188">
+        <v>0</v>
+      </c>
+      <c r="X188">
+        <v>0</v>
+      </c>
+      <c r="Y188">
+        <v>0</v>
+      </c>
+      <c r="Z188">
+        <v>0</v>
+      </c>
+      <c r="AA188">
+        <v>0</v>
+      </c>
+      <c r="AB188">
+        <v>0</v>
+      </c>
+      <c r="AC188">
+        <v>1.96</v>
+      </c>
+      <c r="AD188">
         <v>1.84</v>
-      </c>
-      <c r="Q188">
-        <v>0</v>
-      </c>
-      <c r="R188">
-        <v>0</v>
-      </c>
-      <c r="S188">
-        <v>0</v>
-      </c>
-      <c r="T188">
-        <v>0</v>
-      </c>
-      <c r="U188">
-        <v>0</v>
-      </c>
-      <c r="V188">
-        <v>0</v>
-      </c>
-      <c r="W188">
-        <v>0</v>
-      </c>
-      <c r="X188">
-        <v>0</v>
-      </c>
-      <c r="Y188">
-        <v>0</v>
-      </c>
-      <c r="Z188">
-        <v>0</v>
-      </c>
-      <c r="AA188">
-        <v>1.84</v>
-      </c>
-      <c r="AB188">
-        <v>1.87</v>
-      </c>
-      <c r="AC188">
-        <v>0</v>
-      </c>
-      <c r="AD188">
-        <v>0</v>
       </c>
       <c r="AE188">
         <v>0</v>
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G189">
@@ -31116,13 +31116,13 @@
         </is>
       </c>
       <c r="N189">
-        <v>1.59</v>
+        <v>4.65</v>
       </c>
       <c r="O189">
-        <v>4.5</v>
+        <v>3.89</v>
       </c>
       <c r="P189">
-        <v>6.14</v>
+        <v>1.84</v>
       </c>
       <c r="Q189">
         <v>0</v>
@@ -31155,10 +31155,10 @@
         <v>0</v>
       </c>
       <c r="AA189">
-        <v>1.66</v>
+        <v>1.84</v>
       </c>
       <c r="AB189">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AC189">
         <v>0</v>
@@ -31232,12 +31232,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G190">
@@ -31279,13 +31279,13 @@
         </is>
       </c>
       <c r="N190">
-        <v>2.64</v>
+        <v>1.59</v>
       </c>
       <c r="O190">
-        <v>3.24</v>
+        <v>4.5</v>
       </c>
       <c r="P190">
-        <v>2.6</v>
+        <v>6.14</v>
       </c>
       <c r="Q190">
         <v>0</v>
@@ -31318,10 +31318,10 @@
         <v>0</v>
       </c>
       <c r="AA190">
-        <v>1.99</v>
+        <v>1.66</v>
       </c>
       <c r="AB190">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AC190">
         <v>0</v>
@@ -31383,7 +31383,7 @@
       </c>
       <c r="AU190" t="inlineStr">
         <is>
-          <t>2026-08-23 16:00:00</t>
+          <t>2026-08-23 15:45:00</t>
         </is>
       </c>
     </row>
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G191">
@@ -31442,13 +31442,13 @@
         </is>
       </c>
       <c r="N191">
-        <v>1.63</v>
+        <v>2.64</v>
       </c>
       <c r="O191">
-        <v>3.58</v>
+        <v>3.24</v>
       </c>
       <c r="P191">
-        <v>5.71</v>
+        <v>2.6</v>
       </c>
       <c r="Q191">
         <v>0</v>
@@ -31481,7 +31481,7 @@
         <v>0</v>
       </c>
       <c r="AA191">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AB191">
         <v>1.73</v>
@@ -31563,7 +31563,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G192">
@@ -31605,13 +31605,13 @@
         </is>
       </c>
       <c r="N192">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O192">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P192">
-        <v>0</v>
+        <v>5.71</v>
       </c>
       <c r="Q192">
         <v>0</v>
@@ -31644,10 +31644,10 @@
         <v>0</v>
       </c>
       <c r="AA192">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB192">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC192">
         <v>0</v>
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G193">
@@ -31768,13 +31768,13 @@
         </is>
       </c>
       <c r="N193">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O193">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="P193">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="Q193">
         <v>0</v>
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G194">
@@ -31931,13 +31931,13 @@
         </is>
       </c>
       <c r="N194">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O194">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P194">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="Q194">
         <v>0</v>
@@ -32052,22 +32052,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="G195">
@@ -32094,13 +32094,13 @@
         </is>
       </c>
       <c r="N195">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="O195">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="P195">
-        <v>6.22</v>
+        <v>0</v>
       </c>
       <c r="Q195">
         <v>0</v>
@@ -32133,10 +32133,10 @@
         <v>0</v>
       </c>
       <c r="AA195">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB195">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC195">
         <v>0</v>
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G196">
@@ -32257,13 +32257,13 @@
         </is>
       </c>
       <c r="N196">
-        <v>2.7</v>
+        <v>1.58</v>
       </c>
       <c r="O196">
-        <v>3.29</v>
+        <v>4.07</v>
       </c>
       <c r="P196">
-        <v>2.72</v>
+        <v>6.22</v>
       </c>
       <c r="Q196">
         <v>0</v>
@@ -32296,10 +32296,10 @@
         <v>0</v>
       </c>
       <c r="AA196">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AB196">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AC196">
         <v>0</v>
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G197">
@@ -32420,13 +32420,13 @@
         </is>
       </c>
       <c r="N197">
-        <v>1.91</v>
+        <v>2.7</v>
       </c>
       <c r="O197">
-        <v>3.58</v>
+        <v>3.29</v>
       </c>
       <c r="P197">
-        <v>4.17</v>
+        <v>2.72</v>
       </c>
       <c r="Q197">
         <v>0</v>
@@ -32459,10 +32459,10 @@
         <v>0</v>
       </c>
       <c r="AA197">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="AB197">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AC197">
         <v>0</v>
@@ -32541,7 +32541,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G198">
@@ -32583,13 +32583,13 @@
         </is>
       </c>
       <c r="N198">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O198">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P198">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="Q198">
         <v>0</v>
@@ -32622,10 +32622,10 @@
         <v>0</v>
       </c>
       <c r="AA198">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB198">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC198">
         <v>0</v>
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G199">
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G200">
@@ -33030,7 +33030,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G201">
@@ -33193,7 +33193,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G202">
@@ -33356,22 +33356,22 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="G203">
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G204">
@@ -33682,22 +33682,22 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G205">
@@ -33845,22 +33845,22 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G206">
@@ -34008,7 +34008,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G207">
@@ -34171,7 +34171,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G208">
@@ -34213,13 +34213,13 @@
         </is>
       </c>
       <c r="N208">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O208">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P208">
-        <v>4.94</v>
+        <v>0</v>
       </c>
       <c r="Q208">
         <v>0</v>
@@ -34334,22 +34334,22 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="G209">
@@ -34376,13 +34376,13 @@
         </is>
       </c>
       <c r="N209">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O209">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P209">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="Q209">
         <v>0</v>
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G210">
@@ -34655,27 +34655,27 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G211">
@@ -34702,13 +34702,13 @@
         </is>
       </c>
       <c r="N211">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="O211">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="P211">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="Q211">
         <v>0</v>
@@ -34806,7 +34806,7 @@
       </c>
       <c r="AU211" t="inlineStr">
         <is>
-          <t>2026-08-23 16:30:00</t>
+          <t>2026-08-23 16:00:00</t>
         </is>
       </c>
     </row>
@@ -34823,7 +34823,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -34833,12 +34833,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G212">
@@ -34865,13 +34865,13 @@
         </is>
       </c>
       <c r="N212">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="O212">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P212">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q212">
         <v>0</v>
@@ -34986,7 +34986,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G213">
@@ -35028,13 +35028,13 @@
         </is>
       </c>
       <c r="N213">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="O213">
-        <v>7.65</v>
+        <v>0</v>
       </c>
       <c r="P213">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Q213">
         <v>0</v>
@@ -35144,27 +35144,27 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G214">
@@ -35191,13 +35191,13 @@
         </is>
       </c>
       <c r="N214">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="O214">
-        <v>0</v>
+        <v>7.65</v>
       </c>
       <c r="P214">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q214">
         <v>0</v>
@@ -35295,7 +35295,7 @@
       </c>
       <c r="AU214" t="inlineStr">
         <is>
-          <t>2026-08-23 17:00:00</t>
+          <t>2026-08-23 16:30:00</t>
         </is>
       </c>
     </row>
@@ -35312,7 +35312,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G215">
@@ -35354,13 +35354,13 @@
         </is>
       </c>
       <c r="N215">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O215">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P215">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q215">
         <v>0</v>
@@ -35470,12 +35470,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -35485,12 +35485,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G216">
@@ -35517,13 +35517,13 @@
         </is>
       </c>
       <c r="N216">
-        <v>3.32</v>
+        <v>1.62</v>
       </c>
       <c r="O216">
-        <v>3.01</v>
+        <v>3.65</v>
       </c>
       <c r="P216">
-        <v>2.29</v>
+        <v>4</v>
       </c>
       <c r="Q216">
         <v>0</v>
@@ -35621,7 +35621,7 @@
       </c>
       <c r="AU216" t="inlineStr">
         <is>
-          <t>2026-08-23 17:30:00</t>
+          <t>2026-08-23 17:00:00</t>
         </is>
       </c>
     </row>
@@ -35638,7 +35638,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -35648,12 +35648,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G217">
@@ -35680,13 +35680,13 @@
         </is>
       </c>
       <c r="N217">
-        <v>2.59</v>
+        <v>3.32</v>
       </c>
       <c r="O217">
-        <v>3.57</v>
+        <v>3.01</v>
       </c>
       <c r="P217">
-        <v>2.74</v>
+        <v>2.29</v>
       </c>
       <c r="Q217">
         <v>0</v>
@@ -35796,12 +35796,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -35811,12 +35811,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G218">
@@ -35843,13 +35843,13 @@
         </is>
       </c>
       <c r="N218">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="O218">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="P218">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q218">
         <v>0</v>
@@ -35947,7 +35947,7 @@
       </c>
       <c r="AU218" t="inlineStr">
         <is>
-          <t>2026-08-23 18:00:00</t>
+          <t>2026-08-23 17:30:00</t>
         </is>
       </c>
     </row>
@@ -35964,7 +35964,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -35974,12 +35974,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G219">
@@ -36122,12 +36122,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -36137,12 +36137,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G220">
@@ -36273,7 +36273,7 @@
       </c>
       <c r="AU220" t="inlineStr">
         <is>
-          <t>2026-08-23 18:15:00</t>
+          <t>2026-08-23 18:00:00</t>
         </is>
       </c>
     </row>
@@ -36285,12 +36285,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -36300,12 +36300,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G221">
@@ -36332,13 +36332,13 @@
         </is>
       </c>
       <c r="N221">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="O221">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="P221">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q221">
         <v>0</v>
@@ -36436,7 +36436,7 @@
       </c>
       <c r="AU221" t="inlineStr">
         <is>
-          <t>2026-08-23 18:30:00</t>
+          <t>2026-08-23 18:15:00</t>
         </is>
       </c>
     </row>
@@ -36463,12 +36463,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G222">
@@ -36495,13 +36495,13 @@
         </is>
       </c>
       <c r="N222">
-        <v>2.13</v>
+        <v>3.44</v>
       </c>
       <c r="O222">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="P222">
-        <v>3.55</v>
+        <v>2.18</v>
       </c>
       <c r="Q222">
         <v>0</v>
@@ -36616,7 +36616,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -36626,12 +36626,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G223">
@@ -36658,13 +36658,13 @@
         </is>
       </c>
       <c r="N223">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O223">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P223">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q223">
         <v>0</v>
@@ -36789,12 +36789,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G224">
@@ -36942,7 +36942,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -36952,12 +36952,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G225">
@@ -37100,12 +37100,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -37115,12 +37115,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G226">
@@ -37147,13 +37147,13 @@
         </is>
       </c>
       <c r="N226">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O226">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P226">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="Q226">
         <v>0</v>
@@ -37251,7 +37251,7 @@
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>2026-08-23 19:00:00</t>
+          <t>2026-08-23 18:30:00</t>
         </is>
       </c>
     </row>
@@ -37263,12 +37263,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G227">
@@ -37310,13 +37310,13 @@
         </is>
       </c>
       <c r="N227">
-        <v>2.92</v>
+        <v>1.7</v>
       </c>
       <c r="O227">
-        <v>3.15</v>
+        <v>3.74</v>
       </c>
       <c r="P227">
-        <v>2.62</v>
+        <v>4.07</v>
       </c>
       <c r="Q227">
         <v>0</v>
@@ -37414,7 +37414,7 @@
       </c>
       <c r="AU227" t="inlineStr">
         <is>
-          <t>2026-08-23 19:30:00</t>
+          <t>2026-08-23 19:00:00</t>
         </is>
       </c>
     </row>
@@ -37426,12 +37426,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G228">
@@ -37473,13 +37473,13 @@
         </is>
       </c>
       <c r="N228">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="O228">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P228">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q228">
         <v>0</v>
@@ -37577,7 +37577,7 @@
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>2026-08-23 20:00:00</t>
+          <t>2026-08-23 19:30:00</t>
         </is>
       </c>
     </row>
@@ -37594,7 +37594,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G229">
@@ -37636,13 +37636,13 @@
         </is>
       </c>
       <c r="N229">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="O229">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="P229">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="Q229">
         <v>0</v>
@@ -37752,12 +37752,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G230">
@@ -37799,13 +37799,13 @@
         </is>
       </c>
       <c r="N230">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O230">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="P230">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="Q230">
         <v>0</v>
@@ -37903,7 +37903,7 @@
       </c>
       <c r="AU230" t="inlineStr">
         <is>
-          <t>2026-08-23 20:30:00</t>
+          <t>2026-08-23 20:00:00</t>
         </is>
       </c>
     </row>
@@ -37920,7 +37920,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -37930,12 +37930,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G231">
@@ -38078,12 +38078,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -38093,12 +38093,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="G232">
@@ -38229,7 +38229,7 @@
       </c>
       <c r="AU232" t="inlineStr">
         <is>
-          <t>2026-08-23 21:00:00</t>
+          <t>2026-08-23 20:30:00</t>
         </is>
       </c>
     </row>
@@ -38246,22 +38246,22 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G233">
@@ -38409,7 +38409,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -38419,12 +38419,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G234">
@@ -38451,13 +38451,13 @@
         </is>
       </c>
       <c r="N234">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O234">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P234">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q234">
         <v>0</v>
@@ -38490,10 +38490,10 @@
         <v>0</v>
       </c>
       <c r="AA234">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB234">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC234">
         <v>0</v>
@@ -38572,22 +38572,22 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G235">
@@ -38614,13 +38614,13 @@
         </is>
       </c>
       <c r="N235">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O235">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P235">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q235">
         <v>0</v>
@@ -38717,332 +38717,6 @@
         <v>0</v>
       </c>
       <c r="AU235" t="inlineStr">
-        <is>
-          <t>2026-08-23 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>Ecuador Primera Categoría Serie A</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E236" t="inlineStr">
-        <is>
-          <t>LDU Quito</t>
-        </is>
-      </c>
-      <c r="F236" t="inlineStr">
-        <is>
-          <t>CS Emelec</t>
-        </is>
-      </c>
-      <c r="G236">
-        <v>0</v>
-      </c>
-      <c r="H236">
-        <v>0</v>
-      </c>
-      <c r="I236">
-        <v>0</v>
-      </c>
-      <c r="J236">
-        <v>0</v>
-      </c>
-      <c r="K236">
-        <v>0</v>
-      </c>
-      <c r="L236">
-        <v>0</v>
-      </c>
-      <c r="M236" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N236">
-        <v>1.48</v>
-      </c>
-      <c r="O236">
-        <v>3.8</v>
-      </c>
-      <c r="P236">
-        <v>7</v>
-      </c>
-      <c r="Q236">
-        <v>0</v>
-      </c>
-      <c r="R236">
-        <v>0</v>
-      </c>
-      <c r="S236">
-        <v>0</v>
-      </c>
-      <c r="T236">
-        <v>0</v>
-      </c>
-      <c r="U236">
-        <v>0</v>
-      </c>
-      <c r="V236">
-        <v>0</v>
-      </c>
-      <c r="W236">
-        <v>0</v>
-      </c>
-      <c r="X236">
-        <v>0</v>
-      </c>
-      <c r="Y236">
-        <v>0</v>
-      </c>
-      <c r="Z236">
-        <v>0</v>
-      </c>
-      <c r="AA236">
-        <v>2.03</v>
-      </c>
-      <c r="AB236">
-        <v>1.78</v>
-      </c>
-      <c r="AC236">
-        <v>0</v>
-      </c>
-      <c r="AD236">
-        <v>0</v>
-      </c>
-      <c r="AE236">
-        <v>0</v>
-      </c>
-      <c r="AF236">
-        <v>0</v>
-      </c>
-      <c r="AG236">
-        <v>0</v>
-      </c>
-      <c r="AH236" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI236" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ236">
-        <v>0</v>
-      </c>
-      <c r="AK236">
-        <v>0</v>
-      </c>
-      <c r="AL236">
-        <v>0</v>
-      </c>
-      <c r="AM236">
-        <v>-1</v>
-      </c>
-      <c r="AN236">
-        <v>-1</v>
-      </c>
-      <c r="AO236">
-        <v>-1</v>
-      </c>
-      <c r="AP236">
-        <v>-1</v>
-      </c>
-      <c r="AQ236">
-        <v>0</v>
-      </c>
-      <c r="AR236">
-        <v>0</v>
-      </c>
-      <c r="AS236">
-        <v>0</v>
-      </c>
-      <c r="AT236">
-        <v>0</v>
-      </c>
-      <c r="AU236" t="inlineStr">
-        <is>
-          <t>2026-08-23 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E237" t="inlineStr">
-        <is>
-          <t>Angel City</t>
-        </is>
-      </c>
-      <c r="F237" t="inlineStr">
-        <is>
-          <t>Gotham FC</t>
-        </is>
-      </c>
-      <c r="G237">
-        <v>0</v>
-      </c>
-      <c r="H237">
-        <v>0</v>
-      </c>
-      <c r="I237">
-        <v>0</v>
-      </c>
-      <c r="J237">
-        <v>0</v>
-      </c>
-      <c r="K237">
-        <v>0</v>
-      </c>
-      <c r="L237">
-        <v>0</v>
-      </c>
-      <c r="M237" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N237">
-        <v>3.35</v>
-      </c>
-      <c r="O237">
-        <v>3.05</v>
-      </c>
-      <c r="P237">
-        <v>1.95</v>
-      </c>
-      <c r="Q237">
-        <v>0</v>
-      </c>
-      <c r="R237">
-        <v>0</v>
-      </c>
-      <c r="S237">
-        <v>0</v>
-      </c>
-      <c r="T237">
-        <v>0</v>
-      </c>
-      <c r="U237">
-        <v>0</v>
-      </c>
-      <c r="V237">
-        <v>0</v>
-      </c>
-      <c r="W237">
-        <v>0</v>
-      </c>
-      <c r="X237">
-        <v>0</v>
-      </c>
-      <c r="Y237">
-        <v>0</v>
-      </c>
-      <c r="Z237">
-        <v>0</v>
-      </c>
-      <c r="AA237">
-        <v>0</v>
-      </c>
-      <c r="AB237">
-        <v>0</v>
-      </c>
-      <c r="AC237">
-        <v>0</v>
-      </c>
-      <c r="AD237">
-        <v>0</v>
-      </c>
-      <c r="AE237">
-        <v>0</v>
-      </c>
-      <c r="AF237">
-        <v>0</v>
-      </c>
-      <c r="AG237">
-        <v>0</v>
-      </c>
-      <c r="AH237" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI237" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ237">
-        <v>0</v>
-      </c>
-      <c r="AK237">
-        <v>0</v>
-      </c>
-      <c r="AL237">
-        <v>0</v>
-      </c>
-      <c r="AM237">
-        <v>-1</v>
-      </c>
-      <c r="AN237">
-        <v>-1</v>
-      </c>
-      <c r="AO237">
-        <v>-1</v>
-      </c>
-      <c r="AP237">
-        <v>-1</v>
-      </c>
-      <c r="AQ237">
-        <v>0</v>
-      </c>
-      <c r="AR237">
-        <v>0</v>
-      </c>
-      <c r="AS237">
-        <v>0</v>
-      </c>
-      <c r="AT237">
-        <v>0</v>
-      </c>
-      <c r="AU237" t="inlineStr">
         <is>
           <t>2026-08-23 21:00:00</t>
         </is>

--- a/jogos_2026-08-23.xlsx
+++ b/jogos_2026-08-23.xlsx
@@ -1296,55 +1296,55 @@
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -7194,10 +7194,10 @@
         <v>0</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC42">
         <v>0</v>

--- a/jogos_2026-08-23.xlsx
+++ b/jogos_2026-08-23.xlsx
@@ -1459,55 +1459,55 @@
         <v>4.94</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2274,55 +2274,55 @@
         <v>2.65</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2437,55 +2437,55 @@
         <v>2.1</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2763,55 +2763,55 @@
         <v>5.2</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2926,55 +2926,55 @@
         <v>1.71</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3089,55 +3089,55 @@
         <v>2.8</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3415,55 +3415,55 @@
         <v>2.49</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3578,55 +3578,55 @@
         <v>1.93</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3904,55 +3904,55 @@
         <v>4.76</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4067,55 +4067,55 @@
         <v>0</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4556,34 +4556,34 @@
         <v>2.45</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AA26">
         <v>2</v>
@@ -4592,19 +4592,19 @@
         <v>1.71</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G27">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G28">
@@ -5045,55 +5045,55 @@
         <v>8.25</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5208,34 +5208,34 @@
         <v>2.72</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AA30">
         <v>1.84</v>
@@ -5244,19 +5244,19 @@
         <v>1.87</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5371,40 +5371,40 @@
         <v>7.65</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AC31">
         <v>1.72</v>
@@ -5413,13 +5413,13 @@
         <v>1.98</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -6186,55 +6186,55 @@
         <v>2.86</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6349,55 +6349,55 @@
         <v>6.07</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6512,55 +6512,55 @@
         <v>0</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6838,55 +6838,55 @@
         <v>8.4</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7001,55 +7001,55 @@
         <v>0</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7327,55 +7327,55 @@
         <v>6.13</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7490,34 +7490,34 @@
         <v>2.84</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="AA44">
         <v>1.82</v>
@@ -7526,19 +7526,19 @@
         <v>1.88</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7653,34 +7653,34 @@
         <v>3.11</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W45">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z45">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA45">
         <v>1.57</v>
@@ -7689,19 +7689,19 @@
         <v>2.25</v>
       </c>
       <c r="AC45">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG45">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK45">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7816,40 +7816,40 @@
         <v>6.4</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AC46">
         <v>1.82</v>
@@ -7858,13 +7858,13 @@
         <v>1.88</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG46">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7979,34 +7979,34 @@
         <v>1.74</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T47">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U47">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W47">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X47">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z47">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="AA47">
         <v>1.95</v>
@@ -8015,19 +8015,19 @@
         <v>1.85</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD47">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE47">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF47">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG47">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK47">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8172,10 +8172,10 @@
         <v>0</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC48">
         <v>0</v>
@@ -8305,55 +8305,55 @@
         <v>3.03</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8498,10 +8498,10 @@
         <v>0</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC50">
         <v>0</v>
@@ -8957,55 +8957,55 @@
         <v>2.7</v>
       </c>
       <c r="Q53">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="R53">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S53">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T53">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="U53">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="V53">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W53">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X53">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y53">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z53">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA53">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AB53">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC53">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AD53">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE53">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF53">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG53">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK53">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9120,55 +9120,55 @@
         <v>2.92</v>
       </c>
       <c r="Q54">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R54">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S54">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T54">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U54">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V54">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W54">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X54">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y54">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z54">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA54">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB54">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC54">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD54">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE54">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF54">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG54">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK54">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9283,55 +9283,55 @@
         <v>2.81</v>
       </c>
       <c r="Q55">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R55">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S55">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T55">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U55">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V55">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W55">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X55">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y55">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z55">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA55">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB55">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC55">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD55">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE55">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF55">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG55">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK55">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9772,55 +9772,55 @@
         <v>0</v>
       </c>
       <c r="Q58">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R58">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S58">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T58">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U58">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="V58">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W58">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X58">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z58">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="AA58">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AB58">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC58">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="AD58">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE58">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF58">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG58">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK58">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10261,40 +10261,40 @@
         <v>4.81</v>
       </c>
       <c r="Q61">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="R61">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S61">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T61">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U61">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V61">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W61">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y61">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z61">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AA61">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB61">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AC61">
         <v>1.98</v>
@@ -10303,13 +10303,13 @@
         <v>1.83</v>
       </c>
       <c r="AE61">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF61">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG61">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK61">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10424,10 +10424,10 @@
         <v>0</v>
       </c>
       <c r="Q62">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S62">
         <v>0</v>
@@ -10436,10 +10436,10 @@
         <v>0</v>
       </c>
       <c r="U62">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="V62">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W62">
         <v>0</v>
@@ -10454,25 +10454,25 @@
         <v>0</v>
       </c>
       <c r="AA62">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB62">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC62">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD62">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE62">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF62">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG62">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK62">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O66">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q66">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R66">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S66">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T66">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U66">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V66">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W66">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X66">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y66">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z66">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA66">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB66">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC66">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD66">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE66">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF66">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG66">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK66">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11402,55 +11402,55 @@
         <v>2.27</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S68">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T68">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U68">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V68">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W68">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y68">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z68">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA68">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB68">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC68">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD68">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE68">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF68">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG68">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK68">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11565,55 +11565,55 @@
         <v>8.949999999999999</v>
       </c>
       <c r="Q69">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R69">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S69">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T69">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U69">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V69">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W69">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X69">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y69">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z69">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA69">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB69">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC69">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD69">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE69">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF69">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG69">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK69">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11728,55 +11728,55 @@
         <v>4.33</v>
       </c>
       <c r="Q70">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="R70">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S70">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T70">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U70">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V70">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W70">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X70">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y70">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z70">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA70">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB70">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC70">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD70">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE70">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF70">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG70">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK70">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -12217,55 +12217,55 @@
         <v>1.63</v>
       </c>
       <c r="Q73">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R73">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S73">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T73">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U73">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V73">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W73">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X73">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y73">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z73">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA73">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB73">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC73">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD73">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE73">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF73">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG73">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AK73">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12380,55 +12380,55 @@
         <v>3.45</v>
       </c>
       <c r="Q74">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R74">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S74">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T74">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U74">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V74">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W74">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X74">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y74">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z74">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA74">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB74">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AC74">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AD74">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE74">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF74">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG74">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK74">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12869,55 +12869,55 @@
         <v>1.81</v>
       </c>
       <c r="Q77">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="R77">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S77">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T77">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U77">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V77">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W77">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X77">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y77">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z77">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="AA77">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AB77">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC77">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD77">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE77">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF77">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG77">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK77">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13032,34 +13032,34 @@
         <v>4.42</v>
       </c>
       <c r="Q78">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="R78">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S78">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T78">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U78">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V78">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W78">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X78">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y78">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z78">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA78">
         <v>1.94</v>
@@ -13068,19 +13068,19 @@
         <v>1.79</v>
       </c>
       <c r="AC78">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD78">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE78">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF78">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG78">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK78">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13358,55 +13358,55 @@
         <v>1.53</v>
       </c>
       <c r="Q80">
-        <v>0</v>
+        <v>6.28</v>
       </c>
       <c r="R80">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="S80">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T80">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U80">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="V80">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="W80">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X80">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y80">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z80">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA80">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB80">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AC80">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD80">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE80">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF80">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG80">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK80">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O81">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q81">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R81">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S81">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T81">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U81">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="V81">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W81">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X81">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y81">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z81">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA81">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB81">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AC81">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD81">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE81">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF81">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG81">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK81">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13684,55 +13684,55 @@
         <v>0</v>
       </c>
       <c r="Q82">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R82">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S82">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T82">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U82">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V82">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W82">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X82">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y82">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z82">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA82">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB82">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC82">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD82">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE82">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF82">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG82">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK82">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13847,55 +13847,55 @@
         <v>3.76</v>
       </c>
       <c r="Q83">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R83">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S83">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="T83">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U83">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="V83">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W83">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X83">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y83">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z83">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA83">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB83">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC83">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AD83">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE83">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF83">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG83">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK83">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O84">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q84">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R84">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S84">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T84">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="U84">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="V84">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W84">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X84">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y84">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z84">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA84">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB84">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC84">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD84">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE84">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF84">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG84">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK84">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O85">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="P85">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q85">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R85">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S85">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T85">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U85">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V85">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W85">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X85">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y85">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z85">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA85">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB85">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC85">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD85">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE85">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF85">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG85">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AK85">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O87">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Q87">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R87">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S87">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T87">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="U87">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V87">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W87">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X87">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y87">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z87">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="AA87">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB87">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC87">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AD87">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE87">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF87">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG87">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK87">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14825,55 +14825,55 @@
         <v>2.18</v>
       </c>
       <c r="Q89">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R89">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S89">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T89">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U89">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="V89">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W89">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X89">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y89">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z89">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA89">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB89">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AC89">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD89">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE89">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF89">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG89">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK89">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14988,34 +14988,34 @@
         <v>2.05</v>
       </c>
       <c r="Q90">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R90">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S90">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T90">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U90">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V90">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W90">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X90">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y90">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z90">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA90">
         <v>1.57</v>
@@ -15024,19 +15024,19 @@
         <v>2.25</v>
       </c>
       <c r="AC90">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD90">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE90">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF90">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG90">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK90">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15151,40 +15151,40 @@
         <v>2.28</v>
       </c>
       <c r="Q91">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R91">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S91">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T91">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U91">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="V91">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W91">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X91">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y91">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z91">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA91">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB91">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC91">
         <v>1.98</v>
@@ -15193,13 +15193,13 @@
         <v>1.75</v>
       </c>
       <c r="AE91">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF91">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG91">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK91">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15314,55 +15314,55 @@
         <v>0</v>
       </c>
       <c r="Q92">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R92">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S92">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T92">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U92">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V92">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W92">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X92">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y92">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z92">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA92">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB92">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC92">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD92">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE92">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF92">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG92">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK92">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15477,55 +15477,55 @@
         <v>3.63</v>
       </c>
       <c r="Q93">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R93">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S93">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T93">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U93">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V93">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W93">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X93">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y93">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z93">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA93">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB93">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC93">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD93">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE93">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF93">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG93">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK93">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -16618,55 +16618,55 @@
         <v>6.63</v>
       </c>
       <c r="Q100">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R100">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S100">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T100">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U100">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V100">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W100">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X100">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y100">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z100">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA100">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB100">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AC100">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD100">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE100">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF100">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG100">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK100">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -17270,55 +17270,55 @@
         <v>0</v>
       </c>
       <c r="Q104">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="R104">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S104">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T104">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U104">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V104">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W104">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X104">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y104">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z104">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA104">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB104">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC104">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD104">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE104">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF104">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG104">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK104">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O107">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P107">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q107">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R107">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S107">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T107">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U107">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V107">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W107">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X107">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y107">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z107">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA107">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB107">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AC107">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AD107">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE107">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF107">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG107">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK107">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O108">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P108">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q108">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R108">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S108">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T108">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U108">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V108">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W108">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X108">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y108">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z108">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AA108">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB108">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC108">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD108">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE108">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF108">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG108">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK108">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G117">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G118">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G119">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G120">
@@ -20041,16 +20041,16 @@
         <v>0</v>
       </c>
       <c r="Q121">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R121">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S121">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T121">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U121">
         <v>0</v>
@@ -20065,31 +20065,31 @@
         <v>0</v>
       </c>
       <c r="Y121">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z121">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA121">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB121">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC121">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AD121">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE121">
         <v>0</v>
       </c>
       <c r="AF121">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG121">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK121">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O122">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P122">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q122">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="R122">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S122">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T122">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="U122">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V122">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W122">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X122">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y122">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z122">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="AA122">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB122">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC122">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD122">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE122">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF122">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG122">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AK122">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20358,64 +20358,64 @@
         </is>
       </c>
       <c r="N123">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O123">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P123">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q123">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R123">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S123">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T123">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U123">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V123">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W123">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X123">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y123">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z123">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA123">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB123">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC123">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD123">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE123">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF123">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG123">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK123">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -21345,55 +21345,55 @@
         <v>1.59</v>
       </c>
       <c r="Q129">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R129">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S129">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T129">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U129">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="V129">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W129">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X129">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y129">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z129">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA129">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB129">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC129">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD129">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE129">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF129">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG129">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK129">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21508,55 +21508,55 @@
         <v>2.6</v>
       </c>
       <c r="Q130">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R130">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S130">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T130">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U130">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V130">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W130">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X130">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y130">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z130">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA130">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB130">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC130">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD130">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE130">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF130">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG130">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK130">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G134">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G135">
@@ -22486,55 +22486,55 @@
         <v>2.37</v>
       </c>
       <c r="Q136">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R136">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S136">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T136">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U136">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V136">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W136">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X136">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y136">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z136">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA136">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB136">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC136">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD136">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE136">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF136">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG136">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK136">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22649,34 +22649,34 @@
         <v>1.59</v>
       </c>
       <c r="Q137">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R137">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S137">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T137">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U137">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V137">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W137">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X137">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y137">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z137">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="AA137">
         <v>1.95</v>
@@ -22685,19 +22685,19 @@
         <v>1.85</v>
       </c>
       <c r="AC137">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD137">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE137">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF137">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG137">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK137">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -23138,55 +23138,55 @@
         <v>0</v>
       </c>
       <c r="Q140">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R140">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S140">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T140">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U140">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V140">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W140">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X140">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y140">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z140">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AA140">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB140">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC140">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD140">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE140">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF140">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG140">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23199,10 +23199,10 @@
         </is>
       </c>
       <c r="AJ140">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK140">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL140">
         <v>0</v>
@@ -23618,64 +23618,64 @@
         </is>
       </c>
       <c r="N143">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="O143">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P143">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="Q143">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="R143">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S143">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T143">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="U143">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V143">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W143">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X143">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y143">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z143">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA143">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB143">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC143">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD143">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE143">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF143">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG143">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH143" t="inlineStr">
         <is>
@@ -23688,10 +23688,10 @@
         </is>
       </c>
       <c r="AJ143">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK143">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,64 +23781,64 @@
         </is>
       </c>
       <c r="N144">
-        <v>7.26</v>
+        <v>2.41</v>
       </c>
       <c r="O144">
-        <v>4.6</v>
+        <v>3.34</v>
       </c>
       <c r="P144">
-        <v>1.51</v>
+        <v>3.34</v>
       </c>
       <c r="Q144">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R144">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S144">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T144">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U144">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V144">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W144">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X144">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y144">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z144">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA144">
-        <v>1.77</v>
+        <v>2.15</v>
       </c>
       <c r="AB144">
-        <v>1.96</v>
+        <v>1.63</v>
       </c>
       <c r="AC144">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AD144">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE144">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF144">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG144">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK144">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>2.41</v>
+        <v>7.26</v>
       </c>
       <c r="O145">
-        <v>3.34</v>
+        <v>4.6</v>
       </c>
       <c r="P145">
-        <v>3.34</v>
+        <v>1.51</v>
       </c>
       <c r="Q145">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R145">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S145">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T145">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U145">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V145">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W145">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X145">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y145">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z145">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA145">
-        <v>2.15</v>
+        <v>1.77</v>
       </c>
       <c r="AB145">
-        <v>1.63</v>
+        <v>1.96</v>
       </c>
       <c r="AC145">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD145">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE145">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF145">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG145">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK145">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -25094,55 +25094,55 @@
         <v>0</v>
       </c>
       <c r="Q152">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R152">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S152">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T152">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U152">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="V152">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W152">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X152">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y152">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z152">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AA152">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AB152">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AC152">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD152">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE152">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF152">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG152">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
@@ -25155,10 +25155,10 @@
         </is>
       </c>
       <c r="AJ152">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK152">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -25257,55 +25257,55 @@
         <v>0</v>
       </c>
       <c r="Q153">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R153">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S153">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T153">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U153">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V153">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W153">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X153">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y153">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z153">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA153">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB153">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC153">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD153">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE153">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF153">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG153">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH153" t="inlineStr">
         <is>
@@ -25318,10 +25318,10 @@
         </is>
       </c>
       <c r="AJ153">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK153">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL153">
         <v>0</v>
@@ -25746,55 +25746,55 @@
         <v>3.05</v>
       </c>
       <c r="Q156">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="R156">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="S156">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T156">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U156">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="V156">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W156">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X156">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y156">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z156">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA156">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB156">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC156">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD156">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE156">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF156">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG156">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25807,10 +25807,10 @@
         </is>
       </c>
       <c r="AJ156">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AK156">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -25909,55 +25909,55 @@
         <v>1.51</v>
       </c>
       <c r="Q157">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R157">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="S157">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="T157">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U157">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="V157">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="W157">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="X157">
         <v>0</v>
       </c>
       <c r="Y157">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z157">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AA157">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB157">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AC157">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AD157">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AE157">
         <v>1.77</v>
       </c>
       <c r="AF157">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AG157">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25970,10 +25970,10 @@
         </is>
       </c>
       <c r="AJ157">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AK157">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26072,55 +26072,55 @@
         <v>5.32</v>
       </c>
       <c r="Q158">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="R158">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S158">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T158">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U158">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V158">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="W158">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X158">
         <v>0</v>
       </c>
       <c r="Y158">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Z158">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AA158">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AB158">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AC158">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD158">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AE158">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF158">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG158">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26133,10 +26133,10 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK158">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -26235,55 +26235,55 @@
         <v>2.8</v>
       </c>
       <c r="Q159">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="R159">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S159">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T159">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="U159">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V159">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W159">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X159">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y159">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z159">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AA159">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB159">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC159">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD159">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE159">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AF159">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG159">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AH159" t="inlineStr">
         <is>
@@ -26296,10 +26296,10 @@
         </is>
       </c>
       <c r="AJ159">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK159">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -26398,34 +26398,34 @@
         <v>2.35</v>
       </c>
       <c r="Q160">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R160">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S160">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T160">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U160">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V160">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W160">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X160">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y160">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z160">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA160">
         <v>1.9</v>
@@ -26434,19 +26434,19 @@
         <v>1.81</v>
       </c>
       <c r="AC160">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD160">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE160">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF160">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG160">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH160" t="inlineStr">
         <is>
@@ -26459,10 +26459,10 @@
         </is>
       </c>
       <c r="AJ160">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK160">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL160">
         <v>0</v>
@@ -27041,13 +27041,13 @@
         </is>
       </c>
       <c r="N164">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="O164">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="P164">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q164">
         <v>0</v>

--- a/jogos_2026-08-23.xlsx
+++ b/jogos_2026-08-23.xlsx
@@ -4230,55 +4230,55 @@
         <v>3.56</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S25">
         <v>0</v>
@@ -4405,10 +4405,10 @@
         <v>0</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W25">
         <v>0</v>
@@ -4417,31 +4417,31 @@
         <v>0</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE25">
         <v>0</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -5534,55 +5534,55 @@
         <v>0</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X32">
         <v>0</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="O33">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="P33">
-        <v>2.62</v>
+        <v>2.49</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA33">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AB33">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="O34">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="P34">
-        <v>2.49</v>
+        <v>2.62</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.31</v>
+        <v>1.49</v>
       </c>
       <c r="O45">
-        <v>3.84</v>
+        <v>5.28</v>
       </c>
       <c r="P45">
-        <v>3.11</v>
+        <v>6.4</v>
       </c>
       <c r="Q45">
-        <v>2.5</v>
+        <v>1.87</v>
       </c>
       <c r="R45">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="S45">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="T45">
-        <v>3.4</v>
+        <v>3.94</v>
       </c>
       <c r="U45">
-        <v>2.4</v>
+        <v>1.99</v>
       </c>
       <c r="V45">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="W45">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="X45">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y45">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="Z45">
-        <v>4.33</v>
+        <v>5.35</v>
       </c>
       <c r="AA45">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AB45">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="AC45">
-        <v>2.49</v>
+        <v>1.82</v>
       </c>
       <c r="AD45">
-        <v>1.5</v>
+        <v>1.88</v>
       </c>
       <c r="AE45">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AF45">
         <v>1.53</v>
       </c>
       <c r="AG45">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.34</v>
+        <v>1.11</v>
       </c>
       <c r="AK45">
-        <v>1.62</v>
+        <v>2.6</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.49</v>
+        <v>2.31</v>
       </c>
       <c r="O46">
-        <v>5.28</v>
+        <v>3.84</v>
       </c>
       <c r="P46">
-        <v>6.4</v>
+        <v>3.11</v>
       </c>
       <c r="Q46">
-        <v>1.87</v>
+        <v>2.5</v>
       </c>
       <c r="R46">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="S46">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="T46">
-        <v>3.94</v>
+        <v>3.4</v>
       </c>
       <c r="U46">
-        <v>1.99</v>
+        <v>2.4</v>
       </c>
       <c r="V46">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="W46">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="X46">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="Z46">
-        <v>5.35</v>
+        <v>4.33</v>
       </c>
       <c r="AA46">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AB46">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="AC46">
-        <v>1.82</v>
+        <v>2.49</v>
       </c>
       <c r="AD46">
-        <v>1.88</v>
+        <v>1.5</v>
       </c>
       <c r="AE46">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AF46">
         <v>1.53</v>
       </c>
       <c r="AG46">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.11</v>
+        <v>1.34</v>
       </c>
       <c r="AK46">
-        <v>2.6</v>
+        <v>1.62</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8631,55 +8631,55 @@
         <v>2.32</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U51">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V51">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA51">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC51">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF51">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK51">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8794,10 +8794,10 @@
         <v>0</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S52">
         <v>0</v>
@@ -8806,10 +8806,10 @@
         <v>0</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W52">
         <v>0</v>
@@ -8818,31 +8818,31 @@
         <v>0</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE52">
         <v>0</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>4.35</v>
+        <v>1.96</v>
       </c>
       <c r="O73">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P73">
+        <v>3.45</v>
+      </c>
+      <c r="Q73">
+        <v>2.45</v>
+      </c>
+      <c r="R73">
+        <v>2.5</v>
+      </c>
+      <c r="S73">
+        <v>1.24</v>
+      </c>
+      <c r="T73">
+        <v>3.5</v>
+      </c>
+      <c r="U73">
+        <v>2.1</v>
+      </c>
+      <c r="V73">
         <v>1.63</v>
       </c>
-      <c r="Q73">
-        <v>4.2</v>
-      </c>
-      <c r="R73">
-        <v>2.3</v>
-      </c>
-      <c r="S73">
-        <v>1.25</v>
-      </c>
-      <c r="T73">
-        <v>3.34</v>
-      </c>
-      <c r="U73">
-        <v>2.36</v>
-      </c>
-      <c r="V73">
-        <v>1.52</v>
-      </c>
       <c r="W73">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X73">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y73">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z73">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AA73">
-        <v>1.66</v>
+        <v>1.48</v>
       </c>
       <c r="AB73">
-        <v>2.15</v>
+        <v>2.34</v>
       </c>
       <c r="AC73">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AD73">
-        <v>1.43</v>
+        <v>1.59</v>
       </c>
       <c r="AE73">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF73">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="AG73">
-        <v>2.3</v>
+        <v>2.49</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.94</v>
+        <v>1.32</v>
       </c>
       <c r="AK73">
-        <v>1.22</v>
+        <v>1.75</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.96</v>
+        <v>4.35</v>
       </c>
       <c r="O74">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P74">
-        <v>3.45</v>
+        <v>1.63</v>
       </c>
       <c r="Q74">
-        <v>2.45</v>
+        <v>4.2</v>
       </c>
       <c r="R74">
+        <v>2.3</v>
+      </c>
+      <c r="S74">
+        <v>1.25</v>
+      </c>
+      <c r="T74">
+        <v>3.34</v>
+      </c>
+      <c r="U74">
+        <v>2.36</v>
+      </c>
+      <c r="V74">
+        <v>1.52</v>
+      </c>
+      <c r="W74">
+        <v>1.09</v>
+      </c>
+      <c r="X74">
+        <v>1.03</v>
+      </c>
+      <c r="Y74">
+        <v>1.18</v>
+      </c>
+      <c r="Z74">
+        <v>4.4</v>
+      </c>
+      <c r="AA74">
+        <v>1.66</v>
+      </c>
+      <c r="AB74">
+        <v>2.15</v>
+      </c>
+      <c r="AC74">
         <v>2.5</v>
       </c>
-      <c r="S74">
-        <v>1.24</v>
-      </c>
-      <c r="T74">
-        <v>3.5</v>
-      </c>
-      <c r="U74">
-        <v>2.1</v>
-      </c>
-      <c r="V74">
-        <v>1.63</v>
-      </c>
-      <c r="W74">
-        <v>1.14</v>
-      </c>
-      <c r="X74">
-        <v>1.02</v>
-      </c>
-      <c r="Y74">
-        <v>1.14</v>
-      </c>
-      <c r="Z74">
-        <v>5</v>
-      </c>
-      <c r="AA74">
-        <v>1.48</v>
-      </c>
-      <c r="AB74">
-        <v>2.34</v>
-      </c>
-      <c r="AC74">
-        <v>2.31</v>
-      </c>
       <c r="AD74">
-        <v>1.59</v>
+        <v>1.43</v>
       </c>
       <c r="AE74">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF74">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AG74">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.32</v>
+        <v>1.94</v>
       </c>
       <c r="AK74">
-        <v>1.75</v>
+        <v>1.22</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12543,55 +12543,55 @@
         <v>5.96</v>
       </c>
       <c r="Q75">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="R75">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S75">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T75">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U75">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V75">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W75">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X75">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y75">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z75">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA75">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB75">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC75">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AD75">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE75">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF75">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG75">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK75">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12706,34 +12706,34 @@
         <v>3.44</v>
       </c>
       <c r="Q76">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R76">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S76">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T76">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U76">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V76">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W76">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X76">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y76">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z76">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA76">
         <v>1.85</v>
@@ -12742,19 +12742,19 @@
         <v>1.92</v>
       </c>
       <c r="AC76">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD76">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE76">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF76">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG76">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK76">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -14336,55 +14336,55 @@
         <v>2.6</v>
       </c>
       <c r="Q86">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R86">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S86">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T86">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U86">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V86">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W86">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X86">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y86">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z86">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA86">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB86">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AC86">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD86">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE86">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF86">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG86">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK86">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G152">
@@ -25094,71 +25094,71 @@
         <v>0</v>
       </c>
       <c r="Q152">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="R152">
-        <v>2.98</v>
+        <v>2.01</v>
       </c>
       <c r="S152">
-        <v>1.14</v>
+        <v>1.4</v>
       </c>
       <c r="T152">
-        <v>4.2</v>
+        <v>2.75</v>
       </c>
       <c r="U152">
-        <v>1.97</v>
+        <v>3.08</v>
       </c>
       <c r="V152">
-        <v>1.74</v>
+        <v>1.3</v>
       </c>
       <c r="W152">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="X152">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y152">
-        <v>1.05</v>
+        <v>1.32</v>
       </c>
       <c r="Z152">
-        <v>6.4</v>
+        <v>2.88</v>
       </c>
       <c r="AA152">
-        <v>1.32</v>
+        <v>2.09</v>
       </c>
       <c r="AB152">
-        <v>2.88</v>
+        <v>1.66</v>
       </c>
       <c r="AC152">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="AD152">
+        <v>1.19</v>
+      </c>
+      <c r="AE152">
+        <v>1.02</v>
+      </c>
+      <c r="AF152">
+        <v>1.89</v>
+      </c>
+      <c r="AG152">
         <v>1.8</v>
       </c>
-      <c r="AE152">
+      <c r="AH152" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI152" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ152">
         <v>1.3</v>
       </c>
-      <c r="AF152">
-        <v>1.88</v>
-      </c>
-      <c r="AG152">
-        <v>1.81</v>
-      </c>
-      <c r="AH152" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI152" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ152">
-        <v>1.08</v>
-      </c>
       <c r="AK152">
-        <v>5</v>
+        <v>1.78</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G153">
@@ -25257,55 +25257,55 @@
         <v>0</v>
       </c>
       <c r="Q153">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="R153">
-        <v>2.01</v>
+        <v>2.98</v>
       </c>
       <c r="S153">
-        <v>1.4</v>
+        <v>1.14</v>
       </c>
       <c r="T153">
-        <v>2.75</v>
+        <v>4.2</v>
       </c>
       <c r="U153">
-        <v>3.08</v>
+        <v>1.97</v>
       </c>
       <c r="V153">
+        <v>1.74</v>
+      </c>
+      <c r="W153">
+        <v>1.16</v>
+      </c>
+      <c r="X153">
+        <v>1</v>
+      </c>
+      <c r="Y153">
+        <v>1.05</v>
+      </c>
+      <c r="Z153">
+        <v>6.4</v>
+      </c>
+      <c r="AA153">
+        <v>1.32</v>
+      </c>
+      <c r="AB153">
+        <v>2.88</v>
+      </c>
+      <c r="AC153">
+        <v>1.9</v>
+      </c>
+      <c r="AD153">
+        <v>1.8</v>
+      </c>
+      <c r="AE153">
         <v>1.3</v>
       </c>
-      <c r="W153">
-        <v>1.01</v>
-      </c>
-      <c r="X153">
-        <v>1.01</v>
-      </c>
-      <c r="Y153">
-        <v>1.32</v>
-      </c>
-      <c r="Z153">
-        <v>2.88</v>
-      </c>
-      <c r="AA153">
-        <v>2.09</v>
-      </c>
-      <c r="AB153">
-        <v>1.66</v>
-      </c>
-      <c r="AC153">
-        <v>3.8</v>
-      </c>
-      <c r="AD153">
-        <v>1.19</v>
-      </c>
-      <c r="AE153">
-        <v>1.02</v>
-      </c>
       <c r="AF153">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AG153">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AH153" t="inlineStr">
         <is>
@@ -25318,10 +25318,10 @@
         </is>
       </c>
       <c r="AJ153">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="AK153">
-        <v>1.78</v>
+        <v>5</v>
       </c>
       <c r="AL153">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,13 +25411,13 @@
         </is>
       </c>
       <c r="N154">
-        <v>2.35</v>
+        <v>1.5</v>
       </c>
       <c r="O154">
-        <v>3.31</v>
+        <v>4.17</v>
       </c>
       <c r="P154">
-        <v>3.19</v>
+        <v>7.31</v>
       </c>
       <c r="Q154">
         <v>0</v>
@@ -25450,10 +25450,10 @@
         <v>0</v>
       </c>
       <c r="AA154">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB154">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC154">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,13 +25574,13 @@
         </is>
       </c>
       <c r="N155">
-        <v>1.5</v>
+        <v>2.35</v>
       </c>
       <c r="O155">
-        <v>4.17</v>
+        <v>3.31</v>
       </c>
       <c r="P155">
-        <v>7.31</v>
+        <v>3.19</v>
       </c>
       <c r="Q155">
         <v>0</v>
@@ -25613,10 +25613,10 @@
         <v>0</v>
       </c>
       <c r="AA155">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB155">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC155">
         <v>0</v>
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G181">
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G182">
@@ -29975,64 +29975,64 @@
         </is>
       </c>
       <c r="N182">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O182">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P182">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q182">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R182">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S182">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="T182">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="U182">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="V182">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W182">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X182">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y182">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z182">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AA182">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AB182">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC182">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD182">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE182">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF182">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG182">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH182" t="inlineStr">
         <is>
@@ -30045,10 +30045,10 @@
         </is>
       </c>
       <c r="AJ182">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK182">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL182">
         <v>0</v>
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G183">
@@ -30138,64 +30138,64 @@
         </is>
       </c>
       <c r="N183">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O183">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P183">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="Q183">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R183">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S183">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T183">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U183">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V183">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W183">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X183">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y183">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z183">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AA183">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB183">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC183">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD183">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE183">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF183">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG183">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH183" t="inlineStr">
         <is>
@@ -30208,10 +30208,10 @@
         </is>
       </c>
       <c r="AJ183">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK183">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL183">
         <v>0</v>
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G196">
@@ -32257,64 +32257,64 @@
         </is>
       </c>
       <c r="N196">
-        <v>1.58</v>
+        <v>2.7</v>
       </c>
       <c r="O196">
-        <v>4.07</v>
+        <v>3.29</v>
       </c>
       <c r="P196">
-        <v>6.22</v>
+        <v>2.72</v>
       </c>
       <c r="Q196">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R196">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S196">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T196">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U196">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V196">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W196">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X196">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y196">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z196">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AA196">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AB196">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AC196">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="AD196">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE196">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF196">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG196">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH196" t="inlineStr">
         <is>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK196">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G197">
@@ -32420,64 +32420,64 @@
         </is>
       </c>
       <c r="N197">
-        <v>2.7</v>
+        <v>1.91</v>
       </c>
       <c r="O197">
-        <v>3.29</v>
+        <v>3.58</v>
       </c>
       <c r="P197">
-        <v>2.72</v>
+        <v>4.17</v>
       </c>
       <c r="Q197">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R197">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S197">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T197">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U197">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V197">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W197">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X197">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y197">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z197">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA197">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AB197">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AC197">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AD197">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE197">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF197">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG197">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32490,10 +32490,10 @@
         </is>
       </c>
       <c r="AJ197">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK197">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL197">
         <v>0</v>
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G198">
@@ -32583,64 +32583,64 @@
         </is>
       </c>
       <c r="N198">
-        <v>1.91</v>
+        <v>1.58</v>
       </c>
       <c r="O198">
-        <v>3.58</v>
+        <v>4.07</v>
       </c>
       <c r="P198">
-        <v>4.17</v>
+        <v>6.22</v>
       </c>
       <c r="Q198">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="R198">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S198">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T198">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U198">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V198">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W198">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X198">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y198">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z198">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AA198">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB198">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC198">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD198">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE198">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF198">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG198">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH198" t="inlineStr">
         <is>
@@ -32653,10 +32653,10 @@
         </is>
       </c>
       <c r="AJ198">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK198">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL198">
         <v>0</v>
@@ -33887,64 +33887,64 @@
         </is>
       </c>
       <c r="N206">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O206">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P206">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q206">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="R206">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="S206">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="T206">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U206">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="V206">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W206">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X206">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Y206">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z206">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AA206">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB206">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC206">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AD206">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE206">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF206">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG206">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AH206" t="inlineStr">
         <is>
@@ -33957,10 +33957,10 @@
         </is>
       </c>
       <c r="AJ206">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK206">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL206">
         <v>0</v>

--- a/jogos_2026-08-23.xlsx
+++ b/jogos_2026-08-23.xlsx
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G127">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G128">
@@ -36463,12 +36463,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G222">
@@ -36495,13 +36495,13 @@
         </is>
       </c>
       <c r="N222">
+        <v>2.13</v>
+      </c>
+      <c r="O222">
         <v>3.44</v>
       </c>
-      <c r="O222">
-        <v>3.42</v>
-      </c>
       <c r="P222">
-        <v>2.18</v>
+        <v>3.55</v>
       </c>
       <c r="Q222">
         <v>0</v>
@@ -36626,12 +36626,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G223">
@@ -36658,13 +36658,13 @@
         </is>
       </c>
       <c r="N223">
-        <v>2.13</v>
+        <v>3.44</v>
       </c>
       <c r="O223">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="P223">
-        <v>3.55</v>
+        <v>2.18</v>
       </c>
       <c r="Q223">
         <v>0</v>

--- a/jogos_2026-08-23.xlsx
+++ b/jogos_2026-08-23.xlsx
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q41">
         <v>2.69</v>
@@ -13675,13 +13675,13 @@
         </is>
       </c>
       <c r="N82">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O82">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q82">
         <v>2.72</v>
@@ -17433,55 +17433,55 @@
         <v>5.29</v>
       </c>
       <c r="Q105">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R105">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S105">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T105">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U105">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V105">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W105">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X105">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y105">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z105">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA105">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB105">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC105">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD105">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE105">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF105">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG105">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK105">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17596,10 +17596,10 @@
         <v>3.3</v>
       </c>
       <c r="Q106">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R106">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S106">
         <v>0</v>
@@ -17608,43 +17608,43 @@
         <v>0</v>
       </c>
       <c r="U106">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="V106">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W106">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X106">
         <v>0</v>
       </c>
       <c r="Y106">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z106">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA106">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AB106">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC106">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD106">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE106">
         <v>0</v>
       </c>
       <c r="AF106">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG106">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,80 +20195,80 @@
         </is>
       </c>
       <c r="N122">
-        <v>3.05</v>
+        <v>1.69</v>
       </c>
       <c r="O122">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P122">
-        <v>2.17</v>
+        <v>3.9</v>
       </c>
       <c r="Q122">
-        <v>3.83</v>
+        <v>2.15</v>
       </c>
       <c r="R122">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S122">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="T122">
-        <v>2.83</v>
+        <v>3.25</v>
       </c>
       <c r="U122">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="V122">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="W122">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X122">
         <v>1.04</v>
       </c>
       <c r="Y122">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="Z122">
-        <v>3.26</v>
+        <v>3.9</v>
       </c>
       <c r="AA122">
-        <v>2.02</v>
+        <v>1.68</v>
       </c>
       <c r="AB122">
-        <v>1.76</v>
+        <v>2.05</v>
       </c>
       <c r="AC122">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="AD122">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AE122">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="AF122">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AG122">
+        <v>2.06</v>
+      </c>
+      <c r="AH122" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI122" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ122">
+        <v>1.2</v>
+      </c>
+      <c r="AK122">
         <v>1.95</v>
-      </c>
-      <c r="AH122" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI122" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ122">
-        <v>1.62</v>
-      </c>
-      <c r="AK122">
-        <v>1.3</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,64 +20358,64 @@
         </is>
       </c>
       <c r="N123">
-        <v>1.69</v>
+        <v>3.05</v>
       </c>
       <c r="O123">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P123">
-        <v>3.9</v>
+        <v>2.17</v>
       </c>
       <c r="Q123">
-        <v>2.15</v>
+        <v>3.83</v>
       </c>
       <c r="R123">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S123">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="T123">
-        <v>3.25</v>
+        <v>2.83</v>
       </c>
       <c r="U123">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="V123">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="W123">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X123">
         <v>1.04</v>
       </c>
       <c r="Y123">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="Z123">
-        <v>3.9</v>
+        <v>3.26</v>
       </c>
       <c r="AA123">
-        <v>1.68</v>
+        <v>2.02</v>
       </c>
       <c r="AB123">
-        <v>2.05</v>
+        <v>1.76</v>
       </c>
       <c r="AC123">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="AD123">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AE123">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="AF123">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AG123">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.2</v>
+        <v>1.62</v>
       </c>
       <c r="AK123">
-        <v>1.95</v>
+        <v>1.3</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Savoia</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G131">
@@ -21662,19 +21662,19 @@
         </is>
       </c>
       <c r="N131">
-        <v>2.22</v>
+        <v>1.41</v>
       </c>
       <c r="O131">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="P131">
-        <v>3.25</v>
+        <v>6.76</v>
       </c>
       <c r="Q131">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="R131">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S131">
         <v>0</v>
@@ -21683,43 +21683,43 @@
         <v>0</v>
       </c>
       <c r="U131">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V131">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W131">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X131">
         <v>0</v>
       </c>
       <c r="Y131">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z131">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA131">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB131">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC131">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD131">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE131">
         <v>0</v>
       </c>
       <c r="AF131">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG131">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Savoia</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,19 +21825,19 @@
         </is>
       </c>
       <c r="N132">
-        <v>1.41</v>
+        <v>2.22</v>
       </c>
       <c r="O132">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="P132">
-        <v>6.76</v>
+        <v>3.25</v>
       </c>
       <c r="Q132">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="R132">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S132">
         <v>0</v>
@@ -21846,43 +21846,43 @@
         <v>0</v>
       </c>
       <c r="U132">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="V132">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W132">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X132">
         <v>0</v>
       </c>
       <c r="Y132">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z132">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AA132">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB132">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC132">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD132">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE132">
         <v>0</v>
       </c>
       <c r="AF132">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG132">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -22812,10 +22812,10 @@
         <v>4.16</v>
       </c>
       <c r="Q138">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="R138">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S138">
         <v>0</v>
@@ -22824,34 +22824,34 @@
         <v>0</v>
       </c>
       <c r="U138">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V138">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W138">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X138">
         <v>0</v>
       </c>
       <c r="Y138">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z138">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AA138">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB138">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC138">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD138">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE138">
         <v>0</v>
@@ -23464,34 +23464,34 @@
         <v>3.62</v>
       </c>
       <c r="Q142">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R142">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S142">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T142">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U142">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V142">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W142">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X142">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y142">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z142">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AA142">
         <v>1.79</v>
@@ -23500,19 +23500,19 @@
         <v>1.92</v>
       </c>
       <c r="AC142">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AD142">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE142">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF142">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG142">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH142" t="inlineStr">
         <is>
@@ -23525,10 +23525,10 @@
         </is>
       </c>
       <c r="AJ142">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK142">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL142">
         <v>0</v>
@@ -24270,64 +24270,64 @@
         </is>
       </c>
       <c r="N147">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O147">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P147">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q147">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="R147">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S147">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T147">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U147">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V147">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W147">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X147">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y147">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z147">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA147">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB147">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC147">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD147">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE147">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF147">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG147">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24340,10 +24340,10 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK147">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -24605,34 +24605,34 @@
         <v>4.81</v>
       </c>
       <c r="Q149">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R149">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S149">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T149">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="U149">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V149">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W149">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X149">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y149">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z149">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AA149">
         <v>2.05</v>
@@ -24641,19 +24641,19 @@
         <v>1.68</v>
       </c>
       <c r="AC149">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AD149">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE149">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF149">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG149">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH149" t="inlineStr">
         <is>
@@ -24666,10 +24666,10 @@
         </is>
       </c>
       <c r="AJ149">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK149">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL149">
         <v>0</v>
@@ -24768,34 +24768,34 @@
         <v>5.83</v>
       </c>
       <c r="Q150">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R150">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S150">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T150">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U150">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V150">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W150">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X150">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y150">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z150">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="AA150">
         <v>1.89</v>
@@ -24804,19 +24804,19 @@
         <v>1.83</v>
       </c>
       <c r="AC150">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AD150">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE150">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF150">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG150">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH150" t="inlineStr">
         <is>
@@ -24829,10 +24829,10 @@
         </is>
       </c>
       <c r="AJ150">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK150">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL150">
         <v>0</v>
@@ -24931,55 +24931,55 @@
         <v>4.16</v>
       </c>
       <c r="Q151">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R151">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S151">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T151">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U151">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V151">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W151">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X151">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y151">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z151">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA151">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB151">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AC151">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD151">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE151">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF151">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG151">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH151" t="inlineStr">
         <is>
@@ -24992,10 +24992,10 @@
         </is>
       </c>
       <c r="AJ151">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK151">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL151">
         <v>0</v>
@@ -25420,34 +25420,34 @@
         <v>7.31</v>
       </c>
       <c r="Q154">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R154">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S154">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T154">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U154">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V154">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W154">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X154">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y154">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z154">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="AA154">
         <v>1.8</v>
@@ -25456,19 +25456,19 @@
         <v>2</v>
       </c>
       <c r="AC154">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD154">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE154">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF154">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG154">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK154">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25583,55 +25583,55 @@
         <v>3.19</v>
       </c>
       <c r="Q155">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R155">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S155">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T155">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U155">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="V155">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W155">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X155">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y155">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z155">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA155">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AB155">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC155">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="AD155">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE155">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF155">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG155">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25644,10 +25644,10 @@
         </is>
       </c>
       <c r="AJ155">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK155">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -26561,55 +26561,55 @@
         <v>2.72</v>
       </c>
       <c r="Q161">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R161">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S161">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T161">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U161">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V161">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W161">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X161">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y161">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z161">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AA161">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB161">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC161">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AD161">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE161">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF161">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG161">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH161" t="inlineStr">
         <is>
@@ -26622,10 +26622,10 @@
         </is>
       </c>
       <c r="AJ161">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK161">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -27367,64 +27367,64 @@
         </is>
       </c>
       <c r="N166">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O166">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P166">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q166">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R166">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S166">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="T166">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U166">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="V166">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W166">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X166">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y166">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z166">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AA166">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB166">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC166">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AD166">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE166">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF166">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG166">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH166" t="inlineStr">
         <is>
@@ -27437,10 +27437,10 @@
         </is>
       </c>
       <c r="AJ166">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK166">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AL166">
         <v>0</v>
@@ -27530,64 +27530,64 @@
         </is>
       </c>
       <c r="N167">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O167">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P167">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q167">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R167">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S167">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T167">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U167">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="V167">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W167">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X167">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y167">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z167">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AA167">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB167">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AC167">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD167">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE167">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF167">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG167">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH167" t="inlineStr">
         <is>
@@ -27600,10 +27600,10 @@
         </is>
       </c>
       <c r="AJ167">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK167">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL167">
         <v>0</v>
@@ -27702,34 +27702,34 @@
         <v>12.7</v>
       </c>
       <c r="Q168">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R168">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S168">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T168">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U168">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V168">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W168">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X168">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y168">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z168">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="AA168">
         <v>1.95</v>
@@ -27738,19 +27738,19 @@
         <v>1.77</v>
       </c>
       <c r="AC168">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD168">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE168">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF168">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG168">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH168" t="inlineStr">
         <is>
@@ -27763,10 +27763,10 @@
         </is>
       </c>
       <c r="AJ168">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK168">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AL168">
         <v>0</v>
@@ -27865,55 +27865,55 @@
         <v>9</v>
       </c>
       <c r="Q169">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="R169">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="S169">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T169">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U169">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V169">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W169">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X169">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y169">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z169">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA169">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB169">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AC169">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AD169">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE169">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF169">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG169">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH169" t="inlineStr">
         <is>
@@ -27926,10 +27926,10 @@
         </is>
       </c>
       <c r="AJ169">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK169">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AL169">
         <v>0</v>
@@ -29006,55 +29006,55 @@
         <v>5.64</v>
       </c>
       <c r="Q176">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="R176">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S176">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T176">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U176">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V176">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W176">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X176">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y176">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z176">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA176">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB176">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC176">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD176">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE176">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF176">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG176">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK176">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29169,55 +29169,55 @@
         <v>2.72</v>
       </c>
       <c r="Q177">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="R177">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S177">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T177">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U177">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V177">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W177">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X177">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y177">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z177">
-        <v>0</v>
+        <v>4.87</v>
       </c>
       <c r="AA177">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB177">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC177">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AD177">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE177">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF177">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG177">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29230,10 +29230,10 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK177">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29332,55 +29332,55 @@
         <v>2.5</v>
       </c>
       <c r="Q178">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R178">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S178">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T178">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U178">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="V178">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W178">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X178">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y178">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z178">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AA178">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB178">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC178">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AD178">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE178">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF178">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG178">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH178" t="inlineStr">
         <is>
@@ -29393,10 +29393,10 @@
         </is>
       </c>
       <c r="AJ178">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK178">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL178">
         <v>0</v>
@@ -29486,64 +29486,64 @@
         </is>
       </c>
       <c r="N179">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="O179">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P179">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q179">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R179">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S179">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T179">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="U179">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V179">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W179">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X179">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y179">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z179">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA179">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB179">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC179">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD179">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE179">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF179">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG179">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH179" t="inlineStr">
         <is>
@@ -29556,10 +29556,10 @@
         </is>
       </c>
       <c r="AJ179">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AK179">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL179">
         <v>0</v>
@@ -29649,64 +29649,64 @@
         </is>
       </c>
       <c r="N180">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O180">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P180">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="Q180">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R180">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S180">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T180">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U180">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V180">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W180">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X180">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y180">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z180">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA180">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB180">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC180">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD180">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE180">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF180">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG180">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH180" t="inlineStr">
         <is>
@@ -29719,10 +29719,10 @@
         </is>
       </c>
       <c r="AJ180">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK180">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL180">
         <v>0</v>
@@ -30310,55 +30310,55 @@
         <v>2.77</v>
       </c>
       <c r="Q184">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R184">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S184">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T184">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U184">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V184">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W184">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X184">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y184">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z184">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AA184">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB184">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC184">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD184">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE184">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF184">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG184">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH184" t="inlineStr">
         <is>
@@ -30371,10 +30371,10 @@
         </is>
       </c>
       <c r="AJ184">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK184">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL184">
         <v>0</v>
@@ -30464,64 +30464,64 @@
         </is>
       </c>
       <c r="N185">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O185">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P185">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q185">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R185">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S185">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T185">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U185">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V185">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W185">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X185">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y185">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z185">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA185">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB185">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC185">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD185">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE185">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF185">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG185">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH185" t="inlineStr">
         <is>
@@ -30534,10 +30534,10 @@
         </is>
       </c>
       <c r="AJ185">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK185">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL185">
         <v>0</v>
@@ -30799,55 +30799,55 @@
         <v>2.46</v>
       </c>
       <c r="Q187">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R187">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S187">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T187">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U187">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="V187">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W187">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X187">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y187">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z187">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA187">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB187">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC187">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD187">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE187">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF187">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG187">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH187" t="inlineStr">
         <is>
@@ -30860,10 +30860,10 @@
         </is>
       </c>
       <c r="AJ187">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK187">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL187">
         <v>0</v>
@@ -30962,40 +30962,40 @@
         <v>6.15</v>
       </c>
       <c r="Q188">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="R188">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S188">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T188">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U188">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="V188">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W188">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X188">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y188">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z188">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AA188">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB188">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC188">
         <v>1.96</v>
@@ -31004,13 +31004,13 @@
         <v>1.84</v>
       </c>
       <c r="AE188">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF188">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG188">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH188" t="inlineStr">
         <is>
@@ -31023,10 +31023,10 @@
         </is>
       </c>
       <c r="AJ188">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK188">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AL188">
         <v>0</v>
@@ -31125,34 +31125,34 @@
         <v>1.84</v>
       </c>
       <c r="Q189">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R189">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S189">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T189">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U189">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V189">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W189">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X189">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y189">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z189">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA189">
         <v>1.84</v>
@@ -31161,19 +31161,19 @@
         <v>1.87</v>
       </c>
       <c r="AC189">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AD189">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE189">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF189">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG189">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH189" t="inlineStr">
         <is>
@@ -31186,10 +31186,10 @@
         </is>
       </c>
       <c r="AJ189">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK189">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AL189">
         <v>0</v>
@@ -31288,34 +31288,34 @@
         <v>6.14</v>
       </c>
       <c r="Q190">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R190">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S190">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T190">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U190">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V190">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W190">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X190">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y190">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z190">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA190">
         <v>1.66</v>
@@ -31324,19 +31324,19 @@
         <v>2.1</v>
       </c>
       <c r="AC190">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD190">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE190">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF190">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG190">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH190" t="inlineStr">
         <is>
@@ -31349,10 +31349,10 @@
         </is>
       </c>
       <c r="AJ190">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK190">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AL190">
         <v>0</v>
@@ -31451,34 +31451,34 @@
         <v>2.6</v>
       </c>
       <c r="Q191">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R191">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S191">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T191">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U191">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V191">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W191">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X191">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y191">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z191">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA191">
         <v>1.99</v>
@@ -31487,19 +31487,19 @@
         <v>1.73</v>
       </c>
       <c r="AC191">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AD191">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE191">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF191">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG191">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH191" t="inlineStr">
         <is>
@@ -31512,10 +31512,10 @@
         </is>
       </c>
       <c r="AJ191">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK191">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL191">
         <v>0</v>
@@ -31614,34 +31614,34 @@
         <v>5.71</v>
       </c>
       <c r="Q192">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="R192">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S192">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T192">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U192">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V192">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W192">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X192">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y192">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z192">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA192">
         <v>1.98</v>
@@ -31650,19 +31650,19 @@
         <v>1.73</v>
       </c>
       <c r="AC192">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AD192">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE192">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF192">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG192">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH192" t="inlineStr">
         <is>
@@ -31675,10 +31675,10 @@
         </is>
       </c>
       <c r="AJ192">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK192">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AL192">
         <v>0</v>
@@ -31940,55 +31940,55 @@
         <v>3.46</v>
       </c>
       <c r="Q194">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R194">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S194">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T194">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U194">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V194">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W194">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X194">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y194">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z194">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA194">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB194">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC194">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD194">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE194">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF194">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG194">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH194" t="inlineStr">
         <is>
@@ -32001,10 +32001,10 @@
         </is>
       </c>
       <c r="AJ194">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK194">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -32103,10 +32103,10 @@
         <v>0</v>
       </c>
       <c r="Q195">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="R195">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S195">
         <v>0</v>
@@ -32115,34 +32115,34 @@
         <v>0</v>
       </c>
       <c r="U195">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="V195">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W195">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X195">
         <v>0</v>
       </c>
       <c r="Y195">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z195">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA195">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB195">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC195">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD195">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE195">
         <v>0</v>
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G196">
@@ -32257,64 +32257,64 @@
         </is>
       </c>
       <c r="N196">
-        <v>2.7</v>
+        <v>1.91</v>
       </c>
       <c r="O196">
-        <v>3.29</v>
+        <v>3.58</v>
       </c>
       <c r="P196">
-        <v>2.72</v>
+        <v>4.17</v>
       </c>
       <c r="Q196">
-        <v>3.08</v>
+        <v>2.25</v>
       </c>
       <c r="R196">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S196">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="T196">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="U196">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="V196">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="W196">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X196">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y196">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z196">
-        <v>3.12</v>
+        <v>3.6</v>
       </c>
       <c r="AA196">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AB196">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AC196">
-        <v>3.39</v>
+        <v>3.16</v>
       </c>
       <c r="AD196">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE196">
         <v>1.08</v>
       </c>
       <c r="AF196">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AG196">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AH196" t="inlineStr">
         <is>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK196">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G197">
@@ -32420,64 +32420,64 @@
         </is>
       </c>
       <c r="N197">
-        <v>1.91</v>
+        <v>1.58</v>
       </c>
       <c r="O197">
-        <v>3.58</v>
+        <v>4.07</v>
       </c>
       <c r="P197">
-        <v>4.17</v>
+        <v>6.22</v>
       </c>
       <c r="Q197">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="R197">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="S197">
         <v>1.33</v>
       </c>
       <c r="T197">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U197">
-        <v>2.62</v>
+        <v>2.81</v>
       </c>
       <c r="V197">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W197">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X197">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y197">
         <v>1.25</v>
       </c>
       <c r="Z197">
-        <v>3.6</v>
+        <v>3.38</v>
       </c>
       <c r="AA197">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB197">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC197">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="AD197">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE197">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF197">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AG197">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32490,10 +32490,10 @@
         </is>
       </c>
       <c r="AJ197">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK197">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AL197">
         <v>0</v>
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G198">
@@ -32583,64 +32583,64 @@
         </is>
       </c>
       <c r="N198">
-        <v>1.58</v>
+        <v>2.7</v>
       </c>
       <c r="O198">
-        <v>4.07</v>
+        <v>3.29</v>
       </c>
       <c r="P198">
-        <v>6.22</v>
+        <v>2.72</v>
       </c>
       <c r="Q198">
-        <v>2.18</v>
+        <v>3.08</v>
       </c>
       <c r="R198">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="S198">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="T198">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="U198">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="V198">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W198">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X198">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y198">
+        <v>1.28</v>
+      </c>
+      <c r="Z198">
+        <v>3.12</v>
+      </c>
+      <c r="AA198">
+        <v>2.03</v>
+      </c>
+      <c r="AB198">
+        <v>1.83</v>
+      </c>
+      <c r="AC198">
+        <v>3.39</v>
+      </c>
+      <c r="AD198">
         <v>1.25</v>
       </c>
-      <c r="Z198">
-        <v>3.38</v>
-      </c>
-      <c r="AA198">
-        <v>2</v>
-      </c>
-      <c r="AB198">
-        <v>1.85</v>
-      </c>
-      <c r="AC198">
-        <v>3.1</v>
-      </c>
-      <c r="AD198">
-        <v>1.33</v>
-      </c>
       <c r="AE198">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF198">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AG198">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AH198" t="inlineStr">
         <is>
@@ -32653,10 +32653,10 @@
         </is>
       </c>
       <c r="AJ198">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK198">
-        <v>2.15</v>
+        <v>1.5</v>
       </c>
       <c r="AL198">
         <v>0</v>
@@ -33570,55 +33570,55 @@
         <v>0</v>
       </c>
       <c r="Q204">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="R204">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S204">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T204">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U204">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V204">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W204">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X204">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y204">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z204">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA204">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB204">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC204">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD204">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE204">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF204">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG204">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH204" t="inlineStr">
         <is>
@@ -33631,10 +33631,10 @@
         </is>
       </c>
       <c r="AJ204">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK204">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL204">
         <v>0</v>
@@ -33733,55 +33733,55 @@
         <v>0</v>
       </c>
       <c r="Q205">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R205">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S205">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T205">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U205">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V205">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W205">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X205">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y205">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z205">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA205">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB205">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC205">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD205">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE205">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF205">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG205">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH205" t="inlineStr">
         <is>
@@ -33794,10 +33794,10 @@
         </is>
       </c>
       <c r="AJ205">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AK205">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AL205">
         <v>0</v>
@@ -34050,64 +34050,64 @@
         </is>
       </c>
       <c r="N207">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O207">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P207">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Q207">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R207">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S207">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T207">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="U207">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V207">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W207">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X207">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y207">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z207">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="AA207">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB207">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC207">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AD207">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE207">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF207">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG207">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH207" t="inlineStr">
         <is>
@@ -34120,10 +34120,10 @@
         </is>
       </c>
       <c r="AJ207">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK207">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -34213,13 +34213,13 @@
         </is>
       </c>
       <c r="N208">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O208">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P208">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q208">
         <v>0</v>
@@ -34385,10 +34385,10 @@
         <v>4.94</v>
       </c>
       <c r="Q209">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R209">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S209">
         <v>0</v>
@@ -34397,34 +34397,34 @@
         <v>0</v>
       </c>
       <c r="U209">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="V209">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W209">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X209">
         <v>0</v>
       </c>
       <c r="Y209">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z209">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA209">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB209">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC209">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD209">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE209">
         <v>0</v>
@@ -34874,55 +34874,55 @@
         <v>2.52</v>
       </c>
       <c r="Q212">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R212">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S212">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T212">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U212">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V212">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W212">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X212">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y212">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z212">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA212">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB212">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC212">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AD212">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE212">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF212">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG212">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH212" t="inlineStr">
         <is>
@@ -34935,10 +34935,10 @@
         </is>
       </c>
       <c r="AJ212">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK212">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL212">
         <v>0</v>
@@ -35028,64 +35028,64 @@
         </is>
       </c>
       <c r="N213">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O213">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P213">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q213">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="R213">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="S213">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T213">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="U213">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="V213">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W213">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X213">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y213">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z213">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA213">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB213">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC213">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD213">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE213">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF213">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG213">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH213" t="inlineStr">
         <is>
@@ -35098,10 +35098,10 @@
         </is>
       </c>
       <c r="AJ213">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK213">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AL213">
         <v>0</v>
@@ -35200,55 +35200,55 @@
         <v>16</v>
       </c>
       <c r="Q214">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="R214">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S214">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T214">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U214">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V214">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W214">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X214">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y214">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z214">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA214">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB214">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC214">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD214">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE214">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF214">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG214">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH214" t="inlineStr">
         <is>
@@ -35261,10 +35261,10 @@
         </is>
       </c>
       <c r="AJ214">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK214">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AL214">
         <v>0</v>
@@ -38288,64 +38288,64 @@
         </is>
       </c>
       <c r="N233">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O233">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P233">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="Q233">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="R233">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S233">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T233">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U233">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V233">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W233">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X233">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y233">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z233">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA233">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB233">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC233">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD233">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE233">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF233">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG233">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH233" t="inlineStr">
         <is>
@@ -38358,10 +38358,10 @@
         </is>
       </c>
       <c r="AJ233">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK233">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL233">
         <v>0</v>

--- a/jogos_2026-08-23.xlsx
+++ b/jogos_2026-08-23.xlsx
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,80 +3406,80 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.49</v>
+        <v>3.41</v>
       </c>
       <c r="O19">
-        <v>3.25</v>
+        <v>3.48</v>
       </c>
       <c r="P19">
-        <v>2.49</v>
+        <v>1.93</v>
       </c>
       <c r="Q19">
-        <v>3.1</v>
+        <v>4.08</v>
       </c>
       <c r="R19">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S19">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="T19">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="U19">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="V19">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="W19">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X19">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y19">
+        <v>1.24</v>
+      </c>
+      <c r="Z19">
+        <v>3.9</v>
+      </c>
+      <c r="AA19">
+        <v>1.78</v>
+      </c>
+      <c r="AB19">
+        <v>1.98</v>
+      </c>
+      <c r="AC19">
+        <v>2.91</v>
+      </c>
+      <c r="AD19">
+        <v>1.39</v>
+      </c>
+      <c r="AE19">
+        <v>1.13</v>
+      </c>
+      <c r="AF19">
+        <v>1.62</v>
+      </c>
+      <c r="AG19">
+        <v>2.15</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19">
+        <v>1.69</v>
+      </c>
+      <c r="AK19">
         <v>1.3</v>
-      </c>
-      <c r="Z19">
-        <v>3.2</v>
-      </c>
-      <c r="AA19">
-        <v>1.94</v>
-      </c>
-      <c r="AB19">
-        <v>1.77</v>
-      </c>
-      <c r="AC19">
-        <v>3.4</v>
-      </c>
-      <c r="AD19">
-        <v>1.29</v>
-      </c>
-      <c r="AE19">
-        <v>1.08</v>
-      </c>
-      <c r="AF19">
-        <v>1.72</v>
-      </c>
-      <c r="AG19">
-        <v>2.05</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19">
-        <v>1.41</v>
-      </c>
-      <c r="AK19">
-        <v>1.44</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>3.41</v>
+        <v>1.97</v>
       </c>
       <c r="O20">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="P20">
-        <v>1.93</v>
+        <v>3.4</v>
       </c>
       <c r="Q20">
-        <v>4.08</v>
+        <v>2.5</v>
       </c>
       <c r="R20">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S20">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="T20">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="U20">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="V20">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W20">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X20">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y20">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Z20">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="AA20">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="AB20">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AC20">
-        <v>2.91</v>
+        <v>3.14</v>
       </c>
       <c r="AD20">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="AE20">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF20">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AG20">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.69</v>
+        <v>1.23</v>
       </c>
       <c r="AK20">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.97</v>
+        <v>2.49</v>
       </c>
       <c r="O21">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P21">
-        <v>3.4</v>
+        <v>2.49</v>
       </c>
       <c r="Q21">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="R21">
         <v>2.1</v>
       </c>
       <c r="S21">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T21">
         <v>2.9</v>
       </c>
       <c r="U21">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="V21">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="W21">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X21">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y21">
         <v>1.3</v>
       </c>
       <c r="Z21">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AA21">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AB21">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AC21">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="AD21">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE21">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF21">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AG21">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.23</v>
+        <v>1.41</v>
       </c>
       <c r="AK21">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G118">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G119">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G120">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G121">
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G183">
@@ -30138,64 +30138,64 @@
         </is>
       </c>
       <c r="N183">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="O183">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="P183">
-        <v>3.25</v>
+        <v>3.37</v>
       </c>
       <c r="Q183">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="R183">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="S183">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="T183">
-        <v>2.26</v>
+        <v>2.05</v>
       </c>
       <c r="U183">
-        <v>3.42</v>
+        <v>4</v>
       </c>
       <c r="V183">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="W183">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X183">
+        <v>1.14</v>
+      </c>
+      <c r="Y183">
+        <v>1.65</v>
+      </c>
+      <c r="Z183">
+        <v>2.12</v>
+      </c>
+      <c r="AA183">
+        <v>2.88</v>
+      </c>
+      <c r="AB183">
+        <v>1.33</v>
+      </c>
+      <c r="AC183">
+        <v>6</v>
+      </c>
+      <c r="AD183">
         <v>1.07</v>
       </c>
-      <c r="Y183">
-        <v>1.46</v>
-      </c>
-      <c r="Z183">
-        <v>2.38</v>
-      </c>
-      <c r="AA183">
-        <v>2.49</v>
-      </c>
-      <c r="AB183">
-        <v>1.4</v>
-      </c>
-      <c r="AC183">
-        <v>5</v>
-      </c>
-      <c r="AD183">
-        <v>1.14</v>
-      </c>
       <c r="AE183">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF183">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AG183">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AH183" t="inlineStr">
         <is>
@@ -30208,10 +30208,10 @@
         </is>
       </c>
       <c r="AJ183">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AK183">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AL183">
         <v>0</v>
@@ -30269,12 +30269,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G184">
@@ -30301,64 +30301,64 @@
         </is>
       </c>
       <c r="N184">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="O184">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="P184">
-        <v>3.37</v>
+        <v>3.25</v>
       </c>
       <c r="Q184">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
       <c r="R184">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="S184">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="T184">
+        <v>2.26</v>
+      </c>
+      <c r="U184">
+        <v>3.42</v>
+      </c>
+      <c r="V184">
+        <v>1.25</v>
+      </c>
+      <c r="W184">
+        <v>1.01</v>
+      </c>
+      <c r="X184">
+        <v>1.07</v>
+      </c>
+      <c r="Y184">
+        <v>1.46</v>
+      </c>
+      <c r="Z184">
+        <v>2.38</v>
+      </c>
+      <c r="AA184">
+        <v>2.49</v>
+      </c>
+      <c r="AB184">
+        <v>1.4</v>
+      </c>
+      <c r="AC184">
+        <v>5</v>
+      </c>
+      <c r="AD184">
+        <v>1.14</v>
+      </c>
+      <c r="AE184">
+        <v>1.04</v>
+      </c>
+      <c r="AF184">
         <v>2.05</v>
       </c>
-      <c r="U184">
-        <v>4</v>
-      </c>
-      <c r="V184">
-        <v>1.2</v>
-      </c>
-      <c r="W184">
-        <v>1.03</v>
-      </c>
-      <c r="X184">
-        <v>1.14</v>
-      </c>
-      <c r="Y184">
-        <v>1.65</v>
-      </c>
-      <c r="Z184">
-        <v>2.12</v>
-      </c>
-      <c r="AA184">
-        <v>2.88</v>
-      </c>
-      <c r="AB184">
-        <v>1.33</v>
-      </c>
-      <c r="AC184">
-        <v>6</v>
-      </c>
-      <c r="AD184">
-        <v>1.07</v>
-      </c>
-      <c r="AE184">
-        <v>1.02</v>
-      </c>
-      <c r="AF184">
-        <v>2.3</v>
-      </c>
       <c r="AG184">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AH184" t="inlineStr">
         <is>
@@ -30371,10 +30371,10 @@
         </is>
       </c>
       <c r="AJ184">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AK184">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AL184">
         <v>0</v>
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Batman Petrolspor</t>
         </is>
       </c>
       <c r="G186">
@@ -30627,64 +30627,64 @@
         </is>
       </c>
       <c r="N186">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O186">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P186">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q186">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R186">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S186">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T186">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U186">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V186">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W186">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X186">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y186">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z186">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA186">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB186">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC186">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD186">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE186">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF186">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG186">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH186" t="inlineStr">
         <is>
@@ -30697,10 +30697,10 @@
         </is>
       </c>
       <c r="AJ186">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK186">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AL186">
         <v>0</v>
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Batman Petrolspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G187">
@@ -30790,64 +30790,64 @@
         </is>
       </c>
       <c r="N187">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O187">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P187">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q187">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R187">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S187">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T187">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U187">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V187">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W187">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X187">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y187">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z187">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA187">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB187">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC187">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD187">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE187">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF187">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG187">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH187" t="inlineStr">
         <is>
@@ -30860,10 +30860,10 @@
         </is>
       </c>
       <c r="AJ187">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK187">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL187">
         <v>0</v>
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G201">
@@ -33072,64 +33072,64 @@
         </is>
       </c>
       <c r="N201">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O201">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P201">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Q201">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="R201">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S201">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T201">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U201">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V201">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W201">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X201">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y201">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z201">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA201">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB201">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC201">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD201">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE201">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF201">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG201">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH201" t="inlineStr">
         <is>
@@ -33142,10 +33142,10 @@
         </is>
       </c>
       <c r="AJ201">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK201">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL201">
         <v>0</v>
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G202">
@@ -33235,64 +33235,64 @@
         </is>
       </c>
       <c r="N202">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O202">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P202">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q202">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="R202">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S202">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T202">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U202">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V202">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W202">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X202">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y202">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z202">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AA202">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB202">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC202">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD202">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE202">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF202">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG202">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH202" t="inlineStr">
         <is>
@@ -33305,10 +33305,10 @@
         </is>
       </c>
       <c r="AJ202">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK202">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL202">
         <v>0</v>
@@ -33692,12 +33692,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G205">
@@ -33733,55 +33733,55 @@
         <v>0</v>
       </c>
       <c r="Q205">
-        <v>2.02</v>
+        <v>4.33</v>
       </c>
       <c r="R205">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="S205">
         <v>1.33</v>
       </c>
       <c r="T205">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="U205">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="V205">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W205">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X205">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y205">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z205">
-        <v>3.58</v>
+        <v>3.55</v>
       </c>
       <c r="AA205">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB205">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AC205">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AD205">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AE205">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF205">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AG205">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AH205" t="inlineStr">
         <is>
@@ -33794,10 +33794,10 @@
         </is>
       </c>
       <c r="AJ205">
-        <v>1.13</v>
+        <v>1.9</v>
       </c>
       <c r="AK205">
-        <v>2.4</v>
+        <v>1.16</v>
       </c>
       <c r="AL205">
         <v>0</v>
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G206">
@@ -33896,55 +33896,55 @@
         <v>0</v>
       </c>
       <c r="Q206">
-        <v>4.33</v>
+        <v>2.02</v>
       </c>
       <c r="R206">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S206">
         <v>1.33</v>
       </c>
       <c r="T206">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="U206">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="V206">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W206">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X206">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y206">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z206">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="AA206">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB206">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AC206">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AD206">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AE206">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF206">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AG206">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AH206" t="inlineStr">
         <is>
@@ -33957,10 +33957,10 @@
         </is>
       </c>
       <c r="AJ206">
-        <v>1.9</v>
+        <v>1.13</v>
       </c>
       <c r="AK206">
-        <v>1.16</v>
+        <v>2.4</v>
       </c>
       <c r="AL206">
         <v>0</v>
@@ -37115,12 +37115,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G226">
@@ -37156,55 +37156,55 @@
         <v>0</v>
       </c>
       <c r="Q226">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R226">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S226">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T226">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U226">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V226">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W226">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X226">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y226">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z226">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AA226">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB226">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC226">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD226">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AE226">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF226">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG226">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH226" t="inlineStr">
         <is>
@@ -37217,10 +37217,10 @@
         </is>
       </c>
       <c r="AJ226">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK226">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL226">
         <v>0</v>
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G227">
@@ -37319,55 +37319,55 @@
         <v>0</v>
       </c>
       <c r="Q227">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R227">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S227">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T227">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U227">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V227">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W227">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X227">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y227">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z227">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA227">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB227">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC227">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD227">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE227">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF227">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG227">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH227" t="inlineStr">
         <is>
@@ -37380,10 +37380,10 @@
         </is>
       </c>
       <c r="AJ227">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK227">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL227">
         <v>0</v>

--- a/jogos_2026-08-23.xlsx
+++ b/jogos_2026-08-23.xlsx
@@ -4067,10 +4067,10 @@
         <v>0</v>
       </c>
       <c r="Q23">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="R23">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="S23">
         <v>1.31</v>
@@ -4082,7 +4082,7 @@
         <v>2.4</v>
       </c>
       <c r="V23">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W23">
         <v>1.08</v>
@@ -4097,7 +4097,7 @@
         <v>4.15</v>
       </c>
       <c r="AA23">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AB23">
         <v>2.14</v>
@@ -4106,7 +4106,7 @@
         <v>2.56</v>
       </c>
       <c r="AD23">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE23">
         <v>1.17</v>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AK23">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G155">
@@ -25583,55 +25583,55 @@
         <v>0</v>
       </c>
       <c r="Q155">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="R155">
-        <v>2.01</v>
+        <v>2.98</v>
       </c>
       <c r="S155">
-        <v>1.4</v>
+        <v>1.14</v>
       </c>
       <c r="T155">
-        <v>2.75</v>
+        <v>4.2</v>
       </c>
       <c r="U155">
-        <v>3.08</v>
+        <v>1.97</v>
       </c>
       <c r="V155">
+        <v>1.74</v>
+      </c>
+      <c r="W155">
+        <v>1.16</v>
+      </c>
+      <c r="X155">
+        <v>1</v>
+      </c>
+      <c r="Y155">
+        <v>1.05</v>
+      </c>
+      <c r="Z155">
+        <v>6.4</v>
+      </c>
+      <c r="AA155">
+        <v>1.32</v>
+      </c>
+      <c r="AB155">
+        <v>2.88</v>
+      </c>
+      <c r="AC155">
+        <v>1.9</v>
+      </c>
+      <c r="AD155">
+        <v>1.8</v>
+      </c>
+      <c r="AE155">
         <v>1.3</v>
       </c>
-      <c r="W155">
-        <v>1.01</v>
-      </c>
-      <c r="X155">
-        <v>1.01</v>
-      </c>
-      <c r="Y155">
-        <v>1.32</v>
-      </c>
-      <c r="Z155">
-        <v>2.88</v>
-      </c>
-      <c r="AA155">
-        <v>2.09</v>
-      </c>
-      <c r="AB155">
-        <v>1.66</v>
-      </c>
-      <c r="AC155">
-        <v>3.8</v>
-      </c>
-      <c r="AD155">
-        <v>1.19</v>
-      </c>
-      <c r="AE155">
-        <v>1.02</v>
-      </c>
       <c r="AF155">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AG155">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25644,10 +25644,10 @@
         </is>
       </c>
       <c r="AJ155">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="AK155">
-        <v>1.78</v>
+        <v>5</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G156">
@@ -25746,71 +25746,71 @@
         <v>0</v>
       </c>
       <c r="Q156">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="R156">
-        <v>2.98</v>
+        <v>2.01</v>
       </c>
       <c r="S156">
-        <v>1.14</v>
+        <v>1.4</v>
       </c>
       <c r="T156">
-        <v>4.2</v>
+        <v>2.75</v>
       </c>
       <c r="U156">
-        <v>1.97</v>
+        <v>3.08</v>
       </c>
       <c r="V156">
-        <v>1.74</v>
+        <v>1.3</v>
       </c>
       <c r="W156">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="X156">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y156">
-        <v>1.05</v>
+        <v>1.32</v>
       </c>
       <c r="Z156">
-        <v>6.4</v>
+        <v>2.88</v>
       </c>
       <c r="AA156">
-        <v>1.32</v>
+        <v>2.09</v>
       </c>
       <c r="AB156">
-        <v>2.88</v>
+        <v>1.66</v>
       </c>
       <c r="AC156">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="AD156">
+        <v>1.19</v>
+      </c>
+      <c r="AE156">
+        <v>1.02</v>
+      </c>
+      <c r="AF156">
+        <v>1.89</v>
+      </c>
+      <c r="AG156">
         <v>1.8</v>
       </c>
-      <c r="AE156">
+      <c r="AH156" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI156" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ156">
         <v>1.3</v>
       </c>
-      <c r="AF156">
-        <v>1.88</v>
-      </c>
-      <c r="AG156">
-        <v>1.81</v>
-      </c>
-      <c r="AH156" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI156" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ156">
-        <v>1.08</v>
-      </c>
       <c r="AK156">
-        <v>5</v>
+        <v>1.78</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G200">
@@ -32918,56 +32918,56 @@
         <v>0</v>
       </c>
       <c r="Q200">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="R200">
         <v>2</v>
       </c>
       <c r="S200">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T200">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="U200">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="V200">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W200">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X200">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y200">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z200">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AA200">
+        <v>2.25</v>
+      </c>
+      <c r="AB200">
+        <v>1.57</v>
+      </c>
+      <c r="AC200">
+        <v>4</v>
+      </c>
+      <c r="AD200">
+        <v>1.2</v>
+      </c>
+      <c r="AE200">
+        <v>1.05</v>
+      </c>
+      <c r="AF200">
         <v>2.1</v>
       </c>
-      <c r="AB200">
+      <c r="AG200">
         <v>1.67</v>
       </c>
-      <c r="AC200">
-        <v>3.75</v>
-      </c>
-      <c r="AD200">
-        <v>1.22</v>
-      </c>
-      <c r="AE200">
-        <v>1.06</v>
-      </c>
-      <c r="AF200">
-        <v>1.85</v>
-      </c>
-      <c r="AG200">
-        <v>1.87</v>
-      </c>
       <c r="AH200" t="inlineStr">
         <is>
           <t>[]</t>
@@ -32979,10 +32979,10 @@
         </is>
       </c>
       <c r="AJ200">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK200">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AL200">
         <v>0</v>
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G201">
@@ -33072,64 +33072,64 @@
         </is>
       </c>
       <c r="N201">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O201">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P201">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q201">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="R201">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S201">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T201">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U201">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V201">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W201">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X201">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y201">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z201">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AA201">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB201">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC201">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD201">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE201">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF201">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG201">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH201" t="inlineStr">
         <is>
@@ -33142,10 +33142,10 @@
         </is>
       </c>
       <c r="AJ201">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK201">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL201">
         <v>0</v>
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G202">
@@ -33235,64 +33235,64 @@
         </is>
       </c>
       <c r="N202">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O202">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P202">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Q202">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R202">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S202">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T202">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U202">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V202">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W202">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X202">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y202">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z202">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA202">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB202">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC202">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD202">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE202">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF202">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG202">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH202" t="inlineStr">
         <is>
@@ -33305,10 +33305,10 @@
         </is>
       </c>
       <c r="AJ202">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK202">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL202">
         <v>0</v>

--- a/jogos_2026-08-23.xlsx
+++ b/jogos_2026-08-23.xlsx
@@ -1299,7 +1299,7 @@
         <v>2.2</v>
       </c>
       <c r="R6">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="S6">
         <v>1.28</v>
@@ -1308,10 +1308,10 @@
         <v>3.14</v>
       </c>
       <c r="U6">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="V6">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W6">
         <v>1.08</v>
@@ -1323,28 +1323,28 @@
         <v>1.14</v>
       </c>
       <c r="Z6">
-        <v>4.3</v>
+        <v>4.35</v>
       </c>
       <c r="AA6">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AB6">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AC6">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="AD6">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE6">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF6">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AG6">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK6">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="O7">
         <v>4.2</v>
       </c>
       <c r="P7">
-        <v>4.94</v>
+        <v>4.8</v>
       </c>
       <c r="Q7">
         <v>2.05</v>
@@ -1477,19 +1477,19 @@
         <v>1.55</v>
       </c>
       <c r="W7">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y7">
         <v>1.19</v>
       </c>
       <c r="Z7">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="AA7">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB7">
         <v>2.25</v>
@@ -1501,7 +1501,7 @@
         <v>1.45</v>
       </c>
       <c r="AE7">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AF7">
         <v>1.64</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK7">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1785,55 +1785,55 @@
         <v>3.1</v>
       </c>
       <c r="Q9">
-        <v>2.63</v>
+        <v>2.53</v>
       </c>
       <c r="R9">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="S9">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T9">
+        <v>2.8</v>
+      </c>
+      <c r="U9">
         <v>2.75</v>
       </c>
-      <c r="U9">
-        <v>2.8</v>
-      </c>
       <c r="V9">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W9">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="Z9">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AA9">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AB9">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AC9">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AD9">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE9">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF9">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AG9">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK9">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2265,19 +2265,19 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.35</v>
+        <v>2.58</v>
       </c>
       <c r="O12">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P12">
-        <v>2.65</v>
+        <v>2.27</v>
       </c>
       <c r="Q12">
-        <v>3.46</v>
+        <v>3.06</v>
       </c>
       <c r="R12">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="S12">
         <v>1.36</v>
@@ -2286,13 +2286,13 @@
         <v>2.93</v>
       </c>
       <c r="U12">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="V12">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W12">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X12">
         <v>1.01</v>
@@ -2310,19 +2310,19 @@
         <v>2.03</v>
       </c>
       <c r="AC12">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="AD12">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AE12">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF12">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG12">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>1.5</v>
       </c>
       <c r="AK12">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,19 +2428,19 @@
         </is>
       </c>
       <c r="N13">
-        <v>3.19</v>
+        <v>3.4</v>
       </c>
       <c r="O13">
-        <v>3.7</v>
+        <v>4.05</v>
       </c>
       <c r="P13">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="Q13">
-        <v>3.75</v>
+        <v>4.06</v>
       </c>
       <c r="R13">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="S13">
         <v>1.22</v>
@@ -2467,13 +2467,13 @@
         <v>5.5</v>
       </c>
       <c r="AA13">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AB13">
         <v>2.7</v>
       </c>
       <c r="AC13">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="AD13">
         <v>1.67</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK13">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2754,25 +2754,25 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="O15">
-        <v>4.29</v>
+        <v>3.9</v>
       </c>
       <c r="P15">
-        <v>5.2</v>
+        <v>3.88</v>
       </c>
       <c r="Q15">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="R15">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="S15">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T15">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="U15">
         <v>2.23</v>
@@ -2793,22 +2793,22 @@
         <v>4.6</v>
       </c>
       <c r="AA15">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB15">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="AC15">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="AD15">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AE15">
         <v>1.22</v>
       </c>
       <c r="AF15">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG15">
         <v>2.3</v>
@@ -2827,7 +2827,7 @@
         <v>1.22</v>
       </c>
       <c r="AK15">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.46</v>
+        <v>1.97</v>
       </c>
       <c r="O18">
-        <v>4.55</v>
+        <v>3.5</v>
       </c>
       <c r="P18">
-        <v>5.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q18">
+        <v>2.5</v>
+      </c>
+      <c r="R18">
+        <v>2.1</v>
+      </c>
+      <c r="S18">
+        <v>1.36</v>
+      </c>
+      <c r="T18">
+        <v>2.9</v>
+      </c>
+      <c r="U18">
+        <v>2.7</v>
+      </c>
+      <c r="V18">
+        <v>1.4</v>
+      </c>
+      <c r="W18">
+        <v>1.04</v>
+      </c>
+      <c r="X18">
+        <v>1.05</v>
+      </c>
+      <c r="Y18">
+        <v>1.3</v>
+      </c>
+      <c r="Z18">
+        <v>3.3</v>
+      </c>
+      <c r="AA18">
         <v>1.91</v>
       </c>
-      <c r="R18">
-        <v>2.4</v>
-      </c>
-      <c r="S18">
-        <v>1.25</v>
-      </c>
-      <c r="T18">
-        <v>3.38</v>
-      </c>
-      <c r="U18">
-        <v>2.16</v>
-      </c>
-      <c r="V18">
-        <v>1.52</v>
-      </c>
-      <c r="W18">
-        <v>1.1</v>
-      </c>
-      <c r="X18">
-        <v>1.02</v>
-      </c>
-      <c r="Y18">
-        <v>1.18</v>
-      </c>
-      <c r="Z18">
-        <v>4.5</v>
-      </c>
-      <c r="AA18">
-        <v>1.6</v>
-      </c>
       <c r="AB18">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AC18">
-        <v>2.38</v>
+        <v>3.14</v>
       </c>
       <c r="AD18">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="AE18">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AF18">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG18">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AK18">
-        <v>2.41</v>
+        <v>1.7</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.97</v>
+        <v>1.46</v>
       </c>
       <c r="O20">
-        <v>3.5</v>
+        <v>4.55</v>
       </c>
       <c r="P20">
-        <v>3.4</v>
+        <v>5.3</v>
       </c>
       <c r="Q20">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="R20">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="S20">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="T20">
-        <v>2.9</v>
+        <v>3.38</v>
       </c>
       <c r="U20">
-        <v>2.7</v>
+        <v>2.16</v>
       </c>
       <c r="V20">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="W20">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X20">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="Z20">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="AA20">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AB20">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AC20">
-        <v>3.14</v>
+        <v>2.38</v>
       </c>
       <c r="AD20">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="AE20">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AF20">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG20">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AK20">
-        <v>1.7</v>
+        <v>2.41</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="O26">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="P26">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="Q26">
         <v>3.52</v>
@@ -4565,10 +4565,10 @@
         <v>1.44</v>
       </c>
       <c r="T26">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="U26">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="V26">
         <v>1.34</v>
@@ -4580,19 +4580,19 @@
         <v>1.04</v>
       </c>
       <c r="Y26">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z26">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="AA26">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AB26">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AC26">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AD26">
         <v>1.26</v>
@@ -4601,10 +4601,10 @@
         <v>1.08</v>
       </c>
       <c r="AF26">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AG26">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AK26">
         <v>1.4</v>
@@ -5362,16 +5362,16 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="O31">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="P31">
-        <v>7.65</v>
+        <v>7</v>
       </c>
       <c r="Q31">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="R31">
         <v>3</v>
@@ -5380,13 +5380,13 @@
         <v>1.17</v>
       </c>
       <c r="T31">
-        <v>4.25</v>
+        <v>4.8</v>
       </c>
       <c r="U31">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="V31">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="W31">
         <v>1.25</v>
@@ -5404,19 +5404,19 @@
         <v>1.28</v>
       </c>
       <c r="AB31">
-        <v>3.24</v>
+        <v>3.56</v>
       </c>
       <c r="AC31">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AD31">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="AE31">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AF31">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG31">
         <v>2.4</v>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AK31">
         <v>3.45</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="O35">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P35">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="Q35">
         <v>2.61</v>
@@ -6032,13 +6032,13 @@
         <v>1.24</v>
       </c>
       <c r="T35">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="U35">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="V35">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W35">
         <v>1.12</v>
@@ -6047,16 +6047,16 @@
         <v>1.03</v>
       </c>
       <c r="Y35">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z35">
-        <v>4.6</v>
+        <v>4.86</v>
       </c>
       <c r="AA35">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AB35">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="AC35">
         <v>2.29</v>
@@ -6065,13 +6065,13 @@
         <v>1.55</v>
       </c>
       <c r="AE35">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AF35">
         <v>1.45</v>
       </c>
       <c r="AG35">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AK35">
         <v>1.62</v>
@@ -6177,19 +6177,19 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="O36">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="P36">
-        <v>6.07</v>
+        <v>5.5</v>
       </c>
       <c r="Q36">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="R36">
-        <v>2.45</v>
+        <v>2.31</v>
       </c>
       <c r="S36">
         <v>1.25</v>
@@ -6198,40 +6198,40 @@
         <v>3.55</v>
       </c>
       <c r="U36">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="V36">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="W36">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X36">
         <v>1.03</v>
       </c>
       <c r="Y36">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z36">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="AA36">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AB36">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="AC36">
         <v>2.5</v>
       </c>
       <c r="AD36">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AE36">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF36">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AG36">
         <v>2.01</v>
@@ -6250,7 +6250,7 @@
         <v>1.18</v>
       </c>
       <c r="AK36">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q37">
         <v>2.2</v>
@@ -6355,7 +6355,7 @@
         <v>2.4</v>
       </c>
       <c r="S37">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T37">
         <v>3.4</v>
@@ -6367,19 +6367,19 @@
         <v>1.55</v>
       </c>
       <c r="W37">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X37">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y37">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z37">
-        <v>4.45</v>
+        <v>4.8</v>
       </c>
       <c r="AA37">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AB37">
         <v>2.2</v>
@@ -6388,16 +6388,16 @@
         <v>2.5</v>
       </c>
       <c r="AD37">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AE37">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AF37">
         <v>1.58</v>
       </c>
       <c r="AG37">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6666,19 +6666,19 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="O39">
-        <v>5.15</v>
+        <v>4.65</v>
       </c>
       <c r="P39">
-        <v>8.4</v>
+        <v>7.7</v>
       </c>
       <c r="Q39">
         <v>1.83</v>
       </c>
       <c r="R39">
-        <v>2.35</v>
+        <v>2.62</v>
       </c>
       <c r="S39">
         <v>1.25</v>
@@ -6699,19 +6699,19 @@
         <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z39">
-        <v>4.65</v>
+        <v>4.72</v>
       </c>
       <c r="AA39">
         <v>1.62</v>
       </c>
       <c r="AB39">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="AC39">
-        <v>2.31</v>
+        <v>2.52</v>
       </c>
       <c r="AD39">
         <v>1.52</v>
@@ -6736,7 +6736,7 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AK39">
         <v>2.89</v>
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="O40">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P40">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="Q40">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="R40">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="S40">
         <v>1.3</v>
       </c>
       <c r="T40">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="U40">
-        <v>2.63</v>
+        <v>2.36</v>
       </c>
       <c r="V40">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W40">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X40">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y40">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z40">
-        <v>3.9</v>
+        <v>4.26</v>
       </c>
       <c r="AA40">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AB40">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AC40">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="AD40">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AE40">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AF40">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AG40">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK40">
         <v>1.53</v>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="O41">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="P41">
-        <v>3.98</v>
+        <v>3.8</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7155,40 +7155,40 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="O42">
-        <v>5.01</v>
+        <v>5.5</v>
       </c>
       <c r="P42">
-        <v>6.13</v>
+        <v>6.7</v>
       </c>
       <c r="Q42">
         <v>1.7</v>
       </c>
       <c r="R42">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="S42">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="T42">
         <v>4.35</v>
       </c>
       <c r="U42">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="V42">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="W42">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="X42">
         <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="Z42">
         <v>7</v>
@@ -7200,7 +7200,7 @@
         <v>3.31</v>
       </c>
       <c r="AC42">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AD42">
         <v>1.94</v>
@@ -7209,10 +7209,10 @@
         <v>1.42</v>
       </c>
       <c r="AF42">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AG42">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AK42">
         <v>3.1</v>
@@ -7481,25 +7481,25 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="O44">
-        <v>5.28</v>
+        <v>4.8</v>
       </c>
       <c r="P44">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="Q44">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="R44">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="S44">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="T44">
-        <v>3.94</v>
+        <v>4.5</v>
       </c>
       <c r="U44">
         <v>1.99</v>
@@ -7514,31 +7514,31 @@
         <v>1.02</v>
       </c>
       <c r="Y44">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z44">
-        <v>5.35</v>
+        <v>5.75</v>
       </c>
       <c r="AA44">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB44">
-        <v>2.9</v>
+        <v>2.72</v>
       </c>
       <c r="AC44">
-        <v>1.82</v>
+        <v>2.15</v>
       </c>
       <c r="AD44">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
       <c r="AE44">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AF44">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG44">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AK44">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,19 +7644,19 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.31</v>
+        <v>2.19</v>
       </c>
       <c r="O45">
-        <v>3.84</v>
+        <v>3.6</v>
       </c>
       <c r="P45">
-        <v>3.11</v>
+        <v>3.15</v>
       </c>
       <c r="Q45">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="R45">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="S45">
         <v>1.34</v>
@@ -7665,31 +7665,31 @@
         <v>3.4</v>
       </c>
       <c r="U45">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V45">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="W45">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X45">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y45">
         <v>1.18</v>
       </c>
       <c r="Z45">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="AA45">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="AB45">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AC45">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
       <c r="AD45">
         <v>1.5</v>
@@ -7701,7 +7701,7 @@
         <v>1.53</v>
       </c>
       <c r="AG45">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AK45">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="O47">
-        <v>3.26</v>
+        <v>3.1</v>
       </c>
       <c r="P47">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.58</v>
+        <v>2.4</v>
       </c>
       <c r="O48">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="P48">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="Q48">
         <v>3.32</v>
@@ -8166,19 +8166,19 @@
         <v>1.05</v>
       </c>
       <c r="Y48">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="Z48">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="AA48">
         <v>2.31</v>
       </c>
       <c r="AB48">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AC48">
-        <v>3.92</v>
+        <v>4.13</v>
       </c>
       <c r="AD48">
         <v>1.21</v>
@@ -8785,34 +8785,34 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="O52">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P52">
         <v>2.7</v>
       </c>
       <c r="Q52">
-        <v>2.84</v>
+        <v>3.14</v>
       </c>
       <c r="R52">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="S52">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="T52">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="U52">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="V52">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="W52">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X52">
         <v>1.04</v>
@@ -8821,7 +8821,7 @@
         <v>1.32</v>
       </c>
       <c r="Z52">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="AA52">
         <v>2.11</v>
@@ -8830,16 +8830,16 @@
         <v>1.69</v>
       </c>
       <c r="AC52">
-        <v>3.72</v>
+        <v>3.5</v>
       </c>
       <c r="AD52">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE52">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF52">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG52">
         <v>1.87</v>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AK52">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,16 +8948,16 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.72</v>
+        <v>2.24</v>
       </c>
       <c r="O53">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="P53">
-        <v>2.92</v>
+        <v>3.81</v>
       </c>
       <c r="Q53">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="R53">
         <v>2.02</v>
@@ -8993,16 +8993,16 @@
         <v>1.81</v>
       </c>
       <c r="AC53">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="AD53">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE53">
         <v>1.04</v>
       </c>
       <c r="AF53">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AG53">
         <v>1.89</v>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AK53">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>2.81</v>
       </c>
       <c r="Q54">
-        <v>3.1</v>
+        <v>2.55</v>
       </c>
       <c r="R54">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="S54">
         <v>1.35</v>
@@ -9144,7 +9144,7 @@
         <v>1.02</v>
       </c>
       <c r="Y54">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z54">
         <v>3.5</v>
@@ -9159,7 +9159,7 @@
         <v>3</v>
       </c>
       <c r="AD54">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AE54">
         <v>1.08</v>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AK54">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9772,7 +9772,7 @@
         <v>0</v>
       </c>
       <c r="Q58">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="R58">
         <v>1.99</v>
@@ -9781,10 +9781,10 @@
         <v>1.45</v>
       </c>
       <c r="T58">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="U58">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="V58">
         <v>1.31</v>
@@ -9799,16 +9799,16 @@
         <v>1.35</v>
       </c>
       <c r="Z58">
-        <v>2.96</v>
+        <v>2.74</v>
       </c>
       <c r="AA58">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="AB58">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AC58">
-        <v>4.13</v>
+        <v>4.16</v>
       </c>
       <c r="AD58">
         <v>1.21</v>
@@ -9833,7 +9833,7 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AK58">
         <v>1.4</v>
@@ -11067,22 +11067,22 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.55</v>
+        <v>2.39</v>
       </c>
       <c r="O66">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="P66">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="Q66">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="R66">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="S66">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="T66">
         <v>2.8</v>
@@ -11094,19 +11094,19 @@
         <v>1.33</v>
       </c>
       <c r="W66">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X66">
         <v>1.02</v>
       </c>
       <c r="Y66">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z66">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AA66">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AB66">
         <v>1.73</v>
@@ -11115,16 +11115,16 @@
         <v>3.34</v>
       </c>
       <c r="AD66">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE66">
         <v>1.05</v>
       </c>
       <c r="AF66">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG66">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,7 +11137,7 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AK66">
         <v>1.44</v>
@@ -11393,19 +11393,19 @@
         </is>
       </c>
       <c r="N68">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="O68">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="P68">
-        <v>2.27</v>
+        <v>2.41</v>
       </c>
       <c r="Q68">
-        <v>3.04</v>
+        <v>3.45</v>
       </c>
       <c r="R68">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="S68">
         <v>1.36</v>
@@ -11414,13 +11414,13 @@
         <v>3.05</v>
       </c>
       <c r="U68">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="V68">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="W68">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X68">
         <v>1</v>
@@ -11432,22 +11432,22 @@
         <v>3.95</v>
       </c>
       <c r="AA68">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AB68">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="AC68">
         <v>2.95</v>
       </c>
       <c r="AD68">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AE68">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF68">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AG68">
         <v>2.1</v>
@@ -11466,7 +11466,7 @@
         <v>1.3</v>
       </c>
       <c r="AK68">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11556,7 +11556,7 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="O69">
         <v>3.82</v>
@@ -11568,7 +11568,7 @@
         <v>1.83</v>
       </c>
       <c r="R69">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="S69">
         <v>1.33</v>
@@ -11577,10 +11577,10 @@
         <v>3.05</v>
       </c>
       <c r="U69">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="V69">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W69">
         <v>1.09</v>
@@ -11589,25 +11589,25 @@
         <v>1.01</v>
       </c>
       <c r="Y69">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z69">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AA69">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AB69">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="AC69">
         <v>2.65</v>
       </c>
       <c r="AD69">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AE69">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AF69">
         <v>1.7</v>
@@ -11626,7 +11626,7 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.04</v>
+        <v>1.24</v>
       </c>
       <c r="AK69">
         <v>2.64</v>
@@ -11740,10 +11740,10 @@
         <v>2.7</v>
       </c>
       <c r="U70">
-        <v>2.8</v>
+        <v>2.48</v>
       </c>
       <c r="V70">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W70">
         <v>1.06</v>
@@ -11761,13 +11761,13 @@
         <v>2.03</v>
       </c>
       <c r="AB70">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AC70">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="AD70">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="AE70">
         <v>1.05</v>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AK70">
-        <v>1.73</v>
+        <v>1.86</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.42</v>
+        <v>2.6</v>
       </c>
       <c r="O71">
         <v>3.44</v>
       </c>
       <c r="P71">
-        <v>2.92</v>
+        <v>2.62</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -11921,10 +11921,10 @@
         <v>0</v>
       </c>
       <c r="AA71">
-        <v>1.78</v>
+        <v>1.66</v>
       </c>
       <c r="AB71">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AC71">
         <v>0</v>
@@ -12208,10 +12208,10 @@
         </is>
       </c>
       <c r="N73">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="O73">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P73">
         <v>3.45</v>
@@ -12220,52 +12220,52 @@
         <v>2.45</v>
       </c>
       <c r="R73">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="S73">
         <v>1.24</v>
       </c>
       <c r="T73">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="U73">
         <v>2.1</v>
       </c>
       <c r="V73">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="W73">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X73">
         <v>1.02</v>
       </c>
       <c r="Y73">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z73">
-        <v>5</v>
+        <v>4.55</v>
       </c>
       <c r="AA73">
+        <v>1.5</v>
+      </c>
+      <c r="AB73">
+        <v>2.25</v>
+      </c>
+      <c r="AC73">
+        <v>2.35</v>
+      </c>
+      <c r="AD73">
+        <v>1.57</v>
+      </c>
+      <c r="AE73">
+        <v>1.19</v>
+      </c>
+      <c r="AF73">
         <v>1.48</v>
       </c>
-      <c r="AB73">
-        <v>2.34</v>
-      </c>
-      <c r="AC73">
-        <v>2.31</v>
-      </c>
-      <c r="AD73">
-        <v>1.59</v>
-      </c>
-      <c r="AE73">
-        <v>1.2</v>
-      </c>
-      <c r="AF73">
-        <v>1.46</v>
-      </c>
       <c r="AG73">
-        <v>2.49</v>
+        <v>2.63</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12371,34 +12371,34 @@
         </is>
       </c>
       <c r="N74">
-        <v>4.35</v>
+        <v>4.16</v>
       </c>
       <c r="O74">
-        <v>4</v>
+        <v>3.99</v>
       </c>
       <c r="P74">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="Q74">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="R74">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S74">
         <v>1.25</v>
       </c>
       <c r="T74">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="U74">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="V74">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="W74">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="X74">
         <v>1.03</v>
@@ -12410,7 +12410,7 @@
         <v>4.4</v>
       </c>
       <c r="AA74">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB74">
         <v>2.15</v>
@@ -12441,7 +12441,7 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.94</v>
+        <v>1.25</v>
       </c>
       <c r="AK74">
         <v>1.22</v>
@@ -12860,16 +12860,16 @@
         </is>
       </c>
       <c r="N77">
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="O77">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P77">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="Q77">
-        <v>5.15</v>
+        <v>5.27</v>
       </c>
       <c r="R77">
         <v>2.13</v>
@@ -12899,19 +12899,19 @@
         <v>3.13</v>
       </c>
       <c r="AA77">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="AB77">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AC77">
-        <v>3.6</v>
+        <v>3.86</v>
       </c>
       <c r="AD77">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE77">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AF77">
         <v>1.93</v>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AK77">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13023,16 +13023,16 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="O78">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="P78">
-        <v>4.42</v>
+        <v>4.68</v>
       </c>
       <c r="Q78">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="R78">
         <v>2.2</v>
@@ -13041,10 +13041,10 @@
         <v>1.36</v>
       </c>
       <c r="T78">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="U78">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="V78">
         <v>1.44</v>
@@ -13056,16 +13056,16 @@
         <v>1.05</v>
       </c>
       <c r="Y78">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z78">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AA78">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AB78">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AC78">
         <v>3.25</v>
@@ -13093,7 +13093,7 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AK78">
         <v>2.14</v>
@@ -13349,55 +13349,55 @@
         </is>
       </c>
       <c r="N80">
-        <v>6.02</v>
+        <v>8.25</v>
       </c>
       <c r="O80">
-        <v>4.49</v>
+        <v>5.75</v>
       </c>
       <c r="P80">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="Q80">
-        <v>6.28</v>
+        <v>7</v>
       </c>
       <c r="R80">
         <v>2.64</v>
       </c>
       <c r="S80">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T80">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="U80">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="V80">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="W80">
         <v>1.17</v>
       </c>
       <c r="X80">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y80">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z80">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AA80">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AB80">
-        <v>2.79</v>
+        <v>2.7</v>
       </c>
       <c r="AC80">
         <v>2</v>
       </c>
       <c r="AD80">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AE80">
         <v>1.27</v>
@@ -13406,7 +13406,7 @@
         <v>1.74</v>
       </c>
       <c r="AG80">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AK80">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13512,19 +13512,19 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.6</v>
+        <v>2.87</v>
       </c>
       <c r="O81">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P81">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="Q81">
         <v>3.1</v>
       </c>
       <c r="R81">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="S81">
         <v>1.2</v>
@@ -13533,10 +13533,10 @@
         <v>3.6</v>
       </c>
       <c r="U81">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="V81">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W81">
         <v>1.14</v>
@@ -13545,22 +13545,22 @@
         <v>1.02</v>
       </c>
       <c r="Y81">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="Z81">
-        <v>5.5</v>
+        <v>5.68</v>
       </c>
       <c r="AA81">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AB81">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="AC81">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AD81">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="AE81">
         <v>1.28</v>
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="O82">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P82">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="Q82">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="R82">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="S82">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="T82">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="U82">
-        <v>2.66</v>
+        <v>2.53</v>
       </c>
       <c r="V82">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="W82">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X82">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y82">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z82">
-        <v>3.3</v>
+        <v>3.68</v>
       </c>
       <c r="AA82">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AB82">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="AC82">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AD82">
         <v>1.36</v>
       </c>
       <c r="AE82">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AF82">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AG82">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AK82">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.31</v>
+        <v>2.23</v>
       </c>
       <c r="O83">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="P83">
-        <v>3.76</v>
+        <v>3.3</v>
       </c>
       <c r="Q83">
         <v>2.75</v>
@@ -13853,40 +13853,40 @@
         <v>1.95</v>
       </c>
       <c r="S83">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="T83">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="U83">
-        <v>3.22</v>
+        <v>3</v>
       </c>
       <c r="V83">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W83">
         <v>1.03</v>
       </c>
       <c r="X83">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Y83">
         <v>1.4</v>
       </c>
       <c r="Z83">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AA83">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AB83">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC83">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="AD83">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AE83">
         <v>1.06</v>
@@ -13895,7 +13895,7 @@
         <v>1.95</v>
       </c>
       <c r="AG83">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AK83">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14164,31 +14164,31 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="O85">
         <v>3.3</v>
       </c>
       <c r="P85">
+        <v>3.1</v>
+      </c>
+      <c r="Q85">
         <v>2.7</v>
       </c>
-      <c r="Q85">
-        <v>2.72</v>
-      </c>
       <c r="R85">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="S85">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T85">
-        <v>3.11</v>
+        <v>3.14</v>
       </c>
       <c r="U85">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="V85">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="W85">
         <v>1.07</v>
@@ -14197,31 +14197,31 @@
         <v>1.02</v>
       </c>
       <c r="Y85">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="Z85">
-        <v>3.7</v>
+        <v>3.84</v>
       </c>
       <c r="AA85">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB85">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="AC85">
         <v>2.74</v>
       </c>
       <c r="AD85">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE85">
         <v>1.09</v>
       </c>
       <c r="AF85">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG85">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK85">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14490,7 +14490,7 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="O87">
         <v>3.5</v>
@@ -14508,7 +14508,7 @@
         <v>1.38</v>
       </c>
       <c r="T87">
-        <v>2.68</v>
+        <v>3.2</v>
       </c>
       <c r="U87">
         <v>2.88</v>
@@ -14520,19 +14520,19 @@
         <v>1.07</v>
       </c>
       <c r="X87">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y87">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z87">
         <v>3.87</v>
       </c>
       <c r="AA87">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AB87">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AC87">
         <v>3.18</v>
@@ -14541,7 +14541,7 @@
         <v>1.38</v>
       </c>
       <c r="AE87">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF87">
         <v>1.75</v>
@@ -14563,7 +14563,7 @@
         <v>1.2</v>
       </c>
       <c r="AK87">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14816,10 +14816,10 @@
         </is>
       </c>
       <c r="N89">
-        <v>3.52</v>
+        <v>3.51</v>
       </c>
       <c r="O89">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="P89">
         <v>2.18</v>
@@ -14831,7 +14831,7 @@
         <v>2.22</v>
       </c>
       <c r="S89">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T89">
         <v>3.05</v>
@@ -14849,16 +14849,16 @@
         <v>1.05</v>
       </c>
       <c r="Y89">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="Z89">
-        <v>4.05</v>
+        <v>3.25</v>
       </c>
       <c r="AA89">
         <v>1.73</v>
       </c>
       <c r="AB89">
-        <v>2.06</v>
+        <v>1.78</v>
       </c>
       <c r="AC89">
         <v>2.65</v>
@@ -14870,7 +14870,7 @@
         <v>1.15</v>
       </c>
       <c r="AF89">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AG89">
         <v>2.22</v>
@@ -22003,10 +22003,10 @@
         <v>2.34</v>
       </c>
       <c r="S133">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T133">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U133">
         <v>2.55</v>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK133">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -24309,10 +24309,10 @@
         <v>0</v>
       </c>
       <c r="AA147">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB147">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AC147">
         <v>0</v>
@@ -34385,16 +34385,16 @@
         <v>2.8</v>
       </c>
       <c r="Q209">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R209">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S209">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T209">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U209">
         <v>0</v>
@@ -34409,16 +34409,16 @@
         <v>0</v>
       </c>
       <c r="Y209">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z209">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA209">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AB209">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC209">
         <v>0</v>
@@ -34430,10 +34430,10 @@
         <v>0</v>
       </c>
       <c r="AF209">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG209">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH209" t="inlineStr">
         <is>
@@ -34446,10 +34446,10 @@
         </is>
       </c>
       <c r="AJ209">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK209">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL209">
         <v>0</v>
@@ -36495,13 +36495,13 @@
         </is>
       </c>
       <c r="N222">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O222">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P222">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q222">
         <v>2.63</v>

--- a/jogos_2026-08-23.xlsx
+++ b/jogos_2026-08-23.xlsx
@@ -807,10 +807,10 @@
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="R3">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="S3">
         <v>1.31</v>
@@ -831,19 +831,19 @@
         <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z3">
-        <v>3.55</v>
+        <v>3.74</v>
       </c>
       <c r="AA3">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB3">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AC3">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AD3">
         <v>1.35</v>
@@ -855,7 +855,7 @@
         <v>1.59</v>
       </c>
       <c r="AG3">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -970,22 +970,22 @@
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>5.65</v>
+        <v>5.5</v>
       </c>
       <c r="R4">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="S4">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="T4">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="U4">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="V4">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W4">
         <v>1.1</v>
@@ -1000,25 +1000,25 @@
         <v>4.2</v>
       </c>
       <c r="AA4">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AB4">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="AC4">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="AD4">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE4">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF4">
         <v>1.69</v>
       </c>
       <c r="AG4">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>1.15</v>
       </c>
       <c r="AK4">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="N16">
-        <v>4.95</v>
+        <v>4.1</v>
       </c>
       <c r="O16">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="P16">
         <v>1.71</v>
@@ -2938,10 +2938,10 @@
         <v>2.48</v>
       </c>
       <c r="U16">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="V16">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W16">
         <v>1.03</v>
@@ -2950,31 +2950,31 @@
         <v>1.05</v>
       </c>
       <c r="Y16">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="Z16">
-        <v>2.7</v>
+        <v>2.86</v>
       </c>
       <c r="AA16">
         <v>2.3</v>
       </c>
       <c r="AB16">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AC16">
         <v>4.4</v>
       </c>
       <c r="AD16">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AE16">
         <v>1.04</v>
       </c>
       <c r="AF16">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AG16">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>1.23</v>
       </c>
       <c r="AK16">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,16 +3080,16 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.53</v>
+        <v>2.38</v>
       </c>
       <c r="O17">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="P17">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="Q17">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="R17">
         <v>1.97</v>
@@ -3098,19 +3098,19 @@
         <v>1.4</v>
       </c>
       <c r="T17">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="U17">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="V17">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W17">
         <v>1.02</v>
       </c>
       <c r="X17">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y17">
         <v>1.32</v>
@@ -3128,13 +3128,13 @@
         <v>3.85</v>
       </c>
       <c r="AD17">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE17">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF17">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AG17">
         <v>1.9</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AK17">
         <v>1.5</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.97</v>
+        <v>3.45</v>
       </c>
       <c r="O18">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P18">
-        <v>3.4</v>
+        <v>1.98</v>
       </c>
       <c r="Q18">
-        <v>2.5</v>
+        <v>4.08</v>
       </c>
       <c r="R18">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S18">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="T18">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="U18">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="V18">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W18">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X18">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y18">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="Z18">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="AA18">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="AB18">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC18">
-        <v>3.14</v>
+        <v>2.91</v>
       </c>
       <c r="AD18">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AE18">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF18">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AG18">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>1.23</v>
       </c>
       <c r="AK18">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>3.41</v>
+        <v>1.4</v>
       </c>
       <c r="O19">
-        <v>3.48</v>
+        <v>4.2</v>
       </c>
       <c r="P19">
-        <v>1.93</v>
+        <v>4.7</v>
       </c>
       <c r="Q19">
-        <v>4.08</v>
+        <v>1.91</v>
       </c>
       <c r="R19">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="S19">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="T19">
-        <v>3.2</v>
+        <v>3.38</v>
       </c>
       <c r="U19">
+        <v>2.37</v>
+      </c>
+      <c r="V19">
+        <v>1.55</v>
+      </c>
+      <c r="W19">
+        <v>1.1</v>
+      </c>
+      <c r="X19">
+        <v>1.03</v>
+      </c>
+      <c r="Y19">
+        <v>1.19</v>
+      </c>
+      <c r="Z19">
+        <v>4.52</v>
+      </c>
+      <c r="AA19">
+        <v>1.53</v>
+      </c>
+      <c r="AB19">
+        <v>2.23</v>
+      </c>
+      <c r="AC19">
         <v>2.5</v>
       </c>
-      <c r="V19">
-        <v>1.5</v>
-      </c>
-      <c r="W19">
-        <v>1.06</v>
-      </c>
-      <c r="X19">
-        <v>1</v>
-      </c>
-      <c r="Y19">
-        <v>1.24</v>
-      </c>
-      <c r="Z19">
-        <v>3.9</v>
-      </c>
-      <c r="AA19">
-        <v>1.78</v>
-      </c>
-      <c r="AB19">
-        <v>1.98</v>
-      </c>
-      <c r="AC19">
-        <v>2.91</v>
-      </c>
       <c r="AD19">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AE19">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF19">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG19">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.69</v>
+        <v>1.2</v>
       </c>
       <c r="AK19">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.46</v>
+        <v>1.94</v>
       </c>
       <c r="O20">
-        <v>4.55</v>
+        <v>3.3</v>
       </c>
       <c r="P20">
-        <v>5.3</v>
+        <v>3.3</v>
       </c>
       <c r="Q20">
-        <v>1.91</v>
+        <v>2.41</v>
       </c>
       <c r="R20">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="S20">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="T20">
-        <v>3.38</v>
+        <v>2.7</v>
       </c>
       <c r="U20">
-        <v>2.16</v>
+        <v>2.74</v>
       </c>
       <c r="V20">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
       <c r="W20">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X20">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y20">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="Z20">
-        <v>4.5</v>
+        <v>3.34</v>
       </c>
       <c r="AA20">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AB20">
-        <v>2.25</v>
+        <v>1.84</v>
       </c>
       <c r="AC20">
-        <v>2.38</v>
+        <v>2.85</v>
       </c>
       <c r="AD20">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="AE20">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AF20">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG20">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK20">
-        <v>2.41</v>
+        <v>1.7</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,19 +3732,19 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.49</v>
+        <v>2.33</v>
       </c>
       <c r="O21">
-        <v>3.25</v>
+        <v>3.13</v>
       </c>
       <c r="P21">
-        <v>2.49</v>
+        <v>2.33</v>
       </c>
       <c r="Q21">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="R21">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S21">
         <v>1.37</v>
@@ -3753,43 +3753,43 @@
         <v>2.9</v>
       </c>
       <c r="U21">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="V21">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="W21">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X21">
         <v>1.06</v>
       </c>
       <c r="Y21">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z21">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AA21">
         <v>1.94</v>
       </c>
       <c r="AB21">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AC21">
         <v>3.4</v>
       </c>
       <c r="AD21">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE21">
         <v>1.08</v>
       </c>
       <c r="AF21">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="AG21">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AK21">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,52 +3895,52 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="O22">
-        <v>3.63</v>
+        <v>3.3</v>
       </c>
       <c r="P22">
-        <v>4.76</v>
+        <v>4.65</v>
       </c>
       <c r="Q22">
         <v>2.25</v>
       </c>
       <c r="R22">
-        <v>2.19</v>
+        <v>2.04</v>
       </c>
       <c r="S22">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="T22">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="U22">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="V22">
         <v>1.34</v>
       </c>
       <c r="W22">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X22">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z22">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="AA22">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AB22">
         <v>1.69</v>
       </c>
       <c r="AC22">
-        <v>3.76</v>
+        <v>3.78</v>
       </c>
       <c r="AD22">
         <v>1.19</v>
@@ -3949,7 +3949,7 @@
         <v>1.02</v>
       </c>
       <c r="AF22">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="AG22">
         <v>1.8</v>
@@ -4085,7 +4085,7 @@
         <v>1.49</v>
       </c>
       <c r="W23">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X23">
         <v>1.04</v>
@@ -4097,7 +4097,7 @@
         <v>4.15</v>
       </c>
       <c r="AA23">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AB23">
         <v>2.14</v>
@@ -4221,16 +4221,16 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="O24">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="P24">
-        <v>3.56</v>
+        <v>3.5</v>
       </c>
       <c r="Q24">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R24">
         <v>2.3</v>
@@ -4239,31 +4239,31 @@
         <v>1.29</v>
       </c>
       <c r="T24">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="U24">
         <v>2.5</v>
       </c>
       <c r="V24">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W24">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X24">
         <v>1.04</v>
       </c>
       <c r="Y24">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z24">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="AA24">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AB24">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AC24">
         <v>2.69</v>
@@ -4272,13 +4272,13 @@
         <v>1.36</v>
       </c>
       <c r="AE24">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AF24">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG24">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK24">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -5036,16 +5036,16 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="O29">
-        <v>5.72</v>
+        <v>5.5</v>
       </c>
       <c r="P29">
-        <v>8.25</v>
+        <v>7.8</v>
       </c>
       <c r="Q29">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="R29">
         <v>2.75</v>
@@ -5054,7 +5054,7 @@
         <v>1.18</v>
       </c>
       <c r="T29">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="U29">
         <v>2.02</v>
@@ -5069,7 +5069,7 @@
         <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z29">
         <v>5.55</v>
@@ -5084,13 +5084,13 @@
         <v>2</v>
       </c>
       <c r="AD29">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AE29">
         <v>1.28</v>
       </c>
       <c r="AF29">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AG29">
         <v>2.1</v>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AK29">
-        <v>3.32</v>
+        <v>3.24</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.59</v>
+        <v>2.3</v>
       </c>
       <c r="O30">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="P30">
-        <v>2.72</v>
+        <v>2.95</v>
       </c>
       <c r="Q30">
-        <v>3.19</v>
+        <v>2.8</v>
       </c>
       <c r="R30">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="S30">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T30">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="U30">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="V30">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W30">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X30">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y30">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z30">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="AA30">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AB30">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AC30">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="AD30">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AE30">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF30">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AG30">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK30">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5534,7 +5534,7 @@
         <v>0</v>
       </c>
       <c r="Q32">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="R32">
         <v>2.88</v>
@@ -5546,7 +5546,7 @@
         <v>4.5</v>
       </c>
       <c r="U32">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="V32">
         <v>1.8</v>
@@ -5567,16 +5567,16 @@
         <v>1.29</v>
       </c>
       <c r="AB32">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="AC32">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AD32">
         <v>1.85</v>
       </c>
       <c r="AE32">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AF32">
         <v>1.66</v>
@@ -5688,31 +5688,31 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.56</v>
+        <v>2.45</v>
       </c>
       <c r="O33">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="P33">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="Q33">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="R33">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="S33">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T33">
         <v>3.17</v>
       </c>
       <c r="U33">
-        <v>2.44</v>
+        <v>2.55</v>
       </c>
       <c r="V33">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W33">
         <v>1.08</v>
@@ -5724,28 +5724,28 @@
         <v>1.22</v>
       </c>
       <c r="Z33">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AA33">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AB33">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="AC33">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="AD33">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE33">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AF33">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG33">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>1.45</v>
       </c>
       <c r="AK33">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,19 +5851,19 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.65</v>
+        <v>2.48</v>
       </c>
       <c r="O34">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="P34">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="Q34">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="R34">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S34">
         <v>1.29</v>
@@ -5872,7 +5872,7 @@
         <v>3.24</v>
       </c>
       <c r="U34">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="V34">
         <v>1.46</v>
@@ -5884,25 +5884,25 @@
         <v>1.05</v>
       </c>
       <c r="Y34">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z34">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="AA34">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AB34">
         <v>2.01</v>
       </c>
       <c r="AC34">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="AD34">
         <v>1.4</v>
       </c>
       <c r="AE34">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF34">
         <v>1.6</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AK34">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -7318,34 +7318,34 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.41</v>
+        <v>2.37</v>
       </c>
       <c r="O43">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="P43">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="Q43">
         <v>2.88</v>
       </c>
       <c r="R43">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S43">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T43">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="U43">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="V43">
         <v>1.4</v>
       </c>
       <c r="W43">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X43">
         <v>1.01</v>
@@ -7357,7 +7357,7 @@
         <v>3.73</v>
       </c>
       <c r="AA43">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AB43">
         <v>1.88</v>
@@ -7369,13 +7369,13 @@
         <v>1.3</v>
       </c>
       <c r="AE43">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF43">
         <v>1.67</v>
       </c>
       <c r="AG43">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,80 +7481,80 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.41</v>
+        <v>2.19</v>
       </c>
       <c r="O44">
+        <v>3.6</v>
+      </c>
+      <c r="P44">
+        <v>3.15</v>
+      </c>
+      <c r="Q44">
+        <v>2.73</v>
+      </c>
+      <c r="R44">
+        <v>2.24</v>
+      </c>
+      <c r="S44">
+        <v>1.34</v>
+      </c>
+      <c r="T44">
+        <v>3.4</v>
+      </c>
+      <c r="U44">
+        <v>2.38</v>
+      </c>
+      <c r="V44">
+        <v>1.52</v>
+      </c>
+      <c r="W44">
+        <v>1.11</v>
+      </c>
+      <c r="X44">
+        <v>1.04</v>
+      </c>
+      <c r="Y44">
+        <v>1.18</v>
+      </c>
+      <c r="Z44">
         <v>4.8</v>
       </c>
-      <c r="P44">
-        <v>5.7</v>
-      </c>
-      <c r="Q44">
-        <v>1.85</v>
-      </c>
-      <c r="R44">
-        <v>2.7</v>
-      </c>
-      <c r="S44">
+      <c r="AA44">
+        <v>1.69</v>
+      </c>
+      <c r="AB44">
+        <v>2.26</v>
+      </c>
+      <c r="AC44">
+        <v>2.51</v>
+      </c>
+      <c r="AD44">
+        <v>1.5</v>
+      </c>
+      <c r="AE44">
         <v>1.17</v>
       </c>
-      <c r="T44">
-        <v>4.5</v>
-      </c>
-      <c r="U44">
-        <v>1.99</v>
-      </c>
-      <c r="V44">
+      <c r="AF44">
+        <v>1.53</v>
+      </c>
+      <c r="AG44">
+        <v>2.36</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ44">
+        <v>1.33</v>
+      </c>
+      <c r="AK44">
         <v>1.7</v>
-      </c>
-      <c r="W44">
-        <v>1.19</v>
-      </c>
-      <c r="X44">
-        <v>1.02</v>
-      </c>
-      <c r="Y44">
-        <v>1.1</v>
-      </c>
-      <c r="Z44">
-        <v>5.75</v>
-      </c>
-      <c r="AA44">
-        <v>1.44</v>
-      </c>
-      <c r="AB44">
-        <v>2.72</v>
-      </c>
-      <c r="AC44">
-        <v>2.15</v>
-      </c>
-      <c r="AD44">
-        <v>1.7</v>
-      </c>
-      <c r="AE44">
-        <v>1.3</v>
-      </c>
-      <c r="AF44">
-        <v>1.5</v>
-      </c>
-      <c r="AG44">
-        <v>2.45</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ44">
-        <v>1.2</v>
-      </c>
-      <c r="AK44">
-        <v>2.74</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.19</v>
+        <v>1.41</v>
       </c>
       <c r="O45">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="P45">
-        <v>3.15</v>
+        <v>5.7</v>
       </c>
       <c r="Q45">
-        <v>2.73</v>
+        <v>1.85</v>
       </c>
       <c r="R45">
-        <v>2.24</v>
+        <v>2.7</v>
       </c>
       <c r="S45">
-        <v>1.34</v>
+        <v>1.17</v>
       </c>
       <c r="T45">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="U45">
-        <v>2.38</v>
+        <v>1.99</v>
       </c>
       <c r="V45">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="W45">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="X45">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y45">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="Z45">
-        <v>4.8</v>
+        <v>5.75</v>
       </c>
       <c r="AA45">
-        <v>1.69</v>
+        <v>1.44</v>
       </c>
       <c r="AB45">
-        <v>2.26</v>
+        <v>2.72</v>
       </c>
       <c r="AC45">
-        <v>2.51</v>
+        <v>2.15</v>
       </c>
       <c r="AD45">
+        <v>1.7</v>
+      </c>
+      <c r="AE45">
+        <v>1.3</v>
+      </c>
+      <c r="AF45">
         <v>1.5</v>
       </c>
-      <c r="AE45">
-        <v>1.17</v>
-      </c>
-      <c r="AF45">
-        <v>1.53</v>
-      </c>
       <c r="AG45">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AK45">
-        <v>1.7</v>
+        <v>2.74</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,16 +7807,16 @@
         </is>
       </c>
       <c r="N46">
-        <v>5.23</v>
+        <v>5</v>
       </c>
       <c r="O46">
-        <v>4.02</v>
+        <v>3.6</v>
       </c>
       <c r="P46">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="Q46">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="R46">
         <v>2.2</v>
@@ -7825,13 +7825,13 @@
         <v>1.4</v>
       </c>
       <c r="T46">
+        <v>2.88</v>
+      </c>
+      <c r="U46">
         <v>2.8</v>
       </c>
-      <c r="U46">
-        <v>2.96</v>
-      </c>
       <c r="V46">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="W46">
         <v>1.05</v>
@@ -7840,22 +7840,22 @@
         <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="Z46">
-        <v>3.53</v>
+        <v>3.55</v>
       </c>
       <c r="AA46">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB46">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AC46">
         <v>3.6</v>
       </c>
       <c r="AD46">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE46">
         <v>1.1</v>
@@ -7864,7 +7864,7 @@
         <v>1.91</v>
       </c>
       <c r="AG46">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.25</v>
+        <v>2.1</v>
       </c>
       <c r="AK46">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8459,28 +8459,28 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.72</v>
+        <v>2.35</v>
       </c>
       <c r="O50">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
       <c r="P50">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="Q50">
         <v>2.86</v>
       </c>
       <c r="R50">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="S50">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="T50">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="U50">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="V50">
         <v>1.54</v>
@@ -8492,47 +8492,47 @@
         <v>1.04</v>
       </c>
       <c r="Y50">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z50">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AA50">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="AB50">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="AC50">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="AD50">
         <v>1.48</v>
       </c>
       <c r="AE50">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AF50">
+        <v>1.48</v>
+      </c>
+      <c r="AG50">
+        <v>2.47</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ50">
+        <v>1.24</v>
+      </c>
+      <c r="AK50">
         <v>1.5</v>
-      </c>
-      <c r="AG50">
-        <v>2.5</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ50">
-        <v>1.25</v>
-      </c>
-      <c r="AK50">
-        <v>1.52</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -10252,25 +10252,25 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="O61">
         <v>4.2</v>
       </c>
       <c r="P61">
-        <v>4.81</v>
+        <v>4</v>
       </c>
       <c r="Q61">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="R61">
-        <v>2.63</v>
+        <v>2.44</v>
       </c>
       <c r="S61">
         <v>1.18</v>
       </c>
       <c r="T61">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="U61">
         <v>1.99</v>
@@ -10288,7 +10288,7 @@
         <v>1.06</v>
       </c>
       <c r="Z61">
-        <v>6.3</v>
+        <v>6.25</v>
       </c>
       <c r="AA61">
         <v>1.33</v>
@@ -10297,10 +10297,10 @@
         <v>2.83</v>
       </c>
       <c r="AC61">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AD61">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AE61">
         <v>1.3</v>
@@ -10309,7 +10309,7 @@
         <v>1.4</v>
       </c>
       <c r="AG61">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AK61">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="O75">
-        <v>4.55</v>
+        <v>4.75</v>
       </c>
       <c r="P75">
-        <v>5.96</v>
+        <v>6.25</v>
       </c>
       <c r="Q75">
         <v>1.82</v>
@@ -12555,7 +12555,7 @@
         <v>3.42</v>
       </c>
       <c r="U75">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="V75">
         <v>1.58</v>
@@ -12570,22 +12570,22 @@
         <v>1.17</v>
       </c>
       <c r="Z75">
-        <v>4.65</v>
+        <v>4.6</v>
       </c>
       <c r="AA75">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AB75">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AC75">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="AD75">
         <v>1.55</v>
       </c>
       <c r="AE75">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AF75">
         <v>1.7</v>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AK75">
-        <v>2.76</v>
+        <v>2.6</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12703,7 +12703,7 @@
         <v>3.46</v>
       </c>
       <c r="P76">
-        <v>3.44</v>
+        <v>3.2</v>
       </c>
       <c r="Q76">
         <v>2.5</v>
@@ -12715,7 +12715,7 @@
         <v>1.36</v>
       </c>
       <c r="T76">
-        <v>2.89</v>
+        <v>3.07</v>
       </c>
       <c r="U76">
         <v>2.76</v>
@@ -12733,28 +12733,28 @@
         <v>1.25</v>
       </c>
       <c r="Z76">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="AA76">
         <v>1.85</v>
       </c>
       <c r="AB76">
-        <v>1.92</v>
+        <v>1.82</v>
       </c>
       <c r="AC76">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AD76">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE76">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF76">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AG76">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK76">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -14327,31 +14327,31 @@
         </is>
       </c>
       <c r="N86">
-        <v>2.39</v>
+        <v>2.2</v>
       </c>
       <c r="O86">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="P86">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="Q86">
-        <v>2.82</v>
+        <v>2.65</v>
       </c>
       <c r="R86">
         <v>2.2</v>
       </c>
       <c r="S86">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="T86">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="U86">
         <v>2.32</v>
       </c>
       <c r="V86">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W86">
         <v>1.11</v>
@@ -14360,31 +14360,31 @@
         <v>1.04</v>
       </c>
       <c r="Y86">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z86">
         <v>4.4</v>
       </c>
       <c r="AA86">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AB86">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AC86">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AD86">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AE86">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF86">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AG86">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AK86">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -15305,13 +15305,13 @@
         </is>
       </c>
       <c r="N92">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O92">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P92">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q92">
         <v>4</v>
@@ -17424,13 +17424,13 @@
         </is>
       </c>
       <c r="N105">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O105">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P105">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q105">
         <v>1.88</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,80 +20358,80 @@
         </is>
       </c>
       <c r="N123">
-        <v>3.05</v>
+        <v>1.69</v>
       </c>
       <c r="O123">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P123">
-        <v>2.17</v>
+        <v>3.9</v>
       </c>
       <c r="Q123">
-        <v>3.83</v>
+        <v>2.15</v>
       </c>
       <c r="R123">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S123">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="T123">
-        <v>2.83</v>
+        <v>3.25</v>
       </c>
       <c r="U123">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="V123">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="W123">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X123">
         <v>1.04</v>
       </c>
       <c r="Y123">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="Z123">
-        <v>3.26</v>
+        <v>3.9</v>
       </c>
       <c r="AA123">
-        <v>2.02</v>
+        <v>1.68</v>
       </c>
       <c r="AB123">
-        <v>1.76</v>
+        <v>2.05</v>
       </c>
       <c r="AC123">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="AD123">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AE123">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="AF123">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AG123">
+        <v>2.06</v>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ123">
+        <v>1.2</v>
+      </c>
+      <c r="AK123">
         <v>1.95</v>
-      </c>
-      <c r="AH123" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI123" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ123">
-        <v>1.62</v>
-      </c>
-      <c r="AK123">
-        <v>1.3</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G124">
@@ -20521,64 +20521,64 @@
         </is>
       </c>
       <c r="N124">
-        <v>1.69</v>
+        <v>3.05</v>
       </c>
       <c r="O124">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P124">
-        <v>3.9</v>
+        <v>2.17</v>
       </c>
       <c r="Q124">
-        <v>2.15</v>
+        <v>3.83</v>
       </c>
       <c r="R124">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S124">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="T124">
-        <v>3.25</v>
+        <v>2.83</v>
       </c>
       <c r="U124">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="V124">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="W124">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X124">
         <v>1.04</v>
       </c>
       <c r="Y124">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="Z124">
-        <v>3.9</v>
+        <v>3.26</v>
       </c>
       <c r="AA124">
-        <v>1.68</v>
+        <v>2.02</v>
       </c>
       <c r="AB124">
-        <v>2.05</v>
+        <v>1.76</v>
       </c>
       <c r="AC124">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="AD124">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AE124">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="AF124">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AG124">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.2</v>
+        <v>1.62</v>
       </c>
       <c r="AK124">
-        <v>1.95</v>
+        <v>1.3</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -23292,13 +23292,13 @@
         </is>
       </c>
       <c r="N141">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O141">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P141">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q141">
         <v>2.1</v>
@@ -29975,13 +29975,13 @@
         </is>
       </c>
       <c r="N182">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="O182">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P182">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q182">
         <v>0</v>
@@ -30138,25 +30138,25 @@
         </is>
       </c>
       <c r="N183">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="O183">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="P183">
-        <v>3.37</v>
+        <v>3.2</v>
       </c>
       <c r="Q183">
-        <v>3.1</v>
+        <v>3.32</v>
       </c>
       <c r="R183">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="S183">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="T183">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="U183">
         <v>4</v>
@@ -30168,34 +30168,34 @@
         <v>1.03</v>
       </c>
       <c r="X183">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Y183">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Z183">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AA183">
-        <v>2.88</v>
+        <v>3.19</v>
       </c>
       <c r="AB183">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AC183">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="AD183">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AE183">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF183">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AG183">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AH183" t="inlineStr">
         <is>
@@ -30301,28 +30301,28 @@
         </is>
       </c>
       <c r="N184">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="O184">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="P184">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q184">
-        <v>3.06</v>
+        <v>2.91</v>
       </c>
       <c r="R184">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="S184">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="T184">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="U184">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="V184">
         <v>1.25</v>
@@ -30331,34 +30331,34 @@
         <v>1.01</v>
       </c>
       <c r="X184">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y184">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="Z184">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="AA184">
-        <v>2.49</v>
+        <v>2.44</v>
       </c>
       <c r="AB184">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AC184">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AD184">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AE184">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF184">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AG184">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AH184" t="inlineStr">
         <is>
@@ -30371,10 +30371,10 @@
         </is>
       </c>
       <c r="AJ184">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AK184">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AL184">
         <v>0</v>
@@ -34053,28 +34053,28 @@
         <v>2.25</v>
       </c>
       <c r="O207">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="P207">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="Q207">
-        <v>3.29</v>
+        <v>3.2</v>
       </c>
       <c r="R207">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="S207">
         <v>1.67</v>
       </c>
       <c r="T207">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="U207">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="V207">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="W207">
         <v>1.03</v>
@@ -34086,7 +34086,7 @@
         <v>1.7</v>
       </c>
       <c r="Z207">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AA207">
         <v>3.1</v>
@@ -34104,10 +34104,10 @@
         <v>1.03</v>
       </c>
       <c r="AF207">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AG207">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AH207" t="inlineStr">
         <is>
@@ -34123,7 +34123,7 @@
         <v>1.44</v>
       </c>
       <c r="AK207">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AL207">
         <v>0</v>

--- a/jogos_2026-08-23.xlsx
+++ b/jogos_2026-08-23.xlsx
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>3.45</v>
+        <v>1.94</v>
       </c>
       <c r="O18">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P18">
-        <v>1.98</v>
+        <v>3.3</v>
       </c>
       <c r="Q18">
-        <v>4.08</v>
+        <v>2.41</v>
       </c>
       <c r="R18">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="S18">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="T18">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="U18">
-        <v>2.53</v>
+        <v>2.74</v>
       </c>
       <c r="V18">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="W18">
         <v>1.06</v>
       </c>
       <c r="X18">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y18">
         <v>1.24</v>
       </c>
       <c r="Z18">
-        <v>3.9</v>
+        <v>3.34</v>
       </c>
       <c r="AA18">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AB18">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="AC18">
-        <v>2.91</v>
+        <v>2.85</v>
       </c>
       <c r="AD18">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AE18">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AF18">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AG18">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AK18">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,80 +3406,80 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.4</v>
+        <v>2.33</v>
       </c>
       <c r="O19">
-        <v>4.2</v>
+        <v>3.13</v>
       </c>
       <c r="P19">
-        <v>4.7</v>
+        <v>2.33</v>
       </c>
       <c r="Q19">
-        <v>1.91</v>
+        <v>3.3</v>
       </c>
       <c r="R19">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="S19">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="T19">
-        <v>3.38</v>
+        <v>2.9</v>
       </c>
       <c r="U19">
-        <v>2.37</v>
+        <v>2.7</v>
       </c>
       <c r="V19">
-        <v>1.55</v>
+        <v>1.39</v>
       </c>
       <c r="W19">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X19">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y19">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="Z19">
-        <v>4.52</v>
+        <v>3.4</v>
       </c>
       <c r="AA19">
-        <v>1.53</v>
+        <v>1.94</v>
       </c>
       <c r="AB19">
-        <v>2.23</v>
+        <v>1.75</v>
       </c>
       <c r="AC19">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="AD19">
+        <v>1.28</v>
+      </c>
+      <c r="AE19">
+        <v>1.08</v>
+      </c>
+      <c r="AF19">
+        <v>1.79</v>
+      </c>
+      <c r="AG19">
+        <v>2</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19">
         <v>1.44</v>
       </c>
-      <c r="AE19">
-        <v>1.18</v>
-      </c>
-      <c r="AF19">
-        <v>1.67</v>
-      </c>
-      <c r="AG19">
-        <v>2.05</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19">
-        <v>1.2</v>
-      </c>
       <c r="AK19">
-        <v>2.5</v>
+        <v>1.36</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,65 +3569,65 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.94</v>
+        <v>1.4</v>
       </c>
       <c r="O20">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="P20">
-        <v>3.3</v>
+        <v>4.7</v>
       </c>
       <c r="Q20">
-        <v>2.41</v>
+        <v>1.91</v>
       </c>
       <c r="R20">
+        <v>2.4</v>
+      </c>
+      <c r="S20">
+        <v>1.25</v>
+      </c>
+      <c r="T20">
+        <v>3.38</v>
+      </c>
+      <c r="U20">
+        <v>2.37</v>
+      </c>
+      <c r="V20">
+        <v>1.55</v>
+      </c>
+      <c r="W20">
+        <v>1.1</v>
+      </c>
+      <c r="X20">
+        <v>1.03</v>
+      </c>
+      <c r="Y20">
+        <v>1.19</v>
+      </c>
+      <c r="Z20">
+        <v>4.52</v>
+      </c>
+      <c r="AA20">
+        <v>1.53</v>
+      </c>
+      <c r="AB20">
+        <v>2.23</v>
+      </c>
+      <c r="AC20">
+        <v>2.5</v>
+      </c>
+      <c r="AD20">
+        <v>1.44</v>
+      </c>
+      <c r="AE20">
+        <v>1.18</v>
+      </c>
+      <c r="AF20">
+        <v>1.67</v>
+      </c>
+      <c r="AG20">
         <v>2.05</v>
       </c>
-      <c r="S20">
-        <v>1.36</v>
-      </c>
-      <c r="T20">
-        <v>2.7</v>
-      </c>
-      <c r="U20">
-        <v>2.74</v>
-      </c>
-      <c r="V20">
-        <v>1.37</v>
-      </c>
-      <c r="W20">
-        <v>1.06</v>
-      </c>
-      <c r="X20">
-        <v>1.05</v>
-      </c>
-      <c r="Y20">
-        <v>1.24</v>
-      </c>
-      <c r="Z20">
-        <v>3.34</v>
-      </c>
-      <c r="AA20">
-        <v>1.75</v>
-      </c>
-      <c r="AB20">
-        <v>1.84</v>
-      </c>
-      <c r="AC20">
-        <v>2.85</v>
-      </c>
-      <c r="AD20">
-        <v>1.33</v>
-      </c>
-      <c r="AE20">
-        <v>1.06</v>
-      </c>
-      <c r="AF20">
-        <v>1.7</v>
-      </c>
-      <c r="AG20">
-        <v>2</v>
-      </c>
       <c r="AH20" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AK20">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,65 +3732,65 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.33</v>
+        <v>3.45</v>
       </c>
       <c r="O21">
-        <v>3.13</v>
+        <v>3.45</v>
       </c>
       <c r="P21">
-        <v>2.33</v>
+        <v>1.98</v>
       </c>
       <c r="Q21">
-        <v>3.3</v>
+        <v>4.08</v>
       </c>
       <c r="R21">
+        <v>2.25</v>
+      </c>
+      <c r="S21">
+        <v>1.32</v>
+      </c>
+      <c r="T21">
+        <v>3.2</v>
+      </c>
+      <c r="U21">
+        <v>2.53</v>
+      </c>
+      <c r="V21">
+        <v>1.43</v>
+      </c>
+      <c r="W21">
+        <v>1.06</v>
+      </c>
+      <c r="X21">
+        <v>1</v>
+      </c>
+      <c r="Y21">
+        <v>1.24</v>
+      </c>
+      <c r="Z21">
+        <v>3.9</v>
+      </c>
+      <c r="AA21">
+        <v>1.78</v>
+      </c>
+      <c r="AB21">
+        <v>1.95</v>
+      </c>
+      <c r="AC21">
+        <v>2.91</v>
+      </c>
+      <c r="AD21">
+        <v>1.39</v>
+      </c>
+      <c r="AE21">
+        <v>1.13</v>
+      </c>
+      <c r="AF21">
+        <v>1.62</v>
+      </c>
+      <c r="AG21">
         <v>2.15</v>
       </c>
-      <c r="S21">
-        <v>1.37</v>
-      </c>
-      <c r="T21">
-        <v>2.9</v>
-      </c>
-      <c r="U21">
-        <v>2.7</v>
-      </c>
-      <c r="V21">
-        <v>1.39</v>
-      </c>
-      <c r="W21">
-        <v>1.03</v>
-      </c>
-      <c r="X21">
-        <v>1.06</v>
-      </c>
-      <c r="Y21">
-        <v>1.26</v>
-      </c>
-      <c r="Z21">
-        <v>3.4</v>
-      </c>
-      <c r="AA21">
-        <v>1.94</v>
-      </c>
-      <c r="AB21">
-        <v>1.75</v>
-      </c>
-      <c r="AC21">
-        <v>3.4</v>
-      </c>
-      <c r="AD21">
-        <v>1.28</v>
-      </c>
-      <c r="AE21">
-        <v>1.08</v>
-      </c>
-      <c r="AF21">
-        <v>1.79</v>
-      </c>
-      <c r="AG21">
-        <v>2</v>
-      </c>
       <c r="AH21" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.44</v>
+        <v>1.23</v>
       </c>
       <c r="AK21">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -14499,16 +14499,16 @@
         <v>4.15</v>
       </c>
       <c r="Q87">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="R87">
         <v>2.15</v>
       </c>
       <c r="S87">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T87">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="U87">
         <v>2.88</v>
@@ -14520,19 +14520,19 @@
         <v>1.07</v>
       </c>
       <c r="X87">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y87">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Z87">
-        <v>3.87</v>
+        <v>3.56</v>
       </c>
       <c r="AA87">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AB87">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AC87">
         <v>3.18</v>
@@ -14541,7 +14541,7 @@
         <v>1.38</v>
       </c>
       <c r="AE87">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AF87">
         <v>1.75</v>
@@ -14563,7 +14563,7 @@
         <v>1.2</v>
       </c>
       <c r="AK87">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G119">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G120">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G121">
@@ -27859,22 +27859,22 @@
         <v>2.14</v>
       </c>
       <c r="O169">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="P169">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Q169">
         <v>2.62</v>
       </c>
       <c r="R169">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="S169">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="T169">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="U169">
         <v>3.94</v>
@@ -27883,7 +27883,7 @@
         <v>1.23</v>
       </c>
       <c r="W169">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X169">
         <v>1.13</v>
@@ -27895,25 +27895,25 @@
         <v>2.36</v>
       </c>
       <c r="AA169">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AB169">
         <v>1.44</v>
       </c>
       <c r="AC169">
-        <v>5.35</v>
+        <v>5.5</v>
       </c>
       <c r="AD169">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AE169">
         <v>1.04</v>
       </c>
       <c r="AF169">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AG169">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AH169" t="inlineStr">
         <is>
@@ -27929,7 +27929,7 @@
         <v>1.4</v>
       </c>
       <c r="AK169">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="AL169">
         <v>0</v>
@@ -34702,13 +34702,13 @@
         </is>
       </c>
       <c r="N211">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O211">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P211">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q211">
         <v>0</v>
@@ -34874,7 +34874,7 @@
         <v>0</v>
       </c>
       <c r="Q212">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="R212">
         <v>1.97</v>
@@ -34883,13 +34883,13 @@
         <v>1.45</v>
       </c>
       <c r="T212">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="U212">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="V212">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W212">
         <v>1.01</v>
@@ -34904,25 +34904,25 @@
         <v>2.85</v>
       </c>
       <c r="AA212">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AB212">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AC212">
         <v>3.95</v>
       </c>
       <c r="AD212">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE212">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF212">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AG212">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AH212" t="inlineStr">
         <is>
@@ -34935,10 +34935,10 @@
         </is>
       </c>
       <c r="AJ212">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AK212">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AL212">
         <v>0</v>
@@ -36495,31 +36495,31 @@
         </is>
       </c>
       <c r="N222">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O222">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="P222">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="Q222">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="R222">
         <v>2.16</v>
       </c>
       <c r="S222">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="T222">
-        <v>2.73</v>
+        <v>2.32</v>
       </c>
       <c r="U222">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="V222">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="W222">
         <v>1.07</v>
@@ -36528,31 +36528,31 @@
         <v>1.07</v>
       </c>
       <c r="Y222">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z222">
         <v>3.1</v>
       </c>
       <c r="AA222">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="AB222">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AC222">
         <v>3.42</v>
       </c>
       <c r="AD222">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AE222">
         <v>1.09</v>
       </c>
       <c r="AF222">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AG222">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AH222" t="inlineStr">
         <is>
@@ -36565,7 +36565,7 @@
         </is>
       </c>
       <c r="AJ222">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK222">
         <v>1.73</v>
@@ -37482,16 +37482,16 @@
         <v>0</v>
       </c>
       <c r="Q228">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="R228">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="S228">
         <v>1.4</v>
       </c>
       <c r="T228">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="U228">
         <v>3.2</v>
@@ -37503,7 +37503,7 @@
         <v>1.05</v>
       </c>
       <c r="X228">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y228">
         <v>1.4</v>
@@ -37518,7 +37518,7 @@
         <v>1.6</v>
       </c>
       <c r="AC228">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="AD228">
         <v>1.19</v>
@@ -37543,10 +37543,10 @@
         </is>
       </c>
       <c r="AJ228">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AK228">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AL228">
         <v>0</v>

--- a/jogos_2026-08-23.xlsx
+++ b/jogos_2026-08-23.xlsx
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.41</v>
+        <v>2.29</v>
       </c>
       <c r="O44">
-        <v>4.8</v>
+        <v>3.45</v>
       </c>
       <c r="P44">
-        <v>5.7</v>
+        <v>3.15</v>
       </c>
       <c r="Q44">
-        <v>1.85</v>
+        <v>2.72</v>
       </c>
       <c r="R44">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="S44">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="T44">
+        <v>3.4</v>
+      </c>
+      <c r="U44">
+        <v>2.33</v>
+      </c>
+      <c r="V44">
+        <v>1.54</v>
+      </c>
+      <c r="W44">
+        <v>1.11</v>
+      </c>
+      <c r="X44">
+        <v>1.04</v>
+      </c>
+      <c r="Y44">
+        <v>1.2</v>
+      </c>
+      <c r="Z44">
         <v>4.33</v>
       </c>
-      <c r="U44">
-        <v>2.1</v>
-      </c>
-      <c r="V44">
-        <v>1.77</v>
-      </c>
-      <c r="W44">
-        <v>1.18</v>
-      </c>
-      <c r="X44">
-        <v>1.02</v>
-      </c>
-      <c r="Y44">
-        <v>1.1</v>
-      </c>
-      <c r="Z44">
-        <v>5.75</v>
-      </c>
       <c r="AA44">
-        <v>1.44</v>
+        <v>1.69</v>
       </c>
       <c r="AB44">
-        <v>2.59</v>
+        <v>2.3</v>
       </c>
       <c r="AC44">
-        <v>2.15</v>
+        <v>2.66</v>
       </c>
       <c r="AD44">
-        <v>1.7</v>
+        <v>1.51</v>
       </c>
       <c r="AE44">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AF44">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG44">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AK44">
-        <v>2.74</v>
+        <v>1.71</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,80 +7644,80 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.29</v>
+        <v>1.41</v>
       </c>
       <c r="O45">
-        <v>3.45</v>
+        <v>4.8</v>
       </c>
       <c r="P45">
-        <v>3.15</v>
+        <v>5.7</v>
       </c>
       <c r="Q45">
-        <v>2.72</v>
+        <v>1.85</v>
       </c>
       <c r="R45">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="S45">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="T45">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="U45">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="V45">
-        <v>1.54</v>
+        <v>1.77</v>
       </c>
       <c r="W45">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="X45">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y45">
+        <v>1.1</v>
+      </c>
+      <c r="Z45">
+        <v>5.75</v>
+      </c>
+      <c r="AA45">
+        <v>1.44</v>
+      </c>
+      <c r="AB45">
+        <v>2.59</v>
+      </c>
+      <c r="AC45">
+        <v>2.15</v>
+      </c>
+      <c r="AD45">
+        <v>1.7</v>
+      </c>
+      <c r="AE45">
+        <v>1.3</v>
+      </c>
+      <c r="AF45">
+        <v>1.5</v>
+      </c>
+      <c r="AG45">
+        <v>2.45</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ45">
         <v>1.2</v>
       </c>
-      <c r="Z45">
-        <v>4.33</v>
-      </c>
-      <c r="AA45">
-        <v>1.69</v>
-      </c>
-      <c r="AB45">
-        <v>2.3</v>
-      </c>
-      <c r="AC45">
-        <v>2.66</v>
-      </c>
-      <c r="AD45">
-        <v>1.51</v>
-      </c>
-      <c r="AE45">
-        <v>1.17</v>
-      </c>
-      <c r="AF45">
-        <v>1.53</v>
-      </c>
-      <c r="AG45">
-        <v>2.36</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ45">
-        <v>1.31</v>
-      </c>
       <c r="AK45">
-        <v>1.71</v>
+        <v>2.74</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
+        <v>2.9</v>
+      </c>
+      <c r="O122">
+        <v>3.32</v>
+      </c>
+      <c r="P122">
+        <v>2.2</v>
+      </c>
+      <c r="Q122">
+        <v>3.4</v>
+      </c>
+      <c r="R122">
+        <v>2.15</v>
+      </c>
+      <c r="S122">
+        <v>1.4</v>
+      </c>
+      <c r="T122">
+        <v>2.75</v>
+      </c>
+      <c r="U122">
+        <v>3.03</v>
+      </c>
+      <c r="V122">
+        <v>1.36</v>
+      </c>
+      <c r="W122">
+        <v>1.06</v>
+      </c>
+      <c r="X122">
+        <v>1</v>
+      </c>
+      <c r="Y122">
+        <v>1.3</v>
+      </c>
+      <c r="Z122">
+        <v>2.9</v>
+      </c>
+      <c r="AA122">
+        <v>2</v>
+      </c>
+      <c r="AB122">
         <v>1.7</v>
       </c>
-      <c r="O122">
-        <v>3.6</v>
-      </c>
-      <c r="P122">
-        <v>3.78</v>
-      </c>
-      <c r="Q122">
-        <v>2.16</v>
-      </c>
-      <c r="R122">
-        <v>2.25</v>
-      </c>
-      <c r="S122">
+      <c r="AC122">
+        <v>3.25</v>
+      </c>
+      <c r="AD122">
         <v>1.3</v>
       </c>
-      <c r="T122">
-        <v>3.25</v>
-      </c>
-      <c r="U122">
-        <v>2.5</v>
-      </c>
-      <c r="V122">
-        <v>1.5</v>
-      </c>
-      <c r="W122">
-        <v>1.12</v>
-      </c>
-      <c r="X122">
-        <v>1.04</v>
-      </c>
-      <c r="Y122">
-        <v>1.21</v>
-      </c>
-      <c r="Z122">
-        <v>3.85</v>
-      </c>
-      <c r="AA122">
-        <v>1.7</v>
-      </c>
-      <c r="AB122">
-        <v>2.1</v>
-      </c>
-      <c r="AC122">
-        <v>2.7</v>
-      </c>
-      <c r="AD122">
-        <v>1.42</v>
-      </c>
       <c r="AE122">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF122">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AG122">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AK122">
-        <v>1.98</v>
+        <v>1.36</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,64 +20358,64 @@
         </is>
       </c>
       <c r="N123">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="O123">
-        <v>3.32</v>
+        <v>3.6</v>
       </c>
       <c r="P123">
-        <v>2.2</v>
+        <v>3.78</v>
       </c>
       <c r="Q123">
-        <v>3.4</v>
+        <v>2.16</v>
       </c>
       <c r="R123">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S123">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="T123">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="U123">
-        <v>3.03</v>
+        <v>2.5</v>
       </c>
       <c r="V123">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="W123">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X123">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y123">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="Z123">
-        <v>2.9</v>
+        <v>3.85</v>
       </c>
       <c r="AA123">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AB123">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AC123">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="AD123">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AE123">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AF123">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AG123">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AK123">
-        <v>1.36</v>
+        <v>1.98</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G183">
@@ -30138,64 +30138,64 @@
         </is>
       </c>
       <c r="N183">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="O183">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="P183">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="Q183">
         <v>3.3</v>
       </c>
       <c r="R183">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="S183">
         <v>1.68</v>
       </c>
       <c r="T183">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="U183">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="V183">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="W183">
         <v>1.03</v>
       </c>
       <c r="X183">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Y183">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="Z183">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AA183">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AB183">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AC183">
-        <v>6.1</v>
+        <v>5.6</v>
       </c>
       <c r="AD183">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AE183">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF183">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AG183">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AH183" t="inlineStr">
         <is>
@@ -30208,10 +30208,10 @@
         </is>
       </c>
       <c r="AJ183">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AK183">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AL183">
         <v>0</v>
@@ -30269,12 +30269,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G184">
@@ -30301,64 +30301,64 @@
         </is>
       </c>
       <c r="N184">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="O184">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="P184">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="Q184">
         <v>3.3</v>
       </c>
       <c r="R184">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="S184">
         <v>1.68</v>
       </c>
       <c r="T184">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="U184">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="V184">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="W184">
         <v>1.03</v>
       </c>
       <c r="X184">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Y184">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="Z184">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AA184">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AB184">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AC184">
-        <v>5.6</v>
+        <v>6.1</v>
       </c>
       <c r="AD184">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AE184">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF184">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AG184">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AH184" t="inlineStr">
         <is>
@@ -30371,10 +30371,10 @@
         </is>
       </c>
       <c r="AJ184">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AK184">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AL184">
         <v>0</v>

--- a/jogos_2026-08-23.xlsx
+++ b/jogos_2026-08-23.xlsx
@@ -8136,7 +8136,7 @@
         <v>2.4</v>
       </c>
       <c r="O48">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="P48">
         <v>2.58</v>
@@ -8166,7 +8166,7 @@
         <v>1.05</v>
       </c>
       <c r="Y48">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="Z48">
         <v>2.88</v>
@@ -9772,10 +9772,10 @@
         <v>0</v>
       </c>
       <c r="Q58">
-        <v>3.58</v>
+        <v>3.64</v>
       </c>
       <c r="R58">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S58">
         <v>1.44</v>
@@ -9796,19 +9796,19 @@
         <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="Z58">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="AA58">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AB58">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AC58">
-        <v>3.98</v>
+        <v>3.92</v>
       </c>
       <c r="AD58">
         <v>1.21</v>
@@ -9817,10 +9817,10 @@
         <v>1.02</v>
       </c>
       <c r="AF58">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AG58">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AK58">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -22151,13 +22151,13 @@
         </is>
       </c>
       <c r="N134">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O134">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="P134">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q134">
         <v>0</v>
@@ -27204,13 +27204,13 @@
         </is>
       </c>
       <c r="N165">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O165">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="P165">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="Q165">
         <v>0</v>

--- a/jogos_2026-08-23.xlsx
+++ b/jogos_2026-08-23.xlsx
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q3">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="R3">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="S3">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="T3">
-        <v>2.97</v>
+        <v>2.71</v>
       </c>
       <c r="U3">
-        <v>2.6</v>
+        <v>2.79</v>
       </c>
       <c r="V3">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W3">
+        <v>1.08</v>
+      </c>
+      <c r="X3">
+        <v>1.02</v>
+      </c>
+      <c r="Y3">
+        <v>1.25</v>
+      </c>
+      <c r="Z3">
+        <v>3.3</v>
+      </c>
+      <c r="AA3">
+        <v>1.82</v>
+      </c>
+      <c r="AB3">
+        <v>1.81</v>
+      </c>
+      <c r="AC3">
+        <v>3</v>
+      </c>
+      <c r="AD3">
+        <v>1.26</v>
+      </c>
+      <c r="AE3">
         <v>1.05</v>
       </c>
-      <c r="X3">
-        <v>1.01</v>
-      </c>
-      <c r="Y3">
-        <v>1.22</v>
-      </c>
-      <c r="Z3">
-        <v>3.55</v>
-      </c>
-      <c r="AA3">
-        <v>1.72</v>
-      </c>
-      <c r="AB3">
-        <v>1.92</v>
-      </c>
-      <c r="AC3">
-        <v>2.92</v>
-      </c>
-      <c r="AD3">
-        <v>1.31</v>
-      </c>
-      <c r="AE3">
-        <v>1.08</v>
-      </c>
       <c r="AF3">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="AG3">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AK3">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,43 +961,43 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q4">
-        <v>4.9</v>
+        <v>5.05</v>
       </c>
       <c r="R4">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="S4">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T4">
-        <v>3.14</v>
+        <v>3.04</v>
       </c>
       <c r="U4">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="V4">
         <v>1.5</v>
       </c>
       <c r="W4">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X4">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y4">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="Z4">
-        <v>4.15</v>
+        <v>3.82</v>
       </c>
       <c r="AA4">
         <v>1.58</v>
@@ -1006,19 +1006,19 @@
         <v>2.25</v>
       </c>
       <c r="AC4">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="AD4">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AE4">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF4">
         <v>1.71</v>
       </c>
       <c r="AG4">
-        <v>2.04</v>
+        <v>1.92</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK4">
         <v>1.1</v>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.27</v>
+        <v>2.03</v>
       </c>
       <c r="O5">
-        <v>3.42</v>
+        <v>3.48</v>
       </c>
       <c r="P5">
-        <v>2.71</v>
+        <v>2.95</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1287,31 +1287,31 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q6">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="R6">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="S6">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T6">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="U6">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V6">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W6">
         <v>1.08</v>
@@ -1323,44 +1323,44 @@
         <v>1.18</v>
       </c>
       <c r="Z6">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="AA6">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB6">
+        <v>2.15</v>
+      </c>
+      <c r="AC6">
+        <v>2.49</v>
+      </c>
+      <c r="AD6">
+        <v>1.42</v>
+      </c>
+      <c r="AE6">
+        <v>1.13</v>
+      </c>
+      <c r="AF6">
+        <v>1.62</v>
+      </c>
+      <c r="AG6">
+        <v>2.15</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6">
+        <v>1.25</v>
+      </c>
+      <c r="AK6">
         <v>2.25</v>
-      </c>
-      <c r="AC6">
-        <v>2.43</v>
-      </c>
-      <c r="AD6">
-        <v>1.44</v>
-      </c>
-      <c r="AE6">
-        <v>1.18</v>
-      </c>
-      <c r="AF6">
-        <v>1.6</v>
-      </c>
-      <c r="AG6">
-        <v>2.2</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6">
-        <v>1.22</v>
-      </c>
-      <c r="AK6">
-        <v>2.1</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1453,10 +1453,10 @@
         <v>1.55</v>
       </c>
       <c r="O7">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="P7">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="Q7">
         <v>2.05</v>
@@ -1495,7 +1495,7 @@
         <v>2.27</v>
       </c>
       <c r="AC7">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="AD7">
         <v>1.45</v>
@@ -1504,7 +1504,7 @@
         <v>1.18</v>
       </c>
       <c r="AF7">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AG7">
         <v>2.1</v>
@@ -1791,10 +1791,10 @@
         <v>2.15</v>
       </c>
       <c r="S9">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T9">
-        <v>2.65</v>
+        <v>2.93</v>
       </c>
       <c r="U9">
         <v>2.81</v>
@@ -1821,19 +1821,19 @@
         <v>1.75</v>
       </c>
       <c r="AC9">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AD9">
         <v>1.29</v>
       </c>
       <c r="AE9">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF9">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AG9">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -2265,19 +2265,19 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.58</v>
+        <v>2.9</v>
       </c>
       <c r="O12">
-        <v>3.35</v>
+        <v>3.36</v>
       </c>
       <c r="P12">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="Q12">
         <v>3.06</v>
       </c>
       <c r="R12">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="S12">
         <v>1.36</v>
@@ -2304,16 +2304,16 @@
         <v>4.05</v>
       </c>
       <c r="AA12">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="AB12">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="AC12">
         <v>2.8</v>
       </c>
       <c r="AD12">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AE12">
         <v>1.14</v>
@@ -2322,7 +2322,7 @@
         <v>1.6</v>
       </c>
       <c r="AG12">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>1.34</v>
       </c>
       <c r="AK12">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,28 +2428,28 @@
         </is>
       </c>
       <c r="N13">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O13">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P13">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="Q13">
-        <v>4.06</v>
+        <v>4.2</v>
       </c>
       <c r="R13">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="S13">
         <v>1.22</v>
       </c>
       <c r="T13">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U13">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="V13">
         <v>1.67</v>
@@ -2467,7 +2467,7 @@
         <v>5.5</v>
       </c>
       <c r="AA13">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AB13">
         <v>2.65</v>
@@ -2479,7 +2479,7 @@
         <v>1.67</v>
       </c>
       <c r="AE13">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF13">
         <v>1.44</v>
@@ -2501,7 +2501,7 @@
         <v>1.25</v>
       </c>
       <c r="AK13">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2760,7 +2760,7 @@
         <v>3.9</v>
       </c>
       <c r="P15">
-        <v>4.05</v>
+        <v>3.85</v>
       </c>
       <c r="Q15">
         <v>2.24</v>
@@ -2775,10 +2775,10 @@
         <v>3.6</v>
       </c>
       <c r="U15">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="V15">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W15">
         <v>1.17</v>
@@ -2799,10 +2799,10 @@
         <v>2.38</v>
       </c>
       <c r="AC15">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AD15">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AE15">
         <v>1.21</v>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK15">
         <v>2</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>4.1</v>
+        <v>4.55</v>
       </c>
       <c r="O16">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P16">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="Q16">
         <v>4.8</v>
@@ -2935,13 +2935,13 @@
         <v>1.46</v>
       </c>
       <c r="T16">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="U16">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="V16">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W16">
         <v>1.03</v>
@@ -2953,16 +2953,16 @@
         <v>1.36</v>
       </c>
       <c r="Z16">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="AA16">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="AB16">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AC16">
-        <v>4.4</v>
+        <v>4.32</v>
       </c>
       <c r="AD16">
         <v>1.19</v>
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="O17">
         <v>3.1</v>
@@ -3089,7 +3089,7 @@
         <v>2.62</v>
       </c>
       <c r="Q17">
-        <v>3.14</v>
+        <v>3.16</v>
       </c>
       <c r="R17">
         <v>1.97</v>
@@ -3131,7 +3131,7 @@
         <v>1.2</v>
       </c>
       <c r="AE17">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF17">
         <v>1.9</v>
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="O18">
         <v>3.13</v>
@@ -3252,13 +3252,13 @@
         <v>2.33</v>
       </c>
       <c r="Q18">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="R18">
         <v>2.15</v>
       </c>
       <c r="S18">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T18">
         <v>2.9</v>
@@ -3267,7 +3267,7 @@
         <v>2.7</v>
       </c>
       <c r="V18">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="W18">
         <v>1.03</v>
@@ -3279,13 +3279,13 @@
         <v>1.26</v>
       </c>
       <c r="Z18">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AA18">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AB18">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AC18">
         <v>3.45</v>
@@ -3412,13 +3412,13 @@
         <v>4.2</v>
       </c>
       <c r="P19">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="Q19">
         <v>2</v>
       </c>
       <c r="R19">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S19">
         <v>1.25</v>
@@ -3442,16 +3442,16 @@
         <v>1.18</v>
       </c>
       <c r="Z19">
-        <v>4.52</v>
+        <v>4.5</v>
       </c>
       <c r="AA19">
         <v>1.53</v>
       </c>
       <c r="AB19">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AC19">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AD19">
         <v>1.44</v>
@@ -3460,7 +3460,7 @@
         <v>1.19</v>
       </c>
       <c r="AF19">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG19">
         <v>2.05</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="O20">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P20">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="Q20">
         <v>4.08</v>
@@ -3584,22 +3584,22 @@
         <v>2.15</v>
       </c>
       <c r="S20">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T20">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="U20">
         <v>2.63</v>
       </c>
       <c r="V20">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W20">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X20">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y20">
         <v>1.24</v>
@@ -3617,7 +3617,7 @@
         <v>2.91</v>
       </c>
       <c r="AD20">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE20">
         <v>1.13</v>
@@ -3732,7 +3732,7 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="O21">
         <v>3.3</v>
@@ -3750,13 +3750,13 @@
         <v>1.36</v>
       </c>
       <c r="T21">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="U21">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="V21">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="W21">
         <v>1.06</v>
@@ -3765,10 +3765,10 @@
         <v>1.05</v>
       </c>
       <c r="Y21">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z21">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA21">
         <v>1.93</v>
@@ -3777,7 +3777,7 @@
         <v>1.85</v>
       </c>
       <c r="AC21">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="AD21">
         <v>1.33</v>
@@ -3789,7 +3789,7 @@
         <v>1.7</v>
       </c>
       <c r="AG21">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="O22">
-        <v>3.65</v>
+        <v>3.58</v>
       </c>
       <c r="P22">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Q22">
         <v>2.32</v>
@@ -3916,13 +3916,13 @@
         <v>2.75</v>
       </c>
       <c r="U22">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="V22">
         <v>1.35</v>
       </c>
       <c r="W22">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X22">
         <v>1.07</v>
@@ -3931,13 +3931,13 @@
         <v>1.38</v>
       </c>
       <c r="Z22">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="AA22">
-        <v>2.17</v>
+        <v>2.07</v>
       </c>
       <c r="AB22">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AC22">
         <v>3.95</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK22">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4070,7 +4070,7 @@
         <v>3.3</v>
       </c>
       <c r="R23">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="S23">
         <v>1.31</v>
@@ -4094,13 +4094,13 @@
         <v>1.2</v>
       </c>
       <c r="Z23">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="AA23">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AB23">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC23">
         <v>2.55</v>
@@ -4112,10 +4112,10 @@
         <v>1.17</v>
       </c>
       <c r="AF23">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AG23">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4221,19 +4221,19 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="O24">
         <v>3.5</v>
       </c>
       <c r="P24">
-        <v>3.4</v>
+        <v>2.93</v>
       </c>
       <c r="Q24">
         <v>2.47</v>
       </c>
       <c r="R24">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="S24">
         <v>1.32</v>
@@ -4260,19 +4260,19 @@
         <v>4.05</v>
       </c>
       <c r="AA24">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AB24">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AC24">
-        <v>2.85</v>
+        <v>2.55</v>
       </c>
       <c r="AD24">
         <v>1.44</v>
       </c>
       <c r="AE24">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF24">
         <v>1.61</v>
@@ -4454,7 +4454,7 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AK25">
         <v>2.45</v>
@@ -4553,31 +4553,31 @@
         <v>3.2</v>
       </c>
       <c r="P26">
-        <v>2.49</v>
+        <v>2.53</v>
       </c>
       <c r="Q26">
-        <v>3.46</v>
+        <v>3.44</v>
       </c>
       <c r="R26">
         <v>2.01</v>
       </c>
       <c r="S26">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T26">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="U26">
         <v>2.89</v>
       </c>
       <c r="V26">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W26">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X26">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y26">
         <v>1.33</v>
@@ -4592,7 +4592,7 @@
         <v>1.8</v>
       </c>
       <c r="AC26">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AD26">
         <v>1.25</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="O29">
-        <v>5.5</v>
+        <v>5.55</v>
       </c>
       <c r="P29">
-        <v>7.8</v>
+        <v>7.95</v>
       </c>
       <c r="Q29">
         <v>1.67</v>
@@ -5054,13 +5054,13 @@
         <v>1.18</v>
       </c>
       <c r="T29">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="U29">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="V29">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="W29">
         <v>1.2</v>
@@ -5075,19 +5075,19 @@
         <v>6</v>
       </c>
       <c r="AA29">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AB29">
         <v>2.88</v>
       </c>
       <c r="AC29">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="AD29">
         <v>1.77</v>
       </c>
       <c r="AE29">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AF29">
         <v>1.62</v>
@@ -5202,13 +5202,13 @@
         <v>2.3</v>
       </c>
       <c r="O30">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="P30">
-        <v>2.95</v>
+        <v>2.71</v>
       </c>
       <c r="Q30">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="R30">
         <v>2.2</v>
@@ -5238,10 +5238,10 @@
         <v>3.2</v>
       </c>
       <c r="AA30">
+        <v>1.88</v>
+      </c>
+      <c r="AB30">
         <v>1.87</v>
-      </c>
-      <c r="AB30">
-        <v>1.85</v>
       </c>
       <c r="AC30">
         <v>3.14</v>
@@ -5256,7 +5256,7 @@
         <v>1.71</v>
       </c>
       <c r="AG30">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AK30">
         <v>1.53</v>
@@ -5362,10 +5362,10 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="O31">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="P31">
         <v>7</v>
@@ -5383,7 +5383,7 @@
         <v>4.8</v>
       </c>
       <c r="U31">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="V31">
         <v>1.93</v>
@@ -5401,10 +5401,10 @@
         <v>6.75</v>
       </c>
       <c r="AA31">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AB31">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="AC31">
         <v>1.75</v>
@@ -5419,7 +5419,7 @@
         <v>1.53</v>
       </c>
       <c r="AG31">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5576,7 +5576,7 @@
         <v>1.76</v>
       </c>
       <c r="AE32">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AF32">
         <v>1.66</v>
@@ -5688,16 +5688,16 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="O33">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="P33">
         <v>2.55</v>
       </c>
       <c r="Q33">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="R33">
         <v>2.13</v>
@@ -5709,16 +5709,16 @@
         <v>2.99</v>
       </c>
       <c r="U33">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="V33">
         <v>1.45</v>
       </c>
       <c r="W33">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X33">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y33">
         <v>1.22</v>
@@ -5742,10 +5742,10 @@
         <v>1.1</v>
       </c>
       <c r="AF33">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG33">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5851,10 +5851,10 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="O34">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="P34">
         <v>2.45</v>
@@ -5890,7 +5890,7 @@
         <v>3.8</v>
       </c>
       <c r="AA34">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="AB34">
         <v>2.01</v>
@@ -5902,7 +5902,7 @@
         <v>1.4</v>
       </c>
       <c r="AE34">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF34">
         <v>1.58</v>
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.09</v>
+        <v>2.14</v>
       </c>
       <c r="O35">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="P35">
         <v>2.85</v>
@@ -6044,7 +6044,7 @@
         <v>1.13</v>
       </c>
       <c r="X35">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y35">
         <v>1.13</v>
@@ -6056,19 +6056,19 @@
         <v>1.51</v>
       </c>
       <c r="AB35">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AC35">
         <v>2.34</v>
       </c>
       <c r="AD35">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AE35">
         <v>1.18</v>
       </c>
       <c r="AF35">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AG35">
         <v>2.5</v>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AK35">
         <v>1.58</v>
@@ -6183,7 +6183,7 @@
         <v>4.4</v>
       </c>
       <c r="P36">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Q36">
         <v>1.92</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="O37">
-        <v>4.05</v>
+        <v>3.7</v>
       </c>
       <c r="P37">
-        <v>4.21</v>
+        <v>4</v>
       </c>
       <c r="Q37">
         <v>2.19</v>
@@ -6361,10 +6361,10 @@
         <v>3.4</v>
       </c>
       <c r="U37">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="V37">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W37">
         <v>1.08</v>
@@ -6373,13 +6373,13 @@
         <v>1.03</v>
       </c>
       <c r="Y37">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z37">
         <v>4.8</v>
       </c>
       <c r="AA37">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AB37">
         <v>2.2</v>
@@ -6391,13 +6391,13 @@
         <v>1.44</v>
       </c>
       <c r="AE37">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF37">
         <v>1.57</v>
       </c>
       <c r="AG37">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>1.22</v>
       </c>
       <c r="AK37">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.61</v>
+        <v>2.45</v>
       </c>
       <c r="O38">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="P38">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6666,10 +6666,10 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="O39">
-        <v>5.15</v>
+        <v>5.05</v>
       </c>
       <c r="P39">
         <v>7.7</v>
@@ -6678,52 +6678,52 @@
         <v>1.83</v>
       </c>
       <c r="R39">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="S39">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T39">
-        <v>3.62</v>
+        <v>3.54</v>
       </c>
       <c r="U39">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="V39">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="W39">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X39">
         <v>1</v>
       </c>
       <c r="Y39">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z39">
-        <v>4.65</v>
+        <v>4.4</v>
       </c>
       <c r="AA39">
         <v>1.56</v>
       </c>
       <c r="AB39">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="AC39">
         <v>2.52</v>
       </c>
       <c r="AD39">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AE39">
         <v>1.18</v>
       </c>
       <c r="AF39">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="AG39">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>1.18</v>
       </c>
       <c r="AK39">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6838,10 +6838,10 @@
         <v>2.8</v>
       </c>
       <c r="Q40">
-        <v>2.75</v>
+        <v>2.84</v>
       </c>
       <c r="R40">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="S40">
         <v>1.29</v>
@@ -6874,7 +6874,7 @@
         <v>2.1</v>
       </c>
       <c r="AC40">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="AD40">
         <v>1.4</v>
@@ -6902,7 +6902,7 @@
         <v>1.22</v>
       </c>
       <c r="AK40">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="O41">
-        <v>3.52</v>
+        <v>4.2</v>
       </c>
       <c r="P41">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7031,10 +7031,10 @@
         <v>0</v>
       </c>
       <c r="AA41">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AB41">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AC41">
         <v>0</v>
@@ -7155,7 +7155,7 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="O42">
         <v>5.5</v>
@@ -7170,7 +7170,7 @@
         <v>2.9</v>
       </c>
       <c r="S42">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="T42">
         <v>4.2</v>
@@ -7182,13 +7182,13 @@
         <v>1.88</v>
       </c>
       <c r="W42">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X42">
         <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Z42">
         <v>7</v>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="O43">
-        <v>3.28</v>
+        <v>3.24</v>
       </c>
       <c r="P43">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="Q43">
         <v>2.88</v>
@@ -7333,19 +7333,19 @@
         <v>2.2</v>
       </c>
       <c r="S43">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T43">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="U43">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="V43">
         <v>1.4</v>
       </c>
       <c r="W43">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X43">
         <v>1.01</v>
@@ -7357,13 +7357,13 @@
         <v>3.73</v>
       </c>
       <c r="AA43">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AB43">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AC43">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AD43">
         <v>1.31</v>
@@ -7372,7 +7372,7 @@
         <v>1.13</v>
       </c>
       <c r="AF43">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG43">
         <v>2.1</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.29</v>
+        <v>1.41</v>
       </c>
       <c r="O44">
-        <v>3.45</v>
+        <v>5</v>
       </c>
       <c r="P44">
-        <v>3.15</v>
+        <v>5.9</v>
       </c>
       <c r="Q44">
-        <v>2.72</v>
+        <v>1.85</v>
       </c>
       <c r="R44">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="S44">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="T44">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="U44">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="V44">
-        <v>1.54</v>
+        <v>1.77</v>
       </c>
       <c r="W44">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="X44">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y44">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="Z44">
-        <v>4.33</v>
+        <v>5.75</v>
       </c>
       <c r="AA44">
-        <v>1.69</v>
+        <v>1.44</v>
       </c>
       <c r="AB44">
-        <v>2.3</v>
+        <v>2.59</v>
       </c>
       <c r="AC44">
-        <v>2.66</v>
+        <v>2.15</v>
       </c>
       <c r="AD44">
-        <v>1.51</v>
+        <v>1.7</v>
       </c>
       <c r="AE44">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AF44">
         <v>1.53</v>
       </c>
       <c r="AG44">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AK44">
-        <v>1.71</v>
+        <v>2.7</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.41</v>
+        <v>2.23</v>
       </c>
       <c r="O45">
-        <v>4.8</v>
+        <v>3.51</v>
       </c>
       <c r="P45">
-        <v>5.7</v>
+        <v>2.65</v>
       </c>
       <c r="Q45">
-        <v>1.85</v>
+        <v>2.72</v>
       </c>
       <c r="R45">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="S45">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="T45">
+        <v>3.4</v>
+      </c>
+      <c r="U45">
+        <v>2.38</v>
+      </c>
+      <c r="V45">
+        <v>1.52</v>
+      </c>
+      <c r="W45">
+        <v>1.11</v>
+      </c>
+      <c r="X45">
+        <v>1.04</v>
+      </c>
+      <c r="Y45">
+        <v>1.2</v>
+      </c>
+      <c r="Z45">
         <v>4.33</v>
       </c>
-      <c r="U45">
-        <v>2.1</v>
-      </c>
-      <c r="V45">
-        <v>1.77</v>
-      </c>
-      <c r="W45">
-        <v>1.18</v>
-      </c>
-      <c r="X45">
-        <v>1.02</v>
-      </c>
-      <c r="Y45">
-        <v>1.1</v>
-      </c>
-      <c r="Z45">
-        <v>5.75</v>
-      </c>
       <c r="AA45">
-        <v>1.44</v>
+        <v>1.69</v>
       </c>
       <c r="AB45">
-        <v>2.59</v>
+        <v>2.28</v>
       </c>
       <c r="AC45">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="AD45">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AE45">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AF45">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AG45">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AK45">
-        <v>2.74</v>
+        <v>1.71</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7810,7 +7810,7 @@
         <v>5</v>
       </c>
       <c r="O46">
-        <v>3.8</v>
+        <v>3.51</v>
       </c>
       <c r="P46">
         <v>1.71</v>
@@ -7837,22 +7837,22 @@
         <v>1.05</v>
       </c>
       <c r="X46">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z46">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="AA46">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="AB46">
         <v>1.91</v>
       </c>
       <c r="AC46">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="AD46">
         <v>1.29</v>
@@ -8133,16 +8133,16 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="O48">
-        <v>3.01</v>
+        <v>2.85</v>
       </c>
       <c r="P48">
-        <v>2.58</v>
+        <v>2.43</v>
       </c>
       <c r="Q48">
-        <v>3.32</v>
+        <v>3.36</v>
       </c>
       <c r="R48">
         <v>1.9</v>
@@ -8178,10 +8178,10 @@
         <v>1.63</v>
       </c>
       <c r="AC48">
-        <v>4.13</v>
+        <v>3.92</v>
       </c>
       <c r="AD48">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AE48">
         <v>1.03</v>
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AK48">
         <v>1.46</v>
@@ -8459,16 +8459,16 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="O50">
         <v>3.5</v>
       </c>
       <c r="P50">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="Q50">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="R50">
         <v>2.4</v>
@@ -8477,7 +8477,7 @@
         <v>1.28</v>
       </c>
       <c r="T50">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="U50">
         <v>2.29</v>
@@ -8489,22 +8489,22 @@
         <v>1.1</v>
       </c>
       <c r="X50">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y50">
         <v>1.18</v>
       </c>
       <c r="Z50">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="AA50">
         <v>1.59</v>
       </c>
       <c r="AB50">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="AC50">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AD50">
         <v>1.48</v>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AK50">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8788,10 +8788,10 @@
         <v>2.37</v>
       </c>
       <c r="O52">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="P52">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="Q52">
         <v>3.05</v>
@@ -8815,13 +8815,13 @@
         <v>1.02</v>
       </c>
       <c r="X52">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y52">
         <v>1.33</v>
       </c>
       <c r="Z52">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="AA52">
         <v>2.15</v>
@@ -8839,7 +8839,7 @@
         <v>1.04</v>
       </c>
       <c r="AF52">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AG52">
         <v>1.95</v>
@@ -8957,10 +8957,10 @@
         <v>3.81</v>
       </c>
       <c r="Q53">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="R53">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="S53">
         <v>1.42</v>
@@ -8978,7 +8978,7 @@
         <v>1.04</v>
       </c>
       <c r="X53">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="Y53">
         <v>1.27</v>
@@ -8996,7 +8996,7 @@
         <v>3.15</v>
       </c>
       <c r="AD53">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE53">
         <v>1.04</v>
@@ -9005,7 +9005,7 @@
         <v>1.71</v>
       </c>
       <c r="AG53">
-        <v>1.96</v>
+        <v>1.84</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>1.24</v>
       </c>
       <c r="AK53">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9141,13 +9141,13 @@
         <v>1.09</v>
       </c>
       <c r="X54">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y54">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="Z54">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA54">
         <v>1.88</v>
@@ -9162,7 +9162,7 @@
         <v>1.26</v>
       </c>
       <c r="AE54">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF54">
         <v>1.74</v>
@@ -9603,10 +9603,10 @@
         <v>2.85</v>
       </c>
       <c r="O57">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="P57">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="Q57">
         <v>4.12</v>
@@ -10089,43 +10089,43 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="O60">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="P60">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="Q60">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="R60">
-        <v>2.63</v>
+        <v>2.78</v>
       </c>
       <c r="S60">
         <v>1.17</v>
       </c>
       <c r="T60">
-        <v>3.95</v>
+        <v>3.98</v>
       </c>
       <c r="U60">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="V60">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="W60">
         <v>1.16</v>
       </c>
       <c r="X60">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y60">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z60">
-        <v>5.6</v>
+        <v>6.1</v>
       </c>
       <c r="AA60">
         <v>1.36</v>
@@ -10134,19 +10134,19 @@
         <v>3</v>
       </c>
       <c r="AC60">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AD60">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AE60">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AF60">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AG60">
-        <v>2.64</v>
+        <v>2.54</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AK60">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10904,34 +10904,34 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.39</v>
+        <v>2.6</v>
       </c>
       <c r="O65">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P65">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="Q65">
-        <v>2.89</v>
+        <v>3.36</v>
       </c>
       <c r="R65">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="S65">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T65">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="U65">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="V65">
         <v>1.33</v>
       </c>
       <c r="W65">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X65">
         <v>1.02</v>
@@ -10961,7 +10961,7 @@
         <v>1.75</v>
       </c>
       <c r="AG65">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,7 +10974,7 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK65">
         <v>1.44</v>
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="O67">
         <v>3.32</v>
       </c>
       <c r="P67">
-        <v>2.42</v>
+        <v>2.27</v>
       </c>
       <c r="Q67">
         <v>3.4</v>
@@ -11251,7 +11251,7 @@
         <v>3.05</v>
       </c>
       <c r="U67">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="V67">
         <v>1.4</v>
@@ -11287,7 +11287,7 @@
         <v>1.67</v>
       </c>
       <c r="AG67">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>1.3</v>
       </c>
       <c r="AK67">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11405,7 +11405,7 @@
         <v>1.83</v>
       </c>
       <c r="R68">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="S68">
         <v>1.33</v>
@@ -11420,10 +11420,10 @@
         <v>1.48</v>
       </c>
       <c r="W68">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X68">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y68">
         <v>1.2</v>
@@ -11441,13 +11441,13 @@
         <v>2.65</v>
       </c>
       <c r="AD68">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AE68">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF68">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AG68">
         <v>1.9</v>
@@ -11586,7 +11586,7 @@
         <v>1.06</v>
       </c>
       <c r="X69">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y69">
         <v>1.25</v>
@@ -11601,13 +11601,13 @@
         <v>1.9</v>
       </c>
       <c r="AC69">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AD69">
         <v>1.34</v>
       </c>
       <c r="AE69">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AF69">
         <v>1.65</v>
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
+        <v>2.56</v>
+      </c>
+      <c r="O70">
+        <v>3.29</v>
+      </c>
+      <c r="P70">
         <v>2.6</v>
-      </c>
-      <c r="O70">
-        <v>3.44</v>
-      </c>
-      <c r="P70">
-        <v>2.62</v>
       </c>
       <c r="Q70">
         <v>0</v>
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="O74">
         <v>4.75</v>
       </c>
       <c r="P74">
-        <v>6.2</v>
+        <v>6.65</v>
       </c>
       <c r="Q74">
         <v>1.82</v>
@@ -12395,13 +12395,13 @@
         <v>2.29</v>
       </c>
       <c r="V74">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="W74">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X74">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y74">
         <v>1.17</v>
@@ -12444,7 +12444,7 @@
         <v>1.16</v>
       </c>
       <c r="AK74">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12552,7 +12552,7 @@
         <v>1.35</v>
       </c>
       <c r="T75">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="U75">
         <v>2.76</v>
@@ -12567,7 +12567,7 @@
         <v>1.05</v>
       </c>
       <c r="Y75">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z75">
         <v>3.6</v>
@@ -12576,7 +12576,7 @@
         <v>1.83</v>
       </c>
       <c r="AB75">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AC75">
         <v>3.1</v>
@@ -12591,7 +12591,7 @@
         <v>1.67</v>
       </c>
       <c r="AG75">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12697,22 +12697,22 @@
         </is>
       </c>
       <c r="N76">
-        <v>4.45</v>
+        <v>3.67</v>
       </c>
       <c r="O76">
-        <v>3.1</v>
+        <v>3.17</v>
       </c>
       <c r="P76">
         <v>1.86</v>
       </c>
       <c r="Q76">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="R76">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="S76">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="T76">
         <v>2.48</v>
@@ -12721,7 +12721,7 @@
         <v>3.33</v>
       </c>
       <c r="V76">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W76">
         <v>1.04</v>
@@ -12733,16 +12733,16 @@
         <v>1.36</v>
       </c>
       <c r="Z76">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="AA76">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="AB76">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AC76">
-        <v>3.91</v>
+        <v>3.94</v>
       </c>
       <c r="AD76">
         <v>1.25</v>
@@ -12751,10 +12751,10 @@
         <v>1.04</v>
       </c>
       <c r="AF76">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AG76">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.37</v>
+        <v>1.23</v>
       </c>
       <c r="AK76">
         <v>1.25</v>
@@ -12863,19 +12863,19 @@
         <v>1.73</v>
       </c>
       <c r="O77">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="P77">
-        <v>4.15</v>
+        <v>4.4</v>
       </c>
       <c r="Q77">
         <v>2.18</v>
       </c>
       <c r="R77">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="S77">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T77">
         <v>3</v>
@@ -12887,7 +12887,7 @@
         <v>1.42</v>
       </c>
       <c r="W77">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X77">
         <v>1.05</v>
@@ -13186,13 +13186,13 @@
         </is>
       </c>
       <c r="N79">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="O79">
-        <v>6.05</v>
+        <v>6</v>
       </c>
       <c r="P79">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Q79">
         <v>7.4</v>
@@ -13207,7 +13207,7 @@
         <v>3.88</v>
       </c>
       <c r="U79">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="V79">
         <v>1.65</v>
@@ -13216,25 +13216,25 @@
         <v>1.18</v>
       </c>
       <c r="X79">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y79">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z79">
-        <v>6.5</v>
+        <v>5.4</v>
       </c>
       <c r="AA79">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AB79">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="AC79">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AD79">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="AE79">
         <v>1.27</v>
@@ -13355,7 +13355,7 @@
         <v>3.75</v>
       </c>
       <c r="P80">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="Q80">
         <v>3.1</v>
@@ -13382,22 +13382,22 @@
         <v>1.02</v>
       </c>
       <c r="Y80">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="Z80">
         <v>5.5</v>
       </c>
       <c r="AA80">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AB80">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AC80">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="AD80">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AE80">
         <v>1.3</v>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AK80">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13512,19 +13512,19 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="O81">
         <v>3.4</v>
       </c>
       <c r="P81">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="Q81">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="R81">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="S81">
         <v>1.3</v>
@@ -13533,7 +13533,7 @@
         <v>3.2</v>
       </c>
       <c r="U81">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="V81">
         <v>1.44</v>
@@ -13545,22 +13545,22 @@
         <v>1</v>
       </c>
       <c r="Y81">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z81">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="AA81">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AB81">
         <v>1.87</v>
       </c>
       <c r="AC81">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="AD81">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE81">
         <v>1.1</v>
@@ -13585,7 +13585,7 @@
         <v>1.36</v>
       </c>
       <c r="AK81">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="O82">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P82">
         <v>3.74</v>
@@ -13690,10 +13690,10 @@
         <v>1.95</v>
       </c>
       <c r="S82">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="T82">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="U82">
         <v>3.15</v>
@@ -13708,13 +13708,13 @@
         <v>1.09</v>
       </c>
       <c r="Y82">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Z82">
         <v>2.8</v>
       </c>
       <c r="AA82">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AB82">
         <v>1.66</v>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK82">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -14004,10 +14004,10 @@
         <v>2.15</v>
       </c>
       <c r="O84">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P84">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="Q84">
         <v>2.75</v>
@@ -14016,16 +14016,16 @@
         <v>2.25</v>
       </c>
       <c r="S84">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T84">
         <v>3.2</v>
       </c>
       <c r="U84">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="V84">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W84">
         <v>1.07</v>
@@ -14034,22 +14034,22 @@
         <v>1.02</v>
       </c>
       <c r="Y84">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z84">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="AA84">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AB84">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AC84">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="AD84">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE84">
         <v>1.13</v>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK84">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14164,10 +14164,10 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O85">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P85">
         <v>2.75</v>
@@ -14197,7 +14197,7 @@
         <v>1.04</v>
       </c>
       <c r="Y85">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z85">
         <v>4.4</v>
@@ -14218,10 +14218,10 @@
         <v>1.2</v>
       </c>
       <c r="AF85">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="AG85">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>1.41</v>
       </c>
       <c r="AK85">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14327,19 +14327,19 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="O86">
         <v>3.5</v>
       </c>
       <c r="P86">
-        <v>4.15</v>
+        <v>3.9</v>
       </c>
       <c r="Q86">
         <v>2.4</v>
       </c>
       <c r="R86">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="S86">
         <v>1.3</v>
@@ -14366,7 +14366,7 @@
         <v>3.56</v>
       </c>
       <c r="AA86">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AB86">
         <v>1.95</v>
@@ -14668,22 +14668,22 @@
         <v>2.22</v>
       </c>
       <c r="S88">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T88">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="U88">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="V88">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W88">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X88">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y88">
         <v>1.29</v>
@@ -14692,19 +14692,19 @@
         <v>3.25</v>
       </c>
       <c r="AA88">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="AB88">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="AC88">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="AD88">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="AE88">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF88">
         <v>1.68</v>
@@ -14816,16 +14816,16 @@
         </is>
       </c>
       <c r="N89">
-        <v>3.03</v>
+        <v>3.84</v>
       </c>
       <c r="O89">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="P89">
         <v>1.96</v>
       </c>
       <c r="Q89">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="R89">
         <v>2.4</v>
@@ -14834,13 +14834,13 @@
         <v>1.25</v>
       </c>
       <c r="T89">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="U89">
         <v>2.39</v>
       </c>
       <c r="V89">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W89">
         <v>1.15</v>
@@ -14849,7 +14849,7 @@
         <v>1.01</v>
       </c>
       <c r="Y89">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z89">
         <v>4.8</v>
@@ -14858,7 +14858,7 @@
         <v>1.6</v>
       </c>
       <c r="AB89">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AC89">
         <v>2.4</v>
@@ -14979,16 +14979,16 @@
         </is>
       </c>
       <c r="N90">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="O90">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="P90">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="Q90">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="R90">
         <v>2.5</v>
@@ -14997,10 +14997,10 @@
         <v>1.22</v>
       </c>
       <c r="T90">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="U90">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="V90">
         <v>1.68</v>
@@ -15024,13 +15024,13 @@
         <v>2.68</v>
       </c>
       <c r="AC90">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AD90">
         <v>1.65</v>
       </c>
       <c r="AE90">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AF90">
         <v>1.44</v>
@@ -15142,19 +15142,19 @@
         </is>
       </c>
       <c r="N91">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="O91">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P91">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="Q91">
-        <v>4.22</v>
+        <v>4.33</v>
       </c>
       <c r="R91">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S91">
         <v>1.37</v>
@@ -15163,10 +15163,10 @@
         <v>2.6</v>
       </c>
       <c r="U91">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="V91">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W91">
         <v>1.07</v>
@@ -15175,31 +15175,31 @@
         <v>1.01</v>
       </c>
       <c r="Y91">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z91">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AA91">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB91">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC91">
-        <v>3.28</v>
+        <v>3.42</v>
       </c>
       <c r="AD91">
         <v>1.25</v>
       </c>
       <c r="AE91">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF91">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AG91">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK91">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15305,10 +15305,10 @@
         </is>
       </c>
       <c r="N92">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="O92">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="P92">
         <v>3.4</v>
@@ -15320,7 +15320,7 @@
         <v>2.3</v>
       </c>
       <c r="S92">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T92">
         <v>3.16</v>
@@ -15338,7 +15338,7 @@
         <v>1.01</v>
       </c>
       <c r="Y92">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z92">
         <v>4.05</v>
@@ -15350,13 +15350,13 @@
         <v>2.23</v>
       </c>
       <c r="AC92">
-        <v>2.8</v>
+        <v>2.49</v>
       </c>
       <c r="AD92">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AE92">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF92">
         <v>1.57</v>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK92">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15468,13 +15468,13 @@
         </is>
       </c>
       <c r="N93">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="O93">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="P93">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -15495,10 +15495,10 @@
         <v>1.46</v>
       </c>
       <c r="W93">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X93">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y93">
         <v>1.2</v>
@@ -15516,7 +15516,7 @@
         <v>2.8</v>
       </c>
       <c r="AD93">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE93">
         <v>1.14</v>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
+        <v>1.24</v>
+      </c>
+      <c r="AK93">
         <v>1.25</v>
-      </c>
-      <c r="AK93">
-        <v>1.24</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="O94">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="P94">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="Q94">
         <v>1.95</v>
@@ -15655,13 +15655,13 @@
         <v>2.15</v>
       </c>
       <c r="V94">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="W94">
         <v>1.13</v>
       </c>
       <c r="X94">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y94">
         <v>1.11</v>
@@ -15670,7 +15670,7 @@
         <v>4.9</v>
       </c>
       <c r="AA94">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AB94">
         <v>2.5</v>
@@ -15679,7 +15679,7 @@
         <v>2.15</v>
       </c>
       <c r="AD94">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AE94">
         <v>1.24</v>
@@ -15688,7 +15688,7 @@
         <v>1.57</v>
       </c>
       <c r="AG94">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -16452,13 +16452,13 @@
         <v>4.85</v>
       </c>
       <c r="P99">
-        <v>6.5</v>
+        <v>7.55</v>
       </c>
       <c r="Q99">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="R99">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S99">
         <v>1.26</v>
@@ -16476,7 +16476,7 @@
         <v>1.07</v>
       </c>
       <c r="X99">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y99">
         <v>1.2</v>
@@ -16497,13 +16497,13 @@
         <v>1.4</v>
       </c>
       <c r="AE99">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF99">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AG99">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O101">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P101">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q101">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R101">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S101">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T101">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U101">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V101">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W101">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X101">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y101">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z101">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA101">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB101">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC101">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD101">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE101">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF101">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG101">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK101">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16944,55 +16944,55 @@
         <v>0</v>
       </c>
       <c r="Q102">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R102">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S102">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T102">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U102">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V102">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W102">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X102">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y102">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z102">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA102">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB102">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC102">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD102">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE102">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF102">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG102">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK102">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17261,43 +17261,43 @@
         </is>
       </c>
       <c r="N104">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="O104">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="P104">
-        <v>6.5</v>
+        <v>5.25</v>
       </c>
       <c r="Q104">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="R104">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="S104">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="T104">
-        <v>2.67</v>
+        <v>3.1</v>
       </c>
       <c r="U104">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="V104">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W104">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X104">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y104">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z104">
-        <v>3.42</v>
+        <v>3.68</v>
       </c>
       <c r="AA104">
         <v>1.85</v>
@@ -17306,19 +17306,19 @@
         <v>1.95</v>
       </c>
       <c r="AC104">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AD104">
         <v>1.33</v>
       </c>
       <c r="AE104">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF104">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="AG104">
-        <v>1.69</v>
+        <v>1.84</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK104">
-        <v>2.52</v>
+        <v>2.3</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17593,7 +17593,7 @@
         <v>3.4</v>
       </c>
       <c r="P106">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Q106">
         <v>2.25</v>
@@ -17602,10 +17602,10 @@
         <v>2.01</v>
       </c>
       <c r="S106">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T106">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="U106">
         <v>2.88</v>
@@ -17626,10 +17626,10 @@
         <v>3.08</v>
       </c>
       <c r="AA106">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AB106">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AC106">
         <v>3.42</v>
@@ -17657,7 +17657,7 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AK106">
         <v>2.1</v>
@@ -17750,13 +17750,13 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="O107">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P107">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="Q107">
         <v>2.6</v>
@@ -17765,13 +17765,13 @@
         <v>2.35</v>
       </c>
       <c r="S107">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T107">
         <v>3.3</v>
       </c>
       <c r="U107">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="V107">
         <v>1.48</v>
@@ -17786,13 +17786,13 @@
         <v>1.16</v>
       </c>
       <c r="Z107">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AA107">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AB107">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="AC107">
         <v>2.63</v>
@@ -17801,7 +17801,7 @@
         <v>1.4</v>
       </c>
       <c r="AE107">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AF107">
         <v>1.55</v>
@@ -17916,7 +17916,7 @@
         <v>2.87</v>
       </c>
       <c r="O108">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="P108">
         <v>2.5</v>
@@ -17928,10 +17928,10 @@
         <v>2.1</v>
       </c>
       <c r="S108">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T108">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="U108">
         <v>2.62</v>
@@ -17983,7 +17983,7 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AK108">
         <v>1.4</v>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G118">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G119">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G120">
@@ -20195,13 +20195,13 @@
         </is>
       </c>
       <c r="N122">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="O122">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="P122">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q122">
         <v>3.4</v>
@@ -20216,10 +20216,10 @@
         <v>2.75</v>
       </c>
       <c r="U122">
-        <v>3.03</v>
+        <v>2.8</v>
       </c>
       <c r="V122">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W122">
         <v>1.06</v>
@@ -20228,25 +20228,25 @@
         <v>1</v>
       </c>
       <c r="Y122">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="Z122">
         <v>2.9</v>
       </c>
       <c r="AA122">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AB122">
         <v>1.7</v>
       </c>
       <c r="AC122">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="AD122">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE122">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF122">
         <v>1.75</v>
@@ -20367,7 +20367,7 @@
         <v>3.78</v>
       </c>
       <c r="Q123">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="R123">
         <v>2.25</v>
@@ -20397,7 +20397,7 @@
         <v>3.85</v>
       </c>
       <c r="AA123">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB123">
         <v>2.1</v>
@@ -21336,58 +21336,58 @@
         </is>
       </c>
       <c r="N129">
+        <v>4.4</v>
+      </c>
+      <c r="O129">
         <v>4.2</v>
       </c>
-      <c r="O129">
-        <v>4</v>
-      </c>
       <c r="P129">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="Q129">
         <v>4.4</v>
       </c>
       <c r="R129">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="S129">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T129">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="U129">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="V129">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="W129">
         <v>1.17</v>
       </c>
       <c r="X129">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y129">
         <v>1.09</v>
       </c>
       <c r="Z129">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AA129">
         <v>1.4</v>
       </c>
       <c r="AB129">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="AC129">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AD129">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AE129">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AF129">
         <v>1.45</v>
@@ -21406,7 +21406,7 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AK129">
         <v>1.12</v>
@@ -21508,16 +21508,16 @@
         <v>2.62</v>
       </c>
       <c r="Q130">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="R130">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="S130">
         <v>1.28</v>
       </c>
       <c r="T130">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="U130">
         <v>2.41</v>
@@ -21538,10 +21538,10 @@
         <v>3.8</v>
       </c>
       <c r="AA130">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB130">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="AC130">
         <v>2.59</v>
@@ -21572,7 +21572,7 @@
         <v>1.22</v>
       </c>
       <c r="AK130">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -22151,13 +22151,13 @@
         </is>
       </c>
       <c r="N134">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="O134">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="P134">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="Q134">
         <v>0</v>
@@ -22477,13 +22477,13 @@
         </is>
       </c>
       <c r="N136">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="O136">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="P136">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="Q136">
         <v>3.1</v>
@@ -22522,10 +22522,10 @@
         <v>2.45</v>
       </c>
       <c r="AC136">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="AD136">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AE136">
         <v>1.22</v>
@@ -22550,7 +22550,7 @@
         <v>1.25</v>
       </c>
       <c r="AK136">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22640,13 +22640,13 @@
         </is>
       </c>
       <c r="N137">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="O137">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="P137">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="Q137">
         <v>6</v>
@@ -22676,10 +22676,10 @@
         <v>1.24</v>
       </c>
       <c r="Z137">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AA137">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AB137">
         <v>1.87</v>
@@ -22691,7 +22691,7 @@
         <v>1.33</v>
       </c>
       <c r="AE137">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF137">
         <v>1.91</v>
@@ -22713,7 +22713,7 @@
         <v>2.46</v>
       </c>
       <c r="AK137">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -23036,7 +23036,7 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>1.21</v>
+        <v>1.46</v>
       </c>
       <c r="AK139">
         <v>1.36</v>
@@ -23292,64 +23292,64 @@
         </is>
       </c>
       <c r="N141">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="O141">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P141">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="Q141">
-        <v>2.18</v>
+        <v>2.07</v>
       </c>
       <c r="R141">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="S141">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T141">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U141">
         <v>2.25</v>
       </c>
       <c r="V141">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W141">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X141">
         <v>1.01</v>
       </c>
       <c r="Y141">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z141">
         <v>3.95</v>
       </c>
       <c r="AA141">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="AB141">
-        <v>2.07</v>
+        <v>2.19</v>
       </c>
       <c r="AC141">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="AD141">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AE141">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF141">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG141">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AH141" t="inlineStr">
         <is>
@@ -23362,10 +23362,10 @@
         </is>
       </c>
       <c r="AJ141">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK141">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AL141">
         <v>0</v>
@@ -23618,7 +23618,7 @@
         </is>
       </c>
       <c r="N143">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="O143">
         <v>3.25</v>
@@ -23627,7 +23627,7 @@
         <v>3.25</v>
       </c>
       <c r="Q143">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="R143">
         <v>2.15</v>
@@ -23645,7 +23645,7 @@
         <v>1.44</v>
       </c>
       <c r="W143">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X143">
         <v>1.05</v>
@@ -23675,7 +23675,7 @@
         <v>1.62</v>
       </c>
       <c r="AG143">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH143" t="inlineStr">
         <is>
@@ -23781,10 +23781,10 @@
         </is>
       </c>
       <c r="N144">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="O144">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="P144">
         <v>6</v>
@@ -23799,22 +23799,22 @@
         <v>1.3</v>
       </c>
       <c r="T144">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U144">
         <v>2.32</v>
       </c>
       <c r="V144">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W144">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X144">
         <v>1.01</v>
       </c>
       <c r="Y144">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z144">
         <v>4.2</v>
@@ -23838,7 +23838,7 @@
         <v>1.83</v>
       </c>
       <c r="AG144">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AK144">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23944,13 +23944,13 @@
         </is>
       </c>
       <c r="N145">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O145">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="P145">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="Q145">
         <v>2.88</v>
@@ -23959,10 +23959,10 @@
         <v>2</v>
       </c>
       <c r="S145">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T145">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="U145">
         <v>3.1</v>
@@ -23980,13 +23980,13 @@
         <v>1.4</v>
       </c>
       <c r="Z145">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AA145">
         <v>2.31</v>
       </c>
       <c r="AB145">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AC145">
         <v>3.86</v>
@@ -23995,13 +23995,13 @@
         <v>1.22</v>
       </c>
       <c r="AE145">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF145">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AG145">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24017,7 +24017,7 @@
         <v>1.3</v>
       </c>
       <c r="AK145">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24107,19 +24107,19 @@
         </is>
       </c>
       <c r="N146">
-        <v>6.75</v>
+        <v>7.25</v>
       </c>
       <c r="O146">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="P146">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="Q146">
         <v>6.5</v>
       </c>
       <c r="R146">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="S146">
         <v>1.35</v>
@@ -24137,13 +24137,13 @@
         <v>1.09</v>
       </c>
       <c r="X146">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y146">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z146">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="AA146">
         <v>1.75</v>
@@ -24155,13 +24155,13 @@
         <v>3</v>
       </c>
       <c r="AD146">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE146">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF146">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AG146">
         <v>1.75</v>
@@ -24180,7 +24180,7 @@
         <v>2.7</v>
       </c>
       <c r="AK146">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24273,10 +24273,10 @@
         <v>1.3</v>
       </c>
       <c r="O147">
-        <v>5.94</v>
+        <v>6</v>
       </c>
       <c r="P147">
-        <v>8.199999999999999</v>
+        <v>7.75</v>
       </c>
       <c r="Q147">
         <v>0</v>
@@ -24460,7 +24460,7 @@
         <v>1.53</v>
       </c>
       <c r="W148">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X148">
         <v>1.03</v>
@@ -24472,10 +24472,10 @@
         <v>4.2</v>
       </c>
       <c r="AA148">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AB148">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="AC148">
         <v>2.7</v>
@@ -24490,7 +24490,7 @@
         <v>1.55</v>
       </c>
       <c r="AG148">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH148" t="inlineStr">
         <is>
@@ -24759,22 +24759,22 @@
         </is>
       </c>
       <c r="N150">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="O150">
         <v>3.6</v>
       </c>
       <c r="P150">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="Q150">
         <v>2</v>
       </c>
       <c r="R150">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="S150">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T150">
         <v>2.88</v>
@@ -24798,7 +24798,7 @@
         <v>3.51</v>
       </c>
       <c r="AA150">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AB150">
         <v>1.85</v>
@@ -24922,13 +24922,13 @@
         </is>
       </c>
       <c r="N151">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="O151">
         <v>3.4</v>
       </c>
       <c r="P151">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="Q151">
         <v>2.3</v>
@@ -24958,7 +24958,7 @@
         <v>1.36</v>
       </c>
       <c r="Z151">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AA151">
         <v>2.1</v>
@@ -24973,7 +24973,7 @@
         <v>1.23</v>
       </c>
       <c r="AE151">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF151">
         <v>2</v>
@@ -24992,10 +24992,10 @@
         </is>
       </c>
       <c r="AJ151">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK151">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AL151">
         <v>0</v>
@@ -25097,7 +25097,7 @@
         <v>2.25</v>
       </c>
       <c r="R152">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="S152">
         <v>1.25</v>
@@ -25106,16 +25106,16 @@
         <v>3.6</v>
       </c>
       <c r="U152">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="V152">
         <v>1.55</v>
       </c>
       <c r="W152">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X152">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y152">
         <v>1.18</v>
@@ -25124,10 +25124,10 @@
         <v>4.25</v>
       </c>
       <c r="AA152">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AB152">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC152">
         <v>2.43</v>
@@ -25453,7 +25453,7 @@
         <v>2.01</v>
       </c>
       <c r="AB154">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC154">
         <v>3.6</v>
@@ -25574,65 +25574,65 @@
         </is>
       </c>
       <c r="N155">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="O155">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="P155">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q155">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="R155">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="S155">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="T155">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="U155">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="V155">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="W155">
         <v>1.2</v>
       </c>
       <c r="X155">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y155">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Z155">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AA155">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AB155">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="AC155">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AD155">
+        <v>1.88</v>
+      </c>
+      <c r="AE155">
+        <v>1.35</v>
+      </c>
+      <c r="AF155">
+        <v>1.91</v>
+      </c>
+      <c r="AG155">
         <v>1.8</v>
       </c>
-      <c r="AE155">
-        <v>1.3</v>
-      </c>
-      <c r="AF155">
-        <v>1.88</v>
-      </c>
-      <c r="AG155">
-        <v>1.81</v>
-      </c>
       <c r="AH155" t="inlineStr">
         <is>
           <t>[]</t>
@@ -25644,10 +25644,10 @@
         </is>
       </c>
       <c r="AJ155">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AK155">
-        <v>4.65</v>
+        <v>5.05</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25737,64 +25737,64 @@
         </is>
       </c>
       <c r="N156">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O156">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P156">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q156">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="R156">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="S156">
         <v>1.42</v>
       </c>
       <c r="T156">
-        <v>2.59</v>
+        <v>2.8</v>
       </c>
       <c r="U156">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="V156">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W156">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X156">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y156">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="Z156">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="AA156">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AB156">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AC156">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AD156">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AE156">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF156">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AG156">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25810,7 +25810,7 @@
         <v>1.3</v>
       </c>
       <c r="AK156">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -25900,25 +25900,25 @@
         </is>
       </c>
       <c r="N157">
-        <v>2.35</v>
+        <v>2.51</v>
       </c>
       <c r="O157">
         <v>2.87</v>
       </c>
       <c r="P157">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="Q157">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="R157">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="S157">
         <v>1.5</v>
       </c>
       <c r="T157">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="U157">
         <v>3.6</v>
@@ -25927,10 +25927,10 @@
         <v>1.3</v>
       </c>
       <c r="W157">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X157">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Y157">
         <v>1.44</v>
@@ -25942,22 +25942,22 @@
         <v>2.31</v>
       </c>
       <c r="AB157">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AC157">
-        <v>4.8</v>
+        <v>4.13</v>
       </c>
       <c r="AD157">
         <v>1.18</v>
       </c>
       <c r="AE157">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF157">
         <v>1.95</v>
       </c>
       <c r="AG157">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25973,7 +25973,7 @@
         <v>1.33</v>
       </c>
       <c r="AK157">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26063,13 +26063,13 @@
         </is>
       </c>
       <c r="N158">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="O158">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="P158">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Q158">
         <v>2.05</v>
@@ -26087,7 +26087,7 @@
         <v>2.4</v>
       </c>
       <c r="V158">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W158">
         <v>1.08</v>
@@ -26102,25 +26102,25 @@
         <v>4</v>
       </c>
       <c r="AA158">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AB158">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="AC158">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="AD158">
         <v>1.43</v>
       </c>
       <c r="AE158">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF158">
         <v>1.7</v>
       </c>
       <c r="AG158">
-        <v>2.04</v>
+        <v>1.92</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26238,7 +26238,7 @@
         <v>1.75</v>
       </c>
       <c r="R159">
-        <v>3.11</v>
+        <v>2.92</v>
       </c>
       <c r="S159">
         <v>1.15</v>
@@ -26299,7 +26299,7 @@
         <v>1.13</v>
       </c>
       <c r="AK159">
-        <v>2.43</v>
+        <v>2.71</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -26389,13 +26389,13 @@
         </is>
       </c>
       <c r="N160">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="O160">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="P160">
-        <v>2.99</v>
+        <v>2.95</v>
       </c>
       <c r="Q160">
         <v>2.28</v>
@@ -26416,28 +26416,28 @@
         <v>1.8</v>
       </c>
       <c r="W160">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X160">
         <v>1.01</v>
       </c>
       <c r="Y160">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z160">
-        <v>6.05</v>
+        <v>5.95</v>
       </c>
       <c r="AA160">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB160">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AC160">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AD160">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AE160">
         <v>1.3</v>
@@ -26446,7 +26446,7 @@
         <v>1.33</v>
       </c>
       <c r="AG160">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="AH160" t="inlineStr">
         <is>
@@ -26462,7 +26462,7 @@
         <v>1.36</v>
       </c>
       <c r="AK160">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AL160">
         <v>0</v>
@@ -26552,19 +26552,19 @@
         </is>
       </c>
       <c r="N161">
-        <v>4.35</v>
+        <v>4.2</v>
       </c>
       <c r="O161">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="P161">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="Q161">
-        <v>4.34</v>
+        <v>4.28</v>
       </c>
       <c r="R161">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="S161">
         <v>1.11</v>
@@ -26573,10 +26573,10 @@
         <v>6</v>
       </c>
       <c r="U161">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="V161">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="W161">
         <v>1.41</v>
@@ -26594,7 +26594,7 @@
         <v>1.1</v>
       </c>
       <c r="AB161">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="AC161">
         <v>1.4</v>
@@ -26603,7 +26603,7 @@
         <v>2.7</v>
       </c>
       <c r="AE161">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AF161">
         <v>1.22</v>
@@ -26715,19 +26715,19 @@
         </is>
       </c>
       <c r="N162">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="O162">
         <v>3.6</v>
       </c>
       <c r="P162">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="Q162">
         <v>2.5</v>
       </c>
       <c r="R162">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="S162">
         <v>1.16</v>
@@ -26736,7 +26736,7 @@
         <v>3.9</v>
       </c>
       <c r="U162">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="V162">
         <v>1.67</v>
@@ -26769,10 +26769,10 @@
         <v>1.28</v>
       </c>
       <c r="AF162">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AG162">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AH162" t="inlineStr">
         <is>
@@ -26878,7 +26878,7 @@
         </is>
       </c>
       <c r="N163">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="O163">
         <v>3.38</v>
@@ -26951,7 +26951,7 @@
         <v>1.34</v>
       </c>
       <c r="AK163">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AL163">
         <v>0</v>
@@ -27041,16 +27041,16 @@
         </is>
       </c>
       <c r="N164">
-        <v>2.33</v>
+        <v>2.62</v>
       </c>
       <c r="O164">
         <v>3.05</v>
       </c>
       <c r="P164">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="Q164">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R164">
         <v>1.91</v>
@@ -27059,7 +27059,7 @@
         <v>1.5</v>
       </c>
       <c r="T164">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="U164">
         <v>3.3</v>
@@ -27071,7 +27071,7 @@
         <v>1.02</v>
       </c>
       <c r="X164">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Y164">
         <v>1.5</v>
@@ -27080,16 +27080,16 @@
         <v>2.55</v>
       </c>
       <c r="AA164">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AB164">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AC164">
         <v>5</v>
       </c>
       <c r="AD164">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AE164">
         <v>1.02</v>
@@ -27098,7 +27098,7 @@
         <v>1.95</v>
       </c>
       <c r="AG164">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AH164" t="inlineStr">
         <is>
@@ -27111,7 +27111,7 @@
         </is>
       </c>
       <c r="AJ164">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AK164">
         <v>1.5</v>
@@ -27204,13 +27204,13 @@
         </is>
       </c>
       <c r="N165">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="O165">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="P165">
-        <v>3.73</v>
+        <v>3.14</v>
       </c>
       <c r="Q165">
         <v>0</v>
@@ -27862,19 +27862,19 @@
         <v>3</v>
       </c>
       <c r="P169">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="Q169">
         <v>2.62</v>
       </c>
       <c r="R169">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="S169">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="T169">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="U169">
         <v>3.94</v>
@@ -28022,10 +28022,10 @@
         <v>1.83</v>
       </c>
       <c r="O170">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="P170">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="Q170">
         <v>2.2</v>
@@ -28058,7 +28058,7 @@
         <v>3.96</v>
       </c>
       <c r="AA170">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AB170">
         <v>2.04</v>
@@ -28073,7 +28073,7 @@
         <v>1.14</v>
       </c>
       <c r="AF170">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG170">
         <v>2.08</v>
@@ -28092,7 +28092,7 @@
         <v>1.29</v>
       </c>
       <c r="AK170">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AL170">
         <v>0</v>
@@ -28182,13 +28182,13 @@
         </is>
       </c>
       <c r="N171">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="O171">
         <v>4.9</v>
       </c>
       <c r="P171">
-        <v>10.1</v>
+        <v>7.5</v>
       </c>
       <c r="Q171">
         <v>1.8</v>
@@ -28197,10 +28197,10 @@
         <v>2.38</v>
       </c>
       <c r="S171">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T171">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U171">
         <v>2.81</v>
@@ -28212,7 +28212,7 @@
         <v>1.04</v>
       </c>
       <c r="X171">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y171">
         <v>1.33</v>
@@ -28224,16 +28224,16 @@
         <v>1.91</v>
       </c>
       <c r="AB171">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AC171">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AD171">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE171">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF171">
         <v>2.3</v>
@@ -28348,10 +28348,10 @@
         <v>1.36</v>
       </c>
       <c r="O172">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="P172">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="Q172">
         <v>1.81</v>
@@ -28363,7 +28363,7 @@
         <v>1.3</v>
       </c>
       <c r="T172">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="U172">
         <v>2.3</v>
@@ -28393,13 +28393,13 @@
         <v>2.64</v>
       </c>
       <c r="AD172">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AE172">
         <v>1.14</v>
       </c>
       <c r="AF172">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AG172">
         <v>1.85</v>
@@ -28415,10 +28415,10 @@
         </is>
       </c>
       <c r="AJ172">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AK172">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="AL172">
         <v>0</v>
@@ -28520,16 +28520,16 @@
         <v>4</v>
       </c>
       <c r="R173">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="S173">
         <v>1.25</v>
       </c>
       <c r="T173">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U173">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="V173">
         <v>1.57</v>
@@ -28541,7 +28541,7 @@
         <v>1.03</v>
       </c>
       <c r="Y173">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z173">
         <v>4.5</v>
@@ -28550,19 +28550,19 @@
         <v>1.53</v>
       </c>
       <c r="AB173">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AC173">
         <v>2.38</v>
       </c>
       <c r="AD173">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AE173">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AF173">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AG173">
         <v>2.3</v>
@@ -28578,10 +28578,10 @@
         </is>
       </c>
       <c r="AJ173">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK173">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AL173">
         <v>0</v>
@@ -29163,40 +29163,40 @@
         <v>1.66</v>
       </c>
       <c r="O177">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="P177">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="Q177">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="R177">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="S177">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T177">
         <v>3.4</v>
       </c>
       <c r="U177">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="V177">
         <v>1.52</v>
       </c>
       <c r="W177">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X177">
         <v>1.03</v>
       </c>
       <c r="Y177">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z177">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="AA177">
         <v>1.57</v>
@@ -29205,13 +29205,13 @@
         <v>2.35</v>
       </c>
       <c r="AC177">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="AD177">
         <v>1.53</v>
       </c>
       <c r="AE177">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF177">
         <v>1.62</v>
@@ -29329,7 +29329,7 @@
         <v>3.3</v>
       </c>
       <c r="P178">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="Q178">
         <v>2.97</v>
@@ -29338,16 +29338,16 @@
         <v>2.4</v>
       </c>
       <c r="S178">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T178">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="U178">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="V178">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W178">
         <v>1.14</v>
@@ -29362,25 +29362,25 @@
         <v>4</v>
       </c>
       <c r="AA178">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AB178">
         <v>2.25</v>
       </c>
       <c r="AC178">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AD178">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AE178">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AF178">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AG178">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AH178" t="inlineStr">
         <is>
@@ -29492,25 +29492,25 @@
         <v>3.9</v>
       </c>
       <c r="P179">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="Q179">
         <v>5.5</v>
       </c>
       <c r="R179">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="S179">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T179">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="U179">
         <v>2.63</v>
       </c>
       <c r="V179">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W179">
         <v>1.08</v>
@@ -29525,16 +29525,16 @@
         <v>3.5</v>
       </c>
       <c r="AA179">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AB179">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="AC179">
         <v>2.75</v>
       </c>
       <c r="AD179">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AE179">
         <v>1.15</v>
@@ -29658,7 +29658,7 @@
         <v>1.93</v>
       </c>
       <c r="Q180">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="R180">
         <v>2.3</v>
@@ -29673,7 +29673,7 @@
         <v>2.5</v>
       </c>
       <c r="V180">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W180">
         <v>1.07</v>
@@ -29815,13 +29815,13 @@
         <v>1.66</v>
       </c>
       <c r="O181">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="P181">
-        <v>5.2</v>
+        <v>5.05</v>
       </c>
       <c r="Q181">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R181">
         <v>2.2</v>
@@ -29830,7 +29830,7 @@
         <v>1.36</v>
       </c>
       <c r="T181">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="U181">
         <v>2.7</v>
@@ -29845,7 +29845,7 @@
         <v>1.01</v>
       </c>
       <c r="Y181">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="Z181">
         <v>3.45</v>
@@ -29854,16 +29854,16 @@
         <v>1.91</v>
       </c>
       <c r="AB181">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AC181">
         <v>3.08</v>
       </c>
       <c r="AD181">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE181">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF181">
         <v>1.83</v>
@@ -29882,10 +29882,10 @@
         </is>
       </c>
       <c r="AJ181">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK181">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="AL181">
         <v>0</v>
@@ -30464,13 +30464,13 @@
         </is>
       </c>
       <c r="N185">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="O185">
         <v>2.9</v>
       </c>
       <c r="P185">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="Q185">
         <v>3.25</v>
@@ -30482,16 +30482,16 @@
         <v>1.45</v>
       </c>
       <c r="T185">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="U185">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="V185">
         <v>1.29</v>
       </c>
       <c r="W185">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X185">
         <v>1.1</v>
@@ -30503,13 +30503,13 @@
         <v>2.54</v>
       </c>
       <c r="AA185">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="AB185">
         <v>1.53</v>
       </c>
       <c r="AC185">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="AD185">
         <v>1.16</v>
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Batman Petrolspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G186">
@@ -30627,64 +30627,64 @@
         </is>
       </c>
       <c r="N186">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O186">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P186">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q186">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R186">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S186">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T186">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U186">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V186">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W186">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X186">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y186">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z186">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA186">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB186">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC186">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD186">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE186">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF186">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG186">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH186" t="inlineStr">
         <is>
@@ -30697,10 +30697,10 @@
         </is>
       </c>
       <c r="AJ186">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AK186">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL186">
         <v>0</v>
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Batman Petrolspor</t>
         </is>
       </c>
       <c r="G187">
@@ -30790,64 +30790,64 @@
         </is>
       </c>
       <c r="N187">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O187">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P187">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q187">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R187">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S187">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T187">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="U187">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V187">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W187">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X187">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y187">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z187">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA187">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB187">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC187">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD187">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE187">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF187">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG187">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH187" t="inlineStr">
         <is>
@@ -30860,10 +30860,10 @@
         </is>
       </c>
       <c r="AJ187">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AK187">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AL187">
         <v>0</v>
@@ -30953,13 +30953,13 @@
         </is>
       </c>
       <c r="N188">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="O188">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P188">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="Q188">
         <v>3.2</v>
@@ -31007,10 +31007,10 @@
         <v>1.11</v>
       </c>
       <c r="AF188">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG188">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="AH188" t="inlineStr">
         <is>
@@ -31026,7 +31026,7 @@
         <v>1.28</v>
       </c>
       <c r="AK188">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL188">
         <v>0</v>
@@ -31119,34 +31119,34 @@
         <v>1.43</v>
       </c>
       <c r="O189">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="P189">
-        <v>6.5</v>
+        <v>1.5</v>
       </c>
       <c r="Q189">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="R189">
-        <v>2.98</v>
+        <v>2.63</v>
       </c>
       <c r="S189">
         <v>1.23</v>
       </c>
       <c r="T189">
-        <v>3.94</v>
+        <v>4.1</v>
       </c>
       <c r="U189">
-        <v>2.08</v>
+        <v>1.91</v>
       </c>
       <c r="V189">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="W189">
         <v>1.15</v>
       </c>
       <c r="X189">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y189">
         <v>1.11</v>
@@ -31155,13 +31155,13 @@
         <v>6.25</v>
       </c>
       <c r="AA189">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AB189">
         <v>2.9</v>
       </c>
       <c r="AC189">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="AD189">
         <v>1.8</v>
@@ -31170,10 +31170,10 @@
         <v>1.33</v>
       </c>
       <c r="AF189">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AG189">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AH189" t="inlineStr">
         <is>
@@ -31189,7 +31189,7 @@
         <v>1.08</v>
       </c>
       <c r="AK189">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AL189">
         <v>0</v>
@@ -31285,7 +31285,7 @@
         <v>3.7</v>
       </c>
       <c r="P190">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="Q190">
         <v>4.4</v>
@@ -31309,7 +31309,7 @@
         <v>1.09</v>
       </c>
       <c r="X190">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y190">
         <v>1.25</v>
@@ -31318,7 +31318,7 @@
         <v>3.5</v>
       </c>
       <c r="AA190">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AB190">
         <v>1.85</v>
@@ -31330,10 +31330,10 @@
         <v>1.35</v>
       </c>
       <c r="AE190">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF190">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AG190">
         <v>1.94</v>
@@ -31442,19 +31442,19 @@
         </is>
       </c>
       <c r="N191">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="O191">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="P191">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="Q191">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="R191">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="S191">
         <v>1.3</v>
@@ -31469,7 +31469,7 @@
         <v>1.53</v>
       </c>
       <c r="W191">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X191">
         <v>1.01</v>
@@ -31493,7 +31493,7 @@
         <v>1.48</v>
       </c>
       <c r="AE191">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF191">
         <v>1.73</v>
@@ -31605,13 +31605,13 @@
         </is>
       </c>
       <c r="N192">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="O192">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P192">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="Q192">
         <v>2.88</v>
@@ -31623,13 +31623,13 @@
         <v>1.4</v>
       </c>
       <c r="T192">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="U192">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="V192">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W192">
         <v>1.04</v>
@@ -31638,16 +31638,16 @@
         <v>1.03</v>
       </c>
       <c r="Y192">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z192">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="AA192">
-        <v>2.03</v>
+        <v>1.92</v>
       </c>
       <c r="AB192">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AC192">
         <v>3.18</v>
@@ -31662,7 +31662,7 @@
         <v>1.75</v>
       </c>
       <c r="AG192">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AH192" t="inlineStr">
         <is>
@@ -31675,10 +31675,10 @@
         </is>
       </c>
       <c r="AJ192">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="AK192">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AL192">
         <v>0</v>
@@ -31768,28 +31768,28 @@
         </is>
       </c>
       <c r="N193">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="O193">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P193">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="Q193">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="R193">
         <v>2.15</v>
       </c>
       <c r="S193">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="T193">
         <v>2.73</v>
       </c>
       <c r="U193">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="V193">
         <v>1.38</v>
@@ -31810,7 +31810,7 @@
         <v>2.09</v>
       </c>
       <c r="AB193">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AC193">
         <v>3.6</v>
@@ -31841,7 +31841,7 @@
         <v>1.3</v>
       </c>
       <c r="AK193">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AL193">
         <v>0</v>
@@ -31952,7 +31952,7 @@
         <v>2.44</v>
       </c>
       <c r="U194">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="V194">
         <v>1.3</v>
@@ -31970,10 +31970,10 @@
         <v>2.74</v>
       </c>
       <c r="AA194">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="AB194">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AC194">
         <v>4</v>
@@ -31985,10 +31985,10 @@
         <v>1.01</v>
       </c>
       <c r="AF194">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AG194">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AH194" t="inlineStr">
         <is>
@@ -33072,13 +33072,13 @@
         </is>
       </c>
       <c r="N201">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="O201">
-        <v>3.34</v>
+        <v>3.38</v>
       </c>
       <c r="P201">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="Q201">
         <v>0</v>
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G202">
@@ -33235,80 +33235,80 @@
         </is>
       </c>
       <c r="N202">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O202">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="P202">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="Q202">
-        <v>2.51</v>
+        <v>2.48</v>
       </c>
       <c r="R202">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="S202">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T202">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="U202">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="V202">
+        <v>1.24</v>
+      </c>
+      <c r="W202">
+        <v>1.05</v>
+      </c>
+      <c r="X202">
+        <v>1.05</v>
+      </c>
+      <c r="Y202">
+        <v>1.37</v>
+      </c>
+      <c r="Z202">
+        <v>2.56</v>
+      </c>
+      <c r="AA202">
+        <v>2.4</v>
+      </c>
+      <c r="AB202">
+        <v>1.52</v>
+      </c>
+      <c r="AC202">
+        <v>4.45</v>
+      </c>
+      <c r="AD202">
+        <v>1.14</v>
+      </c>
+      <c r="AE202">
+        <v>1.01</v>
+      </c>
+      <c r="AF202">
+        <v>2.01</v>
+      </c>
+      <c r="AG202">
+        <v>1.66</v>
+      </c>
+      <c r="AH202" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI202" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ202">
         <v>1.3</v>
       </c>
-      <c r="W202">
-        <v>1.03</v>
-      </c>
-      <c r="X202">
-        <v>1.03</v>
-      </c>
-      <c r="Y202">
-        <v>1.33</v>
-      </c>
-      <c r="Z202">
-        <v>2.95</v>
-      </c>
-      <c r="AA202">
-        <v>2.1</v>
-      </c>
-      <c r="AB202">
+      <c r="AK202">
         <v>1.66</v>
-      </c>
-      <c r="AC202">
-        <v>3.68</v>
-      </c>
-      <c r="AD202">
-        <v>1.2</v>
-      </c>
-      <c r="AE202">
-        <v>1.04</v>
-      </c>
-      <c r="AF202">
-        <v>1.88</v>
-      </c>
-      <c r="AG202">
-        <v>1.81</v>
-      </c>
-      <c r="AH202" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI202" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ202">
-        <v>1.25</v>
-      </c>
-      <c r="AK202">
-        <v>1.73</v>
       </c>
       <c r="AL202">
         <v>0</v>
@@ -33366,12 +33366,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G203">
@@ -33398,64 +33398,64 @@
         </is>
       </c>
       <c r="N203">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O203">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P203">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q203">
-        <v>2.35</v>
+        <v>2.87</v>
       </c>
       <c r="R203">
-        <v>2.14</v>
+        <v>1.86</v>
       </c>
       <c r="S203">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T203">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="U203">
         <v>3.2</v>
       </c>
       <c r="V203">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="W203">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X203">
+        <v>1.06</v>
+      </c>
+      <c r="Y203">
+        <v>1.33</v>
+      </c>
+      <c r="Z203">
+        <v>2.95</v>
+      </c>
+      <c r="AA203">
+        <v>2.27</v>
+      </c>
+      <c r="AB203">
+        <v>1.66</v>
+      </c>
+      <c r="AC203">
+        <v>4.05</v>
+      </c>
+      <c r="AD203">
+        <v>1.16</v>
+      </c>
+      <c r="AE203">
         <v>1.02</v>
       </c>
-      <c r="Y203">
-        <v>1.34</v>
-      </c>
-      <c r="Z203">
-        <v>2.88</v>
-      </c>
-      <c r="AA203">
-        <v>2.1</v>
-      </c>
-      <c r="AB203">
-        <v>1.63</v>
-      </c>
-      <c r="AC203">
-        <v>3.75</v>
-      </c>
-      <c r="AD203">
-        <v>1.21</v>
-      </c>
-      <c r="AE203">
-        <v>1.01</v>
-      </c>
       <c r="AF203">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AG203">
-        <v>1.64</v>
+        <v>1.81</v>
       </c>
       <c r="AH203" t="inlineStr">
         <is>
@@ -33468,10 +33468,10 @@
         </is>
       </c>
       <c r="AJ203">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK203">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AL203">
         <v>0</v>
@@ -33564,10 +33564,10 @@
         <v>2.27</v>
       </c>
       <c r="O204">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P204">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="Q204">
         <v>3</v>
@@ -33591,7 +33591,7 @@
         <v>1.07</v>
       </c>
       <c r="X204">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y204">
         <v>1.28</v>
@@ -33609,7 +33609,7 @@
         <v>3.3</v>
       </c>
       <c r="AD204">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE204">
         <v>1.12</v>
@@ -33887,64 +33887,64 @@
         </is>
       </c>
       <c r="N206">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O206">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P206">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q206">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="R206">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S206">
         <v>1.35</v>
       </c>
       <c r="T206">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="U206">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="V206">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W206">
         <v>1.07</v>
       </c>
       <c r="X206">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y206">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z206">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="AA206">
         <v>1.83</v>
       </c>
       <c r="AB206">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AC206">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="AD206">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AE206">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF206">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AG206">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AH206" t="inlineStr">
         <is>
@@ -33957,10 +33957,10 @@
         </is>
       </c>
       <c r="AJ206">
-        <v>1.91</v>
+        <v>1.25</v>
       </c>
       <c r="AK206">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AL206">
         <v>0</v>
@@ -34050,37 +34050,37 @@
         </is>
       </c>
       <c r="N207">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O207">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P207">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q207">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="R207">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="S207">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T207">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="U207">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="V207">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="W207">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X207">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y207">
         <v>1.2</v>
@@ -34089,25 +34089,25 @@
         <v>4.2</v>
       </c>
       <c r="AA207">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AB207">
-        <v>2.37</v>
+        <v>2.41</v>
       </c>
       <c r="AC207">
-        <v>2.41</v>
+        <v>2.21</v>
       </c>
       <c r="AD207">
-        <v>1.45</v>
+        <v>1.59</v>
       </c>
       <c r="AE207">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AF207">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AG207">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="AH207" t="inlineStr">
         <is>
@@ -34120,10 +34120,10 @@
         </is>
       </c>
       <c r="AJ207">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AK207">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -34376,13 +34376,13 @@
         </is>
       </c>
       <c r="N209">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="O209">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P209">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="Q209">
         <v>2.3</v>
@@ -34391,10 +34391,10 @@
         <v>2.25</v>
       </c>
       <c r="S209">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T209">
-        <v>3.22</v>
+        <v>3.28</v>
       </c>
       <c r="U209">
         <v>2.5</v>
@@ -34403,7 +34403,7 @@
         <v>1.44</v>
       </c>
       <c r="W209">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X209">
         <v>1.03</v>
@@ -34412,7 +34412,7 @@
         <v>1.24</v>
       </c>
       <c r="Z209">
-        <v>3.81</v>
+        <v>3.82</v>
       </c>
       <c r="AA209">
         <v>1.76</v>
@@ -34430,10 +34430,10 @@
         <v>1.12</v>
       </c>
       <c r="AF209">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AG209">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AH209" t="inlineStr">
         <is>
@@ -34449,7 +34449,7 @@
         <v>1.22</v>
       </c>
       <c r="AK209">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="AL209">
         <v>0</v>
@@ -34865,28 +34865,28 @@
         </is>
       </c>
       <c r="N212">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="O212">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P212">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="Q212">
         <v>2.8</v>
       </c>
       <c r="R212">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S212">
         <v>1.44</v>
       </c>
       <c r="T212">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="U212">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="V212">
         <v>1.32</v>
@@ -34895,22 +34895,22 @@
         <v>1.03</v>
       </c>
       <c r="X212">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y212">
         <v>1.38</v>
       </c>
       <c r="Z212">
-        <v>2.88</v>
+        <v>3.01</v>
       </c>
       <c r="AA212">
         <v>2.2</v>
       </c>
       <c r="AB212">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AC212">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AD212">
         <v>1.21</v>
@@ -34919,10 +34919,10 @@
         <v>1.04</v>
       </c>
       <c r="AF212">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AG212">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AH212" t="inlineStr">
         <is>
@@ -34938,7 +34938,7 @@
         <v>1.33</v>
       </c>
       <c r="AK212">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AL212">
         <v>0</v>
@@ -35037,46 +35037,46 @@
         <v>0</v>
       </c>
       <c r="Q213">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="R213">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="S213">
         <v>1.42</v>
       </c>
       <c r="T213">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="U213">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="V213">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W213">
+        <v>1.04</v>
+      </c>
+      <c r="X213">
         <v>1.02</v>
       </c>
-      <c r="X213">
-        <v>1.08</v>
-      </c>
       <c r="Y213">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="Z213">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="AA213">
         <v>2.11</v>
       </c>
       <c r="AB213">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AC213">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AD213">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE213">
         <v>1.03</v>
@@ -35085,7 +35085,7 @@
         <v>1.83</v>
       </c>
       <c r="AG213">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH213" t="inlineStr">
         <is>
@@ -35101,7 +35101,7 @@
         <v>1.31</v>
       </c>
       <c r="AK213">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AL213">
         <v>0</v>
@@ -35360,7 +35360,7 @@
         <v>3.2</v>
       </c>
       <c r="P215">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="Q215">
         <v>3.6</v>
@@ -35384,7 +35384,7 @@
         <v>1.05</v>
       </c>
       <c r="X215">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y215">
         <v>1.28</v>
@@ -35396,13 +35396,13 @@
         <v>2.06</v>
       </c>
       <c r="AB215">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AC215">
         <v>3.6</v>
       </c>
       <c r="AD215">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE215">
         <v>1.05</v>
@@ -35424,10 +35424,10 @@
         </is>
       </c>
       <c r="AJ215">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AK215">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AL215">
         <v>0</v>
@@ -35517,7 +35517,7 @@
         </is>
       </c>
       <c r="N216">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O216">
         <v>5.5</v>
@@ -35526,16 +35526,16 @@
         <v>1.33</v>
       </c>
       <c r="Q216">
-        <v>5.51</v>
+        <v>7.1</v>
       </c>
       <c r="R216">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="S216">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="T216">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="U216">
         <v>2.1</v>
@@ -35544,7 +35544,7 @@
         <v>1.67</v>
       </c>
       <c r="W216">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X216">
         <v>1.02</v>
@@ -35680,64 +35680,64 @@
         </is>
       </c>
       <c r="N217">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="O217">
-        <v>7.6</v>
+        <v>6.45</v>
       </c>
       <c r="P217">
         <v>12</v>
       </c>
       <c r="Q217">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="R217">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="S217">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="T217">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U217">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="V217">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="W217">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X217">
         <v>1.03</v>
       </c>
       <c r="Y217">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z217">
         <v>4.6</v>
       </c>
       <c r="AA217">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB217">
         <v>2.3</v>
       </c>
       <c r="AC217">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AD217">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AE217">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF217">
         <v>2.25</v>
       </c>
       <c r="AG217">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AH217" t="inlineStr">
         <is>
@@ -35750,10 +35750,10 @@
         </is>
       </c>
       <c r="AJ217">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AK217">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AL217">
         <v>0</v>
@@ -35843,13 +35843,13 @@
         </is>
       </c>
       <c r="N218">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="O218">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P218">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="Q218">
         <v>0</v>
@@ -36027,10 +36027,10 @@
         <v>3.04</v>
       </c>
       <c r="U219">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="V219">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W219">
         <v>1.08</v>
@@ -36057,7 +36057,7 @@
         <v>1.33</v>
       </c>
       <c r="AE219">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF219">
         <v>1.68</v>
@@ -36175,7 +36175,7 @@
         <v>3</v>
       </c>
       <c r="P220">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q220">
         <v>3.75</v>
@@ -36196,7 +36196,7 @@
         <v>1.3</v>
       </c>
       <c r="W220">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X220">
         <v>1.07</v>
@@ -36332,13 +36332,13 @@
         </is>
       </c>
       <c r="N221">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="O221">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="P221">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="Q221">
         <v>0</v>
@@ -36371,10 +36371,10 @@
         <v>0</v>
       </c>
       <c r="AA221">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AB221">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AC221">
         <v>0</v>
@@ -36658,25 +36658,25 @@
         </is>
       </c>
       <c r="N223">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="O223">
         <v>3</v>
       </c>
       <c r="P223">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="Q223">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="R223">
         <v>2.12</v>
       </c>
       <c r="S223">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="T223">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="U223">
         <v>3.1</v>
@@ -36685,7 +36685,7 @@
         <v>1.31</v>
       </c>
       <c r="W223">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X223">
         <v>1.09</v>
@@ -36694,7 +36694,7 @@
         <v>1.32</v>
       </c>
       <c r="Z223">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="AA223">
         <v>2.17</v>
@@ -36703,19 +36703,19 @@
         <v>1.65</v>
       </c>
       <c r="AC223">
-        <v>3.68</v>
+        <v>3.58</v>
       </c>
       <c r="AD223">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE223">
         <v>1.08</v>
       </c>
       <c r="AF223">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AG223">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AH223" t="inlineStr">
         <is>
@@ -36728,10 +36728,10 @@
         </is>
       </c>
       <c r="AJ223">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK223">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AL223">
         <v>0</v>
@@ -37310,25 +37310,25 @@
         </is>
       </c>
       <c r="N227">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O227">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="P227">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q227">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="R227">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="S227">
         <v>1.53</v>
       </c>
       <c r="T227">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="U227">
         <v>3.75</v>
@@ -37340,34 +37340,34 @@
         <v>1.03</v>
       </c>
       <c r="X227">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y227">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="Z227">
-        <v>2.46</v>
+        <v>2.27</v>
       </c>
       <c r="AA227">
-        <v>2.38</v>
+        <v>2.53</v>
       </c>
       <c r="AB227">
         <v>1.5</v>
       </c>
       <c r="AC227">
-        <v>5.4</v>
+        <v>5.75</v>
       </c>
       <c r="AD227">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AE227">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF227">
         <v>2.04</v>
       </c>
       <c r="AG227">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AH227" t="inlineStr">
         <is>
@@ -37380,10 +37380,10 @@
         </is>
       </c>
       <c r="AJ227">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK227">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AL227">
         <v>0</v>
@@ -37473,19 +37473,19 @@
         </is>
       </c>
       <c r="N228">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O228">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="P228">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q228">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="R228">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="S228">
         <v>1.44</v>
@@ -37494,10 +37494,10 @@
         <v>2.63</v>
       </c>
       <c r="U228">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="V228">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W228">
         <v>1.05</v>
@@ -37506,10 +37506,10 @@
         <v>1.09</v>
       </c>
       <c r="Y228">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="Z228">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="AA228">
         <v>2.45</v>
@@ -37518,16 +37518,16 @@
         <v>1.47</v>
       </c>
       <c r="AC228">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AD228">
         <v>1.15</v>
       </c>
       <c r="AE228">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF228">
-        <v>2.04</v>
+        <v>1.86</v>
       </c>
       <c r="AG228">
         <v>1.64</v>
@@ -37543,7 +37543,7 @@
         </is>
       </c>
       <c r="AJ228">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK228">
         <v>1.57</v>
@@ -37645,13 +37645,13 @@
         <v>0</v>
       </c>
       <c r="Q229">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="R229">
         <v>1.91</v>
       </c>
       <c r="S229">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="T229">
         <v>2.36</v>
@@ -37672,22 +37672,22 @@
         <v>1.48</v>
       </c>
       <c r="Z229">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="AA229">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="AB229">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AC229">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AD229">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AE229">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF229">
         <v>2.14</v>
@@ -37709,7 +37709,7 @@
         <v>1.17</v>
       </c>
       <c r="AK229">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AL229">
         <v>0</v>
@@ -37808,55 +37808,55 @@
         <v>4.07</v>
       </c>
       <c r="Q230">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="R230">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="S230">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="T230">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="U230">
-        <v>2.06</v>
+        <v>2.49</v>
       </c>
       <c r="V230">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W230">
         <v>1.1</v>
       </c>
       <c r="X230">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y230">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z230">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AA230">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB230">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AC230">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AD230">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE230">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF230">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG230">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AH230" t="inlineStr">
         <is>
@@ -37869,10 +37869,10 @@
         </is>
       </c>
       <c r="AJ230">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="AK230">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AL230">
         <v>0</v>
@@ -38125,10 +38125,10 @@
         </is>
       </c>
       <c r="N232">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="O232">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P232">
         <v>2.7</v>
@@ -38155,7 +38155,7 @@
         <v>1.08</v>
       </c>
       <c r="X232">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y232">
         <v>1.24</v>
@@ -38167,7 +38167,7 @@
         <v>1.9</v>
       </c>
       <c r="AB232">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC232">
         <v>2.97</v>
@@ -38288,7 +38288,7 @@
         </is>
       </c>
       <c r="N233">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="O233">
         <v>3.9</v>
@@ -38300,52 +38300,52 @@
         <v>2</v>
       </c>
       <c r="R233">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S233">
         <v>1.22</v>
       </c>
       <c r="T233">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="U233">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="V233">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="W233">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X233">
         <v>1.02</v>
       </c>
       <c r="Y233">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z233">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AA233">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AB233">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AC233">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD233">
         <v>1.65</v>
       </c>
       <c r="AE233">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF233">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="AG233">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AH233" t="inlineStr">
         <is>
@@ -38361,7 +38361,7 @@
         <v>1.2</v>
       </c>
       <c r="AK233">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="AL233">
         <v>0</v>
@@ -38460,10 +38460,10 @@
         <v>0</v>
       </c>
       <c r="Q234">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="R234">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="S234">
         <v>1.35</v>
@@ -38472,16 +38472,16 @@
         <v>2.65</v>
       </c>
       <c r="U234">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V234">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W234">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X234">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y234">
         <v>1.29</v>
@@ -38490,19 +38490,19 @@
         <v>3.05</v>
       </c>
       <c r="AA234">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AB234">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AC234">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="AD234">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE234">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF234">
         <v>1.8</v>
@@ -38521,10 +38521,10 @@
         </is>
       </c>
       <c r="AJ234">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AK234">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AL234">
         <v>0</v>
@@ -38777,13 +38777,13 @@
         </is>
       </c>
       <c r="N236">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="O236">
-        <v>3.84</v>
+        <v>3.7</v>
       </c>
       <c r="P236">
-        <v>4.9</v>
+        <v>7.11</v>
       </c>
       <c r="Q236">
         <v>2.08</v>
@@ -38795,7 +38795,7 @@
         <v>1.38</v>
       </c>
       <c r="T236">
-        <v>2.93</v>
+        <v>2.7</v>
       </c>
       <c r="U236">
         <v>2.78</v>
@@ -38822,7 +38822,7 @@
         <v>1.8</v>
       </c>
       <c r="AC236">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AD236">
         <v>1.29</v>
@@ -38970,25 +38970,25 @@
         <v>1.03</v>
       </c>
       <c r="X237">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y237">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z237">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AA237">
         <v>2.04</v>
       </c>
       <c r="AB237">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="AC237">
         <v>3.5</v>
       </c>
       <c r="AD237">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AE237">
         <v>1.07</v>
@@ -38997,7 +38997,7 @@
         <v>1.83</v>
       </c>
       <c r="AG237">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="AH237" t="inlineStr">
         <is>

--- a/jogos_2026-08-23.xlsx
+++ b/jogos_2026-08-23.xlsx
@@ -635,31 +635,31 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.71</v>
+        <v>1.9</v>
       </c>
       <c r="O2">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="P2">
-        <v>4.25</v>
+        <v>3.35</v>
       </c>
       <c r="Q2">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="R2">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="S2">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="T2">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U2">
-        <v>2.85</v>
+        <v>2.45</v>
       </c>
       <c r="V2">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W2">
         <v>1.05</v>
@@ -668,31 +668,31 @@
         <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z2">
-        <v>3.28</v>
+        <v>3.38</v>
       </c>
       <c r="AA2">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AB2">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AC2">
-        <v>3.25</v>
+        <v>3.31</v>
       </c>
       <c r="AD2">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AE2">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF2">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AG2">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         <v>1.21</v>
       </c>
       <c r="AK2">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>4.53</v>
+        <v>2.03</v>
       </c>
       <c r="O4">
-        <v>3.59</v>
+        <v>3.48</v>
       </c>
       <c r="P4">
+        <v>2.95</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
         <v>1.53</v>
       </c>
-      <c r="Q4">
-        <v>5.05</v>
-      </c>
-      <c r="R4">
-        <v>2.28</v>
-      </c>
-      <c r="S4">
-        <v>1.29</v>
-      </c>
-      <c r="T4">
-        <v>3.04</v>
-      </c>
-      <c r="U4">
-        <v>2.5</v>
-      </c>
-      <c r="V4">
-        <v>1.5</v>
-      </c>
-      <c r="W4">
-        <v>1.08</v>
-      </c>
-      <c r="X4">
-        <v>1</v>
-      </c>
-      <c r="Y4">
-        <v>1.19</v>
-      </c>
-      <c r="Z4">
-        <v>3.82</v>
-      </c>
-      <c r="AA4">
-        <v>1.58</v>
-      </c>
       <c r="AB4">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="AC4">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AD4">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE4">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK4">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.03</v>
+        <v>4.53</v>
       </c>
       <c r="O5">
-        <v>3.48</v>
+        <v>3.59</v>
       </c>
       <c r="P5">
-        <v>2.95</v>
+        <v>1.53</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AA5">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AB5">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="O122">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="P122">
+        <v>3.78</v>
+      </c>
+      <c r="Q122">
+        <v>2.15</v>
+      </c>
+      <c r="R122">
         <v>2.25</v>
       </c>
-      <c r="Q122">
-        <v>3.4</v>
-      </c>
-      <c r="R122">
-        <v>2.15</v>
-      </c>
       <c r="S122">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="T122">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="U122">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="V122">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W122">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X122">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y122">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="Z122">
-        <v>2.9</v>
+        <v>3.85</v>
       </c>
       <c r="AA122">
+        <v>1.67</v>
+      </c>
+      <c r="AB122">
         <v>2.1</v>
       </c>
-      <c r="AB122">
-        <v>1.7</v>
-      </c>
       <c r="AC122">
-        <v>3.35</v>
+        <v>2.7</v>
       </c>
       <c r="AD122">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="AE122">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AF122">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AG122">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AK122">
-        <v>1.36</v>
+        <v>1.98</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="G123">
@@ -20358,64 +20358,64 @@
         </is>
       </c>
       <c r="N123">
+        <v>3.1</v>
+      </c>
+      <c r="O123">
+        <v>3.3</v>
+      </c>
+      <c r="P123">
+        <v>2.25</v>
+      </c>
+      <c r="Q123">
+        <v>3.4</v>
+      </c>
+      <c r="R123">
+        <v>2.15</v>
+      </c>
+      <c r="S123">
+        <v>1.4</v>
+      </c>
+      <c r="T123">
+        <v>2.75</v>
+      </c>
+      <c r="U123">
+        <v>2.8</v>
+      </c>
+      <c r="V123">
+        <v>1.4</v>
+      </c>
+      <c r="W123">
+        <v>1.06</v>
+      </c>
+      <c r="X123">
+        <v>1</v>
+      </c>
+      <c r="Y123">
+        <v>1.34</v>
+      </c>
+      <c r="Z123">
+        <v>2.9</v>
+      </c>
+      <c r="AA123">
+        <v>2.1</v>
+      </c>
+      <c r="AB123">
         <v>1.7</v>
       </c>
-      <c r="O123">
-        <v>3.6</v>
-      </c>
-      <c r="P123">
-        <v>3.78</v>
-      </c>
-      <c r="Q123">
-        <v>2.15</v>
-      </c>
-      <c r="R123">
-        <v>2.25</v>
-      </c>
-      <c r="S123">
-        <v>1.3</v>
-      </c>
-      <c r="T123">
-        <v>3.25</v>
-      </c>
-      <c r="U123">
-        <v>2.5</v>
-      </c>
-      <c r="V123">
-        <v>1.5</v>
-      </c>
-      <c r="W123">
-        <v>1.12</v>
-      </c>
-      <c r="X123">
-        <v>1.04</v>
-      </c>
-      <c r="Y123">
-        <v>1.21</v>
-      </c>
-      <c r="Z123">
-        <v>3.85</v>
-      </c>
-      <c r="AA123">
-        <v>1.67</v>
-      </c>
-      <c r="AB123">
-        <v>2.1</v>
-      </c>
       <c r="AC123">
-        <v>2.7</v>
+        <v>3.35</v>
       </c>
       <c r="AD123">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="AE123">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AF123">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AG123">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AK123">
-        <v>1.98</v>
+        <v>1.36</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -29975,19 +29975,19 @@
         </is>
       </c>
       <c r="N182">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="O182">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="P182">
-        <v>3.25</v>
+        <v>3.17</v>
       </c>
       <c r="Q182">
         <v>2.88</v>
       </c>
       <c r="R182">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="S182">
         <v>1.55</v>
@@ -29996,43 +29996,43 @@
         <v>2.28</v>
       </c>
       <c r="U182">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="V182">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W182">
         <v>1.01</v>
       </c>
       <c r="X182">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y182">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="Z182">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="AA182">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="AB182">
         <v>1.53</v>
       </c>
       <c r="AC182">
-        <v>4.83</v>
+        <v>4.88</v>
       </c>
       <c r="AD182">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AE182">
         <v>1.01</v>
       </c>
       <c r="AF182">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AG182">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AH182" t="inlineStr">
         <is>
@@ -30138,16 +30138,16 @@
         </is>
       </c>
       <c r="N183">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="O183">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="P183">
-        <v>3.2</v>
+        <v>3.37</v>
       </c>
       <c r="Q183">
-        <v>3.3</v>
+        <v>3.39</v>
       </c>
       <c r="R183">
         <v>1.83</v>
@@ -30159,7 +30159,7 @@
         <v>2.04</v>
       </c>
       <c r="U183">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="V183">
         <v>1.2</v>
@@ -30171,7 +30171,7 @@
         <v>1.13</v>
       </c>
       <c r="Y183">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Z183">
         <v>2.11</v>
@@ -30307,22 +30307,22 @@
         <v>2.7</v>
       </c>
       <c r="P184">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Q184">
-        <v>3.3</v>
+        <v>3.62</v>
       </c>
       <c r="R184">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="S184">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="T184">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="U184">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="V184">
         <v>1.16</v>
@@ -30331,19 +30331,19 @@
         <v>1.03</v>
       </c>
       <c r="X184">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Y184">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="Z184">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AA184">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="AB184">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AC184">
         <v>6.1</v>
@@ -30371,7 +30371,7 @@
         </is>
       </c>
       <c r="AJ184">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AK184">
         <v>1.44</v>
@@ -32604,7 +32604,7 @@
         <v>2.89</v>
       </c>
       <c r="U198">
-        <v>2.54</v>
+        <v>2.65</v>
       </c>
       <c r="V198">
         <v>1.4</v>
@@ -32637,10 +32637,10 @@
         <v>1.08</v>
       </c>
       <c r="AF198">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AG198">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AH198" t="inlineStr">
         <is>
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G199">
@@ -32746,64 +32746,64 @@
         </is>
       </c>
       <c r="N199">
-        <v>1.58</v>
+        <v>2.45</v>
       </c>
       <c r="O199">
-        <v>4.07</v>
+        <v>3.3</v>
       </c>
       <c r="P199">
-        <v>6.22</v>
+        <v>2.9</v>
       </c>
       <c r="Q199">
-        <v>2.16</v>
+        <v>2.82</v>
       </c>
       <c r="R199">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S199">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T199">
-        <v>3</v>
+        <v>2.69</v>
       </c>
       <c r="U199">
         <v>2.81</v>
       </c>
       <c r="V199">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W199">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X199">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y199">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z199">
-        <v>3.38</v>
+        <v>3.12</v>
       </c>
       <c r="AA199">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AB199">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AC199">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="AD199">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AE199">
         <v>1.07</v>
       </c>
       <c r="AF199">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="AG199">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AH199" t="inlineStr">
         <is>
@@ -32819,7 +32819,7 @@
         <v>1.25</v>
       </c>
       <c r="AK199">
-        <v>2.15</v>
+        <v>1.49</v>
       </c>
       <c r="AL199">
         <v>0</v>
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G200">
@@ -32909,64 +32909,64 @@
         </is>
       </c>
       <c r="N200">
-        <v>2.49</v>
+        <v>1.58</v>
       </c>
       <c r="O200">
-        <v>3.3</v>
+        <v>4.07</v>
       </c>
       <c r="P200">
-        <v>2.91</v>
+        <v>6.22</v>
       </c>
       <c r="Q200">
-        <v>2.82</v>
+        <v>2.1</v>
       </c>
       <c r="R200">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S200">
         <v>1.33</v>
       </c>
       <c r="T200">
-        <v>2.69</v>
+        <v>3</v>
       </c>
       <c r="U200">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="V200">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W200">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X200">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y200">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z200">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="AA200">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AB200">
         <v>1.85</v>
       </c>
       <c r="AC200">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="AD200">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AE200">
         <v>1.07</v>
       </c>
       <c r="AF200">
-        <v>1.72</v>
+        <v>1.86</v>
       </c>
       <c r="AG200">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AH200" t="inlineStr">
         <is>
@@ -32982,7 +32982,7 @@
         <v>1.25</v>
       </c>
       <c r="AK200">
-        <v>1.49</v>
+        <v>2.15</v>
       </c>
       <c r="AL200">
         <v>0</v>
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G206">
@@ -33887,64 +33887,64 @@
         </is>
       </c>
       <c r="N206">
+        <v>1.48</v>
+      </c>
+      <c r="O206">
+        <v>4.15</v>
+      </c>
+      <c r="P206">
+        <v>4.8</v>
+      </c>
+      <c r="Q206">
+        <v>1.95</v>
+      </c>
+      <c r="R206">
+        <v>2.5</v>
+      </c>
+      <c r="S206">
+        <v>1.28</v>
+      </c>
+      <c r="T206">
+        <v>3.3</v>
+      </c>
+      <c r="U206">
+        <v>2.18</v>
+      </c>
+      <c r="V206">
+        <v>1.6</v>
+      </c>
+      <c r="W206">
+        <v>1.13</v>
+      </c>
+      <c r="X206">
+        <v>1.02</v>
+      </c>
+      <c r="Y206">
+        <v>1.2</v>
+      </c>
+      <c r="Z206">
         <v>4.2</v>
       </c>
-      <c r="O206">
-        <v>3.5</v>
-      </c>
-      <c r="P206">
-        <v>1.68</v>
-      </c>
-      <c r="Q206">
-        <v>4.75</v>
-      </c>
-      <c r="R206">
-        <v>2.2</v>
-      </c>
-      <c r="S206">
-        <v>1.35</v>
-      </c>
-      <c r="T206">
-        <v>2.96</v>
-      </c>
-      <c r="U206">
-        <v>2.55</v>
-      </c>
-      <c r="V206">
+      <c r="AA206">
         <v>1.45</v>
       </c>
-      <c r="W206">
-        <v>1.07</v>
-      </c>
-      <c r="X206">
-        <v>1</v>
-      </c>
-      <c r="Y206">
-        <v>1.21</v>
-      </c>
-      <c r="Z206">
-        <v>3.58</v>
-      </c>
-      <c r="AA206">
-        <v>1.83</v>
-      </c>
       <c r="AB206">
-        <v>1.95</v>
+        <v>2.41</v>
       </c>
       <c r="AC206">
-        <v>2.92</v>
+        <v>2.21</v>
       </c>
       <c r="AD206">
-        <v>1.31</v>
+        <v>1.59</v>
       </c>
       <c r="AE206">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="AF206">
-        <v>1.72</v>
+        <v>1.56</v>
       </c>
       <c r="AG206">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="AH206" t="inlineStr">
         <is>
@@ -33957,10 +33957,10 @@
         </is>
       </c>
       <c r="AJ206">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AK206">
-        <v>1.2</v>
+        <v>2.33</v>
       </c>
       <c r="AL206">
         <v>0</v>
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G207">
@@ -34050,80 +34050,80 @@
         </is>
       </c>
       <c r="N207">
-        <v>1.48</v>
+        <v>4.2</v>
       </c>
       <c r="O207">
-        <v>4.15</v>
+        <v>3.5</v>
       </c>
       <c r="P207">
-        <v>4.8</v>
+        <v>1.68</v>
       </c>
       <c r="Q207">
+        <v>4.75</v>
+      </c>
+      <c r="R207">
+        <v>2.2</v>
+      </c>
+      <c r="S207">
+        <v>1.35</v>
+      </c>
+      <c r="T207">
+        <v>2.96</v>
+      </c>
+      <c r="U207">
+        <v>2.55</v>
+      </c>
+      <c r="V207">
+        <v>1.45</v>
+      </c>
+      <c r="W207">
+        <v>1.07</v>
+      </c>
+      <c r="X207">
+        <v>1</v>
+      </c>
+      <c r="Y207">
+        <v>1.21</v>
+      </c>
+      <c r="Z207">
+        <v>3.58</v>
+      </c>
+      <c r="AA207">
+        <v>1.83</v>
+      </c>
+      <c r="AB207">
         <v>1.95</v>
       </c>
-      <c r="R207">
-        <v>2.5</v>
-      </c>
-      <c r="S207">
-        <v>1.28</v>
-      </c>
-      <c r="T207">
-        <v>3.3</v>
-      </c>
-      <c r="U207">
-        <v>2.18</v>
-      </c>
-      <c r="V207">
-        <v>1.6</v>
-      </c>
-      <c r="W207">
-        <v>1.13</v>
-      </c>
-      <c r="X207">
-        <v>1.02</v>
-      </c>
-      <c r="Y207">
+      <c r="AC207">
+        <v>2.92</v>
+      </c>
+      <c r="AD207">
+        <v>1.31</v>
+      </c>
+      <c r="AE207">
+        <v>1.08</v>
+      </c>
+      <c r="AF207">
+        <v>1.72</v>
+      </c>
+      <c r="AG207">
+        <v>1.93</v>
+      </c>
+      <c r="AH207" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI207" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ207">
+        <v>1.25</v>
+      </c>
+      <c r="AK207">
         <v>1.2</v>
-      </c>
-      <c r="Z207">
-        <v>4.2</v>
-      </c>
-      <c r="AA207">
-        <v>1.45</v>
-      </c>
-      <c r="AB207">
-        <v>2.41</v>
-      </c>
-      <c r="AC207">
-        <v>2.21</v>
-      </c>
-      <c r="AD207">
-        <v>1.59</v>
-      </c>
-      <c r="AE207">
-        <v>1.2</v>
-      </c>
-      <c r="AF207">
-        <v>1.56</v>
-      </c>
-      <c r="AG207">
-        <v>2.25</v>
-      </c>
-      <c r="AH207" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI207" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ207">
-        <v>1.14</v>
-      </c>
-      <c r="AK207">
-        <v>2.33</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -34219,10 +34219,10 @@
         <v>2.75</v>
       </c>
       <c r="P208">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="Q208">
-        <v>3</v>
+        <v>3.29</v>
       </c>
       <c r="R208">
         <v>1.8</v>
@@ -34234,7 +34234,7 @@
         <v>2.28</v>
       </c>
       <c r="U208">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="V208">
         <v>1.16</v>
@@ -36984,13 +36984,13 @@
         </is>
       </c>
       <c r="N225">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="O225">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="P225">
-        <v>4.04</v>
+        <v>4.06</v>
       </c>
       <c r="Q225">
         <v>2.45</v>
@@ -36999,10 +36999,10 @@
         <v>2.2</v>
       </c>
       <c r="S225">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="T225">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="U225">
         <v>2.62</v>
@@ -37023,7 +37023,7 @@
         <v>3.5</v>
       </c>
       <c r="AA225">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AB225">
         <v>1.83</v>
@@ -37147,10 +37147,10 @@
         </is>
       </c>
       <c r="N226">
-        <v>3.72</v>
+        <v>3.74</v>
       </c>
       <c r="O226">
-        <v>3.41</v>
+        <v>3.37</v>
       </c>
       <c r="P226">
         <v>2.05</v>
@@ -37962,22 +37962,22 @@
         </is>
       </c>
       <c r="N231">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O231">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="P231">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="Q231">
         <v>3.6</v>
       </c>
       <c r="R231">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="S231">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="T231">
         <v>2.6</v>
@@ -37989,25 +37989,25 @@
         <v>1.25</v>
       </c>
       <c r="W231">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X231">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y231">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="Z231">
-        <v>2.75</v>
+        <v>2.42</v>
       </c>
       <c r="AA231">
         <v>2.55</v>
       </c>
       <c r="AB231">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="AC231">
-        <v>4.55</v>
+        <v>4.75</v>
       </c>
       <c r="AD231">
         <v>1.13</v>
@@ -38016,7 +38016,7 @@
         <v>1.05</v>
       </c>
       <c r="AF231">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AG231">
         <v>1.67</v>

--- a/jogos_2026-08-23.xlsx
+++ b/jogos_2026-08-23.xlsx
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,64 +25900,64 @@
         </is>
       </c>
       <c r="N157">
-        <v>2.51</v>
+        <v>1.52</v>
       </c>
       <c r="O157">
-        <v>2.87</v>
+        <v>3.9</v>
       </c>
       <c r="P157">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="Q157">
-        <v>3.1</v>
+        <v>2.05</v>
       </c>
       <c r="R157">
-        <v>1.91</v>
+        <v>2.32</v>
       </c>
       <c r="S157">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="T157">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="U157">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="V157">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="W157">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X157">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y157">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="Z157">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="AA157">
-        <v>2.31</v>
+        <v>1.66</v>
       </c>
       <c r="AB157">
-        <v>1.54</v>
+        <v>2.05</v>
       </c>
       <c r="AC157">
-        <v>4.13</v>
+        <v>2.65</v>
       </c>
       <c r="AD157">
-        <v>1.18</v>
+        <v>1.43</v>
       </c>
       <c r="AE157">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AF157">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AG157">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25970,10 +25970,10 @@
         </is>
       </c>
       <c r="AJ157">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
       <c r="AK157">
-        <v>1.44</v>
+        <v>2.39</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,64 +26063,64 @@
         </is>
       </c>
       <c r="N158">
-        <v>1.52</v>
+        <v>2.51</v>
       </c>
       <c r="O158">
-        <v>3.9</v>
+        <v>2.87</v>
       </c>
       <c r="P158">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="Q158">
-        <v>2.05</v>
+        <v>3.1</v>
       </c>
       <c r="R158">
-        <v>2.32</v>
+        <v>1.91</v>
       </c>
       <c r="S158">
+        <v>1.5</v>
+      </c>
+      <c r="T158">
+        <v>2.3</v>
+      </c>
+      <c r="U158">
+        <v>3.6</v>
+      </c>
+      <c r="V158">
         <v>1.3</v>
       </c>
-      <c r="T158">
-        <v>3.2</v>
-      </c>
-      <c r="U158">
-        <v>2.4</v>
-      </c>
-      <c r="V158">
-        <v>1.55</v>
-      </c>
       <c r="W158">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X158">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y158">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="Z158">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="AA158">
-        <v>1.66</v>
+        <v>2.31</v>
       </c>
       <c r="AB158">
-        <v>2.05</v>
+        <v>1.54</v>
       </c>
       <c r="AC158">
-        <v>2.65</v>
+        <v>4.13</v>
       </c>
       <c r="AD158">
-        <v>1.43</v>
+        <v>1.18</v>
       </c>
       <c r="AE158">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="AF158">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AG158">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26133,10 +26133,10 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>1.1</v>
+        <v>1.33</v>
       </c>
       <c r="AK158">
-        <v>2.39</v>
+        <v>1.44</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -34865,64 +34865,64 @@
         </is>
       </c>
       <c r="N212">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="O212">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="P212">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="Q212">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="R212">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="S212">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T212">
         <v>2.75</v>
       </c>
       <c r="U212">
-        <v>3.23</v>
+        <v>2.9</v>
       </c>
       <c r="V212">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W212">
+        <v>1.05</v>
+      </c>
+      <c r="X212">
         <v>1.03</v>
       </c>
-      <c r="X212">
-        <v>1.06</v>
-      </c>
       <c r="Y212">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="Z212">
-        <v>3.01</v>
+        <v>3.3</v>
       </c>
       <c r="AA212">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AB212">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AC212">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="AD212">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE212">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF212">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="AG212">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AH212" t="inlineStr">
         <is>
@@ -34938,7 +34938,7 @@
         <v>1.33</v>
       </c>
       <c r="AK212">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AL212">
         <v>0</v>
@@ -35037,40 +35037,40 @@
         <v>0</v>
       </c>
       <c r="Q213">
-        <v>4.4</v>
+        <v>4.12</v>
       </c>
       <c r="R213">
-        <v>1.93</v>
+        <v>2.17</v>
       </c>
       <c r="S213">
         <v>1.42</v>
       </c>
       <c r="T213">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="U213">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="V213">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W213">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X213">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Y213">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z213">
         <v>3.05</v>
       </c>
       <c r="AA213">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AB213">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AC213">
         <v>3.85</v>
@@ -35098,10 +35098,10 @@
         </is>
       </c>
       <c r="AJ213">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AK213">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AL213">
         <v>0</v>
@@ -36332,13 +36332,13 @@
         </is>
       </c>
       <c r="N221">
-        <v>2.41</v>
+        <v>2.25</v>
       </c>
       <c r="O221">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="P221">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="Q221">
         <v>0</v>
@@ -36658,13 +36658,13 @@
         </is>
       </c>
       <c r="N223">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="O223">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="P223">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="Q223">
         <v>2.62</v>
@@ -36691,13 +36691,13 @@
         <v>1.09</v>
       </c>
       <c r="Y223">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="Z223">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="AA223">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
       <c r="AB223">
         <v>1.65</v>
@@ -36712,10 +36712,10 @@
         <v>1.08</v>
       </c>
       <c r="AF223">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AG223">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AH223" t="inlineStr">
         <is>
@@ -36728,10 +36728,10 @@
         </is>
       </c>
       <c r="AJ223">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AK223">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AL223">
         <v>0</v>
@@ -37645,16 +37645,16 @@
         <v>0</v>
       </c>
       <c r="Q229">
-        <v>2.55</v>
+        <v>2.41</v>
       </c>
       <c r="R229">
         <v>1.91</v>
       </c>
       <c r="S229">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="T229">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="U229">
         <v>3.6</v>
@@ -37666,19 +37666,19 @@
         <v>1.03</v>
       </c>
       <c r="X229">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y229">
         <v>1.48</v>
       </c>
       <c r="Z229">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AA229">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="AB229">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="AC229">
         <v>4.2</v>
@@ -37706,10 +37706,10 @@
         </is>
       </c>
       <c r="AJ229">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK229">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AL229">
         <v>0</v>
@@ -38288,10 +38288,10 @@
         </is>
       </c>
       <c r="N233">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="O233">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="P233">
         <v>3.9</v>
@@ -38312,10 +38312,10 @@
         <v>2.2</v>
       </c>
       <c r="V233">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W233">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X233">
         <v>1.02</v>
@@ -38324,13 +38324,13 @@
         <v>1.14</v>
       </c>
       <c r="Z233">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AA233">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AB233">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AC233">
         <v>2.2</v>
@@ -38339,10 +38339,10 @@
         <v>1.65</v>
       </c>
       <c r="AE233">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF233">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AG233">
         <v>2.4</v>

--- a/jogos_2026-08-23.xlsx
+++ b/jogos_2026-08-23.xlsx
@@ -638,7 +638,7 @@
         <v>1.9</v>
       </c>
       <c r="O2">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P2">
         <v>3.35</v>
@@ -647,52 +647,52 @@
         <v>2.4</v>
       </c>
       <c r="R2">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="S2">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T2">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="U2">
         <v>2.45</v>
       </c>
       <c r="V2">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W2">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X2">
         <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z2">
-        <v>3.38</v>
+        <v>3.34</v>
       </c>
       <c r="AA2">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AB2">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AC2">
-        <v>3.31</v>
+        <v>3.2</v>
       </c>
       <c r="AD2">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE2">
         <v>1.06</v>
       </c>
       <c r="AF2">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AG2">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK2">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="O6">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="P6">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="Q6">
-        <v>2.13</v>
+        <v>1.95</v>
       </c>
       <c r="R6">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="S6">
         <v>1.25</v>
       </c>
       <c r="T6">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U6">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="V6">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W6">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X6">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z6">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AA6">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AB6">
         <v>2.15</v>
       </c>
       <c r="AC6">
-        <v>2.49</v>
+        <v>2.56</v>
       </c>
       <c r="AD6">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE6">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF6">
         <v>1.62</v>
       </c>
       <c r="AG6">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK6">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -2763,10 +2763,10 @@
         <v>3.85</v>
       </c>
       <c r="Q15">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="R15">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="S15">
         <v>1.25</v>
@@ -2775,10 +2775,10 @@
         <v>3.6</v>
       </c>
       <c r="U15">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V15">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W15">
         <v>1.17</v>
@@ -2790,7 +2790,7 @@
         <v>1.12</v>
       </c>
       <c r="Z15">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AA15">
         <v>1.53</v>
@@ -2799,19 +2799,19 @@
         <v>2.38</v>
       </c>
       <c r="AC15">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AD15">
         <v>1.57</v>
       </c>
       <c r="AE15">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF15">
         <v>1.53</v>
       </c>
       <c r="AG15">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>1.25</v>
       </c>
       <c r="AK15">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -6017,7 +6017,7 @@
         <v>2.14</v>
       </c>
       <c r="O35">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="P35">
         <v>2.85</v>
@@ -6029,22 +6029,22 @@
         <v>2.45</v>
       </c>
       <c r="S35">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T35">
         <v>3.8</v>
       </c>
       <c r="U35">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="V35">
         <v>1.58</v>
       </c>
       <c r="W35">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
         <v>1.13</v>
@@ -6056,13 +6056,13 @@
         <v>1.51</v>
       </c>
       <c r="AB35">
-        <v>2.35</v>
+        <v>2.26</v>
       </c>
       <c r="AC35">
         <v>2.34</v>
       </c>
       <c r="AD35">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AE35">
         <v>1.18</v>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AK35">
         <v>1.58</v>
@@ -7031,10 +7031,10 @@
         <v>0</v>
       </c>
       <c r="AA41">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AB41">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC41">
         <v>0</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="O42">
-        <v>5.5</v>
+        <v>5.45</v>
       </c>
       <c r="P42">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="Q42">
         <v>1.7</v>
@@ -7173,7 +7173,7 @@
         <v>1.19</v>
       </c>
       <c r="T42">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="U42">
         <v>1.9</v>
@@ -7197,16 +7197,16 @@
         <v>1.33</v>
       </c>
       <c r="AB42">
-        <v>3.34</v>
+        <v>3.36</v>
       </c>
       <c r="AC42">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AD42">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AE42">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AF42">
         <v>1.5</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.41</v>
+        <v>2.23</v>
       </c>
       <c r="O44">
-        <v>5</v>
+        <v>3.51</v>
       </c>
       <c r="P44">
-        <v>5.9</v>
+        <v>2.65</v>
       </c>
       <c r="Q44">
-        <v>1.85</v>
+        <v>2.72</v>
       </c>
       <c r="R44">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="S44">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="T44">
+        <v>3.4</v>
+      </c>
+      <c r="U44">
+        <v>2.38</v>
+      </c>
+      <c r="V44">
+        <v>1.52</v>
+      </c>
+      <c r="W44">
+        <v>1.11</v>
+      </c>
+      <c r="X44">
+        <v>1.04</v>
+      </c>
+      <c r="Y44">
+        <v>1.2</v>
+      </c>
+      <c r="Z44">
         <v>4.33</v>
       </c>
-      <c r="U44">
-        <v>2.1</v>
-      </c>
-      <c r="V44">
-        <v>1.77</v>
-      </c>
-      <c r="W44">
-        <v>1.18</v>
-      </c>
-      <c r="X44">
-        <v>1.03</v>
-      </c>
-      <c r="Y44">
-        <v>1.08</v>
-      </c>
-      <c r="Z44">
-        <v>5.75</v>
-      </c>
       <c r="AA44">
-        <v>1.44</v>
+        <v>1.69</v>
       </c>
       <c r="AB44">
-        <v>2.59</v>
+        <v>2.28</v>
       </c>
       <c r="AC44">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="AD44">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AE44">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AF44">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AG44">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
       <c r="AK44">
-        <v>2.7</v>
+        <v>1.71</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.23</v>
+        <v>1.41</v>
       </c>
       <c r="O45">
-        <v>3.51</v>
+        <v>5</v>
       </c>
       <c r="P45">
-        <v>2.65</v>
+        <v>5.9</v>
       </c>
       <c r="Q45">
-        <v>2.72</v>
+        <v>1.85</v>
       </c>
       <c r="R45">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="S45">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="T45">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="U45">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="V45">
-        <v>1.52</v>
+        <v>1.77</v>
       </c>
       <c r="W45">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="X45">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y45">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="Z45">
-        <v>4.33</v>
+        <v>5.75</v>
       </c>
       <c r="AA45">
-        <v>1.69</v>
+        <v>1.44</v>
       </c>
       <c r="AB45">
-        <v>2.28</v>
+        <v>2.59</v>
       </c>
       <c r="AC45">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="AD45">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AE45">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AF45">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AG45">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AK45">
-        <v>1.71</v>
+        <v>2.7</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -8785,16 +8785,16 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.37</v>
+        <v>2.66</v>
       </c>
       <c r="O52">
-        <v>3.12</v>
+        <v>3.05</v>
       </c>
       <c r="P52">
-        <v>2.85</v>
+        <v>2.79</v>
       </c>
       <c r="Q52">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="R52">
         <v>2.13</v>
@@ -8803,13 +8803,13 @@
         <v>1.42</v>
       </c>
       <c r="T52">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="U52">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="V52">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="W52">
         <v>1.02</v>
@@ -8821,7 +8821,7 @@
         <v>1.33</v>
       </c>
       <c r="Z52">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AA52">
         <v>2.15</v>
@@ -8836,13 +8836,13 @@
         <v>1.22</v>
       </c>
       <c r="AE52">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF52">
         <v>1.83</v>
       </c>
       <c r="AG52">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK52">
         <v>1.44</v>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="O57">
         <v>2.55</v>
       </c>
       <c r="P57">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Q57">
         <v>4.12</v>
@@ -9654,7 +9654,7 @@
         <v>1.02</v>
       </c>
       <c r="AF57">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="AG57">
         <v>1.44</v>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="AK57">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="O70">
-        <v>3.29</v>
+        <v>3.4</v>
       </c>
       <c r="P70">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="Q70">
         <v>0</v>
@@ -13186,10 +13186,10 @@
         </is>
       </c>
       <c r="N79">
-        <v>9.5</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="O79">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="P79">
         <v>1.28</v>
@@ -13207,10 +13207,10 @@
         <v>3.88</v>
       </c>
       <c r="U79">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="V79">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="W79">
         <v>1.18</v>
@@ -13219,25 +13219,25 @@
         <v>1.01</v>
       </c>
       <c r="Y79">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z79">
-        <v>5.4</v>
+        <v>6.5</v>
       </c>
       <c r="AA79">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AB79">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="AC79">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AD79">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AE79">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AF79">
         <v>1.75</v>
@@ -13256,7 +13256,7 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AK79">
         <v>1.03</v>
@@ -13352,13 +13352,13 @@
         <v>2.87</v>
       </c>
       <c r="O80">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P80">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="Q80">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="R80">
         <v>2.5</v>
@@ -13382,22 +13382,22 @@
         <v>1.02</v>
       </c>
       <c r="Y80">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="Z80">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="AA80">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB80">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="AC80">
         <v>2.08</v>
       </c>
       <c r="AD80">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AE80">
         <v>1.3</v>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AK80">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -16461,7 +16461,7 @@
         <v>2.4</v>
       </c>
       <c r="S99">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="T99">
         <v>3.1</v>
@@ -16470,22 +16470,22 @@
         <v>2.4</v>
       </c>
       <c r="V99">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W99">
         <v>1.07</v>
       </c>
       <c r="X99">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y99">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z99">
         <v>4</v>
       </c>
       <c r="AA99">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AB99">
         <v>2.1</v>
@@ -16494,16 +16494,16 @@
         <v>2.75</v>
       </c>
       <c r="AD99">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE99">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF99">
         <v>1.9</v>
       </c>
       <c r="AG99">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16811,10 +16811,10 @@
         <v>3.14</v>
       </c>
       <c r="AA101">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="AB101">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="AC101">
         <v>3.2</v>
@@ -16826,10 +16826,10 @@
         <v>1.06</v>
       </c>
       <c r="AF101">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AG101">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16974,10 +16974,10 @@
         <v>3.35</v>
       </c>
       <c r="AA102">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AB102">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AC102">
         <v>2.88</v>
@@ -17005,7 +17005,7 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AK102">
         <v>1.37</v>
@@ -17433,55 +17433,55 @@
         <v>3.3</v>
       </c>
       <c r="Q105">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="R105">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="S105">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T105">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U105">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="V105">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W105">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X105">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y105">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Z105">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AA105">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="AB105">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AC105">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="AD105">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AE105">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF105">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG105">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK105">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17596,10 +17596,10 @@
         <v>4.5</v>
       </c>
       <c r="Q106">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="R106">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="S106">
         <v>1.36</v>
@@ -17626,10 +17626,10 @@
         <v>3.08</v>
       </c>
       <c r="AA106">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AB106">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AC106">
         <v>3.42</v>
@@ -17644,7 +17644,7 @@
         <v>1.91</v>
       </c>
       <c r="AG106">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,7 +17657,7 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AK106">
         <v>2.1</v>
@@ -21662,64 +21662,64 @@
         </is>
       </c>
       <c r="N131">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="O131">
+        <v>3.1</v>
+      </c>
+      <c r="P131">
         <v>3</v>
       </c>
-      <c r="P131">
-        <v>3.25</v>
-      </c>
       <c r="Q131">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="R131">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="S131">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T131">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U131">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="V131">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W131">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X131">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y131">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z131">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="AA131">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="AB131">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AC131">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AD131">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE131">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF131">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="AG131">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="AJ131">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK131">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -21861,13 +21861,13 @@
         <v>1.25</v>
       </c>
       <c r="Z132">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AA132">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AB132">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AC132">
         <v>3.1</v>
@@ -22812,52 +22812,52 @@
         <v>4.16</v>
       </c>
       <c r="Q138">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="R138">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="S138">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T138">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U138">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="V138">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W138">
+        <v>1.06</v>
+      </c>
+      <c r="X138">
+        <v>1.04</v>
+      </c>
+      <c r="Y138">
+        <v>1.3</v>
+      </c>
+      <c r="Z138">
+        <v>3.2</v>
+      </c>
+      <c r="AA138">
+        <v>2.1</v>
+      </c>
+      <c r="AB138">
+        <v>1.67</v>
+      </c>
+      <c r="AC138">
+        <v>3.75</v>
+      </c>
+      <c r="AD138">
+        <v>1.22</v>
+      </c>
+      <c r="AE138">
         <v>1.07</v>
       </c>
-      <c r="X138">
-        <v>0</v>
-      </c>
-      <c r="Y138">
-        <v>1.33</v>
-      </c>
-      <c r="Z138">
-        <v>2.87</v>
-      </c>
-      <c r="AA138">
-        <v>2.05</v>
-      </c>
-      <c r="AB138">
-        <v>1.66</v>
-      </c>
-      <c r="AC138">
-        <v>3.5</v>
-      </c>
-      <c r="AD138">
-        <v>1.24</v>
-      </c>
-      <c r="AE138">
-        <v>0</v>
-      </c>
       <c r="AF138">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="AG138">
         <v>1.8</v>
@@ -22873,10 +22873,10 @@
         </is>
       </c>
       <c r="AJ138">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK138">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL138">
         <v>0</v>
@@ -24270,7 +24270,7 @@
         </is>
       </c>
       <c r="N147">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="O147">
         <v>6</v>
@@ -24448,46 +24448,46 @@
         <v>2.3</v>
       </c>
       <c r="S148">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T148">
         <v>3.18</v>
       </c>
       <c r="U148">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="V148">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W148">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X148">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y148">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="Z148">
         <v>4.2</v>
       </c>
       <c r="AA148">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AB148">
-        <v>2.14</v>
+        <v>2.21</v>
       </c>
       <c r="AC148">
-        <v>2.7</v>
+        <v>2.52</v>
       </c>
       <c r="AD148">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AE148">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AF148">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG148">
         <v>2.25</v>
@@ -24503,7 +24503,7 @@
         </is>
       </c>
       <c r="AJ148">
-        <v>1.22</v>
+        <v>1.65</v>
       </c>
       <c r="AK148">
         <v>1.3</v>
@@ -24759,58 +24759,58 @@
         </is>
       </c>
       <c r="N150">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="O150">
         <v>3.6</v>
       </c>
       <c r="P150">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="Q150">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="R150">
         <v>2.06</v>
       </c>
       <c r="S150">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="T150">
         <v>2.88</v>
       </c>
       <c r="U150">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="V150">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W150">
         <v>1.06</v>
       </c>
       <c r="X150">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y150">
         <v>1.29</v>
       </c>
       <c r="Z150">
-        <v>3.51</v>
+        <v>3.52</v>
       </c>
       <c r="AA150">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AB150">
         <v>1.85</v>
       </c>
       <c r="AC150">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AD150">
         <v>1.33</v>
       </c>
       <c r="AE150">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF150">
         <v>1.85</v>
@@ -24829,10 +24829,10 @@
         </is>
       </c>
       <c r="AJ150">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AK150">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AL150">
         <v>0</v>
@@ -24925,10 +24925,10 @@
         <v>1.7</v>
       </c>
       <c r="O151">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P151">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="Q151">
         <v>2.3</v>
@@ -24937,19 +24937,19 @@
         <v>2.1</v>
       </c>
       <c r="S151">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T151">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="U151">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="V151">
         <v>1.35</v>
       </c>
       <c r="W151">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X151">
         <v>1.04</v>
@@ -24958,7 +24958,7 @@
         <v>1.36</v>
       </c>
       <c r="Z151">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AA151">
         <v>2.1</v>
@@ -24970,16 +24970,16 @@
         <v>4</v>
       </c>
       <c r="AD151">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AE151">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF151">
         <v>2</v>
       </c>
       <c r="AG151">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AH151" t="inlineStr">
         <is>
@@ -24992,7 +24992,7 @@
         </is>
       </c>
       <c r="AJ151">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK151">
         <v>2.05</v>
@@ -25417,43 +25417,43 @@
         <v>4.15</v>
       </c>
       <c r="P154">
-        <v>8.75</v>
+        <v>6.4</v>
       </c>
       <c r="Q154">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="R154">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S154">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T154">
+        <v>2.75</v>
+      </c>
+      <c r="U154">
         <v>2.88</v>
       </c>
-      <c r="U154">
-        <v>2.75</v>
-      </c>
       <c r="V154">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W154">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X154">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y154">
         <v>1.28</v>
       </c>
       <c r="Z154">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="AA154">
         <v>2.01</v>
       </c>
       <c r="AB154">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC154">
         <v>3.6</v>
@@ -25462,13 +25462,13 @@
         <v>1.29</v>
       </c>
       <c r="AE154">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF154">
         <v>2.25</v>
       </c>
       <c r="AG154">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -27204,13 +27204,13 @@
         </is>
       </c>
       <c r="N165">
-        <v>2.4</v>
+        <v>2.77</v>
       </c>
       <c r="O165">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="P165">
-        <v>3.14</v>
+        <v>2.56</v>
       </c>
       <c r="Q165">
         <v>0</v>
@@ -27367,13 +27367,13 @@
         </is>
       </c>
       <c r="N166">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O166">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P166">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q166">
         <v>0</v>
@@ -28523,10 +28523,10 @@
         <v>2.43</v>
       </c>
       <c r="S173">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T173">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U173">
         <v>2.25</v>
@@ -28535,13 +28535,13 @@
         <v>1.57</v>
       </c>
       <c r="W173">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X173">
         <v>1.03</v>
       </c>
       <c r="Y173">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z173">
         <v>4.5</v>
@@ -28550,7 +28550,7 @@
         <v>1.53</v>
       </c>
       <c r="AB173">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="AC173">
         <v>2.38</v>
@@ -28562,10 +28562,10 @@
         <v>1.21</v>
       </c>
       <c r="AF173">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AG173">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AH173" t="inlineStr">
         <is>
@@ -28578,10 +28578,10 @@
         </is>
       </c>
       <c r="AJ173">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AK173">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AL173">
         <v>0</v>
@@ -30956,22 +30956,22 @@
         <v>2.8</v>
       </c>
       <c r="O188">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P188">
         <v>2.17</v>
       </c>
       <c r="Q188">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="R188">
         <v>2.25</v>
       </c>
       <c r="S188">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T188">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="U188">
         <v>2.55</v>
@@ -30980,7 +30980,7 @@
         <v>1.45</v>
       </c>
       <c r="W188">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X188">
         <v>1.04</v>
@@ -30992,13 +30992,13 @@
         <v>3.94</v>
       </c>
       <c r="AA188">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AB188">
         <v>2.1</v>
       </c>
       <c r="AC188">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="AD188">
         <v>1.41</v>
@@ -31026,7 +31026,7 @@
         <v>1.28</v>
       </c>
       <c r="AK188">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AL188">
         <v>0</v>
@@ -31605,13 +31605,13 @@
         </is>
       </c>
       <c r="N192">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="O192">
         <v>3.3</v>
       </c>
       <c r="P192">
-        <v>2.82</v>
+        <v>2.85</v>
       </c>
       <c r="Q192">
         <v>2.88</v>
@@ -31626,43 +31626,43 @@
         <v>2.75</v>
       </c>
       <c r="U192">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="V192">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W192">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X192">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y192">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="Z192">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="AA192">
         <v>1.92</v>
       </c>
       <c r="AB192">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC192">
         <v>3.18</v>
       </c>
       <c r="AD192">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AE192">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF192">
         <v>1.75</v>
       </c>
       <c r="AG192">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AH192" t="inlineStr">
         <is>
@@ -31675,7 +31675,7 @@
         </is>
       </c>
       <c r="AJ192">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="AK192">
         <v>1.5</v>
@@ -31768,34 +31768,34 @@
         </is>
       </c>
       <c r="N193">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="O193">
         <v>3.55</v>
       </c>
       <c r="P193">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="Q193">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="R193">
         <v>2.15</v>
       </c>
       <c r="S193">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T193">
         <v>2.73</v>
       </c>
       <c r="U193">
-        <v>2.8</v>
+        <v>2.99</v>
       </c>
       <c r="V193">
         <v>1.38</v>
       </c>
       <c r="W193">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X193">
         <v>1.03</v>
@@ -31810,7 +31810,7 @@
         <v>2.09</v>
       </c>
       <c r="AB193">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AC193">
         <v>3.6</v>
@@ -31822,10 +31822,10 @@
         <v>1.06</v>
       </c>
       <c r="AF193">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AG193">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AH193" t="inlineStr">
         <is>
@@ -31841,7 +31841,7 @@
         <v>1.3</v>
       </c>
       <c r="AK193">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AL193">
         <v>0</v>
@@ -31931,7 +31931,7 @@
         </is>
       </c>
       <c r="N194">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="O194">
         <v>3.1</v>
@@ -31940,19 +31940,19 @@
         <v>3.4</v>
       </c>
       <c r="Q194">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="R194">
         <v>2</v>
       </c>
       <c r="S194">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T194">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="U194">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="V194">
         <v>1.3</v>
@@ -31970,10 +31970,10 @@
         <v>2.74</v>
       </c>
       <c r="AA194">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="AB194">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC194">
         <v>4</v>
@@ -31985,10 +31985,10 @@
         <v>1.01</v>
       </c>
       <c r="AF194">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AG194">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AH194" t="inlineStr">
         <is>
@@ -32001,7 +32001,7 @@
         </is>
       </c>
       <c r="AJ194">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK194">
         <v>1.62</v>
@@ -32103,55 +32103,55 @@
         <v>4.53</v>
       </c>
       <c r="Q195">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="R195">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S195">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T195">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U195">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="V195">
         <v>1.36</v>
       </c>
       <c r="W195">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X195">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y195">
         <v>1.3</v>
       </c>
       <c r="Z195">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AA195">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AB195">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AC195">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AD195">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE195">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF195">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AG195">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
@@ -32164,10 +32164,10 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK195">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G206">
@@ -33887,80 +33887,80 @@
         </is>
       </c>
       <c r="N206">
-        <v>1.48</v>
+        <v>4.2</v>
       </c>
       <c r="O206">
-        <v>4.15</v>
+        <v>3.5</v>
       </c>
       <c r="P206">
-        <v>4.8</v>
+        <v>1.68</v>
       </c>
       <c r="Q206">
+        <v>4.75</v>
+      </c>
+      <c r="R206">
+        <v>2.2</v>
+      </c>
+      <c r="S206">
+        <v>1.35</v>
+      </c>
+      <c r="T206">
+        <v>2.96</v>
+      </c>
+      <c r="U206">
+        <v>2.55</v>
+      </c>
+      <c r="V206">
+        <v>1.45</v>
+      </c>
+      <c r="W206">
+        <v>1.07</v>
+      </c>
+      <c r="X206">
+        <v>1</v>
+      </c>
+      <c r="Y206">
+        <v>1.21</v>
+      </c>
+      <c r="Z206">
+        <v>3.58</v>
+      </c>
+      <c r="AA206">
+        <v>1.83</v>
+      </c>
+      <c r="AB206">
         <v>1.95</v>
       </c>
-      <c r="R206">
-        <v>2.5</v>
-      </c>
-      <c r="S206">
-        <v>1.28</v>
-      </c>
-      <c r="T206">
-        <v>3.3</v>
-      </c>
-      <c r="U206">
-        <v>2.18</v>
-      </c>
-      <c r="V206">
-        <v>1.6</v>
-      </c>
-      <c r="W206">
-        <v>1.13</v>
-      </c>
-      <c r="X206">
-        <v>1.02</v>
-      </c>
-      <c r="Y206">
+      <c r="AC206">
+        <v>2.92</v>
+      </c>
+      <c r="AD206">
+        <v>1.31</v>
+      </c>
+      <c r="AE206">
+        <v>1.08</v>
+      </c>
+      <c r="AF206">
+        <v>1.72</v>
+      </c>
+      <c r="AG206">
+        <v>1.93</v>
+      </c>
+      <c r="AH206" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI206" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ206">
+        <v>1.25</v>
+      </c>
+      <c r="AK206">
         <v>1.2</v>
-      </c>
-      <c r="Z206">
-        <v>4.2</v>
-      </c>
-      <c r="AA206">
-        <v>1.45</v>
-      </c>
-      <c r="AB206">
-        <v>2.41</v>
-      </c>
-      <c r="AC206">
-        <v>2.21</v>
-      </c>
-      <c r="AD206">
-        <v>1.59</v>
-      </c>
-      <c r="AE206">
-        <v>1.2</v>
-      </c>
-      <c r="AF206">
-        <v>1.56</v>
-      </c>
-      <c r="AG206">
-        <v>2.25</v>
-      </c>
-      <c r="AH206" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI206" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ206">
-        <v>1.14</v>
-      </c>
-      <c r="AK206">
-        <v>2.33</v>
       </c>
       <c r="AL206">
         <v>0</v>
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G207">
@@ -34050,64 +34050,64 @@
         </is>
       </c>
       <c r="N207">
+        <v>1.48</v>
+      </c>
+      <c r="O207">
+        <v>4.15</v>
+      </c>
+      <c r="P207">
+        <v>4.8</v>
+      </c>
+      <c r="Q207">
+        <v>1.95</v>
+      </c>
+      <c r="R207">
+        <v>2.5</v>
+      </c>
+      <c r="S207">
+        <v>1.28</v>
+      </c>
+      <c r="T207">
+        <v>3.3</v>
+      </c>
+      <c r="U207">
+        <v>2.18</v>
+      </c>
+      <c r="V207">
+        <v>1.6</v>
+      </c>
+      <c r="W207">
+        <v>1.13</v>
+      </c>
+      <c r="X207">
+        <v>1.02</v>
+      </c>
+      <c r="Y207">
+        <v>1.2</v>
+      </c>
+      <c r="Z207">
         <v>4.2</v>
       </c>
-      <c r="O207">
-        <v>3.5</v>
-      </c>
-      <c r="P207">
-        <v>1.68</v>
-      </c>
-      <c r="Q207">
-        <v>4.75</v>
-      </c>
-      <c r="R207">
-        <v>2.2</v>
-      </c>
-      <c r="S207">
-        <v>1.35</v>
-      </c>
-      <c r="T207">
-        <v>2.96</v>
-      </c>
-      <c r="U207">
-        <v>2.55</v>
-      </c>
-      <c r="V207">
+      <c r="AA207">
         <v>1.45</v>
       </c>
-      <c r="W207">
-        <v>1.07</v>
-      </c>
-      <c r="X207">
-        <v>1</v>
-      </c>
-      <c r="Y207">
-        <v>1.21</v>
-      </c>
-      <c r="Z207">
-        <v>3.58</v>
-      </c>
-      <c r="AA207">
-        <v>1.83</v>
-      </c>
       <c r="AB207">
-        <v>1.95</v>
+        <v>2.41</v>
       </c>
       <c r="AC207">
-        <v>2.92</v>
+        <v>2.21</v>
       </c>
       <c r="AD207">
-        <v>1.31</v>
+        <v>1.59</v>
       </c>
       <c r="AE207">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="AF207">
-        <v>1.72</v>
+        <v>1.56</v>
       </c>
       <c r="AG207">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="AH207" t="inlineStr">
         <is>
@@ -34120,10 +34120,10 @@
         </is>
       </c>
       <c r="AJ207">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AK207">
-        <v>1.2</v>
+        <v>2.33</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -34711,55 +34711,55 @@
         <v>4.94</v>
       </c>
       <c r="Q211">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="R211">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S211">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T211">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U211">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="V211">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W211">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X211">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y211">
         <v>1.36</v>
       </c>
       <c r="Z211">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="AA211">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AB211">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AC211">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AD211">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE211">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF211">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AG211">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AH211" t="inlineStr">
         <is>
@@ -34772,10 +34772,10 @@
         </is>
       </c>
       <c r="AJ211">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK211">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL211">
         <v>0</v>
@@ -36015,22 +36015,22 @@
         <v>4</v>
       </c>
       <c r="Q219">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="R219">
         <v>2.21</v>
       </c>
       <c r="S219">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T219">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="U219">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="V219">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W219">
         <v>1.08</v>
@@ -36039,7 +36039,7 @@
         <v>1.04</v>
       </c>
       <c r="Y219">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z219">
         <v>3.7</v>
@@ -36048,22 +36048,22 @@
         <v>1.75</v>
       </c>
       <c r="AB219">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AC219">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="AD219">
         <v>1.33</v>
       </c>
       <c r="AE219">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF219">
         <v>1.68</v>
       </c>
       <c r="AG219">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AH219" t="inlineStr">
         <is>
@@ -36076,10 +36076,10 @@
         </is>
       </c>
       <c r="AJ219">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK219">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="AL219">
         <v>0</v>
@@ -37811,19 +37811,19 @@
         <v>2.4</v>
       </c>
       <c r="R230">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="S230">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="T230">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="U230">
-        <v>2.49</v>
+        <v>2.35</v>
       </c>
       <c r="V230">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W230">
         <v>1.1</v>
@@ -37832,31 +37832,31 @@
         <v>1.01</v>
       </c>
       <c r="Y230">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z230">
-        <v>4.1</v>
+        <v>3.94</v>
       </c>
       <c r="AA230">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AB230">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AC230">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AD230">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE230">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF230">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG230">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="AH230" t="inlineStr">
         <is>
@@ -37872,7 +37872,7 @@
         <v>1.29</v>
       </c>
       <c r="AK230">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AL230">
         <v>0</v>
@@ -38949,7 +38949,7 @@
         <v>1.95</v>
       </c>
       <c r="Q237">
-        <v>4.39</v>
+        <v>3.9</v>
       </c>
       <c r="R237">
         <v>2.1</v>
@@ -38964,40 +38964,40 @@
         <v>2.88</v>
       </c>
       <c r="V237">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W237">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X237">
         <v>1.06</v>
       </c>
       <c r="Y237">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="Z237">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AA237">
         <v>2.04</v>
       </c>
       <c r="AB237">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AC237">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="AD237">
         <v>1.22</v>
       </c>
       <c r="AE237">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF237">
         <v>1.83</v>
       </c>
       <c r="AG237">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AH237" t="inlineStr">
         <is>
@@ -39010,7 +39010,7 @@
         </is>
       </c>
       <c r="AJ237">
-        <v>1.3</v>
+        <v>1.68</v>
       </c>
       <c r="AK237">
         <v>1.22</v>

--- a/jogos_2026-08-23.xlsx
+++ b/jogos_2026-08-23.xlsx
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="O3">
-        <v>3.04</v>
+        <v>3.15</v>
       </c>
       <c r="P3">
+        <v>2.85</v>
+      </c>
+      <c r="Q3">
+        <v>2.7</v>
+      </c>
+      <c r="R3">
+        <v>2.01</v>
+      </c>
+      <c r="S3">
+        <v>1.36</v>
+      </c>
+      <c r="T3">
+        <v>2.9</v>
+      </c>
+      <c r="U3">
         <v>2.75</v>
-      </c>
-      <c r="Q3">
-        <v>2.93</v>
-      </c>
-      <c r="R3">
-        <v>2.02</v>
-      </c>
-      <c r="S3">
-        <v>1.37</v>
-      </c>
-      <c r="T3">
-        <v>2.71</v>
-      </c>
-      <c r="U3">
-        <v>2.79</v>
       </c>
       <c r="V3">
         <v>1.35</v>
       </c>
       <c r="W3">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X3">
         <v>1.02</v>
       </c>
       <c r="Y3">
+        <v>1.26</v>
+      </c>
+      <c r="Z3">
+        <v>3.2</v>
+      </c>
+      <c r="AA3">
+        <v>1.91</v>
+      </c>
+      <c r="AB3">
+        <v>1.82</v>
+      </c>
+      <c r="AC3">
+        <v>3.28</v>
+      </c>
+      <c r="AD3">
         <v>1.25</v>
-      </c>
-      <c r="Z3">
-        <v>3.3</v>
-      </c>
-      <c r="AA3">
-        <v>1.82</v>
-      </c>
-      <c r="AB3">
-        <v>1.81</v>
-      </c>
-      <c r="AC3">
-        <v>3</v>
-      </c>
-      <c r="AD3">
-        <v>1.26</v>
       </c>
       <c r="AE3">
         <v>1.05</v>
       </c>
       <c r="AF3">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AG3">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>1.25</v>
       </c>
       <c r="AK3">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="O4">
-        <v>3.48</v>
+        <v>3.64</v>
       </c>
       <c r="P4">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1000,10 +1000,10 @@
         <v>0</v>
       </c>
       <c r="AA4">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AB4">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="AC4">
         <v>0</v>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>4.53</v>
+        <v>4.65</v>
       </c>
       <c r="O5">
-        <v>3.59</v>
+        <v>3.95</v>
       </c>
       <c r="P5">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q5">
         <v>5.05</v>
@@ -1145,13 +1145,13 @@
         <v>3.04</v>
       </c>
       <c r="U5">
-        <v>2.5</v>
+        <v>2.23</v>
       </c>
       <c r="V5">
         <v>1.5</v>
       </c>
       <c r="W5">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X5">
         <v>1</v>
@@ -1160,13 +1160,13 @@
         <v>1.19</v>
       </c>
       <c r="Z5">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="AA5">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="AB5">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AC5">
         <v>2.62</v>
@@ -1181,7 +1181,7 @@
         <v>1.71</v>
       </c>
       <c r="AG5">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.17</v>
+        <v>2.16</v>
       </c>
       <c r="AK5">
         <v>1.1</v>
@@ -1486,19 +1486,19 @@
         <v>1.15</v>
       </c>
       <c r="Z7">
-        <v>4.34</v>
+        <v>4.4</v>
       </c>
       <c r="AA7">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AB7">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AC7">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="AD7">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AE7">
         <v>1.18</v>
@@ -1785,31 +1785,31 @@
         <v>3.1</v>
       </c>
       <c r="Q9">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="R9">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="S9">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="T9">
-        <v>2.93</v>
+        <v>2.62</v>
       </c>
       <c r="U9">
-        <v>2.81</v>
+        <v>2.84</v>
       </c>
       <c r="V9">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W9">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X9">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z9">
         <v>3.49</v>
@@ -1824,7 +1824,7 @@
         <v>3.4</v>
       </c>
       <c r="AD9">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE9">
         <v>1.06</v>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="O12">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="P12">
         <v>2.33</v>
@@ -2277,7 +2277,7 @@
         <v>3.06</v>
       </c>
       <c r="R12">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="S12">
         <v>1.36</v>
@@ -2289,10 +2289,10 @@
         <v>2.77</v>
       </c>
       <c r="V12">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W12">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X12">
         <v>1.01</v>
@@ -2301,7 +2301,7 @@
         <v>1.22</v>
       </c>
       <c r="Z12">
-        <v>4.05</v>
+        <v>3.68</v>
       </c>
       <c r="AA12">
         <v>1.79</v>
@@ -2310,19 +2310,19 @@
         <v>2.03</v>
       </c>
       <c r="AC12">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="AD12">
         <v>1.39</v>
       </c>
       <c r="AE12">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AF12">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG12">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.34</v>
+        <v>1.57</v>
       </c>
       <c r="AK12">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,19 +2428,19 @@
         </is>
       </c>
       <c r="N13">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="O13">
-        <v>3.8</v>
+        <v>4.15</v>
       </c>
       <c r="P13">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="Q13">
         <v>4.2</v>
       </c>
       <c r="R13">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="S13">
         <v>1.22</v>
@@ -2452,13 +2452,13 @@
         <v>2.11</v>
       </c>
       <c r="V13">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="W13">
         <v>1.15</v>
       </c>
       <c r="X13">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y13">
         <v>1.14</v>
@@ -2467,19 +2467,19 @@
         <v>5.5</v>
       </c>
       <c r="AA13">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AB13">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="AC13">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AD13">
         <v>1.67</v>
       </c>
       <c r="AE13">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AF13">
         <v>1.44</v>
@@ -2920,10 +2920,10 @@
         <v>4.55</v>
       </c>
       <c r="O16">
-        <v>3.5</v>
+        <v>3.27</v>
       </c>
       <c r="P16">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="Q16">
         <v>4.8</v>
@@ -2935,16 +2935,16 @@
         <v>1.46</v>
       </c>
       <c r="T16">
-        <v>2.48</v>
+        <v>2.53</v>
       </c>
       <c r="U16">
         <v>3.2</v>
       </c>
       <c r="V16">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W16">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X16">
         <v>1.07</v>
@@ -2962,7 +2962,7 @@
         <v>1.61</v>
       </c>
       <c r="AC16">
-        <v>4.32</v>
+        <v>4.2</v>
       </c>
       <c r="AD16">
         <v>1.19</v>
@@ -2971,7 +2971,7 @@
         <v>1.06</v>
       </c>
       <c r="AF16">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AG16">
         <v>1.66</v>
@@ -2990,7 +2990,7 @@
         <v>1.23</v>
       </c>
       <c r="AK16">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="O17">
         <v>3.1</v>
       </c>
       <c r="P17">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="Q17">
         <v>3.16</v>
@@ -3098,16 +3098,16 @@
         <v>1.4</v>
       </c>
       <c r="T17">
-        <v>2.56</v>
+        <v>2.77</v>
       </c>
       <c r="U17">
         <v>3</v>
       </c>
       <c r="V17">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W17">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X17">
         <v>1.07</v>
@@ -3131,13 +3131,13 @@
         <v>1.2</v>
       </c>
       <c r="AE17">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF17">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AG17">
-        <v>1.77</v>
+        <v>1.91</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK17">
         <v>1.5</v>
@@ -3246,13 +3246,13 @@
         <v>2.5</v>
       </c>
       <c r="O18">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="P18">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="Q18">
-        <v>3.22</v>
+        <v>3.26</v>
       </c>
       <c r="R18">
         <v>2.15</v>
@@ -3264,10 +3264,10 @@
         <v>2.9</v>
       </c>
       <c r="U18">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="V18">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="W18">
         <v>1.03</v>
@@ -3282,16 +3282,16 @@
         <v>3.25</v>
       </c>
       <c r="AA18">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AB18">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AC18">
         <v>3.45</v>
       </c>
       <c r="AD18">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AE18">
         <v>1.08</v>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="O19">
         <v>4.2</v>
@@ -3427,37 +3427,37 @@
         <v>3.5</v>
       </c>
       <c r="U19">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="V19">
         <v>1.57</v>
       </c>
       <c r="W19">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X19">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
         <v>1.18</v>
       </c>
       <c r="Z19">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="AA19">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AB19">
         <v>2.25</v>
       </c>
       <c r="AC19">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AD19">
         <v>1.44</v>
       </c>
       <c r="AE19">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AF19">
         <v>1.67</v>
@@ -3479,7 +3479,7 @@
         <v>1.1</v>
       </c>
       <c r="AK19">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3578,7 +3578,7 @@
         <v>1.95</v>
       </c>
       <c r="Q20">
-        <v>4.08</v>
+        <v>3.98</v>
       </c>
       <c r="R20">
         <v>2.15</v>
@@ -3587,19 +3587,19 @@
         <v>1.36</v>
       </c>
       <c r="T20">
-        <v>2.83</v>
+        <v>2.91</v>
       </c>
       <c r="U20">
         <v>2.63</v>
       </c>
       <c r="V20">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W20">
         <v>1.06</v>
       </c>
       <c r="X20">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y20">
         <v>1.24</v>
@@ -3611,13 +3611,13 @@
         <v>1.77</v>
       </c>
       <c r="AB20">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AC20">
         <v>2.91</v>
       </c>
       <c r="AD20">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AE20">
         <v>1.13</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK20">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="O21">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P21">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q21">
         <v>2.5</v>
@@ -3747,19 +3747,19 @@
         <v>2.2</v>
       </c>
       <c r="S21">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T21">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="U21">
         <v>2.62</v>
       </c>
       <c r="V21">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W21">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X21">
         <v>1.05</v>
@@ -3768,19 +3768,19 @@
         <v>1.24</v>
       </c>
       <c r="Z21">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AA21">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AB21">
         <v>1.85</v>
       </c>
       <c r="AC21">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AD21">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE21">
         <v>1.06</v>
@@ -3895,10 +3895,10 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="O22">
-        <v>3.58</v>
+        <v>3.25</v>
       </c>
       <c r="P22">
         <v>4.7</v>
@@ -3916,7 +3916,7 @@
         <v>2.75</v>
       </c>
       <c r="U22">
-        <v>2.86</v>
+        <v>2.95</v>
       </c>
       <c r="V22">
         <v>1.35</v>
@@ -3928,28 +3928,28 @@
         <v>1.07</v>
       </c>
       <c r="Y22">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Z22">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="AA22">
-        <v>2.07</v>
+        <v>2.16</v>
       </c>
       <c r="AB22">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AC22">
         <v>3.95</v>
       </c>
       <c r="AD22">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE22">
         <v>1.02</v>
       </c>
       <c r="AF22">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="AG22">
         <v>1.72</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK22">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4070,13 +4070,13 @@
         <v>3.3</v>
       </c>
       <c r="R23">
-        <v>2.38</v>
+        <v>2.16</v>
       </c>
       <c r="S23">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T23">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="U23">
         <v>2.4</v>
@@ -4085,7 +4085,7 @@
         <v>1.51</v>
       </c>
       <c r="W23">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X23">
         <v>1.04</v>
@@ -4094,16 +4094,16 @@
         <v>1.2</v>
       </c>
       <c r="Z23">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="AA23">
         <v>1.55</v>
       </c>
       <c r="AB23">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC23">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="AD23">
         <v>1.4</v>
@@ -4131,7 +4131,7 @@
         <v>1.3</v>
       </c>
       <c r="AK23">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,28 +4221,28 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="O24">
         <v>3.5</v>
       </c>
       <c r="P24">
-        <v>2.93</v>
+        <v>3.3</v>
       </c>
       <c r="Q24">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="R24">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="S24">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T24">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="U24">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="V24">
         <v>1.44</v>
@@ -4254,13 +4254,13 @@
         <v>1.04</v>
       </c>
       <c r="Y24">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z24">
         <v>4.05</v>
       </c>
       <c r="AA24">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB24">
         <v>2.12</v>
@@ -4272,10 +4272,10 @@
         <v>1.44</v>
       </c>
       <c r="AE24">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF24">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG24">
         <v>2.15</v>
@@ -4294,7 +4294,7 @@
         <v>1.29</v>
       </c>
       <c r="AK24">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4568,22 +4568,22 @@
         <v>2.88</v>
       </c>
       <c r="U26">
-        <v>2.89</v>
+        <v>3.05</v>
       </c>
       <c r="V26">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="W26">
         <v>1.04</v>
       </c>
       <c r="X26">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y26">
         <v>1.33</v>
       </c>
       <c r="Z26">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AA26">
         <v>2.05</v>
@@ -4595,16 +4595,16 @@
         <v>3.65</v>
       </c>
       <c r="AD26">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE26">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF26">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AG26">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -5048,22 +5048,22 @@
         <v>1.67</v>
       </c>
       <c r="R29">
-        <v>2.75</v>
+        <v>2.96</v>
       </c>
       <c r="S29">
+        <v>1.21</v>
+      </c>
+      <c r="T29">
+        <v>3.68</v>
+      </c>
+      <c r="U29">
+        <v>2.03</v>
+      </c>
+      <c r="V29">
+        <v>1.72</v>
+      </c>
+      <c r="W29">
         <v>1.18</v>
-      </c>
-      <c r="T29">
-        <v>4</v>
-      </c>
-      <c r="U29">
-        <v>1.99</v>
-      </c>
-      <c r="V29">
-        <v>1.75</v>
-      </c>
-      <c r="W29">
-        <v>1.2</v>
       </c>
       <c r="X29">
         <v>1.01</v>
@@ -5087,7 +5087,7 @@
         <v>1.77</v>
       </c>
       <c r="AE29">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AF29">
         <v>1.62</v>
@@ -5109,7 +5109,7 @@
         <v>1.03</v>
       </c>
       <c r="AK29">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5205,13 +5205,13 @@
         <v>2.95</v>
       </c>
       <c r="P30">
-        <v>2.71</v>
+        <v>2.95</v>
       </c>
       <c r="Q30">
         <v>2.91</v>
       </c>
       <c r="R30">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="S30">
         <v>1.39</v>
@@ -5241,22 +5241,22 @@
         <v>1.88</v>
       </c>
       <c r="AB30">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="AC30">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="AD30">
         <v>1.27</v>
       </c>
       <c r="AE30">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF30">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AG30">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5377,16 +5377,16 @@
         <v>3</v>
       </c>
       <c r="S31">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="T31">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="U31">
         <v>1.85</v>
       </c>
       <c r="V31">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="W31">
         <v>1.25</v>
@@ -5395,10 +5395,10 @@
         <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Z31">
-        <v>6.75</v>
+        <v>6.7</v>
       </c>
       <c r="AA31">
         <v>1.29</v>
@@ -5410,16 +5410,16 @@
         <v>1.75</v>
       </c>
       <c r="AD31">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AE31">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AF31">
         <v>1.53</v>
       </c>
       <c r="AG31">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>1.04</v>
       </c>
       <c r="AK31">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5534,22 +5534,22 @@
         <v>0</v>
       </c>
       <c r="Q32">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="R32">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="S32">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T32">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="U32">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="V32">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="W32">
         <v>1.2</v>
@@ -5558,31 +5558,31 @@
         <v>0</v>
       </c>
       <c r="Y32">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z32">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="AA32">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AB32">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="AC32">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AD32">
         <v>1.76</v>
       </c>
       <c r="AE32">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AF32">
         <v>1.66</v>
       </c>
       <c r="AG32">
-        <v>2.02</v>
+        <v>2.22</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AK32">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,25 +5688,25 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="O33">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="P33">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="Q33">
         <v>2.9</v>
       </c>
       <c r="R33">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="S33">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T33">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="U33">
         <v>2.55</v>
@@ -5715,19 +5715,19 @@
         <v>1.45</v>
       </c>
       <c r="W33">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X33">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y33">
         <v>1.22</v>
       </c>
       <c r="Z33">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
       <c r="AA33">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AB33">
         <v>1.97</v>
@@ -5742,7 +5742,7 @@
         <v>1.1</v>
       </c>
       <c r="AF33">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AG33">
         <v>2.25</v>
@@ -5872,7 +5872,7 @@
         <v>3.24</v>
       </c>
       <c r="U34">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="V34">
         <v>1.46</v>
@@ -5905,7 +5905,7 @@
         <v>1.15</v>
       </c>
       <c r="AF34">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AG34">
         <v>2.15</v>
@@ -6213,13 +6213,13 @@
         <v>1.19</v>
       </c>
       <c r="Z36">
-        <v>4.6</v>
+        <v>4.62</v>
       </c>
       <c r="AA36">
         <v>1.62</v>
       </c>
       <c r="AB36">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="AC36">
         <v>2.5</v>
@@ -6231,10 +6231,10 @@
         <v>1.16</v>
       </c>
       <c r="AF36">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG36">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="O37">
         <v>3.7</v>
       </c>
       <c r="P37">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Q37">
         <v>2.19</v>
@@ -6361,19 +6361,19 @@
         <v>3.4</v>
       </c>
       <c r="U37">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="V37">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W37">
         <v>1.08</v>
       </c>
       <c r="X37">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z37">
         <v>4.8</v>
@@ -6391,13 +6391,13 @@
         <v>1.44</v>
       </c>
       <c r="AE37">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF37">
         <v>1.57</v>
       </c>
       <c r="AG37">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="O39">
         <v>5.05</v>
       </c>
       <c r="P39">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="Q39">
         <v>1.83</v>
@@ -6687,43 +6687,43 @@
         <v>3.54</v>
       </c>
       <c r="U39">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="V39">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W39">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X39">
         <v>1</v>
       </c>
       <c r="Y39">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z39">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA39">
         <v>1.56</v>
       </c>
       <c r="AB39">
-        <v>2.41</v>
+        <v>2.46</v>
       </c>
       <c r="AC39">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="AD39">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AE39">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AF39">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AG39">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AK39">
         <v>3.03</v>
@@ -6829,7 +6829,7 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="O40">
         <v>3.4</v>
@@ -6838,13 +6838,13 @@
         <v>2.8</v>
       </c>
       <c r="Q40">
-        <v>2.84</v>
+        <v>2.63</v>
       </c>
       <c r="R40">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="S40">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T40">
         <v>3.25</v>
@@ -6856,13 +6856,13 @@
         <v>1.5</v>
       </c>
       <c r="W40">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X40">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y40">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z40">
         <v>4.2</v>
@@ -6874,7 +6874,7 @@
         <v>2.1</v>
       </c>
       <c r="AC40">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="AD40">
         <v>1.4</v>
@@ -6883,7 +6883,7 @@
         <v>1.17</v>
       </c>
       <c r="AF40">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG40">
         <v>2.3</v>
@@ -7318,10 +7318,10 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="O43">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="P43">
         <v>2.7</v>
@@ -7336,10 +7336,10 @@
         <v>1.39</v>
       </c>
       <c r="T43">
-        <v>2.73</v>
+        <v>3.08</v>
       </c>
       <c r="U43">
-        <v>2.69</v>
+        <v>2.58</v>
       </c>
       <c r="V43">
         <v>1.4</v>
@@ -7351,22 +7351,22 @@
         <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z43">
         <v>3.73</v>
       </c>
       <c r="AA43">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AB43">
         <v>1.88</v>
       </c>
       <c r="AC43">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="AD43">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE43">
         <v>1.13</v>
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AK43">
         <v>1.53</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.23</v>
+        <v>1.41</v>
       </c>
       <c r="O44">
-        <v>3.51</v>
+        <v>5</v>
       </c>
       <c r="P44">
-        <v>2.65</v>
+        <v>5.8</v>
       </c>
       <c r="Q44">
-        <v>2.72</v>
+        <v>1.85</v>
       </c>
       <c r="R44">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="S44">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="T44">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="U44">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="V44">
-        <v>1.52</v>
+        <v>1.77</v>
       </c>
       <c r="W44">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="X44">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y44">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="Z44">
-        <v>4.33</v>
+        <v>5.75</v>
       </c>
       <c r="AA44">
-        <v>1.69</v>
+        <v>1.44</v>
       </c>
       <c r="AB44">
-        <v>2.28</v>
+        <v>2.59</v>
       </c>
       <c r="AC44">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="AD44">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AE44">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AF44">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AG44">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AK44">
-        <v>1.71</v>
+        <v>2.7</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.41</v>
+        <v>2.15</v>
       </c>
       <c r="O45">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="P45">
-        <v>5.9</v>
+        <v>2.98</v>
       </c>
       <c r="Q45">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="R45">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="S45">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="T45">
+        <v>3.4</v>
+      </c>
+      <c r="U45">
+        <v>2.46</v>
+      </c>
+      <c r="V45">
+        <v>1.53</v>
+      </c>
+      <c r="W45">
+        <v>1.11</v>
+      </c>
+      <c r="X45">
+        <v>1.04</v>
+      </c>
+      <c r="Y45">
+        <v>1.18</v>
+      </c>
+      <c r="Z45">
         <v>4.33</v>
       </c>
-      <c r="U45">
-        <v>2.1</v>
-      </c>
-      <c r="V45">
-        <v>1.77</v>
-      </c>
-      <c r="W45">
-        <v>1.18</v>
-      </c>
-      <c r="X45">
-        <v>1.03</v>
-      </c>
-      <c r="Y45">
-        <v>1.08</v>
-      </c>
-      <c r="Z45">
-        <v>5.75</v>
-      </c>
       <c r="AA45">
-        <v>1.44</v>
+        <v>1.69</v>
       </c>
       <c r="AB45">
-        <v>2.59</v>
+        <v>2.28</v>
       </c>
       <c r="AC45">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="AD45">
-        <v>1.7</v>
+        <v>1.45</v>
       </c>
       <c r="AE45">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AF45">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AG45">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
       <c r="AK45">
-        <v>2.7</v>
+        <v>1.72</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7813,10 +7813,10 @@
         <v>3.51</v>
       </c>
       <c r="P46">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q46">
-        <v>5.25</v>
+        <v>5.35</v>
       </c>
       <c r="R46">
         <v>2.2</v>
@@ -7834,7 +7834,7 @@
         <v>1.38</v>
       </c>
       <c r="W46">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X46">
         <v>1.01</v>
@@ -7843,19 +7843,19 @@
         <v>1.27</v>
       </c>
       <c r="Z46">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="AA46">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AB46">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AC46">
         <v>3.34</v>
       </c>
       <c r="AD46">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AE46">
         <v>1.1</v>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>2.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK46">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7976,7 +7976,7 @@
         <v>3.1</v>
       </c>
       <c r="P47">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -8139,19 +8139,19 @@
         <v>2.85</v>
       </c>
       <c r="P48">
-        <v>2.43</v>
+        <v>2.58</v>
       </c>
       <c r="Q48">
         <v>3.36</v>
       </c>
       <c r="R48">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="S48">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="T48">
-        <v>2.39</v>
+        <v>2.62</v>
       </c>
       <c r="U48">
         <v>3.22</v>
@@ -8178,10 +8178,10 @@
         <v>1.63</v>
       </c>
       <c r="AC48">
-        <v>3.92</v>
+        <v>3.94</v>
       </c>
       <c r="AD48">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE48">
         <v>1.03</v>
@@ -8206,7 +8206,7 @@
         <v>1.38</v>
       </c>
       <c r="AK48">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8465,10 +8465,10 @@
         <v>3.5</v>
       </c>
       <c r="P50">
-        <v>2.37</v>
+        <v>2.6</v>
       </c>
       <c r="Q50">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="R50">
         <v>2.4</v>
@@ -8486,7 +8486,7 @@
         <v>1.54</v>
       </c>
       <c r="W50">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X50">
         <v>1.03</v>
@@ -8495,13 +8495,13 @@
         <v>1.18</v>
       </c>
       <c r="Z50">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AA50">
         <v>1.59</v>
       </c>
       <c r="AB50">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="AC50">
         <v>2.33</v>
@@ -8969,31 +8969,31 @@
         <v>2.65</v>
       </c>
       <c r="U53">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="V53">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W53">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X53">
         <v>1.05</v>
       </c>
       <c r="Y53">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="Z53">
-        <v>3.35</v>
+        <v>2.9</v>
       </c>
       <c r="AA53">
-        <v>1.88</v>
+        <v>2.14</v>
       </c>
       <c r="AB53">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="AC53">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="AD53">
         <v>1.25</v>
@@ -9126,16 +9126,16 @@
         <v>2.12</v>
       </c>
       <c r="S54">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T54">
+        <v>2.8</v>
+      </c>
+      <c r="U54">
         <v>2.65</v>
       </c>
-      <c r="U54">
-        <v>2.5</v>
-      </c>
       <c r="V54">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W54">
         <v>1.09</v>
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O58">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P58">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q58">
-        <v>3.64</v>
+        <v>3.62</v>
       </c>
       <c r="R58">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="S58">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T58">
-        <v>2.64</v>
+        <v>2.57</v>
       </c>
       <c r="U58">
-        <v>3.16</v>
+        <v>3.28</v>
       </c>
       <c r="V58">
         <v>1.31</v>
       </c>
       <c r="W58">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X58">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y58">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="Z58">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="AA58">
-        <v>2.19</v>
+        <v>2.29</v>
       </c>
       <c r="AB58">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AC58">
-        <v>3.92</v>
+        <v>4.2</v>
       </c>
       <c r="AD58">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AE58">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF58">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AG58">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
       <c r="AK58">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10095,25 +10095,25 @@
         <v>4.33</v>
       </c>
       <c r="P60">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="Q60">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="R60">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="S60">
         <v>1.17</v>
       </c>
       <c r="T60">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="U60">
-        <v>1.83</v>
+        <v>1.99</v>
       </c>
       <c r="V60">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="W60">
         <v>1.16</v>
@@ -10131,22 +10131,22 @@
         <v>1.36</v>
       </c>
       <c r="AB60">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AC60">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AD60">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="AE60">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AF60">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AG60">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10904,16 +10904,16 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.6</v>
+        <v>2.49</v>
       </c>
       <c r="O65">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="P65">
         <v>2.45</v>
       </c>
       <c r="Q65">
-        <v>3.36</v>
+        <v>3.22</v>
       </c>
       <c r="R65">
         <v>2.16</v>
@@ -10925,13 +10925,13 @@
         <v>2.59</v>
       </c>
       <c r="U65">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="V65">
         <v>1.33</v>
       </c>
       <c r="W65">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X65">
         <v>1.02</v>
@@ -10943,7 +10943,7 @@
         <v>3.28</v>
       </c>
       <c r="AA65">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AB65">
         <v>1.73</v>
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="O67">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="P67">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="Q67">
         <v>3.4</v>
@@ -11251,7 +11251,7 @@
         <v>3.05</v>
       </c>
       <c r="U67">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="V67">
         <v>1.4</v>
@@ -11269,7 +11269,7 @@
         <v>3.95</v>
       </c>
       <c r="AA67">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AB67">
         <v>1.85</v>
@@ -11278,10 +11278,10 @@
         <v>2.95</v>
       </c>
       <c r="AD67">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE67">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AF67">
         <v>1.67</v>
@@ -11303,7 +11303,7 @@
         <v>1.3</v>
       </c>
       <c r="AK67">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11393,37 +11393,37 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="O68">
-        <v>3.82</v>
+        <v>3.92</v>
       </c>
       <c r="P68">
-        <v>8.949999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="Q68">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="R68">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="S68">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T68">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="U68">
         <v>2.3</v>
       </c>
       <c r="V68">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W68">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X68">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y68">
         <v>1.2</v>
@@ -11435,19 +11435,19 @@
         <v>1.67</v>
       </c>
       <c r="AB68">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="AC68">
         <v>2.65</v>
       </c>
       <c r="AD68">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AE68">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF68">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG68">
         <v>1.9</v>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK68">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11571,31 +11571,31 @@
         <v>2.1</v>
       </c>
       <c r="S69">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T69">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="U69">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="V69">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W69">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X69">
         <v>1.03</v>
       </c>
       <c r="Y69">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="Z69">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="AA69">
-        <v>1.79</v>
+        <v>2.03</v>
       </c>
       <c r="AB69">
         <v>1.9</v>
@@ -12374,13 +12374,13 @@
         <v>1.37</v>
       </c>
       <c r="O74">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="P74">
-        <v>6.65</v>
+        <v>5.3</v>
       </c>
       <c r="Q74">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="R74">
         <v>2.7</v>
@@ -12389,40 +12389,40 @@
         <v>1.25</v>
       </c>
       <c r="T74">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="U74">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="V74">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W74">
         <v>1.12</v>
       </c>
       <c r="X74">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y74">
         <v>1.17</v>
       </c>
       <c r="Z74">
-        <v>4.65</v>
+        <v>4.7</v>
       </c>
       <c r="AA74">
         <v>1.57</v>
       </c>
       <c r="AB74">
-        <v>2.25</v>
+        <v>2.43</v>
       </c>
       <c r="AC74">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="AD74">
         <v>1.55</v>
       </c>
       <c r="AE74">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AF74">
         <v>1.7</v>
@@ -12441,7 +12441,7 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK74">
         <v>2.75</v>
@@ -12534,10 +12534,10 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="O75">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P75">
         <v>3.2</v>
@@ -12549,7 +12549,7 @@
         <v>2.15</v>
       </c>
       <c r="S75">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T75">
         <v>3</v>
@@ -12567,7 +12567,7 @@
         <v>1.05</v>
       </c>
       <c r="Y75">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z75">
         <v>3.6</v>
@@ -12579,16 +12579,16 @@
         <v>1.9</v>
       </c>
       <c r="AC75">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="AD75">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE75">
         <v>1.07</v>
       </c>
       <c r="AF75">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AG75">
         <v>1.98</v>
@@ -12715,13 +12715,13 @@
         <v>1.47</v>
       </c>
       <c r="T76">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="U76">
         <v>3.33</v>
       </c>
       <c r="V76">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W76">
         <v>1.04</v>
@@ -12739,7 +12739,7 @@
         <v>2.19</v>
       </c>
       <c r="AB76">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC76">
         <v>3.94</v>
@@ -12748,13 +12748,13 @@
         <v>1.25</v>
       </c>
       <c r="AE76">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF76">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AG76">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.23</v>
+        <v>1.37</v>
       </c>
       <c r="AK76">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12860,7 +12860,7 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="O77">
         <v>3.85</v>
@@ -12869,7 +12869,7 @@
         <v>4.4</v>
       </c>
       <c r="Q77">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="R77">
         <v>2.25</v>
@@ -12887,7 +12887,7 @@
         <v>1.42</v>
       </c>
       <c r="W77">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X77">
         <v>1.05</v>
@@ -12933,7 +12933,7 @@
         <v>1.13</v>
       </c>
       <c r="AK77">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13512,7 +13512,7 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="O81">
         <v>3.4</v>
@@ -13527,7 +13527,7 @@
         <v>2.14</v>
       </c>
       <c r="S81">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T81">
         <v>3.2</v>
@@ -13542,19 +13542,19 @@
         <v>1.08</v>
       </c>
       <c r="X81">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y81">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z81">
-        <v>3.68</v>
+        <v>3.9</v>
       </c>
       <c r="AA81">
         <v>1.75</v>
       </c>
       <c r="AB81">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="AC81">
         <v>2.78</v>
@@ -13566,10 +13566,10 @@
         <v>1.1</v>
       </c>
       <c r="AF81">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG81">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13675,13 +13675,13 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="O82">
         <v>3</v>
       </c>
       <c r="P82">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="Q82">
         <v>2.75</v>
@@ -13690,10 +13690,10 @@
         <v>1.95</v>
       </c>
       <c r="S82">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="T82">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="U82">
         <v>3.15</v>
@@ -13702,22 +13702,22 @@
         <v>1.31</v>
       </c>
       <c r="W82">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X82">
         <v>1.09</v>
       </c>
       <c r="Y82">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Z82">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AA82">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AB82">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AC82">
         <v>4.2</v>
@@ -13726,13 +13726,13 @@
         <v>1.2</v>
       </c>
       <c r="AE82">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF82">
         <v>1.95</v>
       </c>
       <c r="AG82">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>1.33</v>
       </c>
       <c r="AK82">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -14004,10 +14004,10 @@
         <v>2.15</v>
       </c>
       <c r="O84">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P84">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="Q84">
         <v>2.75</v>
@@ -14034,31 +14034,31 @@
         <v>1.02</v>
       </c>
       <c r="Y84">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z84">
         <v>3.82</v>
       </c>
       <c r="AA84">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AB84">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AC84">
         <v>2.8</v>
       </c>
       <c r="AD84">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE84">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF84">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AG84">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
         <v>1.36</v>
       </c>
       <c r="AK84">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14173,7 +14173,7 @@
         <v>2.75</v>
       </c>
       <c r="Q85">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="R85">
         <v>2.38</v>
@@ -14194,34 +14194,34 @@
         <v>1.14</v>
       </c>
       <c r="X85">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y85">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z85">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="AA85">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AB85">
         <v>2.2</v>
       </c>
       <c r="AC85">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AD85">
         <v>1.46</v>
       </c>
       <c r="AE85">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AF85">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AG85">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="O86">
         <v>3.5</v>
       </c>
       <c r="P86">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q86">
         <v>2.4</v>
@@ -14345,7 +14345,7 @@
         <v>1.3</v>
       </c>
       <c r="T86">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="U86">
         <v>2.88</v>
@@ -14366,7 +14366,7 @@
         <v>3.56</v>
       </c>
       <c r="AA86">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AB86">
         <v>1.95</v>
@@ -14384,7 +14384,7 @@
         <v>1.7</v>
       </c>
       <c r="AG86">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14662,25 +14662,25 @@
         <v>2.18</v>
       </c>
       <c r="Q88">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="R88">
         <v>2.22</v>
       </c>
       <c r="S88">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T88">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U88">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="V88">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W88">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X88">
         <v>1.04</v>
@@ -14695,22 +14695,22 @@
         <v>1.92</v>
       </c>
       <c r="AB88">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC88">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="AD88">
         <v>1.28</v>
       </c>
       <c r="AE88">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF88">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AG88">
-        <v>1.92</v>
+        <v>2.22</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AK88">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14816,13 +14816,13 @@
         </is>
       </c>
       <c r="N89">
-        <v>3.84</v>
+        <v>3.47</v>
       </c>
       <c r="O89">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="P89">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="Q89">
         <v>4.1</v>
@@ -14846,10 +14846,10 @@
         <v>1.15</v>
       </c>
       <c r="X89">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y89">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z89">
         <v>4.8</v>
@@ -14979,13 +14979,13 @@
         </is>
       </c>
       <c r="N90">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="O90">
         <v>3.95</v>
       </c>
       <c r="P90">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="Q90">
         <v>3.65</v>
@@ -14997,10 +14997,10 @@
         <v>1.22</v>
       </c>
       <c r="T90">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="U90">
-        <v>2.06</v>
+        <v>2.21</v>
       </c>
       <c r="V90">
         <v>1.68</v>
@@ -15009,7 +15009,7 @@
         <v>1.16</v>
       </c>
       <c r="X90">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y90">
         <v>1.14</v>
@@ -15021,10 +15021,10 @@
         <v>1.5</v>
       </c>
       <c r="AB90">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="AC90">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AD90">
         <v>1.65</v>
@@ -15142,19 +15142,19 @@
         </is>
       </c>
       <c r="N91">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O91">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P91">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Q91">
-        <v>4.33</v>
+        <v>4.39</v>
       </c>
       <c r="R91">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="S91">
         <v>1.37</v>
@@ -15163,31 +15163,31 @@
         <v>2.6</v>
       </c>
       <c r="U91">
-        <v>2.83</v>
+        <v>2.87</v>
       </c>
       <c r="V91">
         <v>1.34</v>
       </c>
       <c r="W91">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X91">
         <v>1.01</v>
       </c>
       <c r="Y91">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z91">
         <v>3</v>
       </c>
       <c r="AA91">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AB91">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AC91">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AD91">
         <v>1.25</v>
@@ -15196,10 +15196,10 @@
         <v>1.04</v>
       </c>
       <c r="AF91">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AG91">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.24</v>
+        <v>1.67</v>
       </c>
       <c r="AK91">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15308,7 +15308,7 @@
         <v>1.93</v>
       </c>
       <c r="O92">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P92">
         <v>3.4</v>
@@ -15320,16 +15320,16 @@
         <v>2.3</v>
       </c>
       <c r="S92">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T92">
-        <v>3.16</v>
+        <v>3.22</v>
       </c>
       <c r="U92">
         <v>2.39</v>
       </c>
       <c r="V92">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W92">
         <v>1.12</v>
@@ -15338,7 +15338,7 @@
         <v>1.01</v>
       </c>
       <c r="Y92">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z92">
         <v>4.05</v>
@@ -15350,19 +15350,19 @@
         <v>2.23</v>
       </c>
       <c r="AC92">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="AD92">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AE92">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF92">
         <v>1.57</v>
       </c>
       <c r="AG92">
-        <v>2.3</v>
+        <v>2.07</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15474,7 +15474,7 @@
         <v>3.5</v>
       </c>
       <c r="P93">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="Q93">
         <v>3.6</v>
@@ -15486,19 +15486,19 @@
         <v>1.3</v>
       </c>
       <c r="T93">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="U93">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="V93">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W93">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X93">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y93">
         <v>1.2</v>
@@ -15507,25 +15507,25 @@
         <v>3.9</v>
       </c>
       <c r="AA93">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AB93">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AC93">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AD93">
         <v>1.36</v>
       </c>
       <c r="AE93">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF93">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AG93">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
+        <v>1.67</v>
+      </c>
+      <c r="AK93">
         <v>1.24</v>
-      </c>
-      <c r="AK93">
-        <v>1.25</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15634,10 +15634,10 @@
         <v>1.46</v>
       </c>
       <c r="O94">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="P94">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="Q94">
         <v>1.95</v>
@@ -15649,7 +15649,7 @@
         <v>1.22</v>
       </c>
       <c r="T94">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="U94">
         <v>2.15</v>
@@ -15658,19 +15658,19 @@
         <v>1.7</v>
       </c>
       <c r="W94">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X94">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y94">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z94">
-        <v>4.9</v>
+        <v>5.06</v>
       </c>
       <c r="AA94">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AB94">
         <v>2.5</v>
@@ -15679,10 +15679,10 @@
         <v>2.15</v>
       </c>
       <c r="AD94">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AE94">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AF94">
         <v>1.57</v>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AK94">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -17264,25 +17264,25 @@
         <v>1.5</v>
       </c>
       <c r="O104">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="P104">
         <v>5.25</v>
       </c>
       <c r="Q104">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="R104">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="S104">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T104">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="U104">
-        <v>2.63</v>
+        <v>2.47</v>
       </c>
       <c r="V104">
         <v>1.44</v>
@@ -17294,10 +17294,10 @@
         <v>1.01</v>
       </c>
       <c r="Y104">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z104">
-        <v>3.68</v>
+        <v>3.45</v>
       </c>
       <c r="AA104">
         <v>1.85</v>
@@ -17306,7 +17306,7 @@
         <v>1.95</v>
       </c>
       <c r="AC104">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AD104">
         <v>1.33</v>
@@ -17315,10 +17315,10 @@
         <v>1.11</v>
       </c>
       <c r="AF104">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG104">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17750,13 +17750,13 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="O107">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P107">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="Q107">
         <v>2.6</v>
@@ -17765,7 +17765,7 @@
         <v>2.35</v>
       </c>
       <c r="S107">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T107">
         <v>3.3</v>
@@ -17777,7 +17777,7 @@
         <v>1.48</v>
       </c>
       <c r="W107">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X107">
         <v>1.04</v>
@@ -17786,16 +17786,16 @@
         <v>1.16</v>
       </c>
       <c r="Z107">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="AA107">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AB107">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AC107">
-        <v>2.63</v>
+        <v>2.57</v>
       </c>
       <c r="AD107">
         <v>1.4</v>
@@ -17823,7 +17823,7 @@
         <v>1.25</v>
       </c>
       <c r="AK107">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17913,25 +17913,25 @@
         </is>
       </c>
       <c r="N108">
-        <v>2.87</v>
+        <v>2.84</v>
       </c>
       <c r="O108">
         <v>3</v>
       </c>
       <c r="P108">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="Q108">
         <v>3.3</v>
       </c>
       <c r="R108">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="S108">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T108">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="U108">
         <v>2.62</v>
@@ -17943,7 +17943,7 @@
         <v>1.1</v>
       </c>
       <c r="X108">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y108">
         <v>1.29</v>
@@ -17958,7 +17958,7 @@
         <v>1.83</v>
       </c>
       <c r="AC108">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="AD108">
         <v>1.32</v>
@@ -17967,10 +17967,10 @@
         <v>1.13</v>
       </c>
       <c r="AF108">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AG108">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,7 +17983,7 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AK108">
         <v>1.4</v>
@@ -20204,10 +20204,10 @@
         <v>3.78</v>
       </c>
       <c r="Q122">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="R122">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="S122">
         <v>1.3</v>
@@ -20225,7 +20225,7 @@
         <v>1.12</v>
       </c>
       <c r="X122">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y122">
         <v>1.21</v>
@@ -20234,7 +20234,7 @@
         <v>3.85</v>
       </c>
       <c r="AA122">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AB122">
         <v>2.1</v>
@@ -20243,16 +20243,16 @@
         <v>2.7</v>
       </c>
       <c r="AD122">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE122">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF122">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AG122">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20358,13 +20358,13 @@
         </is>
       </c>
       <c r="N123">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="O123">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="P123">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q123">
         <v>3.4</v>
@@ -20373,49 +20373,49 @@
         <v>2.15</v>
       </c>
       <c r="S123">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T123">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="U123">
-        <v>2.8</v>
+        <v>3.04</v>
       </c>
       <c r="V123">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W123">
         <v>1.06</v>
       </c>
       <c r="X123">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y123">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z123">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AA123">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB123">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AC123">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AD123">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE123">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF123">
         <v>1.75</v>
       </c>
       <c r="AG123">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -21339,16 +21339,16 @@
         <v>4.4</v>
       </c>
       <c r="O129">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="P129">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="Q129">
         <v>4.4</v>
       </c>
       <c r="R129">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="S129">
         <v>1.21</v>
@@ -21357,7 +21357,7 @@
         <v>3.58</v>
       </c>
       <c r="U129">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="V129">
         <v>1.65</v>
@@ -21369,10 +21369,10 @@
         <v>1.02</v>
       </c>
       <c r="Y129">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z129">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="AA129">
         <v>1.4</v>
@@ -21387,13 +21387,13 @@
         <v>1.66</v>
       </c>
       <c r="AE129">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF129">
         <v>1.45</v>
       </c>
       <c r="AG129">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AK129">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21505,10 +21505,10 @@
         <v>3.4</v>
       </c>
       <c r="P130">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Q130">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="R130">
         <v>2.19</v>
@@ -21544,19 +21544,19 @@
         <v>2.07</v>
       </c>
       <c r="AC130">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="AD130">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE130">
         <v>1.12</v>
       </c>
       <c r="AF130">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AG130">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -22477,13 +22477,13 @@
         </is>
       </c>
       <c r="N136">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="O136">
         <v>3.95</v>
       </c>
       <c r="P136">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="Q136">
         <v>3.1</v>
@@ -22510,7 +22510,7 @@
         <v>1.03</v>
       </c>
       <c r="Y136">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="Z136">
         <v>5.25</v>
@@ -22522,10 +22522,10 @@
         <v>2.45</v>
       </c>
       <c r="AC136">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AD136">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AE136">
         <v>1.22</v>
@@ -22643,10 +22643,10 @@
         <v>5.25</v>
       </c>
       <c r="O137">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P137">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="Q137">
         <v>6</v>
@@ -22658,7 +22658,7 @@
         <v>1.36</v>
       </c>
       <c r="T137">
-        <v>3</v>
+        <v>3.03</v>
       </c>
       <c r="U137">
         <v>2.88</v>
@@ -22691,13 +22691,13 @@
         <v>1.33</v>
       </c>
       <c r="AE137">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF137">
         <v>1.91</v>
       </c>
       <c r="AG137">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>2.46</v>
       </c>
       <c r="AK137">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -23301,10 +23301,10 @@
         <v>4.5</v>
       </c>
       <c r="Q141">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="R141">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="S141">
         <v>1.25</v>
@@ -23313,10 +23313,10 @@
         <v>3.5</v>
       </c>
       <c r="U141">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="V141">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="W141">
         <v>1.13</v>
@@ -23325,7 +23325,7 @@
         <v>1.01</v>
       </c>
       <c r="Y141">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z141">
         <v>3.95</v>
@@ -23334,22 +23334,22 @@
         <v>1.61</v>
       </c>
       <c r="AB141">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AC141">
-        <v>2.42</v>
+        <v>2.51</v>
       </c>
       <c r="AD141">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE141">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF141">
         <v>1.62</v>
       </c>
       <c r="AG141">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="AH141" t="inlineStr">
         <is>
@@ -23624,7 +23624,7 @@
         <v>3.25</v>
       </c>
       <c r="P143">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="Q143">
         <v>2.5</v>
@@ -23633,16 +23633,16 @@
         <v>2.15</v>
       </c>
       <c r="S143">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="T143">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="U143">
         <v>2.75</v>
       </c>
       <c r="V143">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W143">
         <v>1.05</v>
@@ -23657,25 +23657,25 @@
         <v>3.6</v>
       </c>
       <c r="AA143">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AB143">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AC143">
-        <v>2.99</v>
+        <v>2.95</v>
       </c>
       <c r="AD143">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE143">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF143">
         <v>1.62</v>
       </c>
       <c r="AG143">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AH143" t="inlineStr">
         <is>
@@ -23784,7 +23784,7 @@
         <v>1.35</v>
       </c>
       <c r="O144">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="P144">
         <v>6</v>
@@ -23799,7 +23799,7 @@
         <v>1.3</v>
       </c>
       <c r="T144">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="U144">
         <v>2.32</v>
@@ -23832,7 +23832,7 @@
         <v>1.41</v>
       </c>
       <c r="AE144">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF144">
         <v>1.83</v>
@@ -23959,7 +23959,7 @@
         <v>2</v>
       </c>
       <c r="S145">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T145">
         <v>2.44</v>
@@ -23980,28 +23980,28 @@
         <v>1.4</v>
       </c>
       <c r="Z145">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="AA145">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="AB145">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AC145">
-        <v>3.86</v>
+        <v>4.33</v>
       </c>
       <c r="AD145">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE145">
         <v>1.06</v>
       </c>
       <c r="AF145">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AG145">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AK145">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24119,7 +24119,7 @@
         <v>6.5</v>
       </c>
       <c r="R146">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="S146">
         <v>1.35</v>
@@ -24128,7 +24128,7 @@
         <v>3</v>
       </c>
       <c r="U146">
-        <v>2.72</v>
+        <v>2.63</v>
       </c>
       <c r="V146">
         <v>1.47</v>
@@ -24137,25 +24137,25 @@
         <v>1.09</v>
       </c>
       <c r="X146">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y146">
         <v>1.25</v>
       </c>
       <c r="Z146">
-        <v>3.8</v>
+        <v>3.68</v>
       </c>
       <c r="AA146">
         <v>1.75</v>
       </c>
       <c r="AB146">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="AC146">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AD146">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AE146">
         <v>1.13</v>
@@ -25100,16 +25100,16 @@
         <v>2.35</v>
       </c>
       <c r="S152">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T152">
-        <v>3.6</v>
+        <v>3.32</v>
       </c>
       <c r="U152">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="V152">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W152">
         <v>1.12</v>
@@ -25124,22 +25124,22 @@
         <v>4.25</v>
       </c>
       <c r="AA152">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AB152">
         <v>2.2</v>
       </c>
       <c r="AC152">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="AD152">
         <v>1.44</v>
       </c>
       <c r="AE152">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF152">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AG152">
         <v>2.2</v>
@@ -25574,34 +25574,34 @@
         </is>
       </c>
       <c r="N155">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="O155">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="P155">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q155">
         <v>1.44</v>
       </c>
       <c r="R155">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="S155">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="T155">
         <v>4.4</v>
       </c>
       <c r="U155">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="V155">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="W155">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X155">
         <v>1.01</v>
@@ -25610,10 +25610,10 @@
         <v>1.04</v>
       </c>
       <c r="Z155">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="AA155">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AB155">
         <v>3.08</v>
@@ -25622,13 +25622,13 @@
         <v>1.82</v>
       </c>
       <c r="AD155">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="AE155">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AF155">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AG155">
         <v>1.8</v>
@@ -25644,10 +25644,10 @@
         </is>
       </c>
       <c r="AJ155">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AK155">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25737,28 +25737,28 @@
         </is>
       </c>
       <c r="N156">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="O156">
         <v>3.2</v>
       </c>
       <c r="P156">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="Q156">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="R156">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="S156">
         <v>1.42</v>
       </c>
       <c r="T156">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="U156">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="V156">
         <v>1.32</v>
@@ -25767,25 +25767,25 @@
         <v>1.07</v>
       </c>
       <c r="X156">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y156">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z156">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="AA156">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AB156">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AC156">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AD156">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE156">
         <v>1.03</v>
@@ -25794,7 +25794,7 @@
         <v>1.83</v>
       </c>
       <c r="AG156">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25810,7 +25810,7 @@
         <v>1.3</v>
       </c>
       <c r="AK156">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -25909,10 +25909,10 @@
         <v>5</v>
       </c>
       <c r="Q157">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="R157">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="S157">
         <v>1.3</v>
@@ -25924,22 +25924,22 @@
         <v>2.4</v>
       </c>
       <c r="V157">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W157">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X157">
         <v>1.04</v>
       </c>
       <c r="Y157">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z157">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="AA157">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AB157">
         <v>2.05</v>
@@ -25951,29 +25951,29 @@
         <v>1.43</v>
       </c>
       <c r="AE157">
+        <v>1.15</v>
+      </c>
+      <c r="AF157">
+        <v>1.71</v>
+      </c>
+      <c r="AG157">
+        <v>1.9</v>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ157">
         <v>1.14</v>
       </c>
-      <c r="AF157">
-        <v>1.7</v>
-      </c>
-      <c r="AG157">
-        <v>1.92</v>
-      </c>
-      <c r="AH157" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI157" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ157">
-        <v>1.1</v>
-      </c>
       <c r="AK157">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26063,13 +26063,13 @@
         </is>
       </c>
       <c r="N158">
-        <v>2.51</v>
+        <v>2.55</v>
       </c>
       <c r="O158">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="P158">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="Q158">
         <v>3.1</v>
@@ -26081,7 +26081,7 @@
         <v>1.5</v>
       </c>
       <c r="T158">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="U158">
         <v>3.6</v>
@@ -26105,10 +26105,10 @@
         <v>2.31</v>
       </c>
       <c r="AB158">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="AC158">
-        <v>4.13</v>
+        <v>4.11</v>
       </c>
       <c r="AD158">
         <v>1.18</v>
@@ -26117,10 +26117,10 @@
         <v>1.03</v>
       </c>
       <c r="AF158">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AG158">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26229,16 +26229,16 @@
         <v>1.37</v>
       </c>
       <c r="O159">
-        <v>5.3</v>
+        <v>4.65</v>
       </c>
       <c r="P159">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="Q159">
         <v>1.75</v>
       </c>
       <c r="R159">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="S159">
         <v>1.15</v>
@@ -26253,13 +26253,13 @@
         <v>2.04</v>
       </c>
       <c r="W159">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="X159">
         <v>1.01</v>
       </c>
       <c r="Y159">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Z159">
         <v>7.8</v>
@@ -26277,13 +26277,13 @@
         <v>2.21</v>
       </c>
       <c r="AE159">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AF159">
         <v>1.36</v>
       </c>
       <c r="AG159">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="AH159" t="inlineStr">
         <is>
@@ -26389,13 +26389,13 @@
         </is>
       </c>
       <c r="N160">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="O160">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P160">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="Q160">
         <v>2.28</v>
@@ -26407,10 +26407,10 @@
         <v>1.18</v>
       </c>
       <c r="T160">
-        <v>4.05</v>
+        <v>4.4</v>
       </c>
       <c r="U160">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="V160">
         <v>1.8</v>
@@ -26425,28 +26425,28 @@
         <v>1.07</v>
       </c>
       <c r="Z160">
-        <v>5.95</v>
+        <v>6.5</v>
       </c>
       <c r="AA160">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AB160">
         <v>2.88</v>
       </c>
       <c r="AC160">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AD160">
         <v>1.86</v>
       </c>
       <c r="AE160">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AF160">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AG160">
-        <v>3.02</v>
+        <v>2.5</v>
       </c>
       <c r="AH160" t="inlineStr">
         <is>
@@ -26462,7 +26462,7 @@
         <v>1.36</v>
       </c>
       <c r="AK160">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AL160">
         <v>0</v>
@@ -26561,10 +26561,10 @@
         <v>1.5</v>
       </c>
       <c r="Q161">
-        <v>4.28</v>
+        <v>4.24</v>
       </c>
       <c r="R161">
-        <v>3.18</v>
+        <v>3.14</v>
       </c>
       <c r="S161">
         <v>1.11</v>
@@ -26573,13 +26573,13 @@
         <v>6</v>
       </c>
       <c r="U161">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="V161">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="W161">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X161">
         <v>1</v>
@@ -26591,22 +26591,22 @@
         <v>13</v>
       </c>
       <c r="AA161">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AB161">
-        <v>5.1</v>
+        <v>5.25</v>
       </c>
       <c r="AC161">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AD161">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AE161">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="AF161">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AG161">
         <v>3.75</v>
@@ -26625,7 +26625,7 @@
         <v>2.63</v>
       </c>
       <c r="AK161">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -26730,7 +26730,7 @@
         <v>2.4</v>
       </c>
       <c r="S162">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="T162">
         <v>3.9</v>
@@ -26739,19 +26739,19 @@
         <v>1.9</v>
       </c>
       <c r="V162">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="W162">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="X162">
         <v>1.02</v>
       </c>
       <c r="Y162">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Z162">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="AA162">
         <v>1.4</v>
@@ -26884,10 +26884,10 @@
         <v>3.38</v>
       </c>
       <c r="P163">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="Q163">
-        <v>3.42</v>
+        <v>3.29</v>
       </c>
       <c r="R163">
         <v>2.03</v>
@@ -26896,7 +26896,7 @@
         <v>1.4</v>
       </c>
       <c r="T163">
-        <v>2.85</v>
+        <v>2.96</v>
       </c>
       <c r="U163">
         <v>2.89</v>
@@ -26905,7 +26905,7 @@
         <v>1.39</v>
       </c>
       <c r="W163">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X163">
         <v>1.01</v>
@@ -26951,7 +26951,7 @@
         <v>1.34</v>
       </c>
       <c r="AK163">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AL163">
         <v>0</v>
@@ -27041,10 +27041,10 @@
         </is>
       </c>
       <c r="N164">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="O164">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="P164">
         <v>2.75</v>
@@ -27065,13 +27065,13 @@
         <v>3.3</v>
       </c>
       <c r="V164">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="W164">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X164">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Y164">
         <v>1.5</v>
@@ -27089,7 +27089,7 @@
         <v>5</v>
       </c>
       <c r="AD164">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AE164">
         <v>1.02</v>
@@ -27114,7 +27114,7 @@
         <v>1.4</v>
       </c>
       <c r="AK164">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL164">
         <v>0</v>
@@ -27530,13 +27530,13 @@
         </is>
       </c>
       <c r="N167">
-        <v>6.7</v>
+        <v>5.5</v>
       </c>
       <c r="O167">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="P167">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="Q167">
         <v>0</v>
@@ -27862,19 +27862,19 @@
         <v>3</v>
       </c>
       <c r="P169">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="Q169">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="R169">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="S169">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="T169">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="U169">
         <v>3.94</v>
@@ -27886,7 +27886,7 @@
         <v>1.04</v>
       </c>
       <c r="X169">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Y169">
         <v>1.57</v>
@@ -27901,7 +27901,7 @@
         <v>1.44</v>
       </c>
       <c r="AC169">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="AD169">
         <v>1.14</v>
@@ -27913,7 +27913,7 @@
         <v>2.3</v>
       </c>
       <c r="AG169">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AH169" t="inlineStr">
         <is>
@@ -27929,7 +27929,7 @@
         <v>1.4</v>
       </c>
       <c r="AK169">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AL169">
         <v>0</v>
@@ -28019,13 +28019,13 @@
         </is>
       </c>
       <c r="N170">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="O170">
         <v>3.7</v>
       </c>
       <c r="P170">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="Q170">
         <v>2.2</v>
@@ -28055,16 +28055,16 @@
         <v>1.17</v>
       </c>
       <c r="Z170">
-        <v>3.96</v>
+        <v>3.65</v>
       </c>
       <c r="AA170">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AB170">
         <v>2.04</v>
       </c>
       <c r="AC170">
-        <v>2.59</v>
+        <v>3</v>
       </c>
       <c r="AD170">
         <v>1.39</v>
@@ -28073,7 +28073,7 @@
         <v>1.14</v>
       </c>
       <c r="AF170">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG170">
         <v>2.08</v>
@@ -28089,7 +28089,7 @@
         </is>
       </c>
       <c r="AJ170">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AK170">
         <v>1.8</v>
@@ -28188,16 +28188,16 @@
         <v>4.9</v>
       </c>
       <c r="P171">
-        <v>7.5</v>
+        <v>9.6</v>
       </c>
       <c r="Q171">
         <v>1.8</v>
       </c>
       <c r="R171">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S171">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="T171">
         <v>3</v>
@@ -28224,16 +28224,16 @@
         <v>1.91</v>
       </c>
       <c r="AB171">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AC171">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="AD171">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE171">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF171">
         <v>2.3</v>
@@ -28345,22 +28345,22 @@
         </is>
       </c>
       <c r="N172">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="O172">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="P172">
         <v>7.4</v>
       </c>
       <c r="Q172">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="R172">
         <v>2.64</v>
       </c>
       <c r="S172">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T172">
         <v>3.22</v>
@@ -28378,31 +28378,31 @@
         <v>1</v>
       </c>
       <c r="Y172">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="Z172">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="AA172">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AB172">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="AC172">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="AD172">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AE172">
         <v>1.14</v>
       </c>
       <c r="AF172">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AG172">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH172" t="inlineStr">
         <is>
@@ -28415,10 +28415,10 @@
         </is>
       </c>
       <c r="AJ172">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AK172">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="AL172">
         <v>0</v>
@@ -28526,7 +28526,7 @@
         <v>1.22</v>
       </c>
       <c r="T173">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="U173">
         <v>2.25</v>
@@ -28578,7 +28578,7 @@
         </is>
       </c>
       <c r="AJ173">
-        <v>1.17</v>
+        <v>1.82</v>
       </c>
       <c r="AK173">
         <v>1.22</v>
@@ -29160,22 +29160,22 @@
         </is>
       </c>
       <c r="N177">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="O177">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P177">
         <v>4.55</v>
       </c>
       <c r="Q177">
-        <v>2.21</v>
+        <v>2.05</v>
       </c>
       <c r="R177">
-        <v>2.21</v>
+        <v>2.45</v>
       </c>
       <c r="S177">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T177">
         <v>3.4</v>
@@ -29184,40 +29184,40 @@
         <v>2.3</v>
       </c>
       <c r="V177">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W177">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X177">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y177">
         <v>1.17</v>
       </c>
       <c r="Z177">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AA177">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AB177">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AC177">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="AD177">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AE177">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AF177">
         <v>1.62</v>
       </c>
       <c r="AG177">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29230,10 +29230,10 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AK177">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29323,34 +29323,34 @@
         </is>
       </c>
       <c r="N178">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="O178">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P178">
         <v>2.7</v>
       </c>
       <c r="Q178">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="R178">
         <v>2.4</v>
       </c>
       <c r="S178">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="T178">
-        <v>2.95</v>
+        <v>3.6</v>
       </c>
       <c r="U178">
         <v>2.3</v>
       </c>
       <c r="V178">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W178">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X178">
         <v>1.04</v>
@@ -29359,28 +29359,28 @@
         <v>1.18</v>
       </c>
       <c r="Z178">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AA178">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AB178">
         <v>2.25</v>
       </c>
       <c r="AC178">
-        <v>2.38</v>
+        <v>2.49</v>
       </c>
       <c r="AD178">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AE178">
         <v>1.19</v>
       </c>
       <c r="AF178">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AG178">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AH178" t="inlineStr">
         <is>
@@ -29396,7 +29396,7 @@
         <v>1.25</v>
       </c>
       <c r="AK178">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AL178">
         <v>0</v>
@@ -29495,16 +29495,16 @@
         <v>1.57</v>
       </c>
       <c r="Q179">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="R179">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="S179">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T179">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U179">
         <v>2.63</v>
@@ -29556,7 +29556,7 @@
         </is>
       </c>
       <c r="AJ179">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK179">
         <v>1.13</v>
@@ -29673,7 +29673,7 @@
         <v>2.5</v>
       </c>
       <c r="V180">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W180">
         <v>1.07</v>
@@ -29703,7 +29703,7 @@
         <v>1.13</v>
       </c>
       <c r="AF180">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AG180">
         <v>2.15</v>
@@ -29719,7 +29719,7 @@
         </is>
       </c>
       <c r="AJ180">
-        <v>1.29</v>
+        <v>1.85</v>
       </c>
       <c r="AK180">
         <v>1.25</v>
@@ -29812,7 +29812,7 @@
         </is>
       </c>
       <c r="N181">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="O181">
         <v>3.8</v>
@@ -29839,31 +29839,31 @@
         <v>1.4</v>
       </c>
       <c r="W181">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X181">
         <v>1.01</v>
       </c>
       <c r="Y181">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z181">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AA181">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AB181">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AC181">
         <v>3.08</v>
       </c>
       <c r="AD181">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE181">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AF181">
         <v>1.83</v>
@@ -29990,16 +29990,16 @@
         <v>1.98</v>
       </c>
       <c r="S182">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="T182">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="U182">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="V182">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W182">
         <v>1.01</v>
@@ -30014,7 +30014,7 @@
         <v>2.64</v>
       </c>
       <c r="AA182">
-        <v>2.44</v>
+        <v>2.51</v>
       </c>
       <c r="AB182">
         <v>1.53</v>
@@ -30023,7 +30023,7 @@
         <v>4.88</v>
       </c>
       <c r="AD182">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AE182">
         <v>1.01</v>
@@ -30045,10 +30045,10 @@
         </is>
       </c>
       <c r="AJ182">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AK182">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="AL182">
         <v>0</v>
@@ -30153,13 +30153,13 @@
         <v>1.83</v>
       </c>
       <c r="S183">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="T183">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="U183">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="V183">
         <v>1.2</v>
@@ -30304,55 +30304,55 @@
         <v>2.55</v>
       </c>
       <c r="O184">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="P184">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Q184">
-        <v>3.62</v>
+        <v>3.44</v>
       </c>
       <c r="R184">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="S184">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="T184">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="U184">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="V184">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W184">
         <v>1.03</v>
       </c>
       <c r="X184">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Y184">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="Z184">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="AA184">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="AB184">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AC184">
-        <v>6.1</v>
+        <v>5.9</v>
       </c>
       <c r="AD184">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AE184">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF184">
         <v>2.38</v>
@@ -30464,13 +30464,13 @@
         </is>
       </c>
       <c r="N185">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="O185">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P185">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="Q185">
         <v>3.25</v>
@@ -30482,10 +30482,10 @@
         <v>1.45</v>
       </c>
       <c r="T185">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="U185">
-        <v>3.2</v>
+        <v>3.48</v>
       </c>
       <c r="V185">
         <v>1.29</v>
@@ -30500,19 +30500,19 @@
         <v>1.46</v>
       </c>
       <c r="Z185">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="AA185">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="AB185">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AC185">
         <v>4.55</v>
       </c>
       <c r="AD185">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AE185">
         <v>1.05</v>
@@ -30627,28 +30627,28 @@
         </is>
       </c>
       <c r="N186">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="O186">
         <v>3.3</v>
       </c>
       <c r="P186">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="Q186">
-        <v>3.65</v>
+        <v>3.73</v>
       </c>
       <c r="R186">
         <v>2.2</v>
       </c>
       <c r="S186">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T186">
-        <v>3.25</v>
+        <v>2.82</v>
       </c>
       <c r="U186">
-        <v>2.63</v>
+        <v>2.53</v>
       </c>
       <c r="V186">
         <v>1.43</v>
@@ -30669,19 +30669,19 @@
         <v>1.75</v>
       </c>
       <c r="AB186">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AC186">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="AD186">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="AE186">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF186">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG186">
         <v>2.15</v>
@@ -31128,13 +31128,13 @@
         <v>1.95</v>
       </c>
       <c r="R189">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="S189">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T189">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="U189">
         <v>1.91</v>
@@ -31149,16 +31149,16 @@
         <v>1.02</v>
       </c>
       <c r="Y189">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z189">
         <v>6.25</v>
       </c>
       <c r="AA189">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB189">
-        <v>2.9</v>
+        <v>2.68</v>
       </c>
       <c r="AC189">
         <v>2.16</v>
@@ -31288,10 +31288,10 @@
         <v>1.74</v>
       </c>
       <c r="Q190">
-        <v>4.4</v>
+        <v>5.05</v>
       </c>
       <c r="R190">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S190">
         <v>1.36</v>
@@ -31303,7 +31303,7 @@
         <v>2.75</v>
       </c>
       <c r="V190">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W190">
         <v>1.09</v>
@@ -31327,16 +31327,16 @@
         <v>3.16</v>
       </c>
       <c r="AD190">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE190">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF190">
         <v>1.78</v>
       </c>
       <c r="AG190">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AH190" t="inlineStr">
         <is>
@@ -31442,10 +31442,10 @@
         </is>
       </c>
       <c r="N191">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="O191">
-        <v>4.5</v>
+        <v>4.35</v>
       </c>
       <c r="P191">
         <v>6.2</v>
@@ -31469,10 +31469,10 @@
         <v>1.53</v>
       </c>
       <c r="W191">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X191">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y191">
         <v>1.19</v>
@@ -31481,16 +31481,16 @@
         <v>4.1</v>
       </c>
       <c r="AA191">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB191">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC191">
         <v>2.7</v>
       </c>
       <c r="AD191">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AE191">
         <v>1.15</v>
@@ -32592,19 +32592,19 @@
         <v>4.17</v>
       </c>
       <c r="Q198">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="R198">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S198">
         <v>1.37</v>
       </c>
       <c r="T198">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="U198">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="V198">
         <v>1.4</v>
@@ -32616,31 +32616,31 @@
         <v>1.03</v>
       </c>
       <c r="Y198">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Z198">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="AA198">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AB198">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AC198">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="AD198">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AE198">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF198">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG198">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AH198" t="inlineStr">
         <is>
@@ -32656,7 +32656,7 @@
         <v>1.29</v>
       </c>
       <c r="AK198">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="AL198">
         <v>0</v>
@@ -32746,13 +32746,13 @@
         </is>
       </c>
       <c r="N199">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O199">
         <v>3.3</v>
       </c>
       <c r="P199">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="Q199">
         <v>2.82</v>
@@ -32761,13 +32761,13 @@
         <v>2.1</v>
       </c>
       <c r="S199">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T199">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="U199">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="V199">
         <v>1.38</v>
@@ -32776,7 +32776,7 @@
         <v>1.05</v>
       </c>
       <c r="X199">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y199">
         <v>1.3</v>
@@ -32794,10 +32794,10 @@
         <v>3.45</v>
       </c>
       <c r="AD199">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AE199">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF199">
         <v>1.7</v>
@@ -32918,7 +32918,7 @@
         <v>6.22</v>
       </c>
       <c r="Q200">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="R200">
         <v>2.2</v>
@@ -32930,13 +32930,13 @@
         <v>3</v>
       </c>
       <c r="U200">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="V200">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W200">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X200">
         <v>1.05</v>
@@ -32948,25 +32948,25 @@
         <v>3.5</v>
       </c>
       <c r="AA200">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AB200">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AC200">
         <v>3.3</v>
       </c>
       <c r="AD200">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE200">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF200">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AG200">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="AH200" t="inlineStr">
         <is>
@@ -33072,13 +33072,13 @@
         </is>
       </c>
       <c r="N201">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="O201">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="P201">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Q201">
         <v>0</v>
@@ -33244,13 +33244,13 @@
         <v>4.05</v>
       </c>
       <c r="Q202">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="R202">
-        <v>2.1</v>
+        <v>1.86</v>
       </c>
       <c r="S202">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="T202">
         <v>2.44</v>
@@ -33259,13 +33259,13 @@
         <v>3.25</v>
       </c>
       <c r="V202">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W202">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X202">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y202">
         <v>1.37</v>
@@ -33274,25 +33274,25 @@
         <v>2.56</v>
       </c>
       <c r="AA202">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="AB202">
         <v>1.52</v>
       </c>
       <c r="AC202">
-        <v>4.45</v>
+        <v>4.33</v>
       </c>
       <c r="AD202">
         <v>1.14</v>
       </c>
       <c r="AE202">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AF202">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AG202">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AH202" t="inlineStr">
         <is>
@@ -33305,10 +33305,10 @@
         </is>
       </c>
       <c r="AJ202">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AK202">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AL202">
         <v>0</v>
@@ -33398,64 +33398,64 @@
         </is>
       </c>
       <c r="N203">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="O203">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="P203">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="Q203">
-        <v>2.87</v>
+        <v>2.55</v>
       </c>
       <c r="R203">
-        <v>1.86</v>
+        <v>2.12</v>
       </c>
       <c r="S203">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="T203">
-        <v>2.65</v>
+        <v>2.54</v>
       </c>
       <c r="U203">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="V203">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W203">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X203">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y203">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z203">
         <v>2.95</v>
       </c>
       <c r="AA203">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="AB203">
         <v>1.66</v>
       </c>
       <c r="AC203">
-        <v>4.05</v>
+        <v>3.6</v>
       </c>
       <c r="AD203">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AE203">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF203">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AG203">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AH203" t="inlineStr">
         <is>
@@ -33471,7 +33471,7 @@
         <v>1.29</v>
       </c>
       <c r="AK203">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AL203">
         <v>0</v>
@@ -33564,13 +33564,13 @@
         <v>2.27</v>
       </c>
       <c r="O204">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P204">
         <v>2.62</v>
       </c>
       <c r="Q204">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="R204">
         <v>2.02</v>
@@ -33579,16 +33579,16 @@
         <v>1.33</v>
       </c>
       <c r="T204">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="U204">
         <v>2.7</v>
       </c>
       <c r="V204">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W204">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X204">
         <v>1.05</v>
@@ -33600,19 +33600,19 @@
         <v>3.3</v>
       </c>
       <c r="AA204">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AB204">
         <v>1.8</v>
       </c>
       <c r="AC204">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AD204">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AE204">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF204">
         <v>1.7</v>
@@ -33733,55 +33733,55 @@
         <v>0</v>
       </c>
       <c r="Q205">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="R205">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S205">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T205">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="U205">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="V205">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="W205">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X205">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y205">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z205">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AA205">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB205">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AC205">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AD205">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AE205">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AF205">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AG205">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AH205" t="inlineStr">
         <is>
@@ -33794,10 +33794,10 @@
         </is>
       </c>
       <c r="AJ205">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK205">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AL205">
         <v>0</v>
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G206">
@@ -33887,64 +33887,64 @@
         </is>
       </c>
       <c r="N206">
-        <v>4.2</v>
+        <v>1.51</v>
       </c>
       <c r="O206">
-        <v>3.5</v>
+        <v>4.05</v>
       </c>
       <c r="P206">
-        <v>1.68</v>
+        <v>4.8</v>
       </c>
       <c r="Q206">
-        <v>4.75</v>
+        <v>1.91</v>
       </c>
       <c r="R206">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="S206">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="T206">
-        <v>2.96</v>
+        <v>3.3</v>
       </c>
       <c r="U206">
-        <v>2.55</v>
+        <v>2.18</v>
       </c>
       <c r="V206">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="W206">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X206">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y206">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z206">
-        <v>3.58</v>
+        <v>4.95</v>
       </c>
       <c r="AA206">
-        <v>1.83</v>
+        <v>1.46</v>
       </c>
       <c r="AB206">
-        <v>1.95</v>
+        <v>2.38</v>
       </c>
       <c r="AC206">
-        <v>2.92</v>
+        <v>2.23</v>
       </c>
       <c r="AD206">
-        <v>1.31</v>
+        <v>1.57</v>
       </c>
       <c r="AE206">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="AF206">
-        <v>1.72</v>
+        <v>1.56</v>
       </c>
       <c r="AG206">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="AH206" t="inlineStr">
         <is>
@@ -33957,10 +33957,10 @@
         </is>
       </c>
       <c r="AJ206">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AK206">
-        <v>1.2</v>
+        <v>2.29</v>
       </c>
       <c r="AL206">
         <v>0</v>
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G207">
@@ -34050,80 +34050,80 @@
         </is>
       </c>
       <c r="N207">
-        <v>1.48</v>
+        <v>3.9</v>
       </c>
       <c r="O207">
-        <v>4.15</v>
+        <v>3.55</v>
       </c>
       <c r="P207">
-        <v>4.8</v>
+        <v>1.68</v>
       </c>
       <c r="Q207">
+        <v>4.7</v>
+      </c>
+      <c r="R207">
+        <v>2.2</v>
+      </c>
+      <c r="S207">
+        <v>1.34</v>
+      </c>
+      <c r="T207">
+        <v>2.96</v>
+      </c>
+      <c r="U207">
+        <v>2.55</v>
+      </c>
+      <c r="V207">
+        <v>1.44</v>
+      </c>
+      <c r="W207">
+        <v>1.05</v>
+      </c>
+      <c r="X207">
+        <v>1.05</v>
+      </c>
+      <c r="Y207">
+        <v>1.21</v>
+      </c>
+      <c r="Z207">
+        <v>3.5</v>
+      </c>
+      <c r="AA207">
+        <v>1.87</v>
+      </c>
+      <c r="AB207">
         <v>1.95</v>
       </c>
-      <c r="R207">
-        <v>2.5</v>
-      </c>
-      <c r="S207">
-        <v>1.28</v>
-      </c>
-      <c r="T207">
-        <v>3.3</v>
-      </c>
-      <c r="U207">
-        <v>2.18</v>
-      </c>
-      <c r="V207">
-        <v>1.6</v>
-      </c>
-      <c r="W207">
-        <v>1.13</v>
-      </c>
-      <c r="X207">
-        <v>1.02</v>
-      </c>
-      <c r="Y207">
+      <c r="AC207">
+        <v>2.92</v>
+      </c>
+      <c r="AD207">
+        <v>1.31</v>
+      </c>
+      <c r="AE207">
+        <v>1.08</v>
+      </c>
+      <c r="AF207">
+        <v>1.72</v>
+      </c>
+      <c r="AG207">
+        <v>2.05</v>
+      </c>
+      <c r="AH207" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI207" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ207">
+        <v>1.29</v>
+      </c>
+      <c r="AK207">
         <v>1.2</v>
-      </c>
-      <c r="Z207">
-        <v>4.2</v>
-      </c>
-      <c r="AA207">
-        <v>1.45</v>
-      </c>
-      <c r="AB207">
-        <v>2.41</v>
-      </c>
-      <c r="AC207">
-        <v>2.21</v>
-      </c>
-      <c r="AD207">
-        <v>1.59</v>
-      </c>
-      <c r="AE207">
-        <v>1.2</v>
-      </c>
-      <c r="AF207">
-        <v>1.56</v>
-      </c>
-      <c r="AG207">
-        <v>2.25</v>
-      </c>
-      <c r="AH207" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI207" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ207">
-        <v>1.14</v>
-      </c>
-      <c r="AK207">
-        <v>2.33</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -34219,22 +34219,22 @@
         <v>2.75</v>
       </c>
       <c r="P208">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="Q208">
-        <v>3.29</v>
+        <v>3</v>
       </c>
       <c r="R208">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="S208">
         <v>1.67</v>
       </c>
       <c r="T208">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="U208">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="V208">
         <v>1.16</v>
@@ -34267,10 +34267,10 @@
         <v>1.02</v>
       </c>
       <c r="AF208">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="AG208">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AH208" t="inlineStr">
         <is>
@@ -34376,25 +34376,25 @@
         </is>
       </c>
       <c r="N209">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="O209">
         <v>3.4</v>
       </c>
       <c r="P209">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="Q209">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="R209">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="S209">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T209">
-        <v>3.28</v>
+        <v>3.16</v>
       </c>
       <c r="U209">
         <v>2.5</v>
@@ -34403,37 +34403,37 @@
         <v>1.44</v>
       </c>
       <c r="W209">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X209">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y209">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z209">
-        <v>3.82</v>
+        <v>3.71</v>
       </c>
       <c r="AA209">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AB209">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="AC209">
-        <v>2.93</v>
+        <v>3.02</v>
       </c>
       <c r="AD209">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE209">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF209">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AG209">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH209" t="inlineStr">
         <is>
@@ -34449,7 +34449,7 @@
         <v>1.22</v>
       </c>
       <c r="AK209">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AL209">
         <v>0</v>
@@ -34865,13 +34865,13 @@
         </is>
       </c>
       <c r="N212">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="O212">
         <v>2.95</v>
       </c>
       <c r="P212">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="Q212">
         <v>2.66</v>
@@ -34880,7 +34880,7 @@
         <v>1.95</v>
       </c>
       <c r="S212">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="T212">
         <v>2.75</v>
@@ -34889,7 +34889,7 @@
         <v>2.9</v>
       </c>
       <c r="V212">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W212">
         <v>1.05</v>
@@ -35098,7 +35098,7 @@
         </is>
       </c>
       <c r="AJ213">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK213">
         <v>1.2</v>
@@ -35354,13 +35354,13 @@
         </is>
       </c>
       <c r="N215">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O215">
-        <v>3.2</v>
+        <v>3.26</v>
       </c>
       <c r="P215">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q215">
         <v>3.6</v>
@@ -35369,10 +35369,10 @@
         <v>2.15</v>
       </c>
       <c r="S215">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T215">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="U215">
         <v>3</v>
@@ -35384,31 +35384,31 @@
         <v>1.05</v>
       </c>
       <c r="X215">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y215">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z215">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="AA215">
         <v>2.06</v>
       </c>
       <c r="AB215">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AC215">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AD215">
         <v>1.25</v>
       </c>
       <c r="AE215">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF215">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="AG215">
         <v>1.93</v>
@@ -35424,10 +35424,10 @@
         </is>
       </c>
       <c r="AJ215">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AK215">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AL215">
         <v>0</v>
@@ -35532,10 +35532,10 @@
         <v>2.74</v>
       </c>
       <c r="S216">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="T216">
-        <v>3.94</v>
+        <v>3.84</v>
       </c>
       <c r="U216">
         <v>2.1</v>
@@ -35568,7 +35568,7 @@
         <v>1.72</v>
       </c>
       <c r="AE216">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF216">
         <v>1.74</v>
@@ -35683,16 +35683,16 @@
         <v>1.19</v>
       </c>
       <c r="O217">
-        <v>6.45</v>
+        <v>5.9</v>
       </c>
       <c r="P217">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q217">
         <v>1.59</v>
       </c>
       <c r="R217">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="S217">
         <v>1.27</v>
@@ -35737,7 +35737,7 @@
         <v>2.25</v>
       </c>
       <c r="AG217">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AH217" t="inlineStr">
         <is>
@@ -35750,10 +35750,10 @@
         </is>
       </c>
       <c r="AJ217">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AK217">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="AL217">
         <v>0</v>
@@ -35843,13 +35843,13 @@
         </is>
       </c>
       <c r="N218">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="O218">
         <v>3.6</v>
       </c>
       <c r="P218">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q218">
         <v>0</v>
@@ -36015,7 +36015,7 @@
         <v>4</v>
       </c>
       <c r="Q219">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="R219">
         <v>2.21</v>
@@ -36051,7 +36051,7 @@
         <v>1.93</v>
       </c>
       <c r="AC219">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="AD219">
         <v>1.33</v>
@@ -36187,22 +36187,22 @@
         <v>1.54</v>
       </c>
       <c r="T220">
-        <v>2.45</v>
+        <v>2.31</v>
       </c>
       <c r="U220">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="V220">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="W220">
         <v>1.02</v>
       </c>
       <c r="X220">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Y220">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="Z220">
         <v>2.6</v>
@@ -36211,7 +36211,7 @@
         <v>2.5</v>
       </c>
       <c r="AB220">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AC220">
         <v>4.75</v>
@@ -36220,13 +36220,13 @@
         <v>1.15</v>
       </c>
       <c r="AE220">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AF220">
         <v>2.03</v>
       </c>
       <c r="AG220">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AH220" t="inlineStr">
         <is>
@@ -36332,13 +36332,13 @@
         </is>
       </c>
       <c r="N221">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O221">
-        <v>3.6</v>
+        <v>3.98</v>
       </c>
       <c r="P221">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="Q221">
         <v>0</v>
@@ -36495,64 +36495,64 @@
         </is>
       </c>
       <c r="N222">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O222">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P222">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q222">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="R222">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S222">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T222">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U222">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V222">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W222">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X222">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y222">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z222">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA222">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB222">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC222">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD222">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE222">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF222">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG222">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH222" t="inlineStr">
         <is>
@@ -36565,10 +36565,10 @@
         </is>
       </c>
       <c r="AJ222">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK222">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AL222">
         <v>0</v>
@@ -36658,13 +36658,13 @@
         </is>
       </c>
       <c r="N223">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="O223">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="P223">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="Q223">
         <v>2.62</v>
@@ -36679,10 +36679,10 @@
         <v>2.34</v>
       </c>
       <c r="U223">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="V223">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W223">
         <v>1.06</v>
@@ -36697,13 +36697,13 @@
         <v>3</v>
       </c>
       <c r="AA223">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="AB223">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC223">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="AD223">
         <v>1.21</v>
@@ -36712,10 +36712,10 @@
         <v>1.08</v>
       </c>
       <c r="AF223">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AG223">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AH223" t="inlineStr">
         <is>
@@ -36731,7 +36731,7 @@
         <v>1.37</v>
       </c>
       <c r="AK223">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AL223">
         <v>0</v>
@@ -36830,55 +36830,55 @@
         <v>0</v>
       </c>
       <c r="Q224">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R224">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="S224">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T224">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U224">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V224">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W224">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X224">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y224">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z224">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AA224">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AB224">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AC224">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD224">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE224">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF224">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG224">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AH224" t="inlineStr">
         <is>
@@ -36891,10 +36891,10 @@
         </is>
       </c>
       <c r="AJ224">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK224">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AL224">
         <v>0</v>
@@ -36984,19 +36984,19 @@
         </is>
       </c>
       <c r="N225">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="O225">
-        <v>3.64</v>
+        <v>3.55</v>
       </c>
       <c r="P225">
         <v>4.06</v>
       </c>
       <c r="Q225">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="R225">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S225">
         <v>1.35</v>
@@ -37014,7 +37014,7 @@
         <v>1.07</v>
       </c>
       <c r="X225">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y225">
         <v>1.22</v>
@@ -37023,10 +37023,10 @@
         <v>3.5</v>
       </c>
       <c r="AA225">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AB225">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AC225">
         <v>3.25</v>
@@ -37057,7 +37057,7 @@
         <v>1.18</v>
       </c>
       <c r="AK225">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AL225">
         <v>0</v>
@@ -37147,10 +37147,10 @@
         </is>
       </c>
       <c r="N226">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="O226">
-        <v>3.37</v>
+        <v>3.33</v>
       </c>
       <c r="P226">
         <v>2.05</v>
@@ -37310,25 +37310,25 @@
         </is>
       </c>
       <c r="N227">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="O227">
-        <v>2.94</v>
+        <v>2.85</v>
       </c>
       <c r="P227">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="Q227">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="R227">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="S227">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="T227">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="U227">
         <v>3.75</v>
@@ -37337,16 +37337,16 @@
         <v>1.22</v>
       </c>
       <c r="W227">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X227">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y227">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="Z227">
-        <v>2.27</v>
+        <v>2.36</v>
       </c>
       <c r="AA227">
         <v>2.53</v>
@@ -37358,7 +37358,7 @@
         <v>5.75</v>
       </c>
       <c r="AD227">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AE227">
         <v>1.03</v>
@@ -37367,7 +37367,7 @@
         <v>2.04</v>
       </c>
       <c r="AG227">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AH227" t="inlineStr">
         <is>
@@ -37380,10 +37380,10 @@
         </is>
       </c>
       <c r="AJ227">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK227">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AL227">
         <v>0</v>
@@ -37482,16 +37482,16 @@
         <v>3.1</v>
       </c>
       <c r="Q228">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="R228">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="S228">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="T228">
-        <v>2.63</v>
+        <v>2.33</v>
       </c>
       <c r="U228">
         <v>3.14</v>
@@ -37518,7 +37518,7 @@
         <v>1.47</v>
       </c>
       <c r="AC228">
-        <v>3.9</v>
+        <v>3.96</v>
       </c>
       <c r="AD228">
         <v>1.15</v>
@@ -37527,7 +37527,7 @@
         <v>1.02</v>
       </c>
       <c r="AF228">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AG228">
         <v>1.64</v>
@@ -37546,7 +37546,7 @@
         <v>1.3</v>
       </c>
       <c r="AK228">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AL228">
         <v>0</v>
@@ -37645,7 +37645,7 @@
         <v>0</v>
       </c>
       <c r="Q229">
-        <v>2.41</v>
+        <v>2.55</v>
       </c>
       <c r="R229">
         <v>1.91</v>
@@ -37654,7 +37654,7 @@
         <v>1.51</v>
       </c>
       <c r="T229">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="U229">
         <v>3.6</v>
@@ -37706,10 +37706,10 @@
         </is>
       </c>
       <c r="AJ229">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK229">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AL229">
         <v>0</v>
@@ -37826,22 +37826,22 @@
         <v>1.44</v>
       </c>
       <c r="W230">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X230">
         <v>1.01</v>
       </c>
       <c r="Y230">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z230">
-        <v>3.94</v>
+        <v>3.9</v>
       </c>
       <c r="AA230">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AB230">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AC230">
         <v>2.3</v>
@@ -37968,19 +37968,19 @@
         <v>2.87</v>
       </c>
       <c r="P231">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="Q231">
         <v>3.6</v>
       </c>
       <c r="R231">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="S231">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="T231">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="U231">
         <v>3.6</v>
@@ -37989,34 +37989,34 @@
         <v>1.25</v>
       </c>
       <c r="W231">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X231">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y231">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Z231">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="AA231">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AB231">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AC231">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="AD231">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AE231">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF231">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="AG231">
         <v>1.67</v>
@@ -38143,13 +38143,13 @@
         <v>1.35</v>
       </c>
       <c r="T232">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U232">
-        <v>2.69</v>
+        <v>2.76</v>
       </c>
       <c r="V232">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W232">
         <v>1.08</v>
@@ -38158,22 +38158,22 @@
         <v>1.05</v>
       </c>
       <c r="Y232">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="Z232">
-        <v>3.34</v>
+        <v>3.45</v>
       </c>
       <c r="AA232">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB232">
         <v>1.85</v>
       </c>
       <c r="AC232">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="AD232">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE232">
         <v>1.08</v>
@@ -38195,10 +38195,10 @@
         </is>
       </c>
       <c r="AJ232">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AK232">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AL232">
         <v>0</v>
@@ -38300,7 +38300,7 @@
         <v>2</v>
       </c>
       <c r="R233">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="S233">
         <v>1.22</v>
@@ -38324,13 +38324,13 @@
         <v>1.14</v>
       </c>
       <c r="Z233">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AA233">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AB233">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AC233">
         <v>2.2</v>
@@ -38451,13 +38451,13 @@
         </is>
       </c>
       <c r="N234">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O234">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P234">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q234">
         <v>2.6</v>
@@ -38469,7 +38469,7 @@
         <v>1.35</v>
       </c>
       <c r="T234">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="U234">
         <v>2.82</v>
@@ -38521,7 +38521,7 @@
         </is>
       </c>
       <c r="AJ234">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AK234">
         <v>1.73</v>
@@ -38623,55 +38623,55 @@
         <v>0</v>
       </c>
       <c r="Q235">
-        <v>0</v>
+        <v>5.49</v>
       </c>
       <c r="R235">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S235">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T235">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U235">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V235">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W235">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X235">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y235">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z235">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA235">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB235">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AC235">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD235">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE235">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF235">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG235">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AH235" t="inlineStr">
         <is>
@@ -38684,10 +38684,10 @@
         </is>
       </c>
       <c r="AJ235">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK235">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AL235">
         <v>0</v>
@@ -38777,13 +38777,13 @@
         </is>
       </c>
       <c r="N236">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="O236">
         <v>3.7</v>
       </c>
       <c r="P236">
-        <v>7.11</v>
+        <v>5</v>
       </c>
       <c r="Q236">
         <v>2.08</v>
@@ -38795,7 +38795,7 @@
         <v>1.38</v>
       </c>
       <c r="T236">
-        <v>2.7</v>
+        <v>2.93</v>
       </c>
       <c r="U236">
         <v>2.78</v>
@@ -38810,10 +38810,10 @@
         <v>1.01</v>
       </c>
       <c r="Y236">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z236">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="AA236">
         <v>1.92</v>
@@ -38847,10 +38847,10 @@
         </is>
       </c>
       <c r="AJ236">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AK236">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AL236">
         <v>0</v>

--- a/jogos_2026-08-23.xlsx
+++ b/jogos_2026-08-23.xlsx
@@ -635,28 +635,28 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="O2">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P2">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="Q2">
         <v>2.4</v>
       </c>
       <c r="R2">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="S2">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T2">
         <v>2.94</v>
       </c>
       <c r="U2">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="V2">
         <v>1.4</v>
@@ -671,29 +671,29 @@
         <v>1.3</v>
       </c>
       <c r="Z2">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="AA2">
+        <v>1.9</v>
+      </c>
+      <c r="AB2">
+        <v>1.8</v>
+      </c>
+      <c r="AC2">
+        <v>3.28</v>
+      </c>
+      <c r="AD2">
+        <v>1.25</v>
+      </c>
+      <c r="AE2">
+        <v>1.05</v>
+      </c>
+      <c r="AF2">
+        <v>1.8</v>
+      </c>
+      <c r="AG2">
         <v>1.89</v>
       </c>
-      <c r="AB2">
-        <v>1.81</v>
-      </c>
-      <c r="AC2">
-        <v>3.2</v>
-      </c>
-      <c r="AD2">
-        <v>1.3</v>
-      </c>
-      <c r="AE2">
-        <v>1.06</v>
-      </c>
-      <c r="AF2">
-        <v>1.77</v>
-      </c>
-      <c r="AG2">
-        <v>1.92</v>
-      </c>
       <c r="AH2" t="inlineStr">
         <is>
           <t>[]</t>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK2">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -10089,34 +10089,34 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="O60">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="P60">
-        <v>4.75</v>
+        <v>5.25</v>
       </c>
       <c r="Q60">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="R60">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="S60">
         <v>1.17</v>
       </c>
       <c r="T60">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="U60">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="V60">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="W60">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X60">
         <v>1.01</v>
@@ -10125,7 +10125,7 @@
         <v>1.05</v>
       </c>
       <c r="Z60">
-        <v>6.1</v>
+        <v>6.55</v>
       </c>
       <c r="AA60">
         <v>1.36</v>
@@ -10134,10 +10134,10 @@
         <v>3.1</v>
       </c>
       <c r="AC60">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AD60">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AE60">
         <v>1.33</v>
@@ -10146,7 +10146,7 @@
         <v>1.44</v>
       </c>
       <c r="AG60">
-        <v>2.57</v>
+        <v>2.45</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AK60">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
           <t>PSG</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>Rennes</t>
         </is>
       </c>
       <c r="G189">

--- a/jogos_2026-08-23.xlsx
+++ b/jogos_2026-08-23.xlsx
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.19</v>
+        <v>2.45</v>
       </c>
       <c r="O3">
         <v>3.15</v>
       </c>
       <c r="P3">
-        <v>2.85</v>
+        <v>2.55</v>
       </c>
       <c r="Q3">
         <v>2.7</v>
@@ -837,10 +837,10 @@
         <v>3.2</v>
       </c>
       <c r="AA3">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AB3">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AC3">
         <v>3.28</v>
@@ -855,7 +855,7 @@
         <v>1.7</v>
       </c>
       <c r="AG3">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK3">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -964,10 +964,10 @@
         <v>1.99</v>
       </c>
       <c r="O4">
-        <v>3.64</v>
+        <v>3.55</v>
       </c>
       <c r="P4">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1124,22 +1124,22 @@
         </is>
       </c>
       <c r="N5">
-        <v>4.65</v>
+        <v>4.75</v>
       </c>
       <c r="O5">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="P5">
         <v>1.54</v>
       </c>
       <c r="Q5">
-        <v>5.05</v>
+        <v>5.15</v>
       </c>
       <c r="R5">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="S5">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T5">
         <v>3.04</v>
@@ -1160,10 +1160,10 @@
         <v>1.19</v>
       </c>
       <c r="Z5">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="AA5">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="AB5">
         <v>2.15</v>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>2.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK5">
         <v>1.1</v>
@@ -3895,46 +3895,46 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="O22">
         <v>3.25</v>
       </c>
       <c r="P22">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="Q22">
         <v>2.32</v>
       </c>
       <c r="R22">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="S22">
         <v>1.45</v>
       </c>
       <c r="T22">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="U22">
         <v>2.95</v>
       </c>
       <c r="V22">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W22">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X22">
         <v>1.07</v>
       </c>
       <c r="Y22">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Z22">
-        <v>3.07</v>
+        <v>3.03</v>
       </c>
       <c r="AA22">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="AB22">
         <v>1.65</v>
@@ -3943,7 +3943,7 @@
         <v>3.95</v>
       </c>
       <c r="AD22">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE22">
         <v>1.02</v>
@@ -3968,7 +3968,7 @@
         <v>1.28</v>
       </c>
       <c r="AK22">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="O33">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P33">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q33">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="R33">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="S33">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="T33">
-        <v>2.94</v>
+        <v>3.24</v>
       </c>
       <c r="U33">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
       <c r="V33">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W33">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X33">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y33">
         <v>1.22</v>
       </c>
       <c r="Z33">
-        <v>3.76</v>
+        <v>3.8</v>
       </c>
       <c r="AA33">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="AB33">
-        <v>1.97</v>
+        <v>2.01</v>
       </c>
       <c r="AC33">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="AD33">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE33">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF33">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AG33">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
+        <v>1.4</v>
+      </c>
+      <c r="AK33">
         <v>1.45</v>
-      </c>
-      <c r="AK33">
-        <v>1.5</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="O34">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="P34">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q34">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="R34">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="S34">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="T34">
-        <v>3.24</v>
+        <v>2.94</v>
       </c>
       <c r="U34">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="V34">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W34">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X34">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y34">
         <v>1.22</v>
       </c>
       <c r="Z34">
-        <v>3.8</v>
+        <v>3.76</v>
       </c>
       <c r="AA34">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="AB34">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="AC34">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="AD34">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE34">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AF34">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AG34">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AK34">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AL34">
         <v>0</v>

--- a/jogos_2026-08-23.xlsx
+++ b/jogos_2026-08-23.xlsx
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="O6">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="P6">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="Q6">
-        <v>1.95</v>
+        <v>2.13</v>
       </c>
       <c r="R6">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S6">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T6">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U6">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="V6">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W6">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X6">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z6">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AA6">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AB6">
         <v>2.15</v>
       </c>
       <c r="AC6">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AD6">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AE6">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AF6">
         <v>1.62</v>
       </c>
       <c r="AG6">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK6">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
+        <v>1.47</v>
+      </c>
+      <c r="O18">
+        <v>4.2</v>
+      </c>
+      <c r="P18">
+        <v>5</v>
+      </c>
+      <c r="Q18">
+        <v>2</v>
+      </c>
+      <c r="R18">
+        <v>2.4</v>
+      </c>
+      <c r="S18">
+        <v>1.25</v>
+      </c>
+      <c r="T18">
+        <v>3.5</v>
+      </c>
+      <c r="U18">
+        <v>2.29</v>
+      </c>
+      <c r="V18">
+        <v>1.57</v>
+      </c>
+      <c r="W18">
+        <v>1.13</v>
+      </c>
+      <c r="X18">
+        <v>1.02</v>
+      </c>
+      <c r="Y18">
+        <v>1.18</v>
+      </c>
+      <c r="Z18">
+        <v>4.45</v>
+      </c>
+      <c r="AA18">
+        <v>1.59</v>
+      </c>
+      <c r="AB18">
+        <v>2.25</v>
+      </c>
+      <c r="AC18">
         <v>2.5</v>
       </c>
-      <c r="O18">
-        <v>3.1</v>
-      </c>
-      <c r="P18">
-        <v>2.55</v>
-      </c>
-      <c r="Q18">
-        <v>3.26</v>
-      </c>
-      <c r="R18">
-        <v>2.15</v>
-      </c>
-      <c r="S18">
-        <v>1.38</v>
-      </c>
-      <c r="T18">
-        <v>2.9</v>
-      </c>
-      <c r="U18">
-        <v>2.73</v>
-      </c>
-      <c r="V18">
-        <v>1.4</v>
-      </c>
-      <c r="W18">
-        <v>1.03</v>
-      </c>
-      <c r="X18">
-        <v>1.06</v>
-      </c>
-      <c r="Y18">
-        <v>1.26</v>
-      </c>
-      <c r="Z18">
-        <v>3.25</v>
-      </c>
-      <c r="AA18">
-        <v>1.92</v>
-      </c>
-      <c r="AB18">
-        <v>1.77</v>
-      </c>
-      <c r="AC18">
-        <v>3.45</v>
-      </c>
       <c r="AD18">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AE18">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AF18">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG18">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.44</v>
+        <v>1.1</v>
       </c>
       <c r="AK18">
-        <v>1.36</v>
+        <v>2.45</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.47</v>
+        <v>3.45</v>
       </c>
       <c r="O19">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="P19">
-        <v>5</v>
+        <v>1.95</v>
       </c>
       <c r="Q19">
-        <v>2</v>
+        <v>3.98</v>
       </c>
       <c r="R19">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="S19">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="T19">
-        <v>3.5</v>
+        <v>2.91</v>
       </c>
       <c r="U19">
-        <v>2.29</v>
+        <v>2.63</v>
       </c>
       <c r="V19">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="W19">
+        <v>1.06</v>
+      </c>
+      <c r="X19">
+        <v>1</v>
+      </c>
+      <c r="Y19">
+        <v>1.24</v>
+      </c>
+      <c r="Z19">
+        <v>3.9</v>
+      </c>
+      <c r="AA19">
+        <v>1.77</v>
+      </c>
+      <c r="AB19">
+        <v>2.1</v>
+      </c>
+      <c r="AC19">
+        <v>2.91</v>
+      </c>
+      <c r="AD19">
+        <v>1.34</v>
+      </c>
+      <c r="AE19">
         <v>1.13</v>
       </c>
-      <c r="X19">
-        <v>1.02</v>
-      </c>
-      <c r="Y19">
-        <v>1.18</v>
-      </c>
-      <c r="Z19">
-        <v>4.45</v>
-      </c>
-      <c r="AA19">
-        <v>1.59</v>
-      </c>
-      <c r="AB19">
-        <v>2.25</v>
-      </c>
-      <c r="AC19">
-        <v>2.5</v>
-      </c>
-      <c r="AD19">
-        <v>1.44</v>
-      </c>
-      <c r="AE19">
-        <v>1.18</v>
-      </c>
       <c r="AF19">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG19">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AK19">
-        <v>2.45</v>
+        <v>1.3</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,80 +3569,80 @@
         </is>
       </c>
       <c r="N20">
-        <v>3.45</v>
+        <v>2.5</v>
       </c>
       <c r="O20">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P20">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="Q20">
-        <v>3.98</v>
+        <v>3.26</v>
       </c>
       <c r="R20">
         <v>2.15</v>
       </c>
       <c r="S20">
+        <v>1.38</v>
+      </c>
+      <c r="T20">
+        <v>2.9</v>
+      </c>
+      <c r="U20">
+        <v>2.73</v>
+      </c>
+      <c r="V20">
+        <v>1.4</v>
+      </c>
+      <c r="W20">
+        <v>1.03</v>
+      </c>
+      <c r="X20">
+        <v>1.06</v>
+      </c>
+      <c r="Y20">
+        <v>1.26</v>
+      </c>
+      <c r="Z20">
+        <v>3.25</v>
+      </c>
+      <c r="AA20">
+        <v>1.92</v>
+      </c>
+      <c r="AB20">
+        <v>1.77</v>
+      </c>
+      <c r="AC20">
+        <v>3.45</v>
+      </c>
+      <c r="AD20">
+        <v>1.28</v>
+      </c>
+      <c r="AE20">
+        <v>1.08</v>
+      </c>
+      <c r="AF20">
+        <v>1.7</v>
+      </c>
+      <c r="AG20">
+        <v>1.95</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20">
+        <v>1.44</v>
+      </c>
+      <c r="AK20">
         <v>1.36</v>
-      </c>
-      <c r="T20">
-        <v>2.91</v>
-      </c>
-      <c r="U20">
-        <v>2.63</v>
-      </c>
-      <c r="V20">
-        <v>1.46</v>
-      </c>
-      <c r="W20">
-        <v>1.06</v>
-      </c>
-      <c r="X20">
-        <v>1</v>
-      </c>
-      <c r="Y20">
-        <v>1.24</v>
-      </c>
-      <c r="Z20">
-        <v>3.9</v>
-      </c>
-      <c r="AA20">
-        <v>1.77</v>
-      </c>
-      <c r="AB20">
-        <v>2.1</v>
-      </c>
-      <c r="AC20">
-        <v>2.91</v>
-      </c>
-      <c r="AD20">
-        <v>1.34</v>
-      </c>
-      <c r="AE20">
-        <v>1.13</v>
-      </c>
-      <c r="AF20">
-        <v>1.62</v>
-      </c>
-      <c r="AG20">
-        <v>2.11</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20">
-        <v>1.22</v>
-      </c>
-      <c r="AK20">
-        <v>1.3</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -6995,7 +6995,7 @@
         <v>1.67</v>
       </c>
       <c r="O41">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="P41">
         <v>4.2</v>
@@ -8133,22 +8133,22 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="O48">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="P48">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="Q48">
-        <v>3.36</v>
+        <v>3.32</v>
       </c>
       <c r="R48">
         <v>2.05</v>
       </c>
       <c r="S48">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="T48">
         <v>2.62</v>
@@ -8169,7 +8169,7 @@
         <v>1.39</v>
       </c>
       <c r="Z48">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="AA48">
         <v>2.27</v>
@@ -8178,10 +8178,10 @@
         <v>1.63</v>
       </c>
       <c r="AC48">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="AD48">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE48">
         <v>1.03</v>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AK48">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8785,16 +8785,16 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.66</v>
+        <v>2.29</v>
       </c>
       <c r="O52">
-        <v>3.05</v>
+        <v>3.12</v>
       </c>
       <c r="P52">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="Q52">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="R52">
         <v>2.13</v>
@@ -8803,28 +8803,28 @@
         <v>1.42</v>
       </c>
       <c r="T52">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="U52">
-        <v>2.99</v>
+        <v>2.87</v>
       </c>
       <c r="V52">
         <v>1.34</v>
       </c>
       <c r="W52">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X52">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y52">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z52">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AA52">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="AB52">
         <v>1.7</v>
@@ -8836,13 +8836,13 @@
         <v>1.22</v>
       </c>
       <c r="AE52">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF52">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AG52">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>1.36</v>
       </c>
       <c r="AK52">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9615,10 +9615,10 @@
         <v>1.65</v>
       </c>
       <c r="S57">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="T57">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="U57">
         <v>4</v>
@@ -9654,7 +9654,7 @@
         <v>1.02</v>
       </c>
       <c r="AF57">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AG57">
         <v>1.44</v>
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AK57">
         <v>1.36</v>
@@ -9763,22 +9763,22 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.83</v>
+        <v>2.87</v>
       </c>
       <c r="O58">
-        <v>3.05</v>
+        <v>3.02</v>
       </c>
       <c r="P58">
-        <v>2.3</v>
+        <v>3.22</v>
       </c>
       <c r="Q58">
-        <v>3.62</v>
+        <v>3.66</v>
       </c>
       <c r="R58">
         <v>1.96</v>
       </c>
       <c r="S58">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="T58">
         <v>2.57</v>
@@ -9796,19 +9796,19 @@
         <v>1.03</v>
       </c>
       <c r="Y58">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Z58">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AA58">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="AB58">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AC58">
-        <v>4.2</v>
+        <v>4.38</v>
       </c>
       <c r="AD58">
         <v>1.15</v>
@@ -9820,7 +9820,7 @@
         <v>1.94</v>
       </c>
       <c r="AG58">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.54</v>
+        <v>1.31</v>
       </c>
       <c r="AK58">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="O70">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P70">
-        <v>2.37</v>
+        <v>2.43</v>
       </c>
       <c r="Q70">
         <v>0</v>
@@ -11758,10 +11758,10 @@
         <v>0</v>
       </c>
       <c r="AA70">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB70">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AC70">
         <v>0</v>
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="O99">
         <v>4.85</v>
       </c>
       <c r="P99">
-        <v>7.55</v>
+        <v>7</v>
       </c>
       <c r="Q99">
         <v>1.83</v>
@@ -16461,49 +16461,49 @@
         <v>2.4</v>
       </c>
       <c r="S99">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T99">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="U99">
         <v>2.4</v>
       </c>
       <c r="V99">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="W99">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X99">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y99">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="Z99">
         <v>4</v>
       </c>
       <c r="AA99">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AB99">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AC99">
         <v>2.75</v>
       </c>
       <c r="AD99">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE99">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF99">
         <v>1.9</v>
       </c>
       <c r="AG99">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16781,7 +16781,7 @@
         <v>2.85</v>
       </c>
       <c r="Q101">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="R101">
         <v>2.06</v>
@@ -16811,10 +16811,10 @@
         <v>3.14</v>
       </c>
       <c r="AA101">
-        <v>2.07</v>
+        <v>1.91</v>
       </c>
       <c r="AB101">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AC101">
         <v>3.2</v>
@@ -16826,10 +16826,10 @@
         <v>1.06</v>
       </c>
       <c r="AF101">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AG101">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16944,10 +16944,10 @@
         <v>0</v>
       </c>
       <c r="Q102">
-        <v>3.42</v>
+        <v>3.44</v>
       </c>
       <c r="R102">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="S102">
         <v>1.33</v>
@@ -16962,7 +16962,7 @@
         <v>1.4</v>
       </c>
       <c r="W102">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X102">
         <v>1.01</v>
@@ -16980,10 +16980,10 @@
         <v>1.83</v>
       </c>
       <c r="AC102">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="AD102">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AE102">
         <v>1.09</v>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AK102">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17439,7 +17439,7 @@
         <v>2</v>
       </c>
       <c r="S105">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="T105">
         <v>2.63</v>
@@ -17448,40 +17448,40 @@
         <v>3.2</v>
       </c>
       <c r="V105">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="W105">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X105">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y105">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Z105">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AA105">
         <v>2.25</v>
       </c>
       <c r="AB105">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AC105">
-        <v>4.5</v>
+        <v>4.05</v>
       </c>
       <c r="AD105">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AE105">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF105">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AG105">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK105">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17590,7 +17590,7 @@
         <v>1.65</v>
       </c>
       <c r="O106">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P106">
         <v>4.5</v>
@@ -17605,13 +17605,13 @@
         <v>1.36</v>
       </c>
       <c r="T106">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="U106">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="V106">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="W106">
         <v>1.02</v>
@@ -21671,16 +21671,16 @@
         <v>3</v>
       </c>
       <c r="Q131">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="R131">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="S131">
         <v>1.44</v>
       </c>
       <c r="T131">
-        <v>2.63</v>
+        <v>2.46</v>
       </c>
       <c r="U131">
         <v>3.2</v>
@@ -21689,37 +21689,37 @@
         <v>1.3</v>
       </c>
       <c r="W131">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X131">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y131">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z131">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="AA131">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="AB131">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AC131">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="AD131">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE131">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF131">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="AG131">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="AJ131">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK131">
         <v>1.57</v>
@@ -21858,7 +21858,7 @@
         <v>1.03</v>
       </c>
       <c r="Y132">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z132">
         <v>3.5</v>
@@ -21879,7 +21879,7 @@
         <v>1.11</v>
       </c>
       <c r="AF132">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG132">
         <v>1.7</v>
@@ -22160,55 +22160,55 @@
         <v>2.68</v>
       </c>
       <c r="Q134">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R134">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S134">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T134">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U134">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="V134">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W134">
         <v>0</v>
       </c>
       <c r="X134">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y134">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z134">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AA134">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AB134">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AC134">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AD134">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE134">
         <v>0</v>
       </c>
       <c r="AF134">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG134">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK134">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22323,55 +22323,55 @@
         <v>0</v>
       </c>
       <c r="Q135">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R135">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="S135">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="T135">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U135">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="V135">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W135">
         <v>0</v>
       </c>
       <c r="X135">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y135">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z135">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AA135">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AB135">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC135">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="AD135">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AE135">
         <v>0</v>
       </c>
       <c r="AF135">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AG135">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK135">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22812,55 +22812,55 @@
         <v>4.16</v>
       </c>
       <c r="Q138">
-        <v>2.42</v>
+        <v>2.47</v>
       </c>
       <c r="R138">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="S138">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T138">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="U138">
         <v>3</v>
       </c>
       <c r="V138">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W138">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X138">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y138">
         <v>1.3</v>
       </c>
       <c r="Z138">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="AA138">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AB138">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AC138">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="AD138">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE138">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AF138">
         <v>1.91</v>
       </c>
       <c r="AG138">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AH138" t="inlineStr">
         <is>
@@ -22876,7 +22876,7 @@
         <v>1.25</v>
       </c>
       <c r="AK138">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AL138">
         <v>0</v>
@@ -24270,13 +24270,13 @@
         </is>
       </c>
       <c r="N147">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="O147">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="P147">
-        <v>7.75</v>
+        <v>8.4</v>
       </c>
       <c r="Q147">
         <v>0</v>
@@ -24436,7 +24436,7 @@
         <v>3.1</v>
       </c>
       <c r="O148">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P148">
         <v>2.03</v>
@@ -24445,7 +24445,7 @@
         <v>3.5</v>
       </c>
       <c r="R148">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S148">
         <v>1.28</v>
@@ -24454,7 +24454,7 @@
         <v>3.18</v>
       </c>
       <c r="U148">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="V148">
         <v>1.52</v>
@@ -24463,7 +24463,7 @@
         <v>1.08</v>
       </c>
       <c r="X148">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y148">
         <v>1.15</v>
@@ -24472,16 +24472,16 @@
         <v>4.2</v>
       </c>
       <c r="AA148">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AB148">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AC148">
         <v>2.52</v>
       </c>
       <c r="AD148">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AE148">
         <v>1.17</v>
@@ -24506,7 +24506,7 @@
         <v>1.65</v>
       </c>
       <c r="AK148">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AL148">
         <v>0</v>
@@ -24605,7 +24605,7 @@
         <v>0</v>
       </c>
       <c r="Q149">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R149">
         <v>0</v>
@@ -24650,10 +24650,10 @@
         <v>0</v>
       </c>
       <c r="AF149">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG149">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH149" t="inlineStr">
         <is>
@@ -24666,10 +24666,10 @@
         </is>
       </c>
       <c r="AJ149">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK149">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL149">
         <v>0</v>
@@ -25411,13 +25411,13 @@
         </is>
       </c>
       <c r="N154">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="O154">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="P154">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="Q154">
         <v>1.91</v>
@@ -25426,16 +25426,16 @@
         <v>2.2</v>
       </c>
       <c r="S154">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T154">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="U154">
         <v>2.88</v>
       </c>
       <c r="V154">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W154">
         <v>1.05</v>
@@ -25453,7 +25453,7 @@
         <v>2.01</v>
       </c>
       <c r="AB154">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC154">
         <v>3.6</v>
@@ -25468,7 +25468,7 @@
         <v>2.25</v>
       </c>
       <c r="AG154">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -27213,55 +27213,55 @@
         <v>2.56</v>
       </c>
       <c r="Q165">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R165">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="S165">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="T165">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U165">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="V165">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W165">
         <v>0</v>
       </c>
       <c r="X165">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y165">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z165">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA165">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AB165">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC165">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AD165">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AE165">
         <v>0</v>
       </c>
       <c r="AF165">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AG165">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH165" t="inlineStr">
         <is>
@@ -27274,10 +27274,10 @@
         </is>
       </c>
       <c r="AJ165">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK165">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL165">
         <v>0</v>
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G183">
@@ -30138,40 +30138,40 @@
         </is>
       </c>
       <c r="N183">
-        <v>2.37</v>
+        <v>2.55</v>
       </c>
       <c r="O183">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="P183">
-        <v>3.37</v>
+        <v>3</v>
       </c>
       <c r="Q183">
-        <v>3.39</v>
+        <v>3.44</v>
       </c>
       <c r="R183">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="S183">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="T183">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="U183">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="V183">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="W183">
         <v>1.03</v>
       </c>
       <c r="X183">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Y183">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="Z183">
         <v>2.11</v>
@@ -30180,22 +30180,22 @@
         <v>2.88</v>
       </c>
       <c r="AB183">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AC183">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AD183">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AE183">
         <v>1.03</v>
       </c>
       <c r="AF183">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AG183">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AH183" t="inlineStr">
         <is>
@@ -30208,10 +30208,10 @@
         </is>
       </c>
       <c r="AJ183">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AK183">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AL183">
         <v>0</v>
@@ -30269,12 +30269,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G184">
@@ -30301,40 +30301,40 @@
         </is>
       </c>
       <c r="N184">
-        <v>2.55</v>
+        <v>2.37</v>
       </c>
       <c r="O184">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="P184">
-        <v>3</v>
+        <v>3.37</v>
       </c>
       <c r="Q184">
-        <v>3.44</v>
+        <v>3.39</v>
       </c>
       <c r="R184">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="S184">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="T184">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="U184">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="V184">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W184">
         <v>1.03</v>
       </c>
       <c r="X184">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Y184">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Z184">
         <v>2.11</v>
@@ -30343,22 +30343,22 @@
         <v>2.88</v>
       </c>
       <c r="AB184">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AC184">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="AD184">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AE184">
         <v>1.03</v>
       </c>
       <c r="AF184">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AG184">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AH184" t="inlineStr">
         <is>
@@ -30371,10 +30371,10 @@
         </is>
       </c>
       <c r="AJ184">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AK184">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AL184">
         <v>0</v>
@@ -30953,16 +30953,16 @@
         </is>
       </c>
       <c r="N188">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="O188">
         <v>3.4</v>
       </c>
       <c r="P188">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="Q188">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="R188">
         <v>2.25</v>
@@ -30971,46 +30971,46 @@
         <v>1.33</v>
       </c>
       <c r="T188">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="U188">
         <v>2.55</v>
       </c>
       <c r="V188">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W188">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X188">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y188">
         <v>1.22</v>
       </c>
       <c r="Z188">
-        <v>3.94</v>
+        <v>3.85</v>
       </c>
       <c r="AA188">
         <v>1.73</v>
       </c>
       <c r="AB188">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="AC188">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="AD188">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AE188">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF188">
         <v>1.57</v>
       </c>
       <c r="AG188">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="AH188" t="inlineStr">
         <is>
@@ -31026,7 +31026,7 @@
         <v>1.28</v>
       </c>
       <c r="AK188">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AL188">
         <v>0</v>
@@ -31931,7 +31931,7 @@
         </is>
       </c>
       <c r="N194">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="O194">
         <v>3.1</v>
@@ -31946,10 +31946,10 @@
         <v>2</v>
       </c>
       <c r="S194">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="T194">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="U194">
         <v>3.2</v>
@@ -31958,7 +31958,7 @@
         <v>1.3</v>
       </c>
       <c r="W194">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X194">
         <v>1.02</v>
@@ -31973,7 +31973,7 @@
         <v>2.19</v>
       </c>
       <c r="AB194">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AC194">
         <v>4</v>
@@ -32103,7 +32103,7 @@
         <v>4.53</v>
       </c>
       <c r="Q195">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="R195">
         <v>2.1</v>
@@ -32148,10 +32148,10 @@
         <v>1.08</v>
       </c>
       <c r="AF195">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AG195">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
@@ -32167,7 +32167,7 @@
         <v>1.22</v>
       </c>
       <c r="AK195">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -34711,7 +34711,7 @@
         <v>4.94</v>
       </c>
       <c r="Q211">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R211">
         <v>2</v>

--- a/jogos_2026-08-23.xlsx
+++ b/jogos_2026-08-23.xlsx
@@ -1456,7 +1456,7 @@
         <v>3.9</v>
       </c>
       <c r="P7">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="Q7">
         <v>2.05</v>
@@ -1471,37 +1471,37 @@
         <v>3.35</v>
       </c>
       <c r="U7">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="V7">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W7">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X7">
         <v>1.03</v>
       </c>
       <c r="Y7">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z7">
         <v>4.34</v>
       </c>
       <c r="AA7">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AB7">
         <v>2.27</v>
       </c>
       <c r="AC7">
-        <v>2.41</v>
+        <v>2.54</v>
       </c>
       <c r="AD7">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AE7">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF7">
         <v>1.64</v>
@@ -1523,7 +1523,7 @@
         <v>1.14</v>
       </c>
       <c r="AK7">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1785,31 +1785,31 @@
         <v>3.1</v>
       </c>
       <c r="Q9">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="R9">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S9">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T9">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="U9">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="V9">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W9">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y9">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z9">
         <v>3.51</v>
@@ -1818,22 +1818,22 @@
         <v>1.95</v>
       </c>
       <c r="AB9">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC9">
         <v>3.3</v>
       </c>
       <c r="AD9">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE9">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF9">
         <v>1.75</v>
       </c>
       <c r="AG9">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>1.22</v>
       </c>
       <c r="AK9">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.33</v>
+        <v>1.95</v>
       </c>
       <c r="O20">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="P20">
-        <v>2.45</v>
+        <v>2.93</v>
       </c>
       <c r="Q20">
-        <v>3.26</v>
+        <v>2.4</v>
       </c>
       <c r="R20">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S20">
+        <v>1.35</v>
+      </c>
+      <c r="T20">
+        <v>2.82</v>
+      </c>
+      <c r="U20">
+        <v>2.62</v>
+      </c>
+      <c r="V20">
         <v>1.37</v>
       </c>
-      <c r="T20">
-        <v>2.9</v>
-      </c>
-      <c r="U20">
-        <v>2.72</v>
-      </c>
-      <c r="V20">
-        <v>1.35</v>
-      </c>
       <c r="W20">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X20">
+        <v>1.05</v>
+      </c>
+      <c r="Y20">
+        <v>1.23</v>
+      </c>
+      <c r="Z20">
+        <v>3.42</v>
+      </c>
+      <c r="AA20">
+        <v>1.85</v>
+      </c>
+      <c r="AB20">
+        <v>1.88</v>
+      </c>
+      <c r="AC20">
+        <v>2.85</v>
+      </c>
+      <c r="AD20">
+        <v>1.27</v>
+      </c>
+      <c r="AE20">
         <v>1.06</v>
-      </c>
-      <c r="Y20">
-        <v>1.26</v>
-      </c>
-      <c r="Z20">
-        <v>3.2</v>
-      </c>
-      <c r="AA20">
-        <v>1.95</v>
-      </c>
-      <c r="AB20">
-        <v>1.8</v>
-      </c>
-      <c r="AC20">
-        <v>3.4</v>
-      </c>
-      <c r="AD20">
-        <v>1.25</v>
-      </c>
-      <c r="AE20">
-        <v>1.08</v>
       </c>
       <c r="AF20">
         <v>1.7</v>
       </c>
       <c r="AG20">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>1.3</v>
       </c>
       <c r="AK20">
-        <v>1.4</v>
+        <v>1.72</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
+        <v>2.33</v>
+      </c>
+      <c r="O21">
+        <v>3.13</v>
+      </c>
+      <c r="P21">
+        <v>2.45</v>
+      </c>
+      <c r="Q21">
+        <v>3.26</v>
+      </c>
+      <c r="R21">
+        <v>2.15</v>
+      </c>
+      <c r="S21">
+        <v>1.37</v>
+      </c>
+      <c r="T21">
+        <v>2.9</v>
+      </c>
+      <c r="U21">
+        <v>2.72</v>
+      </c>
+      <c r="V21">
+        <v>1.35</v>
+      </c>
+      <c r="W21">
+        <v>1.03</v>
+      </c>
+      <c r="X21">
+        <v>1.06</v>
+      </c>
+      <c r="Y21">
+        <v>1.26</v>
+      </c>
+      <c r="Z21">
+        <v>3.2</v>
+      </c>
+      <c r="AA21">
         <v>1.95</v>
       </c>
-      <c r="O21">
-        <v>3.12</v>
-      </c>
-      <c r="P21">
-        <v>2.93</v>
-      </c>
-      <c r="Q21">
-        <v>2.4</v>
-      </c>
-      <c r="R21">
-        <v>2.25</v>
-      </c>
-      <c r="S21">
-        <v>1.35</v>
-      </c>
-      <c r="T21">
-        <v>2.82</v>
-      </c>
-      <c r="U21">
-        <v>2.62</v>
-      </c>
-      <c r="V21">
-        <v>1.37</v>
-      </c>
-      <c r="W21">
-        <v>1.04</v>
-      </c>
-      <c r="X21">
-        <v>1.05</v>
-      </c>
-      <c r="Y21">
-        <v>1.23</v>
-      </c>
-      <c r="Z21">
-        <v>3.42</v>
-      </c>
-      <c r="AA21">
-        <v>1.85</v>
-      </c>
       <c r="AB21">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AC21">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="AD21">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE21">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF21">
         <v>1.7</v>
       </c>
       <c r="AG21">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>1.3</v>
       </c>
       <c r="AK21">
-        <v>1.72</v>
+        <v>1.4</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -6029,16 +6029,16 @@
         <v>2.45</v>
       </c>
       <c r="S35">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T35">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="U35">
         <v>2.31</v>
       </c>
       <c r="V35">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W35">
         <v>1.15</v>
@@ -6056,7 +6056,7 @@
         <v>1.5</v>
       </c>
       <c r="AB35">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="AC35">
         <v>2.34</v>
@@ -6087,7 +6087,7 @@
         <v>1.25</v>
       </c>
       <c r="AK35">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6499,14 +6499,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N38">
         <v>2.61</v>
       </c>
       <c r="O38">
-        <v>3.01</v>
+        <v>2.95</v>
       </c>
       <c r="P38">
         <v>2.7</v>
@@ -6838,16 +6838,16 @@
         <v>2.8</v>
       </c>
       <c r="Q40">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="R40">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S40">
         <v>1.31</v>
       </c>
       <c r="T40">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U40">
         <v>2.4</v>
@@ -6856,7 +6856,7 @@
         <v>1.49</v>
       </c>
       <c r="W40">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X40">
         <v>1.02</v>
@@ -6865,7 +6865,7 @@
         <v>1.2</v>
       </c>
       <c r="Z40">
-        <v>4.2</v>
+        <v>4.23</v>
       </c>
       <c r="AA40">
         <v>1.67</v>
@@ -6874,7 +6874,7 @@
         <v>2.1</v>
       </c>
       <c r="AC40">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="AD40">
         <v>1.4</v>
@@ -6902,7 +6902,7 @@
         <v>1.22</v>
       </c>
       <c r="AK40">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7324,10 +7324,10 @@
         <v>3.18</v>
       </c>
       <c r="P43">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="Q43">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="R43">
         <v>2.08</v>
@@ -7336,19 +7336,19 @@
         <v>1.39</v>
       </c>
       <c r="T43">
-        <v>3.08</v>
+        <v>2.73</v>
       </c>
       <c r="U43">
-        <v>2.76</v>
+        <v>2.58</v>
       </c>
       <c r="V43">
         <v>1.4</v>
       </c>
       <c r="W43">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X43">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y43">
         <v>1.24</v>
@@ -7366,16 +7366,16 @@
         <v>3.2</v>
       </c>
       <c r="AD43">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AE43">
         <v>1.13</v>
       </c>
       <c r="AF43">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AG43">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.41</v>
+        <v>2.15</v>
       </c>
       <c r="O44">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="P44">
-        <v>5.8</v>
+        <v>3.1</v>
       </c>
       <c r="Q44">
-        <v>1.93</v>
+        <v>2.75</v>
       </c>
       <c r="R44">
-        <v>2.65</v>
+        <v>2.28</v>
       </c>
       <c r="S44">
-        <v>1.23</v>
+        <v>1.37</v>
       </c>
       <c r="T44">
-        <v>4.33</v>
+        <v>3.3</v>
       </c>
       <c r="U44">
-        <v>2.12</v>
+        <v>2.55</v>
       </c>
       <c r="V44">
-        <v>1.75</v>
+        <v>1.45</v>
       </c>
       <c r="W44">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="X44">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y44">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="Z44">
-        <v>5.75</v>
+        <v>3.84</v>
       </c>
       <c r="AA44">
-        <v>1.44</v>
+        <v>1.79</v>
       </c>
       <c r="AB44">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="AC44">
-        <v>2.14</v>
+        <v>2.72</v>
       </c>
       <c r="AD44">
-        <v>1.73</v>
+        <v>1.42</v>
       </c>
       <c r="AE44">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AF44">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AG44">
-        <v>2.33</v>
+        <v>2.22</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
       <c r="AK44">
-        <v>2.7</v>
+        <v>1.64</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
+        <v>1.41</v>
+      </c>
+      <c r="O45">
+        <v>4.8</v>
+      </c>
+      <c r="P45">
+        <v>5.8</v>
+      </c>
+      <c r="Q45">
+        <v>1.93</v>
+      </c>
+      <c r="R45">
+        <v>2.65</v>
+      </c>
+      <c r="S45">
+        <v>1.23</v>
+      </c>
+      <c r="T45">
+        <v>4.5</v>
+      </c>
+      <c r="U45">
+        <v>2.1</v>
+      </c>
+      <c r="V45">
+        <v>1.75</v>
+      </c>
+      <c r="W45">
+        <v>1.18</v>
+      </c>
+      <c r="X45">
+        <v>1.03</v>
+      </c>
+      <c r="Y45">
+        <v>1.13</v>
+      </c>
+      <c r="Z45">
+        <v>5.75</v>
+      </c>
+      <c r="AA45">
+        <v>1.39</v>
+      </c>
+      <c r="AB45">
+        <v>2.59</v>
+      </c>
+      <c r="AC45">
         <v>2.15</v>
       </c>
-      <c r="O45">
-        <v>3.6</v>
-      </c>
-      <c r="P45">
-        <v>3.17</v>
-      </c>
-      <c r="Q45">
-        <v>2.5</v>
-      </c>
-      <c r="R45">
-        <v>2.4</v>
-      </c>
-      <c r="S45">
-        <v>1.36</v>
-      </c>
-      <c r="T45">
-        <v>3.4</v>
-      </c>
-      <c r="U45">
-        <v>2.54</v>
-      </c>
-      <c r="V45">
-        <v>1.51</v>
-      </c>
-      <c r="W45">
-        <v>1.08</v>
-      </c>
-      <c r="X45">
-        <v>1.04</v>
-      </c>
-      <c r="Y45">
-        <v>1.22</v>
-      </c>
-      <c r="Z45">
-        <v>4</v>
-      </c>
-      <c r="AA45">
-        <v>1.76</v>
-      </c>
-      <c r="AB45">
-        <v>2.2</v>
-      </c>
-      <c r="AC45">
-        <v>2.6</v>
-      </c>
       <c r="AD45">
-        <v>1.49</v>
+        <v>1.8</v>
       </c>
       <c r="AE45">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AF45">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AG45">
-        <v>2.26</v>
+        <v>2.33</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AK45">
-        <v>1.66</v>
+        <v>2.7</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,61 +7807,61 @@
         </is>
       </c>
       <c r="N46">
-        <v>4.95</v>
+        <v>4.45</v>
       </c>
       <c r="O46">
-        <v>3.51</v>
+        <v>3.7</v>
       </c>
       <c r="P46">
         <v>1.73</v>
       </c>
       <c r="Q46">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="R46">
         <v>2.2</v>
       </c>
       <c r="S46">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T46">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="U46">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="V46">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W46">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X46">
         <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z46">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AA46">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB46">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AC46">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="AD46">
         <v>1.32</v>
       </c>
       <c r="AE46">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF46">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AG46">
         <v>1.85</v>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.25</v>
+        <v>2.12</v>
       </c>
       <c r="AK46">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="O47">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P47">
-        <v>2.72</v>
+        <v>2.63</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -8957,10 +8957,10 @@
         <v>3.45</v>
       </c>
       <c r="Q53">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="R53">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="S53">
         <v>1.38</v>
@@ -8981,7 +8981,7 @@
         <v>1.05</v>
       </c>
       <c r="Y53">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="Z53">
         <v>2.9</v>
@@ -9002,10 +9002,10 @@
         <v>1.04</v>
       </c>
       <c r="AF53">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="AG53">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9107,7 +9107,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N54">
@@ -9120,13 +9120,13 @@
         <v>2.81</v>
       </c>
       <c r="Q54">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="R54">
         <v>2.12</v>
       </c>
       <c r="S54">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="T54">
         <v>2.65</v>
@@ -9150,10 +9150,10 @@
         <v>3.5</v>
       </c>
       <c r="AA54">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AB54">
-        <v>1.88</v>
+        <v>1.71</v>
       </c>
       <c r="AC54">
         <v>3</v>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AK54">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -10904,7 +10904,7 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="O65">
         <v>3.1</v>
@@ -10913,22 +10913,22 @@
         <v>2.55</v>
       </c>
       <c r="Q65">
-        <v>3</v>
+        <v>3.36</v>
       </c>
       <c r="R65">
         <v>2.16</v>
       </c>
       <c r="S65">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="T65">
-        <v>2.86</v>
+        <v>2.59</v>
       </c>
       <c r="U65">
         <v>2.9</v>
       </c>
       <c r="V65">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W65">
         <v>1.05</v>
@@ -10955,10 +10955,10 @@
         <v>1.25</v>
       </c>
       <c r="AE65">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF65">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG65">
         <v>2</v>
@@ -11405,7 +11405,7 @@
         <v>1.86</v>
       </c>
       <c r="R68">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="S68">
         <v>1.32</v>
@@ -11414,7 +11414,7 @@
         <v>3.1</v>
       </c>
       <c r="U68">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="V68">
         <v>1.52</v>
@@ -11577,10 +11577,10 @@
         <v>2.9</v>
       </c>
       <c r="U69">
-        <v>2.65</v>
+        <v>2.48</v>
       </c>
       <c r="V69">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W69">
         <v>1.08</v>
@@ -11589,28 +11589,28 @@
         <v>1.03</v>
       </c>
       <c r="Y69">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="Z69">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="AA69">
-        <v>2.03</v>
+        <v>1.79</v>
       </c>
       <c r="AB69">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AC69">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="AD69">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="AE69">
         <v>1.05</v>
       </c>
       <c r="AF69">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AG69">
         <v>1.96</v>
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.58</v>
+        <v>2.65</v>
       </c>
       <c r="O70">
         <v>3.5</v>
       </c>
       <c r="P70">
-        <v>2.43</v>
+        <v>2.37</v>
       </c>
       <c r="Q70">
         <v>0</v>
@@ -13515,19 +13515,19 @@
         <v>2.15</v>
       </c>
       <c r="O81">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P81">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="Q81">
-        <v>2.63</v>
+        <v>2.77</v>
       </c>
       <c r="R81">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="S81">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T81">
         <v>3.2</v>
@@ -13542,7 +13542,7 @@
         <v>1.11</v>
       </c>
       <c r="X81">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y81">
         <v>1.23</v>
@@ -13551,10 +13551,10 @@
         <v>3.9</v>
       </c>
       <c r="AA81">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB81">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AC81">
         <v>2.88</v>
@@ -13563,13 +13563,13 @@
         <v>1.36</v>
       </c>
       <c r="AE81">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF81">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG81">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13585,7 +13585,7 @@
         <v>1.36</v>
       </c>
       <c r="AK81">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13699,7 +13699,7 @@
         <v>3.15</v>
       </c>
       <c r="V82">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W82">
         <v>1.01</v>
@@ -13708,13 +13708,13 @@
         <v>1.09</v>
       </c>
       <c r="Y82">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Z82">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="AA82">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AB82">
         <v>1.66</v>
@@ -13732,7 +13732,7 @@
         <v>1.85</v>
       </c>
       <c r="AG82">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>1.36</v>
       </c>
       <c r="AK82">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -14336,10 +14336,10 @@
         <v>4</v>
       </c>
       <c r="Q86">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="R86">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="S86">
         <v>1.3</v>
@@ -14363,13 +14363,13 @@
         <v>1.28</v>
       </c>
       <c r="Z86">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="AA86">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AB86">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC86">
         <v>3.19</v>
@@ -14378,7 +14378,7 @@
         <v>1.37</v>
       </c>
       <c r="AE86">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF86">
         <v>1.73</v>
@@ -14397,7 +14397,7 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK86">
         <v>1.91</v>
@@ -14698,7 +14698,7 @@
         <v>1.96</v>
       </c>
       <c r="AC88">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="AD88">
         <v>1.28</v>
@@ -14816,7 +14816,7 @@
         </is>
       </c>
       <c r="N89">
-        <v>3.7</v>
+        <v>3.47</v>
       </c>
       <c r="O89">
         <v>3.9</v>
@@ -14849,7 +14849,7 @@
         <v>1.03</v>
       </c>
       <c r="Y89">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z89">
         <v>4.8</v>
@@ -14858,7 +14858,7 @@
         <v>1.57</v>
       </c>
       <c r="AB89">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="AC89">
         <v>2.43</v>
@@ -14870,10 +14870,10 @@
         <v>1.14</v>
       </c>
       <c r="AF89">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG89">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK89">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14997,7 +14997,7 @@
         <v>1.22</v>
       </c>
       <c r="T90">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="U90">
         <v>2.1</v>
@@ -15024,13 +15024,13 @@
         <v>2.64</v>
       </c>
       <c r="AC90">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="AD90">
         <v>1.69</v>
       </c>
       <c r="AE90">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AF90">
         <v>1.44</v>
@@ -15329,7 +15329,7 @@
         <v>2.39</v>
       </c>
       <c r="V92">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="W92">
         <v>1.12</v>
@@ -15338,7 +15338,7 @@
         <v>1.01</v>
       </c>
       <c r="Y92">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z92">
         <v>4.05</v>
@@ -15347,16 +15347,16 @@
         <v>1.66</v>
       </c>
       <c r="AB92">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="AC92">
-        <v>2.46</v>
+        <v>2.61</v>
       </c>
       <c r="AD92">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AE92">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF92">
         <v>1.57</v>
@@ -17433,16 +17433,16 @@
         <v>3.3</v>
       </c>
       <c r="Q105">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="R105">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="S105">
         <v>1.47</v>
       </c>
       <c r="T105">
-        <v>2.63</v>
+        <v>2.39</v>
       </c>
       <c r="U105">
         <v>3.2</v>
@@ -17596,10 +17596,10 @@
         <v>4.5</v>
       </c>
       <c r="Q106">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="R106">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="S106">
         <v>1.36</v>
@@ -17611,10 +17611,10 @@
         <v>2.92</v>
       </c>
       <c r="V106">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W106">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X106">
         <v>1.01</v>
@@ -17660,7 +17660,7 @@
         <v>1.22</v>
       </c>
       <c r="AK106">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17765,13 +17765,13 @@
         <v>2.35</v>
       </c>
       <c r="S107">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T107">
         <v>3.3</v>
       </c>
       <c r="U107">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="V107">
         <v>1.49</v>
@@ -17780,22 +17780,22 @@
         <v>1.08</v>
       </c>
       <c r="X107">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y107">
         <v>1.2</v>
       </c>
       <c r="Z107">
-        <v>4.22</v>
+        <v>4.5</v>
       </c>
       <c r="AA107">
         <v>1.77</v>
       </c>
       <c r="AB107">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AC107">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AD107">
         <v>1.38</v>
@@ -17804,7 +17804,7 @@
         <v>1.17</v>
       </c>
       <c r="AF107">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AG107">
         <v>2.3</v>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK107">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17916,22 +17916,22 @@
         <v>2.9</v>
       </c>
       <c r="O108">
-        <v>3.09</v>
+        <v>3.2</v>
       </c>
       <c r="P108">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q108">
-        <v>3.06</v>
+        <v>3.3</v>
       </c>
       <c r="R108">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="S108">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="T108">
-        <v>3.09</v>
+        <v>2.62</v>
       </c>
       <c r="U108">
         <v>2.62</v>
@@ -17940,37 +17940,37 @@
         <v>1.4</v>
       </c>
       <c r="W108">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X108">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y108">
         <v>1.29</v>
       </c>
       <c r="Z108">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AA108">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AB108">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AC108">
-        <v>2.99</v>
+        <v>3.25</v>
       </c>
       <c r="AD108">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE108">
         <v>1.11</v>
       </c>
       <c r="AF108">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG108">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -21680,7 +21680,7 @@
         <v>1.44</v>
       </c>
       <c r="T131">
-        <v>2.46</v>
+        <v>2.63</v>
       </c>
       <c r="U131">
         <v>3.2</v>
@@ -21719,7 +21719,7 @@
         <v>1.84</v>
       </c>
       <c r="AG131">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
@@ -21834,7 +21834,7 @@
         <v>6.76</v>
       </c>
       <c r="Q132">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="R132">
         <v>2.25</v>
@@ -21855,25 +21855,25 @@
         <v>1.08</v>
       </c>
       <c r="X132">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y132">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z132">
         <v>3.5</v>
       </c>
       <c r="AA132">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AB132">
         <v>1.83</v>
       </c>
       <c r="AC132">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AD132">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE132">
         <v>1.11</v>
@@ -21882,7 +21882,7 @@
         <v>2</v>
       </c>
       <c r="AG132">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -22640,10 +22640,10 @@
         </is>
       </c>
       <c r="N137">
-        <v>5.55</v>
+        <v>4.8</v>
       </c>
       <c r="O137">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="P137">
         <v>1.5</v>
@@ -22652,31 +22652,31 @@
         <v>6</v>
       </c>
       <c r="R137">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="S137">
         <v>1.36</v>
       </c>
       <c r="T137">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="U137">
         <v>2.88</v>
       </c>
       <c r="V137">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="W137">
         <v>1.08</v>
       </c>
       <c r="X137">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y137">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Z137">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AA137">
         <v>1.77</v>
@@ -22685,19 +22685,19 @@
         <v>1.86</v>
       </c>
       <c r="AC137">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AD137">
         <v>1.32</v>
       </c>
       <c r="AE137">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF137">
         <v>1.91</v>
       </c>
       <c r="AG137">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22710,7 +22710,7 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="AK137">
         <v>1.13</v>
@@ -22803,25 +22803,25 @@
         </is>
       </c>
       <c r="N138">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="O138">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="P138">
-        <v>4.16</v>
+        <v>4</v>
       </c>
       <c r="Q138">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="R138">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="S138">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T138">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="U138">
         <v>3</v>
@@ -22873,10 +22873,10 @@
         </is>
       </c>
       <c r="AJ138">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AK138">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL138">
         <v>0</v>
@@ -24276,7 +24276,7 @@
         <v>6.2</v>
       </c>
       <c r="P147">
-        <v>8.4</v>
+        <v>7.1</v>
       </c>
       <c r="Q147">
         <v>0</v>
@@ -24623,7 +24623,7 @@
         <v>1.36</v>
       </c>
       <c r="W149">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X149">
         <v>1.01</v>
@@ -24759,13 +24759,13 @@
         </is>
       </c>
       <c r="N150">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="O150">
         <v>3.62</v>
       </c>
       <c r="P150">
-        <v>5.25</v>
+        <v>5.6</v>
       </c>
       <c r="Q150">
         <v>2.15</v>
@@ -24774,31 +24774,31 @@
         <v>2.2</v>
       </c>
       <c r="S150">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T150">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="U150">
-        <v>2.86</v>
+        <v>2.63</v>
       </c>
       <c r="V150">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W150">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X150">
         <v>1.02</v>
       </c>
       <c r="Y150">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="Z150">
-        <v>3.4</v>
+        <v>3.51</v>
       </c>
       <c r="AA150">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AB150">
         <v>1.85</v>
@@ -24810,13 +24810,13 @@
         <v>1.33</v>
       </c>
       <c r="AE150">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF150">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG150">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AH150" t="inlineStr">
         <is>
@@ -24832,7 +24832,7 @@
         <v>1.26</v>
       </c>
       <c r="AK150">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AL150">
         <v>0</v>
@@ -24922,13 +24922,13 @@
         </is>
       </c>
       <c r="N151">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="O151">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P151">
-        <v>4.65</v>
+        <v>4.55</v>
       </c>
       <c r="Q151">
         <v>2.3</v>
@@ -24937,19 +24937,19 @@
         <v>2.1</v>
       </c>
       <c r="S151">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T151">
         <v>2.88</v>
       </c>
       <c r="U151">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="V151">
         <v>1.35</v>
       </c>
       <c r="W151">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X151">
         <v>1.04</v>
@@ -24958,7 +24958,7 @@
         <v>1.36</v>
       </c>
       <c r="Z151">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="AA151">
         <v>2.1</v>
@@ -24967,19 +24967,19 @@
         <v>1.72</v>
       </c>
       <c r="AC151">
-        <v>4.01</v>
+        <v>3.52</v>
       </c>
       <c r="AD151">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE151">
         <v>1.04</v>
       </c>
       <c r="AF151">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AG151">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AH151" t="inlineStr">
         <is>
@@ -24992,7 +24992,7 @@
         </is>
       </c>
       <c r="AJ151">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AK151">
         <v>2.05</v>
@@ -25094,16 +25094,16 @@
         <v>3.55</v>
       </c>
       <c r="Q152">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="R152">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S152">
         <v>1.25</v>
       </c>
       <c r="T152">
-        <v>3.6</v>
+        <v>3.24</v>
       </c>
       <c r="U152">
         <v>2.28</v>
@@ -25112,7 +25112,7 @@
         <v>1.55</v>
       </c>
       <c r="W152">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X152">
         <v>1.01</v>
@@ -25121,7 +25121,7 @@
         <v>1.18</v>
       </c>
       <c r="Z152">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="AA152">
         <v>1.6</v>
@@ -25136,10 +25136,10 @@
         <v>1.44</v>
       </c>
       <c r="AE152">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF152">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AG152">
         <v>2.2</v>
@@ -25155,7 +25155,7 @@
         </is>
       </c>
       <c r="AJ152">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK152">
         <v>1.91</v>
@@ -25900,7 +25900,7 @@
         </is>
       </c>
       <c r="N157">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="O157">
         <v>4.1</v>
@@ -25909,10 +25909,10 @@
         <v>4.9</v>
       </c>
       <c r="Q157">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R157">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="S157">
         <v>1.3</v>
@@ -25924,7 +25924,7 @@
         <v>2.4</v>
       </c>
       <c r="V157">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="W157">
         <v>1.09</v>
@@ -25933,13 +25933,13 @@
         <v>1.04</v>
       </c>
       <c r="Y157">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z157">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="AA157">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AB157">
         <v>2.05</v>
@@ -25951,7 +25951,7 @@
         <v>1.43</v>
       </c>
       <c r="AE157">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF157">
         <v>1.71</v>
@@ -25970,10 +25970,10 @@
         </is>
       </c>
       <c r="AJ157">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AK157">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26063,34 +26063,34 @@
         </is>
       </c>
       <c r="N158">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="O158">
         <v>2.9</v>
       </c>
       <c r="P158">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="Q158">
         <v>3.1</v>
       </c>
       <c r="R158">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="S158">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="T158">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="U158">
-        <v>3.22</v>
+        <v>3.6</v>
       </c>
       <c r="V158">
         <v>1.3</v>
       </c>
       <c r="W158">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X158">
         <v>1.09</v>
@@ -26105,10 +26105,10 @@
         <v>2.31</v>
       </c>
       <c r="AB158">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AC158">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="AD158">
         <v>1.18</v>
@@ -26117,10 +26117,10 @@
         <v>1.05</v>
       </c>
       <c r="AF158">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="AG158">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26136,7 +26136,7 @@
         <v>1.32</v>
       </c>
       <c r="AK158">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -27868,7 +27868,7 @@
         <v>2.88</v>
       </c>
       <c r="R169">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="S169">
         <v>1.69</v>
@@ -27883,7 +27883,7 @@
         <v>1.23</v>
       </c>
       <c r="W169">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X169">
         <v>1.1</v>
@@ -27901,7 +27901,7 @@
         <v>1.44</v>
       </c>
       <c r="AC169">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="AD169">
         <v>1.14</v>
@@ -27910,7 +27910,7 @@
         <v>1.04</v>
       </c>
       <c r="AF169">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AG169">
         <v>1.62</v>
@@ -29169,55 +29169,55 @@
         <v>4</v>
       </c>
       <c r="Q177">
-        <v>2.05</v>
+        <v>2.24</v>
       </c>
       <c r="R177">
-        <v>2.45</v>
+        <v>2.16</v>
       </c>
       <c r="S177">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="T177">
         <v>3.4</v>
       </c>
       <c r="U177">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="V177">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="W177">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X177">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y177">
         <v>1.15</v>
       </c>
       <c r="Z177">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="AA177">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AB177">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AC177">
-        <v>2.51</v>
+        <v>2.33</v>
       </c>
       <c r="AD177">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AE177">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AF177">
         <v>1.62</v>
       </c>
       <c r="AG177">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29230,7 +29230,7 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK177">
         <v>2</v>
@@ -29323,28 +29323,28 @@
         </is>
       </c>
       <c r="N178">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="O178">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="P178">
         <v>2.8</v>
       </c>
       <c r="Q178">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="R178">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="S178">
         <v>1.34</v>
       </c>
       <c r="T178">
-        <v>3.6</v>
+        <v>2.95</v>
       </c>
       <c r="U178">
-        <v>2.29</v>
+        <v>2.39</v>
       </c>
       <c r="V178">
         <v>1.5</v>
@@ -29353,19 +29353,19 @@
         <v>1.08</v>
       </c>
       <c r="X178">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y178">
         <v>1.18</v>
       </c>
       <c r="Z178">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AA178">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AB178">
-        <v>2.26</v>
+        <v>2.08</v>
       </c>
       <c r="AC178">
         <v>2.38</v>
@@ -29374,7 +29374,7 @@
         <v>1.46</v>
       </c>
       <c r="AE178">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AF178">
         <v>1.53</v>
@@ -29393,10 +29393,10 @@
         </is>
       </c>
       <c r="AJ178">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AK178">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AL178">
         <v>0</v>
@@ -29498,19 +29498,19 @@
         <v>5.5</v>
       </c>
       <c r="R179">
-        <v>2.21</v>
+        <v>2.42</v>
       </c>
       <c r="S179">
         <v>1.31</v>
       </c>
       <c r="T179">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U179">
-        <v>2.37</v>
+        <v>2.63</v>
       </c>
       <c r="V179">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W179">
         <v>1.08</v>
@@ -29525,25 +29525,25 @@
         <v>3.5</v>
       </c>
       <c r="AA179">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AB179">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AC179">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="AD179">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AE179">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF179">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG179">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH179" t="inlineStr">
         <is>
@@ -29556,10 +29556,10 @@
         </is>
       </c>
       <c r="AJ179">
-        <v>1.25</v>
+        <v>2.25</v>
       </c>
       <c r="AK179">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AL179">
         <v>0</v>
@@ -29667,10 +29667,10 @@
         <v>1.32</v>
       </c>
       <c r="T180">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="U180">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="V180">
         <v>1.44</v>
@@ -29682,7 +29682,7 @@
         <v>1.04</v>
       </c>
       <c r="Y180">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z180">
         <v>3.9</v>
@@ -29697,16 +29697,16 @@
         <v>2.9</v>
       </c>
       <c r="AD180">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE180">
         <v>1.13</v>
       </c>
       <c r="AF180">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG180">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AH180" t="inlineStr">
         <is>
@@ -29719,10 +29719,10 @@
         </is>
       </c>
       <c r="AJ180">
-        <v>1.26</v>
+        <v>1.89</v>
       </c>
       <c r="AK180">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AL180">
         <v>0</v>
@@ -29812,19 +29812,19 @@
         </is>
       </c>
       <c r="N181">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="O181">
-        <v>3.75</v>
+        <v>3.84</v>
       </c>
       <c r="P181">
-        <v>4.7</v>
+        <v>5.05</v>
       </c>
       <c r="Q181">
         <v>2.08</v>
       </c>
       <c r="R181">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="S181">
         <v>1.36</v>
@@ -29839,37 +29839,37 @@
         <v>1.4</v>
       </c>
       <c r="W181">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X181">
         <v>1.01</v>
       </c>
       <c r="Y181">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z181">
         <v>3.5</v>
       </c>
       <c r="AA181">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AB181">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC181">
         <v>3.08</v>
       </c>
       <c r="AD181">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AE181">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF181">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AG181">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH181" t="inlineStr">
         <is>
@@ -29882,10 +29882,10 @@
         </is>
       </c>
       <c r="AJ181">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK181">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AL181">
         <v>0</v>
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G182">
@@ -29975,64 +29975,64 @@
         </is>
       </c>
       <c r="N182">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="O182">
+        <v>2.75</v>
+      </c>
+      <c r="P182">
         <v>2.9</v>
       </c>
-      <c r="P182">
-        <v>3.3</v>
-      </c>
       <c r="Q182">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="R182">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="S182">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="T182">
-        <v>2.5</v>
+        <v>2.09</v>
       </c>
       <c r="U182">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="V182">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="W182">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X182">
         <v>1.1</v>
       </c>
       <c r="Y182">
-        <v>1.43</v>
+        <v>1.68</v>
       </c>
       <c r="Z182">
-        <v>2.43</v>
+        <v>2.06</v>
       </c>
       <c r="AA182">
-        <v>2.45</v>
+        <v>3.28</v>
       </c>
       <c r="AB182">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="AC182">
-        <v>4.8</v>
+        <v>6.05</v>
       </c>
       <c r="AD182">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AE182">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF182">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="AG182">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="AH182" t="inlineStr">
         <is>
@@ -30045,10 +30045,10 @@
         </is>
       </c>
       <c r="AJ182">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK182">
-        <v>1.57</v>
+        <v>1.39</v>
       </c>
       <c r="AL182">
         <v>0</v>
@@ -30144,7 +30144,7 @@
         <v>2.75</v>
       </c>
       <c r="P183">
-        <v>3.37</v>
+        <v>3.15</v>
       </c>
       <c r="Q183">
         <v>3.39</v>
@@ -30174,10 +30174,10 @@
         <v>1.68</v>
       </c>
       <c r="Z183">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="AA183">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AB183">
         <v>1.34</v>
@@ -30208,10 +30208,10 @@
         </is>
       </c>
       <c r="AJ183">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AK183">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AL183">
         <v>0</v>
@@ -30269,12 +30269,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G184">
@@ -30301,64 +30301,64 @@
         </is>
       </c>
       <c r="N184">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="O184">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="P184">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="Q184">
-        <v>3.62</v>
+        <v>2.9</v>
       </c>
       <c r="R184">
-        <v>1.79</v>
+        <v>1.98</v>
       </c>
       <c r="S184">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="T184">
-        <v>2.09</v>
+        <v>2.26</v>
       </c>
       <c r="U184">
-        <v>4.5</v>
+        <v>3.34</v>
       </c>
       <c r="V184">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="W184">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X184">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Y184">
-        <v>1.71</v>
+        <v>1.46</v>
       </c>
       <c r="Z184">
-        <v>2.1</v>
+        <v>2.43</v>
       </c>
       <c r="AA184">
-        <v>3.28</v>
+        <v>2.4</v>
       </c>
       <c r="AB184">
-        <v>1.31</v>
+        <v>1.49</v>
       </c>
       <c r="AC184">
-        <v>6.05</v>
+        <v>4.45</v>
       </c>
       <c r="AD184">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AE184">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF184">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="AG184">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AH184" t="inlineStr">
         <is>
@@ -30371,10 +30371,10 @@
         </is>
       </c>
       <c r="AJ184">
-        <v>1.44</v>
+        <v>1.23</v>
       </c>
       <c r="AK184">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AL184">
         <v>0</v>
@@ -30639,13 +30639,13 @@
         <v>3.78</v>
       </c>
       <c r="R186">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S186">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T186">
-        <v>2.82</v>
+        <v>3.15</v>
       </c>
       <c r="U186">
         <v>2.56</v>
@@ -30660,7 +30660,7 @@
         <v>1.01</v>
       </c>
       <c r="Y186">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z186">
         <v>3.5</v>
@@ -30669,22 +30669,22 @@
         <v>1.75</v>
       </c>
       <c r="AB186">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AC186">
-        <v>2.95</v>
+        <v>2.81</v>
       </c>
       <c r="AD186">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AE186">
         <v>1.1</v>
       </c>
       <c r="AF186">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AG186">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="AH186" t="inlineStr">
         <is>
@@ -30697,7 +30697,7 @@
         </is>
       </c>
       <c r="AJ186">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AK186">
         <v>1.27</v>
@@ -30790,13 +30790,13 @@
         </is>
       </c>
       <c r="N187">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O187">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P187">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q187">
         <v>0</v>
@@ -31116,64 +31116,64 @@
         </is>
       </c>
       <c r="N189">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="O189">
-        <v>4.65</v>
+        <v>4.4</v>
       </c>
       <c r="P189">
         <v>5</v>
       </c>
       <c r="Q189">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="R189">
         <v>2.63</v>
       </c>
       <c r="S189">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="T189">
         <v>3.94</v>
       </c>
       <c r="U189">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="V189">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="W189">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X189">
         <v>1.02</v>
       </c>
       <c r="Y189">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z189">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AA189">
         <v>1.4</v>
       </c>
       <c r="AB189">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AC189">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AD189">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AE189">
         <v>1.36</v>
       </c>
       <c r="AF189">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AG189">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AH189" t="inlineStr">
         <is>
@@ -31186,10 +31186,10 @@
         </is>
       </c>
       <c r="AJ189">
-        <v>2.64</v>
+        <v>2.48</v>
       </c>
       <c r="AK189">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AL189">
         <v>0</v>
@@ -31635,7 +31635,7 @@
         <v>1.05</v>
       </c>
       <c r="X192">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y192">
         <v>1.26</v>
@@ -31644,25 +31644,25 @@
         <v>3.24</v>
       </c>
       <c r="AA192">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="AB192">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AC192">
         <v>3.18</v>
       </c>
       <c r="AD192">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE192">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF192">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AG192">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AH192" t="inlineStr">
         <is>
@@ -31675,10 +31675,10 @@
         </is>
       </c>
       <c r="AJ192">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK192">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL192">
         <v>0</v>
@@ -31768,7 +31768,7 @@
         </is>
       </c>
       <c r="N193">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="O193">
         <v>3.7</v>
@@ -31777,7 +31777,7 @@
         <v>5</v>
       </c>
       <c r="Q193">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="R193">
         <v>2.15</v>
@@ -31789,7 +31789,7 @@
         <v>2.77</v>
       </c>
       <c r="U193">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="V193">
         <v>1.38</v>
@@ -31798,34 +31798,34 @@
         <v>1.04</v>
       </c>
       <c r="X193">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y193">
         <v>1.3</v>
       </c>
       <c r="Z193">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="AA193">
         <v>2.09</v>
       </c>
       <c r="AB193">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AC193">
-        <v>3.12</v>
+        <v>3.55</v>
       </c>
       <c r="AD193">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE193">
         <v>1.06</v>
       </c>
       <c r="AF193">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AG193">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH193" t="inlineStr">
         <is>
@@ -31841,7 +31841,7 @@
         <v>1.3</v>
       </c>
       <c r="AK193">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AL193">
         <v>0</v>
@@ -32266,25 +32266,25 @@
         <v>3.4</v>
       </c>
       <c r="Q196">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="R196">
         <v>2</v>
       </c>
       <c r="S196">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T196">
-        <v>2.44</v>
+        <v>2.75</v>
       </c>
       <c r="U196">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="V196">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W196">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X196">
         <v>1.02</v>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK196">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -32420,64 +32420,64 @@
         </is>
       </c>
       <c r="N197">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="O197">
-        <v>4.38</v>
+        <v>4.7</v>
       </c>
       <c r="P197">
-        <v>7.9</v>
+        <v>8.6</v>
       </c>
       <c r="Q197">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="R197">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="S197">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T197">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="U197">
         <v>2.7</v>
       </c>
       <c r="V197">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W197">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X197">
         <v>1.02</v>
       </c>
       <c r="Y197">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="Z197">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="AA197">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AB197">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AC197">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AD197">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AE197">
         <v>1.07</v>
       </c>
       <c r="AF197">
-        <v>2.46</v>
+        <v>2.26</v>
       </c>
       <c r="AG197">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32490,10 +32490,10 @@
         </is>
       </c>
       <c r="AJ197">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AK197">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AL197">
         <v>0</v>
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G206">
@@ -33887,64 +33887,64 @@
         </is>
       </c>
       <c r="N206">
-        <v>1.56</v>
+        <v>3.8</v>
       </c>
       <c r="O206">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="P206">
+        <v>1.79</v>
+      </c>
+      <c r="Q206">
         <v>4.4</v>
       </c>
-      <c r="Q206">
-        <v>2.01</v>
-      </c>
       <c r="R206">
-        <v>2.43</v>
+        <v>2.2</v>
       </c>
       <c r="S206">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="T206">
-        <v>3.5</v>
+        <v>2.96</v>
       </c>
       <c r="U206">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="V206">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="W206">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X206">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y206">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z206">
-        <v>4.2</v>
+        <v>3.58</v>
       </c>
       <c r="AA206">
-        <v>1.47</v>
+        <v>1.84</v>
       </c>
       <c r="AB206">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AC206">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AD206">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AE206">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AF206">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="AG206">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AH206" t="inlineStr">
         <is>
@@ -33957,10 +33957,10 @@
         </is>
       </c>
       <c r="AJ206">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK206">
-        <v>2.38</v>
+        <v>1.22</v>
       </c>
       <c r="AL206">
         <v>0</v>
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G207">
@@ -34050,64 +34050,64 @@
         </is>
       </c>
       <c r="N207">
-        <v>3.8</v>
+        <v>1.56</v>
       </c>
       <c r="O207">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="P207">
-        <v>1.79</v>
+        <v>4.4</v>
       </c>
       <c r="Q207">
-        <v>4.4</v>
+        <v>2.01</v>
       </c>
       <c r="R207">
+        <v>2.43</v>
+      </c>
+      <c r="S207">
+        <v>1.2</v>
+      </c>
+      <c r="T207">
+        <v>3.5</v>
+      </c>
+      <c r="U207">
         <v>2.2</v>
       </c>
-      <c r="S207">
-        <v>1.35</v>
-      </c>
-      <c r="T207">
-        <v>2.96</v>
-      </c>
-      <c r="U207">
-        <v>2.55</v>
-      </c>
       <c r="V207">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="W207">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X207">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y207">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z207">
-        <v>3.58</v>
+        <v>4.2</v>
       </c>
       <c r="AA207">
-        <v>1.84</v>
+        <v>1.47</v>
       </c>
       <c r="AB207">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AC207">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AD207">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AE207">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AF207">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AG207">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH207" t="inlineStr">
         <is>
@@ -34120,10 +34120,10 @@
         </is>
       </c>
       <c r="AJ207">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK207">
-        <v>1.22</v>
+        <v>2.38</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -34216,7 +34216,7 @@
         <v>2.25</v>
       </c>
       <c r="O208">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="P208">
         <v>3.2</v>
@@ -34225,7 +34225,7 @@
         <v>3.22</v>
       </c>
       <c r="R208">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="S208">
         <v>1.67</v>
@@ -34246,10 +34246,10 @@
         <v>1.15</v>
       </c>
       <c r="Y208">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="Z208">
-        <v>2.17</v>
+        <v>2.35</v>
       </c>
       <c r="AA208">
         <v>3</v>
@@ -34267,10 +34267,10 @@
         <v>1.03</v>
       </c>
       <c r="AF208">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AG208">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AH208" t="inlineStr">
         <is>
@@ -34283,7 +34283,7 @@
         </is>
       </c>
       <c r="AJ208">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AK208">
         <v>1.5</v>
@@ -34886,34 +34886,34 @@
         <v>2.69</v>
       </c>
       <c r="U212">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="V212">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W212">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X212">
         <v>1.03</v>
       </c>
       <c r="Y212">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z212">
-        <v>3.01</v>
+        <v>3.1</v>
       </c>
       <c r="AA212">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB212">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AC212">
-        <v>3.96</v>
+        <v>3.9</v>
       </c>
       <c r="AD212">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AE212">
         <v>1.06</v>
@@ -35040,7 +35040,7 @@
         <v>4.4</v>
       </c>
       <c r="R213">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S213">
         <v>1.42</v>
@@ -35049,16 +35049,16 @@
         <v>2.53</v>
       </c>
       <c r="U213">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="V213">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W213">
         <v>1.04</v>
       </c>
       <c r="X213">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y213">
         <v>1.35</v>
@@ -35067,10 +35067,10 @@
         <v>3.1</v>
       </c>
       <c r="AA213">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AB213">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AC213">
         <v>3.8</v>
@@ -35363,19 +35363,19 @@
         <v>2.15</v>
       </c>
       <c r="Q215">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="R215">
         <v>2.15</v>
       </c>
       <c r="S215">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T215">
-        <v>2.86</v>
+        <v>2.57</v>
       </c>
       <c r="U215">
-        <v>3.02</v>
+        <v>2.81</v>
       </c>
       <c r="V215">
         <v>1.36</v>
@@ -35396,22 +35396,22 @@
         <v>2.06</v>
       </c>
       <c r="AB215">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AC215">
-        <v>3.18</v>
+        <v>3.7</v>
       </c>
       <c r="AD215">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AE215">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF215">
         <v>1.73</v>
       </c>
       <c r="AG215">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="AH215" t="inlineStr">
         <is>
@@ -35424,10 +35424,10 @@
         </is>
       </c>
       <c r="AJ215">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AK215">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AL215">
         <v>0</v>
@@ -35538,7 +35538,7 @@
         <v>3.94</v>
       </c>
       <c r="U216">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="V216">
         <v>1.67</v>
@@ -35574,7 +35574,7 @@
         <v>1.73</v>
       </c>
       <c r="AG216">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH216" t="inlineStr">
         <is>
@@ -36673,25 +36673,25 @@
         <v>2.12</v>
       </c>
       <c r="S223">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T223">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="U223">
         <v>3.1</v>
       </c>
       <c r="V223">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W223">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X223">
         <v>1.09</v>
       </c>
       <c r="Y223">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z223">
         <v>2.9</v>
@@ -36700,10 +36700,10 @@
         <v>2.19</v>
       </c>
       <c r="AB223">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AC223">
-        <v>3.92</v>
+        <v>3.7</v>
       </c>
       <c r="AD223">
         <v>1.25</v>
@@ -36712,10 +36712,10 @@
         <v>1.08</v>
       </c>
       <c r="AF223">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AG223">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AH223" t="inlineStr">
         <is>
@@ -36728,7 +36728,7 @@
         </is>
       </c>
       <c r="AJ223">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK223">
         <v>1.63</v>
@@ -37636,25 +37636,25 @@
         </is>
       </c>
       <c r="N229">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O229">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P229">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q229">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="R229">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="S229">
         <v>1.53</v>
       </c>
       <c r="T229">
-        <v>2.36</v>
+        <v>2.55</v>
       </c>
       <c r="U229">
         <v>3.6</v>
@@ -37666,16 +37666,16 @@
         <v>1.03</v>
       </c>
       <c r="X229">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y229">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="Z229">
-        <v>2.85</v>
+        <v>2.64</v>
       </c>
       <c r="AA229">
-        <v>2.5</v>
+        <v>2.23</v>
       </c>
       <c r="AB229">
         <v>1.53</v>
@@ -37684,10 +37684,10 @@
         <v>4.79</v>
       </c>
       <c r="AD229">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AE229">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF229">
         <v>2.15</v>

--- a/jogos_2026-08-23.xlsx
+++ b/jogos_2026-08-23.xlsx
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
+        <v>1.41</v>
+      </c>
+      <c r="O44">
+        <v>4.8</v>
+      </c>
+      <c r="P44">
+        <v>5.8</v>
+      </c>
+      <c r="Q44">
+        <v>1.93</v>
+      </c>
+      <c r="R44">
+        <v>2.65</v>
+      </c>
+      <c r="S44">
+        <v>1.23</v>
+      </c>
+      <c r="T44">
+        <v>4.5</v>
+      </c>
+      <c r="U44">
+        <v>2.1</v>
+      </c>
+      <c r="V44">
+        <v>1.75</v>
+      </c>
+      <c r="W44">
+        <v>1.18</v>
+      </c>
+      <c r="X44">
+        <v>1.03</v>
+      </c>
+      <c r="Y44">
+        <v>1.13</v>
+      </c>
+      <c r="Z44">
+        <v>5.75</v>
+      </c>
+      <c r="AA44">
+        <v>1.39</v>
+      </c>
+      <c r="AB44">
+        <v>2.59</v>
+      </c>
+      <c r="AC44">
         <v>2.15</v>
       </c>
-      <c r="O44">
-        <v>3.4</v>
-      </c>
-      <c r="P44">
-        <v>3.1</v>
-      </c>
-      <c r="Q44">
-        <v>2.75</v>
-      </c>
-      <c r="R44">
-        <v>2.28</v>
-      </c>
-      <c r="S44">
-        <v>1.37</v>
-      </c>
-      <c r="T44">
-        <v>3.3</v>
-      </c>
-      <c r="U44">
-        <v>2.55</v>
-      </c>
-      <c r="V44">
-        <v>1.45</v>
-      </c>
-      <c r="W44">
-        <v>1.08</v>
-      </c>
-      <c r="X44">
-        <v>1.04</v>
-      </c>
-      <c r="Y44">
-        <v>1.22</v>
-      </c>
-      <c r="Z44">
-        <v>3.84</v>
-      </c>
-      <c r="AA44">
-        <v>1.79</v>
-      </c>
-      <c r="AB44">
-        <v>2.05</v>
-      </c>
-      <c r="AC44">
-        <v>2.72</v>
-      </c>
       <c r="AD44">
-        <v>1.42</v>
+        <v>1.8</v>
       </c>
       <c r="AE44">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AF44">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AG44">
-        <v>2.22</v>
+        <v>2.33</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AK44">
-        <v>1.64</v>
+        <v>2.7</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.41</v>
+        <v>2.15</v>
       </c>
       <c r="O45">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="P45">
-        <v>5.8</v>
+        <v>3.1</v>
       </c>
       <c r="Q45">
-        <v>1.93</v>
+        <v>2.75</v>
       </c>
       <c r="R45">
-        <v>2.65</v>
+        <v>2.28</v>
       </c>
       <c r="S45">
-        <v>1.23</v>
+        <v>1.37</v>
       </c>
       <c r="T45">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="U45">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="V45">
-        <v>1.75</v>
+        <v>1.45</v>
       </c>
       <c r="W45">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="X45">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y45">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="Z45">
-        <v>5.75</v>
+        <v>3.84</v>
       </c>
       <c r="AA45">
-        <v>1.39</v>
+        <v>1.79</v>
       </c>
       <c r="AB45">
-        <v>2.59</v>
+        <v>2.05</v>
       </c>
       <c r="AC45">
-        <v>2.15</v>
+        <v>2.72</v>
       </c>
       <c r="AD45">
-        <v>1.8</v>
+        <v>1.42</v>
       </c>
       <c r="AE45">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AF45">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AG45">
-        <v>2.33</v>
+        <v>2.22</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
       <c r="AK45">
-        <v>2.7</v>
+        <v>1.64</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -24611,10 +24611,10 @@
         <v>2.25</v>
       </c>
       <c r="S149">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T149">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="U149">
         <v>2.7</v>
@@ -24650,10 +24650,10 @@
         <v>1.06</v>
       </c>
       <c r="AF149">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AG149">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AH149" t="inlineStr">
         <is>
@@ -29984,7 +29984,7 @@
         <v>2.9</v>
       </c>
       <c r="Q182">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R182">
         <v>1.8</v>
@@ -29996,7 +29996,7 @@
         <v>2.09</v>
       </c>
       <c r="U182">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="V182">
         <v>1.16</v>
@@ -30005,7 +30005,7 @@
         <v>1.03</v>
       </c>
       <c r="X182">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Y182">
         <v>1.68</v>
@@ -30020,10 +30020,10 @@
         <v>1.31</v>
       </c>
       <c r="AC182">
-        <v>6.05</v>
+        <v>6.1</v>
       </c>
       <c r="AD182">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AE182">
         <v>1.02</v>
@@ -30141,7 +30141,7 @@
         <v>2.35</v>
       </c>
       <c r="O183">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="P183">
         <v>3.15</v>
@@ -30159,7 +30159,7 @@
         <v>2.04</v>
       </c>
       <c r="U183">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="V183">
         <v>1.17</v>
@@ -30313,7 +30313,7 @@
         <v>2.9</v>
       </c>
       <c r="R184">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="S184">
         <v>1.52</v>
@@ -30340,7 +30340,7 @@
         <v>2.43</v>
       </c>
       <c r="AA184">
-        <v>2.4</v>
+        <v>2.51</v>
       </c>
       <c r="AB184">
         <v>1.49</v>
@@ -30349,7 +30349,7 @@
         <v>4.45</v>
       </c>
       <c r="AD184">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AE184">
         <v>1.05</v>
@@ -33724,31 +33724,31 @@
         </is>
       </c>
       <c r="N205">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O205">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P205">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q205">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="R205">
         <v>3</v>
       </c>
       <c r="S205">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="T205">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="U205">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="V205">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="W205">
         <v>1.3</v>
@@ -33794,10 +33794,10 @@
         </is>
       </c>
       <c r="AJ205">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AK205">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AL205">
         <v>0</v>
@@ -34213,13 +34213,13 @@
         </is>
       </c>
       <c r="N208">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O208">
         <v>2.7</v>
       </c>
       <c r="P208">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q208">
         <v>3.22</v>
@@ -34246,10 +34246,10 @@
         <v>1.15</v>
       </c>
       <c r="Y208">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="Z208">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AA208">
         <v>3</v>
@@ -34270,7 +34270,7 @@
         <v>2.3</v>
       </c>
       <c r="AG208">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AH208" t="inlineStr">
         <is>
@@ -34283,7 +34283,7 @@
         </is>
       </c>
       <c r="AJ208">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AK208">
         <v>1.5</v>
@@ -36821,25 +36821,25 @@
         </is>
       </c>
       <c r="N224">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O224">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P224">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q224">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="R224">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="S224">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T224">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U224">
         <v>2.13</v>
@@ -36851,19 +36851,19 @@
         <v>1.17</v>
       </c>
       <c r="X224">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y224">
         <v>1.1</v>
       </c>
       <c r="Z224">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="AA224">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AB224">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="AC224">
         <v>2.14</v>
@@ -36872,13 +36872,13 @@
         <v>1.63</v>
       </c>
       <c r="AE224">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AF224">
         <v>1.44</v>
       </c>
       <c r="AG224">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="AH224" t="inlineStr">
         <is>
@@ -36891,10 +36891,10 @@
         </is>
       </c>
       <c r="AJ224">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AK224">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AL224">
         <v>0</v>
@@ -38614,13 +38614,13 @@
         </is>
       </c>
       <c r="N235">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="O235">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P235">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q235">
         <v>5</v>
@@ -38665,7 +38665,7 @@
         <v>1.79</v>
       </c>
       <c r="AE235">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AF235">
         <v>1.55</v>
@@ -38684,7 +38684,7 @@
         </is>
       </c>
       <c r="AJ235">
-        <v>1.13</v>
+        <v>2.64</v>
       </c>
       <c r="AK235">
         <v>1.06</v>

--- a/jogos_2026-08-23.xlsx
+++ b/jogos_2026-08-23.xlsx
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="O6">
         <v>3.8</v>
@@ -1296,10 +1296,10 @@
         <v>4.33</v>
       </c>
       <c r="Q6">
-        <v>2.13</v>
+        <v>1.95</v>
       </c>
       <c r="R6">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S6">
         <v>1.27</v>
@@ -1314,16 +1314,16 @@
         <v>1.48</v>
       </c>
       <c r="W6">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X6">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z6">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AA6">
         <v>1.61</v>
@@ -1332,19 +1332,19 @@
         <v>2.15</v>
       </c>
       <c r="AC6">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="AD6">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AE6">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AF6">
         <v>1.62</v>
       </c>
       <c r="AG6">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK6">
         <v>2.15</v>
@@ -1453,10 +1453,10 @@
         <v>1.55</v>
       </c>
       <c r="O7">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P7">
-        <v>4.65</v>
+        <v>4.8</v>
       </c>
       <c r="Q7">
         <v>2.05</v>
@@ -1483,25 +1483,25 @@
         <v>1.03</v>
       </c>
       <c r="Y7">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z7">
-        <v>4.34</v>
+        <v>4.39</v>
       </c>
       <c r="AA7">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AB7">
         <v>2.27</v>
       </c>
       <c r="AC7">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="AD7">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AE7">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF7">
         <v>1.64</v>
@@ -1785,7 +1785,7 @@
         <v>3.1</v>
       </c>
       <c r="Q9">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="R9">
         <v>2.15</v>
@@ -1797,7 +1797,7 @@
         <v>2.66</v>
       </c>
       <c r="U9">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="V9">
         <v>1.4</v>
@@ -1812,16 +1812,16 @@
         <v>1.3</v>
       </c>
       <c r="Z9">
-        <v>3.51</v>
+        <v>3.57</v>
       </c>
       <c r="AA9">
         <v>1.95</v>
       </c>
       <c r="AB9">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AC9">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="AD9">
         <v>1.28</v>
@@ -1830,7 +1830,7 @@
         <v>1.11</v>
       </c>
       <c r="AF9">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG9">
         <v>2</v>
@@ -2268,13 +2268,13 @@
         <v>2.58</v>
       </c>
       <c r="O12">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="P12">
         <v>2.27</v>
       </c>
       <c r="Q12">
-        <v>3.06</v>
+        <v>3.54</v>
       </c>
       <c r="R12">
         <v>2.11</v>
@@ -2283,7 +2283,7 @@
         <v>1.36</v>
       </c>
       <c r="T12">
-        <v>2.93</v>
+        <v>3.07</v>
       </c>
       <c r="U12">
         <v>2.62</v>
@@ -2301,19 +2301,19 @@
         <v>1.22</v>
       </c>
       <c r="Z12">
-        <v>3.68</v>
+        <v>4.09</v>
       </c>
       <c r="AA12">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="AB12">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="AC12">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="AD12">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AE12">
         <v>1.1</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.35</v>
+        <v>1.59</v>
       </c>
       <c r="AK12">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2431,16 +2431,16 @@
         <v>3.4</v>
       </c>
       <c r="O13">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P13">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="Q13">
         <v>4.2</v>
       </c>
       <c r="R13">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="S13">
         <v>1.22</v>
@@ -2452,13 +2452,13 @@
         <v>2.05</v>
       </c>
       <c r="V13">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="W13">
         <v>1.15</v>
       </c>
       <c r="X13">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y13">
         <v>1.14</v>
@@ -2467,10 +2467,10 @@
         <v>5.5</v>
       </c>
       <c r="AA13">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AB13">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="AC13">
         <v>2.15</v>
@@ -2479,7 +2479,7 @@
         <v>1.67</v>
       </c>
       <c r="AE13">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AF13">
         <v>1.44</v>
@@ -2757,16 +2757,16 @@
         <v>1.75</v>
       </c>
       <c r="O15">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P15">
-        <v>4.2</v>
+        <v>3.88</v>
       </c>
       <c r="Q15">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="R15">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="S15">
         <v>1.25</v>
@@ -2775,10 +2775,10 @@
         <v>3.6</v>
       </c>
       <c r="U15">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V15">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W15">
         <v>1.17</v>
@@ -2793,13 +2793,13 @@
         <v>4.75</v>
       </c>
       <c r="AA15">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AB15">
-        <v>2.4</v>
+        <v>2.58</v>
       </c>
       <c r="AC15">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AD15">
         <v>1.57</v>
@@ -2808,7 +2808,7 @@
         <v>1.21</v>
       </c>
       <c r="AF15">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG15">
         <v>2.39</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK15">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3246,13 +3246,13 @@
         <v>1.5</v>
       </c>
       <c r="O18">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="P18">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Q18">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="R18">
         <v>2.4</v>
@@ -3264,13 +3264,13 @@
         <v>3.5</v>
       </c>
       <c r="U18">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="V18">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W18">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X18">
         <v>1.03</v>
@@ -3279,7 +3279,7 @@
         <v>1.18</v>
       </c>
       <c r="Z18">
-        <v>4.5</v>
+        <v>4.54</v>
       </c>
       <c r="AA18">
         <v>1.57</v>
@@ -3288,10 +3288,10 @@
         <v>2.38</v>
       </c>
       <c r="AC18">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="AD18">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="AE18">
         <v>1.18</v>
@@ -3300,7 +3300,7 @@
         <v>1.67</v>
       </c>
       <c r="AG18">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AK18">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,52 +3406,52 @@
         </is>
       </c>
       <c r="N19">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="O19">
         <v>3.45</v>
       </c>
       <c r="P19">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="Q19">
-        <v>4.08</v>
+        <v>4.1</v>
       </c>
       <c r="R19">
         <v>2.15</v>
       </c>
       <c r="S19">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T19">
-        <v>3.2</v>
+        <v>2.91</v>
       </c>
       <c r="U19">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="V19">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="W19">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X19">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y19">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z19">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AA19">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AB19">
         <v>1.98</v>
       </c>
       <c r="AC19">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="AD19">
         <v>1.36</v>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.23</v>
+        <v>1.75</v>
       </c>
       <c r="AK19">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3572,16 +3572,16 @@
         <v>1.95</v>
       </c>
       <c r="O20">
-        <v>3.12</v>
+        <v>3.5</v>
       </c>
       <c r="P20">
-        <v>2.93</v>
+        <v>3.3</v>
       </c>
       <c r="Q20">
-        <v>2.4</v>
+        <v>2.57</v>
       </c>
       <c r="R20">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="S20">
         <v>1.35</v>
@@ -3590,7 +3590,7 @@
         <v>2.82</v>
       </c>
       <c r="U20">
-        <v>2.62</v>
+        <v>2.84</v>
       </c>
       <c r="V20">
         <v>1.37</v>
@@ -3611,13 +3611,13 @@
         <v>1.85</v>
       </c>
       <c r="AB20">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AC20">
-        <v>2.85</v>
+        <v>3.14</v>
       </c>
       <c r="AD20">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AE20">
         <v>1.06</v>
@@ -3626,7 +3626,7 @@
         <v>1.7</v>
       </c>
       <c r="AG20">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK20">
         <v>1.72</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="O21">
         <v>3.13</v>
       </c>
       <c r="P21">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="Q21">
         <v>3.26</v>
@@ -3777,7 +3777,7 @@
         <v>1.8</v>
       </c>
       <c r="AC21">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="AD21">
         <v>1.25</v>
@@ -3789,7 +3789,7 @@
         <v>1.7</v>
       </c>
       <c r="AG21">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AK21">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,16 +3895,16 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="O22">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="P22">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="Q22">
-        <v>2.44</v>
+        <v>2.25</v>
       </c>
       <c r="R22">
         <v>2.01</v>
@@ -3913,7 +3913,7 @@
         <v>1.44</v>
       </c>
       <c r="T22">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="U22">
         <v>3.15</v>
@@ -3925,19 +3925,19 @@
         <v>1.05</v>
       </c>
       <c r="X22">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y22">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z22">
-        <v>3.03</v>
+        <v>2.73</v>
       </c>
       <c r="AA22">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="AB22">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AC22">
         <v>3.95</v>
@@ -3946,13 +3946,13 @@
         <v>1.22</v>
       </c>
       <c r="AE22">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AF22">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AG22">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AK22">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4067,7 +4067,7 @@
         <v>0</v>
       </c>
       <c r="Q23">
-        <v>2.94</v>
+        <v>3.4</v>
       </c>
       <c r="R23">
         <v>2.15</v>
@@ -4082,10 +4082,10 @@
         <v>2.4</v>
       </c>
       <c r="V23">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W23">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X23">
         <v>1.04</v>
@@ -4097,13 +4097,13 @@
         <v>4.1</v>
       </c>
       <c r="AA23">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB23">
         <v>2.15</v>
       </c>
       <c r="AC23">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="AD23">
         <v>1.4</v>
@@ -4115,7 +4115,7 @@
         <v>1.53</v>
       </c>
       <c r="AG23">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AK23">
         <v>1.36</v>
@@ -4553,7 +4553,7 @@
         <v>3.2</v>
       </c>
       <c r="P26">
-        <v>2.53</v>
+        <v>2.33</v>
       </c>
       <c r="Q26">
         <v>3.44</v>
@@ -4562,16 +4562,16 @@
         <v>2.01</v>
       </c>
       <c r="S26">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="T26">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="U26">
         <v>2.88</v>
       </c>
       <c r="V26">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W26">
         <v>1.05</v>
@@ -4586,16 +4586,16 @@
         <v>3.1</v>
       </c>
       <c r="AA26">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AB26">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AC26">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="AD26">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE26">
         <v>1.08</v>
@@ -4604,7 +4604,7 @@
         <v>1.8</v>
       </c>
       <c r="AG26">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -4918,10 +4918,10 @@
         <v>0</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE28">
         <v>0</v>
@@ -5042,25 +5042,25 @@
         <v>5</v>
       </c>
       <c r="P29">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="Q29">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="R29">
-        <v>2.75</v>
+        <v>2.99</v>
       </c>
       <c r="S29">
         <v>1.19</v>
       </c>
       <c r="T29">
-        <v>3.86</v>
+        <v>3.85</v>
       </c>
       <c r="U29">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="V29">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="W29">
         <v>1.2</v>
@@ -5084,13 +5084,13 @@
         <v>2</v>
       </c>
       <c r="AD29">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AE29">
         <v>1.3</v>
       </c>
       <c r="AF29">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AG29">
         <v>2.1</v>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="AK29">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,61 +5199,61 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="O30">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P30">
         <v>2.87</v>
       </c>
       <c r="Q30">
-        <v>2.9</v>
+        <v>2.79</v>
       </c>
       <c r="R30">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="S30">
+        <v>1.38</v>
+      </c>
+      <c r="T30">
+        <v>2.77</v>
+      </c>
+      <c r="U30">
+        <v>2.73</v>
+      </c>
+      <c r="V30">
         <v>1.39</v>
-      </c>
-      <c r="T30">
-        <v>2.73</v>
-      </c>
-      <c r="U30">
-        <v>2.77</v>
-      </c>
-      <c r="V30">
-        <v>1.38</v>
       </c>
       <c r="W30">
         <v>1.04</v>
       </c>
       <c r="X30">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y30">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z30">
-        <v>3.48</v>
+        <v>3.28</v>
       </c>
       <c r="AA30">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AB30">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC30">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AD30">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE30">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF30">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG30">
         <v>2.1</v>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK30">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5365,28 +5365,28 @@
         <v>1.26</v>
       </c>
       <c r="O31">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="P31">
         <v>7</v>
       </c>
       <c r="Q31">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="R31">
         <v>3</v>
       </c>
       <c r="S31">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="T31">
         <v>4.2</v>
       </c>
       <c r="U31">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="V31">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="W31">
         <v>1.25</v>
@@ -5398,13 +5398,13 @@
         <v>1.04</v>
       </c>
       <c r="Z31">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
       <c r="AA31">
         <v>1.29</v>
       </c>
       <c r="AB31">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="AC31">
         <v>1.75</v>
@@ -5413,13 +5413,13 @@
         <v>2.07</v>
       </c>
       <c r="AE31">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AF31">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG31">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="AK31">
         <v>3.45</v>
@@ -6014,37 +6014,37 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="O35">
         <v>3.4</v>
       </c>
       <c r="P35">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="Q35">
         <v>2.63</v>
       </c>
       <c r="R35">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S35">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T35">
-        <v>3.8</v>
+        <v>3.34</v>
       </c>
       <c r="U35">
-        <v>2.31</v>
+        <v>2.24</v>
       </c>
       <c r="V35">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W35">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X35">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y35">
         <v>1.13</v>
@@ -6177,19 +6177,19 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="O36">
         <v>4.4</v>
       </c>
       <c r="P36">
-        <v>5.6</v>
+        <v>6.7</v>
       </c>
       <c r="Q36">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="R36">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
       <c r="S36">
         <v>1.25</v>
@@ -6204,7 +6204,7 @@
         <v>1.6</v>
       </c>
       <c r="W36">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X36">
         <v>1.03</v>
@@ -6213,28 +6213,28 @@
         <v>1.19</v>
       </c>
       <c r="Z36">
-        <v>4.65</v>
+        <v>4.71</v>
       </c>
       <c r="AA36">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB36">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC36">
         <v>2.5</v>
       </c>
       <c r="AD36">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AE36">
         <v>1.17</v>
       </c>
       <c r="AF36">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG36">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>1.18</v>
       </c>
       <c r="AK36">
-        <v>2.51</v>
+        <v>2.66</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,10 +6340,10 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="O37">
-        <v>3.75</v>
+        <v>3.94</v>
       </c>
       <c r="P37">
         <v>3.9</v>
@@ -6352,7 +6352,7 @@
         <v>2.19</v>
       </c>
       <c r="R37">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S37">
         <v>1.25</v>
@@ -6361,7 +6361,7 @@
         <v>3.4</v>
       </c>
       <c r="U37">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="V37">
         <v>1.52</v>
@@ -6373,7 +6373,7 @@
         <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z37">
         <v>4.8</v>
@@ -6382,7 +6382,7 @@
         <v>1.55</v>
       </c>
       <c r="AB37">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AC37">
         <v>2.5</v>
@@ -6391,13 +6391,13 @@
         <v>1.44</v>
       </c>
       <c r="AE37">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF37">
         <v>1.57</v>
       </c>
       <c r="AG37">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         <v>1.83</v>
       </c>
       <c r="R39">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="S39">
         <v>1.26</v>
@@ -6702,7 +6702,7 @@
         <v>1.14</v>
       </c>
       <c r="Z39">
-        <v>4.4</v>
+        <v>4.77</v>
       </c>
       <c r="AA39">
         <v>1.56</v>
@@ -6717,13 +6717,13 @@
         <v>1.53</v>
       </c>
       <c r="AE39">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AF39">
         <v>1.81</v>
       </c>
       <c r="AG39">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6835,28 +6835,28 @@
         <v>3.4</v>
       </c>
       <c r="P40">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q40">
         <v>2.75</v>
       </c>
       <c r="R40">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="S40">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T40">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U40">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="V40">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W40">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X40">
         <v>1.02</v>
@@ -6865,28 +6865,28 @@
         <v>1.2</v>
       </c>
       <c r="Z40">
-        <v>4.23</v>
+        <v>4.33</v>
       </c>
       <c r="AA40">
         <v>1.67</v>
       </c>
       <c r="AB40">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC40">
         <v>2.55</v>
       </c>
       <c r="AD40">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AE40">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF40">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG40">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK40">
         <v>1.54</v>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="O42">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="P42">
         <v>6.75</v>
@@ -7170,19 +7170,19 @@
         <v>2.9</v>
       </c>
       <c r="S42">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="T42">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="U42">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V42">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="W42">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X42">
         <v>1.01</v>
@@ -7191,13 +7191,13 @@
         <v>1.04</v>
       </c>
       <c r="Z42">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="AA42">
         <v>1.33</v>
       </c>
       <c r="AB42">
-        <v>3.36</v>
+        <v>3.38</v>
       </c>
       <c r="AC42">
         <v>1.82</v>
@@ -7209,10 +7209,10 @@
         <v>1.43</v>
       </c>
       <c r="AF42">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AG42">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AK42">
         <v>3</v>
@@ -7318,19 +7318,19 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="O43">
         <v>3.18</v>
       </c>
       <c r="P43">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="Q43">
-        <v>2.95</v>
+        <v>2.73</v>
       </c>
       <c r="R43">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="S43">
         <v>1.39</v>
@@ -7354,7 +7354,7 @@
         <v>1.24</v>
       </c>
       <c r="Z43">
-        <v>3.73</v>
+        <v>3.76</v>
       </c>
       <c r="AA43">
         <v>1.86</v>
@@ -7366,16 +7366,16 @@
         <v>3.2</v>
       </c>
       <c r="AD43">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE43">
         <v>1.13</v>
       </c>
       <c r="AF43">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AG43">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7508,7 +7508,7 @@
         <v>1.75</v>
       </c>
       <c r="W44">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X44">
         <v>1.03</v>
@@ -7520,16 +7520,16 @@
         <v>5.75</v>
       </c>
       <c r="AA44">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AB44">
-        <v>2.59</v>
+        <v>2.89</v>
       </c>
       <c r="AC44">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AD44">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AE44">
         <v>1.3</v>
@@ -7644,19 +7644,19 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O45">
         <v>3.4</v>
       </c>
       <c r="P45">
-        <v>3.1</v>
+        <v>2.65</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
       </c>
       <c r="R45">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="S45">
         <v>1.37</v>
@@ -7674,10 +7674,10 @@
         <v>1.08</v>
       </c>
       <c r="X45">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z45">
         <v>3.84</v>
@@ -7692,7 +7692,7 @@
         <v>2.72</v>
       </c>
       <c r="AD45">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AE45">
         <v>1.14</v>
@@ -7717,7 +7717,7 @@
         <v>1.31</v>
       </c>
       <c r="AK45">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>4.45</v>
+        <v>4.8</v>
       </c>
       <c r="O46">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P46">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="Q46">
         <v>5</v>
@@ -7825,7 +7825,7 @@
         <v>1.41</v>
       </c>
       <c r="T46">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="U46">
         <v>2.98</v>
@@ -7834,13 +7834,13 @@
         <v>1.39</v>
       </c>
       <c r="W46">
+        <v>1.08</v>
+      </c>
+      <c r="X46">
         <v>1.05</v>
       </c>
-      <c r="X46">
-        <v>1.01</v>
-      </c>
       <c r="Y46">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z46">
         <v>3.4</v>
@@ -7855,7 +7855,7 @@
         <v>3.4</v>
       </c>
       <c r="AD46">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AE46">
         <v>1.04</v>
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="O48">
         <v>2.95</v>
@@ -8151,7 +8151,7 @@
         <v>1.5</v>
       </c>
       <c r="T48">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="U48">
         <v>3.22</v>
@@ -8166,7 +8166,7 @@
         <v>1.05</v>
       </c>
       <c r="Y48">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="Z48">
         <v>2.66</v>
@@ -8175,13 +8175,13 @@
         <v>2.27</v>
       </c>
       <c r="AB48">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AC48">
-        <v>3.92</v>
+        <v>4.18</v>
       </c>
       <c r="AD48">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AE48">
         <v>1.03</v>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AK48">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8788,10 +8788,10 @@
         <v>2.29</v>
       </c>
       <c r="O52">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="P52">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="Q52">
         <v>3.12</v>
@@ -8803,10 +8803,10 @@
         <v>1.42</v>
       </c>
       <c r="T52">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="U52">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="V52">
         <v>1.34</v>
@@ -8815,31 +8815,31 @@
         <v>1.03</v>
       </c>
       <c r="X52">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y52">
         <v>1.36</v>
       </c>
       <c r="Z52">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AA52">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="AB52">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AC52">
-        <v>3.72</v>
+        <v>3.76</v>
       </c>
       <c r="AD52">
         <v>1.22</v>
       </c>
       <c r="AE52">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF52">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AG52">
         <v>1.95</v>
@@ -8948,7 +8948,7 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="O53">
         <v>3.1</v>
@@ -9606,19 +9606,19 @@
         <v>2.58</v>
       </c>
       <c r="P57">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="Q57">
         <v>4.12</v>
       </c>
       <c r="R57">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="S57">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="T57">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="U57">
         <v>4</v>
@@ -9630,13 +9630,13 @@
         <v>1.03</v>
       </c>
       <c r="X57">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Y57">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Z57">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="AA57">
         <v>3.2</v>
@@ -9645,16 +9645,16 @@
         <v>1.3</v>
       </c>
       <c r="AC57">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="AD57">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AE57">
         <v>1.01</v>
       </c>
       <c r="AF57">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AG57">
         <v>1.44</v>
@@ -9673,7 +9673,7 @@
         <v>1.44</v>
       </c>
       <c r="AK57">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9763,25 +9763,25 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="O58">
-        <v>3.02</v>
+        <v>3.15</v>
       </c>
       <c r="P58">
-        <v>3.22</v>
+        <v>2.35</v>
       </c>
       <c r="Q58">
-        <v>3.73</v>
+        <v>3.66</v>
       </c>
       <c r="R58">
         <v>1.96</v>
       </c>
       <c r="S58">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="T58">
-        <v>2.57</v>
+        <v>2.47</v>
       </c>
       <c r="U58">
         <v>3.28</v>
@@ -9796,19 +9796,19 @@
         <v>1.03</v>
       </c>
       <c r="Y58">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="Z58">
-        <v>2.79</v>
+        <v>2.62</v>
       </c>
       <c r="AA58">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="AB58">
         <v>1.58</v>
       </c>
       <c r="AC58">
-        <v>4.25</v>
+        <v>4.38</v>
       </c>
       <c r="AD58">
         <v>1.15</v>
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="O60">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="P60">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="Q60">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="R60">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="S60">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T60">
-        <v>3.92</v>
+        <v>4.5</v>
       </c>
       <c r="U60">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="V60">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="W60">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="X60">
         <v>1.01</v>
       </c>
       <c r="Y60">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z60">
-        <v>6.4</v>
+        <v>6.25</v>
       </c>
       <c r="AA60">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AB60">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AC60">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AD60">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AE60">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AF60">
         <v>1.44</v>
       </c>
       <c r="AG60">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AK60">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10904,7 +10904,7 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="O65">
         <v>3.1</v>
@@ -10925,7 +10925,7 @@
         <v>2.59</v>
       </c>
       <c r="U65">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="V65">
         <v>1.33</v>
@@ -10940,7 +10940,7 @@
         <v>1.28</v>
       </c>
       <c r="Z65">
-        <v>3.28</v>
+        <v>3.31</v>
       </c>
       <c r="AA65">
         <v>1.95</v>
@@ -10952,7 +10952,7 @@
         <v>3.34</v>
       </c>
       <c r="AD65">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE65">
         <v>1.08</v>
@@ -11230,7 +11230,7 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="O67">
         <v>3.25</v>
@@ -11239,10 +11239,10 @@
         <v>2.44</v>
       </c>
       <c r="Q67">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R67">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S67">
         <v>1.33</v>
@@ -11251,13 +11251,13 @@
         <v>2.95</v>
       </c>
       <c r="U67">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="V67">
         <v>1.4</v>
       </c>
       <c r="W67">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X67">
         <v>1.05</v>
@@ -11278,13 +11278,13 @@
         <v>3.15</v>
       </c>
       <c r="AD67">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE67">
         <v>1.12</v>
       </c>
       <c r="AF67">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AG67">
         <v>2.1</v>
@@ -11414,7 +11414,7 @@
         <v>3.1</v>
       </c>
       <c r="U68">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="V68">
         <v>1.52</v>
@@ -11429,13 +11429,13 @@
         <v>1.2</v>
       </c>
       <c r="Z68">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AA68">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AB68">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AC68">
         <v>2.65</v>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="AK68">
-        <v>2.18</v>
+        <v>2.61</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11577,10 +11577,10 @@
         <v>2.9</v>
       </c>
       <c r="U69">
-        <v>2.48</v>
+        <v>2.65</v>
       </c>
       <c r="V69">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W69">
         <v>1.08</v>
@@ -11626,7 +11626,7 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AK69">
         <v>1.73</v>
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="O70">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P70">
-        <v>2.37</v>
+        <v>2.53</v>
       </c>
       <c r="Q70">
         <v>0</v>
@@ -12697,19 +12697,19 @@
         </is>
       </c>
       <c r="N76">
-        <v>4.35</v>
+        <v>3.67</v>
       </c>
       <c r="O76">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P76">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="Q76">
-        <v>4.95</v>
+        <v>3.93</v>
       </c>
       <c r="R76">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="S76">
         <v>1.47</v>
@@ -12718,7 +12718,7 @@
         <v>2.59</v>
       </c>
       <c r="U76">
-        <v>3.33</v>
+        <v>3.18</v>
       </c>
       <c r="V76">
         <v>1.33</v>
@@ -12739,16 +12739,16 @@
         <v>2.19</v>
       </c>
       <c r="AB76">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AC76">
         <v>3.68</v>
       </c>
       <c r="AD76">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE76">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF76">
         <v>1.9</v>
@@ -12767,7 +12767,7 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.38</v>
+        <v>1.23</v>
       </c>
       <c r="AK76">
         <v>1.26</v>
@@ -12863,7 +12863,7 @@
         <v>1.72</v>
       </c>
       <c r="O77">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="P77">
         <v>4.5</v>
@@ -12875,19 +12875,19 @@
         <v>2.21</v>
       </c>
       <c r="S77">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T77">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="U77">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="V77">
         <v>1.42</v>
       </c>
       <c r="W77">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X77">
         <v>1.05</v>
@@ -12896,13 +12896,13 @@
         <v>1.29</v>
       </c>
       <c r="Z77">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AA77">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB77">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AC77">
         <v>3.3</v>
@@ -12933,7 +12933,7 @@
         <v>1.13</v>
       </c>
       <c r="AK77">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13186,16 +13186,16 @@
         </is>
       </c>
       <c r="N79">
-        <v>8.449999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O79">
-        <v>6</v>
+        <v>6.05</v>
       </c>
       <c r="P79">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Q79">
-        <v>7.5</v>
+        <v>6.28</v>
       </c>
       <c r="R79">
         <v>2.64</v>
@@ -13204,22 +13204,22 @@
         <v>1.2</v>
       </c>
       <c r="T79">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U79">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V79">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="W79">
         <v>1.18</v>
       </c>
       <c r="X79">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y79">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z79">
         <v>6.5</v>
@@ -13231,19 +13231,19 @@
         <v>2.75</v>
       </c>
       <c r="AC79">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AD79">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AE79">
         <v>1.3</v>
       </c>
       <c r="AF79">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG79">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,7 +13256,7 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.13</v>
+        <v>4</v>
       </c>
       <c r="AK79">
         <v>1.03</v>
@@ -13515,10 +13515,10 @@
         <v>2.15</v>
       </c>
       <c r="O81">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P81">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="Q81">
         <v>2.77</v>
@@ -13539,7 +13539,7 @@
         <v>1.44</v>
       </c>
       <c r="W81">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X81">
         <v>1</v>
@@ -13548,16 +13548,16 @@
         <v>1.23</v>
       </c>
       <c r="Z81">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AA81">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AB81">
         <v>2</v>
       </c>
       <c r="AC81">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="AD81">
         <v>1.36</v>
@@ -13675,7 +13675,7 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="O82">
         <v>3</v>
@@ -13699,7 +13699,7 @@
         <v>3.15</v>
       </c>
       <c r="V82">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W82">
         <v>1.01</v>
@@ -13711,7 +13711,7 @@
         <v>1.33</v>
       </c>
       <c r="Z82">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AA82">
         <v>2.18</v>
@@ -14004,31 +14004,31 @@
         <v>2.2</v>
       </c>
       <c r="O84">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P84">
-        <v>2.87</v>
+        <v>2.95</v>
       </c>
       <c r="Q84">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="R84">
         <v>2.25</v>
       </c>
       <c r="S84">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T84">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U84">
-        <v>2.69</v>
+        <v>2.6</v>
       </c>
       <c r="V84">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W84">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X84">
         <v>1.02</v>
@@ -14049,13 +14049,13 @@
         <v>2.78</v>
       </c>
       <c r="AD84">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AE84">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF84">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
       <c r="AG84">
         <v>2.15</v>
@@ -14074,7 +14074,7 @@
         <v>1.36</v>
       </c>
       <c r="AK84">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14327,19 +14327,19 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="O86">
         <v>3.5</v>
       </c>
       <c r="P86">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Q86">
         <v>2.3</v>
       </c>
       <c r="R86">
-        <v>2.08</v>
+        <v>2.19</v>
       </c>
       <c r="S86">
         <v>1.3</v>
@@ -14369,7 +14369,7 @@
         <v>1.89</v>
       </c>
       <c r="AB86">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="AC86">
         <v>3.19</v>
@@ -14384,7 +14384,7 @@
         <v>1.73</v>
       </c>
       <c r="AG86">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14400,7 +14400,7 @@
         <v>1.17</v>
       </c>
       <c r="AK86">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14653,7 +14653,7 @@
         </is>
       </c>
       <c r="N88">
-        <v>3.1</v>
+        <v>3.51</v>
       </c>
       <c r="O88">
         <v>3.2</v>
@@ -14686,13 +14686,13 @@
         <v>1.03</v>
       </c>
       <c r="Y88">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="Z88">
         <v>3.8</v>
       </c>
       <c r="AA88">
-        <v>1.92</v>
+        <v>1.81</v>
       </c>
       <c r="AB88">
         <v>1.96</v>
@@ -14819,7 +14819,7 @@
         <v>3.47</v>
       </c>
       <c r="O89">
-        <v>3.9</v>
+        <v>3.94</v>
       </c>
       <c r="P89">
         <v>1.86</v>
@@ -14837,22 +14837,22 @@
         <v>3.4</v>
       </c>
       <c r="U89">
-        <v>2.39</v>
+        <v>2.2</v>
       </c>
       <c r="V89">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W89">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X89">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y89">
         <v>1.16</v>
       </c>
       <c r="Z89">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AA89">
         <v>1.57</v>
@@ -14864,10 +14864,10 @@
         <v>2.43</v>
       </c>
       <c r="AD89">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AE89">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AF89">
         <v>1.53</v>
@@ -14985,7 +14985,7 @@
         <v>3.9</v>
       </c>
       <c r="P90">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="Q90">
         <v>3.65</v>
@@ -15006,7 +15006,7 @@
         <v>1.68</v>
       </c>
       <c r="W90">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="X90">
         <v>1.01</v>
@@ -15021,13 +15021,13 @@
         <v>1.46</v>
       </c>
       <c r="AB90">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="AC90">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AD90">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AE90">
         <v>1.27</v>
@@ -15142,13 +15142,13 @@
         </is>
       </c>
       <c r="N91">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O91">
         <v>3.35</v>
       </c>
       <c r="P91">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="Q91">
         <v>4.39</v>
@@ -15160,46 +15160,46 @@
         <v>1.37</v>
       </c>
       <c r="T91">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="U91">
-        <v>2.83</v>
+        <v>2.79</v>
       </c>
       <c r="V91">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W91">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X91">
         <v>1.02</v>
       </c>
       <c r="Y91">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z91">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AA91">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AB91">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AC91">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AD91">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE91">
         <v>1.04</v>
       </c>
       <c r="AF91">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AG91">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="AK91">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15326,7 +15326,7 @@
         <v>3.22</v>
       </c>
       <c r="U92">
-        <v>2.39</v>
+        <v>2.47</v>
       </c>
       <c r="V92">
         <v>1.52</v>
@@ -15347,13 +15347,13 @@
         <v>1.66</v>
       </c>
       <c r="AB92">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="AC92">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="AD92">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AE92">
         <v>1.18</v>
@@ -15362,7 +15362,7 @@
         <v>1.57</v>
       </c>
       <c r="AG92">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15468,46 +15468,46 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="O93">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="P93">
-        <v>2</v>
+        <v>2.27</v>
       </c>
       <c r="Q93">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="R93">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="S93">
         <v>1.3</v>
       </c>
       <c r="T93">
-        <v>3.2</v>
+        <v>2.91</v>
       </c>
       <c r="U93">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="V93">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W93">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X93">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y93">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z93">
         <v>3.9</v>
       </c>
       <c r="AA93">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB93">
         <v>2</v>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AK93">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15631,22 +15631,22 @@
         </is>
       </c>
       <c r="N94">
-        <v>1.34</v>
+        <v>1.47</v>
       </c>
       <c r="O94">
-        <v>4.2</v>
+        <v>4.35</v>
       </c>
       <c r="P94">
         <v>5</v>
       </c>
       <c r="Q94">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="R94">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="S94">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T94">
         <v>3.42</v>
@@ -15655,7 +15655,7 @@
         <v>2.25</v>
       </c>
       <c r="V94">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="W94">
         <v>1.12</v>
@@ -15664,7 +15664,7 @@
         <v>1.03</v>
       </c>
       <c r="Y94">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z94">
         <v>5</v>
@@ -15682,13 +15682,13 @@
         <v>1.62</v>
       </c>
       <c r="AE94">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF94">
         <v>1.57</v>
       </c>
       <c r="AG94">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15704,7 +15704,7 @@
         <v>1.2</v>
       </c>
       <c r="AK94">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="O99">
-        <v>4.85</v>
+        <v>4.45</v>
       </c>
       <c r="P99">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="Q99">
         <v>1.83</v>
       </c>
       <c r="R99">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="S99">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T99">
         <v>2.92</v>
       </c>
       <c r="U99">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="V99">
         <v>1.49</v>
       </c>
       <c r="W99">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X99">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y99">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z99">
         <v>4</v>
       </c>
       <c r="AA99">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AB99">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AC99">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="AD99">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE99">
         <v>1.14</v>
       </c>
       <c r="AF99">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AG99">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16772,25 +16772,25 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="O101">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P101">
-        <v>2.85</v>
+        <v>3.02</v>
       </c>
       <c r="Q101">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="R101">
         <v>2.06</v>
       </c>
       <c r="S101">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T101">
-        <v>2.71</v>
+        <v>2.88</v>
       </c>
       <c r="U101">
         <v>2.75</v>
@@ -16799,16 +16799,16 @@
         <v>1.36</v>
       </c>
       <c r="W101">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X101">
         <v>1.01</v>
       </c>
       <c r="Y101">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z101">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="AA101">
         <v>1.91</v>
@@ -16817,10 +16817,10 @@
         <v>1.78</v>
       </c>
       <c r="AC101">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AD101">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE101">
         <v>1.06</v>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK101">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16935,13 +16935,13 @@
         </is>
       </c>
       <c r="N102">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O102">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P102">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q102">
         <v>3.44</v>
@@ -16950,7 +16950,7 @@
         <v>2.2</v>
       </c>
       <c r="S102">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T102">
         <v>2.88</v>
@@ -16962,10 +16962,10 @@
         <v>1.4</v>
       </c>
       <c r="W102">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X102">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y102">
         <v>1.25</v>
@@ -16974,16 +16974,16 @@
         <v>3.35</v>
       </c>
       <c r="AA102">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AB102">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AC102">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="AD102">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AE102">
         <v>1.09</v>
@@ -17008,7 +17008,7 @@
         <v>1.24</v>
       </c>
       <c r="AK102">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17264,16 +17264,16 @@
         <v>1.44</v>
       </c>
       <c r="O104">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P104">
         <v>5.5</v>
       </c>
       <c r="Q104">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="R104">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="S104">
         <v>1.31</v>
@@ -17282,7 +17282,7 @@
         <v>2.97</v>
       </c>
       <c r="U104">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="V104">
         <v>1.44</v>
@@ -17291,16 +17291,16 @@
         <v>1.11</v>
       </c>
       <c r="X104">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y104">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z104">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="AA104">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AB104">
         <v>2.05</v>
@@ -17309,13 +17309,13 @@
         <v>2.7</v>
       </c>
       <c r="AD104">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AE104">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF104">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AG104">
         <v>1.91</v>
@@ -17331,7 +17331,7 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AK104">
         <v>2.4</v>
@@ -17750,13 +17750,13 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="O107">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P107">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="Q107">
         <v>2.6</v>
@@ -17780,28 +17780,28 @@
         <v>1.08</v>
       </c>
       <c r="X107">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y107">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z107">
-        <v>4.5</v>
+        <v>4.21</v>
       </c>
       <c r="AA107">
         <v>1.77</v>
       </c>
       <c r="AB107">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AC107">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="AD107">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AE107">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF107">
         <v>1.6</v>
@@ -17823,7 +17823,7 @@
         <v>1.25</v>
       </c>
       <c r="AK107">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17913,13 +17913,13 @@
         </is>
       </c>
       <c r="N108">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="O108">
         <v>3.2</v>
       </c>
       <c r="P108">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="Q108">
         <v>3.3</v>
@@ -20201,16 +20201,16 @@
         <v>3.6</v>
       </c>
       <c r="P122">
-        <v>4.1</v>
+        <v>4.35</v>
       </c>
       <c r="Q122">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="R122">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="S122">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T122">
         <v>3.25</v>
@@ -20225,28 +20225,28 @@
         <v>1.12</v>
       </c>
       <c r="X122">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y122">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z122">
-        <v>3.85</v>
+        <v>4.33</v>
       </c>
       <c r="AA122">
         <v>1.72</v>
       </c>
       <c r="AB122">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AC122">
         <v>2.75</v>
       </c>
       <c r="AD122">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE122">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AF122">
         <v>1.66</v>
@@ -20358,64 +20358,64 @@
         </is>
       </c>
       <c r="N123">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="O123">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="P123">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="Q123">
-        <v>3.83</v>
+        <v>3.4</v>
       </c>
       <c r="R123">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="S123">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T123">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="U123">
-        <v>3.02</v>
+        <v>2.77</v>
       </c>
       <c r="V123">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W123">
+        <v>1.07</v>
+      </c>
+      <c r="X123">
         <v>1.05</v>
-      </c>
-      <c r="X123">
-        <v>1.04</v>
       </c>
       <c r="Y123">
         <v>1.33</v>
       </c>
       <c r="Z123">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="AA123">
         <v>2.05</v>
       </c>
       <c r="AB123">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AC123">
-        <v>3.62</v>
+        <v>3.8</v>
       </c>
       <c r="AD123">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE123">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF123">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG123">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AK123">
         <v>1.36</v>
@@ -21336,61 +21336,61 @@
         </is>
       </c>
       <c r="N129">
-        <v>4.95</v>
+        <v>4.2</v>
       </c>
       <c r="O129">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P129">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="Q129">
         <v>4.4</v>
       </c>
       <c r="R129">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="S129">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T129">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="U129">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="V129">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="W129">
         <v>1.17</v>
       </c>
       <c r="X129">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y129">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Z129">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="AA129">
         <v>1.4</v>
       </c>
       <c r="AB129">
-        <v>2.59</v>
+        <v>2.43</v>
       </c>
       <c r="AC129">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="AD129">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AE129">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF129">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AG129">
         <v>2.4</v>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AK129">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21508,7 +21508,7 @@
         <v>2.62</v>
       </c>
       <c r="Q130">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="R130">
         <v>2.19</v>
@@ -21520,7 +21520,7 @@
         <v>3.12</v>
       </c>
       <c r="U130">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="V130">
         <v>1.46</v>
@@ -21538,25 +21538,25 @@
         <v>3.98</v>
       </c>
       <c r="AA130">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB130">
         <v>2.07</v>
       </c>
       <c r="AC130">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="AD130">
         <v>1.4</v>
       </c>
       <c r="AE130">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AF130">
         <v>1.53</v>
       </c>
       <c r="AG130">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="AK130">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -21671,7 +21671,7 @@
         <v>3</v>
       </c>
       <c r="Q131">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="R131">
         <v>1.95</v>
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="AJ131">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK131">
         <v>1.57</v>
@@ -21837,28 +21837,28 @@
         <v>1.93</v>
       </c>
       <c r="R132">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S132">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T132">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U132">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="V132">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W132">
         <v>1.08</v>
       </c>
       <c r="X132">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y132">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z132">
         <v>3.5</v>
@@ -21870,16 +21870,16 @@
         <v>1.83</v>
       </c>
       <c r="AC132">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AD132">
         <v>1.3</v>
       </c>
       <c r="AE132">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF132">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AG132">
         <v>1.67</v>
@@ -22151,13 +22151,13 @@
         </is>
       </c>
       <c r="N134">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="O134">
-        <v>3.01</v>
+        <v>3.1</v>
       </c>
       <c r="P134">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="Q134">
         <v>3.18</v>
@@ -22178,7 +22178,7 @@
         <v>1.21</v>
       </c>
       <c r="W134">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X134">
         <v>1.04</v>
@@ -22190,25 +22190,25 @@
         <v>2.36</v>
       </c>
       <c r="AA134">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="AB134">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AC134">
-        <v>5.5</v>
+        <v>5.45</v>
       </c>
       <c r="AD134">
         <v>1.08</v>
       </c>
       <c r="AE134">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF134">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AG134">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22329,28 +22329,28 @@
         <v>1.74</v>
       </c>
       <c r="S135">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="T135">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="U135">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="V135">
         <v>1.14</v>
       </c>
       <c r="W135">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X135">
         <v>1.1</v>
       </c>
       <c r="Y135">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Z135">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AA135">
         <v>3.14</v>
@@ -22480,25 +22480,25 @@
         <v>2.7</v>
       </c>
       <c r="O136">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P136">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="Q136">
         <v>3.1</v>
       </c>
       <c r="R136">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="S136">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T136">
         <v>3.7</v>
       </c>
       <c r="U136">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="V136">
         <v>1.61</v>
@@ -22510,7 +22510,7 @@
         <v>1.03</v>
       </c>
       <c r="Y136">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z136">
         <v>5</v>
@@ -22519,22 +22519,22 @@
         <v>1.5</v>
       </c>
       <c r="AB136">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="AC136">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="AD136">
         <v>1.56</v>
       </c>
       <c r="AE136">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF136">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AG136">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22550,7 +22550,7 @@
         <v>1.25</v>
       </c>
       <c r="AK136">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22640,13 +22640,13 @@
         </is>
       </c>
       <c r="N137">
-        <v>4.8</v>
+        <v>5.25</v>
       </c>
       <c r="O137">
         <v>3.7</v>
       </c>
       <c r="P137">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="Q137">
         <v>6</v>
@@ -22661,7 +22661,7 @@
         <v>2.85</v>
       </c>
       <c r="U137">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="V137">
         <v>1.41</v>
@@ -22682,7 +22682,7 @@
         <v>1.77</v>
       </c>
       <c r="AB137">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="AC137">
         <v>3.4</v>
@@ -22694,7 +22694,7 @@
         <v>1.1</v>
       </c>
       <c r="AF137">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AG137">
         <v>1.87</v>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="AK137">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -22818,13 +22818,13 @@
         <v>1.97</v>
       </c>
       <c r="S138">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T138">
         <v>2.75</v>
       </c>
       <c r="U138">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="V138">
         <v>1.31</v>
@@ -22873,10 +22873,10 @@
         </is>
       </c>
       <c r="AJ138">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AK138">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AL138">
         <v>0</v>
@@ -23295,7 +23295,7 @@
         <v>1.61</v>
       </c>
       <c r="O141">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P141">
         <v>4.3</v>
@@ -23313,7 +23313,7 @@
         <v>3.2</v>
       </c>
       <c r="U141">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="V141">
         <v>1.51</v>
@@ -23331,7 +23331,7 @@
         <v>3.95</v>
       </c>
       <c r="AA141">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AB141">
         <v>2.19</v>
@@ -23343,13 +23343,13 @@
         <v>1.44</v>
       </c>
       <c r="AE141">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AF141">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG141">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AH141" t="inlineStr">
         <is>
@@ -23618,25 +23618,25 @@
         </is>
       </c>
       <c r="N143">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="O143">
         <v>3.38</v>
       </c>
       <c r="P143">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="Q143">
         <v>2.5</v>
       </c>
       <c r="R143">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S143">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="T143">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="U143">
         <v>2.75</v>
@@ -23645,7 +23645,7 @@
         <v>1.4</v>
       </c>
       <c r="W143">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X143">
         <v>1.05</v>
@@ -23654,28 +23654,28 @@
         <v>1.24</v>
       </c>
       <c r="Z143">
-        <v>3.64</v>
+        <v>3.6</v>
       </c>
       <c r="AA143">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="AB143">
         <v>1.85</v>
       </c>
       <c r="AC143">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AD143">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE143">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF143">
         <v>1.62</v>
       </c>
       <c r="AG143">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AH143" t="inlineStr">
         <is>
@@ -23787,13 +23787,13 @@
         <v>4.4</v>
       </c>
       <c r="P144">
-        <v>6.9</v>
+        <v>5.9</v>
       </c>
       <c r="Q144">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="R144">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="S144">
         <v>1.28</v>
@@ -23802,25 +23802,25 @@
         <v>3.5</v>
       </c>
       <c r="U144">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V144">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W144">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X144">
         <v>1.01</v>
       </c>
       <c r="Y144">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z144">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AA144">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AB144">
         <v>2.1</v>
@@ -23829,13 +23829,13 @@
         <v>2.6</v>
       </c>
       <c r="AD144">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AE144">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF144">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AG144">
         <v>1.83</v>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AK144">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="O145">
         <v>3.1</v>
       </c>
       <c r="P145">
-        <v>3.3</v>
+        <v>3.48</v>
       </c>
       <c r="Q145">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="R145">
         <v>2</v>
       </c>
       <c r="S145">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="T145">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="U145">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="V145">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="W145">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X145">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y145">
         <v>1.4</v>
       </c>
       <c r="Z145">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="AA145">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AB145">
         <v>1.62</v>
       </c>
       <c r="AC145">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="AD145">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE145">
         <v>1.05</v>
       </c>
       <c r="AF145">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AG145">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24107,13 +24107,13 @@
         </is>
       </c>
       <c r="N146">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="O146">
-        <v>4.3</v>
+        <v>4.45</v>
       </c>
       <c r="P146">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="Q146">
         <v>6</v>
@@ -24122,49 +24122,49 @@
         <v>2.38</v>
       </c>
       <c r="S146">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T146">
         <v>3</v>
       </c>
       <c r="U146">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="V146">
         <v>1.48</v>
       </c>
       <c r="W146">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X146">
         <v>1.02</v>
       </c>
       <c r="Y146">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z146">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AA146">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AB146">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="AC146">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AD146">
         <v>1.38</v>
       </c>
       <c r="AE146">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AF146">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="AG146">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="AK146">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24270,13 +24270,13 @@
         </is>
       </c>
       <c r="N147">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="O147">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="P147">
-        <v>7.1</v>
+        <v>8.6</v>
       </c>
       <c r="Q147">
         <v>0</v>
@@ -24436,61 +24436,61 @@
         <v>2.7</v>
       </c>
       <c r="O148">
-        <v>3.41</v>
+        <v>3.55</v>
       </c>
       <c r="P148">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="Q148">
-        <v>3.5</v>
+        <v>3.69</v>
       </c>
       <c r="R148">
         <v>2.19</v>
       </c>
       <c r="S148">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T148">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="U148">
         <v>2.38</v>
       </c>
       <c r="V148">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="W148">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X148">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y148">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z148">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AA148">
         <v>1.65</v>
       </c>
       <c r="AB148">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AC148">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="AD148">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AE148">
         <v>1.17</v>
       </c>
       <c r="AF148">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG148">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AH148" t="inlineStr">
         <is>
@@ -24503,10 +24503,10 @@
         </is>
       </c>
       <c r="AJ148">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="AK148">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AL148">
         <v>0</v>
@@ -24623,7 +24623,7 @@
         <v>1.36</v>
       </c>
       <c r="W149">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X149">
         <v>1.01</v>
@@ -24638,7 +24638,7 @@
         <v>1.87</v>
       </c>
       <c r="AB149">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AC149">
         <v>3.2</v>
@@ -24647,7 +24647,7 @@
         <v>1.26</v>
       </c>
       <c r="AE149">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF149">
         <v>1.99</v>
@@ -24762,7 +24762,7 @@
         <v>1.63</v>
       </c>
       <c r="O150">
-        <v>3.62</v>
+        <v>3.7</v>
       </c>
       <c r="P150">
         <v>5.6</v>
@@ -24795,10 +24795,10 @@
         <v>1.29</v>
       </c>
       <c r="Z150">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="AA150">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AB150">
         <v>1.85</v>
@@ -24943,10 +24943,10 @@
         <v>2.88</v>
       </c>
       <c r="U151">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="V151">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="W151">
         <v>1.03</v>
@@ -24967,7 +24967,7 @@
         <v>1.72</v>
       </c>
       <c r="AC151">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="AD151">
         <v>1.2</v>
@@ -24992,7 +24992,7 @@
         </is>
       </c>
       <c r="AJ151">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK151">
         <v>2.05</v>
@@ -25136,13 +25136,13 @@
         <v>1.44</v>
       </c>
       <c r="AE152">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF152">
         <v>1.55</v>
       </c>
       <c r="AG152">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
@@ -25155,10 +25155,10 @@
         </is>
       </c>
       <c r="AJ152">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK152">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -25420,13 +25420,13 @@
         <v>6.4</v>
       </c>
       <c r="Q154">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="R154">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="S154">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T154">
         <v>2.88</v>
@@ -25441,16 +25441,16 @@
         <v>1.03</v>
       </c>
       <c r="X154">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y154">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z154">
-        <v>3.22</v>
+        <v>3.08</v>
       </c>
       <c r="AA154">
-        <v>2.01</v>
+        <v>1.96</v>
       </c>
       <c r="AB154">
         <v>1.75</v>
@@ -25481,7 +25481,7 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AK154">
         <v>2.88</v>
@@ -25574,25 +25574,25 @@
         </is>
       </c>
       <c r="N155">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="O155">
-        <v>7.1</v>
+        <v>7.8</v>
       </c>
       <c r="P155">
-        <v>9.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="Q155">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="R155">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="S155">
         <v>1.13</v>
       </c>
       <c r="T155">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="U155">
         <v>1.89</v>
@@ -25601,7 +25601,7 @@
         <v>1.81</v>
       </c>
       <c r="W155">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="X155">
         <v>1.01</v>
@@ -25610,7 +25610,7 @@
         <v>1.04</v>
       </c>
       <c r="Z155">
-        <v>4.2</v>
+        <v>7.1</v>
       </c>
       <c r="AA155">
         <v>1.33</v>
@@ -25619,19 +25619,19 @@
         <v>3.14</v>
       </c>
       <c r="AC155">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AD155">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AE155">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AF155">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AG155">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25644,10 +25644,10 @@
         </is>
       </c>
       <c r="AJ155">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK155">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25743,37 +25743,37 @@
         <v>3.2</v>
       </c>
       <c r="P156">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="Q156">
         <v>2.54</v>
       </c>
       <c r="R156">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="S156">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="T156">
-        <v>2.75</v>
+        <v>2.18</v>
       </c>
       <c r="U156">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="V156">
         <v>1.32</v>
       </c>
       <c r="W156">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X156">
         <v>1</v>
       </c>
       <c r="Y156">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z156">
-        <v>3.19</v>
+        <v>3.1</v>
       </c>
       <c r="AA156">
         <v>2</v>
@@ -25782,7 +25782,7 @@
         <v>1.73</v>
       </c>
       <c r="AC156">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="AD156">
         <v>1.25</v>
@@ -25794,7 +25794,7 @@
         <v>1.83</v>
       </c>
       <c r="AG156">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25807,10 +25807,10 @@
         </is>
       </c>
       <c r="AJ156">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK156">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -25903,7 +25903,7 @@
         <v>1.5</v>
       </c>
       <c r="O157">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="P157">
         <v>4.9</v>
@@ -25918,10 +25918,10 @@
         <v>1.3</v>
       </c>
       <c r="T157">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U157">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="V157">
         <v>1.51</v>
@@ -25936,7 +25936,7 @@
         <v>1.2</v>
       </c>
       <c r="Z157">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AA157">
         <v>1.68</v>
@@ -25948,7 +25948,7 @@
         <v>2.65</v>
       </c>
       <c r="AD157">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE157">
         <v>1.14</v>
@@ -25957,7 +25957,7 @@
         <v>1.71</v>
       </c>
       <c r="AG157">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25973,7 +25973,7 @@
         <v>1.14</v>
       </c>
       <c r="AK157">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26063,13 +26063,13 @@
         </is>
       </c>
       <c r="N158">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="O158">
         <v>2.9</v>
       </c>
       <c r="P158">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="Q158">
         <v>3.1</v>
@@ -26087,19 +26087,19 @@
         <v>3.6</v>
       </c>
       <c r="V158">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="W158">
         <v>1.02</v>
       </c>
       <c r="X158">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="Y158">
         <v>1.44</v>
       </c>
       <c r="Z158">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="AA158">
         <v>2.31</v>
@@ -26120,7 +26120,7 @@
         <v>1.95</v>
       </c>
       <c r="AG158">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26133,7 +26133,7 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AK158">
         <v>1.53</v>
@@ -26881,7 +26881,7 @@
         <v>2.68</v>
       </c>
       <c r="O163">
-        <v>3.27</v>
+        <v>3.3</v>
       </c>
       <c r="P163">
         <v>2.51</v>
@@ -26914,13 +26914,13 @@
         <v>1.27</v>
       </c>
       <c r="Z163">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="AA163">
         <v>1.98</v>
       </c>
       <c r="AB163">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="AC163">
         <v>3.3</v>
@@ -27044,7 +27044,7 @@
         <v>2.62</v>
       </c>
       <c r="O164">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="P164">
         <v>2.75</v>
@@ -27056,22 +27056,22 @@
         <v>1.91</v>
       </c>
       <c r="S164">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="T164">
-        <v>2.31</v>
+        <v>2.56</v>
       </c>
       <c r="U164">
         <v>3.3</v>
       </c>
       <c r="V164">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="W164">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X164">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y164">
         <v>1.5</v>
@@ -27086,10 +27086,10 @@
         <v>1.53</v>
       </c>
       <c r="AC164">
-        <v>4.91</v>
+        <v>4.55</v>
       </c>
       <c r="AD164">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AE164">
         <v>1.05</v>
@@ -27098,7 +27098,7 @@
         <v>1.95</v>
       </c>
       <c r="AG164">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH164" t="inlineStr">
         <is>
@@ -27204,43 +27204,43 @@
         </is>
       </c>
       <c r="N165">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="O165">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="P165">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="Q165">
-        <v>3.64</v>
+        <v>3.6</v>
       </c>
       <c r="R165">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="S165">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="T165">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U165">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="V165">
         <v>1.14</v>
       </c>
       <c r="W165">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X165">
         <v>1.11</v>
       </c>
       <c r="Y165">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Z165">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AA165">
         <v>3.28</v>
@@ -27249,10 +27249,10 @@
         <v>1.25</v>
       </c>
       <c r="AC165">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="AD165">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AE165">
         <v>0</v>
@@ -27367,10 +27367,10 @@
         </is>
       </c>
       <c r="N166">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="O166">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P166">
         <v>5</v>
@@ -27530,10 +27530,10 @@
         </is>
       </c>
       <c r="N167">
-        <v>5.18</v>
+        <v>5.75</v>
       </c>
       <c r="O167">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="P167">
         <v>1.44</v>
@@ -27699,7 +27699,7 @@
         <v>3.4</v>
       </c>
       <c r="P168">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="Q168">
         <v>2.5</v>
@@ -27732,16 +27732,16 @@
         <v>3.58</v>
       </c>
       <c r="AA168">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="AB168">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="AC168">
         <v>2.83</v>
       </c>
       <c r="AD168">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AE168">
         <v>1.09</v>
@@ -27859,10 +27859,10 @@
         <v>2.2</v>
       </c>
       <c r="O169">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="P169">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="Q169">
         <v>2.88</v>
@@ -27910,10 +27910,10 @@
         <v>1.04</v>
       </c>
       <c r="AF169">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AG169">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AH169" t="inlineStr">
         <is>
@@ -28031,28 +28031,28 @@
         <v>2.2</v>
       </c>
       <c r="R170">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="S170">
         <v>1.31</v>
       </c>
       <c r="T170">
-        <v>3.25</v>
+        <v>2.91</v>
       </c>
       <c r="U170">
-        <v>2.61</v>
+        <v>2.43</v>
       </c>
       <c r="V170">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W170">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X170">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y170">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="Z170">
         <v>3.98</v>
@@ -28061,7 +28061,7 @@
         <v>1.69</v>
       </c>
       <c r="AB170">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AC170">
         <v>3</v>
@@ -28070,13 +28070,13 @@
         <v>1.39</v>
       </c>
       <c r="AE170">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF170">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG170">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AH170" t="inlineStr">
         <is>
@@ -28089,10 +28089,10 @@
         </is>
       </c>
       <c r="AJ170">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK170">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AL170">
         <v>0</v>
@@ -28185,61 +28185,61 @@
         <v>1.31</v>
       </c>
       <c r="O171">
-        <v>4.9</v>
+        <v>4.75</v>
       </c>
       <c r="P171">
-        <v>10.1</v>
+        <v>9.6</v>
       </c>
       <c r="Q171">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="R171">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S171">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T171">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U171">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="V171">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W171">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X171">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y171">
         <v>1.3</v>
       </c>
       <c r="Z171">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="AA171">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AB171">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AC171">
         <v>3.4</v>
       </c>
       <c r="AD171">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AE171">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF171">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AG171">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AH171" t="inlineStr">
         <is>
@@ -28252,10 +28252,10 @@
         </is>
       </c>
       <c r="AJ171">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AK171">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="AL171">
         <v>0</v>
@@ -28345,13 +28345,13 @@
         </is>
       </c>
       <c r="N172">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="O172">
-        <v>4.45</v>
+        <v>4.75</v>
       </c>
       <c r="P172">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="Q172">
         <v>1.83</v>
@@ -28363,7 +28363,7 @@
         <v>1.25</v>
       </c>
       <c r="T172">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U172">
         <v>2.3</v>
@@ -28372,10 +28372,10 @@
         <v>1.53</v>
       </c>
       <c r="W172">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X172">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y172">
         <v>1.2</v>
@@ -28384,13 +28384,13 @@
         <v>4.05</v>
       </c>
       <c r="AA172">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AB172">
         <v>2.15</v>
       </c>
       <c r="AC172">
-        <v>2.51</v>
+        <v>2.7</v>
       </c>
       <c r="AD172">
         <v>1.42</v>
@@ -28415,10 +28415,10 @@
         </is>
       </c>
       <c r="AJ172">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AK172">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="AL172">
         <v>0</v>
@@ -28517,10 +28517,10 @@
         <v>0</v>
       </c>
       <c r="Q173">
-        <v>4</v>
+        <v>4.26</v>
       </c>
       <c r="R173">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="S173">
         <v>1.25</v>
@@ -28529,16 +28529,16 @@
         <v>3.6</v>
       </c>
       <c r="U173">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="V173">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="W173">
         <v>1.12</v>
       </c>
       <c r="X173">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y173">
         <v>1.13</v>
@@ -28547,10 +28547,10 @@
         <v>4.6</v>
       </c>
       <c r="AA173">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AB173">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AC173">
         <v>2.38</v>
@@ -28559,13 +28559,13 @@
         <v>1.5</v>
       </c>
       <c r="AE173">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AF173">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AG173">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="AH173" t="inlineStr">
         <is>
@@ -28578,10 +28578,10 @@
         </is>
       </c>
       <c r="AJ173">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AK173">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AL173">
         <v>0</v>
@@ -29169,16 +29169,16 @@
         <v>4</v>
       </c>
       <c r="Q177">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="R177">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="S177">
         <v>1.31</v>
       </c>
       <c r="T177">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U177">
         <v>2.4</v>
@@ -29187,7 +29187,7 @@
         <v>1.5</v>
       </c>
       <c r="W177">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X177">
         <v>1.03</v>
@@ -29214,10 +29214,10 @@
         <v>1.15</v>
       </c>
       <c r="AF177">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AG177">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29230,10 +29230,10 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AK177">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29326,7 +29326,7 @@
         <v>2.25</v>
       </c>
       <c r="O178">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P178">
         <v>2.8</v>
@@ -29344,7 +29344,7 @@
         <v>2.95</v>
       </c>
       <c r="U178">
-        <v>2.39</v>
+        <v>2.29</v>
       </c>
       <c r="V178">
         <v>1.5</v>
@@ -29365,7 +29365,7 @@
         <v>1.62</v>
       </c>
       <c r="AB178">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AC178">
         <v>2.38</v>
@@ -29374,7 +29374,7 @@
         <v>1.46</v>
       </c>
       <c r="AE178">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AF178">
         <v>1.53</v>
@@ -29486,19 +29486,19 @@
         </is>
       </c>
       <c r="N179">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="O179">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="P179">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="Q179">
         <v>5.5</v>
       </c>
       <c r="R179">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="S179">
         <v>1.31</v>
@@ -29513,7 +29513,7 @@
         <v>1.47</v>
       </c>
       <c r="W179">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X179">
         <v>1</v>
@@ -29525,10 +29525,10 @@
         <v>3.5</v>
       </c>
       <c r="AA179">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AB179">
-        <v>2.09</v>
+        <v>1.93</v>
       </c>
       <c r="AC179">
         <v>2.75</v>
@@ -29540,7 +29540,7 @@
         <v>1.12</v>
       </c>
       <c r="AF179">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG179">
         <v>2</v>
@@ -29667,10 +29667,10 @@
         <v>1.32</v>
       </c>
       <c r="T180">
-        <v>3.24</v>
+        <v>2.94</v>
       </c>
       <c r="U180">
-        <v>2.46</v>
+        <v>2.57</v>
       </c>
       <c r="V180">
         <v>1.44</v>
@@ -29812,10 +29812,10 @@
         </is>
       </c>
       <c r="N181">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="O181">
-        <v>3.84</v>
+        <v>3.75</v>
       </c>
       <c r="P181">
         <v>5.05</v>
@@ -29827,7 +29827,7 @@
         <v>2.2</v>
       </c>
       <c r="S181">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T181">
         <v>2.73</v>
@@ -29866,7 +29866,7 @@
         <v>1.12</v>
       </c>
       <c r="AF181">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AG181">
         <v>1.85</v>
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G183">
@@ -30138,80 +30138,80 @@
         </is>
       </c>
       <c r="N183">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="O183">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="P183">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="Q183">
-        <v>3.39</v>
+        <v>2.9</v>
       </c>
       <c r="R183">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="S183">
-        <v>1.69</v>
+        <v>1.52</v>
       </c>
       <c r="T183">
-        <v>2.04</v>
+        <v>2.26</v>
       </c>
       <c r="U183">
-        <v>4.05</v>
+        <v>3.34</v>
       </c>
       <c r="V183">
+        <v>1.29</v>
+      </c>
+      <c r="W183">
+        <v>1.01</v>
+      </c>
+      <c r="X183">
+        <v>1.07</v>
+      </c>
+      <c r="Y183">
+        <v>1.46</v>
+      </c>
+      <c r="Z183">
+        <v>2.43</v>
+      </c>
+      <c r="AA183">
+        <v>2.51</v>
+      </c>
+      <c r="AB183">
+        <v>1.49</v>
+      </c>
+      <c r="AC183">
+        <v>4.45</v>
+      </c>
+      <c r="AD183">
         <v>1.17</v>
       </c>
-      <c r="W183">
-        <v>1.03</v>
-      </c>
-      <c r="X183">
-        <v>1.13</v>
-      </c>
-      <c r="Y183">
-        <v>1.68</v>
-      </c>
-      <c r="Z183">
-        <v>2.09</v>
-      </c>
-      <c r="AA183">
-        <v>2.92</v>
-      </c>
-      <c r="AB183">
-        <v>1.34</v>
-      </c>
-      <c r="AC183">
-        <v>5.6</v>
-      </c>
-      <c r="AD183">
-        <v>1.09</v>
-      </c>
       <c r="AE183">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF183">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AG183">
+        <v>1.67</v>
+      </c>
+      <c r="AH183" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI183" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ183">
+        <v>1.23</v>
+      </c>
+      <c r="AK183">
         <v>1.57</v>
-      </c>
-      <c r="AH183" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI183" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ183">
-        <v>1.33</v>
-      </c>
-      <c r="AK183">
-        <v>1.44</v>
       </c>
       <c r="AL183">
         <v>0</v>
@@ -30269,12 +30269,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G184">
@@ -30301,64 +30301,64 @@
         </is>
       </c>
       <c r="N184">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="O184">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="P184">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="Q184">
-        <v>2.9</v>
+        <v>3.39</v>
       </c>
       <c r="R184">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="S184">
-        <v>1.52</v>
+        <v>1.69</v>
       </c>
       <c r="T184">
-        <v>2.26</v>
+        <v>2.04</v>
       </c>
       <c r="U184">
-        <v>3.34</v>
+        <v>4.05</v>
       </c>
       <c r="V184">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="W184">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X184">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Y184">
-        <v>1.46</v>
+        <v>1.68</v>
       </c>
       <c r="Z184">
-        <v>2.43</v>
+        <v>2.09</v>
       </c>
       <c r="AA184">
-        <v>2.51</v>
+        <v>2.92</v>
       </c>
       <c r="AB184">
-        <v>1.49</v>
+        <v>1.34</v>
       </c>
       <c r="AC184">
-        <v>4.45</v>
+        <v>5.6</v>
       </c>
       <c r="AD184">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AE184">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF184">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AG184">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AH184" t="inlineStr">
         <is>
@@ -30371,10 +30371,10 @@
         </is>
       </c>
       <c r="AJ184">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AK184">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AL184">
         <v>0</v>
@@ -30467,10 +30467,10 @@
         <v>2.5</v>
       </c>
       <c r="O185">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="P185">
-        <v>2.6</v>
+        <v>2.71</v>
       </c>
       <c r="Q185">
         <v>3.25</v>
@@ -30479,40 +30479,40 @@
         <v>2.01</v>
       </c>
       <c r="S185">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="T185">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="U185">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="V185">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W185">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X185">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Y185">
         <v>1.45</v>
       </c>
       <c r="Z185">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="AA185">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AB185">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AC185">
         <v>4.5</v>
       </c>
       <c r="AD185">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AE185">
         <v>1.05</v>
@@ -30534,7 +30534,7 @@
         </is>
       </c>
       <c r="AJ185">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AK185">
         <v>1.4</v>
@@ -30636,10 +30636,10 @@
         <v>2</v>
       </c>
       <c r="Q186">
-        <v>3.78</v>
+        <v>3.96</v>
       </c>
       <c r="R186">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="S186">
         <v>1.33</v>
@@ -30678,13 +30678,13 @@
         <v>1.33</v>
       </c>
       <c r="AE186">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF186">
         <v>1.65</v>
       </c>
       <c r="AG186">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="AH186" t="inlineStr">
         <is>
@@ -30953,64 +30953,64 @@
         </is>
       </c>
       <c r="N188">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="O188">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P188">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="Q188">
-        <v>3.05</v>
+        <v>3.75</v>
       </c>
       <c r="R188">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S188">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T188">
-        <v>3.3</v>
+        <v>2.91</v>
       </c>
       <c r="U188">
         <v>2.55</v>
       </c>
       <c r="V188">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W188">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X188">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y188">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z188">
-        <v>3.85</v>
+        <v>4.21</v>
       </c>
       <c r="AA188">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AB188">
-        <v>1.99</v>
+        <v>2.14</v>
       </c>
       <c r="AC188">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AD188">
         <v>1.42</v>
       </c>
       <c r="AE188">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF188">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG188">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH188" t="inlineStr">
         <is>
@@ -31023,10 +31023,10 @@
         </is>
       </c>
       <c r="AJ188">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK188">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AL188">
         <v>0</v>
@@ -31122,7 +31122,7 @@
         <v>4.4</v>
       </c>
       <c r="P189">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="Q189">
         <v>5</v>
@@ -31137,10 +31137,10 @@
         <v>3.94</v>
       </c>
       <c r="U189">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="V189">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="W189">
         <v>1.2</v>
@@ -31282,28 +31282,28 @@
         <v>3.72</v>
       </c>
       <c r="O190">
-        <v>3.47</v>
+        <v>3.6</v>
       </c>
       <c r="P190">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="Q190">
         <v>4.4</v>
       </c>
       <c r="R190">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="S190">
         <v>1.36</v>
       </c>
       <c r="T190">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="U190">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="V190">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W190">
         <v>1.09</v>
@@ -31312,28 +31312,28 @@
         <v>1.05</v>
       </c>
       <c r="Y190">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z190">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AA190">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AB190">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AC190">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="AD190">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE190">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF190">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AG190">
         <v>1.94</v>
@@ -31445,16 +31445,16 @@
         <v>1.5</v>
       </c>
       <c r="O191">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="P191">
         <v>5.75</v>
       </c>
       <c r="Q191">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="R191">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="S191">
         <v>1.3</v>
@@ -31463,10 +31463,10 @@
         <v>3.25</v>
       </c>
       <c r="U191">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="V191">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="W191">
         <v>1.08</v>
@@ -31475,10 +31475,10 @@
         <v>1.02</v>
       </c>
       <c r="Y191">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z191">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="AA191">
         <v>1.67</v>
@@ -31487,19 +31487,19 @@
         <v>2.15</v>
       </c>
       <c r="AC191">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AD191">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AE191">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF191">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG191">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH191" t="inlineStr">
         <is>
@@ -31512,10 +31512,10 @@
         </is>
       </c>
       <c r="AJ191">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AK191">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AL191">
         <v>0</v>
@@ -31605,7 +31605,7 @@
         </is>
       </c>
       <c r="N192">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="O192">
         <v>3.15</v>
@@ -31629,7 +31629,7 @@
         <v>2.8</v>
       </c>
       <c r="V192">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W192">
         <v>1.05</v>
@@ -31662,7 +31662,7 @@
         <v>1.75</v>
       </c>
       <c r="AG192">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH192" t="inlineStr">
         <is>
@@ -31675,7 +31675,7 @@
         </is>
       </c>
       <c r="AJ192">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AK192">
         <v>1.5</v>
@@ -31768,16 +31768,16 @@
         </is>
       </c>
       <c r="N193">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="O193">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P193">
-        <v>5</v>
+        <v>5.85</v>
       </c>
       <c r="Q193">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R193">
         <v>2.15</v>
@@ -31789,19 +31789,19 @@
         <v>2.77</v>
       </c>
       <c r="U193">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="V193">
         <v>1.38</v>
       </c>
       <c r="W193">
+        <v>1.05</v>
+      </c>
+      <c r="X193">
         <v>1.04</v>
       </c>
-      <c r="X193">
-        <v>1.03</v>
-      </c>
       <c r="Y193">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="Z193">
         <v>3.38</v>
@@ -31810,22 +31810,22 @@
         <v>2.09</v>
       </c>
       <c r="AB193">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AC193">
         <v>3.55</v>
       </c>
       <c r="AD193">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE193">
         <v>1.06</v>
       </c>
       <c r="AF193">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AG193">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AH193" t="inlineStr">
         <is>
@@ -31841,7 +31841,7 @@
         <v>1.3</v>
       </c>
       <c r="AK193">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AL193">
         <v>0</v>
@@ -32429,28 +32429,28 @@
         <v>8.6</v>
       </c>
       <c r="Q197">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="R197">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="S197">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T197">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="U197">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="V197">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W197">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X197">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y197">
         <v>1.22</v>
@@ -32459,10 +32459,10 @@
         <v>4.1</v>
       </c>
       <c r="AA197">
-        <v>1.92</v>
+        <v>1.74</v>
       </c>
       <c r="AB197">
-        <v>1.79</v>
+        <v>1.97</v>
       </c>
       <c r="AC197">
         <v>3.1</v>
@@ -32471,13 +32471,13 @@
         <v>1.36</v>
       </c>
       <c r="AE197">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF197">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="AG197">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32490,10 +32490,10 @@
         </is>
       </c>
       <c r="AJ197">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AK197">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AL197">
         <v>0</v>
@@ -33570,43 +33570,43 @@
         <v>2.8</v>
       </c>
       <c r="Q204">
-        <v>2.97</v>
+        <v>2.75</v>
       </c>
       <c r="R204">
         <v>2.2</v>
       </c>
       <c r="S204">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T204">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="U204">
         <v>2.7</v>
       </c>
       <c r="V204">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W204">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X204">
         <v>1.05</v>
       </c>
       <c r="Y204">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="Z204">
-        <v>3.84</v>
+        <v>3.6</v>
       </c>
       <c r="AA204">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="AB204">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AC204">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AD204">
         <v>1.38</v>
@@ -33615,7 +33615,7 @@
         <v>1.1</v>
       </c>
       <c r="AF204">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AG204">
         <v>2</v>
@@ -33727,10 +33727,10 @@
         <v>5</v>
       </c>
       <c r="O205">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="P205">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="Q205">
         <v>4.9</v>
@@ -33742,7 +33742,7 @@
         <v>1.13</v>
       </c>
       <c r="T205">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="U205">
         <v>1.77</v>
@@ -33760,7 +33760,7 @@
         <v>1.03</v>
       </c>
       <c r="Z205">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="AA205">
         <v>1.22</v>
@@ -33769,10 +33769,10 @@
         <v>3.5</v>
       </c>
       <c r="AC205">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AD205">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AE205">
         <v>1.47</v>
@@ -33781,7 +33781,7 @@
         <v>1.36</v>
       </c>
       <c r="AG205">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="AH205" t="inlineStr">
         <is>
@@ -33794,7 +33794,7 @@
         </is>
       </c>
       <c r="AJ205">
-        <v>1.13</v>
+        <v>2.57</v>
       </c>
       <c r="AK205">
         <v>1.1</v>
@@ -33896,10 +33896,10 @@
         <v>1.79</v>
       </c>
       <c r="Q206">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="R206">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="S206">
         <v>1.35</v>
@@ -33917,7 +33917,7 @@
         <v>1.07</v>
       </c>
       <c r="X206">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y206">
         <v>1.21</v>
@@ -33926,16 +33926,16 @@
         <v>3.58</v>
       </c>
       <c r="AA206">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AB206">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC206">
-        <v>2.5</v>
+        <v>2.97</v>
       </c>
       <c r="AD206">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE206">
         <v>1.07</v>
@@ -33944,7 +33944,7 @@
         <v>1.71</v>
       </c>
       <c r="AG206">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH206" t="inlineStr">
         <is>
@@ -33957,10 +33957,10 @@
         </is>
       </c>
       <c r="AJ206">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AK206">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AL206">
         <v>0</v>
@@ -34053,31 +34053,31 @@
         <v>1.56</v>
       </c>
       <c r="O207">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="P207">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="Q207">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="R207">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="S207">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="T207">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="U207">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="V207">
         <v>1.6</v>
       </c>
       <c r="W207">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X207">
         <v>1.04</v>
@@ -34089,10 +34089,10 @@
         <v>4.2</v>
       </c>
       <c r="AA207">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AB207">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AC207">
         <v>2.25</v>
@@ -34101,29 +34101,29 @@
         <v>1.5</v>
       </c>
       <c r="AE207">
+        <v>1.18</v>
+      </c>
+      <c r="AF207">
+        <v>1.57</v>
+      </c>
+      <c r="AG207">
+        <v>2.19</v>
+      </c>
+      <c r="AH207" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI207" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ207">
         <v>1.15</v>
       </c>
-      <c r="AF207">
-        <v>1.6</v>
-      </c>
-      <c r="AG207">
-        <v>2.2</v>
-      </c>
-      <c r="AH207" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI207" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ207">
-        <v>1.2</v>
-      </c>
       <c r="AK207">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -34376,19 +34376,19 @@
         </is>
       </c>
       <c r="N209">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="O209">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P209">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="Q209">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="R209">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S209">
         <v>1.31</v>
@@ -34406,7 +34406,7 @@
         <v>1.08</v>
       </c>
       <c r="X209">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y209">
         <v>1.26</v>
@@ -34415,10 +34415,10 @@
         <v>3.67</v>
       </c>
       <c r="AA209">
+        <v>1.75</v>
+      </c>
+      <c r="AB209">
         <v>1.9</v>
-      </c>
-      <c r="AB209">
-        <v>2.02</v>
       </c>
       <c r="AC209">
         <v>3.05</v>
@@ -34430,10 +34430,10 @@
         <v>1.11</v>
       </c>
       <c r="AF209">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG209">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="AH209" t="inlineStr">
         <is>
@@ -34449,7 +34449,7 @@
         <v>1.25</v>
       </c>
       <c r="AK209">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AL209">
         <v>0</v>
@@ -34539,13 +34539,13 @@
         </is>
       </c>
       <c r="N210">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="O210">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="P210">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="Q210">
         <v>3.15</v>
@@ -34865,13 +34865,13 @@
         </is>
       </c>
       <c r="N212">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="O212">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="P212">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="Q212">
         <v>2.8</v>
@@ -34895,34 +34895,34 @@
         <v>1.05</v>
       </c>
       <c r="X212">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y212">
         <v>1.36</v>
       </c>
       <c r="Z212">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AA212">
         <v>2.15</v>
       </c>
       <c r="AB212">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AC212">
-        <v>3.9</v>
+        <v>3.58</v>
       </c>
       <c r="AD212">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AE212">
         <v>1.06</v>
       </c>
       <c r="AF212">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AG212">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AH212" t="inlineStr">
         <is>
@@ -35028,19 +35028,19 @@
         </is>
       </c>
       <c r="N213">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="O213">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P213">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q213">
         <v>4.4</v>
       </c>
       <c r="R213">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="S213">
         <v>1.42</v>
@@ -35055,10 +35055,10 @@
         <v>1.33</v>
       </c>
       <c r="W213">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X213">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Y213">
         <v>1.35</v>
@@ -35073,10 +35073,10 @@
         <v>1.67</v>
       </c>
       <c r="AC213">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="AD213">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AE213">
         <v>1.03</v>
@@ -35085,7 +35085,7 @@
         <v>1.9</v>
       </c>
       <c r="AG213">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH213" t="inlineStr">
         <is>
@@ -35098,10 +35098,10 @@
         </is>
       </c>
       <c r="AJ213">
-        <v>1.91</v>
+        <v>1.25</v>
       </c>
       <c r="AK213">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AL213">
         <v>0</v>
@@ -35366,13 +35366,13 @@
         <v>3.6</v>
       </c>
       <c r="R215">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="S215">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T215">
-        <v>2.57</v>
+        <v>2.65</v>
       </c>
       <c r="U215">
         <v>2.81</v>
@@ -35390,10 +35390,10 @@
         <v>1.27</v>
       </c>
       <c r="Z215">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="AA215">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="AB215">
         <v>1.67</v>
@@ -35517,7 +35517,7 @@
         </is>
       </c>
       <c r="N216">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="O216">
         <v>5.75</v>
@@ -35526,16 +35526,16 @@
         <v>1.32</v>
       </c>
       <c r="Q216">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="R216">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="S216">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="T216">
-        <v>3.94</v>
+        <v>3.84</v>
       </c>
       <c r="U216">
         <v>2.15</v>
@@ -35550,7 +35550,7 @@
         <v>1.02</v>
       </c>
       <c r="Y216">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Z216">
         <v>5.75</v>
@@ -35568,10 +35568,10 @@
         <v>1.75</v>
       </c>
       <c r="AE216">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF216">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AG216">
         <v>2.05</v>
@@ -35680,34 +35680,34 @@
         </is>
       </c>
       <c r="N217">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="O217">
         <v>6</v>
       </c>
       <c r="P217">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Q217">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="R217">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="S217">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T217">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="U217">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="V217">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="W217">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X217">
         <v>1.03</v>
@@ -35731,13 +35731,13 @@
         <v>1.44</v>
       </c>
       <c r="AE217">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF217">
         <v>2.15</v>
       </c>
       <c r="AG217">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AH217" t="inlineStr">
         <is>
@@ -35750,10 +35750,10 @@
         </is>
       </c>
       <c r="AJ217">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AK217">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AL217">
         <v>0</v>
@@ -35843,7 +35843,7 @@
         </is>
       </c>
       <c r="N218">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="O218">
         <v>3.45</v>
@@ -35852,55 +35852,55 @@
         <v>2.25</v>
       </c>
       <c r="Q218">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R218">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S218">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T218">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U218">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="V218">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W218">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X218">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y218">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z218">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA218">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB218">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC218">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD218">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE218">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF218">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG218">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH218" t="inlineStr">
         <is>
@@ -35913,10 +35913,10 @@
         </is>
       </c>
       <c r="AJ218">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK218">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL218">
         <v>0</v>
@@ -36015,7 +36015,7 @@
         <v>4</v>
       </c>
       <c r="Q219">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="R219">
         <v>2.2</v>
@@ -36024,10 +36024,10 @@
         <v>1.31</v>
       </c>
       <c r="T219">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="U219">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="V219">
         <v>1.44</v>
@@ -36036,22 +36036,22 @@
         <v>1.08</v>
       </c>
       <c r="X219">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y219">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z219">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="AA219">
-        <v>1.76</v>
+        <v>1.61</v>
       </c>
       <c r="AB219">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="AC219">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="AD219">
         <v>1.33</v>
@@ -36076,10 +36076,10 @@
         </is>
       </c>
       <c r="AJ219">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK219">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AL219">
         <v>0</v>
@@ -36175,40 +36175,40 @@
         <v>3</v>
       </c>
       <c r="P220">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q220">
         <v>3.75</v>
       </c>
       <c r="R220">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="S220">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="T220">
         <v>2.45</v>
       </c>
       <c r="U220">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="V220">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="W220">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X220">
         <v>1.1</v>
       </c>
       <c r="Y220">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="Z220">
-        <v>2.61</v>
+        <v>2.46</v>
       </c>
       <c r="AA220">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="AB220">
         <v>1.49</v>
@@ -36220,10 +36220,10 @@
         <v>1.15</v>
       </c>
       <c r="AE220">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF220">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AG220">
         <v>1.7</v>
@@ -36242,7 +36242,7 @@
         <v>1.36</v>
       </c>
       <c r="AK220">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AL220">
         <v>0</v>
@@ -36495,19 +36495,19 @@
         </is>
       </c>
       <c r="N222">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="O222">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P222">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Q222">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="R222">
-        <v>2.23</v>
+        <v>2.33</v>
       </c>
       <c r="S222">
         <v>1.3</v>
@@ -36516,10 +36516,10 @@
         <v>3.08</v>
       </c>
       <c r="U222">
-        <v>2.51</v>
+        <v>2.47</v>
       </c>
       <c r="V222">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="W222">
         <v>1.09</v>
@@ -36531,7 +36531,7 @@
         <v>1.18</v>
       </c>
       <c r="Z222">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="AA222">
         <v>1.7</v>
@@ -36543,7 +36543,7 @@
         <v>2.66</v>
       </c>
       <c r="AD222">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AE222">
         <v>1.11</v>
@@ -36565,10 +36565,10 @@
         </is>
       </c>
       <c r="AJ222">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK222">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AL222">
         <v>0</v>
@@ -36703,7 +36703,7 @@
         <v>1.64</v>
       </c>
       <c r="AC223">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="AD223">
         <v>1.25</v>
@@ -37639,22 +37639,22 @@
         <v>1.89</v>
       </c>
       <c r="O229">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="P229">
-        <v>3.35</v>
+        <v>4.31</v>
       </c>
       <c r="Q229">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="R229">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="S229">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="T229">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="U229">
         <v>3.6</v>
@@ -37666,25 +37666,25 @@
         <v>1.03</v>
       </c>
       <c r="X229">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Y229">
         <v>1.48</v>
       </c>
       <c r="Z229">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="AA229">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="AB229">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AC229">
-        <v>4.79</v>
+        <v>5.07</v>
       </c>
       <c r="AD229">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AE229">
         <v>1.01</v>
@@ -37811,7 +37811,7 @@
         <v>2.5</v>
       </c>
       <c r="R230">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="S230">
         <v>1.28</v>
@@ -37820,10 +37820,10 @@
         <v>3.14</v>
       </c>
       <c r="U230">
-        <v>2.47</v>
+        <v>2.08</v>
       </c>
       <c r="V230">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W230">
         <v>1.09</v>
@@ -37835,28 +37835,28 @@
         <v>1.18</v>
       </c>
       <c r="Z230">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="AA230">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB230">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AC230">
         <v>2.3</v>
       </c>
       <c r="AD230">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AE230">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF230">
         <v>1.59</v>
       </c>
       <c r="AG230">
-        <v>2.13</v>
+        <v>1.93</v>
       </c>
       <c r="AH230" t="inlineStr">
         <is>
@@ -37869,10 +37869,10 @@
         </is>
       </c>
       <c r="AJ230">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AK230">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AL230">
         <v>0</v>
@@ -38125,16 +38125,16 @@
         </is>
       </c>
       <c r="N232">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="O232">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="P232">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="Q232">
-        <v>2.88</v>
+        <v>3.03</v>
       </c>
       <c r="R232">
         <v>2.15</v>
@@ -38143,7 +38143,7 @@
         <v>1.35</v>
       </c>
       <c r="T232">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="U232">
         <v>2.76</v>
@@ -38155,10 +38155,10 @@
         <v>1.08</v>
       </c>
       <c r="X232">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y232">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z232">
         <v>3.68</v>
@@ -38195,10 +38195,10 @@
         </is>
       </c>
       <c r="AJ232">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK232">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AL232">
         <v>0</v>
@@ -38451,80 +38451,80 @@
         </is>
       </c>
       <c r="N234">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="O234">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="P234">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="Q234">
-        <v>2.52</v>
+        <v>2.45</v>
       </c>
       <c r="R234">
-        <v>2.04</v>
+        <v>2.17</v>
       </c>
       <c r="S234">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T234">
+        <v>2.65</v>
+      </c>
+      <c r="U234">
         <v>2.74</v>
-      </c>
-      <c r="U234">
-        <v>2.88</v>
       </c>
       <c r="V234">
         <v>1.36</v>
       </c>
       <c r="W234">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X234">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y234">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="Z234">
+        <v>3.2</v>
+      </c>
+      <c r="AA234">
+        <v>1.88</v>
+      </c>
+      <c r="AB234">
+        <v>1.85</v>
+      </c>
+      <c r="AC234">
         <v>3.08</v>
       </c>
-      <c r="AA234">
-        <v>1.95</v>
-      </c>
-      <c r="AB234">
-        <v>1.76</v>
-      </c>
-      <c r="AC234">
-        <v>3.28</v>
-      </c>
       <c r="AD234">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE234">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF234">
+        <v>1.75</v>
+      </c>
+      <c r="AG234">
+        <v>1.92</v>
+      </c>
+      <c r="AH234" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI234" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ234">
+        <v>1.19</v>
+      </c>
+      <c r="AK234">
         <v>1.8</v>
-      </c>
-      <c r="AG234">
-        <v>1.87</v>
-      </c>
-      <c r="AH234" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI234" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ234">
-        <v>1.22</v>
-      </c>
-      <c r="AK234">
-        <v>1.73</v>
       </c>
       <c r="AL234">
         <v>0</v>
@@ -38620,7 +38620,7 @@
         <v>4.6</v>
       </c>
       <c r="P235">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Q235">
         <v>5</v>
@@ -38647,22 +38647,22 @@
         <v>1.01</v>
       </c>
       <c r="Y235">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z235">
-        <v>6.15</v>
+        <v>7</v>
       </c>
       <c r="AA235">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AB235">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="AC235">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AD235">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AE235">
         <v>1.36</v>
@@ -38684,10 +38684,10 @@
         </is>
       </c>
       <c r="AJ235">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="AK235">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AL235">
         <v>0</v>
@@ -38804,7 +38804,7 @@
         <v>1.36</v>
       </c>
       <c r="W236">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X236">
         <v>1.01</v>
@@ -38816,22 +38816,22 @@
         <v>3.31</v>
       </c>
       <c r="AA236">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AB236">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AC236">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="AD236">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE236">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF236">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG236">
         <v>1.75</v>
@@ -38847,10 +38847,10 @@
         </is>
       </c>
       <c r="AJ236">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AK236">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="AL236">
         <v>0</v>
@@ -38958,10 +38958,10 @@
         <v>1.38</v>
       </c>
       <c r="T237">
-        <v>2.67</v>
+        <v>2.72</v>
       </c>
       <c r="U237">
-        <v>2.79</v>
+        <v>2.88</v>
       </c>
       <c r="V237">
         <v>1.35</v>
@@ -38976,13 +38976,13 @@
         <v>1.28</v>
       </c>
       <c r="Z237">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="AA237">
         <v>1.96</v>
       </c>
       <c r="AB237">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AC237">
         <v>3.34</v>
@@ -38991,13 +38991,13 @@
         <v>1.24</v>
       </c>
       <c r="AE237">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF237">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AG237">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AH237" t="inlineStr">
         <is>
@@ -39013,7 +39013,7 @@
         <v>1.25</v>
       </c>
       <c r="AK237">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AL237">
         <v>0</v>

--- a/jogos_2026-08-23.xlsx
+++ b/jogos_2026-08-23.xlsx
@@ -644,34 +644,34 @@
         <v>3.7</v>
       </c>
       <c r="Q2">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="R2">
         <v>2.2</v>
       </c>
       <c r="S2">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="T2">
-        <v>2.71</v>
+        <v>3</v>
       </c>
       <c r="U2">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="V2">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W2">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X2">
         <v>1.03</v>
       </c>
       <c r="Y2">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="Z2">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AA2">
         <v>1.89</v>
@@ -680,7 +680,7 @@
         <v>1.81</v>
       </c>
       <c r="AC2">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AD2">
         <v>1.29</v>
@@ -692,7 +692,7 @@
         <v>1.8</v>
       </c>
       <c r="AG2">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK2">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O3">
         <v>3.15</v>
       </c>
       <c r="P3">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="Q3">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="R3">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="S3">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T3">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U3">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="V3">
         <v>1.4</v>
       </c>
       <c r="W3">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X3">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
+        <v>1.25</v>
+      </c>
+      <c r="Z3">
+        <v>3.3</v>
+      </c>
+      <c r="AA3">
+        <v>1.96</v>
+      </c>
+      <c r="AB3">
+        <v>1.8</v>
+      </c>
+      <c r="AC3">
+        <v>3.2</v>
+      </c>
+      <c r="AD3">
         <v>1.26</v>
       </c>
-      <c r="Z3">
-        <v>3.2</v>
-      </c>
-      <c r="AA3">
-        <v>1.92</v>
-      </c>
-      <c r="AB3">
-        <v>1.81</v>
-      </c>
-      <c r="AC3">
-        <v>3.35</v>
-      </c>
-      <c r="AD3">
-        <v>1.25</v>
-      </c>
       <c r="AE3">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF3">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AG3">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AK3">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -967,7 +967,7 @@
         <v>3.55</v>
       </c>
       <c r="P4">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1130,10 +1130,10 @@
         <v>3.95</v>
       </c>
       <c r="P5">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q5">
-        <v>5</v>
+        <v>4.64</v>
       </c>
       <c r="R5">
         <v>2.27</v>
@@ -1142,13 +1142,13 @@
         <v>1.3</v>
       </c>
       <c r="T5">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="U5">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="V5">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W5">
         <v>1.08</v>
@@ -1160,16 +1160,16 @@
         <v>1.19</v>
       </c>
       <c r="Z5">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="AA5">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AB5">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AC5">
-        <v>2.43</v>
+        <v>2.71</v>
       </c>
       <c r="AD5">
         <v>1.42</v>
@@ -1178,10 +1178,10 @@
         <v>1.12</v>
       </c>
       <c r="AF5">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AG5">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK5">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -2923,7 +2923,7 @@
         <v>3.5</v>
       </c>
       <c r="P16">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="Q16">
         <v>4.8</v>
@@ -2941,7 +2941,7 @@
         <v>3.2</v>
       </c>
       <c r="V16">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W16">
         <v>1.01</v>
@@ -2953,16 +2953,16 @@
         <v>1.4</v>
       </c>
       <c r="Z16">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="AA16">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="AB16">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AC16">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AD16">
         <v>1.19</v>
@@ -2971,10 +2971,10 @@
         <v>1.06</v>
       </c>
       <c r="AF16">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AG16">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>1.23</v>
       </c>
       <c r="AK16">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="O17">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P17">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="Q17">
         <v>3.18</v>
@@ -3098,7 +3098,7 @@
         <v>1.4</v>
       </c>
       <c r="T17">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="U17">
         <v>3</v>
@@ -3107,7 +3107,7 @@
         <v>1.35</v>
       </c>
       <c r="W17">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X17">
         <v>1.07</v>
@@ -3122,22 +3122,22 @@
         <v>2.11</v>
       </c>
       <c r="AB17">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC17">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AD17">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE17">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF17">
         <v>1.8</v>
       </c>
       <c r="AG17">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -4227,22 +4227,22 @@
         <v>3.5</v>
       </c>
       <c r="P24">
-        <v>2.93</v>
+        <v>3.5</v>
       </c>
       <c r="Q24">
         <v>2.47</v>
       </c>
       <c r="R24">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="S24">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T24">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="U24">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="V24">
         <v>1.44</v>
@@ -4251,7 +4251,7 @@
         <v>1.08</v>
       </c>
       <c r="X24">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y24">
         <v>1.18</v>
@@ -4263,22 +4263,22 @@
         <v>1.73</v>
       </c>
       <c r="AB24">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AC24">
-        <v>2.69</v>
+        <v>2.85</v>
       </c>
       <c r="AD24">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE24">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF24">
         <v>1.62</v>
       </c>
       <c r="AG24">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>1.29</v>
       </c>
       <c r="AK24">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4454,7 +4454,7 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AK25">
         <v>2.45</v>
@@ -5534,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="Q32">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="R32">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="S32">
         <v>1.18</v>
@@ -5546,7 +5546,7 @@
         <v>4.3</v>
       </c>
       <c r="U32">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="V32">
         <v>1.8</v>
@@ -5567,22 +5567,22 @@
         <v>1.33</v>
       </c>
       <c r="AB32">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="AC32">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AD32">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AE32">
         <v>1.3</v>
       </c>
       <c r="AF32">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AG32">
-        <v>2.4</v>
+        <v>2.22</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="O33">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P33">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="Q33">
         <v>3.25</v>
@@ -5706,10 +5706,10 @@
         <v>1.29</v>
       </c>
       <c r="T33">
-        <v>3.24</v>
+        <v>3.27</v>
       </c>
       <c r="U33">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="V33">
         <v>1.46</v>
@@ -5727,7 +5727,7 @@
         <v>3.8</v>
       </c>
       <c r="AA33">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AB33">
         <v>2.01</v>
@@ -5739,7 +5739,7 @@
         <v>1.4</v>
       </c>
       <c r="AE33">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF33">
         <v>1.6</v>
@@ -5851,19 +5851,19 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="O34">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P34">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="Q34">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="R34">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="S34">
         <v>1.34</v>
@@ -5872,7 +5872,7 @@
         <v>2.99</v>
       </c>
       <c r="U34">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="V34">
         <v>1.45</v>
@@ -5881,7 +5881,7 @@
         <v>1.06</v>
       </c>
       <c r="X34">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y34">
         <v>1.22</v>
@@ -5896,7 +5896,7 @@
         <v>2</v>
       </c>
       <c r="AC34">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="AD34">
         <v>1.36</v>
@@ -5905,10 +5905,10 @@
         <v>1.14</v>
       </c>
       <c r="AF34">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AG34">
-        <v>2.3</v>
+        <v>2.07</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -7345,13 +7345,13 @@
         <v>1.4</v>
       </c>
       <c r="W43">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X43">
         <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Z43">
         <v>3.76</v>
@@ -7369,13 +7369,13 @@
         <v>1.33</v>
       </c>
       <c r="AE43">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF43">
         <v>1.65</v>
       </c>
       <c r="AG43">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>1.36</v>
       </c>
       <c r="AK43">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -8459,16 +8459,16 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="O50">
         <v>3.5</v>
       </c>
       <c r="P50">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Q50">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="R50">
         <v>2.4</v>
@@ -8477,7 +8477,7 @@
         <v>1.28</v>
       </c>
       <c r="T50">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="U50">
         <v>2.29</v>
@@ -8486,19 +8486,19 @@
         <v>1.54</v>
       </c>
       <c r="W50">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X50">
         <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z50">
         <v>4.4</v>
       </c>
       <c r="AA50">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AB50">
         <v>2.28</v>
@@ -8507,16 +8507,16 @@
         <v>2.33</v>
       </c>
       <c r="AD50">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AE50">
         <v>1.2</v>
       </c>
       <c r="AF50">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AG50">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8631,10 +8631,10 @@
         <v>0</v>
       </c>
       <c r="Q51">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="R51">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S51">
         <v>1.3</v>
@@ -8643,10 +8643,10 @@
         <v>3.2</v>
       </c>
       <c r="U51">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="V51">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="W51">
         <v>1.1</v>
@@ -8655,31 +8655,31 @@
         <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z51">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="AA51">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AB51">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AC51">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AD51">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE51">
         <v>1.11</v>
       </c>
       <c r="AF51">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AG51">
-        <v>2.17</v>
+        <v>2.04</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>1.25</v>
       </c>
       <c r="AK51">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8948,7 +8948,7 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="O53">
         <v>3.1</v>
@@ -8987,7 +8987,7 @@
         <v>2.9</v>
       </c>
       <c r="AA53">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="AB53">
         <v>1.68</v>
@@ -9002,7 +9002,7 @@
         <v>1.04</v>
       </c>
       <c r="AF53">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AG53">
         <v>1.8</v>
@@ -9153,7 +9153,7 @@
         <v>2</v>
       </c>
       <c r="AB54">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AC54">
         <v>3</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q61">
-        <v>2.08</v>
+        <v>2.88</v>
       </c>
       <c r="R61">
-        <v>2.48</v>
+        <v>2.25</v>
       </c>
       <c r="S61">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T61">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U61">
+        <v>2.44</v>
+      </c>
+      <c r="V61">
+        <v>1.46</v>
+      </c>
+      <c r="W61">
+        <v>1.07</v>
+      </c>
+      <c r="X61">
+        <v>1.02</v>
+      </c>
+      <c r="Y61">
+        <v>1.18</v>
+      </c>
+      <c r="Z61">
+        <v>3.9</v>
+      </c>
+      <c r="AA61">
+        <v>1.61</v>
+      </c>
+      <c r="AB61">
         <v>2.07</v>
       </c>
-      <c r="V61">
-        <v>1.58</v>
-      </c>
-      <c r="W61">
-        <v>0</v>
-      </c>
-      <c r="X61">
-        <v>0</v>
-      </c>
-      <c r="Y61">
-        <v>0</v>
-      </c>
-      <c r="Z61">
-        <v>0</v>
-      </c>
-      <c r="AA61">
-        <v>1.47</v>
-      </c>
-      <c r="AB61">
-        <v>2.38</v>
-      </c>
       <c r="AC61">
-        <v>2.16</v>
+        <v>2.59</v>
       </c>
       <c r="AD61">
-        <v>1.56</v>
+        <v>1.39</v>
       </c>
       <c r="AE61">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AF61">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AG61">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AK61">
-        <v>1.98</v>
+        <v>1.5</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,80 +10415,80 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.38</v>
+        <v>1.3</v>
       </c>
       <c r="O62">
+        <v>5</v>
+      </c>
+      <c r="P62">
+        <v>7.5</v>
+      </c>
+      <c r="Q62">
+        <v>1.85</v>
+      </c>
+      <c r="R62">
+        <v>2.45</v>
+      </c>
+      <c r="S62">
+        <v>1.22</v>
+      </c>
+      <c r="T62">
         <v>3.5</v>
       </c>
-      <c r="P62">
-        <v>2.55</v>
-      </c>
-      <c r="Q62">
-        <v>2.98</v>
-      </c>
-      <c r="R62">
+      <c r="U62">
         <v>2.18</v>
       </c>
-      <c r="S62">
-        <v>1.28</v>
-      </c>
-      <c r="T62">
-        <v>3.15</v>
-      </c>
-      <c r="U62">
-        <v>2.44</v>
-      </c>
       <c r="V62">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="W62">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X62">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="Z62">
-        <v>3.9</v>
+        <v>5.15</v>
       </c>
       <c r="AA62">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="AB62">
-        <v>2.07</v>
+        <v>2.43</v>
       </c>
       <c r="AC62">
-        <v>2.59</v>
+        <v>2.19</v>
       </c>
       <c r="AD62">
-        <v>1.39</v>
+        <v>1.6</v>
       </c>
       <c r="AE62">
+        <v>1.21</v>
+      </c>
+      <c r="AF62">
+        <v>1.64</v>
+      </c>
+      <c r="AG62">
+        <v>2.1</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ62">
         <v>1.12</v>
       </c>
-      <c r="AF62">
-        <v>1.53</v>
-      </c>
-      <c r="AG62">
-        <v>2.28</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ62">
-        <v>1.23</v>
-      </c>
       <c r="AK62">
-        <v>1.44</v>
+        <v>2.72</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,65 +10578,65 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.3</v>
+        <v>1.68</v>
       </c>
       <c r="O63">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="P63">
-        <v>7.5</v>
+        <v>3.93</v>
       </c>
       <c r="Q63">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="R63">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="S63">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T63">
         <v>3.5</v>
       </c>
       <c r="U63">
-        <v>2.18</v>
+        <v>2.07</v>
       </c>
       <c r="V63">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="W63">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X63">
         <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Z63">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AA63">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AB63">
+        <v>2.38</v>
+      </c>
+      <c r="AC63">
+        <v>2.16</v>
+      </c>
+      <c r="AD63">
+        <v>1.56</v>
+      </c>
+      <c r="AE63">
+        <v>1.22</v>
+      </c>
+      <c r="AF63">
+        <v>1.52</v>
+      </c>
+      <c r="AG63">
         <v>2.32</v>
       </c>
-      <c r="AC63">
-        <v>2.19</v>
-      </c>
-      <c r="AD63">
-        <v>1.6</v>
-      </c>
-      <c r="AE63">
-        <v>1.21</v>
-      </c>
-      <c r="AF63">
-        <v>1.64</v>
-      </c>
-      <c r="AG63">
-        <v>2.07</v>
-      </c>
       <c r="AH63" t="inlineStr">
         <is>
           <t>[]</t>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AK63">
-        <v>2.72</v>
+        <v>1.98</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -11447,10 +11447,10 @@
         <v>1.14</v>
       </c>
       <c r="AF68">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AG68">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11613,7 +11613,7 @@
         <v>1.65</v>
       </c>
       <c r="AG69">
-        <v>1.96</v>
+        <v>1.82</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -12371,19 +12371,19 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="O74">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="P74">
-        <v>6.64</v>
+        <v>6.6</v>
       </c>
       <c r="Q74">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="R74">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="S74">
         <v>1.25</v>
@@ -12392,13 +12392,13 @@
         <v>3.42</v>
       </c>
       <c r="U74">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="V74">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W74">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X74">
         <v>1.01</v>
@@ -12407,28 +12407,28 @@
         <v>1.17</v>
       </c>
       <c r="Z74">
-        <v>4.65</v>
+        <v>4.6</v>
       </c>
       <c r="AA74">
         <v>1.57</v>
       </c>
       <c r="AB74">
-        <v>2.35</v>
+        <v>2.27</v>
       </c>
       <c r="AC74">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AD74">
         <v>1.55</v>
       </c>
       <c r="AE74">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AF74">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AG74">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,7 +12441,7 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK74">
         <v>2.75</v>
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="O75">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P75">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="Q75">
         <v>2.5</v>
@@ -12555,10 +12555,10 @@
         <v>3</v>
       </c>
       <c r="U75">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="V75">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W75">
         <v>1.1</v>
@@ -12567,31 +12567,31 @@
         <v>1.05</v>
       </c>
       <c r="Y75">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z75">
-        <v>3.6</v>
+        <v>3.74</v>
       </c>
       <c r="AA75">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AB75">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC75">
         <v>3.15</v>
       </c>
       <c r="AD75">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE75">
         <v>1.07</v>
       </c>
       <c r="AF75">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AG75">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK75">
         <v>1.77</v>
@@ -14164,34 +14164,34 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="O85">
         <v>3.4</v>
       </c>
       <c r="P85">
-        <v>2.7</v>
+        <v>2.37</v>
       </c>
       <c r="Q85">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="R85">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S85">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="T85">
         <v>3.28</v>
       </c>
       <c r="U85">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V85">
         <v>1.57</v>
       </c>
       <c r="W85">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X85">
         <v>1.01</v>
@@ -14200,7 +14200,7 @@
         <v>1.17</v>
       </c>
       <c r="Z85">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AA85">
         <v>1.61</v>
@@ -14209,13 +14209,13 @@
         <v>2.45</v>
       </c>
       <c r="AC85">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="AD85">
         <v>1.46</v>
       </c>
       <c r="AE85">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AF85">
         <v>1.47</v>
@@ -14698,10 +14698,10 @@
         <v>1.96</v>
       </c>
       <c r="AC88">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="AD88">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AE88">
         <v>1.11</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Fazendense</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>AD Nogueirense</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Fazendense</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>AD Nogueirense</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G114">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G115">
@@ -20376,7 +20376,7 @@
         <v>1.43</v>
       </c>
       <c r="T123">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="U123">
         <v>2.77</v>
@@ -20385,7 +20385,7 @@
         <v>1.33</v>
       </c>
       <c r="W123">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X123">
         <v>1.05</v>
@@ -20397,7 +20397,7 @@
         <v>3.25</v>
       </c>
       <c r="AA123">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="AB123">
         <v>1.7</v>
@@ -20415,7 +20415,7 @@
         <v>1.73</v>
       </c>
       <c r="AG123">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -21502,10 +21502,10 @@
         <v>2.25</v>
       </c>
       <c r="O130">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P130">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="Q130">
         <v>2.82</v>
@@ -21520,16 +21520,16 @@
         <v>3.12</v>
       </c>
       <c r="U130">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="V130">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W130">
         <v>1.08</v>
       </c>
       <c r="X130">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y130">
         <v>1.19</v>
@@ -21556,7 +21556,7 @@
         <v>1.53</v>
       </c>
       <c r="AG130">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -22975,10 +22975,10 @@
         <v>2.27</v>
       </c>
       <c r="Q139">
-        <v>3</v>
+        <v>3.28</v>
       </c>
       <c r="R139">
-        <v>2.26</v>
+        <v>2.35</v>
       </c>
       <c r="S139">
         <v>1.27</v>
@@ -22987,7 +22987,7 @@
         <v>3.25</v>
       </c>
       <c r="U139">
-        <v>2.18</v>
+        <v>2.31</v>
       </c>
       <c r="V139">
         <v>1.57</v>
@@ -23005,22 +23005,22 @@
         <v>4.25</v>
       </c>
       <c r="AA139">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="AB139">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AC139">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="AD139">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AE139">
         <v>1.15</v>
       </c>
       <c r="AF139">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AG139">
         <v>2.4</v>
@@ -23036,10 +23036,10 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="AK139">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G159">
@@ -26226,58 +26226,58 @@
         </is>
       </c>
       <c r="N159">
+        <v>1.88</v>
+      </c>
+      <c r="O159">
+        <v>3.7</v>
+      </c>
+      <c r="P159">
+        <v>3.1</v>
+      </c>
+      <c r="Q159">
+        <v>2.42</v>
+      </c>
+      <c r="R159">
+        <v>2.69</v>
+      </c>
+      <c r="S159">
+        <v>1.18</v>
+      </c>
+      <c r="T159">
+        <v>4.4</v>
+      </c>
+      <c r="U159">
+        <v>1.93</v>
+      </c>
+      <c r="V159">
+        <v>1.75</v>
+      </c>
+      <c r="W159">
+        <v>1.2</v>
+      </c>
+      <c r="X159">
+        <v>1.01</v>
+      </c>
+      <c r="Y159">
+        <v>1.05</v>
+      </c>
+      <c r="Z159">
+        <v>8</v>
+      </c>
+      <c r="AA159">
         <v>1.33</v>
       </c>
-      <c r="O159">
-        <v>4.7</v>
-      </c>
-      <c r="P159">
-        <v>4.7</v>
-      </c>
-      <c r="Q159">
-        <v>1.79</v>
-      </c>
-      <c r="R159">
-        <v>2.88</v>
-      </c>
-      <c r="S159">
-        <v>1.15</v>
-      </c>
-      <c r="T159">
-        <v>5</v>
-      </c>
-      <c r="U159">
-        <v>1.76</v>
-      </c>
-      <c r="V159">
-        <v>1.99</v>
-      </c>
-      <c r="W159">
-        <v>1.27</v>
-      </c>
-      <c r="X159">
-        <v>1</v>
-      </c>
-      <c r="Y159">
-        <v>1.06</v>
-      </c>
-      <c r="Z159">
-        <v>7.5</v>
-      </c>
-      <c r="AA159">
-        <v>1.25</v>
-      </c>
       <c r="AB159">
-        <v>3.69</v>
+        <v>2.5</v>
       </c>
       <c r="AC159">
-        <v>1.67</v>
+        <v>1.89</v>
       </c>
       <c r="AD159">
-        <v>2.14</v>
+        <v>1.86</v>
       </c>
       <c r="AE159">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="AF159">
         <v>1.36</v>
@@ -26296,10 +26296,10 @@
         </is>
       </c>
       <c r="AJ159">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="AK159">
-        <v>2.68</v>
+        <v>1.73</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G160">
@@ -26389,64 +26389,64 @@
         </is>
       </c>
       <c r="N160">
-        <v>1.89</v>
+        <v>4.25</v>
       </c>
       <c r="O160">
-        <v>3.7</v>
+        <v>5.2</v>
       </c>
       <c r="P160">
-        <v>3.1</v>
+        <v>1.52</v>
       </c>
       <c r="Q160">
-        <v>2.4</v>
+        <v>4.18</v>
       </c>
       <c r="R160">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="S160">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="T160">
-        <v>4.4</v>
+        <v>6.5</v>
       </c>
       <c r="U160">
-        <v>1.98</v>
+        <v>1.48</v>
       </c>
       <c r="V160">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="W160">
+        <v>1.46</v>
+      </c>
+      <c r="X160">
+        <v>1</v>
+      </c>
+      <c r="Y160">
+        <v>1.03</v>
+      </c>
+      <c r="Z160">
+        <v>13</v>
+      </c>
+      <c r="AA160">
+        <v>1.08</v>
+      </c>
+      <c r="AB160">
+        <v>5.65</v>
+      </c>
+      <c r="AC160">
+        <v>1.35</v>
+      </c>
+      <c r="AD160">
+        <v>3.09</v>
+      </c>
+      <c r="AE160">
+        <v>1.83</v>
+      </c>
+      <c r="AF160">
         <v>1.2</v>
       </c>
-      <c r="X160">
-        <v>1.01</v>
-      </c>
-      <c r="Y160">
-        <v>1.1</v>
-      </c>
-      <c r="Z160">
-        <v>6</v>
-      </c>
-      <c r="AA160">
-        <v>1.36</v>
-      </c>
-      <c r="AB160">
-        <v>2.88</v>
-      </c>
-      <c r="AC160">
-        <v>1.89</v>
-      </c>
-      <c r="AD160">
-        <v>1.86</v>
-      </c>
-      <c r="AE160">
-        <v>1.3</v>
-      </c>
-      <c r="AF160">
-        <v>1.25</v>
-      </c>
       <c r="AG160">
-        <v>2.9</v>
+        <v>4.15</v>
       </c>
       <c r="AH160" t="inlineStr">
         <is>
@@ -26459,10 +26459,10 @@
         </is>
       </c>
       <c r="AJ160">
-        <v>1.36</v>
+        <v>2.5</v>
       </c>
       <c r="AK160">
-        <v>1.67</v>
+        <v>1.13</v>
       </c>
       <c r="AL160">
         <v>0</v>
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G161">
@@ -26552,64 +26552,64 @@
         </is>
       </c>
       <c r="N161">
-        <v>4.25</v>
+        <v>1.94</v>
       </c>
       <c r="O161">
-        <v>5.6</v>
+        <v>3.65</v>
       </c>
       <c r="P161">
-        <v>1.45</v>
+        <v>2.99</v>
       </c>
       <c r="Q161">
-        <v>4.18</v>
+        <v>2.5</v>
       </c>
       <c r="R161">
-        <v>3.18</v>
+        <v>2.5</v>
       </c>
       <c r="S161">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="T161">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U161">
-        <v>1.48</v>
+        <v>2.05</v>
       </c>
       <c r="V161">
-        <v>2.44</v>
+        <v>1.71</v>
       </c>
       <c r="W161">
-        <v>1.46</v>
+        <v>1.17</v>
       </c>
       <c r="X161">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y161">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Z161">
-        <v>13.5</v>
+        <v>5.35</v>
       </c>
       <c r="AA161">
-        <v>1.08</v>
+        <v>1.38</v>
       </c>
       <c r="AB161">
-        <v>5</v>
+        <v>2.62</v>
       </c>
       <c r="AC161">
-        <v>1.35</v>
+        <v>1.94</v>
       </c>
       <c r="AD161">
-        <v>2.92</v>
+        <v>1.69</v>
       </c>
       <c r="AE161">
-        <v>1.83</v>
+        <v>1.29</v>
       </c>
       <c r="AF161">
-        <v>1.2</v>
+        <v>1.41</v>
       </c>
       <c r="AG161">
-        <v>4.27</v>
+        <v>2.6</v>
       </c>
       <c r="AH161" t="inlineStr">
         <is>
@@ -26622,10 +26622,10 @@
         </is>
       </c>
       <c r="AJ161">
-        <v>2.5</v>
+        <v>1.36</v>
       </c>
       <c r="AK161">
-        <v>1.16</v>
+        <v>1.76</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G162">
@@ -26715,64 +26715,64 @@
         </is>
       </c>
       <c r="N162">
-        <v>2.02</v>
+        <v>1.33</v>
       </c>
       <c r="O162">
-        <v>3.65</v>
+        <v>5.25</v>
       </c>
       <c r="P162">
-        <v>2.98</v>
+        <v>5.5</v>
       </c>
       <c r="Q162">
-        <v>2.5</v>
+        <v>1.79</v>
       </c>
       <c r="R162">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="S162">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="T162">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="U162">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="V162">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="W162">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="X162">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y162">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="Z162">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="AA162">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AB162">
-        <v>2.5</v>
+        <v>3.73</v>
       </c>
       <c r="AC162">
+        <v>1.69</v>
+      </c>
+      <c r="AD162">
         <v>2.15</v>
       </c>
-      <c r="AD162">
-        <v>1.68</v>
-      </c>
       <c r="AE162">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="AF162">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AG162">
-        <v>2.69</v>
+        <v>2.9</v>
       </c>
       <c r="AH162" t="inlineStr">
         <is>
@@ -26785,10 +26785,10 @@
         </is>
       </c>
       <c r="AJ162">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AK162">
-        <v>1.73</v>
+        <v>2.63</v>
       </c>
       <c r="AL162">
         <v>0</v>
@@ -29984,7 +29984,7 @@
         <v>2.9</v>
       </c>
       <c r="Q182">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R182">
         <v>1.8</v>
@@ -29996,7 +29996,7 @@
         <v>2.09</v>
       </c>
       <c r="U182">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="V182">
         <v>1.16</v>
@@ -30020,7 +30020,7 @@
         <v>1.31</v>
       </c>
       <c r="AC182">
-        <v>6.1</v>
+        <v>6.05</v>
       </c>
       <c r="AD182">
         <v>1.11</v>
@@ -30316,7 +30316,7 @@
         <v>1.81</v>
       </c>
       <c r="S184">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="T184">
         <v>2.04</v>
@@ -30355,10 +30355,10 @@
         <v>1.03</v>
       </c>
       <c r="AF184">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AG184">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AH184" t="inlineStr">
         <is>
@@ -32583,28 +32583,28 @@
         </is>
       </c>
       <c r="N198">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="O198">
         <v>3.3</v>
       </c>
       <c r="P198">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="Q198">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="R198">
         <v>2.1</v>
       </c>
       <c r="S198">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T198">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="U198">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="V198">
         <v>1.39</v>
@@ -32613,25 +32613,25 @@
         <v>1.05</v>
       </c>
       <c r="X198">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y198">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z198">
-        <v>3.48</v>
+        <v>3.35</v>
       </c>
       <c r="AA198">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB198">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC198">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="AD198">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AE198">
         <v>1.06</v>
@@ -32656,7 +32656,7 @@
         <v>1.25</v>
       </c>
       <c r="AK198">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL198">
         <v>0</v>
@@ -32755,28 +32755,28 @@
         <v>6.22</v>
       </c>
       <c r="Q199">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="R199">
         <v>2.25</v>
       </c>
       <c r="S199">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T199">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="U199">
         <v>2.77</v>
       </c>
       <c r="V199">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W199">
         <v>1.06</v>
       </c>
       <c r="X199">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y199">
         <v>1.25</v>
@@ -32788,16 +32788,16 @@
         <v>1.91</v>
       </c>
       <c r="AB199">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AC199">
         <v>3.3</v>
       </c>
       <c r="AD199">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE199">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF199">
         <v>1.93</v>
@@ -32819,7 +32819,7 @@
         <v>1.25</v>
       </c>
       <c r="AK199">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AL199">
         <v>0</v>
@@ -32918,56 +32918,56 @@
         <v>4.17</v>
       </c>
       <c r="Q200">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="R200">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="S200">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T200">
         <v>2.85</v>
       </c>
       <c r="U200">
-        <v>2.84</v>
+        <v>2.69</v>
       </c>
       <c r="V200">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W200">
         <v>1.08</v>
       </c>
       <c r="X200">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y200">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z200">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA200">
+        <v>1.93</v>
+      </c>
+      <c r="AB200">
         <v>1.85</v>
       </c>
-      <c r="AB200">
+      <c r="AC200">
+        <v>3.1</v>
+      </c>
+      <c r="AD200">
+        <v>1.34</v>
+      </c>
+      <c r="AE200">
+        <v>1.1</v>
+      </c>
+      <c r="AF200">
+        <v>1.8</v>
+      </c>
+      <c r="AG200">
         <v>1.91</v>
       </c>
-      <c r="AC200">
-        <v>3.05</v>
-      </c>
-      <c r="AD200">
-        <v>1.29</v>
-      </c>
-      <c r="AE200">
-        <v>1.07</v>
-      </c>
-      <c r="AF200">
-        <v>1.81</v>
-      </c>
-      <c r="AG200">
-        <v>1.87</v>
-      </c>
       <c r="AH200" t="inlineStr">
         <is>
           <t>[]</t>
@@ -32979,10 +32979,10 @@
         </is>
       </c>
       <c r="AJ200">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK200">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AL200">
         <v>0</v>
@@ -33072,13 +33072,13 @@
         </is>
       </c>
       <c r="N201">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="O201">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P201">
-        <v>4.2</v>
+        <v>4.73</v>
       </c>
       <c r="Q201">
         <v>0</v>
@@ -33235,31 +33235,31 @@
         </is>
       </c>
       <c r="N202">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="O202">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="P202">
         <v>4.1</v>
       </c>
       <c r="Q202">
-        <v>2.72</v>
+        <v>2.48</v>
       </c>
       <c r="R202">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="S202">
         <v>1.51</v>
       </c>
       <c r="T202">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="U202">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="V202">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="W202">
         <v>1.05</v>
@@ -33271,28 +33271,28 @@
         <v>1.37</v>
       </c>
       <c r="Z202">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AA202">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="AB202">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AC202">
-        <v>4.45</v>
+        <v>4.33</v>
       </c>
       <c r="AD202">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AE202">
         <v>1.03</v>
       </c>
       <c r="AF202">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="AG202">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AH202" t="inlineStr">
         <is>
@@ -33305,10 +33305,10 @@
         </is>
       </c>
       <c r="AJ202">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AK202">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AL202">
         <v>0</v>
@@ -33398,64 +33398,64 @@
         </is>
       </c>
       <c r="N203">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="O203">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="P203">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="Q203">
-        <v>2.71</v>
+        <v>2.66</v>
       </c>
       <c r="R203">
         <v>2.05</v>
       </c>
       <c r="S203">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="T203">
-        <v>2.54</v>
+        <v>2.41</v>
       </c>
       <c r="U203">
-        <v>3.2</v>
+        <v>2.91</v>
       </c>
       <c r="V203">
         <v>1.3</v>
       </c>
       <c r="W203">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X203">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y203">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Z203">
         <v>2.95</v>
       </c>
       <c r="AA203">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AB203">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AC203">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="AD203">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AE203">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF203">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AG203">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AH203" t="inlineStr">
         <is>
@@ -33468,10 +33468,10 @@
         </is>
       </c>
       <c r="AJ203">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK203">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AL203">
         <v>0</v>
@@ -33564,10 +33564,10 @@
         <v>2.22</v>
       </c>
       <c r="O204">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P204">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="Q204">
         <v>2.75</v>
@@ -33588,7 +33588,7 @@
         <v>1.42</v>
       </c>
       <c r="W204">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X204">
         <v>1.05</v>
@@ -33615,7 +33615,7 @@
         <v>1.1</v>
       </c>
       <c r="AF204">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG204">
         <v>2</v>
@@ -33634,7 +33634,7 @@
         <v>1.25</v>
       </c>
       <c r="AK204">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL204">
         <v>0</v>
@@ -34216,10 +34216,10 @@
         <v>2.3</v>
       </c>
       <c r="O208">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="P208">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q208">
         <v>3.22</v>
@@ -34283,7 +34283,7 @@
         </is>
       </c>
       <c r="AJ208">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AK208">
         <v>1.5</v>
@@ -36211,7 +36211,7 @@
         <v>2.32</v>
       </c>
       <c r="AB220">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AC220">
         <v>4.6</v>
@@ -36226,7 +36226,7 @@
         <v>2.05</v>
       </c>
       <c r="AG220">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AH220" t="inlineStr">
         <is>
@@ -36332,13 +36332,13 @@
         </is>
       </c>
       <c r="N221">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="O221">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P221">
-        <v>2.72</v>
+        <v>2.96</v>
       </c>
       <c r="Q221">
         <v>0</v>
@@ -36568,7 +36568,7 @@
         <v>1.19</v>
       </c>
       <c r="AK222">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AL222">
         <v>0</v>
@@ -36952,12 +36952,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G225">
@@ -36984,64 +36984,64 @@
         </is>
       </c>
       <c r="N225">
-        <v>1.91</v>
+        <v>3.75</v>
       </c>
       <c r="O225">
-        <v>3.55</v>
+        <v>3.33</v>
       </c>
       <c r="P225">
-        <v>3.7</v>
+        <v>2.05</v>
       </c>
       <c r="Q225">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R225">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S225">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T225">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U225">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="V225">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W225">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X225">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y225">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z225">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA225">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AB225">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AC225">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AD225">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE225">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF225">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG225">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH225" t="inlineStr">
         <is>
@@ -37054,10 +37054,10 @@
         </is>
       </c>
       <c r="AJ225">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK225">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AL225">
         <v>0</v>
@@ -37115,12 +37115,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G226">
@@ -37147,64 +37147,64 @@
         </is>
       </c>
       <c r="N226">
-        <v>3.75</v>
+        <v>1.86</v>
       </c>
       <c r="O226">
-        <v>3.33</v>
+        <v>3.64</v>
       </c>
       <c r="P226">
-        <v>2.05</v>
+        <v>4.06</v>
       </c>
       <c r="Q226">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R226">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S226">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T226">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U226">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V226">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W226">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X226">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y226">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z226">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA226">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AB226">
+        <v>1.85</v>
+      </c>
+      <c r="AC226">
+        <v>3.25</v>
+      </c>
+      <c r="AD226">
+        <v>1.33</v>
+      </c>
+      <c r="AE226">
+        <v>1.11</v>
+      </c>
+      <c r="AF226">
         <v>1.7</v>
       </c>
-      <c r="AC226">
-        <v>0</v>
-      </c>
-      <c r="AD226">
-        <v>0</v>
-      </c>
-      <c r="AE226">
-        <v>0</v>
-      </c>
-      <c r="AF226">
-        <v>0</v>
-      </c>
       <c r="AG226">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH226" t="inlineStr">
         <is>
@@ -37217,10 +37217,10 @@
         </is>
       </c>
       <c r="AJ226">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK226">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AL226">
         <v>0</v>
@@ -37319,16 +37319,16 @@
         <v>3.55</v>
       </c>
       <c r="Q227">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="R227">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="S227">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="T227">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="U227">
         <v>3.75</v>
@@ -37340,34 +37340,34 @@
         <v>1.04</v>
       </c>
       <c r="X227">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y227">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="Z227">
-        <v>2.55</v>
+        <v>2.36</v>
       </c>
       <c r="AA227">
         <v>2.53</v>
       </c>
       <c r="AB227">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AC227">
         <v>5.75</v>
       </c>
       <c r="AD227">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AE227">
         <v>1.01</v>
       </c>
       <c r="AF227">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AG227">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AH227" t="inlineStr">
         <is>
@@ -37476,28 +37476,28 @@
         <v>2.16</v>
       </c>
       <c r="O228">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="P228">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q228">
         <v>2.8</v>
       </c>
       <c r="R228">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="S228">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="T228">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="U228">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="V228">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W228">
         <v>1.05</v>
@@ -37512,13 +37512,13 @@
         <v>2.7</v>
       </c>
       <c r="AA228">
-        <v>2.23</v>
+        <v>2.45</v>
       </c>
       <c r="AB228">
         <v>1.62</v>
       </c>
       <c r="AC228">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AD228">
         <v>1.15</v>
@@ -37527,10 +37527,10 @@
         <v>1.02</v>
       </c>
       <c r="AF228">
+        <v>1.87</v>
+      </c>
+      <c r="AG228">
         <v>1.8</v>
-      </c>
-      <c r="AG228">
-        <v>1.85</v>
       </c>
       <c r="AH228" t="inlineStr">
         <is>
@@ -37965,19 +37965,19 @@
         <v>3.1</v>
       </c>
       <c r="O231">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="P231">
         <v>2.4</v>
       </c>
       <c r="Q231">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="R231">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="S231">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="T231">
         <v>2.29</v>
@@ -37989,13 +37989,13 @@
         <v>1.29</v>
       </c>
       <c r="W231">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X231">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Y231">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="Z231">
         <v>2.34</v>
@@ -38004,22 +38004,22 @@
         <v>2.59</v>
       </c>
       <c r="AB231">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AC231">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="AD231">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AE231">
         <v>1.02</v>
       </c>
       <c r="AF231">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AG231">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AH231" t="inlineStr">
         <is>
@@ -38032,7 +38032,7 @@
         </is>
       </c>
       <c r="AJ231">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK231">
         <v>1.33</v>
@@ -38125,13 +38125,13 @@
         </is>
       </c>
       <c r="N232">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="O232">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="P232">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q232">
         <v>3.03</v>
@@ -38146,10 +38146,10 @@
         <v>2.85</v>
       </c>
       <c r="U232">
-        <v>2.76</v>
+        <v>2.62</v>
       </c>
       <c r="V232">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="W232">
         <v>1.08</v>
@@ -38164,13 +38164,13 @@
         <v>3.68</v>
       </c>
       <c r="AA232">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AB232">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AC232">
-        <v>3.15</v>
+        <v>2.97</v>
       </c>
       <c r="AD232">
         <v>1.3</v>
@@ -38179,7 +38179,7 @@
         <v>1.08</v>
       </c>
       <c r="AF232">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG232">
         <v>2</v>
@@ -38195,7 +38195,7 @@
         </is>
       </c>
       <c r="AJ232">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AK232">
         <v>1.53</v>
@@ -38288,28 +38288,28 @@
         </is>
       </c>
       <c r="N233">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="O233">
-        <v>3.95</v>
+        <v>3.98</v>
       </c>
       <c r="P233">
-        <v>3.9</v>
+        <v>3.83</v>
       </c>
       <c r="Q233">
         <v>2</v>
       </c>
       <c r="R233">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="S233">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T233">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U233">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="V233">
         <v>1.63</v>
@@ -38318,34 +38318,34 @@
         <v>1.14</v>
       </c>
       <c r="X233">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y233">
         <v>1.14</v>
       </c>
       <c r="Z233">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AA233">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AB233">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="AC233">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AD233">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AE233">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AF233">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG233">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AH233" t="inlineStr">
         <is>
@@ -38358,7 +38358,7 @@
         </is>
       </c>
       <c r="AJ233">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK233">
         <v>2.15</v>
@@ -38777,7 +38777,7 @@
         </is>
       </c>
       <c r="N236">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="O236">
         <v>3.7</v>
@@ -38798,10 +38798,10 @@
         <v>2.7</v>
       </c>
       <c r="U236">
-        <v>2.78</v>
+        <v>2.93</v>
       </c>
       <c r="V236">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W236">
         <v>1.06</v>
@@ -38816,10 +38816,10 @@
         <v>3.31</v>
       </c>
       <c r="AA236">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AB236">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AC236">
         <v>3.45</v>
@@ -38834,7 +38834,7 @@
         <v>1.95</v>
       </c>
       <c r="AG236">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH236" t="inlineStr">
         <is>

--- a/jogos_2026-08-23.xlsx
+++ b/jogos_2026-08-23.xlsx
@@ -1613,34 +1613,34 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X8">
         <v>0</v>
@@ -1667,10 +1667,10 @@
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -3928,10 +3928,10 @@
         <v>1.07</v>
       </c>
       <c r="Y22">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Z22">
-        <v>2.73</v>
+        <v>2.89</v>
       </c>
       <c r="AA22">
         <v>2.14</v>
@@ -3949,7 +3949,7 @@
         <v>1.02</v>
       </c>
       <c r="AF22">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AG22">
         <v>1.72</v>
@@ -3968,7 +3968,7 @@
         <v>1.2</v>
       </c>
       <c r="AK22">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="O27">
-        <v>3.58</v>
+        <v>3.55</v>
       </c>
       <c r="P27">
-        <v>4.17</v>
+        <v>4.3</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="O28">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="P28">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC28">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="AD28">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -8142,7 +8142,7 @@
         <v>2.7</v>
       </c>
       <c r="Q48">
-        <v>3.32</v>
+        <v>3.36</v>
       </c>
       <c r="R48">
         <v>1.9</v>
@@ -8175,7 +8175,7 @@
         <v>2.27</v>
       </c>
       <c r="AB48">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AC48">
         <v>4.18</v>
@@ -9763,7 +9763,7 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="O58">
         <v>3.15</v>
@@ -9772,7 +9772,7 @@
         <v>2.35</v>
       </c>
       <c r="Q58">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="R58">
         <v>1.96</v>
@@ -9802,16 +9802,16 @@
         <v>2.62</v>
       </c>
       <c r="AA58">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="AB58">
         <v>1.58</v>
       </c>
       <c r="AC58">
-        <v>4.38</v>
+        <v>4.43</v>
       </c>
       <c r="AD58">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AE58">
         <v>1.01</v>
@@ -21010,13 +21010,13 @@
         </is>
       </c>
       <c r="N127">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O127">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P127">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q127">
         <v>0</v>
@@ -21173,13 +21173,13 @@
         </is>
       </c>
       <c r="N128">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O128">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P128">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="Q128">
         <v>0</v>
@@ -21508,13 +21508,13 @@
         <v>2.68</v>
       </c>
       <c r="Q130">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="R130">
         <v>2.19</v>
       </c>
       <c r="S130">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T130">
         <v>3.12</v>
@@ -21556,7 +21556,7 @@
         <v>1.53</v>
       </c>
       <c r="AG130">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -23455,13 +23455,13 @@
         </is>
       </c>
       <c r="N142">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O142">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P142">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q142">
         <v>0</v>
@@ -24605,10 +24605,10 @@
         <v>0</v>
       </c>
       <c r="Q149">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="R149">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="S149">
         <v>1.34</v>
@@ -24617,7 +24617,7 @@
         <v>2.83</v>
       </c>
       <c r="U149">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="V149">
         <v>1.36</v>
@@ -24666,10 +24666,10 @@
         </is>
       </c>
       <c r="AJ149">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="AK149">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AL149">
         <v>0</v>
